--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -439,7 +439,7 @@
     <t>2021-04-20</t>
   </si>
   <si>
-    <t>2021-05-11</t>
+    <t>2021-05-12</t>
   </si>
   <si>
     <t>2021-07-09</t>
@@ -748,10 +748,10 @@
     <t>2021-04-28</t>
   </si>
   <si>
-    <t>2021-06-16</t>
+    <t>2021-05-31</t>
   </si>
   <si>
-    <t>2021-07-20</t>
+    <t>2021-07-22</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -36099,40 +36099,40 @@
         <v>141</v>
       </c>
       <c r="C695">
-        <v>2.896153804967225</v>
+        <v>3.006935468331325</v>
       </c>
       <c r="D695" t="s">
         <v>244</v>
       </c>
       <c r="E695">
-        <v>2.453793284427995</v>
+        <v>2.555888073696882</v>
       </c>
       <c r="F695">
         <v>-1</v>
       </c>
       <c r="G695">
-        <v>0.008663846195032776</v>
+        <v>0.008693064531668675</v>
       </c>
       <c r="H695">
-        <v>0.007126206715572005</v>
+        <v>0.007904111926303119</v>
       </c>
       <c r="I695">
-        <v>0.4423605205392307</v>
+        <v>0.4510473946344429</v>
       </c>
       <c r="J695">
         <v>0.5825951909157121</v>
       </c>
       <c r="K695">
-        <v>4.95</v>
+        <v>4.88</v>
       </c>
       <c r="L695">
-        <v>5.78</v>
+        <v>5.85</v>
       </c>
       <c r="M695">
-        <v>4.01</v>
+        <v>4.59</v>
       </c>
       <c r="N695">
-        <v>4.79</v>
+        <v>5.23</v>
       </c>
       <c r="O695">
         <v>1</v>
@@ -36155,7 +36155,7 @@
         <v>245</v>
       </c>
       <c r="E696">
-        <v>3.013365929424353</v>
+        <v>3.251198093512282</v>
       </c>
       <c r="F696">
         <v>-1</v>
@@ -36164,10 +36164,10 @@
         <v>0.008580719541576375</v>
       </c>
       <c r="H696">
-        <v>0.008326634070575647</v>
+        <v>0.009088801906487717</v>
       </c>
       <c r="I696">
-        <v>0.1259145289992718</v>
+        <v>-0.1119176350886577</v>
       </c>
       <c r="J696">
         <v>0.5825951909157121</v>
@@ -36179,10 +36179,10 @@
         <v>5.86</v>
       </c>
       <c r="M696">
-        <v>4.56</v>
+        <v>5.01</v>
       </c>
       <c r="N696">
-        <v>5.67</v>
+        <v>6.17</v>
       </c>
       <c r="O696">
         <v>1</v>
@@ -36205,7 +36205,7 @@
         <v>245</v>
       </c>
       <c r="E697">
-        <v>3.013365929424353</v>
+        <v>3.251198093512282</v>
       </c>
       <c r="F697">
         <v>-1</v>
@@ -36214,10 +36214,10 @@
         <v>0.00824080811866649</v>
       </c>
       <c r="H697">
-        <v>0.008326634070575647</v>
+        <v>0.009088801906487717</v>
       </c>
       <c r="I697">
-        <v>-0.07417404809084305</v>
+        <v>-0.3120062121787726</v>
       </c>
       <c r="J697">
         <v>0.5825951909157121</v>
@@ -36229,10 +36229,10 @@
         <v>5.59</v>
       </c>
       <c r="M697">
-        <v>4.56</v>
+        <v>5.01</v>
       </c>
       <c r="N697">
-        <v>5.67</v>
+        <v>6.17</v>
       </c>
       <c r="O697">
         <v>1</v>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -751,7 +751,7 @@
     <t>2021-05-31</t>
   </si>
   <si>
-    <t>2021-07-22</t>
+    <t>2021-07-23</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -36155,7 +36155,7 @@
         <v>245</v>
       </c>
       <c r="E696">
-        <v>3.251198093512282</v>
+        <v>3.460239275967954</v>
       </c>
       <c r="F696">
         <v>-1</v>
@@ -36164,10 +36164,10 @@
         <v>0.008580719541576375</v>
       </c>
       <c r="H696">
-        <v>0.009088801906487717</v>
+        <v>0.009099760724032046</v>
       </c>
       <c r="I696">
-        <v>-0.1119176350886577</v>
+        <v>-0.3209588175443292</v>
       </c>
       <c r="J696">
         <v>0.5825951909157121</v>
@@ -36179,10 +36179,10 @@
         <v>5.86</v>
       </c>
       <c r="M696">
-        <v>5.01</v>
+        <v>4.84</v>
       </c>
       <c r="N696">
-        <v>6.17</v>
+        <v>6.28</v>
       </c>
       <c r="O696">
         <v>1</v>
@@ -36205,7 +36205,7 @@
         <v>245</v>
       </c>
       <c r="E697">
-        <v>3.251198093512282</v>
+        <v>3.460239275967954</v>
       </c>
       <c r="F697">
         <v>-1</v>
@@ -36214,10 +36214,10 @@
         <v>0.00824080811866649</v>
       </c>
       <c r="H697">
-        <v>0.009088801906487717</v>
+        <v>0.009099760724032046</v>
       </c>
       <c r="I697">
-        <v>-0.3120062121787726</v>
+        <v>-0.521047394634444</v>
       </c>
       <c r="J697">
         <v>0.5825951909157121</v>
@@ -36229,10 +36229,10 @@
         <v>5.59</v>
       </c>
       <c r="M697">
-        <v>5.01</v>
+        <v>4.84</v>
       </c>
       <c r="N697">
-        <v>6.17</v>
+        <v>6.28</v>
       </c>
       <c r="O697">
         <v>1</v>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -445,7 +445,7 @@
     <t>2021-07-09</t>
   </si>
   <si>
-    <t>2021-07-15</t>
+    <t>2021-07-16</t>
   </si>
   <si>
     <t>2017-04-20</t>
@@ -751,7 +751,7 @@
     <t>2021-05-31</t>
   </si>
   <si>
-    <t>2021-07-23</t>
+    <t>2021-07-29</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -36155,7 +36155,7 @@
         <v>245</v>
       </c>
       <c r="E696">
-        <v>3.460239275967954</v>
+        <v>2.942584266060253</v>
       </c>
       <c r="F696">
         <v>-1</v>
@@ -36164,10 +36164,10 @@
         <v>0.008580719541576375</v>
       </c>
       <c r="H696">
-        <v>0.009099760724032046</v>
+        <v>0.008337415733939747</v>
       </c>
       <c r="I696">
-        <v>-0.3209588175443292</v>
+        <v>0.1966961923633721</v>
       </c>
       <c r="J696">
         <v>0.5825951909157121</v>
@@ -36179,10 +36179,10 @@
         <v>5.86</v>
       </c>
       <c r="M696">
-        <v>4.84</v>
+        <v>4.63</v>
       </c>
       <c r="N696">
-        <v>6.28</v>
+        <v>5.64</v>
       </c>
       <c r="O696">
         <v>1</v>
@@ -36199,40 +36199,40 @@
         <v>143</v>
       </c>
       <c r="C697">
-        <v>2.93919188133351</v>
+        <v>3.093454506514468</v>
       </c>
       <c r="D697" t="s">
         <v>245</v>
       </c>
       <c r="E697">
-        <v>3.460239275967954</v>
+        <v>2.942584266060253</v>
       </c>
       <c r="F697">
         <v>-1</v>
       </c>
       <c r="G697">
-        <v>0.00824080811866649</v>
+        <v>0.008546545493485533</v>
       </c>
       <c r="H697">
-        <v>0.009099760724032046</v>
+        <v>0.008337415733939747</v>
       </c>
       <c r="I697">
-        <v>-0.521047394634444</v>
+        <v>0.150870240454215</v>
       </c>
       <c r="J697">
         <v>0.5825951909157121</v>
       </c>
       <c r="K697">
-        <v>4.55</v>
+        <v>4.68</v>
       </c>
       <c r="L697">
-        <v>5.59</v>
+        <v>5.82</v>
       </c>
       <c r="M697">
-        <v>4.84</v>
+        <v>4.63</v>
       </c>
       <c r="N697">
-        <v>6.28</v>
+        <v>5.64</v>
       </c>
       <c r="O697">
         <v>1</v>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -751,7 +751,7 @@
     <t>2021-05-31</t>
   </si>
   <si>
-    <t>2021-07-29</t>
+    <t>2021-07-30</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -36155,7 +36155,7 @@
         <v>245</v>
       </c>
       <c r="E696">
-        <v>2.942584266060253</v>
+        <v>3.208498795059524</v>
       </c>
       <c r="F696">
         <v>-1</v>
@@ -36164,10 +36164,10 @@
         <v>0.008580719541576375</v>
       </c>
       <c r="H696">
-        <v>0.008337415733939747</v>
+        <v>0.008731501204940475</v>
       </c>
       <c r="I696">
-        <v>0.1966961923633721</v>
+        <v>-0.06921833663589938</v>
       </c>
       <c r="J696">
         <v>0.5825951909157121</v>
@@ -36179,10 +36179,10 @@
         <v>5.86</v>
       </c>
       <c r="M696">
-        <v>4.63</v>
+        <v>4.74</v>
       </c>
       <c r="N696">
-        <v>5.64</v>
+        <v>5.97</v>
       </c>
       <c r="O696">
         <v>1</v>
@@ -36205,7 +36205,7 @@
         <v>245</v>
       </c>
       <c r="E697">
-        <v>2.942584266060253</v>
+        <v>3.208498795059524</v>
       </c>
       <c r="F697">
         <v>-1</v>
@@ -36214,10 +36214,10 @@
         <v>0.008546545493485533</v>
       </c>
       <c r="H697">
-        <v>0.008337415733939747</v>
+        <v>0.008731501204940475</v>
       </c>
       <c r="I697">
-        <v>0.150870240454215</v>
+        <v>-0.1150442885450564</v>
       </c>
       <c r="J697">
         <v>0.5825951909157121</v>
@@ -36229,10 +36229,10 @@
         <v>5.82</v>
       </c>
       <c r="M697">
-        <v>4.63</v>
+        <v>4.74</v>
       </c>
       <c r="N697">
-        <v>5.64</v>
+        <v>5.97</v>
       </c>
       <c r="O697">
         <v>1</v>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="341">
   <si>
     <t>trade_time</t>
   </si>
@@ -448,6 +448,9 @@
     <t>2021-07-16</t>
   </si>
   <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
     <t>2017-04-20</t>
   </si>
   <si>
@@ -751,7 +754,7 @@
     <t>2021-05-31</t>
   </si>
   <si>
-    <t>2021-07-30</t>
+    <t>2021-08-04</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -1391,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P697"/>
+  <dimension ref="A1:P698"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1452,7 +1455,7 @@
         <v>1.855441043116508</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E2">
         <v>1.575397067571232</v>
@@ -1488,7 +1491,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1502,7 +1505,7 @@
         <v>1.844886436180541</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E3">
         <v>1.575397067571232</v>
@@ -1538,7 +1541,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1552,7 +1555,7 @@
         <v>1.879543169394645</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E4">
         <v>1.575397067571232</v>
@@ -1588,7 +1591,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1602,7 +1605,7 @@
         <v>1.931893523774336</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E5">
         <v>1.575397067571232</v>
@@ -1638,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1652,7 +1655,7 @@
         <v>1.864287853699299</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E6">
         <v>1.610229702966436</v>
@@ -1688,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1702,7 +1705,7 @@
         <v>1.420828285447678</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E7">
         <v>1.720097776330612</v>
@@ -1738,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1752,7 +1755,7 @@
         <v>1.444930411725815</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E8">
         <v>1.720097776330612</v>
@@ -1788,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1802,7 +1805,7 @@
         <v>1.415528994207057</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E9">
         <v>1.720097776330612</v>
@@ -1838,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1852,7 +1855,7 @@
         <v>1.417747421950922</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E10">
         <v>1.720097776330612</v>
@@ -1888,7 +1891,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1902,7 +1905,7 @@
         <v>1.837391318446252</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E11">
         <v>1.556576374761795</v>
@@ -1938,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1952,7 +1955,7 @@
         <v>1.827426275381424</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E12">
         <v>1.556576374761795</v>
@@ -1988,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2002,7 +2005,7 @@
         <v>1.861221338322326</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E13">
         <v>1.556576374761795</v>
@@ -2038,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2052,7 +2055,7 @@
         <v>1.913526341635005</v>
       </c>
       <c r="D14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E14">
         <v>1.556576374761795</v>
@@ -2088,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2102,7 +2105,7 @@
         <v>1.84664628863214</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E15">
         <v>1.593631212440523</v>
@@ -2138,7 +2141,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2152,7 +2155,7 @@
         <v>1.404411199189807</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E16">
         <v>1.701186381387154</v>
@@ -2188,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2202,7 +2205,7 @@
         <v>1.428241219065881</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E17">
         <v>1.701186381387154</v>
@@ -2238,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2252,7 +2255,7 @@
         <v>1.399021205815165</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E18">
         <v>1.701186381387154</v>
@@ -2288,7 +2291,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2302,7 +2305,7 @@
         <v>1.398881378074474</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E19">
         <v>1.701186381387154</v>
@@ -2338,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2352,7 +2355,7 @@
         <v>1.772601053603223</v>
       </c>
       <c r="D20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E20">
         <v>1.513212850115657</v>
@@ -2388,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2402,7 +2405,7 @@
         <v>1.819007208305362</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E21">
         <v>1.513212850115657</v>
@@ -2438,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2452,7 +2455,7 @@
         <v>1.871207721197208</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E22">
         <v>1.513212850115657</v>
@@ -2488,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2502,7 +2505,7 @@
         <v>1.805999514927688</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23">
         <v>1.555387718415254</v>
@@ -2538,7 +2541,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2552,7 +2555,7 @@
         <v>1.366585666847875</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E24">
         <v>1.657613875899347</v>
@@ -2588,7 +2591,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2602,7 +2605,7 @@
         <v>1.360986692631565</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E25">
         <v>1.657613875899347</v>
@@ -2638,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2652,7 +2655,7 @@
         <v>1.355413363007501</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E26">
         <v>1.657613875899347</v>
@@ -2688,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2702,7 +2705,7 @@
         <v>1.746707087766096</v>
       </c>
       <c r="D27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E27">
         <v>1.485799595466657</v>
@@ -2738,7 +2741,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2752,7 +2755,7 @@
         <v>1.792320570044649</v>
       </c>
       <c r="D28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E28">
         <v>1.485799595466657</v>
@@ -2788,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2802,7 +2805,7 @@
         <v>1.780303717196457</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E29">
         <v>1.531211209495895</v>
@@ -2838,7 +2841,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2852,7 +2855,7 @@
         <v>1.342673382069711</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E30">
         <v>1.63006850917975</v>
@@ -2888,7 +2891,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2902,7 +2905,7 @@
         <v>1.336942295782803</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E31">
         <v>1.63006850917975</v>
@@ -2938,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2952,7 +2955,7 @@
         <v>1.327934052323203</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E32">
         <v>1.63006850917975</v>
@@ -2988,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3002,7 +3005,7 @@
         <v>1.724897025074506</v>
       </c>
       <c r="D33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E33">
         <v>1.462709860729388</v>
@@ -3038,7 +3041,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3052,7 +3055,7 @@
         <v>1.713714740951758</v>
       </c>
       <c r="D34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E34">
         <v>1.462709860729388</v>
@@ -3088,7 +3091,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3102,7 +3105,7 @@
         <v>1.769842852372705</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E35">
         <v>1.462709860729388</v>
@@ -3138,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3152,7 +3155,7 @@
         <v>1.758660568249956</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36">
         <v>1.510847732595075</v>
@@ -3188,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3202,7 +3205,7 @@
         <v>1.322532456829009</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E37">
         <v>1.606867498612421</v>
@@ -3238,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3252,7 +3255,7 @@
         <v>1.316690094712042</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E38">
         <v>1.606867498612421</v>
@@ -3288,7 +3291,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3302,7 +3305,7 @@
         <v>1.304788679670904</v>
       </c>
       <c r="D39" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E39">
         <v>1.606867498612421</v>
@@ -3338,7 +3341,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3352,7 +3355,7 @@
         <v>1.698715924927888</v>
       </c>
       <c r="D40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E40">
         <v>1.451820073210847</v>
@@ -3388,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3402,7 +3405,7 @@
         <v>1.703822090603589</v>
       </c>
       <c r="D41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E41">
         <v>1.451820073210847</v>
@@ -3438,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3452,7 +3455,7 @@
         <v>1.759241709824535</v>
       </c>
       <c r="D42" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E42">
         <v>1.451820073210847</v>
@@ -3488,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3502,7 +3505,7 @@
         <v>1.748453032479565</v>
       </c>
       <c r="D43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43">
         <v>1.501243727217277</v>
@@ -3538,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3552,7 +3555,7 @@
         <v>1.313033413258619</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E44">
         <v>1.595925230190177</v>
@@ -3588,7 +3591,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3602,7 +3605,7 @@
         <v>1.307138570237948</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E45">
         <v>1.595925230190177</v>
@@ -3638,7 +3641,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3652,7 +3655,7 @@
         <v>1.293872651700511</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E46">
         <v>1.595925230190177</v>
@@ -3688,7 +3691,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3702,7 +3705,7 @@
         <v>1.708440278144118</v>
       </c>
       <c r="D47" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E47">
         <v>1.445287539361757</v>
@@ -3752,7 +3755,7 @@
         <v>1.75288232747506</v>
       </c>
       <c r="D48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E48">
         <v>1.445287539361757</v>
@@ -3802,7 +3805,7 @@
         <v>1.742329765811383</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49">
         <v>1.495482504593743</v>
@@ -3852,7 +3855,7 @@
         <v>1.307335154816763</v>
       </c>
       <c r="D50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E50">
         <v>1.589361214250248</v>
@@ -3902,7 +3905,7 @@
         <v>1.301408829705253</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E51">
         <v>1.589361214250248</v>
@@ -3952,7 +3955,7 @@
         <v>1.287324376806003</v>
       </c>
       <c r="D52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E52">
         <v>1.589361214250248</v>
@@ -4002,7 +4005,7 @@
         <v>1.741577671463358</v>
       </c>
       <c r="D53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E53">
         <v>1.433675083310133</v>
@@ -4052,7 +4055,7 @@
         <v>1.793586527085793</v>
       </c>
       <c r="D54" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E54">
         <v>1.433675083310133</v>
@@ -4102,7 +4105,7 @@
         <v>1.731444837126847</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E55">
         <v>1.485241157810864</v>
@@ -4152,7 +4155,7 @@
         <v>1.297205735321128</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E56">
         <v>1.577692794555001</v>
@@ -4202,7 +4205,7 @@
         <v>1.291223446565996</v>
       </c>
       <c r="D57" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E57">
         <v>1.577692794555001</v>
@@ -4252,7 +4255,7 @@
         <v>1.275683938932566</v>
       </c>
       <c r="D58" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E58">
         <v>1.577692794555001</v>
@@ -4352,7 +4355,7 @@
         <v>1.725587143730334</v>
       </c>
       <c r="D60" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E60">
         <v>1.417249169921011</v>
@@ -4402,7 +4405,7 @@
         <v>1.777556418838578</v>
       </c>
       <c r="D61" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E61">
         <v>1.417249169921011</v>
@@ -4452,7 +4455,7 @@
         <v>1.716048017106683</v>
       </c>
       <c r="D62" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E62">
         <v>1.470754689617085</v>
@@ -4502,7 +4505,7 @@
         <v>1.282877589184112</v>
       </c>
       <c r="D63" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E63">
         <v>1.561187720137498</v>
@@ -4552,7 +4555,7 @@
         <v>1.276816139400598</v>
       </c>
       <c r="D64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E64">
         <v>1.561187720137498</v>
@@ -4602,7 +4605,7 @@
         <v>1.259218445029255</v>
       </c>
       <c r="D65" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E65">
         <v>1.561187720137498</v>
@@ -4652,7 +4655,7 @@
         <v>1.799190602173319</v>
       </c>
       <c r="D66" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E66">
         <v>1.767682200441425</v>
@@ -4702,7 +4705,7 @@
         <v>1.704528128435052</v>
       </c>
       <c r="D67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E67">
         <v>1.395616765595412</v>
@@ -4738,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4752,7 +4755,7 @@
         <v>1.756445277267813</v>
       </c>
       <c r="D68" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E68">
         <v>1.395616765595412</v>
@@ -4788,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4802,7 +4805,7 @@
         <v>1.695770895943651</v>
       </c>
       <c r="D69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E69">
         <v>1.451676472790171</v>
@@ -4838,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4852,7 +4855,7 @@
         <v>1.264007877459131</v>
       </c>
       <c r="D70" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E70">
         <v>1.539451063260933</v>
@@ -4888,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4902,7 +4905,7 @@
         <v>1.257842175124651</v>
       </c>
       <c r="D71" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E71">
         <v>1.539451063260933</v>
@@ -4938,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4952,7 +4955,7 @@
         <v>1.237533914428172</v>
       </c>
       <c r="D72" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E72">
         <v>1.539451063260933</v>
@@ -4988,7 +4991,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5038,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5052,7 +5055,7 @@
         <v>1.678683818930752</v>
       </c>
       <c r="D74" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E74">
         <v>1.369068774396689</v>
@@ -5088,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5102,7 +5105,7 @@
         <v>1.730536996700383</v>
       </c>
       <c r="D75" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E75">
         <v>1.369068774396689</v>
@@ -5138,7 +5141,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5152,7 +5155,7 @@
         <v>1.670886152386294</v>
       </c>
       <c r="D76" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E76">
         <v>1.428263063684791</v>
@@ -5188,7 +5191,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5202,7 +5205,7 @@
         <v>1.240850352606269</v>
       </c>
       <c r="D77" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E77">
         <v>1.51277512993595</v>
@@ -5238,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5252,7 +5255,7 @@
         <v>1.234556708145529</v>
       </c>
       <c r="D78" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E78">
         <v>1.51277512993595</v>
@@ -5288,7 +5291,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5302,7 +5305,7 @@
         <v>1.210921952166319</v>
       </c>
       <c r="D79" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E79">
         <v>1.51277512993595</v>
@@ -5338,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5352,7 +5355,7 @@
         <v>1.661963549027058</v>
       </c>
       <c r="D80" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E80">
         <v>1.351893249619379</v>
@@ -5388,7 +5391,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5402,7 +5405,7 @@
         <v>1.713775339989997</v>
       </c>
       <c r="D81" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E81">
         <v>1.351893249619379</v>
@@ -5438,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5452,7 +5455,7 @@
         <v>1.654786684582984</v>
       </c>
       <c r="D82" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E82">
         <v>1.413115492435404</v>
@@ -5488,7 +5491,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5502,7 +5505,7 @@
         <v>1.225868328583652</v>
       </c>
       <c r="D83" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E83">
         <v>1.495516831545256</v>
@@ -5538,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5552,7 +5555,7 @@
         <v>1.219491910509528</v>
       </c>
       <c r="D84" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E84">
         <v>1.495516831545256</v>
@@ -5588,7 +5591,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5602,7 +5605,7 @@
         <v>1.193705040582317</v>
       </c>
       <c r="D85" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E85">
         <v>1.495516831545256</v>
@@ -5638,7 +5641,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5652,7 +5655,7 @@
         <v>1.600429769178104</v>
       </c>
       <c r="D86" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E86">
         <v>1.338006244585976</v>
@@ -5688,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5702,7 +5705,7 @@
         <v>1.648444633283697</v>
       </c>
       <c r="D87" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E87">
         <v>1.338006244585976</v>
@@ -5738,7 +5741,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5752,7 +5755,7 @@
         <v>1.700222961583904</v>
       </c>
       <c r="D88" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E88">
         <v>1.338006244585976</v>
@@ -5788,7 +5791,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5802,7 +5805,7 @@
         <v>1.641769708780589</v>
       </c>
       <c r="D89" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E89">
         <v>1.400868157875824</v>
@@ -5838,7 +5841,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5852,7 +5855,7 @@
         <v>1.213754844674996</v>
       </c>
       <c r="D90" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E90">
         <v>1.48156290118639</v>
@@ -5888,7 +5891,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5902,7 +5905,7 @@
         <v>1.20731150127541</v>
       </c>
       <c r="D91" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E91">
         <v>1.48156290118639</v>
@@ -5938,7 +5941,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5952,7 +5955,7 @@
         <v>1.179784572886182</v>
       </c>
       <c r="D92" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E92">
         <v>1.48156290118639</v>
@@ -5988,7 +5991,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6002,7 +6005,7 @@
         <v>1.642770386608872</v>
       </c>
       <c r="D93" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E93">
         <v>1.332177501095747</v>
@@ -6052,7 +6055,7 @@
         <v>1.636306139581315</v>
       </c>
       <c r="D94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E94">
         <v>1.395727627472394</v>
@@ -6102,7 +6105,7 @@
         <v>1.208670494931713</v>
       </c>
       <c r="D95" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E95">
         <v>1.475706067366088</v>
@@ -6152,7 +6155,7 @@
         <v>1.202199061202053</v>
       </c>
       <c r="D96" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E96">
         <v>1.475706067366088</v>
@@ -6202,7 +6205,7 @@
         <v>1.173941784230917</v>
       </c>
       <c r="D97" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E97">
         <v>1.475706067366088</v>
@@ -6252,7 +6255,7 @@
         <v>1.635648220856852</v>
       </c>
       <c r="D98" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E98">
         <v>1.324861414989093</v>
@@ -6288,7 +6291,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6302,7 +6305,7 @@
         <v>1.687394874868875</v>
       </c>
       <c r="D99" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E99">
         <v>1.324861414989093</v>
@@ -6338,7 +6341,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6352,7 +6355,7 @@
         <v>1.629448410676523</v>
       </c>
       <c r="D100" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E100">
         <v>1.38927536840002</v>
@@ -6388,7 +6391,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6402,7 +6405,7 @@
         <v>1.202288752351933</v>
       </c>
       <c r="D101" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E101">
         <v>1.468354723013138</v>
@@ -6438,7 +6441,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6452,7 +6455,7 @@
         <v>1.195782060375976</v>
       </c>
       <c r="D102" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E102">
         <v>1.468354723013138</v>
@@ -6488,7 +6491,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6502,7 +6505,7 @@
         <v>1.166608069001115</v>
       </c>
       <c r="D103" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E103">
         <v>1.468354723013138</v>
@@ -6538,7 +6541,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6552,7 +6555,7 @@
         <v>1.636237432923918</v>
       </c>
       <c r="D104" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E104">
         <v>1.325466669958976</v>
@@ -6588,7 +6591,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6602,7 +6605,7 @@
         <v>1.687985545381652</v>
       </c>
       <c r="D105" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E105">
         <v>1.325466669958976</v>
@@ -6638,7 +6641,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6652,7 +6655,7 @@
         <v>1.630015746057932</v>
       </c>
       <c r="D106" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E106">
         <v>1.389809159530085</v>
@@ -6688,7 +6691,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6702,7 +6705,7 @@
         <v>1.202816709699155</v>
       </c>
       <c r="D107" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E107">
         <v>1.468962894874441</v>
@@ -6738,7 +6741,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6752,7 +6755,7 @@
         <v>1.19631293461462</v>
       </c>
       <c r="D108" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E108">
         <v>1.468962894874441</v>
@@ -6788,7 +6791,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6802,7 +6805,7 @@
         <v>1.167214782416708</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E109">
         <v>1.468962894874441</v>
@@ -6838,7 +6841,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6888,7 +6891,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6902,7 +6905,7 @@
         <v>1.686969731933735</v>
       </c>
       <c r="D111" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E111">
         <v>1.32442577469753</v>
@@ -6952,7 +6955,7 @@
         <v>1.688566437853383</v>
       </c>
       <c r="D112" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E112">
         <v>1.388891165154931</v>
@@ -7002,7 +7005,7 @@
         <v>1.116820833577004</v>
       </c>
       <c r="D113" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E113">
         <v>1.46791698325029</v>
@@ -7052,7 +7055,7 @@
         <v>1.189838416471486</v>
       </c>
       <c r="D114" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E114">
         <v>1.46791698325029</v>
@@ -7102,7 +7105,7 @@
         <v>1.16617137897391</v>
       </c>
       <c r="D115" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E115">
         <v>1.46791698325029</v>
@@ -7202,7 +7205,7 @@
         <v>1.679044765444968</v>
       </c>
       <c r="D117" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E117">
         <v>1.316305130023856</v>
@@ -7238,7 +7241,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7252,7 +7255,7 @@
         <v>1.681071963371414</v>
       </c>
       <c r="D118" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E118">
         <v>1.381729343587304</v>
@@ -7288,7 +7291,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7302,7 +7305,7 @@
         <v>1.109345926913525</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E119">
         <v>1.459757202939633</v>
@@ -7338,7 +7341,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7352,7 +7355,7 @@
         <v>1.116606291492413</v>
       </c>
       <c r="D120" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E120">
         <v>1.459757202939633</v>
@@ -7388,7 +7391,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7402,7 +7405,7 @@
         <v>1.158031166481744</v>
       </c>
       <c r="D121" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E121">
         <v>1.459757202939633</v>
@@ -7438,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7452,7 +7455,7 @@
         <v>1.667785062291963</v>
       </c>
       <c r="D122" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E122">
         <v>1.323675609160295</v>
@@ -7488,7 +7491,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7538,7 +7541,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7552,7 +7555,7 @@
         <v>1.705523534148037</v>
       </c>
       <c r="D124" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E124">
         <v>1.306151805217721</v>
@@ -7588,7 +7591,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7602,7 +7605,7 @@
         <v>1.0999999749233</v>
       </c>
       <c r="D125" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E125">
         <v>1.449554946447687</v>
@@ -7638,7 +7641,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7652,7 +7655,7 @@
         <v>1.107015681073126</v>
       </c>
       <c r="D126" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E126">
         <v>1.449554946447687</v>
@@ -7688,7 +7691,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7702,7 +7705,7 @@
         <v>1.074450234602739</v>
       </c>
       <c r="D127" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E127">
         <v>1.449554946447687</v>
@@ -7738,7 +7741,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7752,7 +7755,7 @@
         <v>1.728036618426774</v>
       </c>
       <c r="D128" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E128">
         <v>1.311858607036529</v>
@@ -7788,7 +7791,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7838,7 +7841,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7852,7 +7855,7 @@
         <v>1.735732764200063</v>
       </c>
       <c r="D130" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E130">
         <v>1.301215982596513</v>
@@ -7902,7 +7905,7 @@
         <v>1.095456639402092</v>
       </c>
       <c r="D131" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E131">
         <v>1.444595336729509</v>
@@ -7952,7 +7955,7 @@
         <v>1.102353410067069</v>
       </c>
       <c r="D132" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E132">
         <v>1.444595336729509</v>
@@ -8002,7 +8005,7 @@
         <v>1.069526305530016</v>
       </c>
       <c r="D133" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E133">
         <v>1.444595336729509</v>
@@ -8102,7 +8105,7 @@
         <v>1.767688434264066</v>
       </c>
       <c r="D135" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E135">
         <v>1.290978663803567</v>
@@ -8152,7 +8155,7 @@
         <v>1.08603337246497</v>
       </c>
       <c r="D136" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E136">
         <v>1.434308681460452</v>
@@ -8202,7 +8205,7 @@
         <v>1.092683460749394</v>
       </c>
       <c r="D137" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E137">
         <v>1.434308681460452</v>
@@ -8252,7 +8255,7 @@
         <v>1.059313654975125</v>
       </c>
       <c r="D138" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E138">
         <v>1.434308681460452</v>
@@ -8688,7 +8691,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8738,7 +8741,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8788,7 +8791,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8838,7 +8841,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8888,7 +8891,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8902,7 +8905,7 @@
         <v>1.823420612308294</v>
       </c>
       <c r="D151" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E151">
         <v>2.204728303692967</v>
@@ -8938,7 +8941,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8988,7 +8991,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9038,7 +9041,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9088,7 +9091,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9138,7 +9141,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9188,7 +9191,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9238,7 +9241,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9288,7 +9291,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9302,7 +9305,7 @@
         <v>2.07884565528049</v>
       </c>
       <c r="D159" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E159">
         <v>2.424795934638657</v>
@@ -9338,7 +9341,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9388,7 +9391,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9438,7 +9441,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9452,7 +9455,7 @@
         <v>2.074698477808512</v>
       </c>
       <c r="D162" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E162">
         <v>2.228712809543505</v>
@@ -9488,7 +9491,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9538,7 +9541,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9588,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9638,7 +9641,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9752,7 +9755,7 @@
         <v>2.045995448659537</v>
       </c>
       <c r="D168" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E168">
         <v>2.697722827185737</v>
@@ -9902,7 +9905,7 @@
         <v>2.025703573192318</v>
       </c>
       <c r="D171" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E171">
         <v>2.585859069325287</v>
@@ -9988,7 +9991,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10002,7 +10005,7 @@
         <v>2.002237248721763</v>
       </c>
       <c r="D173" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E173">
         <v>2.933150127071722</v>
@@ -10038,7 +10041,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10088,7 +10091,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10102,7 +10105,7 @@
         <v>2.14690100237887</v>
       </c>
       <c r="D175" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E175">
         <v>3.035145626224377</v>
@@ -10138,7 +10141,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10188,7 +10191,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10202,7 +10205,7 @@
         <v>2.113865641885164</v>
       </c>
       <c r="D177" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E177">
         <v>2.99862999271211</v>
@@ -10238,7 +10241,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10288,7 +10291,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10338,7 +10341,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10352,7 +10355,7 @@
         <v>2.224552854469621</v>
       </c>
       <c r="D180" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E180">
         <v>2.747562112891602</v>
@@ -10388,7 +10391,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10402,7 +10405,7 @@
         <v>2.234582155562626</v>
       </c>
       <c r="D181" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E181">
         <v>2.747562112891602</v>
@@ -10438,7 +10441,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10452,7 +10455,7 @@
         <v>2.532227490792448</v>
       </c>
       <c r="D182" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E182">
         <v>2.747562112891602</v>
@@ -10488,7 +10491,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10538,7 +10541,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10588,7 +10591,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10602,7 +10605,7 @@
         <v>2.219578642489605</v>
       </c>
       <c r="D185" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E185">
         <v>2.748307309478141</v>
@@ -10638,7 +10641,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10652,7 +10655,7 @@
         <v>2.229273046142372</v>
       </c>
       <c r="D186" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E186">
         <v>2.748307309478141</v>
@@ -10688,7 +10691,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10702,7 +10705,7 @@
         <v>2.526938081221619</v>
       </c>
       <c r="D187" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E187">
         <v>2.748307309478141</v>
@@ -10738,7 +10741,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10788,7 +10791,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10838,7 +10841,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10852,7 +10855,7 @@
         <v>2.223095119495316</v>
       </c>
       <c r="D190" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E190">
         <v>2.585306324177835</v>
@@ -10888,7 +10891,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10902,7 +10905,7 @@
         <v>2.233026276055397</v>
       </c>
       <c r="D191" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E191">
         <v>2.585306324177835</v>
@@ -10938,7 +10941,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10952,7 +10955,7 @@
         <v>2.530677384493038</v>
       </c>
       <c r="D192" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E192">
         <v>2.585306324177835</v>
@@ -10988,7 +10991,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11038,7 +11041,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11088,7 +11091,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11102,7 +11105,7 @@
         <v>2.351296670264901</v>
       </c>
       <c r="D195" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E195">
         <v>2.34477901699545</v>
@@ -11138,7 +11141,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11152,7 +11155,7 @@
         <v>2.531296670264901</v>
       </c>
       <c r="D196" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E196">
         <v>2.34477901699545</v>
@@ -11188,7 +11191,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11238,7 +11241,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11288,7 +11291,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11338,7 +11341,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11352,7 +11355,7 @@
         <v>2.354338556588907</v>
       </c>
       <c r="D200" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E200">
         <v>2.692933327062218</v>
@@ -11388,7 +11391,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11402,7 +11405,7 @@
         <v>2.534338556588906</v>
       </c>
       <c r="D201" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E201">
         <v>2.692933327062218</v>
@@ -11438,7 +11441,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11488,7 +11491,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11538,7 +11541,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11588,7 +11591,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11602,7 +11605,7 @@
         <v>2.353252705775172</v>
       </c>
       <c r="D205" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E205">
         <v>3.037215179660817</v>
@@ -11638,7 +11641,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11652,7 +11655,7 @@
         <v>2.533252705775172</v>
       </c>
       <c r="D206" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E206">
         <v>3.037215179660817</v>
@@ -11688,7 +11691,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11702,7 +11705,7 @@
         <v>-1.066638455738899</v>
       </c>
       <c r="D207" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E207">
         <v>-1.465413797453388</v>
@@ -11738,7 +11741,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11752,7 +11755,7 @@
         <v>-1.0366384557389</v>
       </c>
       <c r="D208" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E208">
         <v>-1.465413797453388</v>
@@ -11788,7 +11791,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11802,7 +11805,7 @@
         <v>-0.9510556888450674</v>
       </c>
       <c r="D209" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E209">
         <v>-1.465413797453388</v>
@@ -11838,7 +11841,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11852,7 +11855,7 @@
         <v>-1.819265145803461</v>
       </c>
       <c r="D210" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E210">
         <v>-1.307592851757549</v>
@@ -11888,7 +11891,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11902,7 +11905,7 @@
         <v>-1.771950960365871</v>
       </c>
       <c r="D211" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E211">
         <v>-1.297263464992842</v>
@@ -11938,7 +11941,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11952,7 +11955,7 @@
         <v>-1.016934078228135</v>
       </c>
       <c r="D212" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E212">
         <v>-1.07654556696558</v>
@@ -11988,7 +11991,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12002,7 +12005,7 @@
         <v>-1.083441760674821</v>
       </c>
       <c r="D213" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E213">
         <v>-1.481089607902267</v>
@@ -12038,7 +12041,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12052,7 +12055,7 @@
         <v>-1.053441760674821</v>
       </c>
       <c r="D214" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E214">
         <v>-1.481089607902267</v>
@@ -12088,7 +12091,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12102,7 +12105,7 @@
         <v>-0.9668769824535648</v>
       </c>
       <c r="D215" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E215">
         <v>-1.481089607902267</v>
@@ -12138,7 +12141,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12152,7 +12155,7 @@
         <v>-1.83581385521005</v>
       </c>
       <c r="D216" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E216">
         <v>-1.323195920626619</v>
@@ -12188,7 +12191,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12202,7 +12205,7 @@
         <v>-1.787408546075322</v>
       </c>
       <c r="D217" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E217">
         <v>-1.311375331475824</v>
@@ -12238,7 +12241,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12288,7 +12291,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12302,7 +12305,7 @@
         <v>-1.07759404974841</v>
       </c>
       <c r="D219" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E219">
         <v>-1.503621288834554</v>
@@ -12338,7 +12341,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12352,7 +12355,7 @@
         <v>-0.9896177741137624</v>
       </c>
       <c r="D220" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E220">
         <v>-1.503621288834554</v>
@@ -12388,7 +12391,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12402,7 +12405,7 @@
         <v>-1.859600200509798</v>
       </c>
       <c r="D221" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E221">
         <v>-1.345623046194952</v>
@@ -12438,7 +12441,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12452,7 +12455,7 @@
         <v>-1.809626560915746</v>
       </c>
       <c r="D222" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E222">
         <v>-1.33165907208308</v>
@@ -12488,7 +12491,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12502,7 +12505,7 @@
         <v>-1.047695097971209</v>
       </c>
       <c r="D223" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E223">
         <v>-1.119714428935569</v>
@@ -12538,7 +12541,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12552,7 +12555,7 @@
         <v>-1.107622621715292</v>
       </c>
       <c r="D224" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E224">
         <v>-1.53163495662184</v>
@@ -12602,7 +12605,7 @@
         <v>-1.017891429537125</v>
       </c>
       <c r="D225" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E225">
         <v>-1.53163495662184</v>
@@ -12652,7 +12655,7 @@
         <v>-1.889173794113544</v>
       </c>
       <c r="D226" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E226">
         <v>-1.373506720164198</v>
@@ -12702,7 +12705,7 @@
         <v>-1.837250247248916</v>
       </c>
       <c r="D227" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E227">
         <v>-1.356877872782539</v>
@@ -12802,7 +12805,7 @@
         <v>-1.136466558905362</v>
       </c>
       <c r="D229" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E229">
         <v>-1.55854347811301</v>
@@ -12838,7 +12841,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12852,7 +12855,7 @@
         <v>-1.045049682086217</v>
       </c>
       <c r="D230" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E230">
         <v>-1.55854347811301</v>
@@ -12888,7 +12891,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12902,7 +12905,7 @@
         <v>-1.91758070195225</v>
       </c>
       <c r="D231" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E231">
         <v>-1.400290376126407</v>
@@ -12938,7 +12941,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12952,7 +12955,7 @@
         <v>-1.863784172153202</v>
       </c>
       <c r="D232" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E232">
         <v>-1.38110178540104</v>
@@ -12988,7 +12991,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13002,7 +13005,7 @@
         <v>-1.091913194675672</v>
       </c>
       <c r="D233" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E233">
         <v>-0.942243215869925</v>
@@ -13038,7 +13041,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13052,7 +13055,7 @@
         <v>-1.06938217480964</v>
       </c>
       <c r="D234" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E234">
         <v>-0.942243215869925</v>
@@ -13088,7 +13091,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13102,7 +13105,7 @@
         <v>-1.09938217480964</v>
       </c>
       <c r="D235" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E235">
         <v>-0.942243215869925</v>
@@ -13138,7 +13141,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13152,7 +13155,7 @@
         <v>-1.069955605077879</v>
       </c>
       <c r="D236" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E236">
         <v>-1.583220381123139</v>
@@ -13202,7 +13205,7 @@
         <v>-1.943631724851574</v>
       </c>
       <c r="D237" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E237">
         <v>-1.42485276914577</v>
@@ -13252,7 +13255,7 @@
         <v>-1.888117545191031</v>
       </c>
       <c r="D238" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E238">
         <v>-1.403316723609694</v>
@@ -13302,7 +13305,7 @@
         <v>-1.111780678073619</v>
       </c>
       <c r="D239" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E239">
         <v>-0.8811636624809664</v>
@@ -13352,7 +13355,7 @@
         <v>-1.088104558299923</v>
       </c>
       <c r="D240" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E240">
         <v>-0.8811636624809664</v>
@@ -13402,7 +13405,7 @@
         <v>-1.118104558299923</v>
       </c>
       <c r="D241" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E241">
         <v>-0.8811636624809664</v>
@@ -13452,7 +13455,7 @@
         <v>-1.100958399511376</v>
       </c>
       <c r="D242" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E242">
         <v>-1.613938092389432</v>
@@ -13488,7 +13491,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13502,7 +13505,7 @@
         <v>-1.976059935121095</v>
       </c>
       <c r="D243" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E243">
         <v>-1.455427938828461</v>
@@ -13538,7 +13541,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13552,7 +13555,7 @@
         <v>-1.918407631706518</v>
       </c>
       <c r="D244" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E244">
         <v>-1.430969790828538</v>
@@ -13588,7 +13591,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13602,7 +13605,7 @@
         <v>-1.136511642828615</v>
       </c>
       <c r="D245" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E245">
         <v>-1.028859339414037</v>
@@ -13638,7 +13641,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13652,7 +13655,7 @@
         <v>-1.111410107218897</v>
       </c>
       <c r="D246" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E246">
         <v>-1.028859339414037</v>
@@ -13688,7 +13691,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13702,7 +13705,7 @@
         <v>-1.141410107218897</v>
       </c>
       <c r="D247" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E247">
         <v>-1.028859339414037</v>
@@ -13738,7 +13741,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13752,7 +13755,7 @@
         <v>-1.117512484565025</v>
       </c>
       <c r="D248" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E248">
         <v>-1.630339955971323</v>
@@ -13788,7 +13791,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13802,7 +13805,7 @@
         <v>-1.993375127533532</v>
       </c>
       <c r="D249" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E249">
         <v>-1.471753691674473</v>
@@ -13838,7 +13841,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13852,7 +13855,7 @@
         <v>-1.934581163080772</v>
       </c>
       <c r="D250" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E250">
         <v>-1.445735273589034</v>
@@ -13888,7 +13891,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13902,7 +13905,7 @@
         <v>-1.149716855503595</v>
       </c>
       <c r="D251" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E251">
         <v>-1.032336626753983</v>
@@ -13938,7 +13941,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13952,7 +13955,7 @@
         <v>-1.123854212535088</v>
       </c>
       <c r="D252" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E252">
         <v>-1.032336626753983</v>
@@ -13988,7 +13991,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14002,7 +14005,7 @@
         <v>-1.153854212535088</v>
       </c>
       <c r="D253" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E253">
         <v>-1.032336626753983</v>
@@ -14038,7 +14041,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14052,7 +14055,7 @@
         <v>-1.135440729342402</v>
       </c>
       <c r="D254" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E254">
         <v>-1.64810334332546</v>
@@ -14088,7 +14091,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14102,7 +14105,7 @@
         <v>-2.012127659427111</v>
       </c>
       <c r="D255" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E255">
         <v>-1.489434650316991</v>
@@ -14138,7 +14141,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14152,7 +14155,7 @@
         <v>-1.95209726430005</v>
       </c>
       <c r="D256" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E256">
         <v>-1.461726443643339</v>
@@ -14188,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14202,7 +14205,7 @@
         <v>-1.164018236969687</v>
       </c>
       <c r="D257" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E257">
         <v>-1.112656534851095</v>
@@ -14238,7 +14241,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14252,7 +14255,7 @@
         <v>-1.137331306884979</v>
       </c>
       <c r="D258" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E258">
         <v>-1.112656534851095</v>
@@ -14288,7 +14291,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14302,7 +14305,7 @@
         <v>-1.167331306884979</v>
       </c>
       <c r="D259" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E259">
         <v>-1.112656534851095</v>
@@ -14338,7 +14341,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14352,7 +14355,7 @@
         <v>-2.029751754240792</v>
       </c>
       <c r="D260" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E260">
         <v>-1.506051653998461</v>
@@ -14402,7 +14405,7 @@
         <v>-1.968559330884256</v>
       </c>
       <c r="D261" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E261">
         <v>-1.476755342077862</v>
@@ -14452,7 +14455,7 @@
         <v>-1.177459030157264</v>
       </c>
       <c r="D262" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E262">
         <v>-1.113758929914932</v>
@@ -14502,7 +14505,7 @@
         <v>-1.149997414586239</v>
       </c>
       <c r="D263" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E263">
         <v>-1.113758929914932</v>
@@ -14552,7 +14555,7 @@
         <v>-1.179997414586239</v>
       </c>
       <c r="D264" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E264">
         <v>-1.113758929914932</v>
@@ -14602,7 +14605,7 @@
         <v>-2.049264235927141</v>
       </c>
       <c r="D265" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E265">
         <v>-1.524449136731304</v>
@@ -14638,7 +14641,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14652,7 +14655,7 @@
         <v>-1.986785275316561</v>
       </c>
       <c r="D266" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E266">
         <v>-1.493394557230178</v>
@@ -14688,7 +14691,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14702,7 +14705,7 @@
         <v>-1.192339977729051</v>
       </c>
       <c r="D267" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E267">
         <v>-0.9807727745942727</v>
@@ -14738,7 +14741,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14752,7 +14755,7 @@
         <v>-1.16402067065533</v>
       </c>
       <c r="D268" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E268">
         <v>-0.9807727745942727</v>
@@ -14788,7 +14791,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14802,7 +14805,7 @@
         <v>-1.19402067065533</v>
       </c>
       <c r="D269" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E269">
         <v>-0.9807727745942727</v>
@@ -14838,7 +14841,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14852,7 +14855,7 @@
         <v>-2.083260847634321</v>
       </c>
       <c r="D270" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E270">
         <v>-1.55650308491236</v>
@@ -14888,7 +14891,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14902,7 +14905,7 @@
         <v>-2.018540352185904</v>
       </c>
       <c r="D271" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E271">
         <v>-1.52238507446619</v>
@@ -14938,7 +14941,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14952,7 +14955,7 @@
         <v>-1.218267064020021</v>
       </c>
       <c r="D272" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E272">
         <v>-1.15072047992809</v>
@@ -14988,7 +14991,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15002,7 +15005,7 @@
         <v>-1.188453400387743</v>
       </c>
       <c r="D273" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E273">
         <v>-1.15072047992809</v>
@@ -15038,7 +15041,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15052,7 +15055,7 @@
         <v>-1.218453400387743</v>
       </c>
       <c r="D274" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E274">
         <v>-1.15072047992809</v>
@@ -15088,7 +15091,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15102,7 +15105,7 @@
         <v>-2.129173370599524</v>
       </c>
       <c r="D275" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E275">
         <v>-1.599792035136694</v>
@@ -15138,7 +15141,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15152,7 +15155,7 @@
         <v>-2.061425675834721</v>
       </c>
       <c r="D276" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E276">
         <v>-1.561536852291463</v>
@@ -15188,7 +15191,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15202,7 +15205,7 @@
         <v>-1.253281669446231</v>
       </c>
       <c r="D277" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E277">
         <v>-1.285422798224685</v>
@@ -15238,7 +15241,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15252,7 +15255,7 @@
         <v>-1.221449872936362</v>
       </c>
       <c r="D278" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E278">
         <v>-1.285422798224685</v>
@@ -15288,7 +15291,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15302,7 +15305,7 @@
         <v>-1.251449872936362</v>
       </c>
       <c r="D279" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E279">
         <v>-1.285422798224685</v>
@@ -15338,7 +15341,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15352,7 +15355,7 @@
         <v>-2.169540849194301</v>
       </c>
       <c r="D280" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E280">
         <v>-1.637852800668912</v>
@@ -15388,7 +15391,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15402,7 +15405,7 @@
         <v>-2.099131562434238</v>
       </c>
       <c r="D281" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E281">
         <v>-1.595960108763492</v>
@@ -15438,7 +15441,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15452,7 +15455,7 @@
         <v>-1.284067416858071</v>
       </c>
       <c r="D282" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E282">
         <v>-1.430231131562097</v>
@@ -15488,7 +15491,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15502,7 +15505,7 @@
         <v>-1.250461225684695</v>
       </c>
       <c r="D283" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E283">
         <v>-1.430231131562097</v>
@@ -15538,7 +15541,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15552,7 +15555,7 @@
         <v>-1.280461225684695</v>
       </c>
       <c r="D284" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E284">
         <v>-1.430231131562097</v>
@@ -15588,7 +15591,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15602,7 +15605,7 @@
         <v>-2.189959023684696</v>
       </c>
       <c r="D285" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E285">
         <v>-1.657104222331285</v>
@@ -15638,7 +15641,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15652,7 +15655,7 @@
         <v>-2.11820348366153</v>
       </c>
       <c r="D286" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E286">
         <v>-1.613371650966291</v>
@@ -15688,7 +15691,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15702,7 +15705,7 @@
         <v>-1.299639079601296</v>
       </c>
       <c r="D287" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E287">
         <v>-1.362715372273368</v>
@@ -15738,7 +15741,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15752,7 +15755,7 @@
         <v>-1.265135386252518</v>
       </c>
       <c r="D288" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E288">
         <v>-1.362715372273368</v>
@@ -15788,7 +15791,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15802,7 +15805,7 @@
         <v>-1.295135386252518</v>
       </c>
       <c r="D289" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E289">
         <v>-1.362715372273368</v>
@@ -15838,7 +15841,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15852,7 +15855,7 @@
         <v>-2.214173184477514</v>
       </c>
       <c r="D290" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E290">
         <v>-1.679934716793084</v>
@@ -15888,7 +15891,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15902,7 +15905,7 @@
         <v>-2.140821106380096</v>
       </c>
       <c r="D291" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E291">
         <v>-1.634020210059946</v>
@@ -15938,7 +15941,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15952,7 +15955,7 @@
         <v>-1.318105703326807</v>
       </c>
       <c r="D292" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E292">
         <v>-1.489781742375517</v>
@@ -15988,7 +15991,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16002,7 +16005,7 @@
         <v>-1.282537651261862</v>
       </c>
       <c r="D293" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E293">
         <v>-1.489781742375517</v>
@@ -16038,7 +16041,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16052,7 +16055,7 @@
         <v>-1.312537651261862</v>
       </c>
       <c r="D294" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E294">
         <v>-1.489781742375517</v>
@@ -16088,7 +16091,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16102,7 +16105,7 @@
         <v>-2.241121102143395</v>
       </c>
       <c r="D295" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E295">
         <v>-1.705342753449486</v>
@@ -16138,7 +16141,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16152,7 +16155,7 @@
         <v>-2.165992238265808</v>
       </c>
       <c r="D296" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E296">
         <v>-1.656999972816785</v>
@@ -16188,7 +16191,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16202,7 +16205,7 @@
         <v>-1.338657192184084</v>
       </c>
       <c r="D297" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E297">
         <v>-1.427033480143279</v>
@@ -16238,7 +16241,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16252,7 +16255,7 @@
         <v>-1.301904616265692</v>
       </c>
       <c r="D298" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E298">
         <v>-1.427033480143279</v>
@@ -16288,7 +16291,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16302,7 +16305,7 @@
         <v>-1.331904616265692</v>
       </c>
       <c r="D299" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E299">
         <v>-1.427033480143279</v>
@@ -16338,7 +16341,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16352,7 +16355,7 @@
         <v>1.347720014974502</v>
       </c>
       <c r="D300" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E300">
         <v>1.579062118830282</v>
@@ -16388,7 +16391,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16402,7 +16405,7 @@
         <v>1.334700016044109</v>
       </c>
       <c r="D301" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E301">
         <v>1.593089491417174</v>
@@ -16438,7 +16441,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16452,7 +16455,7 @@
         <v>1.841747387561394</v>
       </c>
       <c r="D302" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E302">
         <v>1.890874754800249</v>
@@ -16488,7 +16491,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16502,7 +16505,7 @@
         <v>1.862485279427185</v>
       </c>
       <c r="D303" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E303">
         <v>1.890874754800249</v>
@@ -16538,7 +16541,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16552,7 +16555,7 @@
         <v>1.441706845387347</v>
       </c>
       <c r="D304" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E304">
         <v>1.664215600520115</v>
@@ -16588,7 +16591,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16602,7 +16605,7 @@
         <v>1.435400191486443</v>
       </c>
       <c r="D305" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E305">
         <v>1.704389685327122</v>
@@ -16638,7 +16641,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16652,7 +16655,7 @@
         <v>1.856584782452771</v>
       </c>
       <c r="D306" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E306">
         <v>1.861880930194354</v>
@@ -16688,7 +16691,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16702,7 +16705,7 @@
         <v>1.9645987906652</v>
       </c>
       <c r="D307" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E307">
         <v>1.861880930194354</v>
@@ -16738,7 +16741,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16752,7 +16755,7 @@
         <v>2.014804950663784</v>
       </c>
       <c r="D308" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E308">
         <v>1.689180786611569</v>
@@ -16788,7 +16791,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16802,7 +16805,7 @@
         <v>1.927301606872644</v>
       </c>
       <c r="D309" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E309">
         <v>1.689180786611569</v>
@@ -16838,7 +16841,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16852,7 +16855,7 @@
         <v>1.922617032689892</v>
       </c>
       <c r="D310" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E310">
         <v>1.689180786611569</v>
@@ -16888,7 +16891,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -16902,7 +16905,7 @@
         <v>1.696992868637676</v>
       </c>
       <c r="D311" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E311">
         <v>1.791368704585461</v>
@@ -16938,7 +16941,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -16988,7 +16991,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17038,7 +17041,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17088,7 +17091,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17138,7 +17141,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17188,7 +17191,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17238,7 +17241,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17252,7 +17255,7 @@
         <v>1.869784887916945</v>
       </c>
       <c r="D318" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E318">
         <v>1.868536559812515</v>
@@ -17288,7 +17291,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17302,7 +17305,7 @@
         <v>1.892281544125805</v>
       </c>
       <c r="D319" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E319">
         <v>1.868536559812515</v>
@@ -17338,7 +17341,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17352,7 +17355,7 @@
         <v>1.879784887916945</v>
       </c>
       <c r="D320" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E320">
         <v>1.868536559812515</v>
@@ -17388,7 +17391,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17402,7 +17405,7 @@
         <v>1.830509026107986</v>
       </c>
       <c r="D321" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E321">
         <v>1.588842690067986</v>
@@ -17438,7 +17441,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17452,7 +17455,7 @@
         <v>1.823342590879987</v>
       </c>
       <c r="D322" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E322">
         <v>1.588842690067986</v>
@@ -17488,7 +17491,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17502,7 +17505,7 @@
         <v>1.597009323671986</v>
       </c>
       <c r="D323" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E323">
         <v>1.690676056463986</v>
@@ -17538,7 +17541,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17552,7 +17555,7 @@
         <v>1.564008728543987</v>
       </c>
       <c r="D324" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E324">
         <v>1.690841103059988</v>
@@ -17588,7 +17591,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17602,7 +17605,7 @@
         <v>1.612175362147987</v>
       </c>
       <c r="D325" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E325">
         <v>1.690841103059988</v>
@@ -17638,7 +17641,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17652,7 +17655,7 @@
         <v>1.608508629355987</v>
       </c>
       <c r="D326" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E326">
         <v>1.690841103059988</v>
@@ -17688,7 +17691,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17702,7 +17705,7 @@
         <v>1.611175163771987</v>
       </c>
       <c r="D327" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E327">
         <v>1.690841103059988</v>
@@ -17738,7 +17741,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17788,7 +17791,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17802,7 +17805,7 @@
         <v>1.787174370267988</v>
       </c>
       <c r="D329" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E329">
         <v>1.578675659711986</v>
@@ -17838,7 +17841,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17852,7 +17855,7 @@
         <v>1.812507439099989</v>
       </c>
       <c r="D330" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E330">
         <v>1.578675659711986</v>
@@ -17888,7 +17891,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17902,7 +17905,7 @@
         <v>1.783507637475988</v>
       </c>
       <c r="D331" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E331">
         <v>1.578675659711986</v>
@@ -17938,7 +17941,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17952,7 +17955,7 @@
         <v>1.797174370267989</v>
       </c>
       <c r="D332" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E332">
         <v>1.578675659711986</v>
@@ -17988,7 +17991,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18002,7 +18005,7 @@
         <v>1.796508232603987</v>
       </c>
       <c r="D333" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E333">
         <v>1.578675659711986</v>
@@ -18038,7 +18041,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18052,7 +18055,7 @@
         <v>1.60619577124814</v>
       </c>
       <c r="D334" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E334">
         <v>1.409496709559184</v>
@@ -18088,7 +18091,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18102,7 +18105,7 @@
         <v>1.639829926132983</v>
       </c>
       <c r="D335" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E335">
         <v>1.409496709559184</v>
@@ -18138,7 +18141,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18152,7 +18155,7 @@
         <v>1.641634855442047</v>
       </c>
       <c r="D336" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E336">
         <v>1.409496709559184</v>
@@ -18188,7 +18191,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18202,7 +18205,7 @@
         <v>1.294651169712725</v>
       </c>
       <c r="D337" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E337">
         <v>1.17011455017335</v>
@@ -18238,7 +18241,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18252,7 +18255,7 @@
         <v>1.309805629866267</v>
       </c>
       <c r="D338" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E338">
         <v>1.17011455017335</v>
@@ -18288,7 +18291,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18302,7 +18305,7 @@
         <v>1.302846240403662</v>
       </c>
       <c r="D339" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E339">
         <v>1.17011455017335</v>
@@ -18338,7 +18341,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18352,7 +18355,7 @@
         <v>1.302846240403662</v>
       </c>
       <c r="D340" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E340">
         <v>1.17011455017335</v>
@@ -18388,7 +18391,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18402,7 +18405,7 @@
         <v>1.306789315595589</v>
       </c>
       <c r="D341" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E341">
         <v>1.17011455017335</v>
@@ -18438,7 +18441,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18452,7 +18455,7 @@
         <v>1.225269010326891</v>
       </c>
       <c r="D342" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E342">
         <v>1.17011455017335</v>
@@ -18488,7 +18491,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18502,7 +18505,7 @@
         <v>1.444294269397325</v>
       </c>
       <c r="D343" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E343">
         <v>1.256000185094495</v>
@@ -18552,7 +18555,7 @@
         <v>1.501117816501946</v>
       </c>
       <c r="D344" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E344">
         <v>1.256000185094495</v>
@@ -18602,7 +18605,7 @@
         <v>1.083058995014017</v>
       </c>
       <c r="D345" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E345">
         <v>1.093353102453659</v>
@@ -18652,7 +18655,7 @@
         <v>1.408730452400234</v>
       </c>
       <c r="D346" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E346">
         <v>1.224172692200284</v>
@@ -18688,7 +18691,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18702,7 +18705,7 @@
         <v>1.47198161896276</v>
       </c>
       <c r="D347" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E347">
         <v>1.224172692200284</v>
@@ -18738,7 +18741,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18788,7 +18791,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18802,7 +18805,7 @@
         <v>1.382122760311682</v>
       </c>
       <c r="D349" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E349">
         <v>1.191863351807043</v>
@@ -18838,7 +18841,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18852,7 +18855,7 @@
         <v>1.442404318382183</v>
       </c>
       <c r="D350" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E350">
         <v>1.191863351807043</v>
@@ -18888,7 +18891,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18938,7 +18941,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18952,7 +18955,7 @@
         <v>1.370401955803482</v>
       </c>
       <c r="D352" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E352">
         <v>1.1776309463328</v>
@@ -19002,7 +19005,7 @@
         <v>1.429375388370835</v>
       </c>
       <c r="D353" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E353">
         <v>1.1776309463328</v>
@@ -19052,7 +19055,7 @@
         <v>1.010452200278918</v>
       </c>
       <c r="D354" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E354">
         <v>1.015068140738506</v>
@@ -19102,7 +19105,7 @@
         <v>1.025068140738506</v>
       </c>
       <c r="D355" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E355">
         <v>1.015068140738506</v>
@@ -19152,7 +19155,7 @@
         <v>1.355513343522262</v>
       </c>
       <c r="D356" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E356">
         <v>1.159551917134175</v>
@@ -19188,7 +19191,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19202,7 +19205,7 @@
         <v>1.4128251006118</v>
       </c>
       <c r="D357" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E357">
         <v>1.159551917134175</v>
@@ -19238,7 +19241,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19252,7 +19255,7 @@
         <v>0.9937025114625451</v>
       </c>
       <c r="D358" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E358">
         <v>1.019315457208822</v>
@@ -19288,7 +19291,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19302,7 +19305,7 @@
         <v>1.009315457208822</v>
       </c>
       <c r="D359" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E359">
         <v>1.019315457208822</v>
@@ -19338,7 +19341,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19352,7 +19355,7 @@
         <v>1.344301537527252</v>
       </c>
       <c r="D360" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E360">
         <v>1.145937581283092</v>
@@ -19402,7 +19405,7 @@
         <v>1.400361976983419</v>
       </c>
       <c r="D361" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E361">
         <v>1.145937581283092</v>
@@ -19552,7 +19555,7 @@
         <v>1.32595157423566</v>
       </c>
       <c r="D364" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E364">
         <v>1.123655483000445</v>
@@ -19588,7 +19591,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19602,7 +19605,7 @@
         <v>1.379964026717319</v>
       </c>
       <c r="D365" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E365">
         <v>1.123655483000445</v>
@@ -19638,7 +19641,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19652,7 +19655,7 @@
         <v>0.9604455210151182</v>
       </c>
       <c r="D366" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E366">
         <v>0.9494825324195202</v>
@@ -19688,7 +19691,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19702,7 +19705,7 @@
         <v>0.9780380495261229</v>
       </c>
       <c r="D367" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E367">
         <v>0.9494825324195202</v>
@@ -19738,7 +19741,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19752,7 +19755,7 @@
         <v>0.9780380495261229</v>
       </c>
       <c r="D368" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E368">
         <v>0.9494825324195202</v>
@@ -19788,7 +19791,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19802,7 +19805,7 @@
         <v>0.93948253241952</v>
       </c>
       <c r="D369" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E369">
         <v>0.9494825324195202</v>
@@ -19838,7 +19841,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19852,7 +19855,7 @@
         <v>1.346901155844391</v>
       </c>
       <c r="D370" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E370">
         <v>1.225539647019887</v>
@@ -19888,7 +19891,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19902,7 +19905,7 @@
         <v>1.331298641136886</v>
       </c>
       <c r="D371" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E371">
         <v>1.225539647019887</v>
@@ -19938,7 +19941,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19952,7 +19955,7 @@
         <v>1.154256377900131</v>
       </c>
       <c r="D372" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E372">
         <v>1.26001537201713</v>
@@ -19988,7 +19991,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20002,7 +20005,7 @@
         <v>1.14857562348788</v>
       </c>
       <c r="D373" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E373">
         <v>1.274334617604878</v>
@@ -20038,7 +20041,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20052,7 +20055,7 @@
         <v>1.324412857309625</v>
       </c>
       <c r="D374" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E374">
         <v>1.205852605838874</v>
@@ -20088,7 +20091,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20102,7 +20105,7 @@
         <v>1.043943419081145</v>
       </c>
       <c r="D375" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E375">
         <v>1.269702413198143</v>
@@ -20138,7 +20141,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20152,7 +20155,7 @@
         <v>1.36666643673015</v>
       </c>
       <c r="D376" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E376">
         <v>1.400907442613152</v>
@@ -20188,7 +20191,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20202,7 +20205,7 @@
         <v>1.3381061852594</v>
       </c>
       <c r="D377" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E377">
         <v>1.400907442613152</v>
@@ -20238,7 +20241,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20252,7 +20255,7 @@
         <v>1.337921514632137</v>
       </c>
       <c r="D378" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E378">
         <v>1.216329758597064</v>
@@ -20302,7 +20305,7 @@
         <v>1.321935254573682</v>
       </c>
       <c r="D379" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E379">
         <v>1.216329758597064</v>
@@ -20352,7 +20355,7 @@
         <v>1.144547620521072</v>
       </c>
       <c r="D380" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E380">
         <v>1.250153116497689</v>
@@ -20402,7 +20405,7 @@
         <v>1.138751742503535</v>
       </c>
       <c r="D381" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E381">
         <v>1.264357238480152</v>
@@ -20452,7 +20455,7 @@
         <v>1.314166856439233</v>
       </c>
       <c r="D382" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E382">
         <v>1.195568230433388</v>
@@ -20502,7 +20505,7 @@
         <v>1.035309148684748</v>
       </c>
       <c r="D383" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E383">
         <v>1.260914644661365</v>
@@ -20652,7 +20655,7 @@
         <v>1.326338641239302</v>
       </c>
       <c r="D386" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E386">
         <v>1.204449888450566</v>
@@ -20688,7 +20691,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20702,7 +20705,7 @@
         <v>1.309857386591409</v>
       </c>
       <c r="D387" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E387">
         <v>1.204449888450566</v>
@@ -20738,7 +20741,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20752,7 +20755,7 @@
         <v>1.132024257408305</v>
       </c>
       <c r="D388" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E388">
         <v>1.237431755549148</v>
@@ -20788,7 +20791,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20802,7 +20805,7 @@
         <v>1.126079881013937</v>
       </c>
       <c r="D389" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E389">
         <v>1.25148737915478</v>
@@ -20838,7 +20841,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20852,7 +20855,7 @@
         <v>1.300950500901255</v>
       </c>
       <c r="D390" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E390">
         <v>1.182302375436465</v>
@@ -20888,7 +20891,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20902,7 +20905,7 @@
         <v>1.024171770422406</v>
       </c>
       <c r="D391" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E391">
         <v>1.249579268563249</v>
@@ -20938,7 +20941,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20952,7 +20955,7 @@
         <v>1.347949275999877</v>
       </c>
       <c r="D392" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E392">
         <v>1.407134279718192</v>
@@ -20988,7 +20991,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21002,7 +21005,7 @@
         <v>1.319301150535088</v>
       </c>
       <c r="D393" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E393">
         <v>1.407134279718192</v>
@@ -21038,7 +21041,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21052,7 +21055,7 @@
         <v>1.31894662096582</v>
       </c>
       <c r="D394" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E394">
         <v>1.196868329195712</v>
@@ -21088,7 +21091,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21102,7 +21105,7 @@
         <v>1.302149468015641</v>
       </c>
       <c r="D395" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E395">
         <v>1.196868329195712</v>
@@ -21138,7 +21141,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21152,7 +21155,7 @@
         <v>1.12403203036048</v>
       </c>
       <c r="D396" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E396">
         <v>1.229313169180409</v>
@@ -21188,7 +21191,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21202,7 +21205,7 @@
         <v>1.117992884475426</v>
       </c>
       <c r="D397" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E397">
         <v>1.243274023295355</v>
@@ -21238,7 +21241,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21252,7 +21255,7 @@
         <v>1.017064058620981</v>
       </c>
       <c r="D398" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E398">
         <v>1.242345197440909</v>
@@ -21288,7 +21291,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21338,7 +21341,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21388,7 +21391,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21402,7 +21405,7 @@
         <v>1.309314370259902</v>
       </c>
       <c r="D401" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E401">
         <v>1.212105582664171</v>
@@ -21438,7 +21441,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21452,7 +21455,7 @@
         <v>1.113617673828013</v>
       </c>
       <c r="D402" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E402">
         <v>1.218734158789721</v>
@@ -21488,7 +21491,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21502,7 +21505,7 @@
         <v>1.107455037549294</v>
       </c>
       <c r="D403" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E403">
         <v>1.232571522511002</v>
@@ -21538,7 +21541,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21552,7 +21555,7 @@
         <v>1.00780227909606</v>
       </c>
       <c r="D404" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E404">
         <v>1.232918764057767</v>
@@ -21588,7 +21591,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21638,7 +21641,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21688,7 +21691,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21738,7 +21741,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21752,7 +21755,7 @@
         <v>1.096911392393543</v>
       </c>
       <c r="D408" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E408">
         <v>1.20176374642348</v>
@@ -21788,7 +21791,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21802,7 +21805,7 @@
         <v>1.090550657915995</v>
       </c>
       <c r="D409" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E409">
         <v>1.215403011945933</v>
@@ -21838,7 +21841,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21852,7 +21855,7 @@
         <v>0.9929449141839808</v>
       </c>
       <c r="D410" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E410">
         <v>1.217797268213918</v>
@@ -21888,7 +21891,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -21938,7 +21941,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -21988,7 +21991,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22002,7 +22005,7 @@
         <v>1.076787728620787</v>
       </c>
       <c r="D413" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E413">
         <v>1.194722566962074</v>
@@ -22038,7 +22041,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22052,7 +22055,7 @@
         <v>1.070188373624195</v>
       </c>
       <c r="D414" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E414">
         <v>1.194722566962074</v>
@@ -22088,7 +22091,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22102,7 +22105,7 @@
         <v>0.9750483752556411</v>
       </c>
       <c r="D415" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E415">
         <v>1.199582568593519</v>
@@ -22138,7 +22141,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22152,7 +22155,7 @@
         <v>1.06618192359011</v>
       </c>
       <c r="D416" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E416">
         <v>1.199582568593519</v>
@@ -22188,7 +22191,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22202,7 +22205,7 @@
         <v>1.301445795242007</v>
       </c>
       <c r="D417" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E417">
         <v>1.466305796873452</v>
@@ -22238,7 +22241,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22252,7 +22255,7 @@
         <v>1.325778053569659</v>
       </c>
       <c r="D418" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E418">
         <v>1.466305796873452</v>
@@ -22288,7 +22291,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22302,7 +22305,7 @@
         <v>1.061021828820504</v>
       </c>
       <c r="D419" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E419">
         <v>1.178520456495379</v>
@@ -22338,7 +22341,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22352,7 +22355,7 @@
         <v>1.05423552639545</v>
       </c>
       <c r="D420" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E420">
         <v>1.178520456495379</v>
@@ -22388,7 +22391,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22402,7 +22405,7 @@
         <v>0.9610273181210012</v>
       </c>
       <c r="D421" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E421">
         <v>1.18531224822093</v>
@@ -22438,7 +22441,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22452,7 +22455,7 @@
         <v>1.052098550645983</v>
       </c>
       <c r="D422" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E422">
         <v>1.18531224822093</v>
@@ -22488,7 +22491,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22502,7 +22505,7 @@
         <v>1.288172527821214</v>
       </c>
       <c r="D423" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E423">
         <v>1.460679389446836</v>
@@ -22538,7 +22541,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22552,7 +22555,7 @@
         <v>1.312816365196303</v>
       </c>
       <c r="D424" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E424">
         <v>1.460679389446836</v>
@@ -22588,7 +22591,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22702,7 +22705,7 @@
         <v>0.8755952802088971</v>
       </c>
       <c r="D427" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E427">
         <v>1.122137607315365</v>
@@ -22752,7 +22755,7 @@
         <v>1.266605330685716</v>
       </c>
       <c r="D428" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E428">
         <v>1.559580979333694</v>
@@ -22838,7 +22841,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22852,7 +22855,7 @@
         <v>0.8602148664207081</v>
       </c>
       <c r="D430" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E430">
         <v>1.107098980500247</v>
@@ -22888,7 +22891,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -22902,7 +22905,7 @@
         <v>1.280896373713855</v>
       </c>
       <c r="D431" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E431">
         <v>1.524099754797897</v>
@@ -22938,7 +22941,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23102,7 +23105,7 @@
         <v>1.302688953291221</v>
       </c>
       <c r="D435" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E435">
         <v>1.419681456386476</v>
@@ -23188,7 +23191,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23238,7 +23241,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23288,7 +23291,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23302,7 +23305,7 @@
         <v>1.257626439327654</v>
       </c>
       <c r="D439" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E439">
         <v>1.411664944525371</v>
@@ -23338,7 +23341,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23352,7 +23355,7 @@
         <v>1.840766780529548</v>
       </c>
       <c r="D440" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E440">
         <v>2.000338151296236</v>
@@ -23388,7 +23391,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23402,7 +23405,7 @@
         <v>2.174266578212954</v>
       </c>
       <c r="D441" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E441">
         <v>2.309284269167179</v>
@@ -23438,7 +23441,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23452,7 +23455,7 @@
         <v>2.096677111858851</v>
       </c>
       <c r="D442" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E442">
         <v>1.937337746663046</v>
@@ -23488,7 +23491,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23502,7 +23505,7 @@
         <v>1.86232005570882</v>
       </c>
       <c r="D443" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E443">
         <v>1.975355842250461</v>
@@ -23538,7 +23541,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23552,7 +23555,7 @@
         <v>1.842592596122513</v>
       </c>
       <c r="D444" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E444">
         <v>2.002261997256608</v>
@@ -23588,7 +23591,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23602,7 +23605,7 @@
         <v>2.176435500091845</v>
       </c>
       <c r="D445" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E445">
         <v>2.311735028352367</v>
@@ -23638,7 +23641,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23652,7 +23655,7 @@
         <v>2.099152378635891</v>
       </c>
       <c r="D446" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E446">
         <v>1.939947805195271</v>
@@ -23688,7 +23691,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23702,7 +23705,7 @@
         <v>1.864648276934749</v>
       </c>
       <c r="D447" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E447">
         <v>1.97756152551713</v>
@@ -23738,7 +23741,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23752,7 +23755,7 @@
         <v>1.84474004582061</v>
       </c>
       <c r="D448" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E448">
         <v>2.004524746267355</v>
@@ -23788,7 +23791,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23802,7 +23805,7 @@
         <v>2.178986497384215</v>
       </c>
       <c r="D449" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E449">
         <v>2.314617511168604</v>
@@ -23838,7 +23841,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23852,7 +23855,7 @@
         <v>2.102063686280291</v>
       </c>
       <c r="D450" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E450">
         <v>1.943017649394564</v>
@@ -23888,7 +23891,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23902,7 +23905,7 @@
         <v>1.867386635610175</v>
       </c>
       <c r="D451" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E451">
         <v>1.980155760051744</v>
@@ -23938,7 +23941,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23952,7 +23955,7 @@
         <v>2.182944230037506</v>
       </c>
       <c r="D452" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E452">
         <v>2.319089525466108</v>
@@ -23988,7 +23991,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24002,7 +24005,7 @@
         <v>2.106580420720769</v>
       </c>
       <c r="D453" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E453">
         <v>1.947780344621405</v>
@@ -24038,7 +24041,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24052,7 +24055,7 @@
         <v>1.871635049192803</v>
       </c>
       <c r="D454" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E454">
         <v>1.984180572919497</v>
@@ -24088,7 +24091,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24102,7 +24105,7 @@
         <v>2.18904965856885</v>
       </c>
       <c r="D455" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E455">
         <v>2.325988314767062</v>
@@ -24138,7 +24141,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24152,7 +24155,7 @@
         <v>2.113548197914732</v>
       </c>
       <c r="D456" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E456">
         <v>1.955127555226921</v>
@@ -24188,7 +24191,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24202,7 +24205,7 @@
         <v>1.878188899028709</v>
       </c>
       <c r="D457" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E457">
         <v>2.015269716995014</v>
@@ -24238,7 +24241,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24252,7 +24255,7 @@
         <v>1.88583444385064</v>
       </c>
       <c r="D458" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E458">
         <v>2.125307034142769</v>
@@ -24288,7 +24291,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24302,7 +24305,7 @@
         <v>2.298073483752043</v>
       </c>
       <c r="D459" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E459">
         <v>2.037664496092738</v>
@@ -24338,7 +24341,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24352,7 +24355,7 @@
         <v>1.897427651995606</v>
       </c>
       <c r="D460" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E460">
         <v>2.100495646236972</v>
@@ -24388,7 +24391,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24402,7 +24405,7 @@
         <v>1.886668859096591</v>
       </c>
       <c r="D461" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E461">
         <v>2.126294507806616</v>
@@ -24438,7 +24441,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24452,7 +24455,7 @@
         <v>2.29919426636051</v>
       </c>
       <c r="D462" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E462">
         <v>2.038997585538931</v>
@@ -24488,7 +24491,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24502,7 +24505,7 @@
         <v>1.898642244602138</v>
       </c>
       <c r="D463" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E463">
         <v>2.102411345144836</v>
@@ -24538,7 +24541,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24552,7 +24555,7 @@
         <v>1.887695818378956</v>
       </c>
       <c r="D464" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E464">
         <v>2.127509844235451</v>
@@ -24588,7 +24591,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24638,7 +24641,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24652,7 +24655,7 @@
         <v>1.900137108409605</v>
       </c>
       <c r="D466" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E466">
         <v>2.104769097816775</v>
@@ -24688,7 +24691,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24702,7 +24705,7 @@
         <v>1.882492570308907</v>
       </c>
       <c r="D467" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E467">
         <v>2.121352154211724</v>
@@ -24738,7 +24741,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24788,7 +24791,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24802,7 +24805,7 @@
         <v>1.911660475077831</v>
       </c>
       <c r="D469" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E469">
         <v>2.092823179170745</v>
@@ -24838,7 +24841,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24852,7 +24855,7 @@
         <v>1.879971436092785</v>
       </c>
       <c r="D470" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E470">
         <v>2.118368563423415</v>
@@ -24888,7 +24891,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24938,7 +24941,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24952,7 +24955,7 @@
         <v>1.90788623273062</v>
       </c>
       <c r="D472" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E472">
         <v>2.087035013041425</v>
@@ -24988,7 +24991,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25052,7 +25055,7 @@
         <v>1.89858988459332</v>
       </c>
       <c r="D474" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E474">
         <v>2.07277816293363</v>
@@ -25102,7 +25105,7 @@
         <v>2.27342525786704</v>
       </c>
       <c r="D475" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E475">
         <v>2.050890844436287</v>
@@ -25138,7 +25141,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25152,7 +25155,7 @@
         <v>1.889192027490578</v>
       </c>
       <c r="D476" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E476">
         <v>2.058365638997408</v>
@@ -25188,7 +25191,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25202,7 +25205,7 @@
         <v>2.266210657543448</v>
       </c>
       <c r="D477" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E477">
         <v>2.042055342718407</v>
@@ -25238,7 +25241,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25252,7 +25255,7 @@
         <v>1.881151085279702</v>
       </c>
       <c r="D478" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E478">
         <v>2.046034075448713</v>
@@ -25288,7 +25291,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25302,7 +25305,7 @@
         <v>2.259792939301354</v>
       </c>
       <c r="D479" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E479">
         <v>2.034195758263333</v>
@@ -25338,7 +25341,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25352,7 +25355,7 @@
         <v>1.873998297987854</v>
       </c>
       <c r="D480" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E480">
         <v>2.061056685064424</v>
@@ -25388,7 +25391,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25402,7 +25405,7 @@
         <v>2.247400638043782</v>
       </c>
       <c r="D481" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E481">
         <v>2.019019283595469</v>
@@ -25438,7 +25441,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25452,7 +25455,7 @@
         <v>1.860186614207387</v>
       </c>
       <c r="D482" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E482">
         <v>2.039929722127505</v>
@@ -25488,7 +25491,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25502,7 +25505,7 @@
         <v>2.218696305669633</v>
       </c>
       <c r="D483" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E483">
         <v>1.983865960247392</v>
@@ -25538,7 +25541,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25552,7 +25555,7 @@
         <v>1.828194560944569</v>
       </c>
       <c r="D484" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E484">
         <v>1.990993261207699</v>
@@ -25588,7 +25591,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25602,7 +25605,7 @@
         <v>1.830127541068264</v>
       </c>
       <c r="D485" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E485">
         <v>2.018032125375022</v>
@@ -25638,7 +25641,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25688,7 +25691,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25702,7 +25705,7 @@
         <v>1.78228507381279</v>
       </c>
       <c r="D487" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E487">
         <v>2.022800472072064</v>
@@ -25738,7 +25741,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25752,7 +25755,7 @@
         <v>1.783722556644772</v>
       </c>
       <c r="D488" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E488">
         <v>1.972929321636883</v>
@@ -25788,7 +25791,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25802,7 +25805,7 @@
         <v>2.163345062458509</v>
       </c>
       <c r="D489" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E489">
         <v>1.877414831999107</v>
@@ -25838,7 +25841,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25852,7 +25855,7 @@
         <v>1.693507313006611</v>
       </c>
       <c r="D490" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E490">
         <v>1.978388335287718</v>
@@ -25888,7 +25891,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25902,7 +25905,7 @@
         <v>1.734543015346852</v>
       </c>
       <c r="D491" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E491">
         <v>1.925129818487629</v>
@@ -25938,7 +25941,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25952,7 +25955,7 @@
         <v>1.684218514250647</v>
       </c>
       <c r="D492" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E492">
         <v>1.570048693213578</v>
@@ -25988,7 +25991,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26002,7 +26005,7 @@
         <v>2.132031608016207</v>
       </c>
       <c r="D493" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E493">
         <v>1.840169754028087</v>
@@ -26038,7 +26041,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26052,7 +26055,7 @@
         <v>1.660262632299145</v>
       </c>
       <c r="D494" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E494">
         <v>1.929555899725715</v>
@@ -26088,7 +26091,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26102,7 +26105,7 @@
         <v>1.680468679922261</v>
       </c>
       <c r="D495" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E495">
         <v>1.872572875128523</v>
@@ -26138,7 +26141,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26152,7 +26155,7 @@
         <v>1.634006631356384</v>
       </c>
       <c r="D496" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E496">
         <v>1.60382087481427</v>
@@ -26188,7 +26191,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26202,7 +26205,7 @@
         <v>2.09863804467423</v>
       </c>
       <c r="D497" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E497">
         <v>1.800450537718246</v>
@@ -26238,7 +26241,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26252,7 +26255,7 @@
         <v>1.624809554037398</v>
       </c>
       <c r="D498" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E498">
         <v>1.877479593897257</v>
@@ -26288,7 +26291,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26302,7 +26305,7 @@
         <v>1.622802262168714</v>
       </c>
       <c r="D499" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E499">
         <v>1.752483946759322</v>
@@ -26338,7 +26341,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26352,7 +26355,7 @@
         <v>1.580459243442377</v>
       </c>
       <c r="D500" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E500">
         <v>1.752483946759322</v>
@@ -26388,7 +26391,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26402,7 +26405,7 @@
         <v>2.071221135479056</v>
       </c>
       <c r="D501" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E501">
         <v>1.767840117089625</v>
@@ -26438,7 +26441,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26452,7 +26455,7 @@
         <v>1.595701734142962</v>
       </c>
       <c r="D502" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E502">
         <v>1.834723709073065</v>
@@ -26488,7 +26491,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26538,7 +26541,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26588,7 +26591,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26602,7 +26605,7 @@
         <v>2.041322179557651</v>
       </c>
       <c r="D505" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E505">
         <v>1.73227748229324</v>
@@ -26638,7 +26641,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26652,7 +26655,7 @@
         <v>1.563958789750633</v>
       </c>
       <c r="D506" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E506">
         <v>1.788097143451137</v>
@@ -26688,7 +26691,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26702,7 +26705,7 @@
         <v>1.472686344256899</v>
       </c>
       <c r="D507" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E507">
         <v>1.788097143451137</v>
@@ -26738,7 +26741,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26752,7 +26755,7 @@
         <v>1.523825085403519</v>
       </c>
       <c r="D508" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E508">
         <v>1.630370751283219</v>
@@ -26788,7 +26791,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26802,7 +26805,7 @@
         <v>1.56168905637971</v>
       </c>
       <c r="D509" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E509">
         <v>1.630370751283219</v>
@@ -26838,7 +26841,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26852,7 +26855,7 @@
         <v>1.565051671294496</v>
       </c>
       <c r="D510" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E510">
         <v>1.630370751283219</v>
@@ -26888,7 +26891,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26902,7 +26905,7 @@
         <v>1.866585623391427</v>
       </c>
       <c r="D511" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E511">
         <v>1.689366599623595</v>
@@ -26938,7 +26941,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26952,7 +26955,7 @@
         <v>2.005245252276134</v>
       </c>
       <c r="D512" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E512">
         <v>1.689366599623595</v>
@@ -26988,7 +26991,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27002,7 +27005,7 @@
         <v>1.4318415411232</v>
       </c>
       <c r="D513" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E513">
         <v>1.73183620839538</v>
@@ -27038,7 +27041,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27052,7 +27055,7 @@
         <v>1.461524840934997</v>
       </c>
       <c r="D514" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E514">
         <v>1.564205583165584</v>
@@ -27088,7 +27091,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27102,7 +27105,7 @@
         <v>1.496369157204806</v>
       </c>
       <c r="D515" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E515">
         <v>1.564205583165584</v>
@@ -27138,7 +27141,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27152,7 +27155,7 @@
         <v>1.508949665433811</v>
       </c>
       <c r="D516" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E516">
         <v>1.564205583165584</v>
@@ -27188,7 +27191,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27202,7 +27205,7 @@
         <v>1.973924573324424</v>
       </c>
       <c r="D517" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E517">
         <v>1.612872963807592</v>
@@ -27252,7 +27255,7 @@
         <v>1.396381565393731</v>
       </c>
       <c r="D518" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E518">
         <v>1.682992506417824</v>
@@ -27302,7 +27305,7 @@
         <v>1.467141600577559</v>
       </c>
       <c r="D519" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E519">
         <v>1.682992506417824</v>
@@ -27352,7 +27355,7 @@
         <v>1.407438029705613</v>
       </c>
       <c r="D520" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E520">
         <v>1.521706666475579</v>
@@ -27402,7 +27405,7 @@
         <v>1.439660791349507</v>
       </c>
       <c r="D521" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E521">
         <v>1.521706666475579</v>
@@ -27452,7 +27455,7 @@
         <v>1.460243940015513</v>
       </c>
       <c r="D522" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E522">
         <v>1.521706666475579</v>
@@ -27502,7 +27505,7 @@
         <v>1.940579116805523</v>
       </c>
       <c r="D523" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E523">
         <v>1.574239241056619</v>
@@ -27538,7 +27541,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27552,7 +27555,7 @@
         <v>1.781069303182167</v>
       </c>
       <c r="D524" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E524">
         <v>1.574239241056619</v>
@@ -27588,7 +27591,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27602,7 +27605,7 @@
         <v>1.358629220348103</v>
       </c>
       <c r="D525" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E525">
         <v>1.630991221802445</v>
@@ -27638,7 +27641,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27652,7 +27655,7 @@
         <v>1.349854686289714</v>
       </c>
       <c r="D526" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E526">
         <v>1.479202912629048</v>
@@ -27688,7 +27691,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27702,7 +27705,7 @@
         <v>1.379286418533347</v>
       </c>
       <c r="D527" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E527">
         <v>1.479202912629048</v>
@@ -27738,7 +27741,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27752,7 +27755,7 @@
         <v>1.408389551684359</v>
       </c>
       <c r="D528" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E528">
         <v>1.479202912629048</v>
@@ -27788,7 +27791,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27802,7 +27805,7 @@
         <v>1.74645545085387</v>
       </c>
       <c r="D529" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E529">
         <v>1.54184264617284</v>
@@ -27852,7 +27855,7 @@
         <v>1.326971711279163</v>
       </c>
       <c r="D530" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E530">
         <v>1.58738515872694</v>
@@ -28052,7 +28055,7 @@
         <v>1.276676327166428</v>
       </c>
       <c r="D534" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E534">
         <v>1.518106691894613</v>
@@ -28088,7 +28091,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28102,7 +28105,7 @@
         <v>1.224852607973696</v>
       </c>
       <c r="D535" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E535">
         <v>1.33929930838555</v>
@@ -28138,7 +28141,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28152,7 +28155,7 @@
         <v>1.248225566013237</v>
       </c>
       <c r="D536" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E536">
         <v>1.33929930838555</v>
@@ -28188,7 +28191,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28202,7 +28205,7 @@
         <v>1.263762437199394</v>
       </c>
       <c r="D537" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E537">
         <v>1.33929930838555</v>
@@ -28238,7 +28241,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28252,7 +28255,7 @@
         <v>1.212947744952629</v>
       </c>
       <c r="D538" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E538">
         <v>1.430324909390002</v>
@@ -28288,7 +28291,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28302,7 +28305,7 @@
         <v>1.146309428698562</v>
       </c>
       <c r="D539" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E539">
         <v>1.238758183620087</v>
@@ -28338,7 +28341,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28352,7 +28355,7 @@
         <v>1.216483509339664</v>
       </c>
       <c r="D540" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E540">
         <v>1.238758183620087</v>
@@ -28388,7 +28391,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28402,7 +28405,7 @@
         <v>1.171021231954409</v>
       </c>
       <c r="D541" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E541">
         <v>1.238758183620087</v>
@@ -28438,7 +28441,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28488,7 +28491,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28538,7 +28541,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28588,7 +28591,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28602,7 +28605,7 @@
         <v>0.913889681656368</v>
       </c>
       <c r="D545" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E545">
         <v>0.9422215166785484</v>
@@ -28638,7 +28641,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28652,7 +28655,7 @@
         <v>0.9595249171276929</v>
       </c>
       <c r="D546" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E546">
         <v>0.9422215166785484</v>
@@ -28688,7 +28691,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28702,7 +28705,7 @@
         <v>0.9589976550364385</v>
       </c>
       <c r="D547" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E547">
         <v>0.9422215166785484</v>
@@ -28738,7 +28741,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28752,7 +28755,7 @@
         <v>0.8504189521355614</v>
       </c>
       <c r="D548" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E548">
         <v>0.937857691146331</v>
@@ -28788,7 +28791,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28802,7 +28805,7 @@
         <v>0.9017680975637474</v>
       </c>
       <c r="D549" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E549">
         <v>0.937857691146331</v>
@@ -28838,7 +28841,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28852,7 +28855,7 @@
         <v>0.908653475416529</v>
       </c>
       <c r="D550" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E550">
         <v>0.937857691146331</v>
@@ -28888,7 +28891,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28938,7 +28941,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -28988,7 +28991,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29038,7 +29041,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29052,7 +29055,7 @@
         <v>0.7994059700977925</v>
       </c>
       <c r="D554" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E554">
         <v>0.9510460107817367</v>
@@ -29088,7 +29091,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29102,7 +29105,7 @@
         <v>0.8553475251011551</v>
       </c>
       <c r="D555" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E555">
         <v>0.9510460107817367</v>
@@ -29138,7 +29141,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29152,7 +29155,7 @@
         <v>0.8681906234838945</v>
       </c>
       <c r="D556" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E556">
         <v>0.9510460107817367</v>
@@ -29188,7 +29191,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29238,7 +29241,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29252,7 +29255,7 @@
         <v>0.7963844516425689</v>
       </c>
       <c r="D558" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E558">
         <v>0.9293442447455118</v>
@@ -29288,7 +29291,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29302,7 +29305,7 @@
         <v>0.9077462565202601</v>
       </c>
       <c r="D559" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E559">
         <v>0.9293442447455118</v>
@@ -29338,7 +29341,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29352,7 +29355,7 @@
         <v>0.8525980168231655</v>
       </c>
       <c r="D560" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E560">
         <v>0.9293442447455118</v>
@@ -29388,7 +29391,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29402,7 +29405,7 @@
         <v>0.8657939932736682</v>
       </c>
       <c r="D561" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E561">
         <v>0.9293442447455118</v>
@@ -29438,7 +29441,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29488,7 +29491,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29538,7 +29541,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29588,7 +29591,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29638,7 +29641,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29688,7 +29691,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29738,7 +29741,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -29788,7 +29791,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -29838,7 +29841,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -29888,7 +29891,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29938,7 +29941,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -29988,7 +29991,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30038,7 +30041,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30088,7 +30091,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30138,7 +30141,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30188,7 +30191,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30238,7 +30241,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30288,7 +30291,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30338,7 +30341,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30388,7 +30391,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30438,7 +30441,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30488,7 +30491,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30502,7 +30505,7 @@
         <v>0.751468861471289</v>
       </c>
       <c r="D583" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E583">
         <v>0.9385035221553486</v>
@@ -30538,7 +30541,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30552,7 +30555,7 @@
         <v>0.7709845877750583</v>
       </c>
       <c r="D584" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E584">
         <v>0.9385035221553486</v>
@@ -30588,7 +30591,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30602,7 +30605,7 @@
         <v>0.8117259226040443</v>
       </c>
       <c r="D585" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E585">
         <v>0.9385035221553486</v>
@@ -30638,7 +30641,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30652,7 +30655,7 @@
         <v>0.830167515424916</v>
       </c>
       <c r="D586" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E586">
         <v>0.9385035221553486</v>
@@ -30688,7 +30691,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30702,7 +30705,7 @@
         <v>0.8384277846341899</v>
       </c>
       <c r="D587" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E587">
         <v>0.9385035221553486</v>
@@ -30738,7 +30741,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31102,7 +31105,7 @@
         <v>0.8616555364163685</v>
       </c>
       <c r="D595" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E595">
         <v>0.9487042537756789</v>
@@ -31152,7 +31155,7 @@
         <v>0.8685708400378545</v>
       </c>
       <c r="D596" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E596">
         <v>0.9487042537756789</v>
@@ -31202,7 +31205,7 @@
         <v>0.9283666743289771</v>
       </c>
       <c r="D597" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E597">
         <v>0.9487042537756789</v>
@@ -31252,7 +31255,7 @@
         <v>0.9119931158630705</v>
       </c>
       <c r="D598" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E598">
         <v>0.9487042537756789</v>
@@ -31302,7 +31305,7 @@
         <v>0.917566191902035</v>
       </c>
       <c r="D599" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E599">
         <v>0.9487042537756789</v>
@@ -31352,7 +31355,7 @@
         <v>0.8850151504748149</v>
       </c>
       <c r="D600" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E600">
         <v>0.9487042537756789</v>
@@ -31402,7 +31405,7 @@
         <v>0.9303840608049012</v>
       </c>
       <c r="D601" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E601">
         <v>0.9487042537756789</v>
@@ -31452,7 +31455,7 @@
         <v>0.9319931158630701</v>
       </c>
       <c r="D602" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E602">
         <v>0.9487042537756789</v>
@@ -31538,7 +31541,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31588,7 +31591,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31638,7 +31641,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -31688,7 +31691,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31738,7 +31741,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31788,7 +31791,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31838,7 +31841,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31888,7 +31891,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -31938,7 +31941,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -31988,7 +31991,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32038,7 +32041,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32088,7 +32091,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32138,7 +32141,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32188,7 +32191,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32238,7 +32241,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32288,7 +32291,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32338,7 +32341,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32388,7 +32391,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32438,7 +32441,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32488,7 +32491,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32538,7 +32541,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32588,7 +32591,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32638,7 +32641,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32688,7 +32691,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32738,7 +32741,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32788,7 +32791,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32838,7 +32841,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32888,7 +32891,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32938,7 +32941,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -32988,7 +32991,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33038,7 +33041,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33088,7 +33091,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33138,7 +33141,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33188,7 +33191,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33238,7 +33241,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33288,7 +33291,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33302,7 +33305,7 @@
         <v>0.9426739735459577</v>
       </c>
       <c r="D639" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E639">
         <v>1.155481591635229</v>
@@ -33338,7 +33341,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33352,7 +33355,7 @@
         <v>0.9523699059372155</v>
       </c>
       <c r="D640" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E640">
         <v>0.9617333668754942</v>
@@ -33388,7 +33391,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33402,7 +33405,7 @@
         <v>0.9489115468641032</v>
       </c>
       <c r="D641" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E641">
         <v>0.9617333668754942</v>
@@ -33438,7 +33441,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33452,7 +33455,7 @@
         <v>0.994540984964766</v>
       </c>
       <c r="D642" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E642">
         <v>0.9617333668754942</v>
@@ -33488,7 +33491,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33502,7 +33505,7 @@
         <v>0.9895196820815877</v>
       </c>
       <c r="D643" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E643">
         <v>0.9617333668754942</v>
@@ -33538,7 +33541,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33552,7 +33555,7 @@
         <v>0.9598379516124478</v>
       </c>
       <c r="D644" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E644">
         <v>0.9617333668754942</v>
@@ -33588,7 +33591,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33602,7 +33605,7 @@
         <v>1.006089726852713</v>
       </c>
       <c r="D645" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E645">
         <v>0.9617333668754942</v>
@@ -33638,7 +33641,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33652,7 +33655,7 @@
         <v>0.9848592544956265</v>
       </c>
       <c r="D646" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E646">
         <v>0.9617333668754942</v>
@@ -33688,7 +33691,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33952,7 +33955,7 @@
         <v>0.9734565125913943</v>
       </c>
       <c r="D652" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E652">
         <v>1.185400334942146</v>
@@ -34002,7 +34005,7 @@
         <v>0.9846444558037319</v>
       </c>
       <c r="D653" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E653">
         <v>1.181231801994401</v>
@@ -34052,7 +34055,7 @@
         <v>0.9774953331205798</v>
       </c>
       <c r="D654" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E654">
         <v>1.181231801994401</v>
@@ -34102,7 +34105,7 @@
         <v>1.023910040074443</v>
       </c>
       <c r="D655" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E655">
         <v>1.181231801994401</v>
@@ -34152,7 +34155,7 @@
         <v>1.015119446695905</v>
       </c>
       <c r="D656" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E656">
         <v>1.181231801994401</v>
@@ -34202,7 +34205,7 @@
         <v>0.9864585657359251</v>
       </c>
       <c r="D657" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E657">
         <v>1.181231801994401</v>
@@ -34252,7 +34255,7 @@
         <v>1.007646508948263</v>
       </c>
       <c r="D658" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E658">
         <v>1.181231801994401</v>
@@ -34302,7 +34305,7 @@
         <v>1.015249159114463</v>
       </c>
       <c r="D659" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E659">
         <v>0.9834565125913941</v>
@@ -34388,7 +34391,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34438,7 +34441,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34488,7 +34491,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34538,7 +34541,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34588,7 +34591,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34602,7 +34605,7 @@
         <v>0.9989502799212269</v>
       </c>
       <c r="D665" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E665">
         <v>1.210178715943846</v>
@@ -34638,7 +34641,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34652,7 +34655,7 @@
         <v>1.011373890427612</v>
       </c>
       <c r="D666" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E666">
         <v>1.203864024011701</v>
@@ -34688,7 +34691,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -34702,7 +34705,7 @@
         <v>1.00116811706971</v>
       </c>
       <c r="D667" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E667">
         <v>1.203864024011701</v>
@@ -34738,7 +34741,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -34752,7 +34755,7 @@
         <v>1.048233175230966</v>
       </c>
       <c r="D668" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E668">
         <v>1.203864024011701</v>
@@ -34788,7 +34791,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -34802,7 +34805,7 @@
         <v>1.036320896056939</v>
       </c>
       <c r="D669" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E669">
         <v>1.203864024011701</v>
@@ -34838,7 +34841,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -34852,7 +34855,7 @@
         <v>1.008505471666571</v>
       </c>
       <c r="D670" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E670">
         <v>1.203864024011701</v>
@@ -34888,7 +34891,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -34902,7 +34905,7 @@
         <v>1.030929082172957</v>
       </c>
       <c r="D671" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E671">
         <v>1.203864024011701</v>
@@ -34938,7 +34941,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -34952,7 +34955,7 @@
         <v>1.040417750840599</v>
       </c>
       <c r="D672" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E672">
         <v>0.9957763031857296</v>
@@ -34988,7 +34991,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35038,7 +35041,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35088,7 +35091,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35138,7 +35141,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35188,7 +35191,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35202,7 +35205,7 @@
         <v>1.019721542843001</v>
       </c>
       <c r="D677" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E677">
         <v>1.230367111793835</v>
@@ -35238,7 +35241,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35252,7 +35255,7 @@
         <v>1.033151923746106</v>
       </c>
       <c r="D678" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E678">
         <v>1.222303818646338</v>
@@ -35288,7 +35291,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35302,7 +35305,7 @@
         <v>1.020455718354215</v>
       </c>
       <c r="D679" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E679">
         <v>1.222303818646338</v>
@@ -35338,7 +35341,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35352,7 +35355,7 @@
         <v>1.053594956548007</v>
       </c>
       <c r="D680" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E680">
         <v>1.222303818646338</v>
@@ -35388,7 +35391,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35402,7 +35405,7 @@
         <v>1.026468375060656</v>
       </c>
       <c r="D681" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E681">
         <v>1.222303818646338</v>
@@ -35438,7 +35441,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35452,7 +35455,7 @@
         <v>1.049898755963761</v>
       </c>
       <c r="D682" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E682">
         <v>1.222303818646338</v>
@@ -35488,7 +35491,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35502,7 +35505,7 @@
         <v>1.060924074184289</v>
       </c>
       <c r="D683" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E683">
         <v>1.017873442550878</v>
@@ -35538,7 +35541,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35588,7 +35591,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35638,7 +35641,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35688,7 +35691,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35738,7 +35741,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -35752,7 +35755,7 @@
         <v>1.047332978384417</v>
       </c>
       <c r="D688" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E688">
         <v>1.257203736644038</v>
@@ -35788,7 +35791,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -35802,7 +35805,7 @@
         <v>1.062101668663253</v>
       </c>
       <c r="D689" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E689">
         <v>1.2468160114229</v>
@@ -35838,7 +35841,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -35852,7 +35855,7 @@
         <v>1.046094908499815</v>
       </c>
       <c r="D690" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E690">
         <v>1.2468160114229</v>
@@ -35888,7 +35891,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -35902,7 +35905,7 @@
         <v>1.076557527942143</v>
       </c>
       <c r="D691" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E691">
         <v>1.2468160114229</v>
@@ -35938,7 +35941,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -35952,7 +35955,7 @@
         <v>1.050346631817136</v>
       </c>
       <c r="D692" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E692">
         <v>1.2468160114229</v>
@@ -35988,7 +35991,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36002,7 +36005,7 @@
         <v>1.075115322095972</v>
       </c>
       <c r="D693" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E693">
         <v>1.2468160114229</v>
@@ -36038,7 +36041,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36052,7 +36055,7 @@
         <v>1.043673116249803</v>
       </c>
       <c r="D694" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E694">
         <v>1.123802357990182</v>
@@ -36088,7 +36091,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36102,7 +36105,7 @@
         <v>3.006935468331325</v>
       </c>
       <c r="D695" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E695">
         <v>2.555888073696882</v>
@@ -36138,7 +36141,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36152,10 +36155,10 @@
         <v>3.139280458423625</v>
       </c>
       <c r="D696" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E696">
-        <v>3.208498795059524</v>
+        <v>2.993365929424353</v>
       </c>
       <c r="F696">
         <v>-1</v>
@@ -36164,10 +36167,10 @@
         <v>0.008580719541576375</v>
       </c>
       <c r="H696">
-        <v>0.008731501204940475</v>
+        <v>0.008306634070575648</v>
       </c>
       <c r="I696">
-        <v>-0.06921833663589938</v>
+        <v>0.1459145289992714</v>
       </c>
       <c r="J696">
         <v>0.5825951909157121</v>
@@ -36179,16 +36182,16 @@
         <v>5.86</v>
       </c>
       <c r="M696">
-        <v>4.74</v>
+        <v>4.56</v>
       </c>
       <c r="N696">
-        <v>5.97</v>
+        <v>5.65</v>
       </c>
       <c r="O696">
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36202,10 +36205,10 @@
         <v>3.093454506514468</v>
       </c>
       <c r="D697" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E697">
-        <v>3.208498795059524</v>
+        <v>2.993365929424353</v>
       </c>
       <c r="F697">
         <v>-1</v>
@@ -36214,10 +36217,10 @@
         <v>0.008546545493485533</v>
       </c>
       <c r="H697">
-        <v>0.008731501204940475</v>
+        <v>0.008306634070575648</v>
       </c>
       <c r="I697">
-        <v>-0.1150442885450564</v>
+        <v>0.1000885770901143</v>
       </c>
       <c r="J697">
         <v>0.5825951909157121</v>
@@ -36229,16 +36232,66 @@
         <v>5.82</v>
       </c>
       <c r="M697">
+        <v>4.56</v>
+      </c>
+      <c r="N697">
+        <v>5.65</v>
+      </c>
+      <c r="O697">
+        <v>1</v>
+      </c>
+      <c r="P697" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="698" spans="1:16">
+      <c r="A698" s="1">
+        <v>3</v>
+      </c>
+      <c r="B698" t="s">
+        <v>144</v>
+      </c>
+      <c r="C698">
+        <v>3.208498795059524</v>
+      </c>
+      <c r="D698" t="s">
+        <v>246</v>
+      </c>
+      <c r="E698">
+        <v>2.993365929424353</v>
+      </c>
+      <c r="F698">
+        <v>-1</v>
+      </c>
+      <c r="G698">
+        <v>0.008731501204940475</v>
+      </c>
+      <c r="H698">
+        <v>0.008306634070575648</v>
+      </c>
+      <c r="I698">
+        <v>0.2151328656351708</v>
+      </c>
+      <c r="J698">
+        <v>0.5825951909157121</v>
+      </c>
+      <c r="K698">
         <v>4.74</v>
       </c>
-      <c r="N697">
+      <c r="L698">
         <v>5.97</v>
       </c>
-      <c r="O697">
-        <v>1</v>
-      </c>
-      <c r="P697" t="s">
-        <v>239</v>
+      <c r="M698">
+        <v>4.56</v>
+      </c>
+      <c r="N698">
+        <v>5.65</v>
+      </c>
+      <c r="O698">
+        <v>1</v>
+      </c>
+      <c r="P698" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -754,7 +754,7 @@
     <t>2021-05-31</t>
   </si>
   <si>
-    <t>2021-08-04</t>
+    <t>2021-08-05</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -36158,7 +36158,7 @@
         <v>246</v>
       </c>
       <c r="E696">
-        <v>2.993365929424353</v>
+        <v>2.871625448515924</v>
       </c>
       <c r="F696">
         <v>-1</v>
@@ -36167,10 +36167,10 @@
         <v>0.008580719541576375</v>
       </c>
       <c r="H696">
-        <v>0.008306634070575648</v>
+        <v>0.008068374551484077</v>
       </c>
       <c r="I696">
-        <v>0.1459145289992714</v>
+        <v>0.2676550099077009</v>
       </c>
       <c r="J696">
         <v>0.5825951909157121</v>
@@ -36182,10 +36182,10 @@
         <v>5.86</v>
       </c>
       <c r="M696">
-        <v>4.56</v>
+        <v>4.46</v>
       </c>
       <c r="N696">
-        <v>5.65</v>
+        <v>5.47</v>
       </c>
       <c r="O696">
         <v>1</v>
@@ -36208,7 +36208,7 @@
         <v>246</v>
       </c>
       <c r="E697">
-        <v>2.993365929424353</v>
+        <v>2.871625448515924</v>
       </c>
       <c r="F697">
         <v>-1</v>
@@ -36217,10 +36217,10 @@
         <v>0.008546545493485533</v>
       </c>
       <c r="H697">
-        <v>0.008306634070575648</v>
+        <v>0.008068374551484077</v>
       </c>
       <c r="I697">
-        <v>0.1000885770901143</v>
+        <v>0.2218290579985438</v>
       </c>
       <c r="J697">
         <v>0.5825951909157121</v>
@@ -36232,10 +36232,10 @@
         <v>5.82</v>
       </c>
       <c r="M697">
-        <v>4.56</v>
+        <v>4.46</v>
       </c>
       <c r="N697">
-        <v>5.65</v>
+        <v>5.47</v>
       </c>
       <c r="O697">
         <v>1</v>
@@ -36258,7 +36258,7 @@
         <v>246</v>
       </c>
       <c r="E698">
-        <v>2.993365929424353</v>
+        <v>2.871625448515924</v>
       </c>
       <c r="F698">
         <v>-1</v>
@@ -36267,10 +36267,10 @@
         <v>0.008731501204940475</v>
       </c>
       <c r="H698">
-        <v>0.008306634070575648</v>
+        <v>0.008068374551484077</v>
       </c>
       <c r="I698">
-        <v>0.2151328656351708</v>
+        <v>0.3368733465436002</v>
       </c>
       <c r="J698">
         <v>0.5825951909157121</v>
@@ -36282,10 +36282,10 @@
         <v>5.97</v>
       </c>
       <c r="M698">
-        <v>4.56</v>
+        <v>4.46</v>
       </c>
       <c r="N698">
-        <v>5.65</v>
+        <v>5.47</v>
       </c>
       <c r="O698">
         <v>1</v>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="340">
   <si>
     <t>trade_time</t>
   </si>
@@ -439,13 +439,13 @@
     <t>2021-04-20</t>
   </si>
   <si>
-    <t>2021-05-12</t>
-  </si>
-  <si>
     <t>2021-07-09</t>
   </si>
   <si>
     <t>2021-07-16</t>
+  </si>
+  <si>
+    <t>2021-07-20</t>
   </si>
   <si>
     <t>2021-07-30</t>
@@ -751,10 +751,7 @@
     <t>2021-04-28</t>
   </si>
   <si>
-    <t>2021-05-31</t>
-  </si>
-  <si>
-    <t>2021-08-05</t>
+    <t>2021-08-09</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -1491,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1541,7 +1538,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1591,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1641,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1691,7 +1688,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1741,7 +1738,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1791,7 +1788,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1841,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1891,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1941,7 +1938,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1991,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2041,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2091,7 +2088,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2141,7 +2138,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2191,7 +2188,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2241,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2291,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2341,7 +2338,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2391,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2441,7 +2438,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2491,7 +2488,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2541,7 +2538,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2591,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2641,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2691,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2741,7 +2738,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2791,7 +2788,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2841,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2891,7 +2888,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2941,7 +2938,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2991,7 +2988,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3041,7 +3038,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3091,7 +3088,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3141,7 +3138,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3191,7 +3188,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3241,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3291,7 +3288,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3341,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3391,7 +3388,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3441,7 +3438,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3491,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3541,7 +3538,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3591,7 +3588,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3641,7 +3638,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3691,7 +3688,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4741,7 +4738,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4791,7 +4788,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4841,7 +4838,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4891,7 +4888,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4941,7 +4938,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4991,7 +4988,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5041,7 +5038,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5091,7 +5088,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5141,7 +5138,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5191,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5241,7 +5238,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5291,7 +5288,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5341,7 +5338,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5391,7 +5388,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5441,7 +5438,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5491,7 +5488,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5541,7 +5538,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5591,7 +5588,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5641,7 +5638,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5691,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5741,7 +5738,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5791,7 +5788,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5841,7 +5838,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5891,7 +5888,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5941,7 +5938,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5991,7 +5988,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6291,7 +6288,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6341,7 +6338,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6391,7 +6388,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6441,7 +6438,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6491,7 +6488,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6541,7 +6538,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6591,7 +6588,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6641,7 +6638,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6691,7 +6688,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6741,7 +6738,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6791,7 +6788,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6841,7 +6838,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6891,7 +6888,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7241,7 +7238,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7291,7 +7288,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7341,7 +7338,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7391,7 +7388,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7441,7 +7438,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7491,7 +7488,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7541,7 +7538,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7591,7 +7588,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7641,7 +7638,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7691,7 +7688,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7741,7 +7738,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7791,7 +7788,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7841,7 +7838,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8691,7 +8688,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8741,7 +8738,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8791,7 +8788,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8841,7 +8838,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8891,7 +8888,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8941,7 +8938,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9091,7 +9088,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9141,7 +9138,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9191,7 +9188,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9241,7 +9238,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9291,7 +9288,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9341,7 +9338,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9391,7 +9388,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9441,7 +9438,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9491,7 +9488,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9541,7 +9538,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9591,7 +9588,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9641,7 +9638,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9991,7 +9988,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10041,7 +10038,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10191,7 +10188,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10241,7 +10238,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10291,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10341,7 +10338,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10391,7 +10388,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10441,7 +10438,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10491,7 +10488,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10541,7 +10538,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10591,7 +10588,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10641,7 +10638,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10691,7 +10688,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10741,7 +10738,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10791,7 +10788,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10841,7 +10838,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10891,7 +10888,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10941,7 +10938,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10991,7 +10988,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11041,7 +11038,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11091,7 +11088,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11141,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11191,7 +11188,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11241,7 +11238,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11291,7 +11288,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11341,7 +11338,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11391,7 +11388,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11441,7 +11438,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11491,7 +11488,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11541,7 +11538,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11591,7 +11588,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11641,7 +11638,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11691,7 +11688,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11741,7 +11738,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11791,7 +11788,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11841,7 +11838,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11891,7 +11888,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11941,7 +11938,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11991,7 +11988,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12041,7 +12038,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12091,7 +12088,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12141,7 +12138,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12191,7 +12188,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12241,7 +12238,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12291,7 +12288,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12341,7 +12338,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12391,7 +12388,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12441,7 +12438,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12491,7 +12488,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12541,7 +12538,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12841,7 +12838,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12891,7 +12888,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12941,7 +12938,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12991,7 +12988,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13041,7 +13038,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13091,7 +13088,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13141,7 +13138,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13491,7 +13488,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13541,7 +13538,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13591,7 +13588,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13641,7 +13638,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13691,7 +13688,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13741,7 +13738,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13791,7 +13788,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13841,7 +13838,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13891,7 +13888,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13941,7 +13938,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13991,7 +13988,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14041,7 +14038,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14091,7 +14088,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14141,7 +14138,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14191,7 +14188,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14241,7 +14238,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14291,7 +14288,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14341,7 +14338,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14641,7 +14638,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14691,7 +14688,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14741,7 +14738,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14791,7 +14788,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14841,7 +14838,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14891,7 +14888,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14941,7 +14938,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14991,7 +14988,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15041,7 +15038,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15091,7 +15088,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15141,7 +15138,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15191,7 +15188,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15241,7 +15238,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15291,7 +15288,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15341,7 +15338,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15391,7 +15388,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15441,7 +15438,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15491,7 +15488,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15541,7 +15538,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15591,7 +15588,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15641,7 +15638,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15691,7 +15688,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15741,7 +15738,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15791,7 +15788,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15841,7 +15838,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15891,7 +15888,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15941,7 +15938,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15991,7 +15988,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16041,7 +16038,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16091,7 +16088,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16141,7 +16138,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16191,7 +16188,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16241,7 +16238,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16291,7 +16288,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16341,7 +16338,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16391,7 +16388,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16441,7 +16438,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16491,7 +16488,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16541,7 +16538,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16591,7 +16588,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16641,7 +16638,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16691,7 +16688,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16741,7 +16738,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16791,7 +16788,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16841,7 +16838,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16891,7 +16888,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -16941,7 +16938,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -16991,7 +16988,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17041,7 +17038,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17091,7 +17088,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17141,7 +17138,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17191,7 +17188,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17241,7 +17238,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17291,7 +17288,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17341,7 +17338,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17391,7 +17388,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17441,7 +17438,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17491,7 +17488,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17541,7 +17538,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17591,7 +17588,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17641,7 +17638,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17691,7 +17688,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17741,7 +17738,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17791,7 +17788,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17841,7 +17838,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17891,7 +17888,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17941,7 +17938,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17991,7 +17988,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18041,7 +18038,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18091,7 +18088,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18141,7 +18138,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18191,7 +18188,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18241,7 +18238,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18291,7 +18288,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18341,7 +18338,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18391,7 +18388,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18441,7 +18438,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18491,7 +18488,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18691,7 +18688,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18741,7 +18738,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18791,7 +18788,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18841,7 +18838,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18891,7 +18888,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18941,7 +18938,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19191,7 +19188,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19241,7 +19238,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19291,7 +19288,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19341,7 +19338,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19591,7 +19588,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19641,7 +19638,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19691,7 +19688,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19741,7 +19738,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19791,7 +19788,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19841,7 +19838,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19891,7 +19888,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19941,7 +19938,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19991,7 +19988,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20041,7 +20038,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20091,7 +20088,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20141,7 +20138,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20191,7 +20188,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20241,7 +20238,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20691,7 +20688,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20741,7 +20738,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20791,7 +20788,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20841,7 +20838,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20891,7 +20888,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20941,7 +20938,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20991,7 +20988,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21041,7 +21038,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21091,7 +21088,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21141,7 +21138,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21191,7 +21188,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21241,7 +21238,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21291,7 +21288,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21341,7 +21338,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21391,7 +21388,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21441,7 +21438,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21491,7 +21488,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21541,7 +21538,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21591,7 +21588,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21641,7 +21638,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21691,7 +21688,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22041,7 +22038,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22091,7 +22088,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22141,7 +22138,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22191,7 +22188,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22241,7 +22238,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22291,7 +22288,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22341,7 +22338,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22391,7 +22388,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22441,7 +22438,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22491,7 +22488,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22541,7 +22538,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22591,7 +22588,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23391,7 +23388,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23441,7 +23438,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23491,7 +23488,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23541,7 +23538,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23591,7 +23588,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23641,7 +23638,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23691,7 +23688,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23741,7 +23738,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23791,7 +23788,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23841,7 +23838,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23891,7 +23888,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23941,7 +23938,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23991,7 +23988,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24041,7 +24038,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24091,7 +24088,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24141,7 +24138,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24191,7 +24188,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24241,7 +24238,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24291,7 +24288,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24341,7 +24338,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24391,7 +24388,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24441,7 +24438,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24491,7 +24488,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24541,7 +24538,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24591,7 +24588,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24641,7 +24638,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24691,7 +24688,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24741,7 +24738,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24791,7 +24788,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24841,7 +24838,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24891,7 +24888,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24941,7 +24938,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24991,7 +24988,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25141,7 +25138,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25191,7 +25188,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25241,7 +25238,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25291,7 +25288,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25341,7 +25338,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25391,7 +25388,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25441,7 +25438,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25491,7 +25488,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25541,7 +25538,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25591,7 +25588,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25641,7 +25638,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25841,7 +25838,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25891,7 +25888,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25941,7 +25938,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25991,7 +25988,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26041,7 +26038,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26091,7 +26088,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26141,7 +26138,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26191,7 +26188,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26241,7 +26238,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26291,7 +26288,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26341,7 +26338,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26391,7 +26388,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26441,7 +26438,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26491,7 +26488,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26541,7 +26538,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26591,7 +26588,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26641,7 +26638,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26691,7 +26688,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26741,7 +26738,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26791,7 +26788,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26841,7 +26838,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26891,7 +26888,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26941,7 +26938,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26991,7 +26988,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27041,7 +27038,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27091,7 +27088,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27141,7 +27138,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27191,7 +27188,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27541,7 +27538,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27591,7 +27588,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27641,7 +27638,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27691,7 +27688,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27741,7 +27738,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27791,7 +27788,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28091,7 +28088,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28141,7 +28138,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28191,7 +28188,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28241,7 +28238,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28291,7 +28288,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28341,7 +28338,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28391,7 +28388,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28441,7 +28438,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28491,7 +28488,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28541,7 +28538,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28591,7 +28588,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28641,7 +28638,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28691,7 +28688,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28741,7 +28738,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28791,7 +28788,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28841,7 +28838,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28891,7 +28888,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28941,7 +28938,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -28991,7 +28988,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29041,7 +29038,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29091,7 +29088,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29141,7 +29138,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29191,7 +29188,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29241,7 +29238,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29291,7 +29288,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29341,7 +29338,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29391,7 +29388,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29441,7 +29438,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29491,7 +29488,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29541,7 +29538,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29591,7 +29588,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29641,7 +29638,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29691,7 +29688,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29741,7 +29738,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -29791,7 +29788,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -29841,7 +29838,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -29891,7 +29888,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29941,7 +29938,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -29991,7 +29988,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30041,7 +30038,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30091,7 +30088,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30141,7 +30138,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30191,7 +30188,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30241,7 +30238,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30291,7 +30288,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30341,7 +30338,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30391,7 +30388,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30441,7 +30438,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30491,7 +30488,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30541,7 +30538,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30591,7 +30588,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30641,7 +30638,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30691,7 +30688,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30741,7 +30738,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -32291,7 +32288,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32341,7 +32338,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32391,7 +32388,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32441,7 +32438,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32491,7 +32488,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32541,7 +32538,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32591,7 +32588,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32641,7 +32638,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32691,7 +32688,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32741,7 +32738,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32791,7 +32788,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32841,7 +32838,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32891,7 +32888,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32941,7 +32938,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -32991,7 +32988,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33041,7 +33038,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33091,7 +33088,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33141,7 +33138,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33191,7 +33188,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33241,7 +33238,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33291,7 +33288,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33341,7 +33338,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33391,7 +33388,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33441,7 +33438,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33491,7 +33488,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33541,7 +33538,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33591,7 +33588,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33641,7 +33638,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33691,7 +33688,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34391,7 +34388,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34441,7 +34438,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34491,7 +34488,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34541,7 +34538,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34591,7 +34588,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34641,7 +34638,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34691,7 +34688,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -34741,7 +34738,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -34791,7 +34788,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -34841,7 +34838,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -34891,7 +34888,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -34941,7 +34938,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -34991,7 +34988,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35591,7 +35588,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35641,7 +35638,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35691,7 +35688,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35741,7 +35738,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -35791,7 +35788,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -35841,7 +35838,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -35891,7 +35888,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -35941,7 +35938,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -35991,7 +35988,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36041,7 +36038,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36091,7 +36088,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36102,40 +36099,40 @@
         <v>141</v>
       </c>
       <c r="C695">
-        <v>3.006935468331325</v>
+        <v>3.139280458423625</v>
       </c>
       <c r="D695" t="s">
         <v>245</v>
       </c>
       <c r="E695">
-        <v>2.555888073696882</v>
+        <v>3.025106410332782</v>
       </c>
       <c r="F695">
         <v>-1</v>
       </c>
       <c r="G695">
-        <v>0.008693064531668675</v>
+        <v>0.008580719541576375</v>
       </c>
       <c r="H695">
-        <v>0.007904111926303119</v>
+        <v>0.008454893589667219</v>
       </c>
       <c r="I695">
-        <v>0.4510473946344429</v>
+        <v>0.1141740480908431</v>
       </c>
       <c r="J695">
         <v>0.5825951909157121</v>
       </c>
       <c r="K695">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="L695">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="M695">
-        <v>4.59</v>
+        <v>4.66</v>
       </c>
       <c r="N695">
-        <v>5.23</v>
+        <v>5.74</v>
       </c>
       <c r="O695">
         <v>1</v>
@@ -36152,40 +36149,40 @@
         <v>142</v>
       </c>
       <c r="C696">
-        <v>3.139280458423625</v>
+        <v>3.093454506514468</v>
       </c>
       <c r="D696" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E696">
-        <v>2.871625448515924</v>
+        <v>3.025106410332782</v>
       </c>
       <c r="F696">
         <v>-1</v>
       </c>
       <c r="G696">
-        <v>0.008580719541576375</v>
+        <v>0.008546545493485533</v>
       </c>
       <c r="H696">
-        <v>0.008068374551484077</v>
+        <v>0.008454893589667219</v>
       </c>
       <c r="I696">
-        <v>0.2676550099077009</v>
+        <v>0.06834809618168602</v>
       </c>
       <c r="J696">
         <v>0.5825951909157121</v>
       </c>
       <c r="K696">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="L696">
-        <v>5.86</v>
+        <v>5.82</v>
       </c>
       <c r="M696">
-        <v>4.46</v>
+        <v>4.66</v>
       </c>
       <c r="N696">
-        <v>5.47</v>
+        <v>5.74</v>
       </c>
       <c r="O696">
         <v>1</v>
@@ -36202,40 +36199,40 @@
         <v>143</v>
       </c>
       <c r="C697">
-        <v>3.093454506514468</v>
+        <v>3.013365929424353</v>
       </c>
       <c r="D697" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E697">
-        <v>2.871625448515924</v>
+        <v>3.025106410332782</v>
       </c>
       <c r="F697">
         <v>-1</v>
       </c>
       <c r="G697">
-        <v>0.008546545493485533</v>
+        <v>0.008326634070575647</v>
       </c>
       <c r="H697">
-        <v>0.008068374551484077</v>
+        <v>0.008454893589667219</v>
       </c>
       <c r="I697">
-        <v>0.2218290579985438</v>
+        <v>-0.01174048090842872</v>
       </c>
       <c r="J697">
         <v>0.5825951909157121</v>
       </c>
       <c r="K697">
-        <v>4.68</v>
+        <v>4.56</v>
       </c>
       <c r="L697">
-        <v>5.82</v>
+        <v>5.67</v>
       </c>
       <c r="M697">
-        <v>4.46</v>
+        <v>4.66</v>
       </c>
       <c r="N697">
-        <v>5.47</v>
+        <v>5.74</v>
       </c>
       <c r="O697">
         <v>1</v>
@@ -36255,10 +36252,10 @@
         <v>3.208498795059524</v>
       </c>
       <c r="D698" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E698">
-        <v>2.871625448515924</v>
+        <v>3.025106410332782</v>
       </c>
       <c r="F698">
         <v>-1</v>
@@ -36267,10 +36264,10 @@
         <v>0.008731501204940475</v>
       </c>
       <c r="H698">
-        <v>0.008068374551484077</v>
+        <v>0.008454893589667219</v>
       </c>
       <c r="I698">
-        <v>0.3368733465436002</v>
+        <v>0.1833923847267425</v>
       </c>
       <c r="J698">
         <v>0.5825951909157121</v>
@@ -36282,10 +36279,10 @@
         <v>5.97</v>
       </c>
       <c r="M698">
-        <v>4.46</v>
+        <v>4.66</v>
       </c>
       <c r="N698">
-        <v>5.47</v>
+        <v>5.74</v>
       </c>
       <c r="O698">
         <v>1</v>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="346">
   <si>
     <t>trade_time</t>
   </si>
@@ -451,6 +451,9 @@
     <t>2021-07-30</t>
   </si>
   <si>
+    <t>2021-11-03</t>
+  </si>
+  <si>
     <t>2017-04-20</t>
   </si>
   <si>
@@ -754,6 +757,9 @@
     <t>2021-08-09</t>
   </si>
   <si>
+    <t>2021-11-04</t>
+  </si>
+  <si>
     <t>2017-03-09</t>
   </si>
   <si>
@@ -1034,6 +1040,18 @@
   </si>
   <si>
     <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>2021-10-28</t>
+  </si>
+  <si>
+    <t>2021-10-29</t>
+  </si>
+  <si>
+    <t>2021-11-01</t>
+  </si>
+  <si>
+    <t>2021-11-02</t>
   </si>
 </sst>
 </file>
@@ -1391,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P698"/>
+  <dimension ref="A1:P702"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1452,7 +1470,7 @@
         <v>1.855441043116508</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E2">
         <v>1.575397067571232</v>
@@ -1488,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1502,7 +1520,7 @@
         <v>1.844886436180541</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E3">
         <v>1.575397067571232</v>
@@ -1538,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1552,7 +1570,7 @@
         <v>1.879543169394645</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E4">
         <v>1.575397067571232</v>
@@ -1588,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1602,7 +1620,7 @@
         <v>1.931893523774336</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E5">
         <v>1.575397067571232</v>
@@ -1638,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1652,7 +1670,7 @@
         <v>1.864287853699299</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E6">
         <v>1.610229702966436</v>
@@ -1688,7 +1706,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1702,7 +1720,7 @@
         <v>1.420828285447678</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E7">
         <v>1.720097776330612</v>
@@ -1738,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1752,7 +1770,7 @@
         <v>1.444930411725815</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E8">
         <v>1.720097776330612</v>
@@ -1788,7 +1806,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1802,7 +1820,7 @@
         <v>1.415528994207057</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E9">
         <v>1.720097776330612</v>
@@ -1838,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1852,7 +1870,7 @@
         <v>1.417747421950922</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E10">
         <v>1.720097776330612</v>
@@ -1888,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1902,7 +1920,7 @@
         <v>1.837391318446252</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E11">
         <v>1.556576374761795</v>
@@ -1938,7 +1956,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1952,7 +1970,7 @@
         <v>1.827426275381424</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E12">
         <v>1.556576374761795</v>
@@ -1988,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2002,7 +2020,7 @@
         <v>1.861221338322326</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E13">
         <v>1.556576374761795</v>
@@ -2038,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2052,7 +2070,7 @@
         <v>1.913526341635005</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14">
         <v>1.556576374761795</v>
@@ -2088,7 +2106,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2102,7 +2120,7 @@
         <v>1.84664628863214</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E15">
         <v>1.593631212440523</v>
@@ -2138,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2152,7 +2170,7 @@
         <v>1.404411199189807</v>
       </c>
       <c r="D16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E16">
         <v>1.701186381387154</v>
@@ -2188,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2202,7 +2220,7 @@
         <v>1.428241219065881</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E17">
         <v>1.701186381387154</v>
@@ -2238,7 +2256,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2252,7 +2270,7 @@
         <v>1.399021205815165</v>
       </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E18">
         <v>1.701186381387154</v>
@@ -2288,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2302,7 +2320,7 @@
         <v>1.398881378074474</v>
       </c>
       <c r="D19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E19">
         <v>1.701186381387154</v>
@@ -2338,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2352,7 +2370,7 @@
         <v>1.772601053603223</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20">
         <v>1.513212850115657</v>
@@ -2388,7 +2406,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2402,7 +2420,7 @@
         <v>1.819007208305362</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E21">
         <v>1.513212850115657</v>
@@ -2438,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2452,7 +2470,7 @@
         <v>1.871207721197208</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E22">
         <v>1.513212850115657</v>
@@ -2488,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2502,7 +2520,7 @@
         <v>1.805999514927688</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E23">
         <v>1.555387718415254</v>
@@ -2538,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2552,7 +2570,7 @@
         <v>1.366585666847875</v>
       </c>
       <c r="D24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E24">
         <v>1.657613875899347</v>
@@ -2588,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2602,7 +2620,7 @@
         <v>1.360986692631565</v>
       </c>
       <c r="D25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E25">
         <v>1.657613875899347</v>
@@ -2638,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2652,7 +2670,7 @@
         <v>1.355413363007501</v>
       </c>
       <c r="D26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E26">
         <v>1.657613875899347</v>
@@ -2688,7 +2706,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2702,7 +2720,7 @@
         <v>1.746707087766096</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E27">
         <v>1.485799595466657</v>
@@ -2738,7 +2756,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2752,7 +2770,7 @@
         <v>1.792320570044649</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28">
         <v>1.485799595466657</v>
@@ -2788,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2802,7 +2820,7 @@
         <v>1.780303717196457</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E29">
         <v>1.531211209495895</v>
@@ -2838,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2852,7 +2870,7 @@
         <v>1.342673382069711</v>
       </c>
       <c r="D30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E30">
         <v>1.63006850917975</v>
@@ -2888,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2902,7 +2920,7 @@
         <v>1.336942295782803</v>
       </c>
       <c r="D31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E31">
         <v>1.63006850917975</v>
@@ -2938,7 +2956,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2952,7 +2970,7 @@
         <v>1.327934052323203</v>
       </c>
       <c r="D32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E32">
         <v>1.63006850917975</v>
@@ -2988,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3002,7 +3020,7 @@
         <v>1.724897025074506</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E33">
         <v>1.462709860729388</v>
@@ -3038,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3052,7 +3070,7 @@
         <v>1.713714740951758</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34">
         <v>1.462709860729388</v>
@@ -3088,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3102,7 +3120,7 @@
         <v>1.769842852372705</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35">
         <v>1.462709860729388</v>
@@ -3138,7 +3156,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3152,7 +3170,7 @@
         <v>1.758660568249956</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E36">
         <v>1.510847732595075</v>
@@ -3188,7 +3206,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3202,7 +3220,7 @@
         <v>1.322532456829009</v>
       </c>
       <c r="D37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E37">
         <v>1.606867498612421</v>
@@ -3238,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3252,7 +3270,7 @@
         <v>1.316690094712042</v>
       </c>
       <c r="D38" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E38">
         <v>1.606867498612421</v>
@@ -3288,7 +3306,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3302,7 +3320,7 @@
         <v>1.304788679670904</v>
       </c>
       <c r="D39" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E39">
         <v>1.606867498612421</v>
@@ -3338,7 +3356,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3352,7 +3370,7 @@
         <v>1.698715924927888</v>
       </c>
       <c r="D40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E40">
         <v>1.451820073210847</v>
@@ -3388,7 +3406,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3402,7 +3420,7 @@
         <v>1.703822090603589</v>
       </c>
       <c r="D41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E41">
         <v>1.451820073210847</v>
@@ -3438,7 +3456,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3452,7 +3470,7 @@
         <v>1.759241709824535</v>
       </c>
       <c r="D42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E42">
         <v>1.451820073210847</v>
@@ -3488,7 +3506,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3502,7 +3520,7 @@
         <v>1.748453032479565</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E43">
         <v>1.501243727217277</v>
@@ -3538,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3552,7 +3570,7 @@
         <v>1.313033413258619</v>
       </c>
       <c r="D44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E44">
         <v>1.595925230190177</v>
@@ -3588,7 +3606,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3602,7 +3620,7 @@
         <v>1.307138570237948</v>
       </c>
       <c r="D45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E45">
         <v>1.595925230190177</v>
@@ -3638,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3652,7 +3670,7 @@
         <v>1.293872651700511</v>
       </c>
       <c r="D46" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E46">
         <v>1.595925230190177</v>
@@ -3688,7 +3706,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3702,7 +3720,7 @@
         <v>1.708440278144118</v>
       </c>
       <c r="D47" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E47">
         <v>1.445287539361757</v>
@@ -3752,7 +3770,7 @@
         <v>1.75288232747506</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E48">
         <v>1.445287539361757</v>
@@ -3802,7 +3820,7 @@
         <v>1.742329765811383</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E49">
         <v>1.495482504593743</v>
@@ -3852,7 +3870,7 @@
         <v>1.307335154816763</v>
       </c>
       <c r="D50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E50">
         <v>1.589361214250248</v>
@@ -3902,7 +3920,7 @@
         <v>1.301408829705253</v>
       </c>
       <c r="D51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E51">
         <v>1.589361214250248</v>
@@ -3952,7 +3970,7 @@
         <v>1.287324376806003</v>
       </c>
       <c r="D52" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E52">
         <v>1.589361214250248</v>
@@ -4002,7 +4020,7 @@
         <v>1.741577671463358</v>
       </c>
       <c r="D53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E53">
         <v>1.433675083310133</v>
@@ -4052,7 +4070,7 @@
         <v>1.793586527085793</v>
       </c>
       <c r="D54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E54">
         <v>1.433675083310133</v>
@@ -4102,7 +4120,7 @@
         <v>1.731444837126847</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E55">
         <v>1.485241157810864</v>
@@ -4152,7 +4170,7 @@
         <v>1.297205735321128</v>
       </c>
       <c r="D56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E56">
         <v>1.577692794555001</v>
@@ -4202,7 +4220,7 @@
         <v>1.291223446565996</v>
       </c>
       <c r="D57" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E57">
         <v>1.577692794555001</v>
@@ -4252,7 +4270,7 @@
         <v>1.275683938932566</v>
       </c>
       <c r="D58" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E58">
         <v>1.577692794555001</v>
@@ -4352,7 +4370,7 @@
         <v>1.725587143730334</v>
       </c>
       <c r="D60" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E60">
         <v>1.417249169921011</v>
@@ -4402,7 +4420,7 @@
         <v>1.777556418838578</v>
       </c>
       <c r="D61" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E61">
         <v>1.417249169921011</v>
@@ -4452,7 +4470,7 @@
         <v>1.716048017106683</v>
       </c>
       <c r="D62" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E62">
         <v>1.470754689617085</v>
@@ -4502,7 +4520,7 @@
         <v>1.282877589184112</v>
       </c>
       <c r="D63" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E63">
         <v>1.561187720137498</v>
@@ -4552,7 +4570,7 @@
         <v>1.276816139400598</v>
       </c>
       <c r="D64" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E64">
         <v>1.561187720137498</v>
@@ -4602,7 +4620,7 @@
         <v>1.259218445029255</v>
       </c>
       <c r="D65" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E65">
         <v>1.561187720137498</v>
@@ -4652,7 +4670,7 @@
         <v>1.799190602173319</v>
       </c>
       <c r="D66" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E66">
         <v>1.767682200441425</v>
@@ -4702,7 +4720,7 @@
         <v>1.704528128435052</v>
       </c>
       <c r="D67" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E67">
         <v>1.395616765595412</v>
@@ -4738,7 +4756,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4752,7 +4770,7 @@
         <v>1.756445277267813</v>
       </c>
       <c r="D68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E68">
         <v>1.395616765595412</v>
@@ -4788,7 +4806,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4802,7 +4820,7 @@
         <v>1.695770895943651</v>
       </c>
       <c r="D69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E69">
         <v>1.451676472790171</v>
@@ -4838,7 +4856,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4852,7 +4870,7 @@
         <v>1.264007877459131</v>
       </c>
       <c r="D70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E70">
         <v>1.539451063260933</v>
@@ -4888,7 +4906,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4902,7 +4920,7 @@
         <v>1.257842175124651</v>
       </c>
       <c r="D71" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E71">
         <v>1.539451063260933</v>
@@ -4938,7 +4956,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4952,7 +4970,7 @@
         <v>1.237533914428172</v>
       </c>
       <c r="D72" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E72">
         <v>1.539451063260933</v>
@@ -4988,7 +5006,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5038,7 +5056,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5052,7 +5070,7 @@
         <v>1.678683818930752</v>
       </c>
       <c r="D74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E74">
         <v>1.369068774396689</v>
@@ -5088,7 +5106,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5102,7 +5120,7 @@
         <v>1.730536996700383</v>
       </c>
       <c r="D75" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E75">
         <v>1.369068774396689</v>
@@ -5138,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5152,7 +5170,7 @@
         <v>1.670886152386294</v>
       </c>
       <c r="D76" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E76">
         <v>1.428263063684791</v>
@@ -5188,7 +5206,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5202,7 +5220,7 @@
         <v>1.240850352606269</v>
       </c>
       <c r="D77" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E77">
         <v>1.51277512993595</v>
@@ -5238,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5252,7 +5270,7 @@
         <v>1.234556708145529</v>
       </c>
       <c r="D78" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E78">
         <v>1.51277512993595</v>
@@ -5288,7 +5306,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5302,7 +5320,7 @@
         <v>1.210921952166319</v>
       </c>
       <c r="D79" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E79">
         <v>1.51277512993595</v>
@@ -5338,7 +5356,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5352,7 +5370,7 @@
         <v>1.661963549027058</v>
       </c>
       <c r="D80" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E80">
         <v>1.351893249619379</v>
@@ -5388,7 +5406,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5402,7 +5420,7 @@
         <v>1.713775339989997</v>
       </c>
       <c r="D81" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E81">
         <v>1.351893249619379</v>
@@ -5438,7 +5456,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5452,7 +5470,7 @@
         <v>1.654786684582984</v>
       </c>
       <c r="D82" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E82">
         <v>1.413115492435404</v>
@@ -5488,7 +5506,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5502,7 +5520,7 @@
         <v>1.225868328583652</v>
       </c>
       <c r="D83" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E83">
         <v>1.495516831545256</v>
@@ -5538,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5552,7 +5570,7 @@
         <v>1.219491910509528</v>
       </c>
       <c r="D84" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E84">
         <v>1.495516831545256</v>
@@ -5588,7 +5606,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5602,7 +5620,7 @@
         <v>1.193705040582317</v>
       </c>
       <c r="D85" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E85">
         <v>1.495516831545256</v>
@@ -5638,7 +5656,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5652,7 +5670,7 @@
         <v>1.600429769178104</v>
       </c>
       <c r="D86" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E86">
         <v>1.338006244585976</v>
@@ -5688,7 +5706,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5702,7 +5720,7 @@
         <v>1.648444633283697</v>
       </c>
       <c r="D87" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E87">
         <v>1.338006244585976</v>
@@ -5738,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5752,7 +5770,7 @@
         <v>1.700222961583904</v>
       </c>
       <c r="D88" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E88">
         <v>1.338006244585976</v>
@@ -5788,7 +5806,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5802,7 +5820,7 @@
         <v>1.641769708780589</v>
       </c>
       <c r="D89" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E89">
         <v>1.400868157875824</v>
@@ -5838,7 +5856,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5852,7 +5870,7 @@
         <v>1.213754844674996</v>
       </c>
       <c r="D90" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E90">
         <v>1.48156290118639</v>
@@ -5888,7 +5906,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5902,7 +5920,7 @@
         <v>1.20731150127541</v>
       </c>
       <c r="D91" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E91">
         <v>1.48156290118639</v>
@@ -5938,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5952,7 +5970,7 @@
         <v>1.179784572886182</v>
       </c>
       <c r="D92" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E92">
         <v>1.48156290118639</v>
@@ -5988,7 +6006,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6002,7 +6020,7 @@
         <v>1.642770386608872</v>
       </c>
       <c r="D93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E93">
         <v>1.332177501095747</v>
@@ -6052,7 +6070,7 @@
         <v>1.636306139581315</v>
       </c>
       <c r="D94" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E94">
         <v>1.395727627472394</v>
@@ -6102,7 +6120,7 @@
         <v>1.208670494931713</v>
       </c>
       <c r="D95" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E95">
         <v>1.475706067366088</v>
@@ -6152,7 +6170,7 @@
         <v>1.202199061202053</v>
       </c>
       <c r="D96" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E96">
         <v>1.475706067366088</v>
@@ -6202,7 +6220,7 @@
         <v>1.173941784230917</v>
       </c>
       <c r="D97" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E97">
         <v>1.475706067366088</v>
@@ -6252,7 +6270,7 @@
         <v>1.635648220856852</v>
       </c>
       <c r="D98" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E98">
         <v>1.324861414989093</v>
@@ -6288,7 +6306,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6302,7 +6320,7 @@
         <v>1.687394874868875</v>
       </c>
       <c r="D99" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E99">
         <v>1.324861414989093</v>
@@ -6338,7 +6356,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6352,7 +6370,7 @@
         <v>1.629448410676523</v>
       </c>
       <c r="D100" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E100">
         <v>1.38927536840002</v>
@@ -6388,7 +6406,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6402,7 +6420,7 @@
         <v>1.202288752351933</v>
       </c>
       <c r="D101" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E101">
         <v>1.468354723013138</v>
@@ -6438,7 +6456,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6452,7 +6470,7 @@
         <v>1.195782060375976</v>
       </c>
       <c r="D102" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E102">
         <v>1.468354723013138</v>
@@ -6488,7 +6506,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6502,7 +6520,7 @@
         <v>1.166608069001115</v>
       </c>
       <c r="D103" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E103">
         <v>1.468354723013138</v>
@@ -6538,7 +6556,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6552,7 +6570,7 @@
         <v>1.636237432923918</v>
       </c>
       <c r="D104" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E104">
         <v>1.325466669958976</v>
@@ -6588,7 +6606,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6602,7 +6620,7 @@
         <v>1.687985545381652</v>
       </c>
       <c r="D105" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E105">
         <v>1.325466669958976</v>
@@ -6638,7 +6656,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6652,7 +6670,7 @@
         <v>1.630015746057932</v>
       </c>
       <c r="D106" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E106">
         <v>1.389809159530085</v>
@@ -6688,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6702,7 +6720,7 @@
         <v>1.202816709699155</v>
       </c>
       <c r="D107" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E107">
         <v>1.468962894874441</v>
@@ -6738,7 +6756,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6752,7 +6770,7 @@
         <v>1.19631293461462</v>
       </c>
       <c r="D108" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E108">
         <v>1.468962894874441</v>
@@ -6788,7 +6806,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6802,7 +6820,7 @@
         <v>1.167214782416708</v>
       </c>
       <c r="D109" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E109">
         <v>1.468962894874441</v>
@@ -6838,7 +6856,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6888,7 +6906,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6902,7 +6920,7 @@
         <v>1.686969731933735</v>
       </c>
       <c r="D111" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E111">
         <v>1.32442577469753</v>
@@ -6952,7 +6970,7 @@
         <v>1.688566437853383</v>
       </c>
       <c r="D112" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E112">
         <v>1.388891165154931</v>
@@ -7002,7 +7020,7 @@
         <v>1.116820833577004</v>
       </c>
       <c r="D113" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E113">
         <v>1.46791698325029</v>
@@ -7052,7 +7070,7 @@
         <v>1.189838416471486</v>
       </c>
       <c r="D114" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E114">
         <v>1.46791698325029</v>
@@ -7102,7 +7120,7 @@
         <v>1.16617137897391</v>
       </c>
       <c r="D115" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E115">
         <v>1.46791698325029</v>
@@ -7202,7 +7220,7 @@
         <v>1.679044765444968</v>
       </c>
       <c r="D117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E117">
         <v>1.316305130023856</v>
@@ -7238,7 +7256,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7252,7 +7270,7 @@
         <v>1.681071963371414</v>
       </c>
       <c r="D118" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E118">
         <v>1.381729343587304</v>
@@ -7288,7 +7306,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7302,7 +7320,7 @@
         <v>1.109345926913525</v>
       </c>
       <c r="D119" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E119">
         <v>1.459757202939633</v>
@@ -7338,7 +7356,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7352,7 +7370,7 @@
         <v>1.116606291492413</v>
       </c>
       <c r="D120" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E120">
         <v>1.459757202939633</v>
@@ -7388,7 +7406,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7402,7 +7420,7 @@
         <v>1.158031166481744</v>
       </c>
       <c r="D121" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E121">
         <v>1.459757202939633</v>
@@ -7438,7 +7456,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7452,7 +7470,7 @@
         <v>1.667785062291963</v>
       </c>
       <c r="D122" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E122">
         <v>1.323675609160295</v>
@@ -7488,7 +7506,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7538,7 +7556,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7552,7 +7570,7 @@
         <v>1.705523534148037</v>
       </c>
       <c r="D124" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E124">
         <v>1.306151805217721</v>
@@ -7588,7 +7606,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7602,7 +7620,7 @@
         <v>1.0999999749233</v>
       </c>
       <c r="D125" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E125">
         <v>1.449554946447687</v>
@@ -7638,7 +7656,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7652,7 +7670,7 @@
         <v>1.107015681073126</v>
       </c>
       <c r="D126" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E126">
         <v>1.449554946447687</v>
@@ -7688,7 +7706,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7702,7 +7720,7 @@
         <v>1.074450234602739</v>
       </c>
       <c r="D127" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E127">
         <v>1.449554946447687</v>
@@ -7738,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7752,7 +7770,7 @@
         <v>1.728036618426774</v>
       </c>
       <c r="D128" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E128">
         <v>1.311858607036529</v>
@@ -7788,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7838,7 +7856,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7852,7 +7870,7 @@
         <v>1.735732764200063</v>
       </c>
       <c r="D130" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E130">
         <v>1.301215982596513</v>
@@ -7902,7 +7920,7 @@
         <v>1.095456639402092</v>
       </c>
       <c r="D131" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E131">
         <v>1.444595336729509</v>
@@ -7952,7 +7970,7 @@
         <v>1.102353410067069</v>
       </c>
       <c r="D132" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E132">
         <v>1.444595336729509</v>
@@ -8002,7 +8020,7 @@
         <v>1.069526305530016</v>
       </c>
       <c r="D133" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E133">
         <v>1.444595336729509</v>
@@ -8102,7 +8120,7 @@
         <v>1.767688434264066</v>
       </c>
       <c r="D135" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E135">
         <v>1.290978663803567</v>
@@ -8152,7 +8170,7 @@
         <v>1.08603337246497</v>
       </c>
       <c r="D136" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E136">
         <v>1.434308681460452</v>
@@ -8202,7 +8220,7 @@
         <v>1.092683460749394</v>
       </c>
       <c r="D137" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E137">
         <v>1.434308681460452</v>
@@ -8252,7 +8270,7 @@
         <v>1.059313654975125</v>
       </c>
       <c r="D138" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E138">
         <v>1.434308681460452</v>
@@ -8688,7 +8706,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8738,7 +8756,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8788,7 +8806,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8838,7 +8856,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8888,7 +8906,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8902,7 +8920,7 @@
         <v>1.823420612308294</v>
       </c>
       <c r="D151" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E151">
         <v>2.204728303692967</v>
@@ -8938,7 +8956,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8988,7 +9006,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9038,7 +9056,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9088,7 +9106,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9138,7 +9156,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9188,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9238,7 +9256,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9288,7 +9306,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9302,7 +9320,7 @@
         <v>2.07884565528049</v>
       </c>
       <c r="D159" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E159">
         <v>2.424795934638657</v>
@@ -9338,7 +9356,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9388,7 +9406,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9438,7 +9456,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9452,7 +9470,7 @@
         <v>2.074698477808512</v>
       </c>
       <c r="D162" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E162">
         <v>2.228712809543505</v>
@@ -9488,7 +9506,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9538,7 +9556,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9588,7 +9606,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9638,7 +9656,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9752,7 +9770,7 @@
         <v>2.045995448659537</v>
       </c>
       <c r="D168" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E168">
         <v>2.697722827185737</v>
@@ -9902,7 +9920,7 @@
         <v>2.025703573192318</v>
       </c>
       <c r="D171" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E171">
         <v>2.585859069325287</v>
@@ -9988,7 +10006,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10002,7 +10020,7 @@
         <v>2.002237248721763</v>
       </c>
       <c r="D173" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E173">
         <v>2.933150127071722</v>
@@ -10038,7 +10056,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10088,7 +10106,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10102,7 +10120,7 @@
         <v>2.14690100237887</v>
       </c>
       <c r="D175" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E175">
         <v>3.035145626224377</v>
@@ -10138,7 +10156,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10188,7 +10206,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10202,7 +10220,7 @@
         <v>2.113865641885164</v>
       </c>
       <c r="D177" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E177">
         <v>2.99862999271211</v>
@@ -10238,7 +10256,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10288,7 +10306,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10338,7 +10356,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10352,7 +10370,7 @@
         <v>2.224552854469621</v>
       </c>
       <c r="D180" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E180">
         <v>2.747562112891602</v>
@@ -10388,7 +10406,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10402,7 +10420,7 @@
         <v>2.234582155562626</v>
       </c>
       <c r="D181" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E181">
         <v>2.747562112891602</v>
@@ -10438,7 +10456,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10452,7 +10470,7 @@
         <v>2.532227490792448</v>
       </c>
       <c r="D182" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E182">
         <v>2.747562112891602</v>
@@ -10488,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10538,7 +10556,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10588,7 +10606,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10602,7 +10620,7 @@
         <v>2.219578642489605</v>
       </c>
       <c r="D185" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E185">
         <v>2.748307309478141</v>
@@ -10638,7 +10656,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10652,7 +10670,7 @@
         <v>2.229273046142372</v>
       </c>
       <c r="D186" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E186">
         <v>2.748307309478141</v>
@@ -10688,7 +10706,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10702,7 +10720,7 @@
         <v>2.526938081221619</v>
       </c>
       <c r="D187" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E187">
         <v>2.748307309478141</v>
@@ -10738,7 +10756,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10788,7 +10806,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10838,7 +10856,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10852,7 +10870,7 @@
         <v>2.223095119495316</v>
       </c>
       <c r="D190" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E190">
         <v>2.585306324177835</v>
@@ -10888,7 +10906,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10902,7 +10920,7 @@
         <v>2.233026276055397</v>
       </c>
       <c r="D191" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E191">
         <v>2.585306324177835</v>
@@ -10938,7 +10956,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10952,7 +10970,7 @@
         <v>2.530677384493038</v>
       </c>
       <c r="D192" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E192">
         <v>2.585306324177835</v>
@@ -10988,7 +11006,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11038,7 +11056,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11088,7 +11106,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11102,7 +11120,7 @@
         <v>2.351296670264901</v>
       </c>
       <c r="D195" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E195">
         <v>2.34477901699545</v>
@@ -11138,7 +11156,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11152,7 +11170,7 @@
         <v>2.531296670264901</v>
       </c>
       <c r="D196" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E196">
         <v>2.34477901699545</v>
@@ -11188,7 +11206,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11238,7 +11256,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11288,7 +11306,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11338,7 +11356,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11352,7 +11370,7 @@
         <v>2.354338556588907</v>
       </c>
       <c r="D200" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E200">
         <v>2.692933327062218</v>
@@ -11388,7 +11406,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11402,7 +11420,7 @@
         <v>2.534338556588906</v>
       </c>
       <c r="D201" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E201">
         <v>2.692933327062218</v>
@@ -11438,7 +11456,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11488,7 +11506,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11538,7 +11556,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11588,7 +11606,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11602,7 +11620,7 @@
         <v>2.353252705775172</v>
       </c>
       <c r="D205" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E205">
         <v>3.037215179660817</v>
@@ -11638,7 +11656,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11652,7 +11670,7 @@
         <v>2.533252705775172</v>
       </c>
       <c r="D206" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E206">
         <v>3.037215179660817</v>
@@ -11688,7 +11706,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11702,7 +11720,7 @@
         <v>-1.066638455738899</v>
       </c>
       <c r="D207" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E207">
         <v>-1.465413797453388</v>
@@ -11738,7 +11756,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11752,7 +11770,7 @@
         <v>-1.0366384557389</v>
       </c>
       <c r="D208" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E208">
         <v>-1.465413797453388</v>
@@ -11788,7 +11806,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11802,7 +11820,7 @@
         <v>-0.9510556888450674</v>
       </c>
       <c r="D209" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E209">
         <v>-1.465413797453388</v>
@@ -11838,7 +11856,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11852,7 +11870,7 @@
         <v>-1.819265145803461</v>
       </c>
       <c r="D210" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E210">
         <v>-1.307592851757549</v>
@@ -11888,7 +11906,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11902,7 +11920,7 @@
         <v>-1.771950960365871</v>
       </c>
       <c r="D211" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E211">
         <v>-1.297263464992842</v>
@@ -11938,7 +11956,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11952,7 +11970,7 @@
         <v>-1.016934078228135</v>
       </c>
       <c r="D212" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E212">
         <v>-1.07654556696558</v>
@@ -11988,7 +12006,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12002,7 +12020,7 @@
         <v>-1.083441760674821</v>
       </c>
       <c r="D213" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E213">
         <v>-1.481089607902267</v>
@@ -12038,7 +12056,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12052,7 +12070,7 @@
         <v>-1.053441760674821</v>
       </c>
       <c r="D214" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E214">
         <v>-1.481089607902267</v>
@@ -12088,7 +12106,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12102,7 +12120,7 @@
         <v>-0.9668769824535648</v>
       </c>
       <c r="D215" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E215">
         <v>-1.481089607902267</v>
@@ -12138,7 +12156,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12152,7 +12170,7 @@
         <v>-1.83581385521005</v>
       </c>
       <c r="D216" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E216">
         <v>-1.323195920626619</v>
@@ -12188,7 +12206,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12202,7 +12220,7 @@
         <v>-1.787408546075322</v>
       </c>
       <c r="D217" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E217">
         <v>-1.311375331475824</v>
@@ -12238,7 +12256,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12288,7 +12306,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12302,7 +12320,7 @@
         <v>-1.07759404974841</v>
       </c>
       <c r="D219" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E219">
         <v>-1.503621288834554</v>
@@ -12338,7 +12356,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12352,7 +12370,7 @@
         <v>-0.9896177741137624</v>
       </c>
       <c r="D220" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E220">
         <v>-1.503621288834554</v>
@@ -12388,7 +12406,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12402,7 +12420,7 @@
         <v>-1.859600200509798</v>
       </c>
       <c r="D221" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E221">
         <v>-1.345623046194952</v>
@@ -12438,7 +12456,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12452,7 +12470,7 @@
         <v>-1.809626560915746</v>
       </c>
       <c r="D222" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E222">
         <v>-1.33165907208308</v>
@@ -12488,7 +12506,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12502,7 +12520,7 @@
         <v>-1.047695097971209</v>
       </c>
       <c r="D223" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E223">
         <v>-1.119714428935569</v>
@@ -12538,7 +12556,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12552,7 +12570,7 @@
         <v>-1.107622621715292</v>
       </c>
       <c r="D224" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E224">
         <v>-1.53163495662184</v>
@@ -12602,7 +12620,7 @@
         <v>-1.017891429537125</v>
       </c>
       <c r="D225" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E225">
         <v>-1.53163495662184</v>
@@ -12652,7 +12670,7 @@
         <v>-1.889173794113544</v>
       </c>
       <c r="D226" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E226">
         <v>-1.373506720164198</v>
@@ -12702,7 +12720,7 @@
         <v>-1.837250247248916</v>
       </c>
       <c r="D227" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E227">
         <v>-1.356877872782539</v>
@@ -12802,7 +12820,7 @@
         <v>-1.136466558905362</v>
       </c>
       <c r="D229" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E229">
         <v>-1.55854347811301</v>
@@ -12838,7 +12856,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12852,7 +12870,7 @@
         <v>-1.045049682086217</v>
       </c>
       <c r="D230" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E230">
         <v>-1.55854347811301</v>
@@ -12888,7 +12906,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12902,7 +12920,7 @@
         <v>-1.91758070195225</v>
       </c>
       <c r="D231" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E231">
         <v>-1.400290376126407</v>
@@ -12938,7 +12956,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12952,7 +12970,7 @@
         <v>-1.863784172153202</v>
       </c>
       <c r="D232" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E232">
         <v>-1.38110178540104</v>
@@ -12988,7 +13006,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13002,7 +13020,7 @@
         <v>-1.091913194675672</v>
       </c>
       <c r="D233" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E233">
         <v>-0.942243215869925</v>
@@ -13038,7 +13056,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13052,7 +13070,7 @@
         <v>-1.06938217480964</v>
       </c>
       <c r="D234" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E234">
         <v>-0.942243215869925</v>
@@ -13088,7 +13106,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13102,7 +13120,7 @@
         <v>-1.09938217480964</v>
       </c>
       <c r="D235" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E235">
         <v>-0.942243215869925</v>
@@ -13138,7 +13156,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13152,7 +13170,7 @@
         <v>-1.069955605077879</v>
       </c>
       <c r="D236" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E236">
         <v>-1.583220381123139</v>
@@ -13202,7 +13220,7 @@
         <v>-1.943631724851574</v>
       </c>
       <c r="D237" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E237">
         <v>-1.42485276914577</v>
@@ -13252,7 +13270,7 @@
         <v>-1.888117545191031</v>
       </c>
       <c r="D238" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E238">
         <v>-1.403316723609694</v>
@@ -13302,7 +13320,7 @@
         <v>-1.111780678073619</v>
       </c>
       <c r="D239" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E239">
         <v>-0.8811636624809664</v>
@@ -13352,7 +13370,7 @@
         <v>-1.088104558299923</v>
       </c>
       <c r="D240" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E240">
         <v>-0.8811636624809664</v>
@@ -13402,7 +13420,7 @@
         <v>-1.118104558299923</v>
       </c>
       <c r="D241" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E241">
         <v>-0.8811636624809664</v>
@@ -13452,7 +13470,7 @@
         <v>-1.100958399511376</v>
       </c>
       <c r="D242" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E242">
         <v>-1.613938092389432</v>
@@ -13488,7 +13506,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13502,7 +13520,7 @@
         <v>-1.976059935121095</v>
       </c>
       <c r="D243" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E243">
         <v>-1.455427938828461</v>
@@ -13538,7 +13556,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13552,7 +13570,7 @@
         <v>-1.918407631706518</v>
       </c>
       <c r="D244" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E244">
         <v>-1.430969790828538</v>
@@ -13588,7 +13606,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13602,7 +13620,7 @@
         <v>-1.136511642828615</v>
       </c>
       <c r="D245" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E245">
         <v>-1.028859339414037</v>
@@ -13638,7 +13656,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13652,7 +13670,7 @@
         <v>-1.111410107218897</v>
       </c>
       <c r="D246" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E246">
         <v>-1.028859339414037</v>
@@ -13688,7 +13706,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13702,7 +13720,7 @@
         <v>-1.141410107218897</v>
       </c>
       <c r="D247" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E247">
         <v>-1.028859339414037</v>
@@ -13738,7 +13756,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13752,7 +13770,7 @@
         <v>-1.117512484565025</v>
       </c>
       <c r="D248" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E248">
         <v>-1.630339955971323</v>
@@ -13788,7 +13806,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13802,7 +13820,7 @@
         <v>-1.993375127533532</v>
       </c>
       <c r="D249" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E249">
         <v>-1.471753691674473</v>
@@ -13838,7 +13856,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13852,7 +13870,7 @@
         <v>-1.934581163080772</v>
       </c>
       <c r="D250" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E250">
         <v>-1.445735273589034</v>
@@ -13888,7 +13906,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13902,7 +13920,7 @@
         <v>-1.149716855503595</v>
       </c>
       <c r="D251" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E251">
         <v>-1.032336626753983</v>
@@ -13938,7 +13956,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13952,7 +13970,7 @@
         <v>-1.123854212535088</v>
       </c>
       <c r="D252" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E252">
         <v>-1.032336626753983</v>
@@ -13988,7 +14006,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14002,7 +14020,7 @@
         <v>-1.153854212535088</v>
       </c>
       <c r="D253" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E253">
         <v>-1.032336626753983</v>
@@ -14038,7 +14056,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14052,7 +14070,7 @@
         <v>-1.135440729342402</v>
       </c>
       <c r="D254" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E254">
         <v>-1.64810334332546</v>
@@ -14088,7 +14106,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14102,7 +14120,7 @@
         <v>-2.012127659427111</v>
       </c>
       <c r="D255" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E255">
         <v>-1.489434650316991</v>
@@ -14138,7 +14156,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14152,7 +14170,7 @@
         <v>-1.95209726430005</v>
       </c>
       <c r="D256" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E256">
         <v>-1.461726443643339</v>
@@ -14188,7 +14206,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14202,7 +14220,7 @@
         <v>-1.164018236969687</v>
       </c>
       <c r="D257" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E257">
         <v>-1.112656534851095</v>
@@ -14238,7 +14256,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14252,7 +14270,7 @@
         <v>-1.137331306884979</v>
       </c>
       <c r="D258" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E258">
         <v>-1.112656534851095</v>
@@ -14288,7 +14306,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14302,7 +14320,7 @@
         <v>-1.167331306884979</v>
       </c>
       <c r="D259" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E259">
         <v>-1.112656534851095</v>
@@ -14338,7 +14356,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14352,7 +14370,7 @@
         <v>-2.029751754240792</v>
       </c>
       <c r="D260" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E260">
         <v>-1.506051653998461</v>
@@ -14402,7 +14420,7 @@
         <v>-1.968559330884256</v>
       </c>
       <c r="D261" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E261">
         <v>-1.476755342077862</v>
@@ -14452,7 +14470,7 @@
         <v>-1.177459030157264</v>
       </c>
       <c r="D262" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E262">
         <v>-1.113758929914932</v>
@@ -14502,7 +14520,7 @@
         <v>-1.149997414586239</v>
       </c>
       <c r="D263" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E263">
         <v>-1.113758929914932</v>
@@ -14552,7 +14570,7 @@
         <v>-1.179997414586239</v>
       </c>
       <c r="D264" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E264">
         <v>-1.113758929914932</v>
@@ -14602,7 +14620,7 @@
         <v>-2.049264235927141</v>
       </c>
       <c r="D265" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E265">
         <v>-1.524449136731304</v>
@@ -14638,7 +14656,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14652,7 +14670,7 @@
         <v>-1.986785275316561</v>
       </c>
       <c r="D266" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E266">
         <v>-1.493394557230178</v>
@@ -14688,7 +14706,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14702,7 +14720,7 @@
         <v>-1.192339977729051</v>
       </c>
       <c r="D267" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E267">
         <v>-0.9807727745942727</v>
@@ -14738,7 +14756,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14752,7 +14770,7 @@
         <v>-1.16402067065533</v>
       </c>
       <c r="D268" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E268">
         <v>-0.9807727745942727</v>
@@ -14788,7 +14806,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14802,7 +14820,7 @@
         <v>-1.19402067065533</v>
       </c>
       <c r="D269" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E269">
         <v>-0.9807727745942727</v>
@@ -14838,7 +14856,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14852,7 +14870,7 @@
         <v>-2.083260847634321</v>
       </c>
       <c r="D270" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E270">
         <v>-1.55650308491236</v>
@@ -14888,7 +14906,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14902,7 +14920,7 @@
         <v>-2.018540352185904</v>
       </c>
       <c r="D271" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E271">
         <v>-1.52238507446619</v>
@@ -14938,7 +14956,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -14952,7 +14970,7 @@
         <v>-1.218267064020021</v>
       </c>
       <c r="D272" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E272">
         <v>-1.15072047992809</v>
@@ -14988,7 +15006,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15002,7 +15020,7 @@
         <v>-1.188453400387743</v>
       </c>
       <c r="D273" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E273">
         <v>-1.15072047992809</v>
@@ -15038,7 +15056,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15052,7 +15070,7 @@
         <v>-1.218453400387743</v>
       </c>
       <c r="D274" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E274">
         <v>-1.15072047992809</v>
@@ -15088,7 +15106,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15102,7 +15120,7 @@
         <v>-2.129173370599524</v>
       </c>
       <c r="D275" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E275">
         <v>-1.599792035136694</v>
@@ -15138,7 +15156,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15152,7 +15170,7 @@
         <v>-2.061425675834721</v>
       </c>
       <c r="D276" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E276">
         <v>-1.561536852291463</v>
@@ -15188,7 +15206,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15202,7 +15220,7 @@
         <v>-1.253281669446231</v>
       </c>
       <c r="D277" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E277">
         <v>-1.285422798224685</v>
@@ -15238,7 +15256,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15252,7 +15270,7 @@
         <v>-1.221449872936362</v>
       </c>
       <c r="D278" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E278">
         <v>-1.285422798224685</v>
@@ -15288,7 +15306,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15302,7 +15320,7 @@
         <v>-1.251449872936362</v>
       </c>
       <c r="D279" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E279">
         <v>-1.285422798224685</v>
@@ -15338,7 +15356,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15352,7 +15370,7 @@
         <v>-2.169540849194301</v>
       </c>
       <c r="D280" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E280">
         <v>-1.637852800668912</v>
@@ -15388,7 +15406,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15402,7 +15420,7 @@
         <v>-2.099131562434238</v>
       </c>
       <c r="D281" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E281">
         <v>-1.595960108763492</v>
@@ -15438,7 +15456,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15452,7 +15470,7 @@
         <v>-1.284067416858071</v>
       </c>
       <c r="D282" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E282">
         <v>-1.430231131562097</v>
@@ -15488,7 +15506,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15502,7 +15520,7 @@
         <v>-1.250461225684695</v>
       </c>
       <c r="D283" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E283">
         <v>-1.430231131562097</v>
@@ -15538,7 +15556,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15552,7 +15570,7 @@
         <v>-1.280461225684695</v>
       </c>
       <c r="D284" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E284">
         <v>-1.430231131562097</v>
@@ -15588,7 +15606,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15602,7 +15620,7 @@
         <v>-2.189959023684696</v>
       </c>
       <c r="D285" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E285">
         <v>-1.657104222331285</v>
@@ -15638,7 +15656,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15652,7 +15670,7 @@
         <v>-2.11820348366153</v>
       </c>
       <c r="D286" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E286">
         <v>-1.613371650966291</v>
@@ -15688,7 +15706,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15702,7 +15720,7 @@
         <v>-1.299639079601296</v>
       </c>
       <c r="D287" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E287">
         <v>-1.362715372273368</v>
@@ -15738,7 +15756,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15752,7 +15770,7 @@
         <v>-1.265135386252518</v>
       </c>
       <c r="D288" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E288">
         <v>-1.362715372273368</v>
@@ -15788,7 +15806,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15802,7 +15820,7 @@
         <v>-1.295135386252518</v>
       </c>
       <c r="D289" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E289">
         <v>-1.362715372273368</v>
@@ -15838,7 +15856,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15852,7 +15870,7 @@
         <v>-2.214173184477514</v>
       </c>
       <c r="D290" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E290">
         <v>-1.679934716793084</v>
@@ -15888,7 +15906,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15902,7 +15920,7 @@
         <v>-2.140821106380096</v>
       </c>
       <c r="D291" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E291">
         <v>-1.634020210059946</v>
@@ -15938,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -15952,7 +15970,7 @@
         <v>-1.318105703326807</v>
       </c>
       <c r="D292" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E292">
         <v>-1.489781742375517</v>
@@ -15988,7 +16006,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16002,7 +16020,7 @@
         <v>-1.282537651261862</v>
       </c>
       <c r="D293" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E293">
         <v>-1.489781742375517</v>
@@ -16038,7 +16056,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16052,7 +16070,7 @@
         <v>-1.312537651261862</v>
       </c>
       <c r="D294" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E294">
         <v>-1.489781742375517</v>
@@ -16088,7 +16106,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16102,7 +16120,7 @@
         <v>-2.241121102143395</v>
       </c>
       <c r="D295" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E295">
         <v>-1.705342753449486</v>
@@ -16138,7 +16156,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16152,7 +16170,7 @@
         <v>-2.165992238265808</v>
       </c>
       <c r="D296" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E296">
         <v>-1.656999972816785</v>
@@ -16188,7 +16206,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16202,7 +16220,7 @@
         <v>-1.338657192184084</v>
       </c>
       <c r="D297" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E297">
         <v>-1.427033480143279</v>
@@ -16238,7 +16256,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16252,7 +16270,7 @@
         <v>-1.301904616265692</v>
       </c>
       <c r="D298" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E298">
         <v>-1.427033480143279</v>
@@ -16288,7 +16306,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16302,7 +16320,7 @@
         <v>-1.331904616265692</v>
       </c>
       <c r="D299" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E299">
         <v>-1.427033480143279</v>
@@ -16338,7 +16356,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16352,7 +16370,7 @@
         <v>1.347720014974502</v>
       </c>
       <c r="D300" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E300">
         <v>1.579062118830282</v>
@@ -16388,7 +16406,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16402,7 +16420,7 @@
         <v>1.334700016044109</v>
       </c>
       <c r="D301" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E301">
         <v>1.593089491417174</v>
@@ -16438,7 +16456,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16452,7 +16470,7 @@
         <v>1.841747387561394</v>
       </c>
       <c r="D302" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E302">
         <v>1.890874754800249</v>
@@ -16488,7 +16506,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16502,7 +16520,7 @@
         <v>1.862485279427185</v>
       </c>
       <c r="D303" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E303">
         <v>1.890874754800249</v>
@@ -16538,7 +16556,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16552,7 +16570,7 @@
         <v>1.441706845387347</v>
       </c>
       <c r="D304" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E304">
         <v>1.664215600520115</v>
@@ -16588,7 +16606,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16602,7 +16620,7 @@
         <v>1.435400191486443</v>
       </c>
       <c r="D305" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E305">
         <v>1.704389685327122</v>
@@ -16638,7 +16656,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16652,7 +16670,7 @@
         <v>1.856584782452771</v>
       </c>
       <c r="D306" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E306">
         <v>1.861880930194354</v>
@@ -16688,7 +16706,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16702,7 +16720,7 @@
         <v>1.9645987906652</v>
       </c>
       <c r="D307" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E307">
         <v>1.861880930194354</v>
@@ -16738,7 +16756,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16752,7 +16770,7 @@
         <v>2.014804950663784</v>
       </c>
       <c r="D308" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E308">
         <v>1.689180786611569</v>
@@ -16788,7 +16806,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16802,7 +16820,7 @@
         <v>1.927301606872644</v>
       </c>
       <c r="D309" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E309">
         <v>1.689180786611569</v>
@@ -16838,7 +16856,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16852,7 +16870,7 @@
         <v>1.922617032689892</v>
       </c>
       <c r="D310" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E310">
         <v>1.689180786611569</v>
@@ -16888,7 +16906,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -16902,7 +16920,7 @@
         <v>1.696992868637676</v>
       </c>
       <c r="D311" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E311">
         <v>1.791368704585461</v>
@@ -16938,7 +16956,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -16988,7 +17006,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17038,7 +17056,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17088,7 +17106,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17138,7 +17156,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17188,7 +17206,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17238,7 +17256,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17252,7 +17270,7 @@
         <v>1.869784887916945</v>
       </c>
       <c r="D318" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E318">
         <v>1.868536559812515</v>
@@ -17288,7 +17306,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17302,7 +17320,7 @@
         <v>1.892281544125805</v>
       </c>
       <c r="D319" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E319">
         <v>1.868536559812515</v>
@@ -17338,7 +17356,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17352,7 +17370,7 @@
         <v>1.879784887916945</v>
       </c>
       <c r="D320" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E320">
         <v>1.868536559812515</v>
@@ -17388,7 +17406,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17402,7 +17420,7 @@
         <v>1.830509026107986</v>
       </c>
       <c r="D321" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E321">
         <v>1.588842690067986</v>
@@ -17438,7 +17456,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17452,7 +17470,7 @@
         <v>1.823342590879987</v>
       </c>
       <c r="D322" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E322">
         <v>1.588842690067986</v>
@@ -17488,7 +17506,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17502,7 +17520,7 @@
         <v>1.597009323671986</v>
       </c>
       <c r="D323" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E323">
         <v>1.690676056463986</v>
@@ -17538,7 +17556,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17552,7 +17570,7 @@
         <v>1.564008728543987</v>
       </c>
       <c r="D324" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E324">
         <v>1.690841103059988</v>
@@ -17588,7 +17606,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17602,7 +17620,7 @@
         <v>1.612175362147987</v>
       </c>
       <c r="D325" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E325">
         <v>1.690841103059988</v>
@@ -17638,7 +17656,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17652,7 +17670,7 @@
         <v>1.608508629355987</v>
       </c>
       <c r="D326" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E326">
         <v>1.690841103059988</v>
@@ -17688,7 +17706,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17702,7 +17720,7 @@
         <v>1.611175163771987</v>
       </c>
       <c r="D327" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E327">
         <v>1.690841103059988</v>
@@ -17738,7 +17756,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17788,7 +17806,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17802,7 +17820,7 @@
         <v>1.787174370267988</v>
       </c>
       <c r="D329" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E329">
         <v>1.578675659711986</v>
@@ -17838,7 +17856,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17852,7 +17870,7 @@
         <v>1.812507439099989</v>
       </c>
       <c r="D330" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E330">
         <v>1.578675659711986</v>
@@ -17888,7 +17906,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17902,7 +17920,7 @@
         <v>1.783507637475988</v>
       </c>
       <c r="D331" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E331">
         <v>1.578675659711986</v>
@@ -17938,7 +17956,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -17952,7 +17970,7 @@
         <v>1.797174370267989</v>
       </c>
       <c r="D332" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E332">
         <v>1.578675659711986</v>
@@ -17988,7 +18006,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18002,7 +18020,7 @@
         <v>1.796508232603987</v>
       </c>
       <c r="D333" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E333">
         <v>1.578675659711986</v>
@@ -18038,7 +18056,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18052,7 +18070,7 @@
         <v>1.60619577124814</v>
       </c>
       <c r="D334" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E334">
         <v>1.409496709559184</v>
@@ -18088,7 +18106,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18102,7 +18120,7 @@
         <v>1.639829926132983</v>
       </c>
       <c r="D335" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E335">
         <v>1.409496709559184</v>
@@ -18138,7 +18156,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18152,7 +18170,7 @@
         <v>1.641634855442047</v>
       </c>
       <c r="D336" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E336">
         <v>1.409496709559184</v>
@@ -18188,7 +18206,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18202,7 +18220,7 @@
         <v>1.294651169712725</v>
       </c>
       <c r="D337" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E337">
         <v>1.17011455017335</v>
@@ -18238,7 +18256,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18252,7 +18270,7 @@
         <v>1.309805629866267</v>
       </c>
       <c r="D338" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E338">
         <v>1.17011455017335</v>
@@ -18288,7 +18306,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18302,7 +18320,7 @@
         <v>1.302846240403662</v>
       </c>
       <c r="D339" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E339">
         <v>1.17011455017335</v>
@@ -18338,7 +18356,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18352,7 +18370,7 @@
         <v>1.302846240403662</v>
       </c>
       <c r="D340" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E340">
         <v>1.17011455017335</v>
@@ -18388,7 +18406,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18402,7 +18420,7 @@
         <v>1.306789315595589</v>
       </c>
       <c r="D341" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E341">
         <v>1.17011455017335</v>
@@ -18438,7 +18456,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18452,7 +18470,7 @@
         <v>1.225269010326891</v>
       </c>
       <c r="D342" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E342">
         <v>1.17011455017335</v>
@@ -18488,7 +18506,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18502,7 +18520,7 @@
         <v>1.444294269397325</v>
       </c>
       <c r="D343" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E343">
         <v>1.256000185094495</v>
@@ -18552,7 +18570,7 @@
         <v>1.501117816501946</v>
       </c>
       <c r="D344" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E344">
         <v>1.256000185094495</v>
@@ -18602,7 +18620,7 @@
         <v>1.083058995014017</v>
       </c>
       <c r="D345" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E345">
         <v>1.093353102453659</v>
@@ -18652,7 +18670,7 @@
         <v>1.408730452400234</v>
       </c>
       <c r="D346" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E346">
         <v>1.224172692200284</v>
@@ -18688,7 +18706,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18702,7 +18720,7 @@
         <v>1.47198161896276</v>
       </c>
       <c r="D347" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E347">
         <v>1.224172692200284</v>
@@ -18738,7 +18756,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18788,7 +18806,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18802,7 +18820,7 @@
         <v>1.382122760311682</v>
       </c>
       <c r="D349" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E349">
         <v>1.191863351807043</v>
@@ -18838,7 +18856,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18852,7 +18870,7 @@
         <v>1.442404318382183</v>
       </c>
       <c r="D350" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E350">
         <v>1.191863351807043</v>
@@ -18888,7 +18906,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18938,7 +18956,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -18952,7 +18970,7 @@
         <v>1.370401955803482</v>
       </c>
       <c r="D352" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E352">
         <v>1.1776309463328</v>
@@ -19002,7 +19020,7 @@
         <v>1.429375388370835</v>
       </c>
       <c r="D353" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E353">
         <v>1.1776309463328</v>
@@ -19052,7 +19070,7 @@
         <v>1.010452200278918</v>
       </c>
       <c r="D354" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E354">
         <v>1.015068140738506</v>
@@ -19102,7 +19120,7 @@
         <v>1.025068140738506</v>
       </c>
       <c r="D355" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E355">
         <v>1.015068140738506</v>
@@ -19152,7 +19170,7 @@
         <v>1.355513343522262</v>
       </c>
       <c r="D356" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E356">
         <v>1.159551917134175</v>
@@ -19188,7 +19206,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19202,7 +19220,7 @@
         <v>1.4128251006118</v>
       </c>
       <c r="D357" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E357">
         <v>1.159551917134175</v>
@@ -19238,7 +19256,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19252,7 +19270,7 @@
         <v>0.9937025114625451</v>
       </c>
       <c r="D358" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E358">
         <v>1.019315457208822</v>
@@ -19288,7 +19306,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19302,7 +19320,7 @@
         <v>1.009315457208822</v>
       </c>
       <c r="D359" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E359">
         <v>1.019315457208822</v>
@@ -19338,7 +19356,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19352,7 +19370,7 @@
         <v>1.344301537527252</v>
       </c>
       <c r="D360" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E360">
         <v>1.145937581283092</v>
@@ -19402,7 +19420,7 @@
         <v>1.400361976983419</v>
       </c>
       <c r="D361" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E361">
         <v>1.145937581283092</v>
@@ -19552,7 +19570,7 @@
         <v>1.32595157423566</v>
       </c>
       <c r="D364" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E364">
         <v>1.123655483000445</v>
@@ -19588,7 +19606,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19602,7 +19620,7 @@
         <v>1.379964026717319</v>
       </c>
       <c r="D365" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E365">
         <v>1.123655483000445</v>
@@ -19638,7 +19656,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19652,7 +19670,7 @@
         <v>0.9604455210151182</v>
       </c>
       <c r="D366" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E366">
         <v>0.9494825324195202</v>
@@ -19688,7 +19706,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19702,7 +19720,7 @@
         <v>0.9780380495261229</v>
       </c>
       <c r="D367" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E367">
         <v>0.9494825324195202</v>
@@ -19738,7 +19756,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19752,7 +19770,7 @@
         <v>0.9780380495261229</v>
       </c>
       <c r="D368" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E368">
         <v>0.9494825324195202</v>
@@ -19788,7 +19806,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19802,7 +19820,7 @@
         <v>0.93948253241952</v>
       </c>
       <c r="D369" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E369">
         <v>0.9494825324195202</v>
@@ -19838,7 +19856,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19852,7 +19870,7 @@
         <v>1.346901155844391</v>
       </c>
       <c r="D370" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E370">
         <v>1.225539647019887</v>
@@ -19888,7 +19906,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19902,7 +19920,7 @@
         <v>1.331298641136886</v>
       </c>
       <c r="D371" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E371">
         <v>1.225539647019887</v>
@@ -19938,7 +19956,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -19952,7 +19970,7 @@
         <v>1.154256377900131</v>
       </c>
       <c r="D372" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E372">
         <v>1.26001537201713</v>
@@ -19988,7 +20006,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20002,7 +20020,7 @@
         <v>1.14857562348788</v>
       </c>
       <c r="D373" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E373">
         <v>1.274334617604878</v>
@@ -20038,7 +20056,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20052,7 +20070,7 @@
         <v>1.324412857309625</v>
       </c>
       <c r="D374" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E374">
         <v>1.205852605838874</v>
@@ -20088,7 +20106,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20102,7 +20120,7 @@
         <v>1.043943419081145</v>
       </c>
       <c r="D375" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E375">
         <v>1.269702413198143</v>
@@ -20138,7 +20156,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20152,7 +20170,7 @@
         <v>1.36666643673015</v>
       </c>
       <c r="D376" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E376">
         <v>1.400907442613152</v>
@@ -20188,7 +20206,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20202,7 +20220,7 @@
         <v>1.3381061852594</v>
       </c>
       <c r="D377" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E377">
         <v>1.400907442613152</v>
@@ -20238,7 +20256,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20252,7 +20270,7 @@
         <v>1.337921514632137</v>
       </c>
       <c r="D378" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E378">
         <v>1.216329758597064</v>
@@ -20302,7 +20320,7 @@
         <v>1.321935254573682</v>
       </c>
       <c r="D379" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E379">
         <v>1.216329758597064</v>
@@ -20352,7 +20370,7 @@
         <v>1.144547620521072</v>
       </c>
       <c r="D380" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E380">
         <v>1.250153116497689</v>
@@ -20402,7 +20420,7 @@
         <v>1.138751742503535</v>
       </c>
       <c r="D381" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E381">
         <v>1.264357238480152</v>
@@ -20452,7 +20470,7 @@
         <v>1.314166856439233</v>
       </c>
       <c r="D382" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E382">
         <v>1.195568230433388</v>
@@ -20502,7 +20520,7 @@
         <v>1.035309148684748</v>
       </c>
       <c r="D383" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E383">
         <v>1.260914644661365</v>
@@ -20652,7 +20670,7 @@
         <v>1.326338641239302</v>
       </c>
       <c r="D386" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E386">
         <v>1.204449888450566</v>
@@ -20688,7 +20706,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20702,7 +20720,7 @@
         <v>1.309857386591409</v>
       </c>
       <c r="D387" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E387">
         <v>1.204449888450566</v>
@@ -20738,7 +20756,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20752,7 +20770,7 @@
         <v>1.132024257408305</v>
       </c>
       <c r="D388" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E388">
         <v>1.237431755549148</v>
@@ -20788,7 +20806,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20802,7 +20820,7 @@
         <v>1.126079881013937</v>
       </c>
       <c r="D389" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E389">
         <v>1.25148737915478</v>
@@ -20838,7 +20856,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20852,7 +20870,7 @@
         <v>1.300950500901255</v>
       </c>
       <c r="D390" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E390">
         <v>1.182302375436465</v>
@@ -20888,7 +20906,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20902,7 +20920,7 @@
         <v>1.024171770422406</v>
       </c>
       <c r="D391" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E391">
         <v>1.249579268563249</v>
@@ -20938,7 +20956,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -20952,7 +20970,7 @@
         <v>1.347949275999877</v>
       </c>
       <c r="D392" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E392">
         <v>1.407134279718192</v>
@@ -20988,7 +21006,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21002,7 +21020,7 @@
         <v>1.319301150535088</v>
       </c>
       <c r="D393" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E393">
         <v>1.407134279718192</v>
@@ -21038,7 +21056,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21052,7 +21070,7 @@
         <v>1.31894662096582</v>
       </c>
       <c r="D394" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E394">
         <v>1.196868329195712</v>
@@ -21088,7 +21106,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21102,7 +21120,7 @@
         <v>1.302149468015641</v>
       </c>
       <c r="D395" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E395">
         <v>1.196868329195712</v>
@@ -21138,7 +21156,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21152,7 +21170,7 @@
         <v>1.12403203036048</v>
       </c>
       <c r="D396" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E396">
         <v>1.229313169180409</v>
@@ -21188,7 +21206,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21202,7 +21220,7 @@
         <v>1.117992884475426</v>
       </c>
       <c r="D397" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E397">
         <v>1.243274023295355</v>
@@ -21238,7 +21256,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21252,7 +21270,7 @@
         <v>1.017064058620981</v>
       </c>
       <c r="D398" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E398">
         <v>1.242345197440909</v>
@@ -21288,7 +21306,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21338,7 +21356,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21388,7 +21406,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21402,7 +21420,7 @@
         <v>1.309314370259902</v>
       </c>
       <c r="D401" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E401">
         <v>1.212105582664171</v>
@@ -21438,7 +21456,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21452,7 +21470,7 @@
         <v>1.113617673828013</v>
       </c>
       <c r="D402" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E402">
         <v>1.218734158789721</v>
@@ -21488,7 +21506,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21502,7 +21520,7 @@
         <v>1.107455037549294</v>
       </c>
       <c r="D403" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E403">
         <v>1.232571522511002</v>
@@ -21538,7 +21556,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21552,7 +21570,7 @@
         <v>1.00780227909606</v>
       </c>
       <c r="D404" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E404">
         <v>1.232918764057767</v>
@@ -21588,7 +21606,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21638,7 +21656,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21688,7 +21706,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21738,7 +21756,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21752,7 +21770,7 @@
         <v>1.096911392393543</v>
       </c>
       <c r="D408" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E408">
         <v>1.20176374642348</v>
@@ -21788,7 +21806,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21802,7 +21820,7 @@
         <v>1.090550657915995</v>
       </c>
       <c r="D409" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E409">
         <v>1.215403011945933</v>
@@ -21838,7 +21856,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21852,7 +21870,7 @@
         <v>0.9929449141839808</v>
       </c>
       <c r="D410" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E410">
         <v>1.217797268213918</v>
@@ -21888,7 +21906,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -21938,7 +21956,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -21988,7 +22006,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22002,7 +22020,7 @@
         <v>1.076787728620787</v>
       </c>
       <c r="D413" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E413">
         <v>1.194722566962074</v>
@@ -22038,7 +22056,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22052,7 +22070,7 @@
         <v>1.070188373624195</v>
       </c>
       <c r="D414" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E414">
         <v>1.194722566962074</v>
@@ -22088,7 +22106,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22102,7 +22120,7 @@
         <v>0.9750483752556411</v>
       </c>
       <c r="D415" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E415">
         <v>1.199582568593519</v>
@@ -22138,7 +22156,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22152,7 +22170,7 @@
         <v>1.06618192359011</v>
       </c>
       <c r="D416" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E416">
         <v>1.199582568593519</v>
@@ -22188,7 +22206,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22202,7 +22220,7 @@
         <v>1.301445795242007</v>
       </c>
       <c r="D417" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E417">
         <v>1.466305796873452</v>
@@ -22238,7 +22256,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22252,7 +22270,7 @@
         <v>1.325778053569659</v>
       </c>
       <c r="D418" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E418">
         <v>1.466305796873452</v>
@@ -22288,7 +22306,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22302,7 +22320,7 @@
         <v>1.061021828820504</v>
       </c>
       <c r="D419" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E419">
         <v>1.178520456495379</v>
@@ -22338,7 +22356,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22352,7 +22370,7 @@
         <v>1.05423552639545</v>
       </c>
       <c r="D420" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E420">
         <v>1.178520456495379</v>
@@ -22388,7 +22406,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22402,7 +22420,7 @@
         <v>0.9610273181210012</v>
       </c>
       <c r="D421" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E421">
         <v>1.18531224822093</v>
@@ -22438,7 +22456,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22452,7 +22470,7 @@
         <v>1.052098550645983</v>
       </c>
       <c r="D422" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E422">
         <v>1.18531224822093</v>
@@ -22488,7 +22506,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22502,7 +22520,7 @@
         <v>1.288172527821214</v>
       </c>
       <c r="D423" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E423">
         <v>1.460679389446836</v>
@@ -22538,7 +22556,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22552,7 +22570,7 @@
         <v>1.312816365196303</v>
       </c>
       <c r="D424" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E424">
         <v>1.460679389446836</v>
@@ -22588,7 +22606,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22702,7 +22720,7 @@
         <v>0.8755952802088971</v>
       </c>
       <c r="D427" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E427">
         <v>1.122137607315365</v>
@@ -22752,7 +22770,7 @@
         <v>1.266605330685716</v>
       </c>
       <c r="D428" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E428">
         <v>1.559580979333694</v>
@@ -22838,7 +22856,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22852,7 +22870,7 @@
         <v>0.8602148664207081</v>
       </c>
       <c r="D430" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E430">
         <v>1.107098980500247</v>
@@ -22888,7 +22906,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -22902,7 +22920,7 @@
         <v>1.280896373713855</v>
       </c>
       <c r="D431" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E431">
         <v>1.524099754797897</v>
@@ -22938,7 +22956,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23102,7 +23120,7 @@
         <v>1.302688953291221</v>
       </c>
       <c r="D435" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E435">
         <v>1.419681456386476</v>
@@ -23188,7 +23206,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23238,7 +23256,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23288,7 +23306,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23302,7 +23320,7 @@
         <v>1.257626439327654</v>
       </c>
       <c r="D439" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E439">
         <v>1.411664944525371</v>
@@ -23338,7 +23356,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23352,7 +23370,7 @@
         <v>1.840766780529548</v>
       </c>
       <c r="D440" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E440">
         <v>2.000338151296236</v>
@@ -23388,7 +23406,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23402,7 +23420,7 @@
         <v>2.174266578212954</v>
       </c>
       <c r="D441" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E441">
         <v>2.309284269167179</v>
@@ -23438,7 +23456,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23452,7 +23470,7 @@
         <v>2.096677111858851</v>
       </c>
       <c r="D442" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E442">
         <v>1.937337746663046</v>
@@ -23488,7 +23506,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23502,7 +23520,7 @@
         <v>1.86232005570882</v>
       </c>
       <c r="D443" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E443">
         <v>1.975355842250461</v>
@@ -23538,7 +23556,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23552,7 +23570,7 @@
         <v>1.842592596122513</v>
       </c>
       <c r="D444" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E444">
         <v>2.002261997256608</v>
@@ -23588,7 +23606,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23602,7 +23620,7 @@
         <v>2.176435500091845</v>
       </c>
       <c r="D445" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E445">
         <v>2.311735028352367</v>
@@ -23638,7 +23656,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23652,7 +23670,7 @@
         <v>2.099152378635891</v>
       </c>
       <c r="D446" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E446">
         <v>1.939947805195271</v>
@@ -23688,7 +23706,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23702,7 +23720,7 @@
         <v>1.864648276934749</v>
       </c>
       <c r="D447" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E447">
         <v>1.97756152551713</v>
@@ -23738,7 +23756,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23752,7 +23770,7 @@
         <v>1.84474004582061</v>
       </c>
       <c r="D448" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E448">
         <v>2.004524746267355</v>
@@ -23788,7 +23806,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23802,7 +23820,7 @@
         <v>2.178986497384215</v>
       </c>
       <c r="D449" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E449">
         <v>2.314617511168604</v>
@@ -23838,7 +23856,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23852,7 +23870,7 @@
         <v>2.102063686280291</v>
       </c>
       <c r="D450" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E450">
         <v>1.943017649394564</v>
@@ -23888,7 +23906,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23902,7 +23920,7 @@
         <v>1.867386635610175</v>
       </c>
       <c r="D451" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E451">
         <v>1.980155760051744</v>
@@ -23938,7 +23956,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -23952,7 +23970,7 @@
         <v>2.182944230037506</v>
       </c>
       <c r="D452" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E452">
         <v>2.319089525466108</v>
@@ -23988,7 +24006,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24002,7 +24020,7 @@
         <v>2.106580420720769</v>
       </c>
       <c r="D453" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E453">
         <v>1.947780344621405</v>
@@ -24038,7 +24056,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24052,7 +24070,7 @@
         <v>1.871635049192803</v>
       </c>
       <c r="D454" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E454">
         <v>1.984180572919497</v>
@@ -24088,7 +24106,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24102,7 +24120,7 @@
         <v>2.18904965856885</v>
       </c>
       <c r="D455" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E455">
         <v>2.325988314767062</v>
@@ -24138,7 +24156,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24152,7 +24170,7 @@
         <v>2.113548197914732</v>
       </c>
       <c r="D456" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E456">
         <v>1.955127555226921</v>
@@ -24188,7 +24206,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24202,7 +24220,7 @@
         <v>1.878188899028709</v>
       </c>
       <c r="D457" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E457">
         <v>2.015269716995014</v>
@@ -24238,7 +24256,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24252,7 +24270,7 @@
         <v>1.88583444385064</v>
       </c>
       <c r="D458" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E458">
         <v>2.125307034142769</v>
@@ -24288,7 +24306,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24302,7 +24320,7 @@
         <v>2.298073483752043</v>
       </c>
       <c r="D459" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E459">
         <v>2.037664496092738</v>
@@ -24338,7 +24356,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24352,7 +24370,7 @@
         <v>1.897427651995606</v>
       </c>
       <c r="D460" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E460">
         <v>2.100495646236972</v>
@@ -24388,7 +24406,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24402,7 +24420,7 @@
         <v>1.886668859096591</v>
       </c>
       <c r="D461" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E461">
         <v>2.126294507806616</v>
@@ -24438,7 +24456,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24452,7 +24470,7 @@
         <v>2.29919426636051</v>
       </c>
       <c r="D462" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E462">
         <v>2.038997585538931</v>
@@ -24488,7 +24506,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24502,7 +24520,7 @@
         <v>1.898642244602138</v>
       </c>
       <c r="D463" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E463">
         <v>2.102411345144836</v>
@@ -24538,7 +24556,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24552,7 +24570,7 @@
         <v>1.887695818378956</v>
       </c>
       <c r="D464" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E464">
         <v>2.127509844235451</v>
@@ -24588,7 +24606,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24638,7 +24656,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24652,7 +24670,7 @@
         <v>1.900137108409605</v>
       </c>
       <c r="D466" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E466">
         <v>2.104769097816775</v>
@@ -24688,7 +24706,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24702,7 +24720,7 @@
         <v>1.882492570308907</v>
       </c>
       <c r="D467" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E467">
         <v>2.121352154211724</v>
@@ -24738,7 +24756,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24788,7 +24806,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24802,7 +24820,7 @@
         <v>1.911660475077831</v>
       </c>
       <c r="D469" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E469">
         <v>2.092823179170745</v>
@@ -24838,7 +24856,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24852,7 +24870,7 @@
         <v>1.879971436092785</v>
       </c>
       <c r="D470" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E470">
         <v>2.118368563423415</v>
@@ -24888,7 +24906,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24938,7 +24956,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -24952,7 +24970,7 @@
         <v>1.90788623273062</v>
       </c>
       <c r="D472" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E472">
         <v>2.087035013041425</v>
@@ -24988,7 +25006,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25052,7 +25070,7 @@
         <v>1.89858988459332</v>
       </c>
       <c r="D474" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E474">
         <v>2.07277816293363</v>
@@ -25102,7 +25120,7 @@
         <v>2.27342525786704</v>
       </c>
       <c r="D475" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E475">
         <v>2.050890844436287</v>
@@ -25138,7 +25156,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25152,7 +25170,7 @@
         <v>1.889192027490578</v>
       </c>
       <c r="D476" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E476">
         <v>2.058365638997408</v>
@@ -25188,7 +25206,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25202,7 +25220,7 @@
         <v>2.266210657543448</v>
       </c>
       <c r="D477" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E477">
         <v>2.042055342718407</v>
@@ -25238,7 +25256,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25252,7 +25270,7 @@
         <v>1.881151085279702</v>
       </c>
       <c r="D478" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E478">
         <v>2.046034075448713</v>
@@ -25288,7 +25306,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25302,7 +25320,7 @@
         <v>2.259792939301354</v>
       </c>
       <c r="D479" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E479">
         <v>2.034195758263333</v>
@@ -25338,7 +25356,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25352,7 +25370,7 @@
         <v>1.873998297987854</v>
       </c>
       <c r="D480" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E480">
         <v>2.061056685064424</v>
@@ -25388,7 +25406,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25402,7 +25420,7 @@
         <v>2.247400638043782</v>
       </c>
       <c r="D481" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E481">
         <v>2.019019283595469</v>
@@ -25438,7 +25456,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25452,7 +25470,7 @@
         <v>1.860186614207387</v>
       </c>
       <c r="D482" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E482">
         <v>2.039929722127505</v>
@@ -25488,7 +25506,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25502,7 +25520,7 @@
         <v>2.218696305669633</v>
       </c>
       <c r="D483" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E483">
         <v>1.983865960247392</v>
@@ -25538,7 +25556,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25552,7 +25570,7 @@
         <v>1.828194560944569</v>
       </c>
       <c r="D484" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E484">
         <v>1.990993261207699</v>
@@ -25588,7 +25606,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25602,7 +25620,7 @@
         <v>1.830127541068264</v>
       </c>
       <c r="D485" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E485">
         <v>2.018032125375022</v>
@@ -25638,7 +25656,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25688,7 +25706,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25702,7 +25720,7 @@
         <v>1.78228507381279</v>
       </c>
       <c r="D487" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E487">
         <v>2.022800472072064</v>
@@ -25738,7 +25756,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25752,7 +25770,7 @@
         <v>1.783722556644772</v>
       </c>
       <c r="D488" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E488">
         <v>1.972929321636883</v>
@@ -25788,7 +25806,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25802,7 +25820,7 @@
         <v>2.163345062458509</v>
       </c>
       <c r="D489" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E489">
         <v>1.877414831999107</v>
@@ -25838,7 +25856,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25852,7 +25870,7 @@
         <v>1.693507313006611</v>
       </c>
       <c r="D490" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E490">
         <v>1.978388335287718</v>
@@ -25888,7 +25906,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25902,7 +25920,7 @@
         <v>1.734543015346852</v>
       </c>
       <c r="D491" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E491">
         <v>1.925129818487629</v>
@@ -25938,7 +25956,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -25952,7 +25970,7 @@
         <v>1.684218514250647</v>
       </c>
       <c r="D492" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E492">
         <v>1.570048693213578</v>
@@ -25988,7 +26006,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26002,7 +26020,7 @@
         <v>2.132031608016207</v>
       </c>
       <c r="D493" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E493">
         <v>1.840169754028087</v>
@@ -26038,7 +26056,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26052,7 +26070,7 @@
         <v>1.660262632299145</v>
       </c>
       <c r="D494" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E494">
         <v>1.929555899725715</v>
@@ -26088,7 +26106,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26102,7 +26120,7 @@
         <v>1.680468679922261</v>
       </c>
       <c r="D495" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E495">
         <v>1.872572875128523</v>
@@ -26138,7 +26156,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26152,7 +26170,7 @@
         <v>1.634006631356384</v>
       </c>
       <c r="D496" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E496">
         <v>1.60382087481427</v>
@@ -26188,7 +26206,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26202,7 +26220,7 @@
         <v>2.09863804467423</v>
       </c>
       <c r="D497" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E497">
         <v>1.800450537718246</v>
@@ -26238,7 +26256,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26252,7 +26270,7 @@
         <v>1.624809554037398</v>
       </c>
       <c r="D498" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E498">
         <v>1.877479593897257</v>
@@ -26288,7 +26306,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26302,7 +26320,7 @@
         <v>1.622802262168714</v>
       </c>
       <c r="D499" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E499">
         <v>1.752483946759322</v>
@@ -26338,7 +26356,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26352,7 +26370,7 @@
         <v>1.580459243442377</v>
       </c>
       <c r="D500" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E500">
         <v>1.752483946759322</v>
@@ -26388,7 +26406,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26402,7 +26420,7 @@
         <v>2.071221135479056</v>
       </c>
       <c r="D501" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E501">
         <v>1.767840117089625</v>
@@ -26438,7 +26456,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26452,7 +26470,7 @@
         <v>1.595701734142962</v>
       </c>
       <c r="D502" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E502">
         <v>1.834723709073065</v>
@@ -26488,7 +26506,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26538,7 +26556,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26588,7 +26606,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26602,7 +26620,7 @@
         <v>2.041322179557651</v>
       </c>
       <c r="D505" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E505">
         <v>1.73227748229324</v>
@@ -26638,7 +26656,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26652,7 +26670,7 @@
         <v>1.563958789750633</v>
       </c>
       <c r="D506" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E506">
         <v>1.788097143451137</v>
@@ -26688,7 +26706,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26702,7 +26720,7 @@
         <v>1.472686344256899</v>
       </c>
       <c r="D507" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E507">
         <v>1.788097143451137</v>
@@ -26738,7 +26756,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26752,7 +26770,7 @@
         <v>1.523825085403519</v>
       </c>
       <c r="D508" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E508">
         <v>1.630370751283219</v>
@@ -26788,7 +26806,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26802,7 +26820,7 @@
         <v>1.56168905637971</v>
       </c>
       <c r="D509" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E509">
         <v>1.630370751283219</v>
@@ -26838,7 +26856,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26852,7 +26870,7 @@
         <v>1.565051671294496</v>
       </c>
       <c r="D510" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E510">
         <v>1.630370751283219</v>
@@ -26888,7 +26906,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26902,7 +26920,7 @@
         <v>1.866585623391427</v>
       </c>
       <c r="D511" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E511">
         <v>1.689366599623595</v>
@@ -26938,7 +26956,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -26952,7 +26970,7 @@
         <v>2.005245252276134</v>
       </c>
       <c r="D512" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E512">
         <v>1.689366599623595</v>
@@ -26988,7 +27006,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27002,7 +27020,7 @@
         <v>1.4318415411232</v>
       </c>
       <c r="D513" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E513">
         <v>1.73183620839538</v>
@@ -27038,7 +27056,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27052,7 +27070,7 @@
         <v>1.461524840934997</v>
       </c>
       <c r="D514" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E514">
         <v>1.564205583165584</v>
@@ -27088,7 +27106,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27102,7 +27120,7 @@
         <v>1.496369157204806</v>
       </c>
       <c r="D515" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E515">
         <v>1.564205583165584</v>
@@ -27138,7 +27156,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27152,7 +27170,7 @@
         <v>1.508949665433811</v>
       </c>
       <c r="D516" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E516">
         <v>1.564205583165584</v>
@@ -27188,7 +27206,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27202,7 +27220,7 @@
         <v>1.973924573324424</v>
       </c>
       <c r="D517" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E517">
         <v>1.612872963807592</v>
@@ -27252,7 +27270,7 @@
         <v>1.396381565393731</v>
       </c>
       <c r="D518" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E518">
         <v>1.682992506417824</v>
@@ -27302,7 +27320,7 @@
         <v>1.467141600577559</v>
       </c>
       <c r="D519" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E519">
         <v>1.682992506417824</v>
@@ -27352,7 +27370,7 @@
         <v>1.407438029705613</v>
       </c>
       <c r="D520" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E520">
         <v>1.521706666475579</v>
@@ -27402,7 +27420,7 @@
         <v>1.439660791349507</v>
       </c>
       <c r="D521" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E521">
         <v>1.521706666475579</v>
@@ -27452,7 +27470,7 @@
         <v>1.460243940015513</v>
       </c>
       <c r="D522" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E522">
         <v>1.521706666475579</v>
@@ -27502,7 +27520,7 @@
         <v>1.940579116805523</v>
       </c>
       <c r="D523" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E523">
         <v>1.574239241056619</v>
@@ -27538,7 +27556,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27552,7 +27570,7 @@
         <v>1.781069303182167</v>
       </c>
       <c r="D524" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E524">
         <v>1.574239241056619</v>
@@ -27588,7 +27606,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27602,7 +27620,7 @@
         <v>1.358629220348103</v>
       </c>
       <c r="D525" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E525">
         <v>1.630991221802445</v>
@@ -27638,7 +27656,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27652,7 +27670,7 @@
         <v>1.349854686289714</v>
       </c>
       <c r="D526" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E526">
         <v>1.479202912629048</v>
@@ -27688,7 +27706,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27702,7 +27720,7 @@
         <v>1.379286418533347</v>
       </c>
       <c r="D527" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E527">
         <v>1.479202912629048</v>
@@ -27738,7 +27756,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27752,7 +27770,7 @@
         <v>1.408389551684359</v>
       </c>
       <c r="D528" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E528">
         <v>1.479202912629048</v>
@@ -27788,7 +27806,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -27802,7 +27820,7 @@
         <v>1.74645545085387</v>
       </c>
       <c r="D529" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E529">
         <v>1.54184264617284</v>
@@ -27852,7 +27870,7 @@
         <v>1.326971711279163</v>
       </c>
       <c r="D530" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E530">
         <v>1.58738515872694</v>
@@ -28052,7 +28070,7 @@
         <v>1.276676327166428</v>
       </c>
       <c r="D534" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E534">
         <v>1.518106691894613</v>
@@ -28088,7 +28106,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28102,7 +28120,7 @@
         <v>1.224852607973696</v>
       </c>
       <c r="D535" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E535">
         <v>1.33929930838555</v>
@@ -28138,7 +28156,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28152,7 +28170,7 @@
         <v>1.248225566013237</v>
       </c>
       <c r="D536" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E536">
         <v>1.33929930838555</v>
@@ -28188,7 +28206,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28202,7 +28220,7 @@
         <v>1.263762437199394</v>
       </c>
       <c r="D537" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E537">
         <v>1.33929930838555</v>
@@ -28238,7 +28256,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28252,7 +28270,7 @@
         <v>1.212947744952629</v>
       </c>
       <c r="D538" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E538">
         <v>1.430324909390002</v>
@@ -28288,7 +28306,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28302,7 +28320,7 @@
         <v>1.146309428698562</v>
       </c>
       <c r="D539" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E539">
         <v>1.238758183620087</v>
@@ -28338,7 +28356,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28352,7 +28370,7 @@
         <v>1.216483509339664</v>
       </c>
       <c r="D540" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E540">
         <v>1.238758183620087</v>
@@ -28388,7 +28406,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28402,7 +28420,7 @@
         <v>1.171021231954409</v>
       </c>
       <c r="D541" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E541">
         <v>1.238758183620087</v>
@@ -28438,7 +28456,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28488,7 +28506,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28538,7 +28556,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28588,7 +28606,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28602,7 +28620,7 @@
         <v>0.913889681656368</v>
       </c>
       <c r="D545" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E545">
         <v>0.9422215166785484</v>
@@ -28638,7 +28656,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28652,7 +28670,7 @@
         <v>0.9595249171276929</v>
       </c>
       <c r="D546" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E546">
         <v>0.9422215166785484</v>
@@ -28688,7 +28706,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28702,7 +28720,7 @@
         <v>0.9589976550364385</v>
       </c>
       <c r="D547" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E547">
         <v>0.9422215166785484</v>
@@ -28738,7 +28756,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28752,7 +28770,7 @@
         <v>0.8504189521355614</v>
       </c>
       <c r="D548" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E548">
         <v>0.937857691146331</v>
@@ -28788,7 +28806,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28802,7 +28820,7 @@
         <v>0.9017680975637474</v>
       </c>
       <c r="D549" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E549">
         <v>0.937857691146331</v>
@@ -28838,7 +28856,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28852,7 +28870,7 @@
         <v>0.908653475416529</v>
       </c>
       <c r="D550" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E550">
         <v>0.937857691146331</v>
@@ -28888,7 +28906,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28938,7 +28956,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -28988,7 +29006,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29038,7 +29056,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29052,7 +29070,7 @@
         <v>0.7994059700977925</v>
       </c>
       <c r="D554" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E554">
         <v>0.9510460107817367</v>
@@ -29088,7 +29106,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29102,7 +29120,7 @@
         <v>0.8553475251011551</v>
       </c>
       <c r="D555" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E555">
         <v>0.9510460107817367</v>
@@ -29138,7 +29156,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29152,7 +29170,7 @@
         <v>0.8681906234838945</v>
       </c>
       <c r="D556" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E556">
         <v>0.9510460107817367</v>
@@ -29188,7 +29206,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29238,7 +29256,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29252,7 +29270,7 @@
         <v>0.7963844516425689</v>
       </c>
       <c r="D558" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E558">
         <v>0.9293442447455118</v>
@@ -29288,7 +29306,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29302,7 +29320,7 @@
         <v>0.9077462565202601</v>
       </c>
       <c r="D559" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E559">
         <v>0.9293442447455118</v>
@@ -29338,7 +29356,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29352,7 +29370,7 @@
         <v>0.8525980168231655</v>
       </c>
       <c r="D560" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E560">
         <v>0.9293442447455118</v>
@@ -29388,7 +29406,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29402,7 +29420,7 @@
         <v>0.8657939932736682</v>
       </c>
       <c r="D561" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E561">
         <v>0.9293442447455118</v>
@@ -29438,7 +29456,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29488,7 +29506,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29538,7 +29556,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29588,7 +29606,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29638,7 +29656,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29688,7 +29706,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29738,7 +29756,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -29788,7 +29806,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -29838,7 +29856,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -29888,7 +29906,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29938,7 +29956,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -29988,7 +30006,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30038,7 +30056,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30088,7 +30106,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30138,7 +30156,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30188,7 +30206,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30238,7 +30256,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30288,7 +30306,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30338,7 +30356,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30388,7 +30406,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30438,7 +30456,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30488,7 +30506,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30502,7 +30520,7 @@
         <v>0.751468861471289</v>
       </c>
       <c r="D583" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E583">
         <v>0.9385035221553486</v>
@@ -30538,7 +30556,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30552,7 +30570,7 @@
         <v>0.7709845877750583</v>
       </c>
       <c r="D584" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E584">
         <v>0.9385035221553486</v>
@@ -30588,7 +30606,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30602,7 +30620,7 @@
         <v>0.8117259226040443</v>
       </c>
       <c r="D585" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E585">
         <v>0.9385035221553486</v>
@@ -30638,7 +30656,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30652,7 +30670,7 @@
         <v>0.830167515424916</v>
       </c>
       <c r="D586" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E586">
         <v>0.9385035221553486</v>
@@ -30688,7 +30706,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30702,7 +30720,7 @@
         <v>0.8384277846341899</v>
       </c>
       <c r="D587" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E587">
         <v>0.9385035221553486</v>
@@ -30738,7 +30756,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31102,7 +31120,7 @@
         <v>0.8616555364163685</v>
       </c>
       <c r="D595" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E595">
         <v>0.9487042537756789</v>
@@ -31152,7 +31170,7 @@
         <v>0.8685708400378545</v>
       </c>
       <c r="D596" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E596">
         <v>0.9487042537756789</v>
@@ -31202,7 +31220,7 @@
         <v>0.9283666743289771</v>
       </c>
       <c r="D597" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E597">
         <v>0.9487042537756789</v>
@@ -31252,7 +31270,7 @@
         <v>0.9119931158630705</v>
       </c>
       <c r="D598" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E598">
         <v>0.9487042537756789</v>
@@ -31302,7 +31320,7 @@
         <v>0.917566191902035</v>
       </c>
       <c r="D599" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E599">
         <v>0.9487042537756789</v>
@@ -31352,7 +31370,7 @@
         <v>0.8850151504748149</v>
       </c>
       <c r="D600" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E600">
         <v>0.9487042537756789</v>
@@ -31402,7 +31420,7 @@
         <v>0.9303840608049012</v>
       </c>
       <c r="D601" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E601">
         <v>0.9487042537756789</v>
@@ -31452,7 +31470,7 @@
         <v>0.9319931158630701</v>
       </c>
       <c r="D602" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E602">
         <v>0.9487042537756789</v>
@@ -31538,7 +31556,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31588,7 +31606,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31638,7 +31656,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -31688,7 +31706,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31738,7 +31756,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31788,7 +31806,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31838,7 +31856,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31888,7 +31906,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -31938,7 +31956,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -31988,7 +32006,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32038,7 +32056,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32088,7 +32106,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32138,7 +32156,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32188,7 +32206,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32238,7 +32256,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32288,7 +32306,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32338,7 +32356,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32388,7 +32406,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32438,7 +32456,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32488,7 +32506,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32538,7 +32556,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32588,7 +32606,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32638,7 +32656,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32688,7 +32706,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32738,7 +32756,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32788,7 +32806,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32838,7 +32856,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32888,7 +32906,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32938,7 +32956,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -32988,7 +33006,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33038,7 +33056,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33088,7 +33106,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33138,7 +33156,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33188,7 +33206,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33238,7 +33256,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33288,7 +33306,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33302,7 +33320,7 @@
         <v>0.9426739735459577</v>
       </c>
       <c r="D639" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E639">
         <v>1.155481591635229</v>
@@ -33338,7 +33356,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33352,7 +33370,7 @@
         <v>0.9523699059372155</v>
       </c>
       <c r="D640" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E640">
         <v>0.9617333668754942</v>
@@ -33388,7 +33406,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33402,7 +33420,7 @@
         <v>0.9489115468641032</v>
       </c>
       <c r="D641" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E641">
         <v>0.9617333668754942</v>
@@ -33438,7 +33456,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33452,7 +33470,7 @@
         <v>0.994540984964766</v>
       </c>
       <c r="D642" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E642">
         <v>0.9617333668754942</v>
@@ -33488,7 +33506,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33502,7 +33520,7 @@
         <v>0.9895196820815877</v>
       </c>
       <c r="D643" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E643">
         <v>0.9617333668754942</v>
@@ -33538,7 +33556,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33552,7 +33570,7 @@
         <v>0.9598379516124478</v>
       </c>
       <c r="D644" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E644">
         <v>0.9617333668754942</v>
@@ -33588,7 +33606,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33602,7 +33620,7 @@
         <v>1.006089726852713</v>
       </c>
       <c r="D645" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E645">
         <v>0.9617333668754942</v>
@@ -33638,7 +33656,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33652,7 +33670,7 @@
         <v>0.9848592544956265</v>
       </c>
       <c r="D646" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E646">
         <v>0.9617333668754942</v>
@@ -33688,7 +33706,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33952,7 +33970,7 @@
         <v>0.9734565125913943</v>
       </c>
       <c r="D652" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E652">
         <v>1.185400334942146</v>
@@ -34002,7 +34020,7 @@
         <v>0.9846444558037319</v>
       </c>
       <c r="D653" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E653">
         <v>1.181231801994401</v>
@@ -34052,7 +34070,7 @@
         <v>0.9774953331205798</v>
       </c>
       <c r="D654" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E654">
         <v>1.181231801994401</v>
@@ -34102,7 +34120,7 @@
         <v>1.023910040074443</v>
       </c>
       <c r="D655" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E655">
         <v>1.181231801994401</v>
@@ -34152,7 +34170,7 @@
         <v>1.015119446695905</v>
       </c>
       <c r="D656" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E656">
         <v>1.181231801994401</v>
@@ -34202,7 +34220,7 @@
         <v>0.9864585657359251</v>
       </c>
       <c r="D657" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E657">
         <v>1.181231801994401</v>
@@ -34252,7 +34270,7 @@
         <v>1.007646508948263</v>
       </c>
       <c r="D658" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E658">
         <v>1.181231801994401</v>
@@ -34302,7 +34320,7 @@
         <v>1.015249159114463</v>
       </c>
       <c r="D659" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E659">
         <v>0.9834565125913941</v>
@@ -34388,7 +34406,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34438,7 +34456,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34488,7 +34506,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34538,7 +34556,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34588,7 +34606,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34602,7 +34620,7 @@
         <v>0.9989502799212269</v>
       </c>
       <c r="D665" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E665">
         <v>1.210178715943846</v>
@@ -34638,7 +34656,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34652,7 +34670,7 @@
         <v>1.011373890427612</v>
       </c>
       <c r="D666" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E666">
         <v>1.203864024011701</v>
@@ -34688,7 +34706,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -34702,7 +34720,7 @@
         <v>1.00116811706971</v>
       </c>
       <c r="D667" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E667">
         <v>1.203864024011701</v>
@@ -34738,7 +34756,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -34752,7 +34770,7 @@
         <v>1.048233175230966</v>
       </c>
       <c r="D668" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E668">
         <v>1.203864024011701</v>
@@ -34788,7 +34806,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -34802,7 +34820,7 @@
         <v>1.036320896056939</v>
       </c>
       <c r="D669" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E669">
         <v>1.203864024011701</v>
@@ -34838,7 +34856,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -34852,7 +34870,7 @@
         <v>1.008505471666571</v>
       </c>
       <c r="D670" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E670">
         <v>1.203864024011701</v>
@@ -34888,7 +34906,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -34902,7 +34920,7 @@
         <v>1.030929082172957</v>
       </c>
       <c r="D671" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E671">
         <v>1.203864024011701</v>
@@ -34938,7 +34956,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -34952,7 +34970,7 @@
         <v>1.040417750840599</v>
       </c>
       <c r="D672" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E672">
         <v>0.9957763031857296</v>
@@ -34988,7 +35006,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35038,7 +35056,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35088,7 +35106,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35138,7 +35156,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35188,7 +35206,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35202,7 +35220,7 @@
         <v>1.019721542843001</v>
       </c>
       <c r="D677" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E677">
         <v>1.230367111793835</v>
@@ -35238,7 +35256,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35252,7 +35270,7 @@
         <v>1.033151923746106</v>
       </c>
       <c r="D678" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E678">
         <v>1.222303818646338</v>
@@ -35288,7 +35306,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35302,7 +35320,7 @@
         <v>1.020455718354215</v>
       </c>
       <c r="D679" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E679">
         <v>1.222303818646338</v>
@@ -35338,7 +35356,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35352,7 +35370,7 @@
         <v>1.053594956548007</v>
       </c>
       <c r="D680" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E680">
         <v>1.222303818646338</v>
@@ -35388,7 +35406,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35402,7 +35420,7 @@
         <v>1.026468375060656</v>
       </c>
       <c r="D681" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E681">
         <v>1.222303818646338</v>
@@ -35438,7 +35456,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35452,7 +35470,7 @@
         <v>1.049898755963761</v>
       </c>
       <c r="D682" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E682">
         <v>1.222303818646338</v>
@@ -35488,7 +35506,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35502,7 +35520,7 @@
         <v>1.060924074184289</v>
       </c>
       <c r="D683" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E683">
         <v>1.017873442550878</v>
@@ -35538,7 +35556,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35588,7 +35606,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35638,7 +35656,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35688,7 +35706,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35738,7 +35756,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -35752,7 +35770,7 @@
         <v>1.047332978384417</v>
       </c>
       <c r="D688" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E688">
         <v>1.257203736644038</v>
@@ -35788,7 +35806,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -35802,7 +35820,7 @@
         <v>1.062101668663253</v>
       </c>
       <c r="D689" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E689">
         <v>1.2468160114229</v>
@@ -35838,7 +35856,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -35852,7 +35870,7 @@
         <v>1.046094908499815</v>
       </c>
       <c r="D690" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E690">
         <v>1.2468160114229</v>
@@ -35888,7 +35906,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -35902,7 +35920,7 @@
         <v>1.076557527942143</v>
       </c>
       <c r="D691" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E691">
         <v>1.2468160114229</v>
@@ -35938,7 +35956,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -35952,7 +35970,7 @@
         <v>1.050346631817136</v>
       </c>
       <c r="D692" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E692">
         <v>1.2468160114229</v>
@@ -35988,7 +36006,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36002,7 +36020,7 @@
         <v>1.075115322095972</v>
       </c>
       <c r="D693" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E693">
         <v>1.2468160114229</v>
@@ -36038,7 +36056,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36052,7 +36070,7 @@
         <v>1.043673116249803</v>
       </c>
       <c r="D694" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E694">
         <v>1.123802357990182</v>
@@ -36088,7 +36106,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36102,7 +36120,7 @@
         <v>3.139280458423625</v>
       </c>
       <c r="D695" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E695">
         <v>3.025106410332782</v>
@@ -36138,7 +36156,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36152,7 +36170,7 @@
         <v>3.093454506514468</v>
       </c>
       <c r="D696" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E696">
         <v>3.025106410332782</v>
@@ -36188,7 +36206,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36202,7 +36220,7 @@
         <v>3.013365929424353</v>
       </c>
       <c r="D697" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E697">
         <v>3.025106410332782</v>
@@ -36238,7 +36256,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36252,7 +36270,7 @@
         <v>3.208498795059524</v>
       </c>
       <c r="D698" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E698">
         <v>3.025106410332782</v>
@@ -36288,7 +36306,207 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>240</v>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="699" spans="1:16">
+      <c r="A699" s="1">
+        <v>0</v>
+      </c>
+      <c r="B699" t="s">
+        <v>145</v>
+      </c>
+      <c r="C699">
+        <v>-0.6713547876021693</v>
+      </c>
+      <c r="D699" t="s">
+        <v>247</v>
+      </c>
+      <c r="E699">
+        <v>-0.836346559131746</v>
+      </c>
+      <c r="F699">
+        <v>-1</v>
+      </c>
+      <c r="G699">
+        <v>0.01261135478760217</v>
+      </c>
+      <c r="H699">
+        <v>0.01247634655913175</v>
+      </c>
+      <c r="I699">
+        <v>0.1649917715295768</v>
+      </c>
+      <c r="J699">
+        <v>1.4991771529576</v>
+      </c>
+      <c r="K699">
+        <v>4.43</v>
+      </c>
+      <c r="L699">
+        <v>5.97</v>
+      </c>
+      <c r="M699">
+        <v>4.44</v>
+      </c>
+      <c r="N699">
+        <v>5.82</v>
+      </c>
+      <c r="O699">
+        <v>1</v>
+      </c>
+      <c r="P699" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="700" spans="1:16">
+      <c r="A700" s="1">
+        <v>0</v>
+      </c>
+      <c r="B700" t="s">
+        <v>145</v>
+      </c>
+      <c r="C700">
+        <v>-0.7003130836946401</v>
+      </c>
+      <c r="D700" t="s">
+        <v>247</v>
+      </c>
+      <c r="E700">
+        <v>-0.8653702238384202</v>
+      </c>
+      <c r="F700">
+        <v>-1</v>
+      </c>
+      <c r="G700">
+        <v>0.01264031308369464</v>
+      </c>
+      <c r="H700">
+        <v>0.01250537022383842</v>
+      </c>
+      <c r="I700">
+        <v>0.1650571401437801</v>
+      </c>
+      <c r="J700">
+        <v>1.505714014378023</v>
+      </c>
+      <c r="K700">
+        <v>4.43</v>
+      </c>
+      <c r="L700">
+        <v>5.97</v>
+      </c>
+      <c r="M700">
+        <v>4.44</v>
+      </c>
+      <c r="N700">
+        <v>5.82</v>
+      </c>
+      <c r="O700">
+        <v>1</v>
+      </c>
+      <c r="P700" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="701" spans="1:16">
+      <c r="A701" s="1">
+        <v>0</v>
+      </c>
+      <c r="B701" t="s">
+        <v>145</v>
+      </c>
+      <c r="C701">
+        <v>-0.7365419644915843</v>
+      </c>
+      <c r="D701" t="s">
+        <v>247</v>
+      </c>
+      <c r="E701">
+        <v>-0.9016808854046587</v>
+      </c>
+      <c r="F701">
+        <v>-1</v>
+      </c>
+      <c r="G701">
+        <v>0.01267654196449158</v>
+      </c>
+      <c r="H701">
+        <v>0.01254168088540466</v>
+      </c>
+      <c r="I701">
+        <v>0.1651389209130745</v>
+      </c>
+      <c r="J701">
+        <v>1.513892091307355</v>
+      </c>
+      <c r="K701">
+        <v>4.43</v>
+      </c>
+      <c r="L701">
+        <v>5.97</v>
+      </c>
+      <c r="M701">
+        <v>4.44</v>
+      </c>
+      <c r="N701">
+        <v>5.82</v>
+      </c>
+      <c r="O701">
+        <v>1</v>
+      </c>
+      <c r="P701" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="702" spans="1:16">
+      <c r="A702" s="1">
+        <v>0</v>
+      </c>
+      <c r="B702" t="s">
+        <v>145</v>
+      </c>
+      <c r="C702">
+        <v>-0.7725148660088745</v>
+      </c>
+      <c r="D702" t="s">
+        <v>247</v>
+      </c>
+      <c r="E702">
+        <v>-0.9377349898599103</v>
+      </c>
+      <c r="F702">
+        <v>-1</v>
+      </c>
+      <c r="G702">
+        <v>0.01271251486600888</v>
+      </c>
+      <c r="H702">
+        <v>0.01257773498985991</v>
+      </c>
+      <c r="I702">
+        <v>0.1652201238510358</v>
+      </c>
+      <c r="J702">
+        <v>1.522012385103583</v>
+      </c>
+      <c r="K702">
+        <v>4.43</v>
+      </c>
+      <c r="L702">
+        <v>5.97</v>
+      </c>
+      <c r="M702">
+        <v>4.44</v>
+      </c>
+      <c r="N702">
+        <v>5.82</v>
+      </c>
+      <c r="O702">
+        <v>1</v>
+      </c>
+      <c r="P702" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2115" uniqueCount="345">
   <si>
     <t>trade_time</t>
   </si>
@@ -1050,9 +1050,6 @@
   <si>
     <t>2021-11-01</t>
   </si>
-  <si>
-    <t>2021-11-02</t>
-  </si>
 </sst>
 </file>
 
@@ -1409,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P702"/>
+  <dimension ref="A1:P701"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -36459,56 +36456,6 @@
         <v>344</v>
       </c>
     </row>
-    <row r="702" spans="1:16">
-      <c r="A702" s="1">
-        <v>0</v>
-      </c>
-      <c r="B702" t="s">
-        <v>145</v>
-      </c>
-      <c r="C702">
-        <v>-0.7725148660088745</v>
-      </c>
-      <c r="D702" t="s">
-        <v>247</v>
-      </c>
-      <c r="E702">
-        <v>-0.9377349898599103</v>
-      </c>
-      <c r="F702">
-        <v>-1</v>
-      </c>
-      <c r="G702">
-        <v>0.01271251486600888</v>
-      </c>
-      <c r="H702">
-        <v>0.01257773498985991</v>
-      </c>
-      <c r="I702">
-        <v>0.1652201238510358</v>
-      </c>
-      <c r="J702">
-        <v>1.522012385103583</v>
-      </c>
-      <c r="K702">
-        <v>4.43</v>
-      </c>
-      <c r="L702">
-        <v>5.97</v>
-      </c>
-      <c r="M702">
-        <v>4.44</v>
-      </c>
-      <c r="N702">
-        <v>5.82</v>
-      </c>
-      <c r="O702">
-        <v>1</v>
-      </c>
-      <c r="P702" t="s">
-        <v>345</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2115" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="343">
   <si>
     <t>trade_time</t>
   </si>
@@ -451,7 +451,7 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-11-03</t>
+    <t>2021-11-09</t>
   </si>
   <si>
     <t>2017-04-20</t>
@@ -757,7 +757,7 @@
     <t>2021-08-09</t>
   </si>
   <si>
-    <t>2021-11-04</t>
+    <t>2021-11-10</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -1042,13 +1042,7 @@
     <t>2020-12-24</t>
   </si>
   <si>
-    <t>2021-10-28</t>
-  </si>
-  <si>
-    <t>2021-10-29</t>
-  </si>
-  <si>
-    <t>2021-11-01</t>
+    <t>2021-11-05</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P701"/>
+  <dimension ref="A1:P699"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -36314,146 +36308,46 @@
         <v>145</v>
       </c>
       <c r="C699">
-        <v>-0.6713547876021693</v>
+        <v>-0.9463529760046061</v>
       </c>
       <c r="D699" t="s">
         <v>247</v>
       </c>
       <c r="E699">
-        <v>-0.836346559131746</v>
+        <v>-0.7844366033779329</v>
       </c>
       <c r="F699">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G699">
-        <v>0.01261135478760217</v>
+        <v>0.01188635297600461</v>
       </c>
       <c r="H699">
-        <v>0.01247634655913175</v>
+        <v>0.01158443660337793</v>
       </c>
       <c r="I699">
-        <v>0.1649917715295768</v>
+        <v>0.1619163726266732</v>
       </c>
       <c r="J699">
-        <v>1.4991771529576</v>
+        <v>1.546109150844483</v>
       </c>
       <c r="K699">
-        <v>4.43</v>
+        <v>4.15</v>
       </c>
       <c r="L699">
-        <v>5.97</v>
+        <v>5.47</v>
       </c>
       <c r="M699">
-        <v>4.44</v>
+        <v>4</v>
       </c>
       <c r="N699">
-        <v>5.82</v>
+        <v>5.4</v>
       </c>
       <c r="O699">
         <v>1</v>
       </c>
       <c r="P699" t="s">
         <v>342</v>
-      </c>
-    </row>
-    <row r="700" spans="1:16">
-      <c r="A700" s="1">
-        <v>0</v>
-      </c>
-      <c r="B700" t="s">
-        <v>145</v>
-      </c>
-      <c r="C700">
-        <v>-0.7003130836946401</v>
-      </c>
-      <c r="D700" t="s">
-        <v>247</v>
-      </c>
-      <c r="E700">
-        <v>-0.8653702238384202</v>
-      </c>
-      <c r="F700">
-        <v>-1</v>
-      </c>
-      <c r="G700">
-        <v>0.01264031308369464</v>
-      </c>
-      <c r="H700">
-        <v>0.01250537022383842</v>
-      </c>
-      <c r="I700">
-        <v>0.1650571401437801</v>
-      </c>
-      <c r="J700">
-        <v>1.505714014378023</v>
-      </c>
-      <c r="K700">
-        <v>4.43</v>
-      </c>
-      <c r="L700">
-        <v>5.97</v>
-      </c>
-      <c r="M700">
-        <v>4.44</v>
-      </c>
-      <c r="N700">
-        <v>5.82</v>
-      </c>
-      <c r="O700">
-        <v>1</v>
-      </c>
-      <c r="P700" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="701" spans="1:16">
-      <c r="A701" s="1">
-        <v>0</v>
-      </c>
-      <c r="B701" t="s">
-        <v>145</v>
-      </c>
-      <c r="C701">
-        <v>-0.7365419644915843</v>
-      </c>
-      <c r="D701" t="s">
-        <v>247</v>
-      </c>
-      <c r="E701">
-        <v>-0.9016808854046587</v>
-      </c>
-      <c r="F701">
-        <v>-1</v>
-      </c>
-      <c r="G701">
-        <v>0.01267654196449158</v>
-      </c>
-      <c r="H701">
-        <v>0.01254168088540466</v>
-      </c>
-      <c r="I701">
-        <v>0.1651389209130745</v>
-      </c>
-      <c r="J701">
-        <v>1.513892091307355</v>
-      </c>
-      <c r="K701">
-        <v>4.43</v>
-      </c>
-      <c r="L701">
-        <v>5.97</v>
-      </c>
-      <c r="M701">
-        <v>4.44</v>
-      </c>
-      <c r="N701">
-        <v>5.82</v>
-      </c>
-      <c r="O701">
-        <v>1</v>
-      </c>
-      <c r="P701" t="s">
-        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -451,7 +451,7 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-11-09</t>
+    <t>2021-11-10</t>
   </si>
   <si>
     <t>2017-04-20</t>
@@ -757,7 +757,7 @@
     <t>2021-08-09</t>
   </si>
   <si>
-    <t>2021-11-10</t>
+    <t>2021-11-11</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -1042,7 +1042,7 @@
     <t>2020-12-24</t>
   </si>
   <si>
-    <t>2021-11-05</t>
+    <t>2021-10-28</t>
   </si>
 </sst>
 </file>
@@ -36308,40 +36308,40 @@
         <v>145</v>
       </c>
       <c r="C699">
-        <v>-0.9463529760046061</v>
+        <v>-0.596708611830401</v>
       </c>
       <c r="D699" t="s">
         <v>247</v>
       </c>
       <c r="E699">
-        <v>-0.7844366033779329</v>
+        <v>-0.8715193570106505</v>
       </c>
       <c r="F699">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G699">
-        <v>0.01188635297600461</v>
+        <v>0.0113967086118304</v>
       </c>
       <c r="H699">
-        <v>0.01158443660337793</v>
+        <v>0.01181151935701065</v>
       </c>
       <c r="I699">
-        <v>0.1619163726266732</v>
+        <v>0.2748107451802495</v>
       </c>
       <c r="J699">
-        <v>1.546109150844483</v>
+        <v>1.4991771529576</v>
       </c>
       <c r="K699">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="L699">
+        <v>5.4</v>
+      </c>
+      <c r="M699">
+        <v>4.23</v>
+      </c>
+      <c r="N699">
         <v>5.47</v>
-      </c>
-      <c r="M699">
-        <v>4</v>
-      </c>
-      <c r="N699">
-        <v>5.4</v>
       </c>
       <c r="O699">
         <v>1</v>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="354">
   <si>
     <t>trade_time</t>
   </si>
@@ -769,6 +769,9 @@
     <t>2021-11-11</t>
   </si>
   <si>
+    <t>2021-11-16</t>
+  </si>
+  <si>
     <t>2021-11-15</t>
   </si>
   <si>
@@ -1430,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P716"/>
+  <dimension ref="A1:P717"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1527,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1577,7 +1580,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1627,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1677,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1727,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1777,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1827,7 +1830,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1877,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1927,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1977,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2027,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2077,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2127,7 +2130,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2177,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2227,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2277,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2327,7 +2330,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2377,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2427,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2477,7 +2480,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2527,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2577,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2627,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2677,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2727,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2777,7 +2780,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2827,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2877,7 +2880,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2927,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2977,7 +2980,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3027,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3077,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3127,7 +3130,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3177,7 +3180,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3227,7 +3230,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3277,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3327,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3377,7 +3380,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3427,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3477,7 +3480,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3527,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3577,7 +3580,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3627,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3677,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3727,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4777,7 +4780,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4827,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4877,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4927,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4977,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5027,7 +5030,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5077,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5127,7 +5130,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5177,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5227,7 +5230,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5277,7 +5280,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5327,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5377,7 +5380,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5427,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5477,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5527,7 +5530,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5577,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5627,7 +5630,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5677,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5727,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5777,7 +5780,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5827,7 +5830,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5877,7 +5880,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5927,7 +5930,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5977,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6027,7 +6030,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6327,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6377,7 +6380,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6427,7 +6430,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6477,7 +6480,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6527,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6577,7 +6580,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6627,7 +6630,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6677,7 +6680,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6727,7 +6730,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6777,7 +6780,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6827,7 +6830,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6877,7 +6880,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6927,7 +6930,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7277,7 +7280,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7327,7 +7330,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7377,7 +7380,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7427,7 +7430,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7477,7 +7480,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7527,7 +7530,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7577,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7627,7 +7630,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7677,7 +7680,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7727,7 +7730,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7777,7 +7780,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7827,7 +7830,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7877,7 +7880,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8727,7 +8730,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8777,7 +8780,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8827,7 +8830,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8877,7 +8880,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8927,7 +8930,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8977,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9127,7 +9130,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9177,7 +9180,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9227,7 +9230,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9277,7 +9280,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9327,7 +9330,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9377,7 +9380,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9427,7 +9430,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9477,7 +9480,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9527,7 +9530,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9577,7 +9580,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9627,7 +9630,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9677,7 +9680,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10027,7 +10030,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10077,7 +10080,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10227,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10277,7 +10280,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10327,7 +10330,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10377,7 +10380,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10427,7 +10430,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10477,7 +10480,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10527,7 +10530,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10577,7 +10580,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10627,7 +10630,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10677,7 +10680,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10727,7 +10730,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10777,7 +10780,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10827,7 +10830,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10877,7 +10880,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10927,7 +10930,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10977,7 +10980,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11027,7 +11030,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11077,7 +11080,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11127,7 +11130,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11177,7 +11180,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11227,7 +11230,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11277,7 +11280,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11327,7 +11330,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11377,7 +11380,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11427,7 +11430,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11477,7 +11480,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11527,7 +11530,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11577,7 +11580,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11627,7 +11630,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11677,7 +11680,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11727,7 +11730,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11777,7 +11780,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11827,7 +11830,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11877,7 +11880,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11927,7 +11930,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11977,7 +11980,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12027,7 +12030,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12077,7 +12080,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12127,7 +12130,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12177,7 +12180,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12227,7 +12230,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12277,7 +12280,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12327,7 +12330,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12377,7 +12380,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12427,7 +12430,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12477,7 +12480,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12527,7 +12530,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12577,7 +12580,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12877,7 +12880,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12927,7 +12930,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12977,7 +12980,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13027,7 +13030,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13077,7 +13080,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13127,7 +13130,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13177,7 +13180,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13527,7 +13530,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13577,7 +13580,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13627,7 +13630,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13677,7 +13680,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13727,7 +13730,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13777,7 +13780,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13827,7 +13830,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13877,7 +13880,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13927,7 +13930,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13977,7 +13980,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14027,7 +14030,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14077,7 +14080,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14127,7 +14130,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14177,7 +14180,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14227,7 +14230,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14277,7 +14280,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14327,7 +14330,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14377,7 +14380,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14677,7 +14680,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14727,7 +14730,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14777,7 +14780,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14827,7 +14830,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14877,7 +14880,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14927,7 +14930,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14977,7 +14980,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15027,7 +15030,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15077,7 +15080,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15127,7 +15130,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15177,7 +15180,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15227,7 +15230,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15277,7 +15280,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15327,7 +15330,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15377,7 +15380,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15427,7 +15430,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15477,7 +15480,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15527,7 +15530,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15577,7 +15580,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15627,7 +15630,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15677,7 +15680,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15727,7 +15730,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15777,7 +15780,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15827,7 +15830,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15877,7 +15880,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15927,7 +15930,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15977,7 +15980,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16027,7 +16030,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16077,7 +16080,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16127,7 +16130,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16177,7 +16180,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16227,7 +16230,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16277,7 +16280,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16327,7 +16330,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16377,7 +16380,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16427,7 +16430,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16477,7 +16480,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16527,7 +16530,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16577,7 +16580,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16627,7 +16630,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16677,7 +16680,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16727,7 +16730,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16777,7 +16780,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16827,7 +16830,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16877,7 +16880,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16927,7 +16930,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -16977,7 +16980,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17027,7 +17030,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17077,7 +17080,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17127,7 +17130,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17177,7 +17180,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17227,7 +17230,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17277,7 +17280,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17327,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17377,7 +17380,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17427,7 +17430,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17477,7 +17480,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17527,7 +17530,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17577,7 +17580,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17627,7 +17630,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17677,7 +17680,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17727,7 +17730,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17777,7 +17780,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17827,7 +17830,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17877,7 +17880,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17927,7 +17930,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17977,7 +17980,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18027,7 +18030,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18077,7 +18080,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18127,7 +18130,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18177,7 +18180,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18227,7 +18230,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18277,7 +18280,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18327,7 +18330,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18377,7 +18380,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18427,7 +18430,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18477,7 +18480,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18527,7 +18530,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18727,7 +18730,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18777,7 +18780,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18827,7 +18830,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18877,7 +18880,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18927,7 +18930,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18977,7 +18980,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19227,7 +19230,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19277,7 +19280,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19327,7 +19330,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19377,7 +19380,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19627,7 +19630,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19677,7 +19680,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19727,7 +19730,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19777,7 +19780,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19827,7 +19830,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19877,7 +19880,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19927,7 +19930,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19977,7 +19980,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20027,7 +20030,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20077,7 +20080,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20127,7 +20130,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20177,7 +20180,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20227,7 +20230,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20277,7 +20280,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20727,7 +20730,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20777,7 +20780,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20827,7 +20830,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20877,7 +20880,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20927,7 +20930,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20977,7 +20980,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21027,7 +21030,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21077,7 +21080,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21127,7 +21130,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21177,7 +21180,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21227,7 +21230,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21277,7 +21280,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21327,7 +21330,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21377,7 +21380,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21427,7 +21430,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21477,7 +21480,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21527,7 +21530,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21577,7 +21580,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21627,7 +21630,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21677,7 +21680,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21727,7 +21730,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22077,7 +22080,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22127,7 +22130,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22177,7 +22180,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22227,7 +22230,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22277,7 +22280,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22327,7 +22330,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22377,7 +22380,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22427,7 +22430,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22477,7 +22480,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22527,7 +22530,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22577,7 +22580,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22627,7 +22630,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23427,7 +23430,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23477,7 +23480,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23527,7 +23530,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23577,7 +23580,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23627,7 +23630,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23677,7 +23680,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23727,7 +23730,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23777,7 +23780,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23827,7 +23830,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23877,7 +23880,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23927,7 +23930,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23977,7 +23980,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24027,7 +24030,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24077,7 +24080,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24127,7 +24130,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24177,7 +24180,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24227,7 +24230,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24277,7 +24280,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24327,7 +24330,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24377,7 +24380,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24427,7 +24430,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24477,7 +24480,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24527,7 +24530,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24577,7 +24580,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24627,7 +24630,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24677,7 +24680,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24727,7 +24730,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24777,7 +24780,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24827,7 +24830,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24877,7 +24880,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24927,7 +24930,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24977,7 +24980,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25027,7 +25030,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25177,7 +25180,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25227,7 +25230,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25277,7 +25280,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25327,7 +25330,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25377,7 +25380,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25427,7 +25430,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25477,7 +25480,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25527,7 +25530,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25577,7 +25580,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25627,7 +25630,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25677,7 +25680,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25877,7 +25880,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25927,7 +25930,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25977,7 +25980,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26027,7 +26030,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26077,7 +26080,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26127,7 +26130,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26177,7 +26180,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26227,7 +26230,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26277,7 +26280,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26327,7 +26330,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26377,7 +26380,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26427,7 +26430,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26477,7 +26480,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26527,7 +26530,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26577,7 +26580,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26627,7 +26630,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26677,7 +26680,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26727,7 +26730,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26777,7 +26780,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26827,7 +26830,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26877,7 +26880,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26927,7 +26930,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26977,7 +26980,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27027,7 +27030,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27077,7 +27080,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27127,7 +27130,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27177,7 +27180,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27227,7 +27230,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27577,7 +27580,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27627,7 +27630,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27677,7 +27680,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27727,7 +27730,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27777,7 +27780,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27827,7 +27830,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28127,7 +28130,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28177,7 +28180,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28227,7 +28230,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28277,7 +28280,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28327,7 +28330,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28377,7 +28380,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28427,7 +28430,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28477,7 +28480,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28527,7 +28530,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28577,7 +28580,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28627,7 +28630,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28677,7 +28680,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28727,7 +28730,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28777,7 +28780,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28827,7 +28830,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28877,7 +28880,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28927,7 +28930,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28977,7 +28980,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29027,7 +29030,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29077,7 +29080,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29127,7 +29130,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29177,7 +29180,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29227,7 +29230,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29277,7 +29280,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29327,7 +29330,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29377,7 +29380,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29427,7 +29430,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29477,7 +29480,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29527,7 +29530,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29577,7 +29580,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29627,7 +29630,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29677,7 +29680,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29727,7 +29730,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29777,7 +29780,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -29827,7 +29830,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -29877,7 +29880,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -29927,7 +29930,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29977,7 +29980,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30027,7 +30030,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30077,7 +30080,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30127,7 +30130,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30177,7 +30180,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30227,7 +30230,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30277,7 +30280,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30327,7 +30330,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30377,7 +30380,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30427,7 +30430,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30477,7 +30480,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30527,7 +30530,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30577,7 +30580,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30627,7 +30630,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30677,7 +30680,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30727,7 +30730,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30777,7 +30780,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -32327,7 +32330,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32377,7 +32380,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32427,7 +32430,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32477,7 +32480,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32527,7 +32530,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32577,7 +32580,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32627,7 +32630,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32677,7 +32680,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32727,7 +32730,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32777,7 +32780,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32827,7 +32830,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32877,7 +32880,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32927,7 +32930,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32977,7 +32980,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33027,7 +33030,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33077,7 +33080,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33127,7 +33130,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33177,7 +33180,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33227,7 +33230,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33277,7 +33280,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33327,7 +33330,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33377,7 +33380,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33427,7 +33430,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33477,7 +33480,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33527,7 +33530,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33577,7 +33580,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33627,7 +33630,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33677,7 +33680,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33727,7 +33730,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34427,7 +34430,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34477,7 +34480,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34527,7 +34530,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34577,7 +34580,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34627,7 +34630,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34677,7 +34680,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34727,7 +34730,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -34777,7 +34780,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -34827,7 +34830,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -34877,7 +34880,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -34927,7 +34930,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -34977,7 +34980,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35027,7 +35030,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35627,7 +35630,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35677,7 +35680,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35727,7 +35730,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35777,7 +35780,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -35827,7 +35830,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -35877,7 +35880,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -35927,7 +35930,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -35977,7 +35980,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36027,7 +36030,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36077,7 +36080,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36127,7 +36130,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36377,7 +36380,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36427,7 +36430,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36444,7 +36447,7 @@
         <v>251</v>
       </c>
       <c r="E701">
-        <v>-0.8266263271261609</v>
+        <v>-0.8416839264191296</v>
       </c>
       <c r="F701">
         <v>1</v>
@@ -36453,10 +36456,10 @@
         <v>0.01158656049936277</v>
       </c>
       <c r="H701">
-        <v>0.01146662632712616</v>
+        <v>0.01124168392641913</v>
       </c>
       <c r="I701">
-        <v>0.1199341722366078</v>
+        <v>0.1048765729436392</v>
       </c>
       <c r="J701">
         <v>1.4991771529576</v>
@@ -36468,16 +36471,16 @@
         <v>5.32</v>
       </c>
       <c r="M701">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="N701">
-        <v>5.32</v>
+        <v>5.2</v>
       </c>
       <c r="O701">
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36527,7 +36530,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36577,7 +36580,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36627,7 +36630,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36677,7 +36680,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36744,7 +36747,7 @@
         <v>251</v>
       </c>
       <c r="E707">
-        <v>-0.9520503215266229</v>
+        <v>-0.9649665355493404</v>
       </c>
       <c r="F707">
         <v>1</v>
@@ -36753,10 +36756,10 @@
         <v>0.01171443179121495</v>
       </c>
       <c r="H707">
-        <v>0.01159205032152662</v>
+        <v>0.01136496653554934</v>
       </c>
       <c r="I707">
-        <v>0.1223814696883245</v>
+        <v>0.1094652556656071</v>
       </c>
       <c r="J707">
         <v>1.529768371104055</v>
@@ -36768,10 +36771,10 @@
         <v>5.32</v>
       </c>
       <c r="M707">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="N707">
-        <v>5.32</v>
+        <v>5.2</v>
       </c>
       <c r="O707">
         <v>1</v>
@@ -36844,7 +36847,7 @@
         <v>251</v>
       </c>
       <c r="E709">
-        <v>-0.9795256778004955</v>
+        <v>-0.9919728003746338</v>
       </c>
       <c r="F709">
         <v>1</v>
@@ -36853,10 +36856,10 @@
         <v>0.01174244325200148</v>
       </c>
       <c r="H709">
-        <v>0.0116195256778005</v>
+        <v>0.01139197280037463</v>
       </c>
       <c r="I709">
-        <v>0.1229175742009847</v>
+        <v>0.1104704516268464</v>
       </c>
       <c r="J709">
         <v>1.536469677512316</v>
@@ -36868,10 +36871,10 @@
         <v>5.32</v>
       </c>
       <c r="M709">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="N709">
-        <v>5.32</v>
+        <v>5.2</v>
       </c>
       <c r="O709">
         <v>1</v>
@@ -36927,7 +36930,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -36944,7 +36947,7 @@
         <v>251</v>
       </c>
       <c r="E711">
-        <v>-1.019047518462381</v>
+        <v>-1.030819877903268</v>
       </c>
       <c r="F711">
         <v>1</v>
@@ -36953,10 +36956,10 @@
         <v>0.01178273625052994</v>
       </c>
       <c r="H711">
-        <v>0.01165904751846238</v>
+        <v>0.01143081987790327</v>
       </c>
       <c r="I711">
-        <v>0.1236887320675581</v>
+        <v>0.1119163726266716</v>
       </c>
       <c r="J711">
         <v>1.546109150844483</v>
@@ -36968,16 +36971,16 @@
         <v>5.32</v>
       </c>
       <c r="M711">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="N711">
-        <v>5.32</v>
+        <v>5.2</v>
       </c>
       <c r="O711">
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37027,7 +37030,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37044,7 +37047,7 @@
         <v>251</v>
       </c>
       <c r="E713">
-        <v>-1.052888299540232</v>
+        <v>-1.064082889548082</v>
       </c>
       <c r="F713">
         <v>1</v>
@@ -37053,10 +37056,10 @@
         <v>0.01181723733953126</v>
       </c>
       <c r="H713">
-        <v>0.01169288829954023</v>
+        <v>0.01146408288954808</v>
       </c>
       <c r="I713">
-        <v>0.1243490399910288</v>
+        <v>0.1131544499831785</v>
       </c>
       <c r="J713">
         <v>1.554362999887862</v>
@@ -37068,16 +37071,16 @@
         <v>5.32</v>
       </c>
       <c r="M713">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="N713">
-        <v>5.32</v>
+        <v>5.2</v>
       </c>
       <c r="O713">
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37127,7 +37130,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37144,7 +37147,7 @@
         <v>251</v>
       </c>
       <c r="E715">
-        <v>-1.09271669875312</v>
+        <v>-1.103231291701239</v>
       </c>
       <c r="F715">
         <v>1</v>
@@ -37153,10 +37156,10 @@
         <v>0.01185784287824099</v>
       </c>
       <c r="H715">
-        <v>0.01173271669875312</v>
+        <v>0.01150323129170124</v>
       </c>
       <c r="I715">
-        <v>0.1251261794878662</v>
+        <v>0.1146115865397475</v>
       </c>
       <c r="J715">
         <v>1.564077243598322</v>
@@ -37168,16 +37171,16 @@
         <v>5.32</v>
       </c>
       <c r="M715">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="N715">
-        <v>5.32</v>
+        <v>5.2</v>
       </c>
       <c r="O715">
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37194,7 +37197,7 @@
         <v>251</v>
       </c>
       <c r="E716">
-        <v>-1.139411473301573</v>
+        <v>-1.149128838391547</v>
       </c>
       <c r="F716">
         <v>1</v>
@@ -37203,10 +37206,10 @@
         <v>0.0119054487703416</v>
       </c>
       <c r="H716">
-        <v>0.01177941147330157</v>
+        <v>0.01154912883839155</v>
       </c>
       <c r="I716">
-        <v>0.126037297040031</v>
+        <v>0.1163199319500574</v>
       </c>
       <c r="J716">
         <v>1.575466213000384</v>
@@ -37218,16 +37221,66 @@
         <v>5.32</v>
       </c>
       <c r="M716">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="N716">
-        <v>5.32</v>
+        <v>5.2</v>
       </c>
       <c r="O716">
         <v>1</v>
       </c>
       <c r="P716" t="s">
         <v>146</v>
+      </c>
+    </row>
+    <row r="717" spans="1:16">
+      <c r="A717" s="1">
+        <v>0</v>
+      </c>
+      <c r="B717" t="s">
+        <v>147</v>
+      </c>
+      <c r="C717">
+        <v>-1.312504992889616</v>
+      </c>
+      <c r="D717" t="s">
+        <v>252</v>
+      </c>
+      <c r="E717">
+        <v>-1.185567098288857</v>
+      </c>
+      <c r="F717">
+        <v>1</v>
+      </c>
+      <c r="G717">
+        <v>0.01195250499288962</v>
+      </c>
+      <c r="H717">
+        <v>0.01182556709828886</v>
+      </c>
+      <c r="I717">
+        <v>0.1269378946007587</v>
+      </c>
+      <c r="J717">
+        <v>1.586723682509477</v>
+      </c>
+      <c r="K717">
+        <v>4.18</v>
+      </c>
+      <c r="L717">
+        <v>5.32</v>
+      </c>
+      <c r="M717">
+        <v>4.1</v>
+      </c>
+      <c r="N717">
+        <v>5.32</v>
+      </c>
+      <c r="O717">
+        <v>1</v>
+      </c>
+      <c r="P717" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -769,7 +769,7 @@
     <t>2021-11-11</t>
   </si>
   <si>
-    <t>2021-11-16</t>
+    <t>2021-11-17</t>
   </si>
   <si>
     <t>2021-11-15</t>
@@ -36447,7 +36447,7 @@
         <v>251</v>
       </c>
       <c r="E701">
-        <v>-0.8416839264191296</v>
+        <v>-0.7617003833599769</v>
       </c>
       <c r="F701">
         <v>1</v>
@@ -36456,10 +36456,10 @@
         <v>0.01158656049936277</v>
       </c>
       <c r="H701">
-        <v>0.01124168392641913</v>
+        <v>0.01126170038335998</v>
       </c>
       <c r="I701">
-        <v>0.1048765729436392</v>
+        <v>0.1848601160027918</v>
       </c>
       <c r="J701">
         <v>1.4991771529576</v>
@@ -36471,10 +36471,10 @@
         <v>5.32</v>
       </c>
       <c r="M701">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="N701">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="O701">
         <v>1</v>
@@ -36588,43 +36588,43 @@
         <v>0</v>
       </c>
       <c r="B704" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C704">
-        <v>-0.6555683652294215</v>
+        <v>-0.7365419644915843</v>
       </c>
       <c r="D704" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E704">
-        <v>-0.9337635462301144</v>
+        <v>-0.9016808854046587</v>
       </c>
       <c r="F704">
         <v>-1</v>
       </c>
       <c r="G704">
-        <v>0.01145556836522942</v>
+        <v>0.01267654196449158</v>
       </c>
       <c r="H704">
-        <v>0.01187376354623011</v>
+        <v>0.01254168088540466</v>
       </c>
       <c r="I704">
-        <v>0.2781951810006928</v>
+        <v>0.1651389209130745</v>
       </c>
       <c r="J704">
         <v>1.513892091307355</v>
       </c>
       <c r="K704">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="L704">
-        <v>5.4</v>
+        <v>5.97</v>
       </c>
       <c r="M704">
-        <v>4.23</v>
+        <v>4.44</v>
       </c>
       <c r="N704">
-        <v>5.47</v>
+        <v>5.82</v>
       </c>
       <c r="O704">
         <v>1</v>
@@ -36635,34 +36635,34 @@
     </row>
     <row r="705" spans="1:16">
       <c r="A705" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B705" t="s">
         <v>146</v>
       </c>
       <c r="C705">
-        <v>-0.6880495404143332</v>
+        <v>-0.6555683652294215</v>
       </c>
       <c r="D705" t="s">
         <v>250</v>
       </c>
       <c r="E705">
-        <v>-0.9681123889881587</v>
+        <v>-0.9337635462301144</v>
       </c>
       <c r="F705">
         <v>-1</v>
       </c>
       <c r="G705">
-        <v>0.01148804954041433</v>
+        <v>0.01145556836522942</v>
       </c>
       <c r="H705">
-        <v>0.01190811238898816</v>
+        <v>0.01187376354623011</v>
       </c>
       <c r="I705">
-        <v>0.2800628485738255</v>
+        <v>0.2781951810006928</v>
       </c>
       <c r="J705">
-        <v>1.522012385103583</v>
+        <v>1.513892091307355</v>
       </c>
       <c r="K705">
         <v>4</v>
@@ -36680,7 +36680,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36691,28 +36691,28 @@
         <v>146</v>
       </c>
       <c r="C706">
-        <v>-0.7190734844162181</v>
+        <v>-0.6880495404143332</v>
       </c>
       <c r="D706" t="s">
         <v>250</v>
       </c>
       <c r="E706">
-        <v>-1.000920209770152</v>
+        <v>-0.9681123889881587</v>
       </c>
       <c r="F706">
         <v>-1</v>
       </c>
       <c r="G706">
-        <v>0.01151907348441622</v>
+        <v>0.01148804954041433</v>
       </c>
       <c r="H706">
-        <v>0.01194092020977015</v>
+        <v>0.01190811238898816</v>
       </c>
       <c r="I706">
-        <v>0.2818467253539341</v>
+        <v>0.2800628485738255</v>
       </c>
       <c r="J706">
-        <v>1.529768371104055</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K706">
         <v>4</v>
@@ -36730,51 +36730,51 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>145</v>
+        <v>350</v>
       </c>
     </row>
     <row r="707" spans="1:16">
       <c r="A707" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B707" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C707">
-        <v>-1.074431791214947</v>
+        <v>-0.7190734844162181</v>
       </c>
       <c r="D707" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E707">
-        <v>-0.9649665355493404</v>
+        <v>-1.000920209770152</v>
       </c>
       <c r="F707">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G707">
-        <v>0.01171443179121495</v>
+        <v>0.01151907348441622</v>
       </c>
       <c r="H707">
-        <v>0.01136496653554934</v>
+        <v>0.01194092020977015</v>
       </c>
       <c r="I707">
-        <v>0.1094652556656071</v>
+        <v>0.2818467253539341</v>
       </c>
       <c r="J707">
         <v>1.529768371104055</v>
       </c>
       <c r="K707">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="L707">
-        <v>5.32</v>
+        <v>5.4</v>
       </c>
       <c r="M707">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="N707">
-        <v>5.2</v>
+        <v>5.47</v>
       </c>
       <c r="O707">
         <v>1</v>
@@ -36847,7 +36847,7 @@
         <v>251</v>
       </c>
       <c r="E709">
-        <v>-0.9919728003746338</v>
+        <v>-0.9112434068243873</v>
       </c>
       <c r="F709">
         <v>1</v>
@@ -36856,10 +36856,10 @@
         <v>0.01174244325200148</v>
       </c>
       <c r="H709">
-        <v>0.01139197280037463</v>
+        <v>0.01141124340682439</v>
       </c>
       <c r="I709">
-        <v>0.1104704516268464</v>
+        <v>0.1911998451770929</v>
       </c>
       <c r="J709">
         <v>1.536469677512316</v>
@@ -36871,10 +36871,10 @@
         <v>5.32</v>
       </c>
       <c r="M709">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="N709">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="O709">
         <v>1</v>
@@ -36947,7 +36947,7 @@
         <v>251</v>
       </c>
       <c r="E711">
-        <v>-1.030819877903268</v>
+        <v>-0.9498976948863778</v>
       </c>
       <c r="F711">
         <v>1</v>
@@ -36956,10 +36956,10 @@
         <v>0.01178273625052994</v>
       </c>
       <c r="H711">
-        <v>0.01143081987790327</v>
+        <v>0.01144989769488638</v>
       </c>
       <c r="I711">
-        <v>0.1119163726266716</v>
+        <v>0.1928385556435614</v>
       </c>
       <c r="J711">
         <v>1.546109150844483</v>
@@ -36971,10 +36971,10 @@
         <v>5.32</v>
       </c>
       <c r="M711">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="N711">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="O711">
         <v>1</v>
@@ -37047,7 +37047,7 @@
         <v>251</v>
       </c>
       <c r="E713">
-        <v>-1.064082889548082</v>
+        <v>-0.9829956295503246</v>
       </c>
       <c r="F713">
         <v>1</v>
@@ -37056,10 +37056,10 @@
         <v>0.01181723733953126</v>
       </c>
       <c r="H713">
-        <v>0.01146408288954808</v>
+        <v>0.01148299562955032</v>
       </c>
       <c r="I713">
-        <v>0.1131544499831785</v>
+        <v>0.1942417099809362</v>
       </c>
       <c r="J713">
         <v>1.554362999887862</v>
@@ -37071,10 +37071,10 @@
         <v>5.32</v>
       </c>
       <c r="M713">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="N713">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="O713">
         <v>1</v>
@@ -37147,7 +37147,7 @@
         <v>251</v>
       </c>
       <c r="E715">
-        <v>-1.103231291701239</v>
+        <v>-1.021949746829272</v>
       </c>
       <c r="F715">
         <v>1</v>
@@ -37156,10 +37156,10 @@
         <v>0.01185784287824099</v>
       </c>
       <c r="H715">
-        <v>0.01150323129170124</v>
+        <v>0.01152194974682927</v>
       </c>
       <c r="I715">
-        <v>0.1146115865397475</v>
+        <v>0.1958931314117143</v>
       </c>
       <c r="J715">
         <v>1.564077243598322</v>
@@ -37171,10 +37171,10 @@
         <v>5.32</v>
       </c>
       <c r="M715">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="N715">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="O715">
         <v>1</v>
@@ -37197,7 +37197,7 @@
         <v>251</v>
       </c>
       <c r="E716">
-        <v>-1.149128838391547</v>
+        <v>-1.067619514131539</v>
       </c>
       <c r="F716">
         <v>1</v>
@@ -37206,10 +37206,10 @@
         <v>0.0119054487703416</v>
       </c>
       <c r="H716">
-        <v>0.01154912883839155</v>
+        <v>0.01156761951413154</v>
       </c>
       <c r="I716">
-        <v>0.1163199319500574</v>
+        <v>0.1978292562100652</v>
       </c>
       <c r="J716">
         <v>1.575466213000384</v>
@@ -37221,10 +37221,10 @@
         <v>5.32</v>
       </c>
       <c r="M716">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="N716">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="O716">
         <v>1</v>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="354">
   <si>
     <t>trade_time</t>
   </si>
@@ -457,7 +457,7 @@
     <t>2021-11-10</t>
   </si>
   <si>
-    <t>2021-11-12</t>
+    <t>2021-11-22</t>
   </si>
   <si>
     <t>2017-04-20</t>
@@ -769,10 +769,7 @@
     <t>2021-11-11</t>
   </si>
   <si>
-    <t>2021-11-17</t>
-  </si>
-  <si>
-    <t>2021-11-15</t>
+    <t>2021-11-23</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -1076,6 +1073,9 @@
   </si>
   <si>
     <t>2021-11-09</t>
+  </si>
+  <si>
+    <t>2021-11-12</t>
   </si>
 </sst>
 </file>
@@ -1433,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P717"/>
+  <dimension ref="A1:P716"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1530,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1580,7 +1580,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1630,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1680,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1730,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1780,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1830,7 +1830,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1930,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1980,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2030,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2080,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2130,7 +2130,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2180,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2230,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2280,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2330,7 +2330,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2380,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2430,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2480,7 +2480,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2530,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2580,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2630,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2680,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2730,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2780,7 +2780,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2830,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2880,7 +2880,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2930,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2980,7 +2980,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3030,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3080,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3130,7 +3130,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3180,7 +3180,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3230,7 +3230,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3280,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3330,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3380,7 +3380,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3430,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3480,7 +3480,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3530,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3580,7 +3580,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3630,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3680,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3730,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4780,7 +4780,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4830,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4880,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4930,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4980,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5030,7 +5030,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5080,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5130,7 +5130,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5180,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5230,7 +5230,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5280,7 +5280,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5330,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5380,7 +5380,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5430,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5480,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5530,7 +5530,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5580,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5630,7 +5630,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5680,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5730,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5780,7 +5780,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5830,7 +5830,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5880,7 +5880,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5930,7 +5930,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5980,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6030,7 +6030,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6330,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6380,7 +6380,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6430,7 +6430,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6480,7 +6480,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6530,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6580,7 +6580,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6630,7 +6630,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6680,7 +6680,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6730,7 +6730,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6780,7 +6780,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6830,7 +6830,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6880,7 +6880,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6930,7 +6930,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7280,7 +7280,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7330,7 +7330,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7380,7 +7380,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7430,7 +7430,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7480,7 +7480,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7530,7 +7530,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7580,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7630,7 +7630,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7680,7 +7680,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7730,7 +7730,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7780,7 +7780,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7830,7 +7830,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7880,7 +7880,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8730,7 +8730,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8780,7 +8780,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8830,7 +8830,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8880,7 +8880,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8930,7 +8930,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8980,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9130,7 +9130,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9180,7 +9180,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9230,7 +9230,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9280,7 +9280,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9330,7 +9330,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9380,7 +9380,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9430,7 +9430,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9480,7 +9480,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9530,7 +9530,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9580,7 +9580,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9630,7 +9630,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9680,7 +9680,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10030,7 +10030,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10080,7 +10080,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10230,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10280,7 +10280,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10330,7 +10330,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10380,7 +10380,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10430,7 +10430,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10480,7 +10480,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10530,7 +10530,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10580,7 +10580,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10630,7 +10630,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10680,7 +10680,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10730,7 +10730,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10780,7 +10780,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10830,7 +10830,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10880,7 +10880,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10930,7 +10930,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10980,7 +10980,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11030,7 +11030,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11080,7 +11080,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11130,7 +11130,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11180,7 +11180,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11230,7 +11230,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11280,7 +11280,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11330,7 +11330,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11380,7 +11380,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11430,7 +11430,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11480,7 +11480,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11530,7 +11530,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11580,7 +11580,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11630,7 +11630,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11680,7 +11680,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11730,7 +11730,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11780,7 +11780,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11830,7 +11830,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11880,7 +11880,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11930,7 +11930,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11980,7 +11980,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12030,7 +12030,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12080,7 +12080,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12130,7 +12130,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12180,7 +12180,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12230,7 +12230,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12280,7 +12280,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12330,7 +12330,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12380,7 +12380,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12430,7 +12430,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12480,7 +12480,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12530,7 +12530,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12580,7 +12580,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12880,7 +12880,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12930,7 +12930,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12980,7 +12980,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13030,7 +13030,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13080,7 +13080,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13130,7 +13130,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13180,7 +13180,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13530,7 +13530,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13580,7 +13580,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13630,7 +13630,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13680,7 +13680,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13730,7 +13730,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13780,7 +13780,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13830,7 +13830,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13880,7 +13880,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13930,7 +13930,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13980,7 +13980,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14030,7 +14030,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14080,7 +14080,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14130,7 +14130,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14180,7 +14180,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14230,7 +14230,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14280,7 +14280,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14330,7 +14330,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14380,7 +14380,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14680,7 +14680,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14730,7 +14730,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14780,7 +14780,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14830,7 +14830,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14880,7 +14880,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14930,7 +14930,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14980,7 +14980,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15030,7 +15030,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15080,7 +15080,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15130,7 +15130,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15180,7 +15180,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15230,7 +15230,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15280,7 +15280,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15330,7 +15330,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15380,7 +15380,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15430,7 +15430,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15480,7 +15480,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15530,7 +15530,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15580,7 +15580,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15630,7 +15630,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15680,7 +15680,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15730,7 +15730,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15780,7 +15780,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15830,7 +15830,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15880,7 +15880,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15930,7 +15930,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15980,7 +15980,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16030,7 +16030,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16080,7 +16080,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16130,7 +16130,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16180,7 +16180,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16230,7 +16230,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16280,7 +16280,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16330,7 +16330,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16380,7 +16380,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16430,7 +16430,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16480,7 +16480,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16530,7 +16530,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16580,7 +16580,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16630,7 +16630,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16680,7 +16680,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16730,7 +16730,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16780,7 +16780,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16830,7 +16830,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16880,7 +16880,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16930,7 +16930,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -16980,7 +16980,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17030,7 +17030,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17080,7 +17080,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17130,7 +17130,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17180,7 +17180,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17230,7 +17230,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17280,7 +17280,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17380,7 +17380,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17430,7 +17430,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17480,7 +17480,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17530,7 +17530,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17580,7 +17580,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17630,7 +17630,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17680,7 +17680,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17730,7 +17730,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17780,7 +17780,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17830,7 +17830,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17880,7 +17880,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17930,7 +17930,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17980,7 +17980,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18030,7 +18030,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18080,7 +18080,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18130,7 +18130,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18180,7 +18180,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18230,7 +18230,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18280,7 +18280,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18330,7 +18330,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18380,7 +18380,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18430,7 +18430,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18480,7 +18480,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18530,7 +18530,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18730,7 +18730,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18780,7 +18780,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18830,7 +18830,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18880,7 +18880,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18930,7 +18930,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18980,7 +18980,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19230,7 +19230,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19280,7 +19280,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19330,7 +19330,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19380,7 +19380,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19630,7 +19630,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19680,7 +19680,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19730,7 +19730,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19780,7 +19780,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19830,7 +19830,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19880,7 +19880,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19930,7 +19930,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19980,7 +19980,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20030,7 +20030,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20080,7 +20080,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20130,7 +20130,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20180,7 +20180,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20230,7 +20230,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20280,7 +20280,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20730,7 +20730,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20780,7 +20780,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20830,7 +20830,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20880,7 +20880,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20930,7 +20930,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20980,7 +20980,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21030,7 +21030,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21080,7 +21080,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21130,7 +21130,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21180,7 +21180,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21230,7 +21230,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21280,7 +21280,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21330,7 +21330,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21380,7 +21380,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21430,7 +21430,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21480,7 +21480,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21530,7 +21530,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21580,7 +21580,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21630,7 +21630,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21680,7 +21680,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21730,7 +21730,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22080,7 +22080,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22130,7 +22130,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22180,7 +22180,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22230,7 +22230,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22280,7 +22280,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22330,7 +22330,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22380,7 +22380,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22430,7 +22430,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22480,7 +22480,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22530,7 +22530,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22580,7 +22580,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22630,7 +22630,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23430,7 +23430,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23480,7 +23480,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23530,7 +23530,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23580,7 +23580,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23630,7 +23630,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23680,7 +23680,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23730,7 +23730,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23780,7 +23780,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23830,7 +23830,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23880,7 +23880,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23930,7 +23930,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23980,7 +23980,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24030,7 +24030,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24080,7 +24080,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24130,7 +24130,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24180,7 +24180,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24230,7 +24230,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24280,7 +24280,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24330,7 +24330,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24380,7 +24380,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24430,7 +24430,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24480,7 +24480,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24530,7 +24530,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24580,7 +24580,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24630,7 +24630,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24680,7 +24680,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24730,7 +24730,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24780,7 +24780,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24830,7 +24830,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24880,7 +24880,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24930,7 +24930,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24980,7 +24980,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25030,7 +25030,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25180,7 +25180,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25230,7 +25230,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25280,7 +25280,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25330,7 +25330,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25380,7 +25380,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25430,7 +25430,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25480,7 +25480,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25530,7 +25530,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25580,7 +25580,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25630,7 +25630,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25680,7 +25680,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25880,7 +25880,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25930,7 +25930,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25980,7 +25980,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26030,7 +26030,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26080,7 +26080,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26130,7 +26130,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26180,7 +26180,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26230,7 +26230,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26280,7 +26280,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26330,7 +26330,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26380,7 +26380,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26430,7 +26430,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26480,7 +26480,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26530,7 +26530,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26580,7 +26580,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26630,7 +26630,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26680,7 +26680,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26730,7 +26730,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26780,7 +26780,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26830,7 +26830,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26880,7 +26880,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26930,7 +26930,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26980,7 +26980,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27030,7 +27030,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27080,7 +27080,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27130,7 +27130,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27180,7 +27180,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27230,7 +27230,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27580,7 +27580,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27630,7 +27630,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27680,7 +27680,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27730,7 +27730,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27780,7 +27780,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27830,7 +27830,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28130,7 +28130,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28180,7 +28180,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28230,7 +28230,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28280,7 +28280,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28330,7 +28330,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28380,7 +28380,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28430,7 +28430,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28480,7 +28480,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28530,7 +28530,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28580,7 +28580,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28630,7 +28630,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28680,7 +28680,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28730,7 +28730,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28780,7 +28780,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28830,7 +28830,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28880,7 +28880,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28930,7 +28930,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28980,7 +28980,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29030,7 +29030,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29080,7 +29080,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29130,7 +29130,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29180,7 +29180,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29230,7 +29230,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29280,7 +29280,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29330,7 +29330,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29380,7 +29380,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29430,7 +29430,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29480,7 +29480,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29530,7 +29530,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29580,7 +29580,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29630,7 +29630,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29680,7 +29680,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29730,7 +29730,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29780,7 +29780,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -29830,7 +29830,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -29880,7 +29880,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -29930,7 +29930,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29980,7 +29980,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30030,7 +30030,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30080,7 +30080,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30130,7 +30130,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30180,7 +30180,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30230,7 +30230,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30280,7 +30280,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30330,7 +30330,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30380,7 +30380,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30430,7 +30430,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30480,7 +30480,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30530,7 +30530,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30580,7 +30580,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30630,7 +30630,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30680,7 +30680,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30730,7 +30730,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30780,7 +30780,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -32330,7 +32330,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32380,7 +32380,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32430,7 +32430,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32480,7 +32480,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32530,7 +32530,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32580,7 +32580,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32630,7 +32630,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32680,7 +32680,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32730,7 +32730,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32780,7 +32780,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32830,7 +32830,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32880,7 +32880,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32930,7 +32930,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32980,7 +32980,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33030,7 +33030,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33080,7 +33080,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33130,7 +33130,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33180,7 +33180,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33230,7 +33230,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33280,7 +33280,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33330,7 +33330,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33380,7 +33380,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33430,7 +33430,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33480,7 +33480,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33530,7 +33530,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33580,7 +33580,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33630,7 +33630,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33680,7 +33680,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33730,7 +33730,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34430,7 +34430,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34480,7 +34480,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34530,7 +34530,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34580,7 +34580,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34630,7 +34630,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34680,7 +34680,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34730,7 +34730,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -34780,7 +34780,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -34830,7 +34830,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -34880,7 +34880,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -34930,7 +34930,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -34980,7 +34980,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35030,7 +35030,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35630,7 +35630,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35680,7 +35680,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35730,7 +35730,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35780,7 +35780,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -35830,7 +35830,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -35880,7 +35880,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -35930,7 +35930,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -35980,7 +35980,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36030,7 +36030,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36080,7 +36080,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36130,7 +36130,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36380,7 +36380,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36430,7 +36430,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36441,46 +36441,46 @@
         <v>147</v>
       </c>
       <c r="C701">
-        <v>-0.9465604993627688</v>
+        <v>-0.6617168403008256</v>
       </c>
       <c r="D701" t="s">
         <v>251</v>
       </c>
       <c r="E701">
-        <v>-0.7617003833599769</v>
+        <v>-0.6617168403008256</v>
       </c>
       <c r="F701">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G701">
-        <v>0.01158656049936277</v>
+        <v>0.01130171684030083</v>
       </c>
       <c r="H701">
-        <v>0.01126170038335998</v>
+        <v>0.01130171684030083</v>
       </c>
       <c r="I701">
-        <v>0.1848601160027918</v>
+        <v>-0</v>
       </c>
       <c r="J701">
         <v>1.4991771529576</v>
       </c>
       <c r="K701">
-        <v>4.18</v>
+        <v>3.99</v>
       </c>
       <c r="L701">
         <v>5.32</v>
       </c>
       <c r="M701">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="N701">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="O701">
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36530,7 +36530,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36580,7 +36580,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36588,81 +36588,81 @@
         <v>0</v>
       </c>
       <c r="B704" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C704">
-        <v>-0.7365419644915843</v>
+        <v>-0.6555683652294215</v>
       </c>
       <c r="D704" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E704">
-        <v>-0.9016808854046587</v>
+        <v>-0.9337635462301144</v>
       </c>
       <c r="F704">
         <v>-1</v>
       </c>
       <c r="G704">
-        <v>0.01267654196449158</v>
+        <v>0.01145556836522942</v>
       </c>
       <c r="H704">
-        <v>0.01254168088540466</v>
+        <v>0.01187376354623011</v>
       </c>
       <c r="I704">
-        <v>0.1651389209130745</v>
+        <v>0.2781951810006928</v>
       </c>
       <c r="J704">
         <v>1.513892091307355</v>
       </c>
       <c r="K704">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="L704">
-        <v>5.97</v>
+        <v>5.4</v>
       </c>
       <c r="M704">
-        <v>4.44</v>
+        <v>4.23</v>
       </c>
       <c r="N704">
-        <v>5.82</v>
+        <v>5.47</v>
       </c>
       <c r="O704">
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="705" spans="1:16">
       <c r="A705" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B705" t="s">
         <v>146</v>
       </c>
       <c r="C705">
-        <v>-0.6555683652294215</v>
+        <v>-0.6880495404143332</v>
       </c>
       <c r="D705" t="s">
         <v>250</v>
       </c>
       <c r="E705">
-        <v>-0.9337635462301144</v>
+        <v>-0.9681123889881587</v>
       </c>
       <c r="F705">
         <v>-1</v>
       </c>
       <c r="G705">
-        <v>0.01145556836522942</v>
+        <v>0.01148804954041433</v>
       </c>
       <c r="H705">
-        <v>0.01187376354623011</v>
+        <v>0.01190811238898816</v>
       </c>
       <c r="I705">
-        <v>0.2781951810006928</v>
+        <v>0.2800628485738255</v>
       </c>
       <c r="J705">
-        <v>1.513892091307355</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K705">
         <v>4</v>
@@ -36691,28 +36691,28 @@
         <v>146</v>
       </c>
       <c r="C706">
-        <v>-0.6880495404143332</v>
+        <v>-0.7190734844162181</v>
       </c>
       <c r="D706" t="s">
         <v>250</v>
       </c>
       <c r="E706">
-        <v>-0.9681123889881587</v>
+        <v>-1.000920209770152</v>
       </c>
       <c r="F706">
         <v>-1</v>
       </c>
       <c r="G706">
-        <v>0.01148804954041433</v>
+        <v>0.01151907348441622</v>
       </c>
       <c r="H706">
-        <v>0.01190811238898816</v>
+        <v>0.01194092020977015</v>
       </c>
       <c r="I706">
-        <v>0.2800628485738255</v>
+        <v>0.2818467253539341</v>
       </c>
       <c r="J706">
-        <v>1.522012385103583</v>
+        <v>1.529768371104055</v>
       </c>
       <c r="K706">
         <v>4</v>
@@ -36730,7 +36730,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>350</v>
+        <v>145</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36741,28 +36741,28 @@
         <v>146</v>
       </c>
       <c r="C707">
-        <v>-0.7190734844162181</v>
+        <v>-0.7458787100492641</v>
       </c>
       <c r="D707" t="s">
         <v>250</v>
       </c>
       <c r="E707">
-        <v>-1.000920209770152</v>
+        <v>-1.029266735877098</v>
       </c>
       <c r="F707">
         <v>-1</v>
       </c>
       <c r="G707">
-        <v>0.01151907348441622</v>
+        <v>0.01154587871004927</v>
       </c>
       <c r="H707">
-        <v>0.01194092020977015</v>
+        <v>0.0119692667358771</v>
       </c>
       <c r="I707">
-        <v>0.2818467253539341</v>
+        <v>0.2833880258278336</v>
       </c>
       <c r="J707">
-        <v>1.529768371104055</v>
+        <v>1.536469677512316</v>
       </c>
       <c r="K707">
         <v>4</v>
@@ -36780,51 +36780,51 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>145</v>
+        <v>249</v>
       </c>
     </row>
     <row r="708" spans="1:16">
       <c r="A708" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B708" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C708">
-        <v>-0.7458787100492641</v>
+        <v>-0.8105140132741413</v>
       </c>
       <c r="D708" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E708">
-        <v>-1.029266735877098</v>
+        <v>-0.8105140132741413</v>
       </c>
       <c r="F708">
         <v>-1</v>
       </c>
       <c r="G708">
-        <v>0.01154587871004927</v>
+        <v>0.01145051401327414</v>
       </c>
       <c r="H708">
-        <v>0.0119692667358771</v>
+        <v>0.01145051401327414</v>
       </c>
       <c r="I708">
-        <v>0.2833880258278336</v>
+        <v>-0</v>
       </c>
       <c r="J708">
         <v>1.536469677512316</v>
       </c>
       <c r="K708">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="L708">
-        <v>5.4</v>
+        <v>5.32</v>
       </c>
       <c r="M708">
-        <v>4.23</v>
+        <v>3.99</v>
       </c>
       <c r="N708">
-        <v>5.47</v>
+        <v>5.32</v>
       </c>
       <c r="O708">
         <v>1</v>
@@ -36835,52 +36835,52 @@
     </row>
     <row r="709" spans="1:16">
       <c r="A709" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B709" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C709">
-        <v>-1.10244325200148</v>
+        <v>-0.7844366033779329</v>
       </c>
       <c r="D709" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E709">
-        <v>-0.9112434068243873</v>
+        <v>-1.070041708072165</v>
       </c>
       <c r="F709">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G709">
-        <v>0.01174244325200148</v>
+        <v>0.01158443660337793</v>
       </c>
       <c r="H709">
-        <v>0.01141124340682439</v>
+        <v>0.01201004170807217</v>
       </c>
       <c r="I709">
-        <v>0.1911998451770929</v>
+        <v>0.2856051046942323</v>
       </c>
       <c r="J709">
-        <v>1.536469677512316</v>
+        <v>1.546109150844483</v>
       </c>
       <c r="K709">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="L709">
-        <v>5.32</v>
+        <v>5.4</v>
       </c>
       <c r="M709">
-        <v>4.01</v>
+        <v>4.23</v>
       </c>
       <c r="N709">
-        <v>5.25</v>
+        <v>5.47</v>
       </c>
       <c r="O709">
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>249</v>
+        <v>350</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36891,28 +36891,28 @@
         <v>146</v>
       </c>
       <c r="C710">
-        <v>-0.7844366033779329</v>
+        <v>-0.8174519995514462</v>
       </c>
       <c r="D710" t="s">
         <v>250</v>
       </c>
       <c r="E710">
-        <v>-1.070041708072165</v>
+        <v>-1.104955489525656</v>
       </c>
       <c r="F710">
         <v>-1</v>
       </c>
       <c r="G710">
-        <v>0.01158443660337793</v>
+        <v>0.01161745199955145</v>
       </c>
       <c r="H710">
-        <v>0.01201004170807217</v>
+        <v>0.01204495548952566</v>
       </c>
       <c r="I710">
-        <v>0.2856051046942323</v>
+        <v>0.2875034899742097</v>
       </c>
       <c r="J710">
-        <v>1.546109150844483</v>
+        <v>1.554362999887862</v>
       </c>
       <c r="K710">
         <v>4</v>
@@ -36941,40 +36941,40 @@
         <v>147</v>
       </c>
       <c r="C711">
-        <v>-1.142736250529939</v>
+        <v>-0.8819083695525682</v>
       </c>
       <c r="D711" t="s">
         <v>251</v>
       </c>
       <c r="E711">
-        <v>-0.9498976948863778</v>
+        <v>-0.8819083695525682</v>
       </c>
       <c r="F711">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G711">
-        <v>0.01178273625052994</v>
+        <v>0.01152190836955257</v>
       </c>
       <c r="H711">
-        <v>0.01144989769488638</v>
+        <v>0.01152190836955257</v>
       </c>
       <c r="I711">
-        <v>0.1928385556435614</v>
+        <v>-0</v>
       </c>
       <c r="J711">
-        <v>1.546109150844483</v>
+        <v>1.554362999887862</v>
       </c>
       <c r="K711">
-        <v>4.18</v>
+        <v>3.99</v>
       </c>
       <c r="L711">
         <v>5.32</v>
       </c>
       <c r="M711">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="N711">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="O711">
         <v>1</v>
@@ -36991,28 +36991,28 @@
         <v>146</v>
       </c>
       <c r="C712">
-        <v>-0.8174519995514462</v>
+        <v>-0.856308974393289</v>
       </c>
       <c r="D712" t="s">
         <v>250</v>
       </c>
       <c r="E712">
-        <v>-1.104955489525656</v>
+        <v>-1.146046740420904</v>
       </c>
       <c r="F712">
         <v>-1</v>
       </c>
       <c r="G712">
-        <v>0.01161745199955145</v>
+        <v>0.01165630897439329</v>
       </c>
       <c r="H712">
-        <v>0.01204495548952566</v>
+        <v>0.0120860467404209</v>
       </c>
       <c r="I712">
-        <v>0.2875034899742097</v>
+        <v>0.2897377660276153</v>
       </c>
       <c r="J712">
-        <v>1.554362999887862</v>
+        <v>1.564077243598322</v>
       </c>
       <c r="K712">
         <v>4</v>
@@ -37041,40 +37041,40 @@
         <v>147</v>
       </c>
       <c r="C713">
-        <v>-1.177237339531261</v>
+        <v>-0.920668201957306</v>
       </c>
       <c r="D713" t="s">
         <v>251</v>
       </c>
       <c r="E713">
-        <v>-0.9829956295503246</v>
+        <v>-0.920668201957306</v>
       </c>
       <c r="F713">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G713">
-        <v>0.01181723733953126</v>
+        <v>0.01156066820195731</v>
       </c>
       <c r="H713">
-        <v>0.01148299562955032</v>
+        <v>0.01156066820195731</v>
       </c>
       <c r="I713">
-        <v>0.1942417099809362</v>
+        <v>-0</v>
       </c>
       <c r="J713">
-        <v>1.554362999887862</v>
+        <v>1.564077243598322</v>
       </c>
       <c r="K713">
-        <v>4.18</v>
+        <v>3.99</v>
       </c>
       <c r="L713">
         <v>5.32</v>
       </c>
       <c r="M713">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="N713">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="O713">
         <v>1</v>
@@ -37088,99 +37088,99 @@
         <v>0</v>
       </c>
       <c r="B714" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C714">
-        <v>-0.856308974393289</v>
+        <v>-0.9661101898715314</v>
       </c>
       <c r="D714" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E714">
-        <v>-1.146046740420904</v>
+        <v>-0.9661101898715314</v>
       </c>
       <c r="F714">
         <v>-1</v>
       </c>
       <c r="G714">
-        <v>0.01165630897439329</v>
+        <v>0.01160611018987153</v>
       </c>
       <c r="H714">
-        <v>0.0120860467404209</v>
+        <v>0.01160611018987153</v>
       </c>
       <c r="I714">
-        <v>0.2897377660276153</v>
+        <v>-0</v>
       </c>
       <c r="J714">
-        <v>1.564077243598322</v>
+        <v>1.575466213000384</v>
       </c>
       <c r="K714">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="L714">
-        <v>5.4</v>
+        <v>5.32</v>
       </c>
       <c r="M714">
-        <v>4.23</v>
+        <v>3.99</v>
       </c>
       <c r="N714">
-        <v>5.47</v>
+        <v>5.32</v>
       </c>
       <c r="O714">
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>353</v>
+        <v>146</v>
       </c>
     </row>
     <row r="715" spans="1:16">
       <c r="A715" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B715" t="s">
         <v>147</v>
       </c>
       <c r="C715">
-        <v>-1.217842878240987</v>
+        <v>-1.011027493212815</v>
       </c>
       <c r="D715" t="s">
         <v>251</v>
       </c>
       <c r="E715">
-        <v>-1.021949746829272</v>
+        <v>-1.011027493212815</v>
       </c>
       <c r="F715">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G715">
-        <v>0.01185784287824099</v>
+        <v>0.01165102749321282</v>
       </c>
       <c r="H715">
-        <v>0.01152194974682927</v>
+        <v>0.01165102749321282</v>
       </c>
       <c r="I715">
-        <v>0.1958931314117143</v>
+        <v>-0</v>
       </c>
       <c r="J715">
-        <v>1.564077243598322</v>
+        <v>1.586723682509477</v>
       </c>
       <c r="K715">
-        <v>4.18</v>
+        <v>3.99</v>
       </c>
       <c r="L715">
         <v>5.32</v>
       </c>
       <c r="M715">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="N715">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="O715">
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>353</v>
+        <v>250</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37191,96 +37191,46 @@
         <v>147</v>
       </c>
       <c r="C716">
-        <v>-1.265448770341604</v>
+        <v>-1.068447687938677</v>
       </c>
       <c r="D716" t="s">
         <v>251</v>
       </c>
       <c r="E716">
-        <v>-1.067619514131539</v>
+        <v>-1.068447687938677</v>
       </c>
       <c r="F716">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G716">
-        <v>0.0119054487703416</v>
+        <v>0.01170844768793868</v>
       </c>
       <c r="H716">
-        <v>0.01156761951413154</v>
+        <v>0.01170844768793868</v>
       </c>
       <c r="I716">
-        <v>0.1978292562100652</v>
+        <v>-0</v>
       </c>
       <c r="J716">
-        <v>1.575466213000384</v>
+        <v>1.60111470875656</v>
       </c>
       <c r="K716">
-        <v>4.18</v>
+        <v>3.99</v>
       </c>
       <c r="L716">
         <v>5.32</v>
       </c>
       <c r="M716">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="N716">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="O716">
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="717" spans="1:16">
-      <c r="A717" s="1">
-        <v>0</v>
-      </c>
-      <c r="B717" t="s">
-        <v>147</v>
-      </c>
-      <c r="C717">
-        <v>-1.312504992889616</v>
-      </c>
-      <c r="D717" t="s">
-        <v>252</v>
-      </c>
-      <c r="E717">
-        <v>-1.185567098288857</v>
-      </c>
-      <c r="F717">
-        <v>1</v>
-      </c>
-      <c r="G717">
-        <v>0.01195250499288962</v>
-      </c>
-      <c r="H717">
-        <v>0.01182556709828886</v>
-      </c>
-      <c r="I717">
-        <v>0.1269378946007587</v>
-      </c>
-      <c r="J717">
-        <v>1.586723682509477</v>
-      </c>
-      <c r="K717">
-        <v>4.18</v>
-      </c>
-      <c r="L717">
-        <v>5.32</v>
-      </c>
-      <c r="M717">
-        <v>4.1</v>
-      </c>
-      <c r="N717">
-        <v>5.32</v>
-      </c>
-      <c r="O717">
-        <v>1</v>
-      </c>
-      <c r="P717" t="s">
-        <v>250</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="348">
   <si>
     <t>trade_time</t>
   </si>
@@ -451,13 +451,13 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-11-03</t>
-  </si>
-  <si>
     <t>2021-11-10</t>
   </si>
   <si>
     <t>2021-11-22</t>
+  </si>
+  <si>
+    <t>2021-11-18</t>
   </si>
   <si>
     <t>2017-04-20</t>
@@ -763,13 +763,10 @@
     <t>2021-08-09</t>
   </si>
   <si>
-    <t>2021-11-04</t>
-  </si>
-  <si>
     <t>2021-11-11</t>
   </si>
   <si>
-    <t>2021-11-23</t>
+    <t>2021-11-24</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -1060,22 +1057,7 @@
     <t>2021-10-29</t>
   </si>
   <si>
-    <t>2021-11-01</t>
-  </si>
-  <si>
-    <t>2021-11-02</t>
-  </si>
-  <si>
-    <t>2021-11-05</t>
-  </si>
-  <si>
-    <t>2021-11-08</t>
-  </si>
-  <si>
-    <t>2021-11-09</t>
-  </si>
-  <si>
-    <t>2021-11-12</t>
+    <t>2021-11-17</t>
   </si>
 </sst>
 </file>
@@ -1433,7 +1415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P716"/>
+  <dimension ref="A1:P702"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1530,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1580,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1630,7 +1612,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1680,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1730,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1780,7 +1762,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1830,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1880,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1930,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1980,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2030,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2080,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2130,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2180,7 +2162,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2230,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2280,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2330,7 +2312,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2380,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2430,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2480,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2530,7 +2512,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2580,7 +2562,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2630,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2680,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2730,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2780,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2830,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2880,7 +2862,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2930,7 +2912,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2980,7 +2962,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3030,7 +3012,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3080,7 +3062,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3130,7 +3112,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3180,7 +3162,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3230,7 +3212,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3280,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3330,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3380,7 +3362,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3430,7 +3412,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3480,7 +3462,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3530,7 +3512,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3580,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3630,7 +3612,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3680,7 +3662,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3730,7 +3712,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4780,7 +4762,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4830,7 +4812,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4880,7 +4862,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4930,7 +4912,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4980,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5030,7 +5012,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5080,7 +5062,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5130,7 +5112,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5180,7 +5162,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5230,7 +5212,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5280,7 +5262,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5330,7 +5312,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5380,7 +5362,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5430,7 +5412,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5480,7 +5462,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5530,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5580,7 +5562,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5630,7 +5612,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5680,7 +5662,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5730,7 +5712,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5780,7 +5762,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5830,7 +5812,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5880,7 +5862,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5930,7 +5912,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5980,7 +5962,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6030,7 +6012,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6330,7 +6312,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6380,7 +6362,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6430,7 +6412,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6480,7 +6462,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6530,7 +6512,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6580,7 +6562,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6630,7 +6612,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6680,7 +6662,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6730,7 +6712,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6780,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6830,7 +6812,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6880,7 +6862,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6930,7 +6912,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7280,7 +7262,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7330,7 +7312,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7380,7 +7362,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7430,7 +7412,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7480,7 +7462,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7530,7 +7512,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7580,7 +7562,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7630,7 +7612,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7680,7 +7662,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7730,7 +7712,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7780,7 +7762,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7830,7 +7812,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7880,7 +7862,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8730,7 +8712,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8780,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8830,7 +8812,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8880,7 +8862,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8930,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8980,7 +8962,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9130,7 +9112,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9180,7 +9162,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9230,7 +9212,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9280,7 +9262,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9330,7 +9312,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9380,7 +9362,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9430,7 +9412,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9480,7 +9462,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9530,7 +9512,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9580,7 +9562,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9630,7 +9612,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9680,7 +9662,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10030,7 +10012,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10080,7 +10062,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10230,7 +10212,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10280,7 +10262,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10330,7 +10312,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10380,7 +10362,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10430,7 +10412,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10480,7 +10462,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10530,7 +10512,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10580,7 +10562,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10630,7 +10612,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10680,7 +10662,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10730,7 +10712,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10780,7 +10762,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10830,7 +10812,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10880,7 +10862,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10930,7 +10912,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10980,7 +10962,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11030,7 +11012,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11080,7 +11062,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11130,7 +11112,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11180,7 +11162,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11230,7 +11212,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11280,7 +11262,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11330,7 +11312,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11380,7 +11362,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11430,7 +11412,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11480,7 +11462,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11530,7 +11512,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11580,7 +11562,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11630,7 +11612,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11680,7 +11662,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11730,7 +11712,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11780,7 +11762,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11830,7 +11812,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11880,7 +11862,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11930,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11980,7 +11962,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12030,7 +12012,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12080,7 +12062,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12130,7 +12112,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12180,7 +12162,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12230,7 +12212,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12280,7 +12262,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12330,7 +12312,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12380,7 +12362,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12430,7 +12412,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12480,7 +12462,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12530,7 +12512,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12580,7 +12562,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12880,7 +12862,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12930,7 +12912,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12980,7 +12962,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13030,7 +13012,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13080,7 +13062,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13130,7 +13112,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13180,7 +13162,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13530,7 +13512,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13580,7 +13562,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13630,7 +13612,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13680,7 +13662,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13730,7 +13712,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13780,7 +13762,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13830,7 +13812,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13880,7 +13862,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13930,7 +13912,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13980,7 +13962,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14030,7 +14012,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14080,7 +14062,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14130,7 +14112,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14180,7 +14162,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14230,7 +14212,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14280,7 +14262,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14330,7 +14312,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14380,7 +14362,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14680,7 +14662,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14730,7 +14712,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14780,7 +14762,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14830,7 +14812,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14880,7 +14862,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14930,7 +14912,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14980,7 +14962,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15030,7 +15012,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15080,7 +15062,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15130,7 +15112,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15180,7 +15162,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15230,7 +15212,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15280,7 +15262,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15330,7 +15312,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15380,7 +15362,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15430,7 +15412,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15480,7 +15462,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15530,7 +15512,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15580,7 +15562,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15630,7 +15612,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15680,7 +15662,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15730,7 +15712,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15780,7 +15762,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15830,7 +15812,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15880,7 +15862,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15930,7 +15912,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -15980,7 +15962,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16030,7 +16012,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16080,7 +16062,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16130,7 +16112,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16180,7 +16162,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16230,7 +16212,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16280,7 +16262,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16330,7 +16312,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16380,7 +16362,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16430,7 +16412,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16480,7 +16462,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16530,7 +16512,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16580,7 +16562,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16630,7 +16612,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16680,7 +16662,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16730,7 +16712,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16780,7 +16762,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16830,7 +16812,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16880,7 +16862,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16930,7 +16912,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -16980,7 +16962,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17030,7 +17012,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17080,7 +17062,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17130,7 +17112,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17180,7 +17162,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17230,7 +17212,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17280,7 +17262,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17330,7 +17312,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17380,7 +17362,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17430,7 +17412,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17480,7 +17462,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17530,7 +17512,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17580,7 +17562,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17630,7 +17612,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17680,7 +17662,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17730,7 +17712,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17780,7 +17762,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17830,7 +17812,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17880,7 +17862,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17930,7 +17912,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -17980,7 +17962,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18030,7 +18012,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18080,7 +18062,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18130,7 +18112,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18180,7 +18162,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18230,7 +18212,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18280,7 +18262,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18330,7 +18312,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18380,7 +18362,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18430,7 +18412,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18480,7 +18462,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18530,7 +18512,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18730,7 +18712,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18780,7 +18762,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18830,7 +18812,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18880,7 +18862,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18930,7 +18912,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -18980,7 +18962,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19230,7 +19212,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19280,7 +19262,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19330,7 +19312,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19380,7 +19362,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19630,7 +19612,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19680,7 +19662,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19730,7 +19712,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19780,7 +19762,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19830,7 +19812,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19880,7 +19862,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19930,7 +19912,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -19980,7 +19962,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20030,7 +20012,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20080,7 +20062,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20130,7 +20112,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20180,7 +20162,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20230,7 +20212,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20280,7 +20262,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20730,7 +20712,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20780,7 +20762,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20830,7 +20812,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20880,7 +20862,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20930,7 +20912,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -20980,7 +20962,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21030,7 +21012,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21080,7 +21062,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21130,7 +21112,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21180,7 +21162,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21230,7 +21212,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21280,7 +21262,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21330,7 +21312,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21380,7 +21362,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21430,7 +21412,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21480,7 +21462,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21530,7 +21512,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21580,7 +21562,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21630,7 +21612,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21680,7 +21662,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21730,7 +21712,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22080,7 +22062,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22130,7 +22112,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22180,7 +22162,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22230,7 +22212,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22280,7 +22262,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22330,7 +22312,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22380,7 +22362,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22430,7 +22412,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22480,7 +22462,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22530,7 +22512,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22580,7 +22562,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22630,7 +22612,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23430,7 +23412,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23480,7 +23462,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23530,7 +23512,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23580,7 +23562,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23630,7 +23612,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23680,7 +23662,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23730,7 +23712,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23780,7 +23762,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23830,7 +23812,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23880,7 +23862,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23930,7 +23912,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -23980,7 +23962,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24030,7 +24012,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24080,7 +24062,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24130,7 +24112,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24180,7 +24162,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24230,7 +24212,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24280,7 +24262,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24330,7 +24312,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24380,7 +24362,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24430,7 +24412,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24480,7 +24462,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24530,7 +24512,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24580,7 +24562,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24630,7 +24612,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24680,7 +24662,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24730,7 +24712,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24780,7 +24762,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24830,7 +24812,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24880,7 +24862,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24930,7 +24912,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -24980,7 +24962,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25030,7 +25012,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25180,7 +25162,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25230,7 +25212,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25280,7 +25262,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25330,7 +25312,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25380,7 +25362,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25430,7 +25412,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25480,7 +25462,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25530,7 +25512,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25580,7 +25562,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25630,7 +25612,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25680,7 +25662,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25880,7 +25862,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25930,7 +25912,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -25980,7 +25962,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26030,7 +26012,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26080,7 +26062,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26130,7 +26112,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26180,7 +26162,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26230,7 +26212,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26280,7 +26262,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26330,7 +26312,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26380,7 +26362,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26430,7 +26412,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26480,7 +26462,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26530,7 +26512,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26580,7 +26562,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26630,7 +26612,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26680,7 +26662,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26730,7 +26712,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26780,7 +26762,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26830,7 +26812,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26880,7 +26862,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26930,7 +26912,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -26980,7 +26962,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27030,7 +27012,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27080,7 +27062,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27130,7 +27112,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27180,7 +27162,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27230,7 +27212,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27580,7 +27562,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27630,7 +27612,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27680,7 +27662,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27730,7 +27712,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27780,7 +27762,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27830,7 +27812,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28130,7 +28112,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28180,7 +28162,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28230,7 +28212,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28280,7 +28262,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28330,7 +28312,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28380,7 +28362,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28430,7 +28412,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28480,7 +28462,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28530,7 +28512,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28580,7 +28562,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28630,7 +28612,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28680,7 +28662,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28730,7 +28712,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28780,7 +28762,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28830,7 +28812,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28880,7 +28862,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28930,7 +28912,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -28980,7 +28962,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29030,7 +29012,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29080,7 +29062,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29130,7 +29112,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29180,7 +29162,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29230,7 +29212,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29280,7 +29262,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29330,7 +29312,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29380,7 +29362,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29430,7 +29412,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29480,7 +29462,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29530,7 +29512,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29580,7 +29562,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29630,7 +29612,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29680,7 +29662,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29730,7 +29712,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29780,7 +29762,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -29830,7 +29812,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -29880,7 +29862,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -29930,7 +29912,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -29980,7 +29962,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30030,7 +30012,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30080,7 +30062,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30130,7 +30112,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30180,7 +30162,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30230,7 +30212,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30280,7 +30262,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30330,7 +30312,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30380,7 +30362,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30430,7 +30412,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30480,7 +30462,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30530,7 +30512,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30580,7 +30562,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30630,7 +30612,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30680,7 +30662,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30730,7 +30712,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30780,7 +30762,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -32330,7 +32312,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32380,7 +32362,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32430,7 +32412,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32480,7 +32462,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32530,7 +32512,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32580,7 +32562,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32630,7 +32612,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32680,7 +32662,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32730,7 +32712,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32780,7 +32762,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32830,7 +32812,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32880,7 +32862,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32930,7 +32912,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -32980,7 +32962,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33030,7 +33012,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33080,7 +33062,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33130,7 +33112,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33180,7 +33162,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33230,7 +33212,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33280,7 +33262,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33330,7 +33312,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33380,7 +33362,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33430,7 +33412,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33480,7 +33462,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33530,7 +33512,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33580,7 +33562,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33630,7 +33612,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33680,7 +33662,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33730,7 +33712,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34430,7 +34412,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34480,7 +34462,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34530,7 +34512,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34580,7 +34562,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34630,7 +34612,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34680,7 +34662,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34730,7 +34712,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -34780,7 +34762,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -34830,7 +34812,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -34880,7 +34862,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -34930,7 +34912,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -34980,7 +34962,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35030,7 +35012,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35630,7 +35612,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35680,7 +35662,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35730,7 +35712,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35780,7 +35762,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -35830,7 +35812,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -35880,7 +35862,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -35930,7 +35912,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -35980,7 +35962,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36030,7 +36012,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36080,7 +36062,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36130,7 +36112,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36341,78 +36323,78 @@
         <v>145</v>
       </c>
       <c r="C699">
-        <v>-0.6713547876021693</v>
+        <v>-0.596708611830401</v>
       </c>
       <c r="D699" t="s">
         <v>249</v>
       </c>
       <c r="E699">
-        <v>-0.836346559131746</v>
+        <v>-0.8715193570106505</v>
       </c>
       <c r="F699">
         <v>-1</v>
       </c>
       <c r="G699">
-        <v>0.01261135478760217</v>
+        <v>0.0113967086118304</v>
       </c>
       <c r="H699">
-        <v>0.01247634655913175</v>
+        <v>0.01181151935701065</v>
       </c>
       <c r="I699">
-        <v>0.1649917715295768</v>
+        <v>0.2748107451802495</v>
       </c>
       <c r="J699">
         <v>1.4991771529576</v>
       </c>
       <c r="K699">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="L699">
-        <v>5.97</v>
+        <v>5.4</v>
       </c>
       <c r="M699">
-        <v>4.44</v>
+        <v>4.23</v>
       </c>
       <c r="N699">
-        <v>5.82</v>
+        <v>5.47</v>
       </c>
       <c r="O699">
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="700" spans="1:16">
       <c r="A700" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B700" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C700">
-        <v>-0.596708611830401</v>
+        <v>-0.6228560575120898</v>
       </c>
       <c r="D700" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E700">
-        <v>-0.8715193570106505</v>
+        <v>-0.8991702808190363</v>
       </c>
       <c r="F700">
         <v>-1</v>
       </c>
       <c r="G700">
-        <v>0.0113967086118304</v>
+        <v>0.01142285605751209</v>
       </c>
       <c r="H700">
-        <v>0.01181151935701065</v>
+        <v>0.01183917028081904</v>
       </c>
       <c r="I700">
-        <v>0.2748107451802495</v>
+        <v>0.2763142233069464</v>
       </c>
       <c r="J700">
-        <v>1.4991771529576</v>
+        <v>1.505714014378023</v>
       </c>
       <c r="K700">
         <v>4</v>
@@ -36435,34 +36417,34 @@
     </row>
     <row r="701" spans="1:16">
       <c r="A701" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B701" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C701">
-        <v>-0.6617168403008256</v>
+        <v>-1.011027493212815</v>
       </c>
       <c r="D701" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E701">
-        <v>-0.6617168403008256</v>
+        <v>-0.9468947300379096</v>
       </c>
       <c r="F701">
         <v>-1</v>
       </c>
       <c r="G701">
-        <v>0.01130171684030083</v>
+        <v>0.01165102749321282</v>
       </c>
       <c r="H701">
-        <v>0.01130171684030083</v>
+        <v>0.01174689473003791</v>
       </c>
       <c r="I701">
-        <v>-0</v>
+        <v>-0.06413276317490535</v>
       </c>
       <c r="J701">
-        <v>1.4991771529576</v>
+        <v>1.586723682509477</v>
       </c>
       <c r="K701">
         <v>3.99</v>
@@ -36471,16 +36453,16 @@
         <v>5.32</v>
       </c>
       <c r="M701">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="N701">
-        <v>5.32</v>
+        <v>5.4</v>
       </c>
       <c r="O701">
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>346</v>
+        <v>249</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36488,749 +36470,49 @@
         <v>0</v>
       </c>
       <c r="B702" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C702">
-        <v>-0.7003130836946401</v>
+        <v>-1.330403417515747</v>
       </c>
       <c r="D702" t="s">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="E702">
-        <v>-0.8653702238384202</v>
+        <v>-1.214027408971957</v>
       </c>
       <c r="F702">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G702">
-        <v>0.01264031308369464</v>
+        <v>0.01177040341751575</v>
       </c>
       <c r="H702">
-        <v>0.01250537022383842</v>
+        <v>0.01185402740897196</v>
       </c>
       <c r="I702">
-        <v>0.1650571401437801</v>
+        <v>0.1163760085437895</v>
       </c>
       <c r="J702">
-        <v>1.505714014378023</v>
+        <v>1.637600854378937</v>
       </c>
       <c r="K702">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="L702">
-        <v>5.97</v>
+        <v>5.22</v>
       </c>
       <c r="M702">
-        <v>4.44</v>
+        <v>3.99</v>
       </c>
       <c r="N702">
-        <v>5.82</v>
+        <v>5.32</v>
       </c>
       <c r="O702">
         <v>1</v>
       </c>
       <c r="P702" t="s">
         <v>347</v>
-      </c>
-    </row>
-    <row r="703" spans="1:16">
-      <c r="A703" s="1">
-        <v>1</v>
-      </c>
-      <c r="B703" t="s">
-        <v>146</v>
-      </c>
-      <c r="C703">
-        <v>-0.6228560575120898</v>
-      </c>
-      <c r="D703" t="s">
-        <v>250</v>
-      </c>
-      <c r="E703">
-        <v>-0.8991702808190363</v>
-      </c>
-      <c r="F703">
-        <v>-1</v>
-      </c>
-      <c r="G703">
-        <v>0.01142285605751209</v>
-      </c>
-      <c r="H703">
-        <v>0.01183917028081904</v>
-      </c>
-      <c r="I703">
-        <v>0.2763142233069464</v>
-      </c>
-      <c r="J703">
-        <v>1.505714014378023</v>
-      </c>
-      <c r="K703">
-        <v>4</v>
-      </c>
-      <c r="L703">
-        <v>5.4</v>
-      </c>
-      <c r="M703">
-        <v>4.23</v>
-      </c>
-      <c r="N703">
-        <v>5.47</v>
-      </c>
-      <c r="O703">
-        <v>1</v>
-      </c>
-      <c r="P703" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="704" spans="1:16">
-      <c r="A704" s="1">
-        <v>0</v>
-      </c>
-      <c r="B704" t="s">
-        <v>146</v>
-      </c>
-      <c r="C704">
-        <v>-0.6555683652294215</v>
-      </c>
-      <c r="D704" t="s">
-        <v>250</v>
-      </c>
-      <c r="E704">
-        <v>-0.9337635462301144</v>
-      </c>
-      <c r="F704">
-        <v>-1</v>
-      </c>
-      <c r="G704">
-        <v>0.01145556836522942</v>
-      </c>
-      <c r="H704">
-        <v>0.01187376354623011</v>
-      </c>
-      <c r="I704">
-        <v>0.2781951810006928</v>
-      </c>
-      <c r="J704">
-        <v>1.513892091307355</v>
-      </c>
-      <c r="K704">
-        <v>4</v>
-      </c>
-      <c r="L704">
-        <v>5.4</v>
-      </c>
-      <c r="M704">
-        <v>4.23</v>
-      </c>
-      <c r="N704">
-        <v>5.47</v>
-      </c>
-      <c r="O704">
-        <v>1</v>
-      </c>
-      <c r="P704" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="705" spans="1:16">
-      <c r="A705" s="1">
-        <v>0</v>
-      </c>
-      <c r="B705" t="s">
-        <v>146</v>
-      </c>
-      <c r="C705">
-        <v>-0.6880495404143332</v>
-      </c>
-      <c r="D705" t="s">
-        <v>250</v>
-      </c>
-      <c r="E705">
-        <v>-0.9681123889881587</v>
-      </c>
-      <c r="F705">
-        <v>-1</v>
-      </c>
-      <c r="G705">
-        <v>0.01148804954041433</v>
-      </c>
-      <c r="H705">
-        <v>0.01190811238898816</v>
-      </c>
-      <c r="I705">
-        <v>0.2800628485738255</v>
-      </c>
-      <c r="J705">
-        <v>1.522012385103583</v>
-      </c>
-      <c r="K705">
-        <v>4</v>
-      </c>
-      <c r="L705">
-        <v>5.4</v>
-      </c>
-      <c r="M705">
-        <v>4.23</v>
-      </c>
-      <c r="N705">
-        <v>5.47</v>
-      </c>
-      <c r="O705">
-        <v>1</v>
-      </c>
-      <c r="P705" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="706" spans="1:16">
-      <c r="A706" s="1">
-        <v>0</v>
-      </c>
-      <c r="B706" t="s">
-        <v>146</v>
-      </c>
-      <c r="C706">
-        <v>-0.7190734844162181</v>
-      </c>
-      <c r="D706" t="s">
-        <v>250</v>
-      </c>
-      <c r="E706">
-        <v>-1.000920209770152</v>
-      </c>
-      <c r="F706">
-        <v>-1</v>
-      </c>
-      <c r="G706">
-        <v>0.01151907348441622</v>
-      </c>
-      <c r="H706">
-        <v>0.01194092020977015</v>
-      </c>
-      <c r="I706">
-        <v>0.2818467253539341</v>
-      </c>
-      <c r="J706">
-        <v>1.529768371104055</v>
-      </c>
-      <c r="K706">
-        <v>4</v>
-      </c>
-      <c r="L706">
-        <v>5.4</v>
-      </c>
-      <c r="M706">
-        <v>4.23</v>
-      </c>
-      <c r="N706">
-        <v>5.47</v>
-      </c>
-      <c r="O706">
-        <v>1</v>
-      </c>
-      <c r="P706" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="707" spans="1:16">
-      <c r="A707" s="1">
-        <v>0</v>
-      </c>
-      <c r="B707" t="s">
-        <v>146</v>
-      </c>
-      <c r="C707">
-        <v>-0.7458787100492641</v>
-      </c>
-      <c r="D707" t="s">
-        <v>250</v>
-      </c>
-      <c r="E707">
-        <v>-1.029266735877098</v>
-      </c>
-      <c r="F707">
-        <v>-1</v>
-      </c>
-      <c r="G707">
-        <v>0.01154587871004927</v>
-      </c>
-      <c r="H707">
-        <v>0.0119692667358771</v>
-      </c>
-      <c r="I707">
-        <v>0.2833880258278336</v>
-      </c>
-      <c r="J707">
-        <v>1.536469677512316</v>
-      </c>
-      <c r="K707">
-        <v>4</v>
-      </c>
-      <c r="L707">
-        <v>5.4</v>
-      </c>
-      <c r="M707">
-        <v>4.23</v>
-      </c>
-      <c r="N707">
-        <v>5.47</v>
-      </c>
-      <c r="O707">
-        <v>1</v>
-      </c>
-      <c r="P707" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="708" spans="1:16">
-      <c r="A708" s="1">
-        <v>1</v>
-      </c>
-      <c r="B708" t="s">
-        <v>147</v>
-      </c>
-      <c r="C708">
-        <v>-0.8105140132741413</v>
-      </c>
-      <c r="D708" t="s">
-        <v>251</v>
-      </c>
-      <c r="E708">
-        <v>-0.8105140132741413</v>
-      </c>
-      <c r="F708">
-        <v>-1</v>
-      </c>
-      <c r="G708">
-        <v>0.01145051401327414</v>
-      </c>
-      <c r="H708">
-        <v>0.01145051401327414</v>
-      </c>
-      <c r="I708">
-        <v>-0</v>
-      </c>
-      <c r="J708">
-        <v>1.536469677512316</v>
-      </c>
-      <c r="K708">
-        <v>3.99</v>
-      </c>
-      <c r="L708">
-        <v>5.32</v>
-      </c>
-      <c r="M708">
-        <v>3.99</v>
-      </c>
-      <c r="N708">
-        <v>5.32</v>
-      </c>
-      <c r="O708">
-        <v>1</v>
-      </c>
-      <c r="P708" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="709" spans="1:16">
-      <c r="A709" s="1">
-        <v>0</v>
-      </c>
-      <c r="B709" t="s">
-        <v>146</v>
-      </c>
-      <c r="C709">
-        <v>-0.7844366033779329</v>
-      </c>
-      <c r="D709" t="s">
-        <v>250</v>
-      </c>
-      <c r="E709">
-        <v>-1.070041708072165</v>
-      </c>
-      <c r="F709">
-        <v>-1</v>
-      </c>
-      <c r="G709">
-        <v>0.01158443660337793</v>
-      </c>
-      <c r="H709">
-        <v>0.01201004170807217</v>
-      </c>
-      <c r="I709">
-        <v>0.2856051046942323</v>
-      </c>
-      <c r="J709">
-        <v>1.546109150844483</v>
-      </c>
-      <c r="K709">
-        <v>4</v>
-      </c>
-      <c r="L709">
-        <v>5.4</v>
-      </c>
-      <c r="M709">
-        <v>4.23</v>
-      </c>
-      <c r="N709">
-        <v>5.47</v>
-      </c>
-      <c r="O709">
-        <v>1</v>
-      </c>
-      <c r="P709" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="710" spans="1:16">
-      <c r="A710" s="1">
-        <v>0</v>
-      </c>
-      <c r="B710" t="s">
-        <v>146</v>
-      </c>
-      <c r="C710">
-        <v>-0.8174519995514462</v>
-      </c>
-      <c r="D710" t="s">
-        <v>250</v>
-      </c>
-      <c r="E710">
-        <v>-1.104955489525656</v>
-      </c>
-      <c r="F710">
-        <v>-1</v>
-      </c>
-      <c r="G710">
-        <v>0.01161745199955145</v>
-      </c>
-      <c r="H710">
-        <v>0.01204495548952566</v>
-      </c>
-      <c r="I710">
-        <v>0.2875034899742097</v>
-      </c>
-      <c r="J710">
-        <v>1.554362999887862</v>
-      </c>
-      <c r="K710">
-        <v>4</v>
-      </c>
-      <c r="L710">
-        <v>5.4</v>
-      </c>
-      <c r="M710">
-        <v>4.23</v>
-      </c>
-      <c r="N710">
-        <v>5.47</v>
-      </c>
-      <c r="O710">
-        <v>1</v>
-      </c>
-      <c r="P710" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="711" spans="1:16">
-      <c r="A711" s="1">
-        <v>1</v>
-      </c>
-      <c r="B711" t="s">
-        <v>147</v>
-      </c>
-      <c r="C711">
-        <v>-0.8819083695525682</v>
-      </c>
-      <c r="D711" t="s">
-        <v>251</v>
-      </c>
-      <c r="E711">
-        <v>-0.8819083695525682</v>
-      </c>
-      <c r="F711">
-        <v>-1</v>
-      </c>
-      <c r="G711">
-        <v>0.01152190836955257</v>
-      </c>
-      <c r="H711">
-        <v>0.01152190836955257</v>
-      </c>
-      <c r="I711">
-        <v>-0</v>
-      </c>
-      <c r="J711">
-        <v>1.554362999887862</v>
-      </c>
-      <c r="K711">
-        <v>3.99</v>
-      </c>
-      <c r="L711">
-        <v>5.32</v>
-      </c>
-      <c r="M711">
-        <v>3.99</v>
-      </c>
-      <c r="N711">
-        <v>5.32</v>
-      </c>
-      <c r="O711">
-        <v>1</v>
-      </c>
-      <c r="P711" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="712" spans="1:16">
-      <c r="A712" s="1">
-        <v>0</v>
-      </c>
-      <c r="B712" t="s">
-        <v>146</v>
-      </c>
-      <c r="C712">
-        <v>-0.856308974393289</v>
-      </c>
-      <c r="D712" t="s">
-        <v>250</v>
-      </c>
-      <c r="E712">
-        <v>-1.146046740420904</v>
-      </c>
-      <c r="F712">
-        <v>-1</v>
-      </c>
-      <c r="G712">
-        <v>0.01165630897439329</v>
-      </c>
-      <c r="H712">
-        <v>0.0120860467404209</v>
-      </c>
-      <c r="I712">
-        <v>0.2897377660276153</v>
-      </c>
-      <c r="J712">
-        <v>1.564077243598322</v>
-      </c>
-      <c r="K712">
-        <v>4</v>
-      </c>
-      <c r="L712">
-        <v>5.4</v>
-      </c>
-      <c r="M712">
-        <v>4.23</v>
-      </c>
-      <c r="N712">
-        <v>5.47</v>
-      </c>
-      <c r="O712">
-        <v>1</v>
-      </c>
-      <c r="P712" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="713" spans="1:16">
-      <c r="A713" s="1">
-        <v>1</v>
-      </c>
-      <c r="B713" t="s">
-        <v>147</v>
-      </c>
-      <c r="C713">
-        <v>-0.920668201957306</v>
-      </c>
-      <c r="D713" t="s">
-        <v>251</v>
-      </c>
-      <c r="E713">
-        <v>-0.920668201957306</v>
-      </c>
-      <c r="F713">
-        <v>-1</v>
-      </c>
-      <c r="G713">
-        <v>0.01156066820195731</v>
-      </c>
-      <c r="H713">
-        <v>0.01156066820195731</v>
-      </c>
-      <c r="I713">
-        <v>-0</v>
-      </c>
-      <c r="J713">
-        <v>1.564077243598322</v>
-      </c>
-      <c r="K713">
-        <v>3.99</v>
-      </c>
-      <c r="L713">
-        <v>5.32</v>
-      </c>
-      <c r="M713">
-        <v>3.99</v>
-      </c>
-      <c r="N713">
-        <v>5.32</v>
-      </c>
-      <c r="O713">
-        <v>1</v>
-      </c>
-      <c r="P713" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="714" spans="1:16">
-      <c r="A714" s="1">
-        <v>0</v>
-      </c>
-      <c r="B714" t="s">
-        <v>147</v>
-      </c>
-      <c r="C714">
-        <v>-0.9661101898715314</v>
-      </c>
-      <c r="D714" t="s">
-        <v>251</v>
-      </c>
-      <c r="E714">
-        <v>-0.9661101898715314</v>
-      </c>
-      <c r="F714">
-        <v>-1</v>
-      </c>
-      <c r="G714">
-        <v>0.01160611018987153</v>
-      </c>
-      <c r="H714">
-        <v>0.01160611018987153</v>
-      </c>
-      <c r="I714">
-        <v>-0</v>
-      </c>
-      <c r="J714">
-        <v>1.575466213000384</v>
-      </c>
-      <c r="K714">
-        <v>3.99</v>
-      </c>
-      <c r="L714">
-        <v>5.32</v>
-      </c>
-      <c r="M714">
-        <v>3.99</v>
-      </c>
-      <c r="N714">
-        <v>5.32</v>
-      </c>
-      <c r="O714">
-        <v>1</v>
-      </c>
-      <c r="P714" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="715" spans="1:16">
-      <c r="A715" s="1">
-        <v>0</v>
-      </c>
-      <c r="B715" t="s">
-        <v>147</v>
-      </c>
-      <c r="C715">
-        <v>-1.011027493212815</v>
-      </c>
-      <c r="D715" t="s">
-        <v>251</v>
-      </c>
-      <c r="E715">
-        <v>-1.011027493212815</v>
-      </c>
-      <c r="F715">
-        <v>-1</v>
-      </c>
-      <c r="G715">
-        <v>0.01165102749321282</v>
-      </c>
-      <c r="H715">
-        <v>0.01165102749321282</v>
-      </c>
-      <c r="I715">
-        <v>-0</v>
-      </c>
-      <c r="J715">
-        <v>1.586723682509477</v>
-      </c>
-      <c r="K715">
-        <v>3.99</v>
-      </c>
-      <c r="L715">
-        <v>5.32</v>
-      </c>
-      <c r="M715">
-        <v>3.99</v>
-      </c>
-      <c r="N715">
-        <v>5.32</v>
-      </c>
-      <c r="O715">
-        <v>1</v>
-      </c>
-      <c r="P715" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="716" spans="1:16">
-      <c r="A716" s="1">
-        <v>0</v>
-      </c>
-      <c r="B716" t="s">
-        <v>147</v>
-      </c>
-      <c r="C716">
-        <v>-1.068447687938677</v>
-      </c>
-      <c r="D716" t="s">
-        <v>251</v>
-      </c>
-      <c r="E716">
-        <v>-1.068447687938677</v>
-      </c>
-      <c r="F716">
-        <v>-1</v>
-      </c>
-      <c r="G716">
-        <v>0.01170844768793868</v>
-      </c>
-      <c r="H716">
-        <v>0.01170844768793868</v>
-      </c>
-      <c r="I716">
-        <v>-0</v>
-      </c>
-      <c r="J716">
-        <v>1.60111470875656</v>
-      </c>
-      <c r="K716">
-        <v>3.99</v>
-      </c>
-      <c r="L716">
-        <v>5.32</v>
-      </c>
-      <c r="M716">
-        <v>3.99</v>
-      </c>
-      <c r="N716">
-        <v>5.32</v>
-      </c>
-      <c r="O716">
-        <v>1</v>
-      </c>
-      <c r="P716" t="s">
-        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2169" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="361">
   <si>
     <t>trade_time</t>
   </si>
@@ -451,19 +451,19 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-11-10</t>
+    <t>2021-11-24</t>
+  </si>
+  <si>
+    <t>2021-11-26</t>
   </si>
   <si>
     <t>2021-11-16</t>
   </si>
   <si>
-    <t>2021-11-24</t>
+    <t>2021-11-18</t>
   </si>
   <si>
-    <t>2021-11-22</t>
-  </si>
-  <si>
-    <t>2021-11-18</t>
+    <t>2021-11-25</t>
   </si>
   <si>
     <t>2017-04-20</t>
@@ -769,10 +769,10 @@
     <t>2021-08-09</t>
   </si>
   <si>
-    <t>2021-11-11</t>
+    <t>2021-11-29</t>
   </si>
   <si>
-    <t>2021-11-25</t>
+    <t>2021-11-22</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -1084,16 +1084,19 @@
     <t>2021-11-09</t>
   </si>
   <si>
-    <t>2021-11-12</t>
+    <t>2021-11-10</t>
   </si>
   <si>
-    <t>2021-11-15</t>
+    <t>2021-11-11</t>
+  </si>
+  <si>
+    <t>2021-11-12</t>
   </si>
   <si>
     <t>2021-11-17</t>
   </si>
   <si>
-    <t>2021-11-19</t>
+    <t>2021-11-23</t>
   </si>
 </sst>
 </file>
@@ -1451,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P719"/>
+  <dimension ref="A1:P725"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -36365,7 +36368,7 @@
         <v>251</v>
       </c>
       <c r="E699">
-        <v>-0.8715193570106505</v>
+        <v>-0.4468731812388809</v>
       </c>
       <c r="F699">
         <v>-1</v>
@@ -36374,10 +36377,10 @@
         <v>0.0113967086118304</v>
       </c>
       <c r="H699">
-        <v>0.01181151935701065</v>
+        <v>0.01094687318123888</v>
       </c>
       <c r="I699">
-        <v>0.2748107451802495</v>
+        <v>-0.1498354305915202</v>
       </c>
       <c r="J699">
         <v>1.4991771529576</v>
@@ -36389,10 +36392,10 @@
         <v>5.4</v>
       </c>
       <c r="M699">
-        <v>4.23</v>
+        <v>3.8</v>
       </c>
       <c r="N699">
-        <v>5.47</v>
+        <v>5.25</v>
       </c>
       <c r="O699">
         <v>1</v>
@@ -36403,96 +36406,96 @@
     </row>
     <row r="700" spans="1:16">
       <c r="A700" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B700" t="s">
         <v>146</v>
       </c>
       <c r="C700">
-        <v>-0.8680274779434312</v>
+        <v>-0.54680735347549</v>
       </c>
       <c r="D700" t="s">
-        <v>148</v>
+        <v>251</v>
       </c>
       <c r="E700">
-        <v>-0.6877989173683101</v>
+        <v>-0.4468731812388809</v>
       </c>
       <c r="F700">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G700">
-        <v>0.01126802747794343</v>
+        <v>0.01108680735347549</v>
       </c>
       <c r="H700">
-        <v>0.01132779891736831</v>
+        <v>0.01094687318123888</v>
       </c>
       <c r="I700">
-        <v>0.180228560575121</v>
+        <v>-0.09993417223660916</v>
       </c>
       <c r="J700">
-        <v>1.505714014378023</v>
+        <v>1.4991771529576</v>
       </c>
       <c r="K700">
-        <v>4.03</v>
+        <v>3.88</v>
       </c>
       <c r="L700">
-        <v>5.2</v>
+        <v>5.27</v>
       </c>
       <c r="M700">
-        <v>3.99</v>
+        <v>3.8</v>
       </c>
       <c r="N700">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="O700">
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="701" spans="1:16">
       <c r="A701" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B701" t="s">
         <v>147</v>
       </c>
       <c r="C701">
-        <v>-0.6228560575120898</v>
+        <v>-0.8680274779434312</v>
       </c>
       <c r="D701" t="s">
         <v>252</v>
       </c>
       <c r="E701">
-        <v>-0.7330846180872115</v>
+        <v>-0.6877989173683101</v>
       </c>
       <c r="F701">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G701">
-        <v>0.01142285605751209</v>
+        <v>0.01126802747794343</v>
       </c>
       <c r="H701">
-        <v>0.01143308461808721</v>
+        <v>0.01132779891736831</v>
       </c>
       <c r="I701">
-        <v>0.1102285605751216</v>
+        <v>0.180228560575121</v>
       </c>
       <c r="J701">
         <v>1.505714014378023</v>
       </c>
       <c r="K701">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="L701">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M701">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="N701">
-        <v>5.35</v>
+        <v>5.32</v>
       </c>
       <c r="O701">
         <v>1</v>
@@ -36503,102 +36506,102 @@
     </row>
     <row r="702" spans="1:16">
       <c r="A702" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B702" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C702">
-        <v>-0.9009851279686432</v>
+        <v>-0.6228560575120898</v>
       </c>
       <c r="D702" t="s">
-        <v>148</v>
+        <v>251</v>
       </c>
       <c r="E702">
-        <v>-0.7204294443163484</v>
+        <v>-0.4717132546364855</v>
       </c>
       <c r="F702">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G702">
-        <v>0.01130098512796864</v>
+        <v>0.01142285605751209</v>
       </c>
       <c r="H702">
-        <v>0.01136042944431635</v>
+        <v>0.01097171325463649</v>
       </c>
       <c r="I702">
-        <v>0.1805556836522948</v>
+        <v>-0.1511428028756043</v>
       </c>
       <c r="J702">
-        <v>1.513892091307355</v>
+        <v>1.505714014378023</v>
       </c>
       <c r="K702">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="L702">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="M702">
-        <v>3.99</v>
+        <v>3.8</v>
       </c>
       <c r="N702">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="O702">
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="703" spans="1:16">
       <c r="A703" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B703" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C703">
-        <v>-0.6555683652294215</v>
+        <v>-0.5721703757867278</v>
       </c>
       <c r="D703" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E703">
-        <v>-0.7661240488817169</v>
+        <v>-0.4717132546364855</v>
       </c>
       <c r="F703">
         <v>-1</v>
       </c>
       <c r="G703">
-        <v>0.01145556836522942</v>
+        <v>0.01111217037578673</v>
       </c>
       <c r="H703">
-        <v>0.01146612404888172</v>
+        <v>0.01097171325463649</v>
       </c>
       <c r="I703">
-        <v>0.1105556836522954</v>
+        <v>-0.1004571211502423</v>
       </c>
       <c r="J703">
-        <v>1.513892091307355</v>
+        <v>1.505714014378023</v>
       </c>
       <c r="K703">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="L703">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="M703">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="N703">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="O703">
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36606,31 +36609,31 @@
         <v>0</v>
       </c>
       <c r="B704" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C704">
-        <v>-0.9337099119674415</v>
+        <v>-0.9009851279686432</v>
       </c>
       <c r="D704" t="s">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="E704">
-        <v>-0.7528294165632978</v>
+        <v>-0.7204294443163484</v>
       </c>
       <c r="F704">
         <v>1</v>
       </c>
       <c r="G704">
-        <v>0.01133370991196744</v>
+        <v>0.01130098512796864</v>
       </c>
       <c r="H704">
-        <v>0.0113928294165633</v>
+        <v>0.01136042944431635</v>
       </c>
       <c r="I704">
-        <v>0.1808804954041436</v>
+        <v>0.1805556836522948</v>
       </c>
       <c r="J704">
-        <v>1.522012385103583</v>
+        <v>1.513892091307355</v>
       </c>
       <c r="K704">
         <v>4.03</v>
@@ -36648,7 +36651,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36656,31 +36659,31 @@
         <v>1</v>
       </c>
       <c r="B705" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C705">
-        <v>-0.6880495404143332</v>
+        <v>-0.6555683652294215</v>
       </c>
       <c r="D705" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E705">
-        <v>-0.7989300358184774</v>
+        <v>-0.5027899469679502</v>
       </c>
       <c r="F705">
         <v>-1</v>
       </c>
       <c r="G705">
-        <v>0.01148804954041433</v>
+        <v>0.01145556836522942</v>
       </c>
       <c r="H705">
-        <v>0.01149893003581848</v>
+        <v>0.01100278994696795</v>
       </c>
       <c r="I705">
-        <v>0.1108804954041442</v>
+        <v>-0.1527784182614713</v>
       </c>
       <c r="J705">
-        <v>1.522012385103583</v>
+        <v>1.513892091307355</v>
       </c>
       <c r="K705">
         <v>4</v>
@@ -36689,66 +36692,66 @@
         <v>5.4</v>
       </c>
       <c r="M705">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="N705">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="O705">
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="706" spans="1:16">
       <c r="A706" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B706" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C706">
-        <v>-0.7190734844162181</v>
+        <v>-0.6039013142725391</v>
       </c>
       <c r="D706" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E706">
-        <v>-0.8302642192603811</v>
+        <v>-0.5027899469679502</v>
       </c>
       <c r="F706">
         <v>-1</v>
       </c>
       <c r="G706">
-        <v>0.01151907348441622</v>
+        <v>0.01114390131427254</v>
       </c>
       <c r="H706">
-        <v>0.01153026421926038</v>
+        <v>0.01100278994696795</v>
       </c>
       <c r="I706">
-        <v>0.111190734844163</v>
+        <v>-0.1011113673045889</v>
       </c>
       <c r="J706">
-        <v>1.529768371104055</v>
+        <v>1.513892091307355</v>
       </c>
       <c r="K706">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="L706">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="M706">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="N706">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="O706">
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36759,78 +36762,78 @@
         <v>147</v>
       </c>
       <c r="C707">
-        <v>-0.7458787100492641</v>
+        <v>-0.9337099119674415</v>
       </c>
       <c r="D707" t="s">
         <v>252</v>
       </c>
       <c r="E707">
-        <v>-0.8573374971497572</v>
+        <v>-0.7528294165632978</v>
       </c>
       <c r="F707">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G707">
-        <v>0.01154587871004927</v>
+        <v>0.01133370991196744</v>
       </c>
       <c r="H707">
-        <v>0.01155733749714976</v>
+        <v>0.0113928294165633</v>
       </c>
       <c r="I707">
-        <v>0.1114587871004931</v>
+        <v>0.1808804954041436</v>
       </c>
       <c r="J707">
-        <v>1.536469677512316</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K707">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="L707">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M707">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="N707">
-        <v>5.35</v>
+        <v>5.32</v>
       </c>
       <c r="O707">
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="708" spans="1:16">
       <c r="A708" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B708" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C708">
-        <v>-0.7844366033779329</v>
+        <v>-0.6880495404143332</v>
       </c>
       <c r="D708" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E708">
-        <v>-0.8962809694117126</v>
+        <v>-0.5336470633936168</v>
       </c>
       <c r="F708">
         <v>-1</v>
       </c>
       <c r="G708">
-        <v>0.01158443660337793</v>
+        <v>0.01148804954041433</v>
       </c>
       <c r="H708">
-        <v>0.01159628096941171</v>
+        <v>0.01103364706339362</v>
       </c>
       <c r="I708">
-        <v>0.1118443660337798</v>
+        <v>-0.1544024770207164</v>
       </c>
       <c r="J708">
-        <v>1.546109150844483</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K708">
         <v>4</v>
@@ -36839,66 +36842,66 @@
         <v>5.4</v>
       </c>
       <c r="M708">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="N708">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="O708">
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="709" spans="1:16">
       <c r="A709" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B709" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C709">
-        <v>-0.8174519995514462</v>
+        <v>-0.6354080542019034</v>
       </c>
       <c r="D709" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E709">
-        <v>-0.9296265195469617</v>
+        <v>-0.5336470633936168</v>
       </c>
       <c r="F709">
         <v>-1</v>
       </c>
       <c r="G709">
-        <v>0.01161745199955145</v>
+        <v>0.0111754080542019</v>
       </c>
       <c r="H709">
-        <v>0.01162962651954696</v>
+        <v>0.01103364706339362</v>
       </c>
       <c r="I709">
-        <v>0.1121745199955155</v>
+        <v>-0.1017609908082866</v>
       </c>
       <c r="J709">
-        <v>1.554362999887862</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K709">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="L709">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="M709">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="N709">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="O709">
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36909,78 +36912,78 @@
         <v>147</v>
       </c>
       <c r="C710">
-        <v>-0.856308974393289</v>
+        <v>-0.9649665355493404</v>
       </c>
       <c r="D710" t="s">
         <v>252</v>
       </c>
       <c r="E710">
-        <v>-0.9688720641372228</v>
+        <v>-0.783775800705178</v>
       </c>
       <c r="F710">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G710">
-        <v>0.01165630897439329</v>
+        <v>0.01136496653554934</v>
       </c>
       <c r="H710">
-        <v>0.01166887206413722</v>
+        <v>0.01142377580070518</v>
       </c>
       <c r="I710">
-        <v>0.1125630897439338</v>
+        <v>0.1811907348441624</v>
       </c>
       <c r="J710">
-        <v>1.564077243598322</v>
+        <v>1.529768371104055</v>
       </c>
       <c r="K710">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="L710">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M710">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="N710">
-        <v>5.35</v>
+        <v>5.32</v>
       </c>
       <c r="O710">
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="711" spans="1:16">
       <c r="A711" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B711" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C711">
-        <v>-0.9018648520015349</v>
+        <v>-0.7190734844162181</v>
       </c>
       <c r="D711" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E711">
-        <v>-1.014883500521551</v>
+        <v>-0.5631198101954071</v>
       </c>
       <c r="F711">
         <v>-1</v>
       </c>
       <c r="G711">
-        <v>0.01170186485200153</v>
+        <v>0.01151907348441622</v>
       </c>
       <c r="H711">
-        <v>0.01171488350052155</v>
+        <v>0.01106311981019541</v>
       </c>
       <c r="I711">
-        <v>0.1130186485200158</v>
+        <v>-0.155953674220811</v>
       </c>
       <c r="J711">
-        <v>1.575466213000384</v>
+        <v>1.529768371104055</v>
       </c>
       <c r="K711">
         <v>4</v>
@@ -36989,66 +36992,66 @@
         <v>5.4</v>
       </c>
       <c r="M711">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="N711">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="O711">
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>145</v>
+        <v>351</v>
       </c>
     </row>
     <row r="712" spans="1:16">
       <c r="A712" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B712" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C712">
-        <v>-1.011027493212815</v>
+        <v>-0.6655012798837321</v>
       </c>
       <c r="D712" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E712">
-        <v>-1.060363677338289</v>
+        <v>-0.5631198101954071</v>
       </c>
       <c r="F712">
         <v>-1</v>
       </c>
       <c r="G712">
-        <v>0.01165102749321282</v>
+        <v>0.01120550127988373</v>
       </c>
       <c r="H712">
-        <v>0.01176036367733829</v>
+        <v>0.01106311981019541</v>
       </c>
       <c r="I712">
-        <v>0.04933618412547425</v>
+        <v>-0.102381469688325</v>
       </c>
       <c r="J712">
-        <v>1.586723682509477</v>
+        <v>1.529768371104055</v>
       </c>
       <c r="K712">
-        <v>3.99</v>
+        <v>3.88</v>
       </c>
       <c r="L712">
-        <v>5.32</v>
+        <v>5.27</v>
       </c>
       <c r="M712">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="N712">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="O712">
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>251</v>
+        <v>351</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37056,31 +37059,31 @@
         <v>0</v>
       </c>
       <c r="B713" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C713">
-        <v>-1.004458835026242</v>
+        <v>-0.7458787100492641</v>
       </c>
       <c r="D713" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E713">
-        <v>-1.118503423376505</v>
+        <v>-0.5885847745468009</v>
       </c>
       <c r="F713">
         <v>-1</v>
       </c>
       <c r="G713">
-        <v>0.01180445883502624</v>
+        <v>0.01154587871004927</v>
       </c>
       <c r="H713">
-        <v>0.01181850342337651</v>
+        <v>0.0110885847745468</v>
       </c>
       <c r="I713">
-        <v>0.1140445883502634</v>
+        <v>-0.1572939355024632</v>
       </c>
       <c r="J713">
-        <v>1.60111470875656</v>
+        <v>1.536469677512316</v>
       </c>
       <c r="K713">
         <v>4</v>
@@ -37089,66 +37092,66 @@
         <v>5.4</v>
       </c>
       <c r="M713">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="N713">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="O713">
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="714" spans="1:16">
       <c r="A714" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B714" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C714">
-        <v>-1.061577724511335</v>
+        <v>-0.6915023487477869</v>
       </c>
       <c r="D714" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E714">
-        <v>-1.176193501756449</v>
+        <v>-0.5885847745468009</v>
       </c>
       <c r="F714">
         <v>-1</v>
       </c>
       <c r="G714">
-        <v>0.01186157772451133</v>
+        <v>0.01123150234874778</v>
       </c>
       <c r="H714">
-        <v>0.01187619350175645</v>
+        <v>0.0110885847745468</v>
       </c>
       <c r="I714">
-        <v>0.1146157772451142</v>
+        <v>-0.102917574200986</v>
       </c>
       <c r="J714">
-        <v>1.615394431127834</v>
+        <v>1.536469677512316</v>
       </c>
       <c r="K714">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="L714">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="M714">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="N714">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="O714">
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37159,146 +37162,146 @@
         <v>147</v>
       </c>
       <c r="C715">
-        <v>-1.10247255173636</v>
+        <v>-1.030819877903268</v>
       </c>
       <c r="D715" t="s">
         <v>252</v>
       </c>
       <c r="E715">
-        <v>-1.217497277253725</v>
+        <v>-0.8489755118694884</v>
       </c>
       <c r="F715">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G715">
-        <v>0.01190247255173636</v>
+        <v>0.01143081987790327</v>
       </c>
       <c r="H715">
-        <v>0.01191749727725372</v>
+        <v>0.01148897551186949</v>
       </c>
       <c r="I715">
-        <v>0.1150247255173644</v>
+        <v>0.1818443660337792</v>
       </c>
       <c r="J715">
-        <v>1.62561813793409</v>
+        <v>1.546109150844483</v>
       </c>
       <c r="K715">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="L715">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M715">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="N715">
-        <v>5.35</v>
+        <v>5.32</v>
       </c>
       <c r="O715">
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>146</v>
+        <v>353</v>
       </c>
     </row>
     <row r="716" spans="1:16">
       <c r="A716" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B716" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C716">
-        <v>-1.330403417515747</v>
+        <v>-0.7289035052765955</v>
       </c>
       <c r="D716" t="s">
-        <v>148</v>
+        <v>251</v>
       </c>
       <c r="E716">
-        <v>-1.214027408971957</v>
+        <v>-0.6252147732090361</v>
       </c>
       <c r="F716">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G716">
-        <v>0.01177040341751575</v>
+        <v>0.01126890350527659</v>
       </c>
       <c r="H716">
-        <v>0.01185402740897196</v>
+        <v>0.01112521477320904</v>
       </c>
       <c r="I716">
-        <v>0.1163760085437895</v>
+        <v>-0.1036887320675595</v>
       </c>
       <c r="J716">
-        <v>1.637600854378937</v>
+        <v>1.546109150844483</v>
       </c>
       <c r="K716">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="L716">
-        <v>5.22</v>
+        <v>5.27</v>
       </c>
       <c r="M716">
-        <v>3.99</v>
+        <v>3.8</v>
       </c>
       <c r="N716">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="O716">
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="717" spans="1:16">
       <c r="A717" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B717" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C717">
-        <v>-1.150403417515746</v>
+        <v>-0.7609284395649034</v>
       </c>
       <c r="D717" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E717">
-        <v>-1.265907451690905</v>
+        <v>-0.6565793995738742</v>
       </c>
       <c r="F717">
         <v>-1</v>
       </c>
       <c r="G717">
-        <v>0.01195040341751575</v>
+        <v>0.0113009284395649</v>
       </c>
       <c r="H717">
-        <v>0.0119659074516909</v>
+        <v>0.01115657939957388</v>
       </c>
       <c r="I717">
-        <v>0.1155040341751583</v>
+        <v>-0.1043490399910292</v>
       </c>
       <c r="J717">
-        <v>1.637600854378937</v>
+        <v>1.554362999887862</v>
       </c>
       <c r="K717">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="L717">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="M717">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="N717">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="O717">
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37306,49 +37309,49 @@
         <v>0</v>
       </c>
       <c r="B718" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C718">
-        <v>-1.204591693036235</v>
+        <v>-0.7986197051614914</v>
       </c>
       <c r="D718" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E718">
-        <v>-1.320637609966599</v>
+        <v>-0.6934935256736248</v>
       </c>
       <c r="F718">
         <v>-1</v>
       </c>
       <c r="G718">
-        <v>0.01200459169303624</v>
+        <v>0.01133861970516149</v>
       </c>
       <c r="H718">
-        <v>0.0120206376099666</v>
+        <v>0.01119349352567362</v>
       </c>
       <c r="I718">
-        <v>0.1160459169303634</v>
+        <v>-0.1051261794878666</v>
       </c>
       <c r="J718">
-        <v>1.651147923259059</v>
+        <v>1.564077243598322</v>
       </c>
       <c r="K718">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="L718">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="M718">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="N718">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="O718">
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>149</v>
+        <v>355</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37356,49 +37359,349 @@
         <v>0</v>
       </c>
       <c r="B719" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C719">
-        <v>-1.263641542615024</v>
+        <v>-0.8428089064414896</v>
       </c>
       <c r="D719" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E719">
-        <v>-1.380277958041175</v>
+        <v>-0.7367716094014582</v>
       </c>
       <c r="F719">
         <v>-1</v>
       </c>
       <c r="G719">
-        <v>0.01206364154261502</v>
+        <v>0.01138280890644149</v>
       </c>
       <c r="H719">
-        <v>0.01208027795804117</v>
+        <v>0.01123677160940146</v>
       </c>
       <c r="I719">
-        <v>0.116636415426151</v>
+        <v>-0.1060372970400314</v>
       </c>
       <c r="J719">
-        <v>1.665910385653756</v>
+        <v>1.575466213000384</v>
       </c>
       <c r="K719">
+        <v>3.88</v>
+      </c>
+      <c r="L719">
+        <v>5.27</v>
+      </c>
+      <c r="M719">
+        <v>3.8</v>
+      </c>
+      <c r="N719">
+        <v>5.25</v>
+      </c>
+      <c r="O719">
+        <v>1</v>
+      </c>
+      <c r="P719" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="720" spans="1:16">
+      <c r="A720" s="1">
+        <v>0</v>
+      </c>
+      <c r="B720" t="s">
+        <v>146</v>
+      </c>
+      <c r="C720">
+        <v>-0.8864878881367728</v>
+      </c>
+      <c r="D720" t="s">
+        <v>251</v>
+      </c>
+      <c r="E720">
+        <v>-0.7795499935360137</v>
+      </c>
+      <c r="F720">
+        <v>-1</v>
+      </c>
+      <c r="G720">
+        <v>0.01142648788813677</v>
+      </c>
+      <c r="H720">
+        <v>0.01127954999353601</v>
+      </c>
+      <c r="I720">
+        <v>-0.1069378946007591</v>
+      </c>
+      <c r="J720">
+        <v>1.586723682509477</v>
+      </c>
+      <c r="K720">
+        <v>3.88</v>
+      </c>
+      <c r="L720">
+        <v>5.27</v>
+      </c>
+      <c r="M720">
+        <v>3.8</v>
+      </c>
+      <c r="N720">
+        <v>5.25</v>
+      </c>
+      <c r="O720">
+        <v>1</v>
+      </c>
+      <c r="P720" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="721" spans="1:16">
+      <c r="A721" s="1">
+        <v>0</v>
+      </c>
+      <c r="B721" t="s">
+        <v>146</v>
+      </c>
+      <c r="C721">
+        <v>-0.9423250699754551</v>
+      </c>
+      <c r="D721" t="s">
+        <v>251</v>
+      </c>
+      <c r="E721">
+        <v>-0.8342358932749292</v>
+      </c>
+      <c r="F721">
+        <v>-1</v>
+      </c>
+      <c r="G721">
+        <v>0.01148232506997545</v>
+      </c>
+      <c r="H721">
+        <v>0.01133423589327493</v>
+      </c>
+      <c r="I721">
+        <v>-0.1080891767005259</v>
+      </c>
+      <c r="J721">
+        <v>1.60111470875656</v>
+      </c>
+      <c r="K721">
+        <v>3.88</v>
+      </c>
+      <c r="L721">
+        <v>5.27</v>
+      </c>
+      <c r="M721">
+        <v>3.8</v>
+      </c>
+      <c r="N721">
+        <v>5.25</v>
+      </c>
+      <c r="O721">
+        <v>1</v>
+      </c>
+      <c r="P721" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="722" spans="1:16">
+      <c r="A722" s="1">
+        <v>0</v>
+      </c>
+      <c r="B722" t="s">
+        <v>148</v>
+      </c>
+      <c r="C722">
+        <v>-1.330403417515747</v>
+      </c>
+      <c r="D722" t="s">
+        <v>145</v>
+      </c>
+      <c r="E722">
+        <v>-1.150403417515746</v>
+      </c>
+      <c r="F722">
+        <v>1</v>
+      </c>
+      <c r="G722">
+        <v>0.01177040341751575</v>
+      </c>
+      <c r="H722">
+        <v>0.01195040341751575</v>
+      </c>
+      <c r="I722">
+        <v>0.1800000000000006</v>
+      </c>
+      <c r="J722">
+        <v>1.637600854378937</v>
+      </c>
+      <c r="K722">
         <v>4</v>
       </c>
-      <c r="L719">
+      <c r="L722">
+        <v>5.22</v>
+      </c>
+      <c r="M722">
+        <v>4</v>
+      </c>
+      <c r="N722">
         <v>5.4</v>
       </c>
-      <c r="M719">
+      <c r="O722">
+        <v>1</v>
+      </c>
+      <c r="P722" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="723" spans="1:16">
+      <c r="A723" s="1">
+        <v>0</v>
+      </c>
+      <c r="B723" t="s">
+        <v>149</v>
+      </c>
+      <c r="C723">
+        <v>-1.42715909512542</v>
+      </c>
+      <c r="D723" t="s">
+        <v>146</v>
+      </c>
+      <c r="E723">
+        <v>-1.238756754724413</v>
+      </c>
+      <c r="F723">
+        <v>1</v>
+      </c>
+      <c r="G723">
+        <v>0.01212715909512542</v>
+      </c>
+      <c r="H723">
+        <v>0.01177875675472441</v>
+      </c>
+      <c r="I723">
+        <v>0.1884023404010069</v>
+      </c>
+      <c r="J723">
+        <v>1.677514627506292</v>
+      </c>
+      <c r="K723">
         <v>4.04</v>
       </c>
-      <c r="N719">
+      <c r="L723">
         <v>5.35</v>
       </c>
-      <c r="O719">
-        <v>1</v>
-      </c>
-      <c r="P719" t="s">
-        <v>359</v>
+      <c r="M723">
+        <v>3.88</v>
+      </c>
+      <c r="N723">
+        <v>5.27</v>
+      </c>
+      <c r="O723">
+        <v>1</v>
+      </c>
+      <c r="P723" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="724" spans="1:16">
+      <c r="A724" s="1">
+        <v>0</v>
+      </c>
+      <c r="B724" t="s">
+        <v>149</v>
+      </c>
+      <c r="C724">
+        <v>-1.46853878015609</v>
+      </c>
+      <c r="D724" t="s">
+        <v>146</v>
+      </c>
+      <c r="E724">
+        <v>-1.278497640347928</v>
+      </c>
+      <c r="F724">
+        <v>1</v>
+      </c>
+      <c r="G724">
+        <v>0.01216853878015609</v>
+      </c>
+      <c r="H724">
+        <v>0.01181849764034793</v>
+      </c>
+      <c r="I724">
+        <v>0.1900411398081614</v>
+      </c>
+      <c r="J724">
+        <v>1.687757123801012</v>
+      </c>
+      <c r="K724">
+        <v>4.04</v>
+      </c>
+      <c r="L724">
+        <v>5.35</v>
+      </c>
+      <c r="M724">
+        <v>3.88</v>
+      </c>
+      <c r="N724">
+        <v>5.27</v>
+      </c>
+      <c r="O724">
+        <v>1</v>
+      </c>
+      <c r="P724" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="725" spans="1:16">
+      <c r="A725" s="1">
+        <v>0</v>
+      </c>
+      <c r="B725" t="s">
+        <v>149</v>
+      </c>
+      <c r="C725">
+        <v>-1.516702985935216</v>
+      </c>
+      <c r="D725" t="s">
+        <v>146</v>
+      </c>
+      <c r="E725">
+        <v>-1.324754352828871</v>
+      </c>
+      <c r="F725">
+        <v>1</v>
+      </c>
+      <c r="G725">
+        <v>0.01221670298593521</v>
+      </c>
+      <c r="H725">
+        <v>0.01186475435282887</v>
+      </c>
+      <c r="I725">
+        <v>0.1919486331063451</v>
+      </c>
+      <c r="J725">
+        <v>1.699678956914657</v>
+      </c>
+      <c r="K725">
+        <v>4.04</v>
+      </c>
+      <c r="L725">
+        <v>5.35</v>
+      </c>
+      <c r="M725">
+        <v>3.88</v>
+      </c>
+      <c r="N725">
+        <v>5.27</v>
+      </c>
+      <c r="O725">
+        <v>1</v>
+      </c>
+      <c r="P725" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -460,7 +460,7 @@
     <t>2021-11-16</t>
   </si>
   <si>
-    <t>2021-11-18</t>
+    <t>2021-11-29</t>
   </si>
   <si>
     <t>2021-11-25</t>
@@ -769,7 +769,7 @@
     <t>2021-08-09</t>
   </si>
   <si>
-    <t>2021-11-29</t>
+    <t>2021-11-30</t>
   </si>
   <si>
     <t>2021-11-22</t>
@@ -1081,12 +1081,6 @@
     <t>2021-11-08</t>
   </si>
   <si>
-    <t>2021-11-09</t>
-  </si>
-  <si>
-    <t>2021-11-10</t>
-  </si>
-  <si>
     <t>2021-11-11</t>
   </si>
   <si>
@@ -1094,6 +1088,12 @@
   </si>
   <si>
     <t>2021-11-17</t>
+  </si>
+  <si>
+    <t>2021-11-18</t>
+  </si>
+  <si>
+    <t>2021-11-19</t>
   </si>
   <si>
     <t>2021-11-23</t>
@@ -36368,7 +36368,7 @@
         <v>251</v>
       </c>
       <c r="E699">
-        <v>-0.4468731812388809</v>
+        <v>-0.5418484958276091</v>
       </c>
       <c r="F699">
         <v>-1</v>
@@ -36377,10 +36377,10 @@
         <v>0.0113967086118304</v>
       </c>
       <c r="H699">
-        <v>0.01094687318123888</v>
+        <v>0.01094184849582761</v>
       </c>
       <c r="I699">
-        <v>-0.1498354305915202</v>
+        <v>-0.05486011600279195</v>
       </c>
       <c r="J699">
         <v>1.4991771529576</v>
@@ -36392,10 +36392,10 @@
         <v>5.4</v>
       </c>
       <c r="M699">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N699">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O699">
         <v>1</v>
@@ -36418,7 +36418,7 @@
         <v>251</v>
       </c>
       <c r="E700">
-        <v>-0.4468731812388809</v>
+        <v>-0.5418484958276091</v>
       </c>
       <c r="F700">
         <v>-1</v>
@@ -36427,10 +36427,10 @@
         <v>0.01108680735347549</v>
       </c>
       <c r="H700">
-        <v>0.01094687318123888</v>
+        <v>0.01094184849582761</v>
       </c>
       <c r="I700">
-        <v>-0.09993417223660916</v>
+        <v>-0.004958857647880954</v>
       </c>
       <c r="J700">
         <v>1.4991771529576</v>
@@ -36442,10 +36442,10 @@
         <v>5.27</v>
       </c>
       <c r="M700">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N700">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O700">
         <v>1</v>
@@ -36518,7 +36518,7 @@
         <v>251</v>
       </c>
       <c r="E702">
-        <v>-0.4717132546364855</v>
+        <v>-0.5668846750678265</v>
       </c>
       <c r="F702">
         <v>-1</v>
@@ -36527,10 +36527,10 @@
         <v>0.01142285605751209</v>
       </c>
       <c r="H702">
-        <v>0.01097171325463649</v>
+        <v>0.01096688467506783</v>
       </c>
       <c r="I702">
-        <v>-0.1511428028756043</v>
+        <v>-0.05597138244426336</v>
       </c>
       <c r="J702">
         <v>1.505714014378023</v>
@@ -36542,10 +36542,10 @@
         <v>5.4</v>
       </c>
       <c r="M702">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N702">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O702">
         <v>1</v>
@@ -36568,7 +36568,7 @@
         <v>251</v>
       </c>
       <c r="E703">
-        <v>-0.4717132546364855</v>
+        <v>-0.5668846750678265</v>
       </c>
       <c r="F703">
         <v>-1</v>
@@ -36577,10 +36577,10 @@
         <v>0.01111217037578673</v>
       </c>
       <c r="H703">
-        <v>0.01097171325463649</v>
+        <v>0.01096688467506783</v>
       </c>
       <c r="I703">
-        <v>-0.1004571211502423</v>
+        <v>-0.005285700718901332</v>
       </c>
       <c r="J703">
         <v>1.505714014378023</v>
@@ -36592,10 +36592,10 @@
         <v>5.27</v>
       </c>
       <c r="M703">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N703">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O703">
         <v>1</v>
@@ -36659,43 +36659,43 @@
         <v>1</v>
       </c>
       <c r="B705" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C705">
-        <v>-0.6555683652294215</v>
+        <v>-0.6039013142725391</v>
       </c>
       <c r="D705" t="s">
         <v>251</v>
       </c>
       <c r="E705">
-        <v>-0.5027899469679502</v>
+        <v>-0.5982067097071715</v>
       </c>
       <c r="F705">
         <v>-1</v>
       </c>
       <c r="G705">
-        <v>0.01145556836522942</v>
+        <v>0.01114390131427254</v>
       </c>
       <c r="H705">
-        <v>0.01100278994696795</v>
+        <v>0.01099820670970717</v>
       </c>
       <c r="I705">
-        <v>-0.1527784182614713</v>
+        <v>-0.005694604565367634</v>
       </c>
       <c r="J705">
         <v>1.513892091307355</v>
       </c>
       <c r="K705">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="L705">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="M705">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N705">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O705">
         <v>1</v>
@@ -36706,96 +36706,96 @@
     </row>
     <row r="706" spans="1:16">
       <c r="A706" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B706" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C706">
-        <v>-0.6039013142725391</v>
+        <v>-0.9337099119674415</v>
       </c>
       <c r="D706" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E706">
-        <v>-0.5027899469679502</v>
+        <v>-0.7528294165632978</v>
       </c>
       <c r="F706">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G706">
-        <v>0.01114390131427254</v>
+        <v>0.01133370991196744</v>
       </c>
       <c r="H706">
-        <v>0.01100278994696795</v>
+        <v>0.0113928294165633</v>
       </c>
       <c r="I706">
-        <v>-0.1011113673045889</v>
+        <v>0.1808804954041436</v>
       </c>
       <c r="J706">
-        <v>1.513892091307355</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K706">
-        <v>3.88</v>
+        <v>4.03</v>
       </c>
       <c r="L706">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="M706">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="N706">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="O706">
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="707" spans="1:16">
       <c r="A707" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B707" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C707">
-        <v>-0.9337099119674415</v>
+        <v>-0.6354080542019034</v>
       </c>
       <c r="D707" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E707">
-        <v>-0.7528294165632978</v>
+        <v>-0.6293074349467247</v>
       </c>
       <c r="F707">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G707">
-        <v>0.01133370991196744</v>
+        <v>0.0111754080542019</v>
       </c>
       <c r="H707">
-        <v>0.0113928294165633</v>
+        <v>0.01102930743494672</v>
       </c>
       <c r="I707">
-        <v>0.1808804954041436</v>
+        <v>-0.006100619255178685</v>
       </c>
       <c r="J707">
         <v>1.522012385103583</v>
       </c>
       <c r="K707">
-        <v>4.03</v>
+        <v>3.88</v>
       </c>
       <c r="L707">
+        <v>5.27</v>
+      </c>
+      <c r="M707">
+        <v>3.83</v>
+      </c>
+      <c r="N707">
         <v>5.2</v>
-      </c>
-      <c r="M707">
-        <v>3.99</v>
-      </c>
-      <c r="N707">
-        <v>5.32</v>
       </c>
       <c r="O707">
         <v>1</v>
@@ -36806,84 +36806,84 @@
     </row>
     <row r="708" spans="1:16">
       <c r="A708" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B708" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C708">
-        <v>-0.6880495404143332</v>
+        <v>-0.9649665355493404</v>
       </c>
       <c r="D708" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E708">
-        <v>-0.5336470633936168</v>
+        <v>-0.783775800705178</v>
       </c>
       <c r="F708">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G708">
-        <v>0.01148804954041433</v>
+        <v>0.01136496653554934</v>
       </c>
       <c r="H708">
-        <v>0.01103364706339362</v>
+        <v>0.01142377580070518</v>
       </c>
       <c r="I708">
-        <v>-0.1544024770207164</v>
+        <v>0.1811907348441624</v>
       </c>
       <c r="J708">
-        <v>1.522012385103583</v>
+        <v>1.529768371104055</v>
       </c>
       <c r="K708">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="L708">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M708">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="N708">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="O708">
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="709" spans="1:16">
       <c r="A709" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B709" t="s">
         <v>146</v>
       </c>
       <c r="C709">
-        <v>-0.6354080542019034</v>
+        <v>-0.6655012798837321</v>
       </c>
       <c r="D709" t="s">
         <v>251</v>
       </c>
       <c r="E709">
-        <v>-0.5336470633936168</v>
+        <v>-0.6590128613285291</v>
       </c>
       <c r="F709">
         <v>-1</v>
       </c>
       <c r="G709">
-        <v>0.0111754080542019</v>
+        <v>0.01120550127988373</v>
       </c>
       <c r="H709">
-        <v>0.01103364706339362</v>
+        <v>0.01105901286132853</v>
       </c>
       <c r="I709">
-        <v>-0.1017609908082866</v>
+        <v>-0.00648841855520299</v>
       </c>
       <c r="J709">
-        <v>1.522012385103583</v>
+        <v>1.529768371104055</v>
       </c>
       <c r="K709">
         <v>3.88</v>
@@ -36892,16 +36892,16 @@
         <v>5.27</v>
       </c>
       <c r="M709">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N709">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O709">
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36912,28 +36912,28 @@
         <v>147</v>
       </c>
       <c r="C710">
-        <v>-0.9649665355493404</v>
+        <v>-0.9919728003746338</v>
       </c>
       <c r="D710" t="s">
         <v>252</v>
       </c>
       <c r="E710">
-        <v>-0.783775800705178</v>
+        <v>-0.8105140132741413</v>
       </c>
       <c r="F710">
         <v>1</v>
       </c>
       <c r="G710">
-        <v>0.01136496653554934</v>
+        <v>0.01139197280037463</v>
       </c>
       <c r="H710">
-        <v>0.01142377580070518</v>
+        <v>0.01145051401327414</v>
       </c>
       <c r="I710">
-        <v>0.1811907348441624</v>
+        <v>0.1814587871004925</v>
       </c>
       <c r="J710">
-        <v>1.529768371104055</v>
+        <v>1.536469677512316</v>
       </c>
       <c r="K710">
         <v>4.03</v>
@@ -36951,7 +36951,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -36959,99 +36959,99 @@
         <v>1</v>
       </c>
       <c r="B711" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C711">
-        <v>-0.7190734844162181</v>
+        <v>-0.6915023487477869</v>
       </c>
       <c r="D711" t="s">
         <v>251</v>
       </c>
       <c r="E711">
-        <v>-0.5631198101954071</v>
+        <v>-0.6846788648721702</v>
       </c>
       <c r="F711">
         <v>-1</v>
       </c>
       <c r="G711">
-        <v>0.01151907348441622</v>
+        <v>0.01123150234874778</v>
       </c>
       <c r="H711">
-        <v>0.01106311981019541</v>
+        <v>0.01108467886487217</v>
       </c>
       <c r="I711">
-        <v>-0.155953674220811</v>
+        <v>-0.006823483875616709</v>
       </c>
       <c r="J711">
-        <v>1.529768371104055</v>
+        <v>1.536469677512316</v>
       </c>
       <c r="K711">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="L711">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="M711">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N711">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O711">
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="712" spans="1:16">
       <c r="A712" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B712" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C712">
-        <v>-0.6655012798837321</v>
+        <v>-1.030819877903268</v>
       </c>
       <c r="D712" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E712">
-        <v>-0.5631198101954071</v>
+        <v>-0.8489755118694884</v>
       </c>
       <c r="F712">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G712">
-        <v>0.01120550127988373</v>
+        <v>0.01143081987790327</v>
       </c>
       <c r="H712">
-        <v>0.01106311981019541</v>
+        <v>0.01148897551186949</v>
       </c>
       <c r="I712">
-        <v>-0.102381469688325</v>
+        <v>0.1818443660337792</v>
       </c>
       <c r="J712">
-        <v>1.529768371104055</v>
+        <v>1.546109150844483</v>
       </c>
       <c r="K712">
-        <v>3.88</v>
+        <v>4.03</v>
       </c>
       <c r="L712">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="M712">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="N712">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="O712">
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37059,81 +37059,81 @@
         <v>0</v>
       </c>
       <c r="B713" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C713">
-        <v>-0.7458787100492641</v>
+        <v>-1.064082889548082</v>
       </c>
       <c r="D713" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E713">
-        <v>-0.5885847745468009</v>
+        <v>-0.8819083695525682</v>
       </c>
       <c r="F713">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G713">
-        <v>0.01154587871004927</v>
+        <v>0.01146408288954808</v>
       </c>
       <c r="H713">
-        <v>0.0110885847745468</v>
+        <v>0.01152190836955257</v>
       </c>
       <c r="I713">
-        <v>-0.1572939355024632</v>
+        <v>0.182174519995514</v>
       </c>
       <c r="J713">
-        <v>1.536469677512316</v>
+        <v>1.554362999887862</v>
       </c>
       <c r="K713">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="L713">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M713">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="N713">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="O713">
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="714" spans="1:16">
       <c r="A714" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B714" t="s">
         <v>146</v>
       </c>
       <c r="C714">
-        <v>-0.6915023487477869</v>
+        <v>-0.8864878881367728</v>
       </c>
       <c r="D714" t="s">
         <v>251</v>
       </c>
       <c r="E714">
-        <v>-0.5885847745468009</v>
+        <v>-0.8771517040112986</v>
       </c>
       <c r="F714">
         <v>-1</v>
       </c>
       <c r="G714">
-        <v>0.01123150234874778</v>
+        <v>0.01142648788813677</v>
       </c>
       <c r="H714">
-        <v>0.0110885847745468</v>
+        <v>0.0112771517040113</v>
       </c>
       <c r="I714">
-        <v>-0.102917574200986</v>
+        <v>-0.009336184125474212</v>
       </c>
       <c r="J714">
-        <v>1.536469677512316</v>
+        <v>1.586723682509477</v>
       </c>
       <c r="K714">
         <v>3.88</v>
@@ -37142,16 +37142,16 @@
         <v>5.27</v>
       </c>
       <c r="M714">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N714">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O714">
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37162,28 +37162,28 @@
         <v>147</v>
       </c>
       <c r="C715">
-        <v>-1.030819877903268</v>
+        <v>-1.252492276288939</v>
       </c>
       <c r="D715" t="s">
         <v>252</v>
       </c>
       <c r="E715">
-        <v>-0.8489755118694884</v>
+        <v>-1.068447687938677</v>
       </c>
       <c r="F715">
         <v>1</v>
       </c>
       <c r="G715">
-        <v>0.01143081987790327</v>
+        <v>0.01165249227628894</v>
       </c>
       <c r="H715">
-        <v>0.01148897551186949</v>
+        <v>0.01170844768793868</v>
       </c>
       <c r="I715">
-        <v>0.1818443660337792</v>
+        <v>0.1840445883502619</v>
       </c>
       <c r="J715">
-        <v>1.546109150844483</v>
+        <v>1.60111470875656</v>
       </c>
       <c r="K715">
         <v>4.03</v>
@@ -37201,57 +37201,57 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="716" spans="1:16">
       <c r="A716" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B716" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C716">
-        <v>-0.7289035052765955</v>
+        <v>-0.9728832466399586</v>
       </c>
       <c r="D716" t="s">
         <v>251</v>
       </c>
       <c r="E716">
-        <v>-0.6252147732090361</v>
+        <v>-1.072011272271327</v>
       </c>
       <c r="F716">
         <v>-1</v>
       </c>
       <c r="G716">
-        <v>0.01126890350527659</v>
+        <v>0.01147288324663996</v>
       </c>
       <c r="H716">
-        <v>0.01112521477320904</v>
+        <v>0.01147201127227133</v>
       </c>
       <c r="I716">
-        <v>-0.1036887320675595</v>
+        <v>0.09912802563136847</v>
       </c>
       <c r="J716">
-        <v>1.546109150844483</v>
+        <v>1.637600854378937</v>
       </c>
       <c r="K716">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="L716">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="M716">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N716">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O716">
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37259,49 +37259,49 @@
         <v>0</v>
       </c>
       <c r="B717" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C717">
-        <v>-0.7609284395649034</v>
+        <v>-1.024362108384423</v>
       </c>
       <c r="D717" t="s">
         <v>251</v>
       </c>
       <c r="E717">
-        <v>-0.6565793995738742</v>
+        <v>-1.123896546082196</v>
       </c>
       <c r="F717">
         <v>-1</v>
       </c>
       <c r="G717">
-        <v>0.0113009284395649</v>
+        <v>0.01152436210838442</v>
       </c>
       <c r="H717">
-        <v>0.01115657939957388</v>
+        <v>0.0115238965460822</v>
       </c>
       <c r="I717">
-        <v>-0.1043490399910292</v>
+        <v>0.09953443769777248</v>
       </c>
       <c r="J717">
-        <v>1.554362999887862</v>
+        <v>1.651147923259059</v>
       </c>
       <c r="K717">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="L717">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="M717">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N717">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O717">
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37309,49 +37309,49 @@
         <v>0</v>
       </c>
       <c r="B718" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C718">
-        <v>-0.7986197051614914</v>
+        <v>-1.080459465484273</v>
       </c>
       <c r="D718" t="s">
         <v>251</v>
       </c>
       <c r="E718">
-        <v>-0.6934935256736248</v>
+        <v>-1.180436777053885</v>
       </c>
       <c r="F718">
         <v>-1</v>
       </c>
       <c r="G718">
-        <v>0.01133861970516149</v>
+        <v>0.01158045946548427</v>
       </c>
       <c r="H718">
-        <v>0.01119349352567362</v>
+        <v>0.01158043677705389</v>
       </c>
       <c r="I718">
-        <v>-0.1051261794878666</v>
+        <v>0.09997731156961276</v>
       </c>
       <c r="J718">
-        <v>1.564077243598322</v>
+        <v>1.665910385653756</v>
       </c>
       <c r="K718">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="L718">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="M718">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N718">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O718">
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37359,99 +37359,99 @@
         <v>0</v>
       </c>
       <c r="B719" t="s">
+        <v>149</v>
+      </c>
+      <c r="C719">
+        <v>-1.42715909512542</v>
+      </c>
+      <c r="D719" t="s">
         <v>146</v>
       </c>
-      <c r="C719">
-        <v>-0.8428089064414896</v>
-      </c>
-      <c r="D719" t="s">
-        <v>251</v>
-      </c>
       <c r="E719">
-        <v>-0.7367716094014582</v>
+        <v>-1.238756754724413</v>
       </c>
       <c r="F719">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G719">
-        <v>0.01138280890644149</v>
+        <v>0.01212715909512542</v>
       </c>
       <c r="H719">
-        <v>0.01123677160940146</v>
+        <v>0.01177875675472441</v>
       </c>
       <c r="I719">
-        <v>-0.1060372970400314</v>
+        <v>0.1884023404010069</v>
       </c>
       <c r="J719">
-        <v>1.575466213000384</v>
+        <v>1.677514627506292</v>
       </c>
       <c r="K719">
+        <v>4.04</v>
+      </c>
+      <c r="L719">
+        <v>5.35</v>
+      </c>
+      <c r="M719">
         <v>3.88</v>
       </c>
-      <c r="L719">
+      <c r="N719">
         <v>5.27</v>
       </c>
-      <c r="M719">
-        <v>3.8</v>
-      </c>
-      <c r="N719">
-        <v>5.25</v>
-      </c>
       <c r="O719">
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>356</v>
+        <v>252</v>
       </c>
     </row>
     <row r="720" spans="1:16">
       <c r="A720" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B720" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C720">
-        <v>-0.8864878881367728</v>
+        <v>-1.124555584523909</v>
       </c>
       <c r="D720" t="s">
         <v>251</v>
       </c>
       <c r="E720">
-        <v>-0.7795499935360137</v>
+        <v>-1.224881023349099</v>
       </c>
       <c r="F720">
         <v>-1</v>
       </c>
       <c r="G720">
-        <v>0.01142648788813677</v>
+        <v>0.01162455558452391</v>
       </c>
       <c r="H720">
-        <v>0.01127954999353601</v>
+        <v>0.0116248810233491</v>
       </c>
       <c r="I720">
-        <v>-0.1069378946007591</v>
+        <v>0.1003254388251893</v>
       </c>
       <c r="J720">
-        <v>1.586723682509477</v>
+        <v>1.677514627506292</v>
       </c>
       <c r="K720">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="L720">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="M720">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N720">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O720">
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>357</v>
+        <v>252</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37459,99 +37459,99 @@
         <v>0</v>
       </c>
       <c r="B721" t="s">
+        <v>149</v>
+      </c>
+      <c r="C721">
+        <v>-1.46853878015609</v>
+      </c>
+      <c r="D721" t="s">
         <v>146</v>
       </c>
-      <c r="C721">
-        <v>-0.9423250699754551</v>
-      </c>
-      <c r="D721" t="s">
-        <v>251</v>
-      </c>
       <c r="E721">
-        <v>-0.8342358932749292</v>
+        <v>-1.278497640347928</v>
       </c>
       <c r="F721">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G721">
-        <v>0.01148232506997545</v>
+        <v>0.01216853878015609</v>
       </c>
       <c r="H721">
-        <v>0.01133423589327493</v>
+        <v>0.01181849764034793</v>
       </c>
       <c r="I721">
-        <v>-0.1080891767005259</v>
+        <v>0.1900411398081614</v>
       </c>
       <c r="J721">
-        <v>1.60111470875656</v>
+        <v>1.687757123801012</v>
       </c>
       <c r="K721">
+        <v>4.04</v>
+      </c>
+      <c r="L721">
+        <v>5.35</v>
+      </c>
+      <c r="M721">
         <v>3.88</v>
       </c>
-      <c r="L721">
+      <c r="N721">
         <v>5.27</v>
       </c>
-      <c r="M721">
-        <v>3.8</v>
-      </c>
-      <c r="N721">
-        <v>5.25</v>
-      </c>
       <c r="O721">
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="722" spans="1:16">
       <c r="A722" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B722" t="s">
         <v>148</v>
       </c>
       <c r="C722">
-        <v>-1.330403417515747</v>
+        <v>-1.163477070443847</v>
       </c>
       <c r="D722" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="E722">
-        <v>-1.150403417515746</v>
+        <v>-1.264109784157877</v>
       </c>
       <c r="F722">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G722">
-        <v>0.01177040341751575</v>
+        <v>0.01166347707044385</v>
       </c>
       <c r="H722">
-        <v>0.01195040341751575</v>
+        <v>0.01166410978415788</v>
       </c>
       <c r="I722">
-        <v>0.1800000000000006</v>
+        <v>0.1006327137140302</v>
       </c>
       <c r="J722">
-        <v>1.637600854378937</v>
+        <v>1.687757123801012</v>
       </c>
       <c r="K722">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L722">
-        <v>5.22</v>
+        <v>5.25</v>
       </c>
       <c r="M722">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="N722">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="O722">
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37562,28 +37562,28 @@
         <v>149</v>
       </c>
       <c r="C723">
-        <v>-1.42715909512542</v>
+        <v>-1.516702985935216</v>
       </c>
       <c r="D723" t="s">
         <v>146</v>
       </c>
       <c r="E723">
-        <v>-1.238756754724413</v>
+        <v>-1.324754352828871</v>
       </c>
       <c r="F723">
         <v>1</v>
       </c>
       <c r="G723">
-        <v>0.01212715909512542</v>
+        <v>0.01221670298593521</v>
       </c>
       <c r="H723">
-        <v>0.01177875675472441</v>
+        <v>0.01186475435282887</v>
       </c>
       <c r="I723">
-        <v>0.1884023404010069</v>
+        <v>0.1919486331063451</v>
       </c>
       <c r="J723">
-        <v>1.677514627506292</v>
+        <v>1.699678956914657</v>
       </c>
       <c r="K723">
         <v>4.04</v>
@@ -37601,57 +37601,57 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>252</v>
+        <v>145</v>
       </c>
     </row>
     <row r="724" spans="1:16">
       <c r="A724" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B724" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C724">
-        <v>-1.46853878015609</v>
+        <v>-1.208780036275697</v>
       </c>
       <c r="D724" t="s">
-        <v>146</v>
+        <v>251</v>
       </c>
       <c r="E724">
-        <v>-1.278497640347928</v>
+        <v>-1.309770404983137</v>
       </c>
       <c r="F724">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G724">
-        <v>0.01216853878015609</v>
+        <v>0.0117087800362757</v>
       </c>
       <c r="H724">
-        <v>0.01181849764034793</v>
+        <v>0.01170977040498314</v>
       </c>
       <c r="I724">
-        <v>0.1900411398081614</v>
+        <v>0.10099036870744</v>
       </c>
       <c r="J724">
-        <v>1.687757123801012</v>
+        <v>1.699678956914657</v>
       </c>
       <c r="K724">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="L724">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="M724">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="N724">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="O724">
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>360</v>
+        <v>145</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -37659,49 +37659,49 @@
         <v>0</v>
       </c>
       <c r="B725" t="s">
+        <v>148</v>
+      </c>
+      <c r="C725">
+        <v>-1.213102463254955</v>
+      </c>
+      <c r="D725" t="s">
+        <v>251</v>
+      </c>
+      <c r="E725">
+        <v>-1.314126956385915</v>
+      </c>
+      <c r="F725">
+        <v>-1</v>
+      </c>
+      <c r="G725">
+        <v>0.01171310246325496</v>
+      </c>
+      <c r="H725">
+        <v>0.01171412695638591</v>
+      </c>
+      <c r="I725">
+        <v>0.1010244931309607</v>
+      </c>
+      <c r="J725">
+        <v>1.700816437698672</v>
+      </c>
+      <c r="K725">
+        <v>3.8</v>
+      </c>
+      <c r="L725">
+        <v>5.25</v>
+      </c>
+      <c r="M725">
+        <v>3.83</v>
+      </c>
+      <c r="N725">
+        <v>5.2</v>
+      </c>
+      <c r="O725">
+        <v>1</v>
+      </c>
+      <c r="P725" t="s">
         <v>149</v>
-      </c>
-      <c r="C725">
-        <v>-1.516702985935216</v>
-      </c>
-      <c r="D725" t="s">
-        <v>146</v>
-      </c>
-      <c r="E725">
-        <v>-1.324754352828871</v>
-      </c>
-      <c r="F725">
-        <v>1</v>
-      </c>
-      <c r="G725">
-        <v>0.01221670298593521</v>
-      </c>
-      <c r="H725">
-        <v>0.01186475435282887</v>
-      </c>
-      <c r="I725">
-        <v>0.1919486331063451</v>
-      </c>
-      <c r="J725">
-        <v>1.699678956914657</v>
-      </c>
-      <c r="K725">
-        <v>4.04</v>
-      </c>
-      <c r="L725">
-        <v>5.35</v>
-      </c>
-      <c r="M725">
-        <v>3.88</v>
-      </c>
-      <c r="N725">
-        <v>5.27</v>
-      </c>
-      <c r="O725">
-        <v>1</v>
-      </c>
-      <c r="P725" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="362">
   <si>
     <t>trade_time</t>
   </si>
@@ -451,9 +451,6 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-11-24</t>
-  </si>
-  <si>
     <t>2021-11-26</t>
   </si>
   <si>
@@ -461,6 +458,9 @@
   </si>
   <si>
     <t>2021-11-29</t>
+  </si>
+  <si>
+    <t>2021-11-18</t>
   </si>
   <si>
     <t>2021-11-25</t>
@@ -769,10 +769,13 @@
     <t>2021-08-09</t>
   </si>
   <si>
-    <t>2021-11-30</t>
+    <t>2021-12-01</t>
   </si>
   <si>
     <t>2021-11-22</t>
+  </si>
+  <si>
+    <t>2021-11-24</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -1075,22 +1078,22 @@
     <t>2021-11-04</t>
   </si>
   <si>
-    <t>2021-11-05</t>
-  </si>
-  <si>
     <t>2021-11-08</t>
   </si>
   <si>
-    <t>2021-11-11</t>
+    <t>2021-11-09</t>
+  </si>
+  <si>
+    <t>2021-11-10</t>
   </si>
   <si>
     <t>2021-11-12</t>
   </si>
   <si>
-    <t>2021-11-17</t>
+    <t>2021-11-15</t>
   </si>
   <si>
-    <t>2021-11-18</t>
+    <t>2021-11-17</t>
   </si>
   <si>
     <t>2021-11-19</t>
@@ -1454,7 +1457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P725"/>
+  <dimension ref="A1:P723"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1551,7 +1554,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1601,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1651,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1701,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1751,7 +1754,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1801,7 +1804,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1851,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1901,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1951,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2001,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2051,7 +2054,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2101,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2151,7 +2154,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2201,7 +2204,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2251,7 +2254,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2301,7 +2304,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2351,7 +2354,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2401,7 +2404,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2451,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2501,7 +2504,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2551,7 +2554,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2601,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2651,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2701,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2751,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2801,7 +2804,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2851,7 +2854,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2901,7 +2904,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2951,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3001,7 +3004,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3051,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3101,7 +3104,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3151,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3201,7 +3204,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3251,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3301,7 +3304,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3351,7 +3354,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3401,7 +3404,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3451,7 +3454,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3501,7 +3504,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3551,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3601,7 +3604,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3651,7 +3654,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3701,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3751,7 +3754,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4801,7 +4804,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4851,7 +4854,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4901,7 +4904,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4951,7 +4954,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5001,7 +5004,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5051,7 +5054,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5101,7 +5104,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5151,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5201,7 +5204,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5251,7 +5254,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5301,7 +5304,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5351,7 +5354,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5401,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5451,7 +5454,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5501,7 +5504,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5551,7 +5554,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5601,7 +5604,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5651,7 +5654,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5701,7 +5704,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5751,7 +5754,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5801,7 +5804,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5851,7 +5854,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5901,7 +5904,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5951,7 +5954,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6001,7 +6004,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6051,7 +6054,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6351,7 +6354,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6401,7 +6404,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6451,7 +6454,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6501,7 +6504,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6551,7 +6554,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6601,7 +6604,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6651,7 +6654,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6701,7 +6704,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6751,7 +6754,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6801,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6851,7 +6854,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6901,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6951,7 +6954,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7301,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7351,7 +7354,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7401,7 +7404,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7451,7 +7454,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7501,7 +7504,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7551,7 +7554,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7601,7 +7604,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7651,7 +7654,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7701,7 +7704,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7751,7 +7754,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7801,7 +7804,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7851,7 +7854,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7901,7 +7904,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8751,7 +8754,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8801,7 +8804,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8851,7 +8854,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8901,7 +8904,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8951,7 +8954,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9001,7 +9004,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9151,7 +9154,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9201,7 +9204,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9251,7 +9254,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9301,7 +9304,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9351,7 +9354,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9401,7 +9404,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9451,7 +9454,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9501,7 +9504,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9551,7 +9554,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9601,7 +9604,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9651,7 +9654,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9701,7 +9704,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10051,7 +10054,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10101,7 +10104,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10251,7 +10254,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10301,7 +10304,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10351,7 +10354,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10401,7 +10404,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10451,7 +10454,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10501,7 +10504,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10551,7 +10554,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10601,7 +10604,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10651,7 +10654,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10701,7 +10704,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10751,7 +10754,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10801,7 +10804,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10851,7 +10854,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10901,7 +10904,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10951,7 +10954,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11001,7 +11004,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11051,7 +11054,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11101,7 +11104,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11151,7 +11154,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11201,7 +11204,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11251,7 +11254,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11301,7 +11304,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11351,7 +11354,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11401,7 +11404,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11451,7 +11454,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11501,7 +11504,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11551,7 +11554,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11601,7 +11604,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11651,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11701,7 +11704,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11751,7 +11754,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11801,7 +11804,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11851,7 +11854,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11901,7 +11904,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11951,7 +11954,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12001,7 +12004,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12051,7 +12054,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12101,7 +12104,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12151,7 +12154,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12201,7 +12204,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12251,7 +12254,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12301,7 +12304,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12351,7 +12354,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12401,7 +12404,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12451,7 +12454,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12501,7 +12504,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12551,7 +12554,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12601,7 +12604,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12901,7 +12904,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12951,7 +12954,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13001,7 +13004,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13051,7 +13054,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13101,7 +13104,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13151,7 +13154,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13201,7 +13204,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13551,7 +13554,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13601,7 +13604,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13651,7 +13654,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13701,7 +13704,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13751,7 +13754,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13801,7 +13804,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13851,7 +13854,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13901,7 +13904,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13951,7 +13954,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14001,7 +14004,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14051,7 +14054,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14101,7 +14104,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14151,7 +14154,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14201,7 +14204,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14251,7 +14254,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14301,7 +14304,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14351,7 +14354,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14401,7 +14404,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14701,7 +14704,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14751,7 +14754,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14801,7 +14804,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14851,7 +14854,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14901,7 +14904,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14951,7 +14954,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15001,7 +15004,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15051,7 +15054,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15101,7 +15104,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15151,7 +15154,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15201,7 +15204,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15251,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15301,7 +15304,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15351,7 +15354,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15401,7 +15404,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15451,7 +15454,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15501,7 +15504,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15551,7 +15554,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15601,7 +15604,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15651,7 +15654,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15701,7 +15704,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15751,7 +15754,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15801,7 +15804,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15851,7 +15854,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15901,7 +15904,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -15951,7 +15954,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16001,7 +16004,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16051,7 +16054,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16101,7 +16104,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16151,7 +16154,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16201,7 +16204,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16251,7 +16254,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16301,7 +16304,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16351,7 +16354,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16401,7 +16404,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16451,7 +16454,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16501,7 +16504,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16551,7 +16554,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16601,7 +16604,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16651,7 +16654,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16701,7 +16704,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16751,7 +16754,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16801,7 +16804,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16851,7 +16854,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16901,7 +16904,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16951,7 +16954,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17001,7 +17004,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17051,7 +17054,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17101,7 +17104,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17151,7 +17154,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17201,7 +17204,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17251,7 +17254,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17301,7 +17304,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17351,7 +17354,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17401,7 +17404,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17451,7 +17454,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17501,7 +17504,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17551,7 +17554,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17601,7 +17604,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17651,7 +17654,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17701,7 +17704,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17751,7 +17754,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17801,7 +17804,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17851,7 +17854,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17901,7 +17904,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17951,7 +17954,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18001,7 +18004,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18051,7 +18054,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18101,7 +18104,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18151,7 +18154,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18201,7 +18204,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18251,7 +18254,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18301,7 +18304,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18351,7 +18354,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18401,7 +18404,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18451,7 +18454,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18501,7 +18504,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18551,7 +18554,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18751,7 +18754,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18801,7 +18804,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18851,7 +18854,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18901,7 +18904,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -18951,7 +18954,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19001,7 +19004,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19251,7 +19254,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19301,7 +19304,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19351,7 +19354,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19401,7 +19404,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19651,7 +19654,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19701,7 +19704,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19751,7 +19754,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19801,7 +19804,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19851,7 +19854,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19901,7 +19904,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19951,7 +19954,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20001,7 +20004,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20051,7 +20054,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20101,7 +20104,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20151,7 +20154,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20201,7 +20204,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20251,7 +20254,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20301,7 +20304,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20751,7 +20754,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20801,7 +20804,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20851,7 +20854,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20901,7 +20904,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20951,7 +20954,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21001,7 +21004,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21051,7 +21054,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21101,7 +21104,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21151,7 +21154,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21201,7 +21204,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21251,7 +21254,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21301,7 +21304,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21351,7 +21354,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21401,7 +21404,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21451,7 +21454,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21501,7 +21504,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21551,7 +21554,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21601,7 +21604,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21651,7 +21654,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21701,7 +21704,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21751,7 +21754,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22101,7 +22104,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22151,7 +22154,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22201,7 +22204,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22251,7 +22254,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22301,7 +22304,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22351,7 +22354,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22401,7 +22404,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22451,7 +22454,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22501,7 +22504,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22551,7 +22554,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22601,7 +22604,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22651,7 +22654,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23451,7 +23454,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23501,7 +23504,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23551,7 +23554,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23601,7 +23604,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23651,7 +23654,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23701,7 +23704,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23751,7 +23754,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23801,7 +23804,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23851,7 +23854,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -23901,7 +23904,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -23951,7 +23954,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24001,7 +24004,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24051,7 +24054,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24101,7 +24104,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24151,7 +24154,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24201,7 +24204,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24251,7 +24254,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24301,7 +24304,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24351,7 +24354,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24401,7 +24404,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24451,7 +24454,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24501,7 +24504,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24551,7 +24554,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24601,7 +24604,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24651,7 +24654,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24701,7 +24704,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24751,7 +24754,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24801,7 +24804,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24851,7 +24854,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -24901,7 +24904,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -24951,7 +24954,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25001,7 +25004,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25051,7 +25054,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25201,7 +25204,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25251,7 +25254,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25301,7 +25304,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25351,7 +25354,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25401,7 +25404,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25451,7 +25454,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25501,7 +25504,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25551,7 +25554,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25601,7 +25604,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25651,7 +25654,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25701,7 +25704,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25901,7 +25904,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25951,7 +25954,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26001,7 +26004,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26051,7 +26054,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26101,7 +26104,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26151,7 +26154,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26201,7 +26204,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26251,7 +26254,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26301,7 +26304,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26351,7 +26354,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26401,7 +26404,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26451,7 +26454,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26501,7 +26504,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26551,7 +26554,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26601,7 +26604,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26651,7 +26654,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26701,7 +26704,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26751,7 +26754,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26801,7 +26804,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26851,7 +26854,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -26901,7 +26904,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -26951,7 +26954,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27001,7 +27004,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27051,7 +27054,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27101,7 +27104,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27151,7 +27154,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27201,7 +27204,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27251,7 +27254,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27601,7 +27604,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27651,7 +27654,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27701,7 +27704,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27751,7 +27754,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27801,7 +27804,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27851,7 +27854,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28151,7 +28154,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28201,7 +28204,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28251,7 +28254,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28301,7 +28304,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28351,7 +28354,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28401,7 +28404,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28451,7 +28454,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28501,7 +28504,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28551,7 +28554,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28601,7 +28604,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28651,7 +28654,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28701,7 +28704,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28751,7 +28754,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28801,7 +28804,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28851,7 +28854,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -28901,7 +28904,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -28951,7 +28954,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29001,7 +29004,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29051,7 +29054,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29101,7 +29104,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29151,7 +29154,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29201,7 +29204,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29251,7 +29254,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29301,7 +29304,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29351,7 +29354,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29401,7 +29404,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29451,7 +29454,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29501,7 +29504,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29551,7 +29554,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29601,7 +29604,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29651,7 +29654,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29701,7 +29704,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29751,7 +29754,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29801,7 +29804,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -29851,7 +29854,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -29901,7 +29904,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -29951,7 +29954,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30001,7 +30004,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30051,7 +30054,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30101,7 +30104,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30151,7 +30154,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30201,7 +30204,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30251,7 +30254,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30301,7 +30304,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30351,7 +30354,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30401,7 +30404,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30451,7 +30454,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30501,7 +30504,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30551,7 +30554,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30601,7 +30604,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30651,7 +30654,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30701,7 +30704,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30751,7 +30754,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -30801,7 +30804,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -32351,7 +32354,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32401,7 +32404,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32451,7 +32454,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32501,7 +32504,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32551,7 +32554,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32601,7 +32604,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32651,7 +32654,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -32701,7 +32704,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32751,7 +32754,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32801,7 +32804,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32851,7 +32854,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -32901,7 +32904,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -32951,7 +32954,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33001,7 +33004,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33051,7 +33054,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33101,7 +33104,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33151,7 +33154,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33201,7 +33204,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33251,7 +33254,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33301,7 +33304,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33351,7 +33354,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33401,7 +33404,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33451,7 +33454,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33501,7 +33504,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33551,7 +33554,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33601,7 +33604,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33651,7 +33654,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -33701,7 +33704,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33751,7 +33754,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34451,7 +34454,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34501,7 +34504,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34551,7 +34554,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34601,7 +34604,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34651,7 +34654,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34701,7 +34704,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34751,7 +34754,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -34801,7 +34804,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -34851,7 +34854,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -34901,7 +34904,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -34951,7 +34954,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35001,7 +35004,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35051,7 +35054,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35651,7 +35654,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35701,7 +35704,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35751,7 +35754,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35801,7 +35804,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -35851,7 +35854,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -35901,7 +35904,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -35951,7 +35954,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36001,7 +36004,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36051,7 +36054,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36101,7 +36104,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36151,7 +36154,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36362,246 +36365,246 @@
         <v>145</v>
       </c>
       <c r="C699">
-        <v>-0.596708611830401</v>
+        <v>-0.54680735347549</v>
       </c>
       <c r="D699" t="s">
         <v>251</v>
       </c>
       <c r="E699">
-        <v>-0.5418484958276091</v>
+        <v>-0.5068238104163365</v>
       </c>
       <c r="F699">
         <v>-1</v>
       </c>
       <c r="G699">
-        <v>0.0113967086118304</v>
+        <v>0.01108680735347549</v>
       </c>
       <c r="H699">
-        <v>0.01094184849582761</v>
+        <v>0.01106682381041634</v>
       </c>
       <c r="I699">
-        <v>-0.05486011600279195</v>
+        <v>-0.03998354305915353</v>
       </c>
       <c r="J699">
         <v>1.4991771529576</v>
       </c>
       <c r="K699">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="L699">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="M699">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="N699">
-        <v>5.2</v>
+        <v>5.28</v>
       </c>
       <c r="O699">
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="700" spans="1:16">
       <c r="A700" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B700" t="s">
         <v>146</v>
       </c>
       <c r="C700">
-        <v>-0.54680735347549</v>
+        <v>-0.8680274779434312</v>
       </c>
       <c r="D700" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E700">
-        <v>-0.5418484958276091</v>
+        <v>-0.6877989173683101</v>
       </c>
       <c r="F700">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G700">
-        <v>0.01108680735347549</v>
+        <v>0.01126802747794343</v>
       </c>
       <c r="H700">
-        <v>0.01094184849582761</v>
+        <v>0.01132779891736831</v>
       </c>
       <c r="I700">
-        <v>-0.004958857647880954</v>
+        <v>0.180228560575121</v>
       </c>
       <c r="J700">
-        <v>1.4991771529576</v>
+        <v>1.505714014378023</v>
       </c>
       <c r="K700">
-        <v>3.88</v>
+        <v>4.03</v>
       </c>
       <c r="L700">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="M700">
-        <v>3.83</v>
+        <v>3.99</v>
       </c>
       <c r="N700">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O700">
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="701" spans="1:16">
       <c r="A701" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B701" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C701">
-        <v>-0.8680274779434312</v>
+        <v>-0.5721703757867278</v>
       </c>
       <c r="D701" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E701">
-        <v>-0.6877989173683101</v>
+        <v>-0.5320560954991667</v>
       </c>
       <c r="F701">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G701">
-        <v>0.01126802747794343</v>
+        <v>0.01111217037578673</v>
       </c>
       <c r="H701">
-        <v>0.01132779891736831</v>
+        <v>0.01109205609549917</v>
       </c>
       <c r="I701">
-        <v>0.180228560575121</v>
+        <v>-0.04011428028756114</v>
       </c>
       <c r="J701">
         <v>1.505714014378023</v>
       </c>
       <c r="K701">
-        <v>4.03</v>
+        <v>3.88</v>
       </c>
       <c r="L701">
-        <v>5.2</v>
+        <v>5.27</v>
       </c>
       <c r="M701">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="N701">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="O701">
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="702" spans="1:16">
       <c r="A702" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B702" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C702">
-        <v>-0.6228560575120898</v>
+        <v>-0.9009851279686432</v>
       </c>
       <c r="D702" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E702">
-        <v>-0.5668846750678265</v>
+        <v>-0.7204294443163484</v>
       </c>
       <c r="F702">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G702">
-        <v>0.01142285605751209</v>
+        <v>0.01130098512796864</v>
       </c>
       <c r="H702">
-        <v>0.01096688467506783</v>
+        <v>0.01136042944431635</v>
       </c>
       <c r="I702">
-        <v>-0.05597138244426336</v>
+        <v>0.1805556836522948</v>
       </c>
       <c r="J702">
-        <v>1.505714014378023</v>
+        <v>1.513892091307355</v>
       </c>
       <c r="K702">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="L702">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M702">
-        <v>3.83</v>
+        <v>3.99</v>
       </c>
       <c r="N702">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O702">
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="703" spans="1:16">
       <c r="A703" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B703" t="s">
         <v>146</v>
       </c>
       <c r="C703">
-        <v>-0.5721703757867278</v>
+        <v>-0.9337099119674415</v>
       </c>
       <c r="D703" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E703">
-        <v>-0.5668846750678265</v>
+        <v>-0.7528294165632978</v>
       </c>
       <c r="F703">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G703">
-        <v>0.01111217037578673</v>
+        <v>0.01133370991196744</v>
       </c>
       <c r="H703">
-        <v>0.01096688467506783</v>
+        <v>0.0113928294165633</v>
       </c>
       <c r="I703">
-        <v>-0.005285700718901332</v>
+        <v>0.1808804954041436</v>
       </c>
       <c r="J703">
-        <v>1.505714014378023</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K703">
-        <v>3.88</v>
+        <v>4.03</v>
       </c>
       <c r="L703">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="M703">
-        <v>3.83</v>
+        <v>3.99</v>
       </c>
       <c r="N703">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O703">
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36609,31 +36612,31 @@
         <v>0</v>
       </c>
       <c r="B704" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C704">
-        <v>-0.9009851279686432</v>
+        <v>-0.9649665355493404</v>
       </c>
       <c r="D704" t="s">
         <v>252</v>
       </c>
       <c r="E704">
-        <v>-0.7204294443163484</v>
+        <v>-0.783775800705178</v>
       </c>
       <c r="F704">
         <v>1</v>
       </c>
       <c r="G704">
-        <v>0.01130098512796864</v>
+        <v>0.01136496653554934</v>
       </c>
       <c r="H704">
-        <v>0.01136042944431635</v>
+        <v>0.01142377580070518</v>
       </c>
       <c r="I704">
-        <v>0.1805556836522948</v>
+        <v>0.1811907348441624</v>
       </c>
       <c r="J704">
-        <v>1.513892091307355</v>
+        <v>1.529768371104055</v>
       </c>
       <c r="K704">
         <v>4.03</v>
@@ -36651,57 +36654,57 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="705" spans="1:16">
       <c r="A705" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B705" t="s">
         <v>146</v>
       </c>
       <c r="C705">
-        <v>-0.6039013142725391</v>
+        <v>-0.9919728003746338</v>
       </c>
       <c r="D705" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E705">
-        <v>-0.5982067097071715</v>
+        <v>-0.8105140132741413</v>
       </c>
       <c r="F705">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G705">
-        <v>0.01114390131427254</v>
+        <v>0.01139197280037463</v>
       </c>
       <c r="H705">
-        <v>0.01099820670970717</v>
+        <v>0.01145051401327414</v>
       </c>
       <c r="I705">
-        <v>-0.005694604565367634</v>
+        <v>0.1814587871004925</v>
       </c>
       <c r="J705">
-        <v>1.513892091307355</v>
+        <v>1.536469677512316</v>
       </c>
       <c r="K705">
-        <v>3.88</v>
+        <v>4.03</v>
       </c>
       <c r="L705">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="M705">
-        <v>3.83</v>
+        <v>3.99</v>
       </c>
       <c r="N705">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O705">
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36709,31 +36712,31 @@
         <v>0</v>
       </c>
       <c r="B706" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C706">
-        <v>-0.9337099119674415</v>
+        <v>-1.064082889548082</v>
       </c>
       <c r="D706" t="s">
         <v>252</v>
       </c>
       <c r="E706">
-        <v>-0.7528294165632978</v>
+        <v>-0.8819083695525682</v>
       </c>
       <c r="F706">
         <v>1</v>
       </c>
       <c r="G706">
-        <v>0.01133370991196744</v>
+        <v>0.01146408288954808</v>
       </c>
       <c r="H706">
-        <v>0.0113928294165633</v>
+        <v>0.01152190836955257</v>
       </c>
       <c r="I706">
-        <v>0.1808804954041436</v>
+        <v>0.182174519995514</v>
       </c>
       <c r="J706">
-        <v>1.522012385103583</v>
+        <v>1.554362999887862</v>
       </c>
       <c r="K706">
         <v>4.03</v>
@@ -36751,57 +36754,57 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="707" spans="1:16">
       <c r="A707" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B707" t="s">
         <v>146</v>
       </c>
       <c r="C707">
-        <v>-0.6354080542019034</v>
+        <v>-1.103231291701239</v>
       </c>
       <c r="D707" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E707">
-        <v>-0.6293074349467247</v>
+        <v>-0.920668201957306</v>
       </c>
       <c r="F707">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G707">
-        <v>0.0111754080542019</v>
+        <v>0.01150323129170124</v>
       </c>
       <c r="H707">
-        <v>0.01102930743494672</v>
+        <v>0.01156066820195731</v>
       </c>
       <c r="I707">
-        <v>-0.006100619255178685</v>
+        <v>0.1825630897439332</v>
       </c>
       <c r="J707">
-        <v>1.522012385103583</v>
+        <v>1.564077243598322</v>
       </c>
       <c r="K707">
-        <v>3.88</v>
+        <v>4.03</v>
       </c>
       <c r="L707">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="M707">
-        <v>3.83</v>
+        <v>3.99</v>
       </c>
       <c r="N707">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="O707">
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36809,31 +36812,31 @@
         <v>0</v>
       </c>
       <c r="B708" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C708">
-        <v>-0.9649665355493404</v>
+        <v>-1.149128838391547</v>
       </c>
       <c r="D708" t="s">
         <v>252</v>
       </c>
       <c r="E708">
-        <v>-0.783775800705178</v>
+        <v>-0.9661101898715314</v>
       </c>
       <c r="F708">
         <v>1</v>
       </c>
       <c r="G708">
-        <v>0.01136496653554934</v>
+        <v>0.01154912883839155</v>
       </c>
       <c r="H708">
-        <v>0.01142377580070518</v>
+        <v>0.01160611018987153</v>
       </c>
       <c r="I708">
-        <v>0.1811907348441624</v>
+        <v>0.1830186485200151</v>
       </c>
       <c r="J708">
-        <v>1.529768371104055</v>
+        <v>1.575466213000384</v>
       </c>
       <c r="K708">
         <v>4.03</v>
@@ -36851,57 +36854,57 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="709" spans="1:16">
       <c r="A709" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B709" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C709">
-        <v>-0.6655012798837321</v>
+        <v>-0.8342358932749292</v>
       </c>
       <c r="D709" t="s">
         <v>251</v>
       </c>
       <c r="E709">
-        <v>-0.6590128613285291</v>
+        <v>-0.9003027758003226</v>
       </c>
       <c r="F709">
         <v>-1</v>
       </c>
       <c r="G709">
-        <v>0.01120550127988373</v>
+        <v>0.01133423589327493</v>
       </c>
       <c r="H709">
-        <v>0.01105901286132853</v>
+        <v>0.01146030277580032</v>
       </c>
       <c r="I709">
-        <v>-0.00648841855520299</v>
+        <v>0.06606688252539339</v>
       </c>
       <c r="J709">
-        <v>1.529768371104055</v>
+        <v>1.60111470875656</v>
       </c>
       <c r="K709">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="L709">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="M709">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="N709">
-        <v>5.2</v>
+        <v>5.28</v>
       </c>
       <c r="O709">
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -36912,146 +36915,146 @@
         <v>147</v>
       </c>
       <c r="C710">
-        <v>-0.9919728003746338</v>
+        <v>-0.8884988382857681</v>
       </c>
       <c r="D710" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E710">
-        <v>-0.8105140132741413</v>
+        <v>-0.9554225041534385</v>
       </c>
       <c r="F710">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G710">
-        <v>0.01139197280037463</v>
+        <v>0.01138849883828577</v>
       </c>
       <c r="H710">
-        <v>0.01145051401327414</v>
+        <v>0.01151542250415344</v>
       </c>
       <c r="I710">
-        <v>0.1814587871004925</v>
+        <v>0.0669236658676704</v>
       </c>
       <c r="J710">
-        <v>1.536469677512316</v>
+        <v>1.615394431127834</v>
       </c>
       <c r="K710">
-        <v>4.03</v>
+        <v>3.8</v>
       </c>
       <c r="L710">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="M710">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="N710">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="O710">
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="711" spans="1:16">
       <c r="A711" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B711" t="s">
+        <v>148</v>
+      </c>
+      <c r="C711">
+        <v>-1.282472551736361</v>
+      </c>
+      <c r="D711" t="s">
+        <v>253</v>
+      </c>
+      <c r="E711">
+        <v>-1.10247255173636</v>
+      </c>
+      <c r="F711">
+        <v>1</v>
+      </c>
+      <c r="G711">
+        <v>0.01172247255173636</v>
+      </c>
+      <c r="H711">
+        <v>0.01190247255173636</v>
+      </c>
+      <c r="I711">
+        <v>0.1800000000000006</v>
+      </c>
+      <c r="J711">
+        <v>1.62561813793409</v>
+      </c>
+      <c r="K711">
+        <v>4</v>
+      </c>
+      <c r="L711">
+        <v>5.22</v>
+      </c>
+      <c r="M711">
+        <v>4</v>
+      </c>
+      <c r="N711">
+        <v>5.4</v>
+      </c>
+      <c r="O711">
+        <v>1</v>
+      </c>
+      <c r="P711" t="s">
         <v>146</v>
-      </c>
-      <c r="C711">
-        <v>-0.6915023487477869</v>
-      </c>
-      <c r="D711" t="s">
-        <v>251</v>
-      </c>
-      <c r="E711">
-        <v>-0.6846788648721702</v>
-      </c>
-      <c r="F711">
-        <v>-1</v>
-      </c>
-      <c r="G711">
-        <v>0.01123150234874778</v>
-      </c>
-      <c r="H711">
-        <v>0.01108467886487217</v>
-      </c>
-      <c r="I711">
-        <v>-0.006823483875616709</v>
-      </c>
-      <c r="J711">
-        <v>1.536469677512316</v>
-      </c>
-      <c r="K711">
-        <v>3.88</v>
-      </c>
-      <c r="L711">
-        <v>5.27</v>
-      </c>
-      <c r="M711">
-        <v>3.83</v>
-      </c>
-      <c r="N711">
-        <v>5.2</v>
-      </c>
-      <c r="O711">
-        <v>1</v>
-      </c>
-      <c r="P711" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="712" spans="1:16">
       <c r="A712" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B712" t="s">
         <v>147</v>
       </c>
       <c r="C712">
-        <v>-1.030819877903268</v>
+        <v>-0.9273489241495421</v>
       </c>
       <c r="D712" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E712">
-        <v>-0.8489755118694884</v>
+        <v>-0.9948860124255878</v>
       </c>
       <c r="F712">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G712">
-        <v>0.01143081987790327</v>
+        <v>0.01142734892414954</v>
       </c>
       <c r="H712">
-        <v>0.01148897551186949</v>
+        <v>0.01155488601242559</v>
       </c>
       <c r="I712">
-        <v>0.1818443660337792</v>
+        <v>0.06753708827604576</v>
       </c>
       <c r="J712">
-        <v>1.546109150844483</v>
+        <v>1.62561813793409</v>
       </c>
       <c r="K712">
-        <v>4.03</v>
+        <v>3.8</v>
       </c>
       <c r="L712">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="M712">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="N712">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="O712">
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>353</v>
+        <v>146</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37062,46 +37065,46 @@
         <v>147</v>
       </c>
       <c r="C713">
-        <v>-1.064082889548082</v>
+        <v>-0.9728832466399586</v>
       </c>
       <c r="D713" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E713">
-        <v>-0.8819083695525682</v>
+        <v>-1.041139297902695</v>
       </c>
       <c r="F713">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G713">
-        <v>0.01146408288954808</v>
+        <v>0.01147288324663996</v>
       </c>
       <c r="H713">
-        <v>0.01152190836955257</v>
+        <v>0.0116011392979027</v>
       </c>
       <c r="I713">
-        <v>0.182174519995514</v>
+        <v>0.06825605126273615</v>
       </c>
       <c r="J713">
-        <v>1.554362999887862</v>
+        <v>1.637600854378937</v>
       </c>
       <c r="K713">
-        <v>4.03</v>
+        <v>3.8</v>
       </c>
       <c r="L713">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="M713">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="N713">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="O713">
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37109,49 +37112,49 @@
         <v>0</v>
       </c>
       <c r="B714" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C714">
-        <v>-0.8864878881367728</v>
+        <v>-1.024362108384423</v>
       </c>
       <c r="D714" t="s">
         <v>251</v>
       </c>
       <c r="E714">
-        <v>-0.8771517040112986</v>
+        <v>-1.093430983779967</v>
       </c>
       <c r="F714">
         <v>-1</v>
       </c>
       <c r="G714">
-        <v>0.01142648788813677</v>
+        <v>0.01152436210838442</v>
       </c>
       <c r="H714">
-        <v>0.0112771517040113</v>
+        <v>0.01165343098377997</v>
       </c>
       <c r="I714">
-        <v>-0.009336184125474212</v>
+        <v>0.06906887539554329</v>
       </c>
       <c r="J714">
-        <v>1.586723682509477</v>
+        <v>1.651147923259059</v>
       </c>
       <c r="K714">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="L714">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="M714">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="N714">
-        <v>5.2</v>
+        <v>5.28</v>
       </c>
       <c r="O714">
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>355</v>
+        <v>148</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37159,81 +37162,81 @@
         <v>0</v>
       </c>
       <c r="B715" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C715">
-        <v>-1.252492276288939</v>
+        <v>-1.380277958041175</v>
       </c>
       <c r="D715" t="s">
-        <v>252</v>
+        <v>145</v>
       </c>
       <c r="E715">
-        <v>-1.068447687938677</v>
+        <v>-1.193732296336574</v>
       </c>
       <c r="F715">
         <v>1</v>
       </c>
       <c r="G715">
-        <v>0.01165249227628894</v>
+        <v>0.01208027795804117</v>
       </c>
       <c r="H715">
-        <v>0.01170844768793868</v>
+        <v>0.01173373229633657</v>
       </c>
       <c r="I715">
-        <v>0.1840445883502619</v>
+        <v>0.1865456617046011</v>
       </c>
       <c r="J715">
-        <v>1.60111470875656</v>
+        <v>1.665910385653756</v>
       </c>
       <c r="K715">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="L715">
-        <v>5.2</v>
+        <v>5.35</v>
       </c>
       <c r="M715">
-        <v>3.99</v>
+        <v>3.88</v>
       </c>
       <c r="N715">
-        <v>5.32</v>
+        <v>5.27</v>
       </c>
       <c r="O715">
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="716" spans="1:16">
       <c r="A716" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B716" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C716">
-        <v>-0.9728832466399586</v>
+        <v>-1.080459465484273</v>
       </c>
       <c r="D716" t="s">
         <v>251</v>
       </c>
       <c r="E716">
-        <v>-1.072011272271327</v>
+        <v>-1.150414088623497</v>
       </c>
       <c r="F716">
         <v>-1</v>
       </c>
       <c r="G716">
-        <v>0.01147288324663996</v>
+        <v>0.01158045946548427</v>
       </c>
       <c r="H716">
-        <v>0.01147201127227133</v>
+        <v>0.0117104140886235</v>
       </c>
       <c r="I716">
-        <v>0.09912802563136847</v>
+        <v>0.06995462313922474</v>
       </c>
       <c r="J716">
-        <v>1.637600854378937</v>
+        <v>1.665910385653756</v>
       </c>
       <c r="K716">
         <v>3.8</v>
@@ -37242,16 +37245,16 @@
         <v>5.25</v>
       </c>
       <c r="M716">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="N716">
-        <v>5.2</v>
+        <v>5.28</v>
       </c>
       <c r="O716">
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37259,81 +37262,81 @@
         <v>0</v>
       </c>
       <c r="B717" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C717">
-        <v>-1.024362108384423</v>
+        <v>-1.42715909512542</v>
       </c>
       <c r="D717" t="s">
-        <v>251</v>
+        <v>145</v>
       </c>
       <c r="E717">
-        <v>-1.123896546082196</v>
+        <v>-1.238756754724413</v>
       </c>
       <c r="F717">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G717">
-        <v>0.01152436210838442</v>
+        <v>0.01212715909512542</v>
       </c>
       <c r="H717">
-        <v>0.0115238965460822</v>
+        <v>0.01177875675472441</v>
       </c>
       <c r="I717">
-        <v>0.09953443769777248</v>
+        <v>0.1884023404010069</v>
       </c>
       <c r="J717">
-        <v>1.651147923259059</v>
+        <v>1.677514627506292</v>
       </c>
       <c r="K717">
-        <v>3.8</v>
+        <v>4.04</v>
       </c>
       <c r="L717">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="M717">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="N717">
-        <v>5.2</v>
+        <v>5.27</v>
       </c>
       <c r="O717">
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>358</v>
+        <v>252</v>
       </c>
     </row>
     <row r="718" spans="1:16">
       <c r="A718" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B718" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C718">
-        <v>-1.080459465484273</v>
+        <v>-1.124555584523909</v>
       </c>
       <c r="D718" t="s">
         <v>251</v>
       </c>
       <c r="E718">
-        <v>-1.180436777053885</v>
+        <v>-1.195206462174287</v>
       </c>
       <c r="F718">
         <v>-1</v>
       </c>
       <c r="G718">
-        <v>0.01158045946548427</v>
+        <v>0.01162455558452391</v>
       </c>
       <c r="H718">
-        <v>0.01158043677705389</v>
+        <v>0.01175520646217429</v>
       </c>
       <c r="I718">
-        <v>0.09997731156961276</v>
+        <v>0.07065087765037781</v>
       </c>
       <c r="J718">
-        <v>1.665910385653756</v>
+        <v>1.677514627506292</v>
       </c>
       <c r="K718">
         <v>3.8</v>
@@ -37342,16 +37345,16 @@
         <v>5.25</v>
       </c>
       <c r="M718">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="N718">
-        <v>5.2</v>
+        <v>5.28</v>
       </c>
       <c r="O718">
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>359</v>
+        <v>252</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37362,28 +37365,28 @@
         <v>149</v>
       </c>
       <c r="C719">
-        <v>-1.42715909512542</v>
+        <v>-1.46853878015609</v>
       </c>
       <c r="D719" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E719">
-        <v>-1.238756754724413</v>
+        <v>-1.278497640347928</v>
       </c>
       <c r="F719">
         <v>1</v>
       </c>
       <c r="G719">
-        <v>0.01212715909512542</v>
+        <v>0.01216853878015609</v>
       </c>
       <c r="H719">
-        <v>0.01177875675472441</v>
+        <v>0.01181849764034793</v>
       </c>
       <c r="I719">
-        <v>0.1884023404010069</v>
+        <v>0.1900411398081614</v>
       </c>
       <c r="J719">
-        <v>1.677514627506292</v>
+        <v>1.687757123801012</v>
       </c>
       <c r="K719">
         <v>4.04</v>
@@ -37401,7 +37404,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>252</v>
+        <v>361</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37409,31 +37412,31 @@
         <v>1</v>
       </c>
       <c r="B720" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C720">
-        <v>-1.124555584523909</v>
+        <v>-1.163477070443847</v>
       </c>
       <c r="D720" t="s">
         <v>251</v>
       </c>
       <c r="E720">
-        <v>-1.224881023349099</v>
+        <v>-1.234742497871907</v>
       </c>
       <c r="F720">
         <v>-1</v>
       </c>
       <c r="G720">
-        <v>0.01162455558452391</v>
+        <v>0.01166347707044385</v>
       </c>
       <c r="H720">
-        <v>0.0116248810233491</v>
+        <v>0.01179474249787191</v>
       </c>
       <c r="I720">
-        <v>0.1003254388251893</v>
+        <v>0.07126542742806041</v>
       </c>
       <c r="J720">
-        <v>1.677514627506292</v>
+        <v>1.687757123801012</v>
       </c>
       <c r="K720">
         <v>3.8</v>
@@ -37442,16 +37445,16 @@
         <v>5.25</v>
       </c>
       <c r="M720">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="N720">
-        <v>5.2</v>
+        <v>5.28</v>
       </c>
       <c r="O720">
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>252</v>
+        <v>361</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37462,28 +37465,28 @@
         <v>149</v>
       </c>
       <c r="C721">
-        <v>-1.46853878015609</v>
+        <v>-1.516702985935216</v>
       </c>
       <c r="D721" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E721">
-        <v>-1.278497640347928</v>
+        <v>-1.324754352828871</v>
       </c>
       <c r="F721">
         <v>1</v>
       </c>
       <c r="G721">
-        <v>0.01216853878015609</v>
+        <v>0.01221670298593521</v>
       </c>
       <c r="H721">
-        <v>0.01181849764034793</v>
+        <v>0.01186475435282887</v>
       </c>
       <c r="I721">
-        <v>0.1900411398081614</v>
+        <v>0.1919486331063451</v>
       </c>
       <c r="J721">
-        <v>1.687757123801012</v>
+        <v>1.699678956914657</v>
       </c>
       <c r="K721">
         <v>4.04</v>
@@ -37501,7 +37504,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>360</v>
+        <v>253</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37509,31 +37512,31 @@
         <v>1</v>
       </c>
       <c r="B722" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C722">
-        <v>-1.163477070443847</v>
+        <v>-1.208780036275697</v>
       </c>
       <c r="D722" t="s">
         <v>251</v>
       </c>
       <c r="E722">
-        <v>-1.264109784157877</v>
+        <v>-1.280760773690576</v>
       </c>
       <c r="F722">
         <v>-1</v>
       </c>
       <c r="G722">
-        <v>0.01166347707044385</v>
+        <v>0.0117087800362757</v>
       </c>
       <c r="H722">
-        <v>0.01166410978415788</v>
+        <v>0.01184076077369058</v>
       </c>
       <c r="I722">
-        <v>0.1006327137140302</v>
+        <v>0.07198073741487931</v>
       </c>
       <c r="J722">
-        <v>1.687757123801012</v>
+        <v>1.699678956914657</v>
       </c>
       <c r="K722">
         <v>3.8</v>
@@ -37542,16 +37545,16 @@
         <v>5.25</v>
       </c>
       <c r="M722">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="N722">
-        <v>5.2</v>
+        <v>5.28</v>
       </c>
       <c r="O722">
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>360</v>
+        <v>253</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37559,148 +37562,48 @@
         <v>0</v>
       </c>
       <c r="B723" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C723">
-        <v>-1.516702985935216</v>
+        <v>-1.213102463254955</v>
       </c>
       <c r="D723" t="s">
-        <v>146</v>
+        <v>251</v>
       </c>
       <c r="E723">
-        <v>-1.324754352828871</v>
+        <v>-1.285151449516874</v>
       </c>
       <c r="F723">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G723">
-        <v>0.01221670298593521</v>
+        <v>0.01171310246325496</v>
       </c>
       <c r="H723">
-        <v>0.01186475435282887</v>
+        <v>0.01184515144951688</v>
       </c>
       <c r="I723">
-        <v>0.1919486331063451</v>
+        <v>0.0720489862619198</v>
       </c>
       <c r="J723">
-        <v>1.699678956914657</v>
+        <v>1.700816437698672</v>
       </c>
       <c r="K723">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="L723">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="M723">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="N723">
-        <v>5.27</v>
+        <v>5.28</v>
       </c>
       <c r="O723">
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="724" spans="1:16">
-      <c r="A724" s="1">
-        <v>1</v>
-      </c>
-      <c r="B724" t="s">
-        <v>148</v>
-      </c>
-      <c r="C724">
-        <v>-1.208780036275697</v>
-      </c>
-      <c r="D724" t="s">
-        <v>251</v>
-      </c>
-      <c r="E724">
-        <v>-1.309770404983137</v>
-      </c>
-      <c r="F724">
-        <v>-1</v>
-      </c>
-      <c r="G724">
-        <v>0.0117087800362757</v>
-      </c>
-      <c r="H724">
-        <v>0.01170977040498314</v>
-      </c>
-      <c r="I724">
-        <v>0.10099036870744</v>
-      </c>
-      <c r="J724">
-        <v>1.699678956914657</v>
-      </c>
-      <c r="K724">
-        <v>3.8</v>
-      </c>
-      <c r="L724">
-        <v>5.25</v>
-      </c>
-      <c r="M724">
-        <v>3.83</v>
-      </c>
-      <c r="N724">
-        <v>5.2</v>
-      </c>
-      <c r="O724">
-        <v>1</v>
-      </c>
-      <c r="P724" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="725" spans="1:16">
-      <c r="A725" s="1">
-        <v>0</v>
-      </c>
-      <c r="B725" t="s">
-        <v>148</v>
-      </c>
-      <c r="C725">
-        <v>-1.213102463254955</v>
-      </c>
-      <c r="D725" t="s">
-        <v>251</v>
-      </c>
-      <c r="E725">
-        <v>-1.314126956385915</v>
-      </c>
-      <c r="F725">
-        <v>-1</v>
-      </c>
-      <c r="G725">
-        <v>0.01171310246325496</v>
-      </c>
-      <c r="H725">
-        <v>0.01171412695638591</v>
-      </c>
-      <c r="I725">
-        <v>0.1010244931309607</v>
-      </c>
-      <c r="J725">
-        <v>1.700816437698672</v>
-      </c>
-      <c r="K725">
-        <v>3.8</v>
-      </c>
-      <c r="L725">
-        <v>5.25</v>
-      </c>
-      <c r="M725">
-        <v>3.83</v>
-      </c>
-      <c r="N725">
-        <v>5.2</v>
-      </c>
-      <c r="O725">
-        <v>1</v>
-      </c>
-      <c r="P725" t="s">
         <v>149</v>
       </c>
     </row>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2235" uniqueCount="366">
   <si>
     <t>trade_time</t>
   </si>
@@ -451,22 +451,25 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-11-16</t>
+    <t>2021-11-29</t>
   </si>
   <si>
-    <t>2021-11-29</t>
+    <t>2021-12-02</t>
   </si>
   <si>
     <t>2021-11-04</t>
   </si>
   <si>
-    <t>2021-12-01</t>
+    <t>2021-11-16</t>
   </si>
   <si>
     <t>2021-11-18</t>
   </si>
   <si>
     <t>2021-11-25</t>
+  </si>
+  <si>
+    <t>2021-11-30</t>
   </si>
   <si>
     <t>2017-04-20</t>
@@ -772,13 +775,10 @@
     <t>2021-08-09</t>
   </si>
   <si>
-    <t>2021-11-22</t>
+    <t>2021-12-06</t>
   </si>
   <si>
-    <t>2021-12-02</t>
-  </si>
-  <si>
-    <t>2021-11-05</t>
+    <t>2021-11-10</t>
   </si>
   <si>
     <t>2021-11-24</t>
@@ -1069,6 +1069,9 @@
     <t>2020-12-24</t>
   </si>
   <si>
+    <t>2021-10-28</t>
+  </si>
+  <si>
     <t>2021-10-29</t>
   </si>
   <si>
@@ -1081,13 +1084,13 @@
     <t>2021-11-03</t>
   </si>
   <si>
+    <t>2021-11-05</t>
+  </si>
+  <si>
     <t>2021-11-08</t>
   </si>
   <si>
     <t>2021-11-09</t>
-  </si>
-  <si>
-    <t>2021-11-10</t>
   </si>
   <si>
     <t>2021-11-11</t>
@@ -1103,6 +1106,9 @@
   </si>
   <si>
     <t>2021-11-19</t>
+  </si>
+  <si>
+    <t>2021-11-22</t>
   </si>
   <si>
     <t>2021-11-23</t>
@@ -1463,7 +1469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P733"/>
+  <dimension ref="A1:P741"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1524,7 +1530,7 @@
         <v>1.855441043116508</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E2">
         <v>1.575397067571232</v>
@@ -1574,7 +1580,7 @@
         <v>1.844886436180541</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E3">
         <v>1.575397067571232</v>
@@ -1624,7 +1630,7 @@
         <v>1.879543169394645</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E4">
         <v>1.575397067571232</v>
@@ -1674,7 +1680,7 @@
         <v>1.931893523774336</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E5">
         <v>1.575397067571232</v>
@@ -1724,7 +1730,7 @@
         <v>1.864287853699299</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E6">
         <v>1.610229702966436</v>
@@ -1774,7 +1780,7 @@
         <v>1.420828285447678</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E7">
         <v>1.720097776330612</v>
@@ -1824,7 +1830,7 @@
         <v>1.444930411725815</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E8">
         <v>1.720097776330612</v>
@@ -1874,7 +1880,7 @@
         <v>1.415528994207057</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E9">
         <v>1.720097776330612</v>
@@ -1924,7 +1930,7 @@
         <v>1.417747421950922</v>
       </c>
       <c r="D10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E10">
         <v>1.720097776330612</v>
@@ -1974,7 +1980,7 @@
         <v>1.837391318446252</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E11">
         <v>1.556576374761795</v>
@@ -2024,7 +2030,7 @@
         <v>1.827426275381424</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E12">
         <v>1.556576374761795</v>
@@ -2074,7 +2080,7 @@
         <v>1.861221338322326</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E13">
         <v>1.556576374761795</v>
@@ -2124,7 +2130,7 @@
         <v>1.913526341635005</v>
       </c>
       <c r="D14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E14">
         <v>1.556576374761795</v>
@@ -2174,7 +2180,7 @@
         <v>1.84664628863214</v>
       </c>
       <c r="D15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E15">
         <v>1.593631212440523</v>
@@ -2224,7 +2230,7 @@
         <v>1.404411199189807</v>
       </c>
       <c r="D16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E16">
         <v>1.701186381387154</v>
@@ -2274,7 +2280,7 @@
         <v>1.428241219065881</v>
       </c>
       <c r="D17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E17">
         <v>1.701186381387154</v>
@@ -2324,7 +2330,7 @@
         <v>1.399021205815165</v>
       </c>
       <c r="D18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E18">
         <v>1.701186381387154</v>
@@ -2374,7 +2380,7 @@
         <v>1.398881378074474</v>
       </c>
       <c r="D19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E19">
         <v>1.701186381387154</v>
@@ -2424,7 +2430,7 @@
         <v>1.772601053603223</v>
       </c>
       <c r="D20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E20">
         <v>1.513212850115657</v>
@@ -2474,7 +2480,7 @@
         <v>1.819007208305362</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E21">
         <v>1.513212850115657</v>
@@ -2524,7 +2530,7 @@
         <v>1.871207721197208</v>
       </c>
       <c r="D22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E22">
         <v>1.513212850115657</v>
@@ -2574,7 +2580,7 @@
         <v>1.805999514927688</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E23">
         <v>1.555387718415254</v>
@@ -2624,7 +2630,7 @@
         <v>1.366585666847875</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E24">
         <v>1.657613875899347</v>
@@ -2674,7 +2680,7 @@
         <v>1.360986692631565</v>
       </c>
       <c r="D25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E25">
         <v>1.657613875899347</v>
@@ -2724,7 +2730,7 @@
         <v>1.355413363007501</v>
       </c>
       <c r="D26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E26">
         <v>1.657613875899347</v>
@@ -2774,7 +2780,7 @@
         <v>1.746707087766096</v>
       </c>
       <c r="D27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E27">
         <v>1.485799595466657</v>
@@ -2824,7 +2830,7 @@
         <v>1.792320570044649</v>
       </c>
       <c r="D28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E28">
         <v>1.485799595466657</v>
@@ -2874,7 +2880,7 @@
         <v>1.780303717196457</v>
       </c>
       <c r="D29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E29">
         <v>1.531211209495895</v>
@@ -2924,7 +2930,7 @@
         <v>1.342673382069711</v>
       </c>
       <c r="D30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E30">
         <v>1.63006850917975</v>
@@ -2974,7 +2980,7 @@
         <v>1.336942295782803</v>
       </c>
       <c r="D31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E31">
         <v>1.63006850917975</v>
@@ -3024,7 +3030,7 @@
         <v>1.327934052323203</v>
       </c>
       <c r="D32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E32">
         <v>1.63006850917975</v>
@@ -3074,7 +3080,7 @@
         <v>1.724897025074506</v>
       </c>
       <c r="D33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E33">
         <v>1.462709860729388</v>
@@ -3124,7 +3130,7 @@
         <v>1.713714740951758</v>
       </c>
       <c r="D34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E34">
         <v>1.462709860729388</v>
@@ -3174,7 +3180,7 @@
         <v>1.769842852372705</v>
       </c>
       <c r="D35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E35">
         <v>1.462709860729388</v>
@@ -3224,7 +3230,7 @@
         <v>1.758660568249956</v>
       </c>
       <c r="D36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E36">
         <v>1.510847732595075</v>
@@ -3274,7 +3280,7 @@
         <v>1.322532456829009</v>
       </c>
       <c r="D37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E37">
         <v>1.606867498612421</v>
@@ -3324,7 +3330,7 @@
         <v>1.316690094712042</v>
       </c>
       <c r="D38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E38">
         <v>1.606867498612421</v>
@@ -3374,7 +3380,7 @@
         <v>1.304788679670904</v>
       </c>
       <c r="D39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E39">
         <v>1.606867498612421</v>
@@ -3424,7 +3430,7 @@
         <v>1.698715924927888</v>
       </c>
       <c r="D40" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E40">
         <v>1.451820073210847</v>
@@ -3474,7 +3480,7 @@
         <v>1.703822090603589</v>
       </c>
       <c r="D41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E41">
         <v>1.451820073210847</v>
@@ -3524,7 +3530,7 @@
         <v>1.759241709824535</v>
       </c>
       <c r="D42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E42">
         <v>1.451820073210847</v>
@@ -3574,7 +3580,7 @@
         <v>1.748453032479565</v>
       </c>
       <c r="D43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E43">
         <v>1.501243727217277</v>
@@ -3624,7 +3630,7 @@
         <v>1.313033413258619</v>
       </c>
       <c r="D44" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E44">
         <v>1.595925230190177</v>
@@ -3674,7 +3680,7 @@
         <v>1.307138570237948</v>
       </c>
       <c r="D45" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E45">
         <v>1.595925230190177</v>
@@ -3724,7 +3730,7 @@
         <v>1.293872651700511</v>
       </c>
       <c r="D46" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E46">
         <v>1.595925230190177</v>
@@ -3774,7 +3780,7 @@
         <v>1.708440278144118</v>
       </c>
       <c r="D47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E47">
         <v>1.445287539361757</v>
@@ -3824,7 +3830,7 @@
         <v>1.75288232747506</v>
       </c>
       <c r="D48" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E48">
         <v>1.445287539361757</v>
@@ -3874,7 +3880,7 @@
         <v>1.742329765811383</v>
       </c>
       <c r="D49" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E49">
         <v>1.495482504593743</v>
@@ -3924,7 +3930,7 @@
         <v>1.307335154816763</v>
       </c>
       <c r="D50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E50">
         <v>1.589361214250248</v>
@@ -3974,7 +3980,7 @@
         <v>1.301408829705253</v>
       </c>
       <c r="D51" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E51">
         <v>1.589361214250248</v>
@@ -4024,7 +4030,7 @@
         <v>1.287324376806003</v>
       </c>
       <c r="D52" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E52">
         <v>1.589361214250248</v>
@@ -4074,7 +4080,7 @@
         <v>1.741577671463358</v>
       </c>
       <c r="D53" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E53">
         <v>1.433675083310133</v>
@@ -4124,7 +4130,7 @@
         <v>1.793586527085793</v>
       </c>
       <c r="D54" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E54">
         <v>1.433675083310133</v>
@@ -4174,7 +4180,7 @@
         <v>1.731444837126847</v>
       </c>
       <c r="D55" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E55">
         <v>1.485241157810864</v>
@@ -4224,7 +4230,7 @@
         <v>1.297205735321128</v>
       </c>
       <c r="D56" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E56">
         <v>1.577692794555001</v>
@@ -4274,7 +4280,7 @@
         <v>1.291223446565996</v>
       </c>
       <c r="D57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E57">
         <v>1.577692794555001</v>
@@ -4324,7 +4330,7 @@
         <v>1.275683938932566</v>
       </c>
       <c r="D58" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E58">
         <v>1.577692794555001</v>
@@ -4424,7 +4430,7 @@
         <v>1.725587143730334</v>
       </c>
       <c r="D60" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E60">
         <v>1.417249169921011</v>
@@ -4474,7 +4480,7 @@
         <v>1.777556418838578</v>
       </c>
       <c r="D61" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E61">
         <v>1.417249169921011</v>
@@ -4524,7 +4530,7 @@
         <v>1.716048017106683</v>
       </c>
       <c r="D62" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E62">
         <v>1.470754689617085</v>
@@ -4574,7 +4580,7 @@
         <v>1.282877589184112</v>
       </c>
       <c r="D63" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E63">
         <v>1.561187720137498</v>
@@ -4624,7 +4630,7 @@
         <v>1.276816139400598</v>
       </c>
       <c r="D64" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E64">
         <v>1.561187720137498</v>
@@ -4674,7 +4680,7 @@
         <v>1.259218445029255</v>
       </c>
       <c r="D65" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E65">
         <v>1.561187720137498</v>
@@ -4724,7 +4730,7 @@
         <v>1.799190602173319</v>
       </c>
       <c r="D66" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E66">
         <v>1.767682200441425</v>
@@ -4774,7 +4780,7 @@
         <v>1.704528128435052</v>
       </c>
       <c r="D67" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E67">
         <v>1.395616765595412</v>
@@ -4824,7 +4830,7 @@
         <v>1.756445277267813</v>
       </c>
       <c r="D68" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E68">
         <v>1.395616765595412</v>
@@ -4874,7 +4880,7 @@
         <v>1.695770895943651</v>
       </c>
       <c r="D69" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E69">
         <v>1.451676472790171</v>
@@ -4924,7 +4930,7 @@
         <v>1.264007877459131</v>
       </c>
       <c r="D70" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E70">
         <v>1.539451063260933</v>
@@ -4974,7 +4980,7 @@
         <v>1.257842175124651</v>
       </c>
       <c r="D71" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E71">
         <v>1.539451063260933</v>
@@ -5024,7 +5030,7 @@
         <v>1.237533914428172</v>
       </c>
       <c r="D72" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E72">
         <v>1.539451063260933</v>
@@ -5124,7 +5130,7 @@
         <v>1.678683818930752</v>
       </c>
       <c r="D74" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E74">
         <v>1.369068774396689</v>
@@ -5174,7 +5180,7 @@
         <v>1.730536996700383</v>
       </c>
       <c r="D75" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E75">
         <v>1.369068774396689</v>
@@ -5224,7 +5230,7 @@
         <v>1.670886152386294</v>
       </c>
       <c r="D76" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E76">
         <v>1.428263063684791</v>
@@ -5274,7 +5280,7 @@
         <v>1.240850352606269</v>
       </c>
       <c r="D77" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E77">
         <v>1.51277512993595</v>
@@ -5324,7 +5330,7 @@
         <v>1.234556708145529</v>
       </c>
       <c r="D78" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E78">
         <v>1.51277512993595</v>
@@ -5374,7 +5380,7 @@
         <v>1.210921952166319</v>
       </c>
       <c r="D79" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E79">
         <v>1.51277512993595</v>
@@ -5424,7 +5430,7 @@
         <v>1.661963549027058</v>
       </c>
       <c r="D80" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E80">
         <v>1.351893249619379</v>
@@ -5474,7 +5480,7 @@
         <v>1.713775339989997</v>
       </c>
       <c r="D81" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E81">
         <v>1.351893249619379</v>
@@ -5524,7 +5530,7 @@
         <v>1.654786684582984</v>
       </c>
       <c r="D82" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E82">
         <v>1.413115492435404</v>
@@ -5574,7 +5580,7 @@
         <v>1.225868328583652</v>
       </c>
       <c r="D83" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E83">
         <v>1.495516831545256</v>
@@ -5624,7 +5630,7 @@
         <v>1.219491910509528</v>
       </c>
       <c r="D84" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E84">
         <v>1.495516831545256</v>
@@ -5674,7 +5680,7 @@
         <v>1.193705040582317</v>
       </c>
       <c r="D85" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E85">
         <v>1.495516831545256</v>
@@ -5724,7 +5730,7 @@
         <v>1.600429769178104</v>
       </c>
       <c r="D86" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E86">
         <v>1.338006244585976</v>
@@ -5774,7 +5780,7 @@
         <v>1.648444633283697</v>
       </c>
       <c r="D87" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E87">
         <v>1.338006244585976</v>
@@ -5824,7 +5830,7 @@
         <v>1.700222961583904</v>
       </c>
       <c r="D88" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E88">
         <v>1.338006244585976</v>
@@ -5874,7 +5880,7 @@
         <v>1.641769708780589</v>
       </c>
       <c r="D89" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E89">
         <v>1.400868157875824</v>
@@ -5924,7 +5930,7 @@
         <v>1.213754844674996</v>
       </c>
       <c r="D90" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E90">
         <v>1.48156290118639</v>
@@ -5974,7 +5980,7 @@
         <v>1.20731150127541</v>
       </c>
       <c r="D91" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E91">
         <v>1.48156290118639</v>
@@ -6024,7 +6030,7 @@
         <v>1.179784572886182</v>
       </c>
       <c r="D92" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E92">
         <v>1.48156290118639</v>
@@ -6074,7 +6080,7 @@
         <v>1.642770386608872</v>
       </c>
       <c r="D93" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E93">
         <v>1.332177501095747</v>
@@ -6124,7 +6130,7 @@
         <v>1.636306139581315</v>
       </c>
       <c r="D94" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E94">
         <v>1.395727627472394</v>
@@ -6174,7 +6180,7 @@
         <v>1.208670494931713</v>
       </c>
       <c r="D95" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E95">
         <v>1.475706067366088</v>
@@ -6224,7 +6230,7 @@
         <v>1.202199061202053</v>
       </c>
       <c r="D96" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E96">
         <v>1.475706067366088</v>
@@ -6274,7 +6280,7 @@
         <v>1.173941784230917</v>
       </c>
       <c r="D97" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E97">
         <v>1.475706067366088</v>
@@ -6324,7 +6330,7 @@
         <v>1.635648220856852</v>
       </c>
       <c r="D98" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E98">
         <v>1.324861414989093</v>
@@ -6374,7 +6380,7 @@
         <v>1.687394874868875</v>
       </c>
       <c r="D99" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E99">
         <v>1.324861414989093</v>
@@ -6424,7 +6430,7 @@
         <v>1.629448410676523</v>
       </c>
       <c r="D100" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E100">
         <v>1.38927536840002</v>
@@ -6474,7 +6480,7 @@
         <v>1.202288752351933</v>
       </c>
       <c r="D101" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E101">
         <v>1.468354723013138</v>
@@ -6524,7 +6530,7 @@
         <v>1.195782060375976</v>
       </c>
       <c r="D102" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E102">
         <v>1.468354723013138</v>
@@ -6574,7 +6580,7 @@
         <v>1.166608069001115</v>
       </c>
       <c r="D103" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E103">
         <v>1.468354723013138</v>
@@ -6624,7 +6630,7 @@
         <v>1.636237432923918</v>
       </c>
       <c r="D104" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E104">
         <v>1.325466669958976</v>
@@ -6674,7 +6680,7 @@
         <v>1.687985545381652</v>
       </c>
       <c r="D105" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E105">
         <v>1.325466669958976</v>
@@ -6724,7 +6730,7 @@
         <v>1.630015746057932</v>
       </c>
       <c r="D106" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E106">
         <v>1.389809159530085</v>
@@ -6774,7 +6780,7 @@
         <v>1.202816709699155</v>
       </c>
       <c r="D107" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E107">
         <v>1.468962894874441</v>
@@ -6824,7 +6830,7 @@
         <v>1.19631293461462</v>
       </c>
       <c r="D108" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E108">
         <v>1.468962894874441</v>
@@ -6874,7 +6880,7 @@
         <v>1.167214782416708</v>
       </c>
       <c r="D109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E109">
         <v>1.468962894874441</v>
@@ -6974,7 +6980,7 @@
         <v>1.686969731933735</v>
       </c>
       <c r="D111" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E111">
         <v>1.32442577469753</v>
@@ -7024,7 +7030,7 @@
         <v>1.688566437853383</v>
       </c>
       <c r="D112" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E112">
         <v>1.388891165154931</v>
@@ -7074,7 +7080,7 @@
         <v>1.116820833577004</v>
       </c>
       <c r="D113" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E113">
         <v>1.46791698325029</v>
@@ -7124,7 +7130,7 @@
         <v>1.189838416471486</v>
       </c>
       <c r="D114" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E114">
         <v>1.46791698325029</v>
@@ -7174,7 +7180,7 @@
         <v>1.16617137897391</v>
       </c>
       <c r="D115" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E115">
         <v>1.46791698325029</v>
@@ -7274,7 +7280,7 @@
         <v>1.679044765444968</v>
       </c>
       <c r="D117" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E117">
         <v>1.316305130023856</v>
@@ -7324,7 +7330,7 @@
         <v>1.681071963371414</v>
       </c>
       <c r="D118" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E118">
         <v>1.381729343587304</v>
@@ -7374,7 +7380,7 @@
         <v>1.109345926913525</v>
       </c>
       <c r="D119" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E119">
         <v>1.459757202939633</v>
@@ -7424,7 +7430,7 @@
         <v>1.116606291492413</v>
       </c>
       <c r="D120" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E120">
         <v>1.459757202939633</v>
@@ -7474,7 +7480,7 @@
         <v>1.158031166481744</v>
       </c>
       <c r="D121" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E121">
         <v>1.459757202939633</v>
@@ -7524,7 +7530,7 @@
         <v>1.667785062291963</v>
       </c>
       <c r="D122" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E122">
         <v>1.323675609160295</v>
@@ -7624,7 +7630,7 @@
         <v>1.705523534148037</v>
       </c>
       <c r="D124" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E124">
         <v>1.306151805217721</v>
@@ -7674,7 +7680,7 @@
         <v>1.0999999749233</v>
       </c>
       <c r="D125" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E125">
         <v>1.449554946447687</v>
@@ -7724,7 +7730,7 @@
         <v>1.107015681073126</v>
       </c>
       <c r="D126" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E126">
         <v>1.449554946447687</v>
@@ -7774,7 +7780,7 @@
         <v>1.074450234602739</v>
       </c>
       <c r="D127" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E127">
         <v>1.449554946447687</v>
@@ -7824,7 +7830,7 @@
         <v>1.728036618426774</v>
       </c>
       <c r="D128" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E128">
         <v>1.311858607036529</v>
@@ -7924,7 +7930,7 @@
         <v>1.735732764200063</v>
       </c>
       <c r="D130" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E130">
         <v>1.301215982596513</v>
@@ -7974,7 +7980,7 @@
         <v>1.095456639402092</v>
       </c>
       <c r="D131" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E131">
         <v>1.444595336729509</v>
@@ -8024,7 +8030,7 @@
         <v>1.102353410067069</v>
       </c>
       <c r="D132" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E132">
         <v>1.444595336729509</v>
@@ -8074,7 +8080,7 @@
         <v>1.069526305530016</v>
       </c>
       <c r="D133" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E133">
         <v>1.444595336729509</v>
@@ -8174,7 +8180,7 @@
         <v>1.767688434264066</v>
       </c>
       <c r="D135" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E135">
         <v>1.290978663803567</v>
@@ -8224,7 +8230,7 @@
         <v>1.08603337246497</v>
       </c>
       <c r="D136" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E136">
         <v>1.434308681460452</v>
@@ -8274,7 +8280,7 @@
         <v>1.092683460749394</v>
       </c>
       <c r="D137" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E137">
         <v>1.434308681460452</v>
@@ -8324,7 +8330,7 @@
         <v>1.059313654975125</v>
       </c>
       <c r="D138" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E138">
         <v>1.434308681460452</v>
@@ -8974,7 +8980,7 @@
         <v>1.823420612308294</v>
       </c>
       <c r="D151" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E151">
         <v>2.204728303692967</v>
@@ -9060,7 +9066,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9110,7 +9116,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9374,7 +9380,7 @@
         <v>2.07884565528049</v>
       </c>
       <c r="D159" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E159">
         <v>2.424795934638657</v>
@@ -9524,7 +9530,7 @@
         <v>2.074698477808512</v>
       </c>
       <c r="D162" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E162">
         <v>2.228712809543505</v>
@@ -9824,7 +9830,7 @@
         <v>2.045995448659537</v>
       </c>
       <c r="D168" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E168">
         <v>2.697722827185737</v>
@@ -9974,7 +9980,7 @@
         <v>2.025703573192318</v>
       </c>
       <c r="D171" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E171">
         <v>2.585859069325287</v>
@@ -10074,7 +10080,7 @@
         <v>2.002237248721763</v>
       </c>
       <c r="D173" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E173">
         <v>2.933150127071722</v>
@@ -10160,7 +10166,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10174,7 +10180,7 @@
         <v>2.14690100237887</v>
       </c>
       <c r="D175" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E175">
         <v>3.035145626224377</v>
@@ -10210,7 +10216,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10274,7 +10280,7 @@
         <v>2.113865641885164</v>
       </c>
       <c r="D177" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E177">
         <v>2.99862999271211</v>
@@ -10424,7 +10430,7 @@
         <v>2.224552854469621</v>
       </c>
       <c r="D180" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E180">
         <v>2.747562112891602</v>
@@ -10474,7 +10480,7 @@
         <v>2.234582155562626</v>
       </c>
       <c r="D181" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E181">
         <v>2.747562112891602</v>
@@ -10524,7 +10530,7 @@
         <v>2.532227490792448</v>
       </c>
       <c r="D182" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E182">
         <v>2.747562112891602</v>
@@ -10674,7 +10680,7 @@
         <v>2.219578642489605</v>
       </c>
       <c r="D185" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E185">
         <v>2.748307309478141</v>
@@ -10724,7 +10730,7 @@
         <v>2.229273046142372</v>
       </c>
       <c r="D186" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E186">
         <v>2.748307309478141</v>
@@ -10774,7 +10780,7 @@
         <v>2.526938081221619</v>
       </c>
       <c r="D187" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E187">
         <v>2.748307309478141</v>
@@ -10924,7 +10930,7 @@
         <v>2.223095119495316</v>
       </c>
       <c r="D190" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E190">
         <v>2.585306324177835</v>
@@ -10974,7 +10980,7 @@
         <v>2.233026276055397</v>
       </c>
       <c r="D191" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E191">
         <v>2.585306324177835</v>
@@ -11024,7 +11030,7 @@
         <v>2.530677384493038</v>
       </c>
       <c r="D192" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E192">
         <v>2.585306324177835</v>
@@ -11174,7 +11180,7 @@
         <v>2.351296670264901</v>
       </c>
       <c r="D195" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E195">
         <v>2.34477901699545</v>
@@ -11224,7 +11230,7 @@
         <v>2.531296670264901</v>
       </c>
       <c r="D196" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E196">
         <v>2.34477901699545</v>
@@ -11424,7 +11430,7 @@
         <v>2.354338556588907</v>
       </c>
       <c r="D200" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E200">
         <v>2.692933327062218</v>
@@ -11474,7 +11480,7 @@
         <v>2.534338556588906</v>
       </c>
       <c r="D201" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E201">
         <v>2.692933327062218</v>
@@ -11674,7 +11680,7 @@
         <v>2.353252705775172</v>
       </c>
       <c r="D205" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E205">
         <v>3.037215179660817</v>
@@ -11724,7 +11730,7 @@
         <v>2.533252705775172</v>
       </c>
       <c r="D206" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E206">
         <v>3.037215179660817</v>
@@ -11774,7 +11780,7 @@
         <v>-1.066638455738899</v>
       </c>
       <c r="D207" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E207">
         <v>-1.465413797453388</v>
@@ -11824,7 +11830,7 @@
         <v>-1.0366384557389</v>
       </c>
       <c r="D208" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E208">
         <v>-1.465413797453388</v>
@@ -11874,7 +11880,7 @@
         <v>-0.9510556888450674</v>
       </c>
       <c r="D209" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E209">
         <v>-1.465413797453388</v>
@@ -11924,7 +11930,7 @@
         <v>-1.819265145803461</v>
       </c>
       <c r="D210" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E210">
         <v>-1.307592851757549</v>
@@ -11974,7 +11980,7 @@
         <v>-1.771950960365871</v>
       </c>
       <c r="D211" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E211">
         <v>-1.297263464992842</v>
@@ -12024,7 +12030,7 @@
         <v>-1.016934078228135</v>
       </c>
       <c r="D212" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E212">
         <v>-1.07654556696558</v>
@@ -12074,7 +12080,7 @@
         <v>-1.083441760674821</v>
       </c>
       <c r="D213" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E213">
         <v>-1.481089607902267</v>
@@ -12124,7 +12130,7 @@
         <v>-1.053441760674821</v>
       </c>
       <c r="D214" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E214">
         <v>-1.481089607902267</v>
@@ -12174,7 +12180,7 @@
         <v>-0.9668769824535648</v>
       </c>
       <c r="D215" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E215">
         <v>-1.481089607902267</v>
@@ -12224,7 +12230,7 @@
         <v>-1.83581385521005</v>
       </c>
       <c r="D216" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E216">
         <v>-1.323195920626619</v>
@@ -12274,7 +12280,7 @@
         <v>-1.787408546075322</v>
       </c>
       <c r="D217" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E217">
         <v>-1.311375331475824</v>
@@ -12374,7 +12380,7 @@
         <v>-1.07759404974841</v>
       </c>
       <c r="D219" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E219">
         <v>-1.503621288834554</v>
@@ -12424,7 +12430,7 @@
         <v>-0.9896177741137624</v>
       </c>
       <c r="D220" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E220">
         <v>-1.503621288834554</v>
@@ -12474,7 +12480,7 @@
         <v>-1.859600200509798</v>
       </c>
       <c r="D221" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E221">
         <v>-1.345623046194952</v>
@@ -12524,7 +12530,7 @@
         <v>-1.809626560915746</v>
       </c>
       <c r="D222" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E222">
         <v>-1.33165907208308</v>
@@ -12574,7 +12580,7 @@
         <v>-1.047695097971209</v>
       </c>
       <c r="D223" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E223">
         <v>-1.119714428935569</v>
@@ -12624,7 +12630,7 @@
         <v>-1.107622621715292</v>
       </c>
       <c r="D224" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E224">
         <v>-1.53163495662184</v>
@@ -12674,7 +12680,7 @@
         <v>-1.017891429537125</v>
       </c>
       <c r="D225" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E225">
         <v>-1.53163495662184</v>
@@ -12724,7 +12730,7 @@
         <v>-1.889173794113544</v>
       </c>
       <c r="D226" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E226">
         <v>-1.373506720164198</v>
@@ -12774,7 +12780,7 @@
         <v>-1.837250247248916</v>
       </c>
       <c r="D227" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E227">
         <v>-1.356877872782539</v>
@@ -12874,7 +12880,7 @@
         <v>-1.136466558905362</v>
       </c>
       <c r="D229" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E229">
         <v>-1.55854347811301</v>
@@ -12924,7 +12930,7 @@
         <v>-1.045049682086217</v>
       </c>
       <c r="D230" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E230">
         <v>-1.55854347811301</v>
@@ -12974,7 +12980,7 @@
         <v>-1.91758070195225</v>
       </c>
       <c r="D231" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E231">
         <v>-1.400290376126407</v>
@@ -13024,7 +13030,7 @@
         <v>-1.863784172153202</v>
       </c>
       <c r="D232" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E232">
         <v>-1.38110178540104</v>
@@ -13074,7 +13080,7 @@
         <v>-1.091913194675672</v>
       </c>
       <c r="D233" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E233">
         <v>-0.942243215869925</v>
@@ -13124,7 +13130,7 @@
         <v>-1.06938217480964</v>
       </c>
       <c r="D234" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E234">
         <v>-0.942243215869925</v>
@@ -13174,7 +13180,7 @@
         <v>-1.09938217480964</v>
       </c>
       <c r="D235" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E235">
         <v>-0.942243215869925</v>
@@ -13224,7 +13230,7 @@
         <v>-1.069955605077879</v>
       </c>
       <c r="D236" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E236">
         <v>-1.583220381123139</v>
@@ -13274,7 +13280,7 @@
         <v>-1.943631724851574</v>
       </c>
       <c r="D237" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E237">
         <v>-1.42485276914577</v>
@@ -13324,7 +13330,7 @@
         <v>-1.888117545191031</v>
       </c>
       <c r="D238" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E238">
         <v>-1.403316723609694</v>
@@ -13374,7 +13380,7 @@
         <v>-1.111780678073619</v>
       </c>
       <c r="D239" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E239">
         <v>-0.8811636624809664</v>
@@ -13424,7 +13430,7 @@
         <v>-1.088104558299923</v>
       </c>
       <c r="D240" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E240">
         <v>-0.8811636624809664</v>
@@ -13474,7 +13480,7 @@
         <v>-1.118104558299923</v>
       </c>
       <c r="D241" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E241">
         <v>-0.8811636624809664</v>
@@ -13524,7 +13530,7 @@
         <v>-1.100958399511376</v>
       </c>
       <c r="D242" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E242">
         <v>-1.613938092389432</v>
@@ -13574,7 +13580,7 @@
         <v>-1.976059935121095</v>
       </c>
       <c r="D243" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E243">
         <v>-1.455427938828461</v>
@@ -13624,7 +13630,7 @@
         <v>-1.918407631706518</v>
       </c>
       <c r="D244" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E244">
         <v>-1.430969790828538</v>
@@ -13674,7 +13680,7 @@
         <v>-1.136511642828615</v>
       </c>
       <c r="D245" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E245">
         <v>-1.028859339414037</v>
@@ -13724,7 +13730,7 @@
         <v>-1.111410107218897</v>
       </c>
       <c r="D246" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E246">
         <v>-1.028859339414037</v>
@@ -13774,7 +13780,7 @@
         <v>-1.141410107218897</v>
       </c>
       <c r="D247" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E247">
         <v>-1.028859339414037</v>
@@ -13824,7 +13830,7 @@
         <v>-1.117512484565025</v>
       </c>
       <c r="D248" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E248">
         <v>-1.630339955971323</v>
@@ -13874,7 +13880,7 @@
         <v>-1.993375127533532</v>
       </c>
       <c r="D249" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E249">
         <v>-1.471753691674473</v>
@@ -13924,7 +13930,7 @@
         <v>-1.934581163080772</v>
       </c>
       <c r="D250" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E250">
         <v>-1.445735273589034</v>
@@ -13974,7 +13980,7 @@
         <v>-1.149716855503595</v>
       </c>
       <c r="D251" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E251">
         <v>-1.032336626753983</v>
@@ -14024,7 +14030,7 @@
         <v>-1.123854212535088</v>
       </c>
       <c r="D252" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E252">
         <v>-1.032336626753983</v>
@@ -14074,7 +14080,7 @@
         <v>-1.153854212535088</v>
       </c>
       <c r="D253" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E253">
         <v>-1.032336626753983</v>
@@ -14124,7 +14130,7 @@
         <v>-1.135440729342402</v>
       </c>
       <c r="D254" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E254">
         <v>-1.64810334332546</v>
@@ -14174,7 +14180,7 @@
         <v>-2.012127659427111</v>
       </c>
       <c r="D255" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E255">
         <v>-1.489434650316991</v>
@@ -14224,7 +14230,7 @@
         <v>-1.95209726430005</v>
       </c>
       <c r="D256" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E256">
         <v>-1.461726443643339</v>
@@ -14274,7 +14280,7 @@
         <v>-1.164018236969687</v>
       </c>
       <c r="D257" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E257">
         <v>-1.112656534851095</v>
@@ -14324,7 +14330,7 @@
         <v>-1.137331306884979</v>
       </c>
       <c r="D258" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E258">
         <v>-1.112656534851095</v>
@@ -14374,7 +14380,7 @@
         <v>-1.167331306884979</v>
       </c>
       <c r="D259" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E259">
         <v>-1.112656534851095</v>
@@ -14424,7 +14430,7 @@
         <v>-2.029751754240792</v>
       </c>
       <c r="D260" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E260">
         <v>-1.506051653998461</v>
@@ -14474,7 +14480,7 @@
         <v>-1.968559330884256</v>
       </c>
       <c r="D261" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E261">
         <v>-1.476755342077862</v>
@@ -14524,7 +14530,7 @@
         <v>-1.177459030157264</v>
       </c>
       <c r="D262" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E262">
         <v>-1.113758929914932</v>
@@ -14574,7 +14580,7 @@
         <v>-1.149997414586239</v>
       </c>
       <c r="D263" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E263">
         <v>-1.113758929914932</v>
@@ -14624,7 +14630,7 @@
         <v>-1.179997414586239</v>
       </c>
       <c r="D264" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E264">
         <v>-1.113758929914932</v>
@@ -14674,7 +14680,7 @@
         <v>-2.049264235927141</v>
       </c>
       <c r="D265" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E265">
         <v>-1.524449136731304</v>
@@ -14724,7 +14730,7 @@
         <v>-1.986785275316561</v>
       </c>
       <c r="D266" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E266">
         <v>-1.493394557230178</v>
@@ -14774,7 +14780,7 @@
         <v>-1.192339977729051</v>
       </c>
       <c r="D267" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E267">
         <v>-0.9807727745942727</v>
@@ -14824,7 +14830,7 @@
         <v>-1.16402067065533</v>
       </c>
       <c r="D268" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E268">
         <v>-0.9807727745942727</v>
@@ -14874,7 +14880,7 @@
         <v>-1.19402067065533</v>
       </c>
       <c r="D269" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E269">
         <v>-0.9807727745942727</v>
@@ -14924,7 +14930,7 @@
         <v>-2.083260847634321</v>
       </c>
       <c r="D270" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E270">
         <v>-1.55650308491236</v>
@@ -14974,7 +14980,7 @@
         <v>-2.018540352185904</v>
       </c>
       <c r="D271" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E271">
         <v>-1.52238507446619</v>
@@ -15024,7 +15030,7 @@
         <v>-1.218267064020021</v>
       </c>
       <c r="D272" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E272">
         <v>-1.15072047992809</v>
@@ -15074,7 +15080,7 @@
         <v>-1.188453400387743</v>
       </c>
       <c r="D273" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E273">
         <v>-1.15072047992809</v>
@@ -15124,7 +15130,7 @@
         <v>-1.218453400387743</v>
       </c>
       <c r="D274" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E274">
         <v>-1.15072047992809</v>
@@ -15174,7 +15180,7 @@
         <v>-2.129173370599524</v>
       </c>
       <c r="D275" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E275">
         <v>-1.599792035136694</v>
@@ -15224,7 +15230,7 @@
         <v>-2.061425675834721</v>
       </c>
       <c r="D276" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E276">
         <v>-1.561536852291463</v>
@@ -15274,7 +15280,7 @@
         <v>-1.253281669446231</v>
       </c>
       <c r="D277" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E277">
         <v>-1.285422798224685</v>
@@ -15324,7 +15330,7 @@
         <v>-1.221449872936362</v>
       </c>
       <c r="D278" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E278">
         <v>-1.285422798224685</v>
@@ -15374,7 +15380,7 @@
         <v>-1.251449872936362</v>
       </c>
       <c r="D279" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E279">
         <v>-1.285422798224685</v>
@@ -15424,7 +15430,7 @@
         <v>-2.169540849194301</v>
       </c>
       <c r="D280" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E280">
         <v>-1.637852800668912</v>
@@ -15474,7 +15480,7 @@
         <v>-2.099131562434238</v>
       </c>
       <c r="D281" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E281">
         <v>-1.595960108763492</v>
@@ -15524,7 +15530,7 @@
         <v>-1.284067416858071</v>
       </c>
       <c r="D282" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E282">
         <v>-1.430231131562097</v>
@@ -15574,7 +15580,7 @@
         <v>-1.250461225684695</v>
       </c>
       <c r="D283" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E283">
         <v>-1.430231131562097</v>
@@ -15624,7 +15630,7 @@
         <v>-1.280461225684695</v>
       </c>
       <c r="D284" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E284">
         <v>-1.430231131562097</v>
@@ -15674,7 +15680,7 @@
         <v>-2.189959023684696</v>
       </c>
       <c r="D285" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E285">
         <v>-1.657104222331285</v>
@@ -15724,7 +15730,7 @@
         <v>-2.11820348366153</v>
       </c>
       <c r="D286" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E286">
         <v>-1.613371650966291</v>
@@ -15774,7 +15780,7 @@
         <v>-1.299639079601296</v>
       </c>
       <c r="D287" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E287">
         <v>-1.362715372273368</v>
@@ -15824,7 +15830,7 @@
         <v>-1.265135386252518</v>
       </c>
       <c r="D288" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E288">
         <v>-1.362715372273368</v>
@@ -15874,7 +15880,7 @@
         <v>-1.295135386252518</v>
       </c>
       <c r="D289" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E289">
         <v>-1.362715372273368</v>
@@ -15924,7 +15930,7 @@
         <v>-2.214173184477514</v>
       </c>
       <c r="D290" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E290">
         <v>-1.679934716793084</v>
@@ -15974,7 +15980,7 @@
         <v>-2.140821106380096</v>
       </c>
       <c r="D291" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E291">
         <v>-1.634020210059946</v>
@@ -16024,7 +16030,7 @@
         <v>-1.318105703326807</v>
       </c>
       <c r="D292" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E292">
         <v>-1.489781742375517</v>
@@ -16074,7 +16080,7 @@
         <v>-1.282537651261862</v>
       </c>
       <c r="D293" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E293">
         <v>-1.489781742375517</v>
@@ -16124,7 +16130,7 @@
         <v>-1.312537651261862</v>
       </c>
       <c r="D294" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E294">
         <v>-1.489781742375517</v>
@@ -16174,7 +16180,7 @@
         <v>-2.241121102143395</v>
       </c>
       <c r="D295" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E295">
         <v>-1.705342753449486</v>
@@ -16224,7 +16230,7 @@
         <v>-2.165992238265808</v>
       </c>
       <c r="D296" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E296">
         <v>-1.656999972816785</v>
@@ -16274,7 +16280,7 @@
         <v>-1.338657192184084</v>
       </c>
       <c r="D297" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E297">
         <v>-1.427033480143279</v>
@@ -16324,7 +16330,7 @@
         <v>-1.301904616265692</v>
       </c>
       <c r="D298" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E298">
         <v>-1.427033480143279</v>
@@ -16374,7 +16380,7 @@
         <v>-1.331904616265692</v>
       </c>
       <c r="D299" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E299">
         <v>-1.427033480143279</v>
@@ -16424,7 +16430,7 @@
         <v>1.347720014974502</v>
       </c>
       <c r="D300" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E300">
         <v>1.579062118830282</v>
@@ -16474,7 +16480,7 @@
         <v>1.334700016044109</v>
       </c>
       <c r="D301" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E301">
         <v>1.593089491417174</v>
@@ -16524,7 +16530,7 @@
         <v>1.841747387561394</v>
       </c>
       <c r="D302" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E302">
         <v>1.890874754800249</v>
@@ -16574,7 +16580,7 @@
         <v>1.862485279427185</v>
       </c>
       <c r="D303" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E303">
         <v>1.890874754800249</v>
@@ -16624,7 +16630,7 @@
         <v>1.441706845387347</v>
       </c>
       <c r="D304" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E304">
         <v>1.664215600520115</v>
@@ -16674,7 +16680,7 @@
         <v>1.435400191486443</v>
       </c>
       <c r="D305" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E305">
         <v>1.704389685327122</v>
@@ -16724,7 +16730,7 @@
         <v>1.856584782452771</v>
       </c>
       <c r="D306" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E306">
         <v>1.861880930194354</v>
@@ -16774,7 +16780,7 @@
         <v>1.9645987906652</v>
       </c>
       <c r="D307" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E307">
         <v>1.861880930194354</v>
@@ -16824,7 +16830,7 @@
         <v>2.014804950663784</v>
       </c>
       <c r="D308" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E308">
         <v>1.689180786611569</v>
@@ -16874,7 +16880,7 @@
         <v>1.927301606872644</v>
       </c>
       <c r="D309" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E309">
         <v>1.689180786611569</v>
@@ -16924,7 +16930,7 @@
         <v>1.922617032689892</v>
       </c>
       <c r="D310" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E310">
         <v>1.689180786611569</v>
@@ -16974,7 +16980,7 @@
         <v>1.696992868637676</v>
       </c>
       <c r="D311" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E311">
         <v>1.791368704585461</v>
@@ -17324,7 +17330,7 @@
         <v>1.869784887916945</v>
       </c>
       <c r="D318" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E318">
         <v>1.868536559812515</v>
@@ -17374,7 +17380,7 @@
         <v>1.892281544125805</v>
       </c>
       <c r="D319" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E319">
         <v>1.868536559812515</v>
@@ -17424,7 +17430,7 @@
         <v>1.879784887916945</v>
       </c>
       <c r="D320" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E320">
         <v>1.868536559812515</v>
@@ -17474,7 +17480,7 @@
         <v>1.830509026107986</v>
       </c>
       <c r="D321" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E321">
         <v>1.588842690067986</v>
@@ -17524,7 +17530,7 @@
         <v>1.823342590879987</v>
       </c>
       <c r="D322" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E322">
         <v>1.588842690067986</v>
@@ -17574,7 +17580,7 @@
         <v>1.597009323671986</v>
       </c>
       <c r="D323" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E323">
         <v>1.690676056463986</v>
@@ -17624,7 +17630,7 @@
         <v>1.564008728543987</v>
       </c>
       <c r="D324" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E324">
         <v>1.690841103059988</v>
@@ -17674,7 +17680,7 @@
         <v>1.612175362147987</v>
       </c>
       <c r="D325" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E325">
         <v>1.690841103059988</v>
@@ -17724,7 +17730,7 @@
         <v>1.608508629355987</v>
       </c>
       <c r="D326" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E326">
         <v>1.690841103059988</v>
@@ -17774,7 +17780,7 @@
         <v>1.611175163771987</v>
       </c>
       <c r="D327" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E327">
         <v>1.690841103059988</v>
@@ -17874,7 +17880,7 @@
         <v>1.787174370267988</v>
       </c>
       <c r="D329" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E329">
         <v>1.578675659711986</v>
@@ -17924,7 +17930,7 @@
         <v>1.812507439099989</v>
       </c>
       <c r="D330" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E330">
         <v>1.578675659711986</v>
@@ -17974,7 +17980,7 @@
         <v>1.783507637475988</v>
       </c>
       <c r="D331" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E331">
         <v>1.578675659711986</v>
@@ -18024,7 +18030,7 @@
         <v>1.797174370267989</v>
       </c>
       <c r="D332" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E332">
         <v>1.578675659711986</v>
@@ -18074,7 +18080,7 @@
         <v>1.796508232603987</v>
       </c>
       <c r="D333" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E333">
         <v>1.578675659711986</v>
@@ -18124,7 +18130,7 @@
         <v>1.60619577124814</v>
       </c>
       <c r="D334" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E334">
         <v>1.409496709559184</v>
@@ -18174,7 +18180,7 @@
         <v>1.639829926132983</v>
       </c>
       <c r="D335" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E335">
         <v>1.409496709559184</v>
@@ -18224,7 +18230,7 @@
         <v>1.641634855442047</v>
       </c>
       <c r="D336" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E336">
         <v>1.409496709559184</v>
@@ -18274,7 +18280,7 @@
         <v>1.294651169712725</v>
       </c>
       <c r="D337" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E337">
         <v>1.17011455017335</v>
@@ -18324,7 +18330,7 @@
         <v>1.309805629866267</v>
       </c>
       <c r="D338" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E338">
         <v>1.17011455017335</v>
@@ -18374,7 +18380,7 @@
         <v>1.302846240403662</v>
       </c>
       <c r="D339" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E339">
         <v>1.17011455017335</v>
@@ -18424,7 +18430,7 @@
         <v>1.302846240403662</v>
       </c>
       <c r="D340" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E340">
         <v>1.17011455017335</v>
@@ -18474,7 +18480,7 @@
         <v>1.306789315595589</v>
       </c>
       <c r="D341" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E341">
         <v>1.17011455017335</v>
@@ -18524,7 +18530,7 @@
         <v>1.225269010326891</v>
       </c>
       <c r="D342" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E342">
         <v>1.17011455017335</v>
@@ -18574,7 +18580,7 @@
         <v>1.444294269397325</v>
       </c>
       <c r="D343" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E343">
         <v>1.256000185094495</v>
@@ -18624,7 +18630,7 @@
         <v>1.501117816501946</v>
       </c>
       <c r="D344" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E344">
         <v>1.256000185094495</v>
@@ -18674,7 +18680,7 @@
         <v>1.083058995014017</v>
       </c>
       <c r="D345" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E345">
         <v>1.093353102453659</v>
@@ -18724,7 +18730,7 @@
         <v>1.408730452400234</v>
       </c>
       <c r="D346" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E346">
         <v>1.224172692200284</v>
@@ -18774,7 +18780,7 @@
         <v>1.47198161896276</v>
       </c>
       <c r="D347" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E347">
         <v>1.224172692200284</v>
@@ -18874,7 +18880,7 @@
         <v>1.382122760311682</v>
       </c>
       <c r="D349" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E349">
         <v>1.191863351807043</v>
@@ -18924,7 +18930,7 @@
         <v>1.442404318382183</v>
       </c>
       <c r="D350" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E350">
         <v>1.191863351807043</v>
@@ -19024,7 +19030,7 @@
         <v>1.370401955803482</v>
       </c>
       <c r="D352" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E352">
         <v>1.1776309463328</v>
@@ -19074,7 +19080,7 @@
         <v>1.429375388370835</v>
       </c>
       <c r="D353" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E353">
         <v>1.1776309463328</v>
@@ -19124,7 +19130,7 @@
         <v>1.010452200278918</v>
       </c>
       <c r="D354" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E354">
         <v>1.015068140738506</v>
@@ -19174,7 +19180,7 @@
         <v>1.025068140738506</v>
       </c>
       <c r="D355" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E355">
         <v>1.015068140738506</v>
@@ -19224,7 +19230,7 @@
         <v>1.355513343522262</v>
       </c>
       <c r="D356" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E356">
         <v>1.159551917134175</v>
@@ -19274,7 +19280,7 @@
         <v>1.4128251006118</v>
       </c>
       <c r="D357" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E357">
         <v>1.159551917134175</v>
@@ -19324,7 +19330,7 @@
         <v>0.9937025114625451</v>
       </c>
       <c r="D358" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E358">
         <v>1.019315457208822</v>
@@ -19374,7 +19380,7 @@
         <v>1.009315457208822</v>
       </c>
       <c r="D359" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E359">
         <v>1.019315457208822</v>
@@ -19424,7 +19430,7 @@
         <v>1.344301537527252</v>
       </c>
       <c r="D360" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E360">
         <v>1.145937581283092</v>
@@ -19474,7 +19480,7 @@
         <v>1.400361976983419</v>
       </c>
       <c r="D361" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E361">
         <v>1.145937581283092</v>
@@ -19624,7 +19630,7 @@
         <v>1.32595157423566</v>
       </c>
       <c r="D364" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E364">
         <v>1.123655483000445</v>
@@ -19674,7 +19680,7 @@
         <v>1.379964026717319</v>
       </c>
       <c r="D365" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E365">
         <v>1.123655483000445</v>
@@ -19724,7 +19730,7 @@
         <v>0.9604455210151182</v>
       </c>
       <c r="D366" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E366">
         <v>0.9494825324195202</v>
@@ -19774,7 +19780,7 @@
         <v>0.9780380495261229</v>
       </c>
       <c r="D367" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E367">
         <v>0.9494825324195202</v>
@@ -19824,7 +19830,7 @@
         <v>0.9780380495261229</v>
       </c>
       <c r="D368" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E368">
         <v>0.9494825324195202</v>
@@ -19874,7 +19880,7 @@
         <v>0.93948253241952</v>
       </c>
       <c r="D369" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E369">
         <v>0.9494825324195202</v>
@@ -19924,7 +19930,7 @@
         <v>1.346901155844391</v>
       </c>
       <c r="D370" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E370">
         <v>1.225539647019887</v>
@@ -19974,7 +19980,7 @@
         <v>1.331298641136886</v>
       </c>
       <c r="D371" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E371">
         <v>1.225539647019887</v>
@@ -20024,7 +20030,7 @@
         <v>1.154256377900131</v>
       </c>
       <c r="D372" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E372">
         <v>1.26001537201713</v>
@@ -20074,7 +20080,7 @@
         <v>1.14857562348788</v>
       </c>
       <c r="D373" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E373">
         <v>1.274334617604878</v>
@@ -20124,7 +20130,7 @@
         <v>1.324412857309625</v>
       </c>
       <c r="D374" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E374">
         <v>1.205852605838874</v>
@@ -20174,7 +20180,7 @@
         <v>1.043943419081145</v>
       </c>
       <c r="D375" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E375">
         <v>1.269702413198143</v>
@@ -20224,7 +20230,7 @@
         <v>1.36666643673015</v>
       </c>
       <c r="D376" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E376">
         <v>1.400907442613152</v>
@@ -20274,7 +20280,7 @@
         <v>1.3381061852594</v>
       </c>
       <c r="D377" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E377">
         <v>1.400907442613152</v>
@@ -20324,7 +20330,7 @@
         <v>1.337921514632137</v>
       </c>
       <c r="D378" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E378">
         <v>1.216329758597064</v>
@@ -20374,7 +20380,7 @@
         <v>1.321935254573682</v>
       </c>
       <c r="D379" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E379">
         <v>1.216329758597064</v>
@@ -20424,7 +20430,7 @@
         <v>1.144547620521072</v>
       </c>
       <c r="D380" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E380">
         <v>1.250153116497689</v>
@@ -20474,7 +20480,7 @@
         <v>1.138751742503535</v>
       </c>
       <c r="D381" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E381">
         <v>1.264357238480152</v>
@@ -20524,7 +20530,7 @@
         <v>1.314166856439233</v>
       </c>
       <c r="D382" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E382">
         <v>1.195568230433388</v>
@@ -20574,7 +20580,7 @@
         <v>1.035309148684748</v>
       </c>
       <c r="D383" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E383">
         <v>1.260914644661365</v>
@@ -20724,7 +20730,7 @@
         <v>1.326338641239302</v>
       </c>
       <c r="D386" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E386">
         <v>1.204449888450566</v>
@@ -20774,7 +20780,7 @@
         <v>1.309857386591409</v>
       </c>
       <c r="D387" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E387">
         <v>1.204449888450566</v>
@@ -20824,7 +20830,7 @@
         <v>1.132024257408305</v>
       </c>
       <c r="D388" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E388">
         <v>1.237431755549148</v>
@@ -20874,7 +20880,7 @@
         <v>1.126079881013937</v>
       </c>
       <c r="D389" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E389">
         <v>1.25148737915478</v>
@@ -20924,7 +20930,7 @@
         <v>1.300950500901255</v>
       </c>
       <c r="D390" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E390">
         <v>1.182302375436465</v>
@@ -20974,7 +20980,7 @@
         <v>1.024171770422406</v>
       </c>
       <c r="D391" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E391">
         <v>1.249579268563249</v>
@@ -21024,7 +21030,7 @@
         <v>1.347949275999877</v>
       </c>
       <c r="D392" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E392">
         <v>1.407134279718192</v>
@@ -21074,7 +21080,7 @@
         <v>1.319301150535088</v>
       </c>
       <c r="D393" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E393">
         <v>1.407134279718192</v>
@@ -21124,7 +21130,7 @@
         <v>1.31894662096582</v>
       </c>
       <c r="D394" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E394">
         <v>1.196868329195712</v>
@@ -21174,7 +21180,7 @@
         <v>1.302149468015641</v>
       </c>
       <c r="D395" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E395">
         <v>1.196868329195712</v>
@@ -21224,7 +21230,7 @@
         <v>1.12403203036048</v>
       </c>
       <c r="D396" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E396">
         <v>1.229313169180409</v>
@@ -21274,7 +21280,7 @@
         <v>1.117992884475426</v>
       </c>
       <c r="D397" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E397">
         <v>1.243274023295355</v>
@@ -21324,7 +21330,7 @@
         <v>1.017064058620981</v>
       </c>
       <c r="D398" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E398">
         <v>1.242345197440909</v>
@@ -21474,7 +21480,7 @@
         <v>1.309314370259902</v>
       </c>
       <c r="D401" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E401">
         <v>1.212105582664171</v>
@@ -21524,7 +21530,7 @@
         <v>1.113617673828013</v>
       </c>
       <c r="D402" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E402">
         <v>1.218734158789721</v>
@@ -21574,7 +21580,7 @@
         <v>1.107455037549294</v>
       </c>
       <c r="D403" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E403">
         <v>1.232571522511002</v>
@@ -21624,7 +21630,7 @@
         <v>1.00780227909606</v>
       </c>
       <c r="D404" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E404">
         <v>1.232918764057767</v>
@@ -21810,7 +21816,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21824,7 +21830,7 @@
         <v>1.096911392393543</v>
       </c>
       <c r="D408" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E408">
         <v>1.20176374642348</v>
@@ -21860,7 +21866,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21874,7 +21880,7 @@
         <v>1.090550657915995</v>
       </c>
       <c r="D409" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E409">
         <v>1.215403011945933</v>
@@ -21910,7 +21916,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21924,7 +21930,7 @@
         <v>0.9929449141839808</v>
       </c>
       <c r="D410" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E410">
         <v>1.217797268213918</v>
@@ -21960,7 +21966,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22010,7 +22016,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22060,7 +22066,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22074,7 +22080,7 @@
         <v>1.076787728620787</v>
       </c>
       <c r="D413" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E413">
         <v>1.194722566962074</v>
@@ -22124,7 +22130,7 @@
         <v>1.070188373624195</v>
       </c>
       <c r="D414" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E414">
         <v>1.194722566962074</v>
@@ -22174,7 +22180,7 @@
         <v>0.9750483752556411</v>
       </c>
       <c r="D415" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E415">
         <v>1.199582568593519</v>
@@ -22224,7 +22230,7 @@
         <v>1.06618192359011</v>
       </c>
       <c r="D416" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E416">
         <v>1.199582568593519</v>
@@ -22274,7 +22280,7 @@
         <v>1.301445795242007</v>
       </c>
       <c r="D417" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E417">
         <v>1.466305796873452</v>
@@ -22324,7 +22330,7 @@
         <v>1.325778053569659</v>
       </c>
       <c r="D418" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E418">
         <v>1.466305796873452</v>
@@ -22374,7 +22380,7 @@
         <v>1.061021828820504</v>
       </c>
       <c r="D419" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E419">
         <v>1.178520456495379</v>
@@ -22424,7 +22430,7 @@
         <v>1.05423552639545</v>
       </c>
       <c r="D420" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E420">
         <v>1.178520456495379</v>
@@ -22474,7 +22480,7 @@
         <v>0.9610273181210012</v>
       </c>
       <c r="D421" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E421">
         <v>1.18531224822093</v>
@@ -22524,7 +22530,7 @@
         <v>1.052098550645983</v>
       </c>
       <c r="D422" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E422">
         <v>1.18531224822093</v>
@@ -22574,7 +22580,7 @@
         <v>1.288172527821214</v>
       </c>
       <c r="D423" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E423">
         <v>1.460679389446836</v>
@@ -22624,7 +22630,7 @@
         <v>1.312816365196303</v>
       </c>
       <c r="D424" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E424">
         <v>1.460679389446836</v>
@@ -22774,7 +22780,7 @@
         <v>0.8755952802088971</v>
       </c>
       <c r="D427" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E427">
         <v>1.122137607315365</v>
@@ -22824,7 +22830,7 @@
         <v>1.266605330685716</v>
       </c>
       <c r="D428" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E428">
         <v>1.559580979333694</v>
@@ -22910,7 +22916,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22924,7 +22930,7 @@
         <v>0.8602148664207081</v>
       </c>
       <c r="D430" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E430">
         <v>1.107098980500247</v>
@@ -22960,7 +22966,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -22974,7 +22980,7 @@
         <v>1.280896373713855</v>
       </c>
       <c r="D431" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E431">
         <v>1.524099754797897</v>
@@ -23010,7 +23016,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23174,7 +23180,7 @@
         <v>1.302688953291221</v>
       </c>
       <c r="D435" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E435">
         <v>1.419681456386476</v>
@@ -23260,7 +23266,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23310,7 +23316,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23360,7 +23366,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23374,7 +23380,7 @@
         <v>1.257626439327654</v>
       </c>
       <c r="D439" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E439">
         <v>1.411664944525371</v>
@@ -23410,7 +23416,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23424,7 +23430,7 @@
         <v>1.840766780529548</v>
       </c>
       <c r="D440" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E440">
         <v>2.000338151296236</v>
@@ -23474,7 +23480,7 @@
         <v>2.174266578212954</v>
       </c>
       <c r="D441" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E441">
         <v>2.309284269167179</v>
@@ -23524,7 +23530,7 @@
         <v>2.096677111858851</v>
       </c>
       <c r="D442" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E442">
         <v>1.937337746663046</v>
@@ -23574,7 +23580,7 @@
         <v>1.86232005570882</v>
       </c>
       <c r="D443" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E443">
         <v>1.975355842250461</v>
@@ -23624,7 +23630,7 @@
         <v>1.842592596122513</v>
       </c>
       <c r="D444" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E444">
         <v>2.002261997256608</v>
@@ -23674,7 +23680,7 @@
         <v>2.176435500091845</v>
       </c>
       <c r="D445" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E445">
         <v>2.311735028352367</v>
@@ -23724,7 +23730,7 @@
         <v>2.099152378635891</v>
       </c>
       <c r="D446" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E446">
         <v>1.939947805195271</v>
@@ -23774,7 +23780,7 @@
         <v>1.864648276934749</v>
       </c>
       <c r="D447" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E447">
         <v>1.97756152551713</v>
@@ -23824,7 +23830,7 @@
         <v>1.84474004582061</v>
       </c>
       <c r="D448" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E448">
         <v>2.004524746267355</v>
@@ -23874,7 +23880,7 @@
         <v>2.178986497384215</v>
       </c>
       <c r="D449" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E449">
         <v>2.314617511168604</v>
@@ -23924,7 +23930,7 @@
         <v>2.102063686280291</v>
       </c>
       <c r="D450" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E450">
         <v>1.943017649394564</v>
@@ -23974,7 +23980,7 @@
         <v>1.867386635610175</v>
       </c>
       <c r="D451" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E451">
         <v>1.980155760051744</v>
@@ -24024,7 +24030,7 @@
         <v>2.182944230037506</v>
       </c>
       <c r="D452" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E452">
         <v>2.319089525466108</v>
@@ -24074,7 +24080,7 @@
         <v>2.106580420720769</v>
       </c>
       <c r="D453" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E453">
         <v>1.947780344621405</v>
@@ -24124,7 +24130,7 @@
         <v>1.871635049192803</v>
       </c>
       <c r="D454" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E454">
         <v>1.984180572919497</v>
@@ -24174,7 +24180,7 @@
         <v>2.18904965856885</v>
       </c>
       <c r="D455" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E455">
         <v>2.325988314767062</v>
@@ -24224,7 +24230,7 @@
         <v>2.113548197914732</v>
       </c>
       <c r="D456" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E456">
         <v>1.955127555226921</v>
@@ -24274,7 +24280,7 @@
         <v>1.878188899028709</v>
       </c>
       <c r="D457" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E457">
         <v>2.015269716995014</v>
@@ -24324,7 +24330,7 @@
         <v>1.88583444385064</v>
       </c>
       <c r="D458" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E458">
         <v>2.125307034142769</v>
@@ -24374,7 +24380,7 @@
         <v>2.298073483752043</v>
       </c>
       <c r="D459" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E459">
         <v>2.037664496092738</v>
@@ -24424,7 +24430,7 @@
         <v>1.897427651995606</v>
       </c>
       <c r="D460" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E460">
         <v>2.100495646236972</v>
@@ -24474,7 +24480,7 @@
         <v>1.886668859096591</v>
       </c>
       <c r="D461" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E461">
         <v>2.126294507806616</v>
@@ -24524,7 +24530,7 @@
         <v>2.29919426636051</v>
       </c>
       <c r="D462" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E462">
         <v>2.038997585538931</v>
@@ -24574,7 +24580,7 @@
         <v>1.898642244602138</v>
       </c>
       <c r="D463" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E463">
         <v>2.102411345144836</v>
@@ -24624,7 +24630,7 @@
         <v>1.887695818378956</v>
       </c>
       <c r="D464" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E464">
         <v>2.127509844235451</v>
@@ -24724,7 +24730,7 @@
         <v>1.900137108409605</v>
       </c>
       <c r="D466" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E466">
         <v>2.104769097816775</v>
@@ -24774,7 +24780,7 @@
         <v>1.882492570308907</v>
       </c>
       <c r="D467" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E467">
         <v>2.121352154211724</v>
@@ -24874,7 +24880,7 @@
         <v>1.911660475077831</v>
       </c>
       <c r="D469" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E469">
         <v>2.092823179170745</v>
@@ -24924,7 +24930,7 @@
         <v>1.879971436092785</v>
       </c>
       <c r="D470" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E470">
         <v>2.118368563423415</v>
@@ -25024,7 +25030,7 @@
         <v>1.90788623273062</v>
       </c>
       <c r="D472" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E472">
         <v>2.087035013041425</v>
@@ -25124,7 +25130,7 @@
         <v>1.89858988459332</v>
       </c>
       <c r="D474" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E474">
         <v>2.07277816293363</v>
@@ -25174,7 +25180,7 @@
         <v>2.27342525786704</v>
       </c>
       <c r="D475" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E475">
         <v>2.050890844436287</v>
@@ -25224,7 +25230,7 @@
         <v>1.889192027490578</v>
       </c>
       <c r="D476" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E476">
         <v>2.058365638997408</v>
@@ -25274,7 +25280,7 @@
         <v>2.266210657543448</v>
       </c>
       <c r="D477" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E477">
         <v>2.042055342718407</v>
@@ -25324,7 +25330,7 @@
         <v>1.881151085279702</v>
       </c>
       <c r="D478" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E478">
         <v>2.046034075448713</v>
@@ -25374,7 +25380,7 @@
         <v>2.259792939301354</v>
       </c>
       <c r="D479" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E479">
         <v>2.034195758263333</v>
@@ -25424,7 +25430,7 @@
         <v>1.873998297987854</v>
       </c>
       <c r="D480" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E480">
         <v>2.061056685064424</v>
@@ -25474,7 +25480,7 @@
         <v>2.247400638043782</v>
       </c>
       <c r="D481" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E481">
         <v>2.019019283595469</v>
@@ -25524,7 +25530,7 @@
         <v>1.860186614207387</v>
       </c>
       <c r="D482" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E482">
         <v>2.039929722127505</v>
@@ -25574,7 +25580,7 @@
         <v>2.218696305669633</v>
       </c>
       <c r="D483" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E483">
         <v>1.983865960247392</v>
@@ -25624,7 +25630,7 @@
         <v>1.828194560944569</v>
       </c>
       <c r="D484" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E484">
         <v>1.990993261207699</v>
@@ -25674,7 +25680,7 @@
         <v>1.830127541068264</v>
       </c>
       <c r="D485" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E485">
         <v>2.018032125375022</v>
@@ -25760,7 +25766,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25774,7 +25780,7 @@
         <v>1.78228507381279</v>
       </c>
       <c r="D487" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E487">
         <v>2.022800472072064</v>
@@ -25810,7 +25816,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25824,7 +25830,7 @@
         <v>1.783722556644772</v>
       </c>
       <c r="D488" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E488">
         <v>1.972929321636883</v>
@@ -25860,7 +25866,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25874,7 +25880,7 @@
         <v>2.163345062458509</v>
       </c>
       <c r="D489" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E489">
         <v>1.877414831999107</v>
@@ -25924,7 +25930,7 @@
         <v>1.693507313006611</v>
       </c>
       <c r="D490" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E490">
         <v>1.978388335287718</v>
@@ -25974,7 +25980,7 @@
         <v>1.734543015346852</v>
       </c>
       <c r="D491" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E491">
         <v>1.925129818487629</v>
@@ -26024,7 +26030,7 @@
         <v>1.684218514250647</v>
       </c>
       <c r="D492" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E492">
         <v>1.570048693213578</v>
@@ -26074,7 +26080,7 @@
         <v>2.132031608016207</v>
       </c>
       <c r="D493" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E493">
         <v>1.840169754028087</v>
@@ -26124,7 +26130,7 @@
         <v>1.660262632299145</v>
       </c>
       <c r="D494" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E494">
         <v>1.929555899725715</v>
@@ -26174,7 +26180,7 @@
         <v>1.680468679922261</v>
       </c>
       <c r="D495" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E495">
         <v>1.872572875128523</v>
@@ -26224,7 +26230,7 @@
         <v>1.634006631356384</v>
       </c>
       <c r="D496" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E496">
         <v>1.60382087481427</v>
@@ -26274,7 +26280,7 @@
         <v>2.09863804467423</v>
       </c>
       <c r="D497" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E497">
         <v>1.800450537718246</v>
@@ -26324,7 +26330,7 @@
         <v>1.624809554037398</v>
       </c>
       <c r="D498" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E498">
         <v>1.877479593897257</v>
@@ -26374,7 +26380,7 @@
         <v>1.622802262168714</v>
       </c>
       <c r="D499" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E499">
         <v>1.752483946759322</v>
@@ -26424,7 +26430,7 @@
         <v>1.580459243442377</v>
       </c>
       <c r="D500" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E500">
         <v>1.752483946759322</v>
@@ -26474,7 +26480,7 @@
         <v>2.071221135479056</v>
       </c>
       <c r="D501" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E501">
         <v>1.767840117089625</v>
@@ -26524,7 +26530,7 @@
         <v>1.595701734142962</v>
       </c>
       <c r="D502" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E502">
         <v>1.834723709073065</v>
@@ -26674,7 +26680,7 @@
         <v>2.041322179557651</v>
       </c>
       <c r="D505" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E505">
         <v>1.73227748229324</v>
@@ -26724,7 +26730,7 @@
         <v>1.563958789750633</v>
       </c>
       <c r="D506" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E506">
         <v>1.788097143451137</v>
@@ -26774,7 +26780,7 @@
         <v>1.472686344256899</v>
       </c>
       <c r="D507" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E507">
         <v>1.788097143451137</v>
@@ -26824,7 +26830,7 @@
         <v>1.523825085403519</v>
       </c>
       <c r="D508" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E508">
         <v>1.630370751283219</v>
@@ -26874,7 +26880,7 @@
         <v>1.56168905637971</v>
       </c>
       <c r="D509" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E509">
         <v>1.630370751283219</v>
@@ -26924,7 +26930,7 @@
         <v>1.565051671294496</v>
       </c>
       <c r="D510" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E510">
         <v>1.630370751283219</v>
@@ -26974,7 +26980,7 @@
         <v>1.866585623391427</v>
       </c>
       <c r="D511" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E511">
         <v>1.689366599623595</v>
@@ -27024,7 +27030,7 @@
         <v>2.005245252276134</v>
       </c>
       <c r="D512" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E512">
         <v>1.689366599623595</v>
@@ -27074,7 +27080,7 @@
         <v>1.4318415411232</v>
       </c>
       <c r="D513" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E513">
         <v>1.73183620839538</v>
@@ -27124,7 +27130,7 @@
         <v>1.461524840934997</v>
       </c>
       <c r="D514" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E514">
         <v>1.564205583165584</v>
@@ -27174,7 +27180,7 @@
         <v>1.496369157204806</v>
       </c>
       <c r="D515" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E515">
         <v>1.564205583165584</v>
@@ -27224,7 +27230,7 @@
         <v>1.508949665433811</v>
       </c>
       <c r="D516" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E516">
         <v>1.564205583165584</v>
@@ -27274,7 +27280,7 @@
         <v>1.973924573324424</v>
       </c>
       <c r="D517" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E517">
         <v>1.612872963807592</v>
@@ -27324,7 +27330,7 @@
         <v>1.396381565393731</v>
       </c>
       <c r="D518" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E518">
         <v>1.682992506417824</v>
@@ -27374,7 +27380,7 @@
         <v>1.467141600577559</v>
       </c>
       <c r="D519" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E519">
         <v>1.682992506417824</v>
@@ -27424,7 +27430,7 @@
         <v>1.407438029705613</v>
       </c>
       <c r="D520" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E520">
         <v>1.521706666475579</v>
@@ -27474,7 +27480,7 @@
         <v>1.439660791349507</v>
       </c>
       <c r="D521" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E521">
         <v>1.521706666475579</v>
@@ -27524,7 +27530,7 @@
         <v>1.460243940015513</v>
       </c>
       <c r="D522" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E522">
         <v>1.521706666475579</v>
@@ -27574,7 +27580,7 @@
         <v>1.940579116805523</v>
       </c>
       <c r="D523" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E523">
         <v>1.574239241056619</v>
@@ -27624,7 +27630,7 @@
         <v>1.781069303182167</v>
       </c>
       <c r="D524" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E524">
         <v>1.574239241056619</v>
@@ -27674,7 +27680,7 @@
         <v>1.358629220348103</v>
       </c>
       <c r="D525" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E525">
         <v>1.630991221802445</v>
@@ -27724,7 +27730,7 @@
         <v>1.349854686289714</v>
       </c>
       <c r="D526" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E526">
         <v>1.479202912629048</v>
@@ -27774,7 +27780,7 @@
         <v>1.379286418533347</v>
       </c>
       <c r="D527" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E527">
         <v>1.479202912629048</v>
@@ -27824,7 +27830,7 @@
         <v>1.408389551684359</v>
       </c>
       <c r="D528" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E528">
         <v>1.479202912629048</v>
@@ -27874,7 +27880,7 @@
         <v>1.74645545085387</v>
       </c>
       <c r="D529" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E529">
         <v>1.54184264617284</v>
@@ -27924,7 +27930,7 @@
         <v>1.326971711279163</v>
       </c>
       <c r="D530" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E530">
         <v>1.58738515872694</v>
@@ -28124,7 +28130,7 @@
         <v>1.276676327166428</v>
       </c>
       <c r="D534" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E534">
         <v>1.518106691894613</v>
@@ -28174,7 +28180,7 @@
         <v>1.224852607973696</v>
       </c>
       <c r="D535" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E535">
         <v>1.33929930838555</v>
@@ -28224,7 +28230,7 @@
         <v>1.248225566013237</v>
       </c>
       <c r="D536" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E536">
         <v>1.33929930838555</v>
@@ -28274,7 +28280,7 @@
         <v>1.263762437199394</v>
       </c>
       <c r="D537" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E537">
         <v>1.33929930838555</v>
@@ -28324,7 +28330,7 @@
         <v>1.212947744952629</v>
       </c>
       <c r="D538" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E538">
         <v>1.430324909390002</v>
@@ -28374,7 +28380,7 @@
         <v>1.146309428698562</v>
       </c>
       <c r="D539" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E539">
         <v>1.238758183620087</v>
@@ -28424,7 +28430,7 @@
         <v>1.216483509339664</v>
       </c>
       <c r="D540" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E540">
         <v>1.238758183620087</v>
@@ -28474,7 +28480,7 @@
         <v>1.171021231954409</v>
       </c>
       <c r="D541" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E541">
         <v>1.238758183620087</v>
@@ -28674,7 +28680,7 @@
         <v>0.913889681656368</v>
       </c>
       <c r="D545" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E545">
         <v>0.9422215166785484</v>
@@ -28724,7 +28730,7 @@
         <v>0.9595249171276929</v>
       </c>
       <c r="D546" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E546">
         <v>0.9422215166785484</v>
@@ -28774,7 +28780,7 @@
         <v>0.9589976550364385</v>
       </c>
       <c r="D547" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E547">
         <v>0.9422215166785484</v>
@@ -28824,7 +28830,7 @@
         <v>0.8504189521355614</v>
       </c>
       <c r="D548" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E548">
         <v>0.937857691146331</v>
@@ -28874,7 +28880,7 @@
         <v>0.9017680975637474</v>
       </c>
       <c r="D549" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E549">
         <v>0.937857691146331</v>
@@ -28924,7 +28930,7 @@
         <v>0.908653475416529</v>
       </c>
       <c r="D550" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E550">
         <v>0.937857691146331</v>
@@ -29124,7 +29130,7 @@
         <v>0.7994059700977925</v>
       </c>
       <c r="D554" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E554">
         <v>0.9510460107817367</v>
@@ -29174,7 +29180,7 @@
         <v>0.8553475251011551</v>
       </c>
       <c r="D555" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E555">
         <v>0.9510460107817367</v>
@@ -29224,7 +29230,7 @@
         <v>0.8681906234838945</v>
       </c>
       <c r="D556" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E556">
         <v>0.9510460107817367</v>
@@ -29324,7 +29330,7 @@
         <v>0.7963844516425689</v>
       </c>
       <c r="D558" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E558">
         <v>0.9293442447455118</v>
@@ -29374,7 +29380,7 @@
         <v>0.9077462565202601</v>
       </c>
       <c r="D559" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E559">
         <v>0.9293442447455118</v>
@@ -29424,7 +29430,7 @@
         <v>0.8525980168231655</v>
       </c>
       <c r="D560" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E560">
         <v>0.9293442447455118</v>
@@ -29474,7 +29480,7 @@
         <v>0.8657939932736682</v>
       </c>
       <c r="D561" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E561">
         <v>0.9293442447455118</v>
@@ -30574,7 +30580,7 @@
         <v>0.751468861471289</v>
       </c>
       <c r="D583" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E583">
         <v>0.9385035221553486</v>
@@ -30624,7 +30630,7 @@
         <v>0.7709845877750583</v>
       </c>
       <c r="D584" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E584">
         <v>0.9385035221553486</v>
@@ -30674,7 +30680,7 @@
         <v>0.8117259226040443</v>
       </c>
       <c r="D585" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E585">
         <v>0.9385035221553486</v>
@@ -30724,7 +30730,7 @@
         <v>0.830167515424916</v>
       </c>
       <c r="D586" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E586">
         <v>0.9385035221553486</v>
@@ -30774,7 +30780,7 @@
         <v>0.8384277846341899</v>
       </c>
       <c r="D587" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E587">
         <v>0.9385035221553486</v>
@@ -31174,7 +31180,7 @@
         <v>0.8616555364163685</v>
       </c>
       <c r="D595" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E595">
         <v>0.9487042537756789</v>
@@ -31224,7 +31230,7 @@
         <v>0.8685708400378545</v>
       </c>
       <c r="D596" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E596">
         <v>0.9487042537756789</v>
@@ -31274,7 +31280,7 @@
         <v>0.9283666743289771</v>
       </c>
       <c r="D597" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E597">
         <v>0.9487042537756789</v>
@@ -31324,7 +31330,7 @@
         <v>0.9119931158630705</v>
       </c>
       <c r="D598" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E598">
         <v>0.9487042537756789</v>
@@ -31374,7 +31380,7 @@
         <v>0.917566191902035</v>
       </c>
       <c r="D599" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E599">
         <v>0.9487042537756789</v>
@@ -31424,7 +31430,7 @@
         <v>0.8850151504748149</v>
       </c>
       <c r="D600" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E600">
         <v>0.9487042537756789</v>
@@ -31474,7 +31480,7 @@
         <v>0.9303840608049012</v>
       </c>
       <c r="D601" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E601">
         <v>0.9487042537756789</v>
@@ -31524,7 +31530,7 @@
         <v>0.9319931158630701</v>
       </c>
       <c r="D602" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E602">
         <v>0.9487042537756789</v>
@@ -31610,7 +31616,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31660,7 +31666,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31710,7 +31716,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -31760,7 +31766,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31810,7 +31816,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31860,7 +31866,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31910,7 +31916,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31960,7 +31966,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32010,7 +32016,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32060,7 +32066,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32110,7 +32116,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32160,7 +32166,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32210,7 +32216,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32260,7 +32266,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32310,7 +32316,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -33374,7 +33380,7 @@
         <v>0.9426739735459577</v>
       </c>
       <c r="D639" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E639">
         <v>1.155481591635229</v>
@@ -33424,7 +33430,7 @@
         <v>0.9523699059372155</v>
       </c>
       <c r="D640" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E640">
         <v>0.9617333668754942</v>
@@ -33474,7 +33480,7 @@
         <v>0.9489115468641032</v>
       </c>
       <c r="D641" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E641">
         <v>0.9617333668754942</v>
@@ -33524,7 +33530,7 @@
         <v>0.994540984964766</v>
       </c>
       <c r="D642" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E642">
         <v>0.9617333668754942</v>
@@ -33574,7 +33580,7 @@
         <v>0.9895196820815877</v>
       </c>
       <c r="D643" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E643">
         <v>0.9617333668754942</v>
@@ -33624,7 +33630,7 @@
         <v>0.9598379516124478</v>
       </c>
       <c r="D644" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E644">
         <v>0.9617333668754942</v>
@@ -33674,7 +33680,7 @@
         <v>1.006089726852713</v>
       </c>
       <c r="D645" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E645">
         <v>0.9617333668754942</v>
@@ -33724,7 +33730,7 @@
         <v>0.9848592544956265</v>
       </c>
       <c r="D646" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E646">
         <v>0.9617333668754942</v>
@@ -34024,7 +34030,7 @@
         <v>0.9734565125913943</v>
       </c>
       <c r="D652" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E652">
         <v>1.185400334942146</v>
@@ -34074,7 +34080,7 @@
         <v>0.9846444558037319</v>
       </c>
       <c r="D653" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E653">
         <v>1.181231801994401</v>
@@ -34124,7 +34130,7 @@
         <v>0.9774953331205798</v>
       </c>
       <c r="D654" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E654">
         <v>1.181231801994401</v>
@@ -34174,7 +34180,7 @@
         <v>1.023910040074443</v>
       </c>
       <c r="D655" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E655">
         <v>1.181231801994401</v>
@@ -34224,7 +34230,7 @@
         <v>1.015119446695905</v>
       </c>
       <c r="D656" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E656">
         <v>1.181231801994401</v>
@@ -34274,7 +34280,7 @@
         <v>0.9864585657359251</v>
       </c>
       <c r="D657" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E657">
         <v>1.181231801994401</v>
@@ -34324,7 +34330,7 @@
         <v>1.007646508948263</v>
       </c>
       <c r="D658" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E658">
         <v>1.181231801994401</v>
@@ -34374,7 +34380,7 @@
         <v>1.015249159114463</v>
       </c>
       <c r="D659" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E659">
         <v>0.9834565125913941</v>
@@ -34674,7 +34680,7 @@
         <v>0.9989502799212269</v>
       </c>
       <c r="D665" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E665">
         <v>1.210178715943846</v>
@@ -34724,7 +34730,7 @@
         <v>1.011373890427612</v>
       </c>
       <c r="D666" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E666">
         <v>1.203864024011701</v>
@@ -34774,7 +34780,7 @@
         <v>1.00116811706971</v>
       </c>
       <c r="D667" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E667">
         <v>1.203864024011701</v>
@@ -34824,7 +34830,7 @@
         <v>1.048233175230966</v>
       </c>
       <c r="D668" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E668">
         <v>1.203864024011701</v>
@@ -34874,7 +34880,7 @@
         <v>1.036320896056939</v>
       </c>
       <c r="D669" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E669">
         <v>1.203864024011701</v>
@@ -34924,7 +34930,7 @@
         <v>1.008505471666571</v>
       </c>
       <c r="D670" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E670">
         <v>1.203864024011701</v>
@@ -34974,7 +34980,7 @@
         <v>1.030929082172957</v>
       </c>
       <c r="D671" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E671">
         <v>1.203864024011701</v>
@@ -35024,7 +35030,7 @@
         <v>1.040417750840599</v>
       </c>
       <c r="D672" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E672">
         <v>0.9957763031857296</v>
@@ -35110,7 +35116,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35160,7 +35166,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35210,7 +35216,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35260,7 +35266,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35274,7 +35280,7 @@
         <v>1.019721542843001</v>
       </c>
       <c r="D677" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E677">
         <v>1.230367111793835</v>
@@ -35310,7 +35316,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35324,7 +35330,7 @@
         <v>1.033151923746106</v>
       </c>
       <c r="D678" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E678">
         <v>1.222303818646338</v>
@@ -35360,7 +35366,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35374,7 +35380,7 @@
         <v>1.020455718354215</v>
       </c>
       <c r="D679" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E679">
         <v>1.222303818646338</v>
@@ -35410,7 +35416,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35424,7 +35430,7 @@
         <v>1.053594956548007</v>
       </c>
       <c r="D680" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E680">
         <v>1.222303818646338</v>
@@ -35460,7 +35466,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35474,7 +35480,7 @@
         <v>1.026468375060656</v>
       </c>
       <c r="D681" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E681">
         <v>1.222303818646338</v>
@@ -35510,7 +35516,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35524,7 +35530,7 @@
         <v>1.049898755963761</v>
       </c>
       <c r="D682" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E682">
         <v>1.222303818646338</v>
@@ -35560,7 +35566,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35574,7 +35580,7 @@
         <v>1.060924074184289</v>
       </c>
       <c r="D683" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E683">
         <v>1.017873442550878</v>
@@ -35610,7 +35616,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35824,7 +35830,7 @@
         <v>1.047332978384417</v>
       </c>
       <c r="D688" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E688">
         <v>1.257203736644038</v>
@@ -35874,7 +35880,7 @@
         <v>1.062101668663253</v>
       </c>
       <c r="D689" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E689">
         <v>1.2468160114229</v>
@@ -35924,7 +35930,7 @@
         <v>1.046094908499815</v>
       </c>
       <c r="D690" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E690">
         <v>1.2468160114229</v>
@@ -35974,7 +35980,7 @@
         <v>1.076557527942143</v>
       </c>
       <c r="D691" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E691">
         <v>1.2468160114229</v>
@@ -36024,7 +36030,7 @@
         <v>1.050346631817136</v>
       </c>
       <c r="D692" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E692">
         <v>1.2468160114229</v>
@@ -36074,7 +36080,7 @@
         <v>1.075115322095972</v>
       </c>
       <c r="D693" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E693">
         <v>1.2468160114229</v>
@@ -36124,7 +36130,7 @@
         <v>1.043673116249803</v>
       </c>
       <c r="D694" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E694">
         <v>1.123802357990182</v>
@@ -36174,7 +36180,7 @@
         <v>3.139280458423625</v>
       </c>
       <c r="D695" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E695">
         <v>3.025106410332782</v>
@@ -36210,7 +36216,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36224,7 +36230,7 @@
         <v>3.093454506514468</v>
       </c>
       <c r="D696" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E696">
         <v>3.025106410332782</v>
@@ -36260,7 +36266,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36274,7 +36280,7 @@
         <v>3.013365929424353</v>
       </c>
       <c r="D697" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E697">
         <v>3.025106410332782</v>
@@ -36310,7 +36316,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36324,7 +36330,7 @@
         <v>3.208498795059524</v>
       </c>
       <c r="D698" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E698">
         <v>3.025106410332782</v>
@@ -36360,7 +36366,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36371,40 +36377,40 @@
         <v>145</v>
       </c>
       <c r="C699">
-        <v>-0.8680274779434312</v>
+        <v>-0.4468731812388809</v>
       </c>
       <c r="D699" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E699">
-        <v>-0.6877989173683101</v>
+        <v>-0.1116839264191301</v>
       </c>
       <c r="F699">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G699">
-        <v>0.01126802747794343</v>
+        <v>0.01094687318123888</v>
       </c>
       <c r="H699">
-        <v>0.01132779891736831</v>
+        <v>0.01197168392641913</v>
       </c>
       <c r="I699">
-        <v>0.180228560575121</v>
+        <v>-0.3351892548197508</v>
       </c>
       <c r="J699">
-        <v>1.505714014378023</v>
+        <v>1.4991771529576</v>
       </c>
       <c r="K699">
+        <v>3.8</v>
+      </c>
+      <c r="L699">
+        <v>5.25</v>
+      </c>
+      <c r="M699">
         <v>4.03</v>
       </c>
-      <c r="L699">
-        <v>5.2</v>
-      </c>
-      <c r="M699">
-        <v>3.99</v>
-      </c>
       <c r="N699">
-        <v>5.32</v>
+        <v>5.93</v>
       </c>
       <c r="O699">
         <v>1</v>
@@ -36415,52 +36421,52 @@
     </row>
     <row r="700" spans="1:16">
       <c r="A700" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B700" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C700">
-        <v>-0.9009851279686432</v>
+        <v>-0.3169225520614258</v>
       </c>
       <c r="D700" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E700">
-        <v>-0.7204294443163484</v>
+        <v>-0.1116839264191301</v>
       </c>
       <c r="F700">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G700">
-        <v>0.01130098512796864</v>
+        <v>0.01089692255206143</v>
       </c>
       <c r="H700">
-        <v>0.01136042944431635</v>
+        <v>0.01197168392641913</v>
       </c>
       <c r="I700">
-        <v>0.1805556836522948</v>
+        <v>-0.2052386256422958</v>
       </c>
       <c r="J700">
-        <v>1.513892091307355</v>
+        <v>1.4991771529576</v>
       </c>
       <c r="K700">
+        <v>3.74</v>
+      </c>
+      <c r="L700">
+        <v>5.29</v>
+      </c>
+      <c r="M700">
         <v>4.03</v>
       </c>
-      <c r="L700">
-        <v>5.2</v>
-      </c>
-      <c r="M700">
-        <v>3.99</v>
-      </c>
       <c r="N700">
-        <v>5.32</v>
+        <v>5.93</v>
       </c>
       <c r="O700">
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36471,46 +36477,46 @@
         <v>145</v>
       </c>
       <c r="C701">
-        <v>-0.9337099119674415</v>
+        <v>-0.4717132546364855</v>
       </c>
       <c r="D701" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E701">
-        <v>-0.7528294165632978</v>
+        <v>-0.1380274779434316</v>
       </c>
       <c r="F701">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G701">
-        <v>0.01133370991196744</v>
+        <v>0.01097171325463649</v>
       </c>
       <c r="H701">
-        <v>0.0113928294165633</v>
+        <v>0.01199802747794343</v>
       </c>
       <c r="I701">
-        <v>0.1808804954041436</v>
+        <v>-0.3336857766930539</v>
       </c>
       <c r="J701">
-        <v>1.522012385103583</v>
+        <v>1.505714014378023</v>
       </c>
       <c r="K701">
+        <v>3.8</v>
+      </c>
+      <c r="L701">
+        <v>5.25</v>
+      </c>
+      <c r="M701">
         <v>4.03</v>
       </c>
-      <c r="L701">
-        <v>5.2</v>
-      </c>
-      <c r="M701">
-        <v>3.99</v>
-      </c>
       <c r="N701">
-        <v>5.32</v>
+        <v>5.93</v>
       </c>
       <c r="O701">
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36521,46 +36527,46 @@
         <v>146</v>
       </c>
       <c r="C702">
-        <v>-0.5336470633936168</v>
+        <v>-0.3413704137738049</v>
       </c>
       <c r="D702" t="s">
         <v>253</v>
       </c>
       <c r="E702">
-        <v>-0.4023263202874023</v>
+        <v>-0.1380274779434316</v>
       </c>
       <c r="F702">
         <v>-1</v>
       </c>
       <c r="G702">
-        <v>0.01103364706339362</v>
+        <v>0.0109213704137738</v>
       </c>
       <c r="H702">
-        <v>0.0109823263202874</v>
+        <v>0.01199802747794343</v>
       </c>
       <c r="I702">
-        <v>-0.1313207431062144</v>
+        <v>-0.2033429358303733</v>
       </c>
       <c r="J702">
-        <v>1.522012385103583</v>
+        <v>1.505714014378023</v>
       </c>
       <c r="K702">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="L702">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="M702">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N702">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O702">
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36571,28 +36577,28 @@
         <v>147</v>
       </c>
       <c r="C703">
-        <v>-0.9721715677020031</v>
+        <v>-0.9016808854046587</v>
       </c>
       <c r="D703" t="s">
         <v>254</v>
       </c>
       <c r="E703">
-        <v>-0.7973480052376649</v>
+        <v>-0.6555683652294215</v>
       </c>
       <c r="F703">
         <v>1</v>
       </c>
       <c r="G703">
-        <v>0.012612171567702</v>
+        <v>0.01254168088540466</v>
       </c>
       <c r="H703">
-        <v>0.01177734800523767</v>
+        <v>0.01145556836522942</v>
       </c>
       <c r="I703">
-        <v>0.1748235624643382</v>
+        <v>0.2461125201752372</v>
       </c>
       <c r="J703">
-        <v>1.529768371104055</v>
+        <v>1.513892091307355</v>
       </c>
       <c r="K703">
         <v>4.44</v>
@@ -36601,16 +36607,16 @@
         <v>5.82</v>
       </c>
       <c r="M703">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="N703">
-        <v>5.49</v>
+        <v>5.4</v>
       </c>
       <c r="O703">
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36618,31 +36624,31 @@
         <v>1</v>
       </c>
       <c r="B704" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C704">
-        <v>-0.9649665355493404</v>
+        <v>-0.9009851279686432</v>
       </c>
       <c r="D704" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E704">
-        <v>-0.783775800705178</v>
+        <v>-0.6555683652294215</v>
       </c>
       <c r="F704">
         <v>1</v>
       </c>
       <c r="G704">
-        <v>0.01136496653554934</v>
+        <v>0.01130098512796864</v>
       </c>
       <c r="H704">
-        <v>0.01142377580070518</v>
+        <v>0.01145556836522942</v>
       </c>
       <c r="I704">
-        <v>0.1811907348441624</v>
+        <v>0.2454167627392216</v>
       </c>
       <c r="J704">
-        <v>1.529768371104055</v>
+        <v>1.513892091307355</v>
       </c>
       <c r="K704">
         <v>4.03</v>
@@ -36651,16 +36657,16 @@
         <v>5.2</v>
       </c>
       <c r="M704">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="N704">
-        <v>5.32</v>
+        <v>5.4</v>
       </c>
       <c r="O704">
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36668,31 +36674,31 @@
         <v>2</v>
       </c>
       <c r="B705" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C705">
-        <v>-0.5631198101954071</v>
+        <v>-0.5027899469679502</v>
       </c>
       <c r="D705" t="s">
         <v>253</v>
       </c>
       <c r="E705">
-        <v>-0.4313337079291646</v>
+        <v>-0.1709851279686436</v>
       </c>
       <c r="F705">
         <v>-1</v>
       </c>
       <c r="G705">
-        <v>0.01106311981019541</v>
+        <v>0.01100278994696795</v>
       </c>
       <c r="H705">
-        <v>0.01101133370792916</v>
+        <v>0.01203098512796864</v>
       </c>
       <c r="I705">
-        <v>-0.1317861022662425</v>
+        <v>-0.3318048189993066</v>
       </c>
       <c r="J705">
-        <v>1.529768371104055</v>
+        <v>1.513892091307355</v>
       </c>
       <c r="K705">
         <v>3.8</v>
@@ -36701,16 +36707,16 @@
         <v>5.25</v>
       </c>
       <c r="M705">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N705">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O705">
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36718,49 +36724,49 @@
         <v>3</v>
       </c>
       <c r="B706" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C706">
-        <v>-0.6249059124616503</v>
+        <v>-0.3719564214895099</v>
       </c>
       <c r="D706" t="s">
         <v>253</v>
       </c>
       <c r="E706">
-        <v>-0.4313337079291646</v>
+        <v>-0.1709851279686436</v>
       </c>
       <c r="F706">
         <v>-1</v>
       </c>
       <c r="G706">
-        <v>0.01118490591246165</v>
+        <v>0.01095195642148951</v>
       </c>
       <c r="H706">
-        <v>0.01101133370792916</v>
+        <v>0.01203098512796864</v>
       </c>
       <c r="I706">
-        <v>-0.1935722045324857</v>
+        <v>-0.2009712935208663</v>
       </c>
       <c r="J706">
-        <v>1.529768371104055</v>
+        <v>1.513892091307355</v>
       </c>
       <c r="K706">
-        <v>3.86</v>
+        <v>3.74</v>
       </c>
       <c r="L706">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="M706">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N706">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O706">
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36768,49 +36774,49 @@
         <v>0</v>
       </c>
       <c r="B707" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C707">
-        <v>-0.9919728003746338</v>
+        <v>-0.9377349898599103</v>
       </c>
       <c r="D707" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E707">
-        <v>-0.8105140132741413</v>
+        <v>-0.6880495404143332</v>
       </c>
       <c r="F707">
         <v>1</v>
       </c>
       <c r="G707">
-        <v>0.01139197280037463</v>
+        <v>0.01257773498985991</v>
       </c>
       <c r="H707">
-        <v>0.01145051401327414</v>
+        <v>0.01148804954041433</v>
       </c>
       <c r="I707">
-        <v>0.1814587871004925</v>
+        <v>0.2496854494455771</v>
       </c>
       <c r="J707">
-        <v>1.536469677512316</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K707">
-        <v>4.03</v>
+        <v>4.44</v>
       </c>
       <c r="L707">
-        <v>5.2</v>
+        <v>5.82</v>
       </c>
       <c r="M707">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="N707">
-        <v>5.32</v>
+        <v>5.4</v>
       </c>
       <c r="O707">
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>147</v>
+        <v>354</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36818,49 +36824,49 @@
         <v>1</v>
       </c>
       <c r="B708" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C708">
-        <v>-0.5885847745468009</v>
+        <v>-0.9337099119674415</v>
       </c>
       <c r="D708" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E708">
-        <v>-0.4563965938960628</v>
+        <v>-0.6880495404143332</v>
       </c>
       <c r="F708">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G708">
-        <v>0.0110885847745468</v>
+        <v>0.01133370991196744</v>
       </c>
       <c r="H708">
-        <v>0.01103639659389606</v>
+        <v>0.01148804954041433</v>
       </c>
       <c r="I708">
-        <v>-0.1321881806507381</v>
+        <v>0.2456603715531083</v>
       </c>
       <c r="J708">
-        <v>1.536469677512316</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K708">
-        <v>3.8</v>
+        <v>4.03</v>
       </c>
       <c r="L708">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="M708">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="N708">
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="O708">
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>147</v>
+        <v>354</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -36868,181 +36874,181 @@
         <v>2</v>
       </c>
       <c r="B709" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C709">
-        <v>-0.6507729551975396</v>
+        <v>-0.5336470633936168</v>
       </c>
       <c r="D709" t="s">
         <v>253</v>
       </c>
       <c r="E709">
-        <v>-0.4563965938960628</v>
+        <v>-0.2037099119674419</v>
       </c>
       <c r="F709">
         <v>-1</v>
       </c>
       <c r="G709">
-        <v>0.01121077295519754</v>
+        <v>0.01103364706339362</v>
       </c>
       <c r="H709">
-        <v>0.01103639659389606</v>
+        <v>0.01206370991196744</v>
       </c>
       <c r="I709">
-        <v>-0.1943763613014768</v>
+        <v>-0.3299371514261749</v>
       </c>
       <c r="J709">
-        <v>1.536469677512316</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K709">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="L709">
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="M709">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N709">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O709">
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>147</v>
+        <v>354</v>
       </c>
     </row>
     <row r="710" spans="1:16">
       <c r="A710" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B710" t="s">
         <v>146</v>
       </c>
       <c r="C710">
-        <v>-0.6252147732090361</v>
+        <v>-0.4023263202874023</v>
       </c>
       <c r="D710" t="s">
         <v>253</v>
       </c>
       <c r="E710">
-        <v>-0.4924482241583679</v>
+        <v>-0.2037099119674419</v>
       </c>
       <c r="F710">
         <v>-1</v>
       </c>
       <c r="G710">
-        <v>0.01112521477320904</v>
+        <v>0.0109823263202874</v>
       </c>
       <c r="H710">
-        <v>0.01107244822415837</v>
+        <v>0.01206370991196744</v>
       </c>
       <c r="I710">
-        <v>-0.1327665490506682</v>
+        <v>-0.1986164083199604</v>
       </c>
       <c r="J710">
-        <v>1.546109150844483</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K710">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="L710">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="M710">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N710">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O710">
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>254</v>
+        <v>354</v>
       </c>
     </row>
     <row r="711" spans="1:16">
       <c r="A711" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B711" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C711">
-        <v>-0.6879813222597049</v>
+        <v>-0.9721715677020031</v>
       </c>
       <c r="D711" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E711">
-        <v>-0.4924482241583679</v>
+        <v>-0.7190734844162181</v>
       </c>
       <c r="F711">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G711">
-        <v>0.0112479813222597</v>
+        <v>0.012612171567702</v>
       </c>
       <c r="H711">
-        <v>0.01107244822415837</v>
+        <v>0.01151907348441622</v>
       </c>
       <c r="I711">
-        <v>-0.195533098101337</v>
+        <v>0.253098083285785</v>
       </c>
       <c r="J711">
-        <v>1.546109150844483</v>
+        <v>1.529768371104055</v>
       </c>
       <c r="K711">
-        <v>3.86</v>
+        <v>4.44</v>
       </c>
       <c r="L711">
-        <v>5.28</v>
+        <v>5.82</v>
       </c>
       <c r="M711">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="N711">
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="O711">
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>254</v>
+        <v>355</v>
       </c>
     </row>
     <row r="712" spans="1:16">
       <c r="A712" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B712" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C712">
-        <v>-1.064082889548082</v>
+        <v>-0.9649665355493404</v>
       </c>
       <c r="D712" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E712">
-        <v>-0.8819083695525682</v>
+        <v>-0.7190734844162181</v>
       </c>
       <c r="F712">
         <v>1</v>
       </c>
       <c r="G712">
-        <v>0.01146408288954808</v>
+        <v>0.01136496653554934</v>
       </c>
       <c r="H712">
-        <v>0.01152190836955257</v>
+        <v>0.01151907348441622</v>
       </c>
       <c r="I712">
-        <v>0.182174519995514</v>
+        <v>0.2458930511331223</v>
       </c>
       <c r="J712">
-        <v>1.554362999887862</v>
+        <v>1.529768371104055</v>
       </c>
       <c r="K712">
         <v>4.03</v>
@@ -37051,10 +37057,10 @@
         <v>5.2</v>
       </c>
       <c r="M712">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="N712">
-        <v>5.32</v>
+        <v>5.4</v>
       </c>
       <c r="O712">
         <v>1</v>
@@ -37065,34 +37071,34 @@
     </row>
     <row r="713" spans="1:16">
       <c r="A713" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B713" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C713">
-        <v>-0.6565793995738742</v>
+        <v>-0.5631198101954071</v>
       </c>
       <c r="D713" t="s">
         <v>253</v>
       </c>
       <c r="E713">
-        <v>-0.5233176195806024</v>
+        <v>-0.2349665355493409</v>
       </c>
       <c r="F713">
         <v>-1</v>
       </c>
       <c r="G713">
-        <v>0.01115657939957388</v>
+        <v>0.01106311981019541</v>
       </c>
       <c r="H713">
-        <v>0.0111033176195806</v>
+        <v>0.01209496653554934</v>
       </c>
       <c r="I713">
-        <v>-0.1332617799932718</v>
+        <v>-0.3281532746460663</v>
       </c>
       <c r="J713">
-        <v>1.554362999887862</v>
+        <v>1.529768371104055</v>
       </c>
       <c r="K713">
         <v>3.8</v>
@@ -37101,10 +37107,10 @@
         <v>5.25</v>
       </c>
       <c r="M713">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N713">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O713">
         <v>1</v>
@@ -37115,46 +37121,46 @@
     </row>
     <row r="714" spans="1:16">
       <c r="A714" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B714" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C714">
-        <v>-0.7198411795671458</v>
+        <v>-0.4313337079291646</v>
       </c>
       <c r="D714" t="s">
         <v>253</v>
       </c>
       <c r="E714">
-        <v>-0.5233176195806024</v>
+        <v>-0.2349665355493409</v>
       </c>
       <c r="F714">
         <v>-1</v>
       </c>
       <c r="G714">
-        <v>0.01127984117956715</v>
+        <v>0.01101133370792916</v>
       </c>
       <c r="H714">
-        <v>0.0111033176195806</v>
+        <v>0.01209496653554934</v>
       </c>
       <c r="I714">
-        <v>-0.1965235599865434</v>
+        <v>-0.1963671723798237</v>
       </c>
       <c r="J714">
-        <v>1.554362999887862</v>
+        <v>1.529768371104055</v>
       </c>
       <c r="K714">
-        <v>3.86</v>
+        <v>3.74</v>
       </c>
       <c r="L714">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="M714">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N714">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O714">
         <v>1</v>
@@ -37168,31 +37174,31 @@
         <v>0</v>
       </c>
       <c r="B715" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C715">
-        <v>-1.103231291701239</v>
+        <v>-0.9919728003746338</v>
       </c>
       <c r="D715" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E715">
-        <v>-0.920668201957306</v>
+        <v>-0.7458787100492641</v>
       </c>
       <c r="F715">
         <v>1</v>
       </c>
       <c r="G715">
-        <v>0.01150323129170124</v>
+        <v>0.01139197280037463</v>
       </c>
       <c r="H715">
-        <v>0.01156066820195731</v>
+        <v>0.01154587871004927</v>
       </c>
       <c r="I715">
-        <v>0.1825630897439332</v>
+        <v>0.2460940903253697</v>
       </c>
       <c r="J715">
-        <v>1.564077243598322</v>
+        <v>1.536469677512316</v>
       </c>
       <c r="K715">
         <v>4.03</v>
@@ -37201,16 +37207,16 @@
         <v>5.2</v>
       </c>
       <c r="M715">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="N715">
-        <v>5.32</v>
+        <v>5.4</v>
       </c>
       <c r="O715">
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>356</v>
+        <v>147</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37218,31 +37224,31 @@
         <v>1</v>
       </c>
       <c r="B716" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C716">
-        <v>-0.6934935256736248</v>
+        <v>-0.5885847745468009</v>
       </c>
       <c r="D716" t="s">
         <v>253</v>
       </c>
       <c r="E716">
-        <v>-0.5596488910577255</v>
+        <v>-0.2619728003746342</v>
       </c>
       <c r="F716">
         <v>-1</v>
       </c>
       <c r="G716">
-        <v>0.01119349352567362</v>
+        <v>0.0110885847745468</v>
       </c>
       <c r="H716">
-        <v>0.01113964889105772</v>
+        <v>0.01212197280037463</v>
       </c>
       <c r="I716">
-        <v>-0.1338446346158992</v>
+        <v>-0.3266119741721667</v>
       </c>
       <c r="J716">
-        <v>1.564077243598322</v>
+        <v>1.536469677512316</v>
       </c>
       <c r="K716">
         <v>3.8</v>
@@ -37251,16 +37257,16 @@
         <v>5.25</v>
       </c>
       <c r="M716">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N716">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O716">
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>356</v>
+        <v>147</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37268,49 +37274,49 @@
         <v>2</v>
       </c>
       <c r="B717" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C717">
-        <v>-0.7573381602895237</v>
+        <v>-0.4563965938960628</v>
       </c>
       <c r="D717" t="s">
         <v>253</v>
       </c>
       <c r="E717">
-        <v>-0.5596488910577255</v>
+        <v>-0.2619728003746342</v>
       </c>
       <c r="F717">
         <v>-1</v>
       </c>
       <c r="G717">
-        <v>0.01131733816028952</v>
+        <v>0.01103639659389606</v>
       </c>
       <c r="H717">
-        <v>0.01113964889105772</v>
+        <v>0.01212197280037463</v>
       </c>
       <c r="I717">
-        <v>-0.1976892692317982</v>
+        <v>-0.1944237935214286</v>
       </c>
       <c r="J717">
-        <v>1.564077243598322</v>
+        <v>1.536469677512316</v>
       </c>
       <c r="K717">
-        <v>3.86</v>
+        <v>3.74</v>
       </c>
       <c r="L717">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="M717">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N717">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O717">
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>356</v>
+        <v>147</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37318,31 +37324,31 @@
         <v>0</v>
       </c>
       <c r="B718" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C718">
-        <v>-1.149128838391547</v>
+        <v>-1.030819877903268</v>
       </c>
       <c r="D718" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E718">
-        <v>-0.9661101898715314</v>
+        <v>-0.7844366033779329</v>
       </c>
       <c r="F718">
         <v>1</v>
       </c>
       <c r="G718">
-        <v>0.01154912883839155</v>
+        <v>0.01143081987790327</v>
       </c>
       <c r="H718">
-        <v>0.01160611018987153</v>
+        <v>0.01158443660337793</v>
       </c>
       <c r="I718">
-        <v>0.1830186485200151</v>
+        <v>0.2463832745253347</v>
       </c>
       <c r="J718">
-        <v>1.575466213000384</v>
+        <v>1.546109150844483</v>
       </c>
       <c r="K718">
         <v>4.03</v>
@@ -37351,16 +37357,16 @@
         <v>5.2</v>
       </c>
       <c r="M718">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="N718">
-        <v>5.32</v>
+        <v>5.4</v>
       </c>
       <c r="O718">
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37368,31 +37374,31 @@
         <v>1</v>
       </c>
       <c r="B719" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C719">
-        <v>-0.7367716094014582</v>
+        <v>-0.6252147732090361</v>
       </c>
       <c r="D719" t="s">
         <v>253</v>
       </c>
       <c r="E719">
-        <v>-0.6022436366214361</v>
+        <v>-0.300819877903268</v>
       </c>
       <c r="F719">
         <v>-1</v>
       </c>
       <c r="G719">
-        <v>0.01123677160940146</v>
+        <v>0.01112521477320904</v>
       </c>
       <c r="H719">
-        <v>0.01118224363662144</v>
+        <v>0.01216081987790327</v>
       </c>
       <c r="I719">
-        <v>-0.1345279727800222</v>
+        <v>-0.324394895305768</v>
       </c>
       <c r="J719">
-        <v>1.575466213000384</v>
+        <v>1.546109150844483</v>
       </c>
       <c r="K719">
         <v>3.8</v>
@@ -37401,16 +37407,16 @@
         <v>5.25</v>
       </c>
       <c r="M719">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N719">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O719">
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37418,49 +37424,49 @@
         <v>2</v>
       </c>
       <c r="B720" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C720">
-        <v>-0.801299582181481</v>
+        <v>-0.4924482241583679</v>
       </c>
       <c r="D720" t="s">
         <v>253</v>
       </c>
       <c r="E720">
-        <v>-0.6022436366214361</v>
+        <v>-0.300819877903268</v>
       </c>
       <c r="F720">
         <v>-1</v>
       </c>
       <c r="G720">
-        <v>0.01136129958218148</v>
+        <v>0.01107244822415837</v>
       </c>
       <c r="H720">
-        <v>0.01118224363662144</v>
+        <v>0.01216081987790327</v>
       </c>
       <c r="I720">
-        <v>-0.1990559455600449</v>
+        <v>-0.1916283462550998</v>
       </c>
       <c r="J720">
-        <v>1.575466213000384</v>
+        <v>1.546109150844483</v>
       </c>
       <c r="K720">
-        <v>3.86</v>
+        <v>3.74</v>
       </c>
       <c r="L720">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="M720">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N720">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O720">
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37468,49 +37474,49 @@
         <v>0</v>
       </c>
       <c r="B721" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C721">
-        <v>-0.7795499935360137</v>
+        <v>-1.064082889548082</v>
       </c>
       <c r="D721" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E721">
-        <v>-0.6443465725854463</v>
+        <v>-0.8174519995514462</v>
       </c>
       <c r="F721">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G721">
-        <v>0.01127954999353601</v>
+        <v>0.01146408288954808</v>
       </c>
       <c r="H721">
-        <v>0.01122434657258545</v>
+        <v>0.01161745199955145</v>
       </c>
       <c r="I721">
-        <v>-0.1352034209505675</v>
+        <v>0.2466308899966361</v>
       </c>
       <c r="J721">
-        <v>1.586723682509477</v>
+        <v>1.554362999887862</v>
       </c>
       <c r="K721">
-        <v>3.8</v>
+        <v>4.03</v>
       </c>
       <c r="L721">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="M721">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="N721">
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="O721">
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37518,49 +37524,49 @@
         <v>1</v>
       </c>
       <c r="B722" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C722">
-        <v>-0.8447534144865827</v>
+        <v>-0.5233176195806024</v>
       </c>
       <c r="D722" t="s">
         <v>253</v>
       </c>
       <c r="E722">
-        <v>-0.6443465725854463</v>
+        <v>-0.3340828895480827</v>
       </c>
       <c r="F722">
         <v>-1</v>
       </c>
       <c r="G722">
-        <v>0.01140475341448658</v>
+        <v>0.0111033176195806</v>
       </c>
       <c r="H722">
-        <v>0.01122434657258545</v>
+        <v>0.01219408288954808</v>
       </c>
       <c r="I722">
-        <v>-0.2004068419011364</v>
+        <v>-0.1892347300325197</v>
       </c>
       <c r="J722">
-        <v>1.586723682509477</v>
+        <v>1.554362999887862</v>
       </c>
       <c r="K722">
-        <v>3.86</v>
+        <v>3.74</v>
       </c>
       <c r="L722">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="M722">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N722">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O722">
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37568,99 +37574,99 @@
         <v>0</v>
       </c>
       <c r="B723" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C723">
-        <v>-0.8342358932749292</v>
+        <v>-1.103231291701239</v>
       </c>
       <c r="D723" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E723">
-        <v>-0.6981690107495364</v>
+        <v>-0.856308974393289</v>
       </c>
       <c r="F723">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G723">
-        <v>0.01133423589327493</v>
+        <v>0.01150323129170124</v>
       </c>
       <c r="H723">
-        <v>0.01127816901074954</v>
+        <v>0.01165630897439329</v>
       </c>
       <c r="I723">
-        <v>-0.1360668825253928</v>
+        <v>0.2469223173079502</v>
       </c>
       <c r="J723">
-        <v>1.60111470875656</v>
+        <v>1.564077243598322</v>
       </c>
       <c r="K723">
-        <v>3.8</v>
+        <v>4.03</v>
       </c>
       <c r="L723">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="M723">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="N723">
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="O723">
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="724" spans="1:16">
       <c r="A724" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B724" t="s">
         <v>146</v>
       </c>
       <c r="C724">
-        <v>-0.8884988382857681</v>
+        <v>-0.5596488910577255</v>
       </c>
       <c r="D724" t="s">
         <v>253</v>
       </c>
       <c r="E724">
-        <v>-0.7515751724180992</v>
+        <v>-0.3732312917012397</v>
       </c>
       <c r="F724">
         <v>-1</v>
       </c>
       <c r="G724">
-        <v>0.01138849883828577</v>
+        <v>0.01113964889105772</v>
       </c>
       <c r="H724">
-        <v>0.0113315751724181</v>
+        <v>0.01223323129170124</v>
       </c>
       <c r="I724">
-        <v>-0.1369236658676689</v>
+        <v>-0.1864175993564858</v>
       </c>
       <c r="J724">
-        <v>1.615394431127834</v>
+        <v>1.564077243598322</v>
       </c>
       <c r="K724">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="L724">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="M724">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N724">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O724">
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -37668,37 +37674,37 @@
         <v>0</v>
       </c>
       <c r="B725" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C725">
-        <v>-1.282472551736361</v>
+        <v>-1.149128838391547</v>
       </c>
       <c r="D725" t="s">
         <v>255</v>
       </c>
       <c r="E725">
-        <v>-1.10247255173636</v>
+        <v>-0.9018648520015349</v>
       </c>
       <c r="F725">
         <v>1</v>
       </c>
       <c r="G725">
-        <v>0.01172247255173636</v>
+        <v>0.01154912883839155</v>
       </c>
       <c r="H725">
-        <v>0.01190247255173636</v>
+        <v>0.01170186485200153</v>
       </c>
       <c r="I725">
-        <v>0.1800000000000006</v>
+        <v>0.2472639863900117</v>
       </c>
       <c r="J725">
-        <v>1.62561813793409</v>
+        <v>1.575466213000384</v>
       </c>
       <c r="K725">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="L725">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="M725">
         <v>4</v>
@@ -37710,7 +37716,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>145</v>
+        <v>254</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -37721,46 +37727,46 @@
         <v>146</v>
       </c>
       <c r="C726">
-        <v>-0.9273489241495421</v>
+        <v>-0.6022436366214361</v>
       </c>
       <c r="D726" t="s">
         <v>253</v>
       </c>
       <c r="E726">
-        <v>-0.7898118358734978</v>
+        <v>-0.419128838391547</v>
       </c>
       <c r="F726">
         <v>-1</v>
       </c>
       <c r="G726">
-        <v>0.01142734892414954</v>
+        <v>0.01118224363662144</v>
       </c>
       <c r="H726">
-        <v>0.0113698118358735</v>
+        <v>0.01227912883839155</v>
       </c>
       <c r="I726">
-        <v>-0.1375370882760443</v>
+        <v>-0.1831147982298891</v>
       </c>
       <c r="J726">
-        <v>1.62561813793409</v>
+        <v>1.575466213000384</v>
       </c>
       <c r="K726">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="L726">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="M726">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N726">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O726">
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>145</v>
+        <v>254</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -37768,99 +37774,99 @@
         <v>0</v>
       </c>
       <c r="B727" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C727">
-        <v>-0.9728832466399586</v>
+        <v>-1.194496440513195</v>
       </c>
       <c r="D727" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E727">
-        <v>-0.8346271953772231</v>
+        <v>-0.9468947300379096</v>
       </c>
       <c r="F727">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G727">
-        <v>0.01147288324663996</v>
+        <v>0.01159449644051319</v>
       </c>
       <c r="H727">
-        <v>0.01141462719537722</v>
+        <v>0.01174689473003791</v>
       </c>
       <c r="I727">
-        <v>-0.1382560512627355</v>
+        <v>0.2476017104752852</v>
       </c>
       <c r="J727">
-        <v>1.637600854378937</v>
+        <v>1.586723682509477</v>
       </c>
       <c r="K727">
-        <v>3.8</v>
+        <v>4.03</v>
       </c>
       <c r="L727">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="M727">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="N727">
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="O727">
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="728" spans="1:16">
       <c r="A728" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B728" t="s">
         <v>146</v>
       </c>
       <c r="C728">
-        <v>-1.024362108384423</v>
+        <v>-0.6443465725854463</v>
       </c>
       <c r="D728" t="s">
         <v>253</v>
       </c>
       <c r="E728">
-        <v>-0.8852932329888805</v>
+        <v>-0.4644964405131953</v>
       </c>
       <c r="F728">
         <v>-1</v>
       </c>
       <c r="G728">
-        <v>0.01152436210838442</v>
+        <v>0.01122434657258545</v>
       </c>
       <c r="H728">
-        <v>0.01146529323298888</v>
+        <v>0.01232449644051319</v>
       </c>
       <c r="I728">
-        <v>-0.1390688753955427</v>
+        <v>-0.179850132072251</v>
       </c>
       <c r="J728">
-        <v>1.651147923259059</v>
+        <v>1.586723682509477</v>
       </c>
       <c r="K728">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="L728">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="M728">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N728">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O728">
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>149</v>
+        <v>359</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -37868,99 +37874,99 @@
         <v>0</v>
       </c>
       <c r="B729" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C729">
-        <v>-1.380277958041175</v>
+        <v>-0.6981690107495364</v>
       </c>
       <c r="D729" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E729">
-        <v>-1.193732296336574</v>
+        <v>-0.522492276288939</v>
       </c>
       <c r="F729">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G729">
-        <v>0.01208027795804117</v>
+        <v>0.01127816901074954</v>
       </c>
       <c r="H729">
-        <v>0.01173373229633657</v>
+        <v>0.01238249227628894</v>
       </c>
       <c r="I729">
-        <v>0.1865456617046011</v>
+        <v>-0.1756767344605974</v>
       </c>
       <c r="J729">
-        <v>1.665910385653756</v>
+        <v>1.60111470875656</v>
       </c>
       <c r="K729">
-        <v>4.04</v>
+        <v>3.74</v>
       </c>
       <c r="L729">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="M729">
-        <v>3.88</v>
+        <v>4.03</v>
       </c>
       <c r="N729">
-        <v>5.27</v>
+        <v>5.93</v>
       </c>
       <c r="O729">
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="730" spans="1:16">
       <c r="A730" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B730" t="s">
         <v>146</v>
       </c>
       <c r="C730">
-        <v>-1.080459465484273</v>
+        <v>-0.7515751724180992</v>
       </c>
       <c r="D730" t="s">
         <v>253</v>
       </c>
       <c r="E730">
-        <v>-0.9405048423450477</v>
+        <v>-0.5800395574451711</v>
       </c>
       <c r="F730">
         <v>-1</v>
       </c>
       <c r="G730">
-        <v>0.01158045946548427</v>
+        <v>0.0113315751724181</v>
       </c>
       <c r="H730">
-        <v>0.01152050484234505</v>
+        <v>0.01244003955744517</v>
       </c>
       <c r="I730">
-        <v>-0.139954623139225</v>
+        <v>-0.1715356149729281</v>
       </c>
       <c r="J730">
-        <v>1.665910385653756</v>
+        <v>1.615394431127834</v>
       </c>
       <c r="K730">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="L730">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="M730">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N730">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O730">
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -37968,37 +37974,37 @@
         <v>0</v>
       </c>
       <c r="B731" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C731">
-        <v>-1.42715909512542</v>
+        <v>-1.282472551736361</v>
       </c>
       <c r="D731" t="s">
         <v>256</v>
       </c>
       <c r="E731">
-        <v>-1.238756754724413</v>
+        <v>-1.03739837518427</v>
       </c>
       <c r="F731">
         <v>1</v>
       </c>
       <c r="G731">
-        <v>0.01212715909512542</v>
+        <v>0.01172247255173636</v>
       </c>
       <c r="H731">
-        <v>0.01177875675472441</v>
+        <v>0.01157739837518427</v>
       </c>
       <c r="I731">
-        <v>0.1884023404010069</v>
+        <v>0.245074176552091</v>
       </c>
       <c r="J731">
-        <v>1.677514627506292</v>
+        <v>1.62561813793409</v>
       </c>
       <c r="K731">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="L731">
-        <v>5.35</v>
+        <v>5.22</v>
       </c>
       <c r="M731">
         <v>3.88</v>
@@ -38010,57 +38016,57 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>252</v>
+        <v>148</v>
       </c>
     </row>
     <row r="732" spans="1:16">
       <c r="A732" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B732" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C732">
-        <v>-1.46853878015609</v>
+        <v>-0.7898118358734978</v>
       </c>
       <c r="D732" t="s">
-        <v>146</v>
+        <v>253</v>
       </c>
       <c r="E732">
-        <v>-1.163477070443847</v>
+        <v>-0.6212410958743844</v>
       </c>
       <c r="F732">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G732">
-        <v>0.01216853878015609</v>
+        <v>0.0113698118358735</v>
       </c>
       <c r="H732">
-        <v>0.01166347707044385</v>
+        <v>0.01248124109587439</v>
       </c>
       <c r="I732">
-        <v>0.305061709712243</v>
+        <v>-0.1685707399991134</v>
       </c>
       <c r="J732">
-        <v>1.687757123801012</v>
+        <v>1.62561813793409</v>
       </c>
       <c r="K732">
-        <v>4.04</v>
+        <v>3.74</v>
       </c>
       <c r="L732">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="M732">
-        <v>3.8</v>
+        <v>4.03</v>
       </c>
       <c r="N732">
-        <v>5.25</v>
+        <v>5.93</v>
       </c>
       <c r="O732">
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>363</v>
+        <v>148</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38068,49 +38074,449 @@
         <v>0</v>
       </c>
       <c r="B733" t="s">
+        <v>146</v>
+      </c>
+      <c r="C733">
+        <v>-0.8346271953772231</v>
+      </c>
+      <c r="D733" t="s">
+        <v>253</v>
+      </c>
+      <c r="E733">
+        <v>-0.6695314431471155</v>
+      </c>
+      <c r="F733">
+        <v>-1</v>
+      </c>
+      <c r="G733">
+        <v>0.01141462719537722</v>
+      </c>
+      <c r="H733">
+        <v>0.01252953144314711</v>
+      </c>
+      <c r="I733">
+        <v>-0.1650957522301075</v>
+      </c>
+      <c r="J733">
+        <v>1.637600854378937</v>
+      </c>
+      <c r="K733">
+        <v>3.74</v>
+      </c>
+      <c r="L733">
+        <v>5.29</v>
+      </c>
+      <c r="M733">
+        <v>4.03</v>
+      </c>
+      <c r="N733">
+        <v>5.93</v>
+      </c>
+      <c r="O733">
+        <v>1</v>
+      </c>
+      <c r="P733" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="734" spans="1:16">
+      <c r="A734" s="1">
+        <v>0</v>
+      </c>
+      <c r="B734" t="s">
+        <v>146</v>
+      </c>
+      <c r="C734">
+        <v>-0.8852932329888805</v>
+      </c>
+      <c r="D734" t="s">
+        <v>253</v>
+      </c>
+      <c r="E734">
+        <v>-0.7241261307340077</v>
+      </c>
+      <c r="F734">
+        <v>-1</v>
+      </c>
+      <c r="G734">
+        <v>0.01146529323298888</v>
+      </c>
+      <c r="H734">
+        <v>0.01258412613073401</v>
+      </c>
+      <c r="I734">
+        <v>-0.1611671022548729</v>
+      </c>
+      <c r="J734">
+        <v>1.651147923259059</v>
+      </c>
+      <c r="K734">
+        <v>3.74</v>
+      </c>
+      <c r="L734">
+        <v>5.29</v>
+      </c>
+      <c r="M734">
+        <v>4.03</v>
+      </c>
+      <c r="N734">
+        <v>5.93</v>
+      </c>
+      <c r="O734">
+        <v>1</v>
+      </c>
+      <c r="P734" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="735" spans="1:16">
+      <c r="A735" s="1">
+        <v>0</v>
+      </c>
+      <c r="B735" t="s">
         <v>150</v>
       </c>
-      <c r="C733">
+      <c r="C735">
+        <v>-1.380277958041175</v>
+      </c>
+      <c r="D735" t="s">
+        <v>145</v>
+      </c>
+      <c r="E735">
+        <v>-1.080459465484273</v>
+      </c>
+      <c r="F735">
+        <v>1</v>
+      </c>
+      <c r="G735">
+        <v>0.01208027795804117</v>
+      </c>
+      <c r="H735">
+        <v>0.01158045946548427</v>
+      </c>
+      <c r="I735">
+        <v>0.2998184925569021</v>
+      </c>
+      <c r="J735">
+        <v>1.665910385653756</v>
+      </c>
+      <c r="K735">
+        <v>4.04</v>
+      </c>
+      <c r="L735">
+        <v>5.35</v>
+      </c>
+      <c r="M735">
+        <v>3.8</v>
+      </c>
+      <c r="N735">
+        <v>5.25</v>
+      </c>
+      <c r="O735">
+        <v>1</v>
+      </c>
+      <c r="P735" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="736" spans="1:16">
+      <c r="A736" s="1">
+        <v>1</v>
+      </c>
+      <c r="B736" t="s">
+        <v>146</v>
+      </c>
+      <c r="C736">
+        <v>-0.9405048423450477</v>
+      </c>
+      <c r="D736" t="s">
+        <v>253</v>
+      </c>
+      <c r="E736">
+        <v>-0.7836188541846374</v>
+      </c>
+      <c r="F736">
+        <v>-1</v>
+      </c>
+      <c r="G736">
+        <v>0.01152050484234505</v>
+      </c>
+      <c r="H736">
+        <v>0.01264361885418464</v>
+      </c>
+      <c r="I736">
+        <v>-0.1568859881604103</v>
+      </c>
+      <c r="J736">
+        <v>1.665910385653756</v>
+      </c>
+      <c r="K736">
+        <v>3.74</v>
+      </c>
+      <c r="L736">
+        <v>5.29</v>
+      </c>
+      <c r="M736">
+        <v>4.03</v>
+      </c>
+      <c r="N736">
+        <v>5.93</v>
+      </c>
+      <c r="O736">
+        <v>1</v>
+      </c>
+      <c r="P736" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="737" spans="1:16">
+      <c r="A737" s="1">
+        <v>0</v>
+      </c>
+      <c r="B737" t="s">
+        <v>150</v>
+      </c>
+      <c r="C737">
+        <v>-1.42715909512542</v>
+      </c>
+      <c r="D737" t="s">
+        <v>145</v>
+      </c>
+      <c r="E737">
+        <v>-1.124555584523909</v>
+      </c>
+      <c r="F737">
+        <v>1</v>
+      </c>
+      <c r="G737">
+        <v>0.01212715909512542</v>
+      </c>
+      <c r="H737">
+        <v>0.01162455558452391</v>
+      </c>
+      <c r="I737">
+        <v>0.3026035106015108</v>
+      </c>
+      <c r="J737">
+        <v>1.677514627506292</v>
+      </c>
+      <c r="K737">
+        <v>4.04</v>
+      </c>
+      <c r="L737">
+        <v>5.35</v>
+      </c>
+      <c r="M737">
+        <v>3.8</v>
+      </c>
+      <c r="N737">
+        <v>5.25</v>
+      </c>
+      <c r="O737">
+        <v>1</v>
+      </c>
+      <c r="P737" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="738" spans="1:16">
+      <c r="A738" s="1">
+        <v>1</v>
+      </c>
+      <c r="B738" t="s">
+        <v>146</v>
+      </c>
+      <c r="C738">
+        <v>-0.983904706873532</v>
+      </c>
+      <c r="D738" t="s">
+        <v>253</v>
+      </c>
+      <c r="E738">
+        <v>-0.8303839488503577</v>
+      </c>
+      <c r="F738">
+        <v>-1</v>
+      </c>
+      <c r="G738">
+        <v>0.01156390470687353</v>
+      </c>
+      <c r="H738">
+        <v>0.01269038394885036</v>
+      </c>
+      <c r="I738">
+        <v>-0.1535207580231743</v>
+      </c>
+      <c r="J738">
+        <v>1.677514627506292</v>
+      </c>
+      <c r="K738">
+        <v>3.74</v>
+      </c>
+      <c r="L738">
+        <v>5.29</v>
+      </c>
+      <c r="M738">
+        <v>4.03</v>
+      </c>
+      <c r="N738">
+        <v>5.93</v>
+      </c>
+      <c r="O738">
+        <v>1</v>
+      </c>
+      <c r="P738" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="739" spans="1:16">
+      <c r="A739" s="1">
+        <v>0</v>
+      </c>
+      <c r="B739" t="s">
+        <v>150</v>
+      </c>
+      <c r="C739">
+        <v>-1.46853878015609</v>
+      </c>
+      <c r="D739" t="s">
+        <v>145</v>
+      </c>
+      <c r="E739">
+        <v>-1.163477070443847</v>
+      </c>
+      <c r="F739">
+        <v>1</v>
+      </c>
+      <c r="G739">
+        <v>0.01216853878015609</v>
+      </c>
+      <c r="H739">
+        <v>0.01166347707044385</v>
+      </c>
+      <c r="I739">
+        <v>0.305061709712243</v>
+      </c>
+      <c r="J739">
+        <v>1.687757123801012</v>
+      </c>
+      <c r="K739">
+        <v>4.04</v>
+      </c>
+      <c r="L739">
+        <v>5.35</v>
+      </c>
+      <c r="M739">
+        <v>3.8</v>
+      </c>
+      <c r="N739">
+        <v>5.25</v>
+      </c>
+      <c r="O739">
+        <v>1</v>
+      </c>
+      <c r="P739" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="740" spans="1:16">
+      <c r="A740" s="1">
+        <v>0</v>
+      </c>
+      <c r="B740" t="s">
+        <v>150</v>
+      </c>
+      <c r="C740">
         <v>-1.516702985935216</v>
       </c>
-      <c r="D733" t="s">
+      <c r="D740" t="s">
+        <v>145</v>
+      </c>
+      <c r="E740">
+        <v>-1.208780036275697</v>
+      </c>
+      <c r="F740">
+        <v>1</v>
+      </c>
+      <c r="G740">
+        <v>0.01221670298593521</v>
+      </c>
+      <c r="H740">
+        <v>0.0117087800362757</v>
+      </c>
+      <c r="I740">
+        <v>0.3079229496595186</v>
+      </c>
+      <c r="J740">
+        <v>1.699678956914657</v>
+      </c>
+      <c r="K740">
+        <v>4.04</v>
+      </c>
+      <c r="L740">
+        <v>5.35</v>
+      </c>
+      <c r="M740">
+        <v>3.8</v>
+      </c>
+      <c r="N740">
+        <v>5.25</v>
+      </c>
+      <c r="O740">
+        <v>1</v>
+      </c>
+      <c r="P740" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="741" spans="1:16">
+      <c r="A741" s="1">
+        <v>0</v>
+      </c>
+      <c r="B741" t="s">
+        <v>151</v>
+      </c>
+      <c r="C741">
+        <v>-1.298506883780213</v>
+      </c>
+      <c r="D741" t="s">
         <v>146</v>
       </c>
-      <c r="E733">
-        <v>-1.208780036275697</v>
-      </c>
-      <c r="F733">
-        <v>1</v>
-      </c>
-      <c r="G733">
-        <v>0.01221670298593521</v>
-      </c>
-      <c r="H733">
-        <v>0.0117087800362757</v>
-      </c>
-      <c r="I733">
-        <v>0.3079229496595186</v>
-      </c>
-      <c r="J733">
-        <v>1.699678956914657</v>
-      </c>
-      <c r="K733">
-        <v>4.04</v>
-      </c>
-      <c r="L733">
-        <v>5.35</v>
-      </c>
-      <c r="M733">
-        <v>3.8</v>
-      </c>
-      <c r="N733">
-        <v>5.25</v>
-      </c>
-      <c r="O733">
-        <v>1</v>
-      </c>
-      <c r="P733" t="s">
-        <v>255</v>
+      <c r="E741">
+        <v>-1.055800455701827</v>
+      </c>
+      <c r="F741">
+        <v>1</v>
+      </c>
+      <c r="G741">
+        <v>0.01169850688378021</v>
+      </c>
+      <c r="H741">
+        <v>0.01163580045570183</v>
+      </c>
+      <c r="I741">
+        <v>0.2427064280783862</v>
+      </c>
+      <c r="J741">
+        <v>1.696738089759847</v>
+      </c>
+      <c r="K741">
+        <v>3.83</v>
+      </c>
+      <c r="L741">
+        <v>5.2</v>
+      </c>
+      <c r="M741">
+        <v>3.74</v>
+      </c>
+      <c r="N741">
+        <v>5.29</v>
+      </c>
+      <c r="O741">
+        <v>1</v>
+      </c>
+      <c r="P741" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2247" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="369">
   <si>
     <t>trade_time</t>
   </si>
@@ -451,7 +451,7 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-12-02</t>
+    <t>2021-11-11</t>
   </si>
   <si>
     <t>2021-12-06</t>
@@ -460,22 +460,19 @@
     <t>2021-11-04</t>
   </si>
   <si>
-    <t>2021-11-11</t>
-  </si>
-  <si>
     <t>2021-11-16</t>
-  </si>
-  <si>
-    <t>2021-11-18</t>
   </si>
   <si>
     <t>2021-11-25</t>
   </si>
   <si>
-    <t>2021-11-30</t>
+    <t>2021-12-08</t>
   </si>
   <si>
-    <t>2021-12-08</t>
+    <t>2021-12-09</t>
+  </si>
+  <si>
+    <t>2021-11-30</t>
   </si>
   <si>
     <t>2017-04-20</t>
@@ -781,13 +778,16 @@
     <t>2021-08-09</t>
   </si>
   <si>
-    <t>2021-12-09</t>
-  </si>
-  <si>
     <t>2021-11-26</t>
   </si>
   <si>
+    <t>2021-12-13</t>
+  </si>
+  <si>
     <t>2021-11-29</t>
+  </si>
+  <si>
+    <t>2021-12-02</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -1108,6 +1108,9 @@
     <t>2021-11-17</t>
   </si>
   <si>
+    <t>2021-11-18</t>
+  </si>
+  <si>
     <t>2021-11-19</t>
   </si>
   <si>
@@ -1115,6 +1118,9 @@
   </si>
   <si>
     <t>2021-11-23</t>
+  </si>
+  <si>
+    <t>2021-11-24</t>
   </si>
 </sst>
 </file>
@@ -1472,7 +1478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P745"/>
+  <dimension ref="A1:P738"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1533,7 +1539,7 @@
         <v>1.855441043116508</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E2">
         <v>1.575397067571232</v>
@@ -1583,7 +1589,7 @@
         <v>1.844886436180541</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3">
         <v>1.575397067571232</v>
@@ -1633,7 +1639,7 @@
         <v>1.879543169394645</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E4">
         <v>1.575397067571232</v>
@@ -1683,7 +1689,7 @@
         <v>1.931893523774336</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E5">
         <v>1.575397067571232</v>
@@ -1733,7 +1739,7 @@
         <v>1.864287853699299</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E6">
         <v>1.610229702966436</v>
@@ -1783,7 +1789,7 @@
         <v>1.420828285447678</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7">
         <v>1.720097776330612</v>
@@ -1833,7 +1839,7 @@
         <v>1.444930411725815</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E8">
         <v>1.720097776330612</v>
@@ -1883,7 +1889,7 @@
         <v>1.415528994207057</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E9">
         <v>1.720097776330612</v>
@@ -1933,7 +1939,7 @@
         <v>1.417747421950922</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E10">
         <v>1.720097776330612</v>
@@ -1983,7 +1989,7 @@
         <v>1.837391318446252</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E11">
         <v>1.556576374761795</v>
@@ -2033,7 +2039,7 @@
         <v>1.827426275381424</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E12">
         <v>1.556576374761795</v>
@@ -2083,7 +2089,7 @@
         <v>1.861221338322326</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E13">
         <v>1.556576374761795</v>
@@ -2133,7 +2139,7 @@
         <v>1.913526341635005</v>
       </c>
       <c r="D14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E14">
         <v>1.556576374761795</v>
@@ -2183,7 +2189,7 @@
         <v>1.84664628863214</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E15">
         <v>1.593631212440523</v>
@@ -2233,7 +2239,7 @@
         <v>1.404411199189807</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E16">
         <v>1.701186381387154</v>
@@ -2283,7 +2289,7 @@
         <v>1.428241219065881</v>
       </c>
       <c r="D17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E17">
         <v>1.701186381387154</v>
@@ -2333,7 +2339,7 @@
         <v>1.399021205815165</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E18">
         <v>1.701186381387154</v>
@@ -2383,7 +2389,7 @@
         <v>1.398881378074474</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E19">
         <v>1.701186381387154</v>
@@ -2433,7 +2439,7 @@
         <v>1.772601053603223</v>
       </c>
       <c r="D20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E20">
         <v>1.513212850115657</v>
@@ -2483,7 +2489,7 @@
         <v>1.819007208305362</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E21">
         <v>1.513212850115657</v>
@@ -2533,7 +2539,7 @@
         <v>1.871207721197208</v>
       </c>
       <c r="D22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E22">
         <v>1.513212850115657</v>
@@ -2583,7 +2589,7 @@
         <v>1.805999514927688</v>
       </c>
       <c r="D23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E23">
         <v>1.555387718415254</v>
@@ -2633,7 +2639,7 @@
         <v>1.366585666847875</v>
       </c>
       <c r="D24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E24">
         <v>1.657613875899347</v>
@@ -2683,7 +2689,7 @@
         <v>1.360986692631565</v>
       </c>
       <c r="D25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E25">
         <v>1.657613875899347</v>
@@ -2733,7 +2739,7 @@
         <v>1.355413363007501</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E26">
         <v>1.657613875899347</v>
@@ -2783,7 +2789,7 @@
         <v>1.746707087766096</v>
       </c>
       <c r="D27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E27">
         <v>1.485799595466657</v>
@@ -2833,7 +2839,7 @@
         <v>1.792320570044649</v>
       </c>
       <c r="D28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E28">
         <v>1.485799595466657</v>
@@ -2883,7 +2889,7 @@
         <v>1.780303717196457</v>
       </c>
       <c r="D29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E29">
         <v>1.531211209495895</v>
@@ -2933,7 +2939,7 @@
         <v>1.342673382069711</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E30">
         <v>1.63006850917975</v>
@@ -2983,7 +2989,7 @@
         <v>1.336942295782803</v>
       </c>
       <c r="D31" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E31">
         <v>1.63006850917975</v>
@@ -3033,7 +3039,7 @@
         <v>1.327934052323203</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E32">
         <v>1.63006850917975</v>
@@ -3083,7 +3089,7 @@
         <v>1.724897025074506</v>
       </c>
       <c r="D33" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E33">
         <v>1.462709860729388</v>
@@ -3133,7 +3139,7 @@
         <v>1.713714740951758</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E34">
         <v>1.462709860729388</v>
@@ -3183,7 +3189,7 @@
         <v>1.769842852372705</v>
       </c>
       <c r="D35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E35">
         <v>1.462709860729388</v>
@@ -3233,7 +3239,7 @@
         <v>1.758660568249956</v>
       </c>
       <c r="D36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E36">
         <v>1.510847732595075</v>
@@ -3283,7 +3289,7 @@
         <v>1.322532456829009</v>
       </c>
       <c r="D37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E37">
         <v>1.606867498612421</v>
@@ -3333,7 +3339,7 @@
         <v>1.316690094712042</v>
       </c>
       <c r="D38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E38">
         <v>1.606867498612421</v>
@@ -3383,7 +3389,7 @@
         <v>1.304788679670904</v>
       </c>
       <c r="D39" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E39">
         <v>1.606867498612421</v>
@@ -3433,7 +3439,7 @@
         <v>1.698715924927888</v>
       </c>
       <c r="D40" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E40">
         <v>1.451820073210847</v>
@@ -3483,7 +3489,7 @@
         <v>1.703822090603589</v>
       </c>
       <c r="D41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E41">
         <v>1.451820073210847</v>
@@ -3533,7 +3539,7 @@
         <v>1.759241709824535</v>
       </c>
       <c r="D42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E42">
         <v>1.451820073210847</v>
@@ -3583,7 +3589,7 @@
         <v>1.748453032479565</v>
       </c>
       <c r="D43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E43">
         <v>1.501243727217277</v>
@@ -3633,7 +3639,7 @@
         <v>1.313033413258619</v>
       </c>
       <c r="D44" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E44">
         <v>1.595925230190177</v>
@@ -3683,7 +3689,7 @@
         <v>1.307138570237948</v>
       </c>
       <c r="D45" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E45">
         <v>1.595925230190177</v>
@@ -3733,7 +3739,7 @@
         <v>1.293872651700511</v>
       </c>
       <c r="D46" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E46">
         <v>1.595925230190177</v>
@@ -3783,7 +3789,7 @@
         <v>1.708440278144118</v>
       </c>
       <c r="D47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E47">
         <v>1.445287539361757</v>
@@ -3833,7 +3839,7 @@
         <v>1.75288232747506</v>
       </c>
       <c r="D48" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E48">
         <v>1.445287539361757</v>
@@ -3883,7 +3889,7 @@
         <v>1.742329765811383</v>
       </c>
       <c r="D49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49">
         <v>1.495482504593743</v>
@@ -3933,7 +3939,7 @@
         <v>1.307335154816763</v>
       </c>
       <c r="D50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E50">
         <v>1.589361214250248</v>
@@ -3983,7 +3989,7 @@
         <v>1.301408829705253</v>
       </c>
       <c r="D51" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E51">
         <v>1.589361214250248</v>
@@ -4033,7 +4039,7 @@
         <v>1.287324376806003</v>
       </c>
       <c r="D52" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E52">
         <v>1.589361214250248</v>
@@ -4083,7 +4089,7 @@
         <v>1.741577671463358</v>
       </c>
       <c r="D53" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E53">
         <v>1.433675083310133</v>
@@ -4133,7 +4139,7 @@
         <v>1.793586527085793</v>
       </c>
       <c r="D54" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E54">
         <v>1.433675083310133</v>
@@ -4183,7 +4189,7 @@
         <v>1.731444837126847</v>
       </c>
       <c r="D55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E55">
         <v>1.485241157810864</v>
@@ -4233,7 +4239,7 @@
         <v>1.297205735321128</v>
       </c>
       <c r="D56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E56">
         <v>1.577692794555001</v>
@@ -4283,7 +4289,7 @@
         <v>1.291223446565996</v>
       </c>
       <c r="D57" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E57">
         <v>1.577692794555001</v>
@@ -4333,7 +4339,7 @@
         <v>1.275683938932566</v>
       </c>
       <c r="D58" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E58">
         <v>1.577692794555001</v>
@@ -4433,7 +4439,7 @@
         <v>1.725587143730334</v>
       </c>
       <c r="D60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E60">
         <v>1.417249169921011</v>
@@ -4483,7 +4489,7 @@
         <v>1.777556418838578</v>
       </c>
       <c r="D61" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E61">
         <v>1.417249169921011</v>
@@ -4533,7 +4539,7 @@
         <v>1.716048017106683</v>
       </c>
       <c r="D62" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E62">
         <v>1.470754689617085</v>
@@ -4583,7 +4589,7 @@
         <v>1.282877589184112</v>
       </c>
       <c r="D63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E63">
         <v>1.561187720137498</v>
@@ -4633,7 +4639,7 @@
         <v>1.276816139400598</v>
       </c>
       <c r="D64" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E64">
         <v>1.561187720137498</v>
@@ -4683,7 +4689,7 @@
         <v>1.259218445029255</v>
       </c>
       <c r="D65" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E65">
         <v>1.561187720137498</v>
@@ -4733,7 +4739,7 @@
         <v>1.799190602173319</v>
       </c>
       <c r="D66" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E66">
         <v>1.767682200441425</v>
@@ -4783,7 +4789,7 @@
         <v>1.704528128435052</v>
       </c>
       <c r="D67" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E67">
         <v>1.395616765595412</v>
@@ -4833,7 +4839,7 @@
         <v>1.756445277267813</v>
       </c>
       <c r="D68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E68">
         <v>1.395616765595412</v>
@@ -4883,7 +4889,7 @@
         <v>1.695770895943651</v>
       </c>
       <c r="D69" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E69">
         <v>1.451676472790171</v>
@@ -4933,7 +4939,7 @@
         <v>1.264007877459131</v>
       </c>
       <c r="D70" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E70">
         <v>1.539451063260933</v>
@@ -4983,7 +4989,7 @@
         <v>1.257842175124651</v>
       </c>
       <c r="D71" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E71">
         <v>1.539451063260933</v>
@@ -5033,7 +5039,7 @@
         <v>1.237533914428172</v>
       </c>
       <c r="D72" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E72">
         <v>1.539451063260933</v>
@@ -5133,7 +5139,7 @@
         <v>1.678683818930752</v>
       </c>
       <c r="D74" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E74">
         <v>1.369068774396689</v>
@@ -5183,7 +5189,7 @@
         <v>1.730536996700383</v>
       </c>
       <c r="D75" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E75">
         <v>1.369068774396689</v>
@@ -5233,7 +5239,7 @@
         <v>1.670886152386294</v>
       </c>
       <c r="D76" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E76">
         <v>1.428263063684791</v>
@@ -5283,7 +5289,7 @@
         <v>1.240850352606269</v>
       </c>
       <c r="D77" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E77">
         <v>1.51277512993595</v>
@@ -5333,7 +5339,7 @@
         <v>1.234556708145529</v>
       </c>
       <c r="D78" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E78">
         <v>1.51277512993595</v>
@@ -5383,7 +5389,7 @@
         <v>1.210921952166319</v>
       </c>
       <c r="D79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E79">
         <v>1.51277512993595</v>
@@ -5433,7 +5439,7 @@
         <v>1.661963549027058</v>
       </c>
       <c r="D80" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E80">
         <v>1.351893249619379</v>
@@ -5483,7 +5489,7 @@
         <v>1.713775339989997</v>
       </c>
       <c r="D81" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E81">
         <v>1.351893249619379</v>
@@ -5533,7 +5539,7 @@
         <v>1.654786684582984</v>
       </c>
       <c r="D82" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E82">
         <v>1.413115492435404</v>
@@ -5583,7 +5589,7 @@
         <v>1.225868328583652</v>
       </c>
       <c r="D83" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E83">
         <v>1.495516831545256</v>
@@ -5633,7 +5639,7 @@
         <v>1.219491910509528</v>
       </c>
       <c r="D84" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E84">
         <v>1.495516831545256</v>
@@ -5683,7 +5689,7 @@
         <v>1.193705040582317</v>
       </c>
       <c r="D85" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E85">
         <v>1.495516831545256</v>
@@ -5733,7 +5739,7 @@
         <v>1.600429769178104</v>
       </c>
       <c r="D86" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E86">
         <v>1.338006244585976</v>
@@ -5783,7 +5789,7 @@
         <v>1.648444633283697</v>
       </c>
       <c r="D87" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E87">
         <v>1.338006244585976</v>
@@ -5833,7 +5839,7 @@
         <v>1.700222961583904</v>
       </c>
       <c r="D88" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E88">
         <v>1.338006244585976</v>
@@ -5883,7 +5889,7 @@
         <v>1.641769708780589</v>
       </c>
       <c r="D89" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E89">
         <v>1.400868157875824</v>
@@ -5933,7 +5939,7 @@
         <v>1.213754844674996</v>
       </c>
       <c r="D90" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E90">
         <v>1.48156290118639</v>
@@ -5983,7 +5989,7 @@
         <v>1.20731150127541</v>
       </c>
       <c r="D91" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E91">
         <v>1.48156290118639</v>
@@ -6033,7 +6039,7 @@
         <v>1.179784572886182</v>
       </c>
       <c r="D92" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E92">
         <v>1.48156290118639</v>
@@ -6083,7 +6089,7 @@
         <v>1.642770386608872</v>
       </c>
       <c r="D93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E93">
         <v>1.332177501095747</v>
@@ -6133,7 +6139,7 @@
         <v>1.636306139581315</v>
       </c>
       <c r="D94" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E94">
         <v>1.395727627472394</v>
@@ -6183,7 +6189,7 @@
         <v>1.208670494931713</v>
       </c>
       <c r="D95" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E95">
         <v>1.475706067366088</v>
@@ -6233,7 +6239,7 @@
         <v>1.202199061202053</v>
       </c>
       <c r="D96" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E96">
         <v>1.475706067366088</v>
@@ -6283,7 +6289,7 @@
         <v>1.173941784230917</v>
       </c>
       <c r="D97" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E97">
         <v>1.475706067366088</v>
@@ -6333,7 +6339,7 @@
         <v>1.635648220856852</v>
       </c>
       <c r="D98" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E98">
         <v>1.324861414989093</v>
@@ -6383,7 +6389,7 @@
         <v>1.687394874868875</v>
       </c>
       <c r="D99" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E99">
         <v>1.324861414989093</v>
@@ -6433,7 +6439,7 @@
         <v>1.629448410676523</v>
       </c>
       <c r="D100" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E100">
         <v>1.38927536840002</v>
@@ -6483,7 +6489,7 @@
         <v>1.202288752351933</v>
       </c>
       <c r="D101" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E101">
         <v>1.468354723013138</v>
@@ -6533,7 +6539,7 @@
         <v>1.195782060375976</v>
       </c>
       <c r="D102" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E102">
         <v>1.468354723013138</v>
@@ -6583,7 +6589,7 @@
         <v>1.166608069001115</v>
       </c>
       <c r="D103" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E103">
         <v>1.468354723013138</v>
@@ -6633,7 +6639,7 @@
         <v>1.636237432923918</v>
       </c>
       <c r="D104" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E104">
         <v>1.325466669958976</v>
@@ -6683,7 +6689,7 @@
         <v>1.687985545381652</v>
       </c>
       <c r="D105" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E105">
         <v>1.325466669958976</v>
@@ -6733,7 +6739,7 @@
         <v>1.630015746057932</v>
       </c>
       <c r="D106" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E106">
         <v>1.389809159530085</v>
@@ -6783,7 +6789,7 @@
         <v>1.202816709699155</v>
       </c>
       <c r="D107" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E107">
         <v>1.468962894874441</v>
@@ -6833,7 +6839,7 @@
         <v>1.19631293461462</v>
       </c>
       <c r="D108" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E108">
         <v>1.468962894874441</v>
@@ -6883,7 +6889,7 @@
         <v>1.167214782416708</v>
       </c>
       <c r="D109" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E109">
         <v>1.468962894874441</v>
@@ -6983,7 +6989,7 @@
         <v>1.686969731933735</v>
       </c>
       <c r="D111" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E111">
         <v>1.32442577469753</v>
@@ -7033,7 +7039,7 @@
         <v>1.688566437853383</v>
       </c>
       <c r="D112" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E112">
         <v>1.388891165154931</v>
@@ -7083,7 +7089,7 @@
         <v>1.116820833577004</v>
       </c>
       <c r="D113" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E113">
         <v>1.46791698325029</v>
@@ -7133,7 +7139,7 @@
         <v>1.189838416471486</v>
       </c>
       <c r="D114" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E114">
         <v>1.46791698325029</v>
@@ -7183,7 +7189,7 @@
         <v>1.16617137897391</v>
       </c>
       <c r="D115" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E115">
         <v>1.46791698325029</v>
@@ -7283,7 +7289,7 @@
         <v>1.679044765444968</v>
       </c>
       <c r="D117" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E117">
         <v>1.316305130023856</v>
@@ -7333,7 +7339,7 @@
         <v>1.681071963371414</v>
       </c>
       <c r="D118" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E118">
         <v>1.381729343587304</v>
@@ -7383,7 +7389,7 @@
         <v>1.109345926913525</v>
       </c>
       <c r="D119" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E119">
         <v>1.459757202939633</v>
@@ -7433,7 +7439,7 @@
         <v>1.116606291492413</v>
       </c>
       <c r="D120" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E120">
         <v>1.459757202939633</v>
@@ -7483,7 +7489,7 @@
         <v>1.158031166481744</v>
       </c>
       <c r="D121" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E121">
         <v>1.459757202939633</v>
@@ -7533,7 +7539,7 @@
         <v>1.667785062291963</v>
       </c>
       <c r="D122" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E122">
         <v>1.323675609160295</v>
@@ -7633,7 +7639,7 @@
         <v>1.705523534148037</v>
       </c>
       <c r="D124" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E124">
         <v>1.306151805217721</v>
@@ -7683,7 +7689,7 @@
         <v>1.0999999749233</v>
       </c>
       <c r="D125" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E125">
         <v>1.449554946447687</v>
@@ -7733,7 +7739,7 @@
         <v>1.107015681073126</v>
       </c>
       <c r="D126" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E126">
         <v>1.449554946447687</v>
@@ -7783,7 +7789,7 @@
         <v>1.074450234602739</v>
       </c>
       <c r="D127" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E127">
         <v>1.449554946447687</v>
@@ -7833,7 +7839,7 @@
         <v>1.728036618426774</v>
       </c>
       <c r="D128" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E128">
         <v>1.311858607036529</v>
@@ -7933,7 +7939,7 @@
         <v>1.735732764200063</v>
       </c>
       <c r="D130" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E130">
         <v>1.301215982596513</v>
@@ -7983,7 +7989,7 @@
         <v>1.095456639402092</v>
       </c>
       <c r="D131" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E131">
         <v>1.444595336729509</v>
@@ -8033,7 +8039,7 @@
         <v>1.102353410067069</v>
       </c>
       <c r="D132" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E132">
         <v>1.444595336729509</v>
@@ -8083,7 +8089,7 @@
         <v>1.069526305530016</v>
       </c>
       <c r="D133" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E133">
         <v>1.444595336729509</v>
@@ -8183,7 +8189,7 @@
         <v>1.767688434264066</v>
       </c>
       <c r="D135" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E135">
         <v>1.290978663803567</v>
@@ -8233,7 +8239,7 @@
         <v>1.08603337246497</v>
       </c>
       <c r="D136" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E136">
         <v>1.434308681460452</v>
@@ -8283,7 +8289,7 @@
         <v>1.092683460749394</v>
       </c>
       <c r="D137" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E137">
         <v>1.434308681460452</v>
@@ -8333,7 +8339,7 @@
         <v>1.059313654975125</v>
       </c>
       <c r="D138" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E138">
         <v>1.434308681460452</v>
@@ -8983,7 +8989,7 @@
         <v>1.823420612308294</v>
       </c>
       <c r="D151" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E151">
         <v>2.204728303692967</v>
@@ -9069,7 +9075,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9119,7 +9125,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9383,7 +9389,7 @@
         <v>2.07884565528049</v>
       </c>
       <c r="D159" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E159">
         <v>2.424795934638657</v>
@@ -9533,7 +9539,7 @@
         <v>2.074698477808512</v>
       </c>
       <c r="D162" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E162">
         <v>2.228712809543505</v>
@@ -9833,7 +9839,7 @@
         <v>2.045995448659537</v>
       </c>
       <c r="D168" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E168">
         <v>2.697722827185737</v>
@@ -9983,7 +9989,7 @@
         <v>2.025703573192318</v>
       </c>
       <c r="D171" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E171">
         <v>2.585859069325287</v>
@@ -10083,7 +10089,7 @@
         <v>2.002237248721763</v>
       </c>
       <c r="D173" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E173">
         <v>2.933150127071722</v>
@@ -10169,7 +10175,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10183,7 +10189,7 @@
         <v>2.14690100237887</v>
       </c>
       <c r="D175" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E175">
         <v>3.035145626224377</v>
@@ -10219,7 +10225,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10283,7 +10289,7 @@
         <v>2.113865641885164</v>
       </c>
       <c r="D177" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E177">
         <v>2.99862999271211</v>
@@ -10433,7 +10439,7 @@
         <v>2.224552854469621</v>
       </c>
       <c r="D180" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E180">
         <v>2.747562112891602</v>
@@ -10483,7 +10489,7 @@
         <v>2.234582155562626</v>
       </c>
       <c r="D181" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E181">
         <v>2.747562112891602</v>
@@ -10533,7 +10539,7 @@
         <v>2.532227490792448</v>
       </c>
       <c r="D182" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E182">
         <v>2.747562112891602</v>
@@ -10683,7 +10689,7 @@
         <v>2.219578642489605</v>
       </c>
       <c r="D185" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E185">
         <v>2.748307309478141</v>
@@ -10733,7 +10739,7 @@
         <v>2.229273046142372</v>
       </c>
       <c r="D186" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E186">
         <v>2.748307309478141</v>
@@ -10783,7 +10789,7 @@
         <v>2.526938081221619</v>
       </c>
       <c r="D187" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E187">
         <v>2.748307309478141</v>
@@ -10933,7 +10939,7 @@
         <v>2.223095119495316</v>
       </c>
       <c r="D190" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E190">
         <v>2.585306324177835</v>
@@ -10983,7 +10989,7 @@
         <v>2.233026276055397</v>
       </c>
       <c r="D191" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E191">
         <v>2.585306324177835</v>
@@ -11033,7 +11039,7 @@
         <v>2.530677384493038</v>
       </c>
       <c r="D192" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E192">
         <v>2.585306324177835</v>
@@ -11183,7 +11189,7 @@
         <v>2.351296670264901</v>
       </c>
       <c r="D195" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E195">
         <v>2.34477901699545</v>
@@ -11233,7 +11239,7 @@
         <v>2.531296670264901</v>
       </c>
       <c r="D196" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E196">
         <v>2.34477901699545</v>
@@ -11433,7 +11439,7 @@
         <v>2.354338556588907</v>
       </c>
       <c r="D200" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E200">
         <v>2.692933327062218</v>
@@ -11483,7 +11489,7 @@
         <v>2.534338556588906</v>
       </c>
       <c r="D201" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E201">
         <v>2.692933327062218</v>
@@ -11683,7 +11689,7 @@
         <v>2.353252705775172</v>
       </c>
       <c r="D205" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E205">
         <v>3.037215179660817</v>
@@ -11733,7 +11739,7 @@
         <v>2.533252705775172</v>
       </c>
       <c r="D206" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E206">
         <v>3.037215179660817</v>
@@ -11783,7 +11789,7 @@
         <v>-1.066638455738899</v>
       </c>
       <c r="D207" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E207">
         <v>-1.465413797453388</v>
@@ -11833,7 +11839,7 @@
         <v>-1.0366384557389</v>
       </c>
       <c r="D208" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E208">
         <v>-1.465413797453388</v>
@@ -11883,7 +11889,7 @@
         <v>-0.9510556888450674</v>
       </c>
       <c r="D209" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E209">
         <v>-1.465413797453388</v>
@@ -11933,7 +11939,7 @@
         <v>-1.819265145803461</v>
       </c>
       <c r="D210" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E210">
         <v>-1.307592851757549</v>
@@ -11983,7 +11989,7 @@
         <v>-1.771950960365871</v>
       </c>
       <c r="D211" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E211">
         <v>-1.297263464992842</v>
@@ -12033,7 +12039,7 @@
         <v>-1.016934078228135</v>
       </c>
       <c r="D212" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E212">
         <v>-1.07654556696558</v>
@@ -12083,7 +12089,7 @@
         <v>-1.083441760674821</v>
       </c>
       <c r="D213" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E213">
         <v>-1.481089607902267</v>
@@ -12133,7 +12139,7 @@
         <v>-1.053441760674821</v>
       </c>
       <c r="D214" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E214">
         <v>-1.481089607902267</v>
@@ -12183,7 +12189,7 @@
         <v>-0.9668769824535648</v>
       </c>
       <c r="D215" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E215">
         <v>-1.481089607902267</v>
@@ -12233,7 +12239,7 @@
         <v>-1.83581385521005</v>
       </c>
       <c r="D216" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E216">
         <v>-1.323195920626619</v>
@@ -12283,7 +12289,7 @@
         <v>-1.787408546075322</v>
       </c>
       <c r="D217" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E217">
         <v>-1.311375331475824</v>
@@ -12383,7 +12389,7 @@
         <v>-1.07759404974841</v>
       </c>
       <c r="D219" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E219">
         <v>-1.503621288834554</v>
@@ -12433,7 +12439,7 @@
         <v>-0.9896177741137624</v>
       </c>
       <c r="D220" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E220">
         <v>-1.503621288834554</v>
@@ -12483,7 +12489,7 @@
         <v>-1.859600200509798</v>
       </c>
       <c r="D221" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E221">
         <v>-1.345623046194952</v>
@@ -12533,7 +12539,7 @@
         <v>-1.809626560915746</v>
       </c>
       <c r="D222" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E222">
         <v>-1.33165907208308</v>
@@ -12583,7 +12589,7 @@
         <v>-1.047695097971209</v>
       </c>
       <c r="D223" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E223">
         <v>-1.119714428935569</v>
@@ -12633,7 +12639,7 @@
         <v>-1.107622621715292</v>
       </c>
       <c r="D224" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E224">
         <v>-1.53163495662184</v>
@@ -12683,7 +12689,7 @@
         <v>-1.017891429537125</v>
       </c>
       <c r="D225" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E225">
         <v>-1.53163495662184</v>
@@ -12733,7 +12739,7 @@
         <v>-1.889173794113544</v>
       </c>
       <c r="D226" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E226">
         <v>-1.373506720164198</v>
@@ -12783,7 +12789,7 @@
         <v>-1.837250247248916</v>
       </c>
       <c r="D227" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E227">
         <v>-1.356877872782539</v>
@@ -12883,7 +12889,7 @@
         <v>-1.136466558905362</v>
       </c>
       <c r="D229" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E229">
         <v>-1.55854347811301</v>
@@ -12933,7 +12939,7 @@
         <v>-1.045049682086217</v>
       </c>
       <c r="D230" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E230">
         <v>-1.55854347811301</v>
@@ -12983,7 +12989,7 @@
         <v>-1.91758070195225</v>
       </c>
       <c r="D231" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E231">
         <v>-1.400290376126407</v>
@@ -13033,7 +13039,7 @@
         <v>-1.863784172153202</v>
       </c>
       <c r="D232" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E232">
         <v>-1.38110178540104</v>
@@ -13083,7 +13089,7 @@
         <v>-1.091913194675672</v>
       </c>
       <c r="D233" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E233">
         <v>-0.942243215869925</v>
@@ -13133,7 +13139,7 @@
         <v>-1.06938217480964</v>
       </c>
       <c r="D234" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E234">
         <v>-0.942243215869925</v>
@@ -13183,7 +13189,7 @@
         <v>-1.09938217480964</v>
       </c>
       <c r="D235" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E235">
         <v>-0.942243215869925</v>
@@ -13233,7 +13239,7 @@
         <v>-1.069955605077879</v>
       </c>
       <c r="D236" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E236">
         <v>-1.583220381123139</v>
@@ -13283,7 +13289,7 @@
         <v>-1.943631724851574</v>
       </c>
       <c r="D237" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E237">
         <v>-1.42485276914577</v>
@@ -13333,7 +13339,7 @@
         <v>-1.888117545191031</v>
       </c>
       <c r="D238" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E238">
         <v>-1.403316723609694</v>
@@ -13383,7 +13389,7 @@
         <v>-1.111780678073619</v>
       </c>
       <c r="D239" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E239">
         <v>-0.8811636624809664</v>
@@ -13433,7 +13439,7 @@
         <v>-1.088104558299923</v>
       </c>
       <c r="D240" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E240">
         <v>-0.8811636624809664</v>
@@ -13483,7 +13489,7 @@
         <v>-1.118104558299923</v>
       </c>
       <c r="D241" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E241">
         <v>-0.8811636624809664</v>
@@ -13533,7 +13539,7 @@
         <v>-1.100958399511376</v>
       </c>
       <c r="D242" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E242">
         <v>-1.613938092389432</v>
@@ -13583,7 +13589,7 @@
         <v>-1.976059935121095</v>
       </c>
       <c r="D243" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E243">
         <v>-1.455427938828461</v>
@@ -13633,7 +13639,7 @@
         <v>-1.918407631706518</v>
       </c>
       <c r="D244" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E244">
         <v>-1.430969790828538</v>
@@ -13683,7 +13689,7 @@
         <v>-1.136511642828615</v>
       </c>
       <c r="D245" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E245">
         <v>-1.028859339414037</v>
@@ -13733,7 +13739,7 @@
         <v>-1.111410107218897</v>
       </c>
       <c r="D246" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E246">
         <v>-1.028859339414037</v>
@@ -13783,7 +13789,7 @@
         <v>-1.141410107218897</v>
       </c>
       <c r="D247" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E247">
         <v>-1.028859339414037</v>
@@ -13833,7 +13839,7 @@
         <v>-1.117512484565025</v>
       </c>
       <c r="D248" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E248">
         <v>-1.630339955971323</v>
@@ -13883,7 +13889,7 @@
         <v>-1.993375127533532</v>
       </c>
       <c r="D249" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E249">
         <v>-1.471753691674473</v>
@@ -13933,7 +13939,7 @@
         <v>-1.934581163080772</v>
       </c>
       <c r="D250" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E250">
         <v>-1.445735273589034</v>
@@ -13983,7 +13989,7 @@
         <v>-1.149716855503595</v>
       </c>
       <c r="D251" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E251">
         <v>-1.032336626753983</v>
@@ -14033,7 +14039,7 @@
         <v>-1.123854212535088</v>
       </c>
       <c r="D252" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E252">
         <v>-1.032336626753983</v>
@@ -14083,7 +14089,7 @@
         <v>-1.153854212535088</v>
       </c>
       <c r="D253" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E253">
         <v>-1.032336626753983</v>
@@ -14133,7 +14139,7 @@
         <v>-1.135440729342402</v>
       </c>
       <c r="D254" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E254">
         <v>-1.64810334332546</v>
@@ -14183,7 +14189,7 @@
         <v>-2.012127659427111</v>
       </c>
       <c r="D255" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E255">
         <v>-1.489434650316991</v>
@@ -14233,7 +14239,7 @@
         <v>-1.95209726430005</v>
       </c>
       <c r="D256" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E256">
         <v>-1.461726443643339</v>
@@ -14283,7 +14289,7 @@
         <v>-1.164018236969687</v>
       </c>
       <c r="D257" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E257">
         <v>-1.112656534851095</v>
@@ -14333,7 +14339,7 @@
         <v>-1.137331306884979</v>
       </c>
       <c r="D258" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E258">
         <v>-1.112656534851095</v>
@@ -14383,7 +14389,7 @@
         <v>-1.167331306884979</v>
       </c>
       <c r="D259" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E259">
         <v>-1.112656534851095</v>
@@ -14433,7 +14439,7 @@
         <v>-2.029751754240792</v>
       </c>
       <c r="D260" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E260">
         <v>-1.506051653998461</v>
@@ -14483,7 +14489,7 @@
         <v>-1.968559330884256</v>
       </c>
       <c r="D261" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E261">
         <v>-1.476755342077862</v>
@@ -14533,7 +14539,7 @@
         <v>-1.177459030157264</v>
       </c>
       <c r="D262" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E262">
         <v>-1.113758929914932</v>
@@ -14583,7 +14589,7 @@
         <v>-1.149997414586239</v>
       </c>
       <c r="D263" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E263">
         <v>-1.113758929914932</v>
@@ -14633,7 +14639,7 @@
         <v>-1.179997414586239</v>
       </c>
       <c r="D264" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E264">
         <v>-1.113758929914932</v>
@@ -14683,7 +14689,7 @@
         <v>-2.049264235927141</v>
       </c>
       <c r="D265" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E265">
         <v>-1.524449136731304</v>
@@ -14733,7 +14739,7 @@
         <v>-1.986785275316561</v>
       </c>
       <c r="D266" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E266">
         <v>-1.493394557230178</v>
@@ -14783,7 +14789,7 @@
         <v>-1.192339977729051</v>
       </c>
       <c r="D267" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E267">
         <v>-0.9807727745942727</v>
@@ -14833,7 +14839,7 @@
         <v>-1.16402067065533</v>
       </c>
       <c r="D268" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E268">
         <v>-0.9807727745942727</v>
@@ -14883,7 +14889,7 @@
         <v>-1.19402067065533</v>
       </c>
       <c r="D269" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E269">
         <v>-0.9807727745942727</v>
@@ -14933,7 +14939,7 @@
         <v>-2.083260847634321</v>
       </c>
       <c r="D270" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E270">
         <v>-1.55650308491236</v>
@@ -14983,7 +14989,7 @@
         <v>-2.018540352185904</v>
       </c>
       <c r="D271" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E271">
         <v>-1.52238507446619</v>
@@ -15033,7 +15039,7 @@
         <v>-1.218267064020021</v>
       </c>
       <c r="D272" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E272">
         <v>-1.15072047992809</v>
@@ -15083,7 +15089,7 @@
         <v>-1.188453400387743</v>
       </c>
       <c r="D273" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E273">
         <v>-1.15072047992809</v>
@@ -15133,7 +15139,7 @@
         <v>-1.218453400387743</v>
       </c>
       <c r="D274" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E274">
         <v>-1.15072047992809</v>
@@ -15183,7 +15189,7 @@
         <v>-2.129173370599524</v>
       </c>
       <c r="D275" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E275">
         <v>-1.599792035136694</v>
@@ -15233,7 +15239,7 @@
         <v>-2.061425675834721</v>
       </c>
       <c r="D276" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E276">
         <v>-1.561536852291463</v>
@@ -15283,7 +15289,7 @@
         <v>-1.253281669446231</v>
       </c>
       <c r="D277" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E277">
         <v>-1.285422798224685</v>
@@ -15333,7 +15339,7 @@
         <v>-1.221449872936362</v>
       </c>
       <c r="D278" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E278">
         <v>-1.285422798224685</v>
@@ -15383,7 +15389,7 @@
         <v>-1.251449872936362</v>
       </c>
       <c r="D279" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E279">
         <v>-1.285422798224685</v>
@@ -15433,7 +15439,7 @@
         <v>-2.169540849194301</v>
       </c>
       <c r="D280" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E280">
         <v>-1.637852800668912</v>
@@ -15483,7 +15489,7 @@
         <v>-2.099131562434238</v>
       </c>
       <c r="D281" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E281">
         <v>-1.595960108763492</v>
@@ -15533,7 +15539,7 @@
         <v>-1.284067416858071</v>
       </c>
       <c r="D282" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E282">
         <v>-1.430231131562097</v>
@@ -15583,7 +15589,7 @@
         <v>-1.250461225684695</v>
       </c>
       <c r="D283" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E283">
         <v>-1.430231131562097</v>
@@ -15633,7 +15639,7 @@
         <v>-1.280461225684695</v>
       </c>
       <c r="D284" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E284">
         <v>-1.430231131562097</v>
@@ -15683,7 +15689,7 @@
         <v>-2.189959023684696</v>
       </c>
       <c r="D285" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E285">
         <v>-1.657104222331285</v>
@@ -15733,7 +15739,7 @@
         <v>-2.11820348366153</v>
       </c>
       <c r="D286" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E286">
         <v>-1.613371650966291</v>
@@ -15783,7 +15789,7 @@
         <v>-1.299639079601296</v>
       </c>
       <c r="D287" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E287">
         <v>-1.362715372273368</v>
@@ -15833,7 +15839,7 @@
         <v>-1.265135386252518</v>
       </c>
       <c r="D288" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E288">
         <v>-1.362715372273368</v>
@@ -15883,7 +15889,7 @@
         <v>-1.295135386252518</v>
       </c>
       <c r="D289" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E289">
         <v>-1.362715372273368</v>
@@ -15933,7 +15939,7 @@
         <v>-2.214173184477514</v>
       </c>
       <c r="D290" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E290">
         <v>-1.679934716793084</v>
@@ -15983,7 +15989,7 @@
         <v>-2.140821106380096</v>
       </c>
       <c r="D291" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E291">
         <v>-1.634020210059946</v>
@@ -16033,7 +16039,7 @@
         <v>-1.318105703326807</v>
       </c>
       <c r="D292" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E292">
         <v>-1.489781742375517</v>
@@ -16083,7 +16089,7 @@
         <v>-1.282537651261862</v>
       </c>
       <c r="D293" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E293">
         <v>-1.489781742375517</v>
@@ -16133,7 +16139,7 @@
         <v>-1.312537651261862</v>
       </c>
       <c r="D294" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E294">
         <v>-1.489781742375517</v>
@@ -16183,7 +16189,7 @@
         <v>-2.241121102143395</v>
       </c>
       <c r="D295" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E295">
         <v>-1.705342753449486</v>
@@ -16233,7 +16239,7 @@
         <v>-2.165992238265808</v>
       </c>
       <c r="D296" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E296">
         <v>-1.656999972816785</v>
@@ -16283,7 +16289,7 @@
         <v>-1.338657192184084</v>
       </c>
       <c r="D297" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E297">
         <v>-1.427033480143279</v>
@@ -16333,7 +16339,7 @@
         <v>-1.301904616265692</v>
       </c>
       <c r="D298" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E298">
         <v>-1.427033480143279</v>
@@ -16383,7 +16389,7 @@
         <v>-1.331904616265692</v>
       </c>
       <c r="D299" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E299">
         <v>-1.427033480143279</v>
@@ -16433,7 +16439,7 @@
         <v>1.347720014974502</v>
       </c>
       <c r="D300" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E300">
         <v>1.579062118830282</v>
@@ -16483,7 +16489,7 @@
         <v>1.334700016044109</v>
       </c>
       <c r="D301" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E301">
         <v>1.593089491417174</v>
@@ -16533,7 +16539,7 @@
         <v>1.841747387561394</v>
       </c>
       <c r="D302" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E302">
         <v>1.890874754800249</v>
@@ -16583,7 +16589,7 @@
         <v>1.862485279427185</v>
       </c>
       <c r="D303" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E303">
         <v>1.890874754800249</v>
@@ -16633,7 +16639,7 @@
         <v>1.441706845387347</v>
       </c>
       <c r="D304" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E304">
         <v>1.664215600520115</v>
@@ -16683,7 +16689,7 @@
         <v>1.435400191486443</v>
       </c>
       <c r="D305" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E305">
         <v>1.704389685327122</v>
@@ -16733,7 +16739,7 @@
         <v>1.856584782452771</v>
       </c>
       <c r="D306" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E306">
         <v>1.861880930194354</v>
@@ -16783,7 +16789,7 @@
         <v>1.9645987906652</v>
       </c>
       <c r="D307" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E307">
         <v>1.861880930194354</v>
@@ -16833,7 +16839,7 @@
         <v>2.014804950663784</v>
       </c>
       <c r="D308" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E308">
         <v>1.689180786611569</v>
@@ -16883,7 +16889,7 @@
         <v>1.927301606872644</v>
       </c>
       <c r="D309" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E309">
         <v>1.689180786611569</v>
@@ -16933,7 +16939,7 @@
         <v>1.922617032689892</v>
       </c>
       <c r="D310" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E310">
         <v>1.689180786611569</v>
@@ -16983,7 +16989,7 @@
         <v>1.696992868637676</v>
       </c>
       <c r="D311" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E311">
         <v>1.791368704585461</v>
@@ -17333,7 +17339,7 @@
         <v>1.869784887916945</v>
       </c>
       <c r="D318" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E318">
         <v>1.868536559812515</v>
@@ -17383,7 +17389,7 @@
         <v>1.892281544125805</v>
       </c>
       <c r="D319" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E319">
         <v>1.868536559812515</v>
@@ -17433,7 +17439,7 @@
         <v>1.879784887916945</v>
       </c>
       <c r="D320" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E320">
         <v>1.868536559812515</v>
@@ -17483,7 +17489,7 @@
         <v>1.830509026107986</v>
       </c>
       <c r="D321" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E321">
         <v>1.588842690067986</v>
@@ -17533,7 +17539,7 @@
         <v>1.823342590879987</v>
       </c>
       <c r="D322" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E322">
         <v>1.588842690067986</v>
@@ -17583,7 +17589,7 @@
         <v>1.597009323671986</v>
       </c>
       <c r="D323" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E323">
         <v>1.690676056463986</v>
@@ -17633,7 +17639,7 @@
         <v>1.564008728543987</v>
       </c>
       <c r="D324" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E324">
         <v>1.690841103059988</v>
@@ -17683,7 +17689,7 @@
         <v>1.612175362147987</v>
       </c>
       <c r="D325" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E325">
         <v>1.690841103059988</v>
@@ -17733,7 +17739,7 @@
         <v>1.608508629355987</v>
       </c>
       <c r="D326" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E326">
         <v>1.690841103059988</v>
@@ -17783,7 +17789,7 @@
         <v>1.611175163771987</v>
       </c>
       <c r="D327" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E327">
         <v>1.690841103059988</v>
@@ -17883,7 +17889,7 @@
         <v>1.787174370267988</v>
       </c>
       <c r="D329" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E329">
         <v>1.578675659711986</v>
@@ -17933,7 +17939,7 @@
         <v>1.812507439099989</v>
       </c>
       <c r="D330" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E330">
         <v>1.578675659711986</v>
@@ -17983,7 +17989,7 @@
         <v>1.783507637475988</v>
       </c>
       <c r="D331" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E331">
         <v>1.578675659711986</v>
@@ -18033,7 +18039,7 @@
         <v>1.797174370267989</v>
       </c>
       <c r="D332" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E332">
         <v>1.578675659711986</v>
@@ -18083,7 +18089,7 @@
         <v>1.796508232603987</v>
       </c>
       <c r="D333" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E333">
         <v>1.578675659711986</v>
@@ -18133,7 +18139,7 @@
         <v>1.60619577124814</v>
       </c>
       <c r="D334" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E334">
         <v>1.409496709559184</v>
@@ -18183,7 +18189,7 @@
         <v>1.639829926132983</v>
       </c>
       <c r="D335" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E335">
         <v>1.409496709559184</v>
@@ -18233,7 +18239,7 @@
         <v>1.641634855442047</v>
       </c>
       <c r="D336" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E336">
         <v>1.409496709559184</v>
@@ -18283,7 +18289,7 @@
         <v>1.294651169712725</v>
       </c>
       <c r="D337" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E337">
         <v>1.17011455017335</v>
@@ -18333,7 +18339,7 @@
         <v>1.309805629866267</v>
       </c>
       <c r="D338" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E338">
         <v>1.17011455017335</v>
@@ -18383,7 +18389,7 @@
         <v>1.302846240403662</v>
       </c>
       <c r="D339" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E339">
         <v>1.17011455017335</v>
@@ -18433,7 +18439,7 @@
         <v>1.302846240403662</v>
       </c>
       <c r="D340" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E340">
         <v>1.17011455017335</v>
@@ -18483,7 +18489,7 @@
         <v>1.306789315595589</v>
       </c>
       <c r="D341" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E341">
         <v>1.17011455017335</v>
@@ -18533,7 +18539,7 @@
         <v>1.225269010326891</v>
       </c>
       <c r="D342" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E342">
         <v>1.17011455017335</v>
@@ -18583,7 +18589,7 @@
         <v>1.444294269397325</v>
       </c>
       <c r="D343" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E343">
         <v>1.256000185094495</v>
@@ -18633,7 +18639,7 @@
         <v>1.501117816501946</v>
       </c>
       <c r="D344" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E344">
         <v>1.256000185094495</v>
@@ -18683,7 +18689,7 @@
         <v>1.083058995014017</v>
       </c>
       <c r="D345" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E345">
         <v>1.093353102453659</v>
@@ -18733,7 +18739,7 @@
         <v>1.408730452400234</v>
       </c>
       <c r="D346" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E346">
         <v>1.224172692200284</v>
@@ -18783,7 +18789,7 @@
         <v>1.47198161896276</v>
       </c>
       <c r="D347" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E347">
         <v>1.224172692200284</v>
@@ -18883,7 +18889,7 @@
         <v>1.382122760311682</v>
       </c>
       <c r="D349" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E349">
         <v>1.191863351807043</v>
@@ -18933,7 +18939,7 @@
         <v>1.442404318382183</v>
       </c>
       <c r="D350" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E350">
         <v>1.191863351807043</v>
@@ -19033,7 +19039,7 @@
         <v>1.370401955803482</v>
       </c>
       <c r="D352" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E352">
         <v>1.1776309463328</v>
@@ -19083,7 +19089,7 @@
         <v>1.429375388370835</v>
       </c>
       <c r="D353" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E353">
         <v>1.1776309463328</v>
@@ -19133,7 +19139,7 @@
         <v>1.010452200278918</v>
       </c>
       <c r="D354" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E354">
         <v>1.015068140738506</v>
@@ -19183,7 +19189,7 @@
         <v>1.025068140738506</v>
       </c>
       <c r="D355" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E355">
         <v>1.015068140738506</v>
@@ -19233,7 +19239,7 @@
         <v>1.355513343522262</v>
       </c>
       <c r="D356" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E356">
         <v>1.159551917134175</v>
@@ -19283,7 +19289,7 @@
         <v>1.4128251006118</v>
       </c>
       <c r="D357" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E357">
         <v>1.159551917134175</v>
@@ -19333,7 +19339,7 @@
         <v>0.9937025114625451</v>
       </c>
       <c r="D358" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E358">
         <v>1.019315457208822</v>
@@ -19383,7 +19389,7 @@
         <v>1.009315457208822</v>
       </c>
       <c r="D359" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E359">
         <v>1.019315457208822</v>
@@ -19433,7 +19439,7 @@
         <v>1.344301537527252</v>
       </c>
       <c r="D360" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E360">
         <v>1.145937581283092</v>
@@ -19483,7 +19489,7 @@
         <v>1.400361976983419</v>
       </c>
       <c r="D361" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E361">
         <v>1.145937581283092</v>
@@ -19633,7 +19639,7 @@
         <v>1.32595157423566</v>
       </c>
       <c r="D364" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E364">
         <v>1.123655483000445</v>
@@ -19683,7 +19689,7 @@
         <v>1.379964026717319</v>
       </c>
       <c r="D365" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E365">
         <v>1.123655483000445</v>
@@ -19733,7 +19739,7 @@
         <v>0.9604455210151182</v>
       </c>
       <c r="D366" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E366">
         <v>0.9494825324195202</v>
@@ -19783,7 +19789,7 @@
         <v>0.9780380495261229</v>
       </c>
       <c r="D367" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E367">
         <v>0.9494825324195202</v>
@@ -19833,7 +19839,7 @@
         <v>0.9780380495261229</v>
       </c>
       <c r="D368" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E368">
         <v>0.9494825324195202</v>
@@ -19883,7 +19889,7 @@
         <v>0.93948253241952</v>
       </c>
       <c r="D369" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E369">
         <v>0.9494825324195202</v>
@@ -19933,7 +19939,7 @@
         <v>1.346901155844391</v>
       </c>
       <c r="D370" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E370">
         <v>1.225539647019887</v>
@@ -19983,7 +19989,7 @@
         <v>1.331298641136886</v>
       </c>
       <c r="D371" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E371">
         <v>1.225539647019887</v>
@@ -20033,7 +20039,7 @@
         <v>1.154256377900131</v>
       </c>
       <c r="D372" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E372">
         <v>1.26001537201713</v>
@@ -20083,7 +20089,7 @@
         <v>1.14857562348788</v>
       </c>
       <c r="D373" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E373">
         <v>1.274334617604878</v>
@@ -20133,7 +20139,7 @@
         <v>1.324412857309625</v>
       </c>
       <c r="D374" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E374">
         <v>1.205852605838874</v>
@@ -20183,7 +20189,7 @@
         <v>1.043943419081145</v>
       </c>
       <c r="D375" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E375">
         <v>1.269702413198143</v>
@@ -20233,7 +20239,7 @@
         <v>1.36666643673015</v>
       </c>
       <c r="D376" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E376">
         <v>1.400907442613152</v>
@@ -20283,7 +20289,7 @@
         <v>1.3381061852594</v>
       </c>
       <c r="D377" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E377">
         <v>1.400907442613152</v>
@@ -20333,7 +20339,7 @@
         <v>1.337921514632137</v>
       </c>
       <c r="D378" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E378">
         <v>1.216329758597064</v>
@@ -20383,7 +20389,7 @@
         <v>1.321935254573682</v>
       </c>
       <c r="D379" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E379">
         <v>1.216329758597064</v>
@@ -20433,7 +20439,7 @@
         <v>1.144547620521072</v>
       </c>
       <c r="D380" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E380">
         <v>1.250153116497689</v>
@@ -20483,7 +20489,7 @@
         <v>1.138751742503535</v>
       </c>
       <c r="D381" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E381">
         <v>1.264357238480152</v>
@@ -20533,7 +20539,7 @@
         <v>1.314166856439233</v>
       </c>
       <c r="D382" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E382">
         <v>1.195568230433388</v>
@@ -20583,7 +20589,7 @@
         <v>1.035309148684748</v>
       </c>
       <c r="D383" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E383">
         <v>1.260914644661365</v>
@@ -20733,7 +20739,7 @@
         <v>1.326338641239302</v>
       </c>
       <c r="D386" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E386">
         <v>1.204449888450566</v>
@@ -20783,7 +20789,7 @@
         <v>1.309857386591409</v>
       </c>
       <c r="D387" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E387">
         <v>1.204449888450566</v>
@@ -20833,7 +20839,7 @@
         <v>1.132024257408305</v>
       </c>
       <c r="D388" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E388">
         <v>1.237431755549148</v>
@@ -20883,7 +20889,7 @@
         <v>1.126079881013937</v>
       </c>
       <c r="D389" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E389">
         <v>1.25148737915478</v>
@@ -20933,7 +20939,7 @@
         <v>1.300950500901255</v>
       </c>
       <c r="D390" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E390">
         <v>1.182302375436465</v>
@@ -20983,7 +20989,7 @@
         <v>1.024171770422406</v>
       </c>
       <c r="D391" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E391">
         <v>1.249579268563249</v>
@@ -21033,7 +21039,7 @@
         <v>1.347949275999877</v>
       </c>
       <c r="D392" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E392">
         <v>1.407134279718192</v>
@@ -21083,7 +21089,7 @@
         <v>1.319301150535088</v>
       </c>
       <c r="D393" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E393">
         <v>1.407134279718192</v>
@@ -21133,7 +21139,7 @@
         <v>1.31894662096582</v>
       </c>
       <c r="D394" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E394">
         <v>1.196868329195712</v>
@@ -21183,7 +21189,7 @@
         <v>1.302149468015641</v>
       </c>
       <c r="D395" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E395">
         <v>1.196868329195712</v>
@@ -21233,7 +21239,7 @@
         <v>1.12403203036048</v>
       </c>
       <c r="D396" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E396">
         <v>1.229313169180409</v>
@@ -21283,7 +21289,7 @@
         <v>1.117992884475426</v>
       </c>
       <c r="D397" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E397">
         <v>1.243274023295355</v>
@@ -21333,7 +21339,7 @@
         <v>1.017064058620981</v>
       </c>
       <c r="D398" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E398">
         <v>1.242345197440909</v>
@@ -21483,7 +21489,7 @@
         <v>1.309314370259902</v>
       </c>
       <c r="D401" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E401">
         <v>1.212105582664171</v>
@@ -21533,7 +21539,7 @@
         <v>1.113617673828013</v>
       </c>
       <c r="D402" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E402">
         <v>1.218734158789721</v>
@@ -21583,7 +21589,7 @@
         <v>1.107455037549294</v>
       </c>
       <c r="D403" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E403">
         <v>1.232571522511002</v>
@@ -21633,7 +21639,7 @@
         <v>1.00780227909606</v>
       </c>
       <c r="D404" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E404">
         <v>1.232918764057767</v>
@@ -21819,7 +21825,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21833,7 +21839,7 @@
         <v>1.096911392393543</v>
       </c>
       <c r="D408" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E408">
         <v>1.20176374642348</v>
@@ -21869,7 +21875,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21883,7 +21889,7 @@
         <v>1.090550657915995</v>
       </c>
       <c r="D409" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E409">
         <v>1.215403011945933</v>
@@ -21919,7 +21925,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21933,7 +21939,7 @@
         <v>0.9929449141839808</v>
       </c>
       <c r="D410" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E410">
         <v>1.217797268213918</v>
@@ -21969,7 +21975,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22019,7 +22025,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22069,7 +22075,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22083,7 +22089,7 @@
         <v>1.076787728620787</v>
       </c>
       <c r="D413" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E413">
         <v>1.194722566962074</v>
@@ -22133,7 +22139,7 @@
         <v>1.070188373624195</v>
       </c>
       <c r="D414" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E414">
         <v>1.194722566962074</v>
@@ -22183,7 +22189,7 @@
         <v>0.9750483752556411</v>
       </c>
       <c r="D415" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E415">
         <v>1.199582568593519</v>
@@ -22233,7 +22239,7 @@
         <v>1.06618192359011</v>
       </c>
       <c r="D416" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E416">
         <v>1.199582568593519</v>
@@ -22283,7 +22289,7 @@
         <v>1.301445795242007</v>
       </c>
       <c r="D417" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E417">
         <v>1.466305796873452</v>
@@ -22333,7 +22339,7 @@
         <v>1.325778053569659</v>
       </c>
       <c r="D418" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E418">
         <v>1.466305796873452</v>
@@ -22383,7 +22389,7 @@
         <v>1.061021828820504</v>
       </c>
       <c r="D419" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E419">
         <v>1.178520456495379</v>
@@ -22433,7 +22439,7 @@
         <v>1.05423552639545</v>
       </c>
       <c r="D420" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E420">
         <v>1.178520456495379</v>
@@ -22483,7 +22489,7 @@
         <v>0.9610273181210012</v>
       </c>
       <c r="D421" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E421">
         <v>1.18531224822093</v>
@@ -22533,7 +22539,7 @@
         <v>1.052098550645983</v>
       </c>
       <c r="D422" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E422">
         <v>1.18531224822093</v>
@@ -22583,7 +22589,7 @@
         <v>1.288172527821214</v>
       </c>
       <c r="D423" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E423">
         <v>1.460679389446836</v>
@@ -22633,7 +22639,7 @@
         <v>1.312816365196303</v>
       </c>
       <c r="D424" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E424">
         <v>1.460679389446836</v>
@@ -22783,7 +22789,7 @@
         <v>0.8755952802088971</v>
       </c>
       <c r="D427" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E427">
         <v>1.122137607315365</v>
@@ -22833,7 +22839,7 @@
         <v>1.266605330685716</v>
       </c>
       <c r="D428" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E428">
         <v>1.559580979333694</v>
@@ -22919,7 +22925,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22933,7 +22939,7 @@
         <v>0.8602148664207081</v>
       </c>
       <c r="D430" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E430">
         <v>1.107098980500247</v>
@@ -22969,7 +22975,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -22983,7 +22989,7 @@
         <v>1.280896373713855</v>
       </c>
       <c r="D431" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E431">
         <v>1.524099754797897</v>
@@ -23019,7 +23025,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23183,7 +23189,7 @@
         <v>1.302688953291221</v>
       </c>
       <c r="D435" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E435">
         <v>1.419681456386476</v>
@@ -23269,7 +23275,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23319,7 +23325,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23369,7 +23375,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23383,7 +23389,7 @@
         <v>1.257626439327654</v>
       </c>
       <c r="D439" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E439">
         <v>1.411664944525371</v>
@@ -23419,7 +23425,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23433,7 +23439,7 @@
         <v>1.840766780529548</v>
       </c>
       <c r="D440" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E440">
         <v>2.000338151296236</v>
@@ -23483,7 +23489,7 @@
         <v>2.174266578212954</v>
       </c>
       <c r="D441" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E441">
         <v>2.309284269167179</v>
@@ -23533,7 +23539,7 @@
         <v>2.096677111858851</v>
       </c>
       <c r="D442" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E442">
         <v>1.937337746663046</v>
@@ -23583,7 +23589,7 @@
         <v>1.86232005570882</v>
       </c>
       <c r="D443" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E443">
         <v>1.975355842250461</v>
@@ -23633,7 +23639,7 @@
         <v>1.842592596122513</v>
       </c>
       <c r="D444" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E444">
         <v>2.002261997256608</v>
@@ -23683,7 +23689,7 @@
         <v>2.176435500091845</v>
       </c>
       <c r="D445" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E445">
         <v>2.311735028352367</v>
@@ -23733,7 +23739,7 @@
         <v>2.099152378635891</v>
       </c>
       <c r="D446" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E446">
         <v>1.939947805195271</v>
@@ -23783,7 +23789,7 @@
         <v>1.864648276934749</v>
       </c>
       <c r="D447" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E447">
         <v>1.97756152551713</v>
@@ -23833,7 +23839,7 @@
         <v>1.84474004582061</v>
       </c>
       <c r="D448" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E448">
         <v>2.004524746267355</v>
@@ -23883,7 +23889,7 @@
         <v>2.178986497384215</v>
       </c>
       <c r="D449" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E449">
         <v>2.314617511168604</v>
@@ -23933,7 +23939,7 @@
         <v>2.102063686280291</v>
       </c>
       <c r="D450" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E450">
         <v>1.943017649394564</v>
@@ -23983,7 +23989,7 @@
         <v>1.867386635610175</v>
       </c>
       <c r="D451" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E451">
         <v>1.980155760051744</v>
@@ -24033,7 +24039,7 @@
         <v>2.182944230037506</v>
       </c>
       <c r="D452" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E452">
         <v>2.319089525466108</v>
@@ -24083,7 +24089,7 @@
         <v>2.106580420720769</v>
       </c>
       <c r="D453" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E453">
         <v>1.947780344621405</v>
@@ -24133,7 +24139,7 @@
         <v>1.871635049192803</v>
       </c>
       <c r="D454" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E454">
         <v>1.984180572919497</v>
@@ -24183,7 +24189,7 @@
         <v>2.18904965856885</v>
       </c>
       <c r="D455" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E455">
         <v>2.325988314767062</v>
@@ -24233,7 +24239,7 @@
         <v>2.113548197914732</v>
       </c>
       <c r="D456" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E456">
         <v>1.955127555226921</v>
@@ -24283,7 +24289,7 @@
         <v>1.878188899028709</v>
       </c>
       <c r="D457" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E457">
         <v>2.015269716995014</v>
@@ -24333,7 +24339,7 @@
         <v>1.88583444385064</v>
       </c>
       <c r="D458" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E458">
         <v>2.125307034142769</v>
@@ -24383,7 +24389,7 @@
         <v>2.298073483752043</v>
       </c>
       <c r="D459" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E459">
         <v>2.037664496092738</v>
@@ -24433,7 +24439,7 @@
         <v>1.897427651995606</v>
       </c>
       <c r="D460" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E460">
         <v>2.100495646236972</v>
@@ -24483,7 +24489,7 @@
         <v>1.886668859096591</v>
       </c>
       <c r="D461" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E461">
         <v>2.126294507806616</v>
@@ -24533,7 +24539,7 @@
         <v>2.29919426636051</v>
       </c>
       <c r="D462" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E462">
         <v>2.038997585538931</v>
@@ -24583,7 +24589,7 @@
         <v>1.898642244602138</v>
       </c>
       <c r="D463" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E463">
         <v>2.102411345144836</v>
@@ -24633,7 +24639,7 @@
         <v>1.887695818378956</v>
       </c>
       <c r="D464" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E464">
         <v>2.127509844235451</v>
@@ -24733,7 +24739,7 @@
         <v>1.900137108409605</v>
       </c>
       <c r="D466" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E466">
         <v>2.104769097816775</v>
@@ -24783,7 +24789,7 @@
         <v>1.882492570308907</v>
       </c>
       <c r="D467" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E467">
         <v>2.121352154211724</v>
@@ -24883,7 +24889,7 @@
         <v>1.911660475077831</v>
       </c>
       <c r="D469" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E469">
         <v>2.092823179170745</v>
@@ -24933,7 +24939,7 @@
         <v>1.879971436092785</v>
       </c>
       <c r="D470" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E470">
         <v>2.118368563423415</v>
@@ -25033,7 +25039,7 @@
         <v>1.90788623273062</v>
       </c>
       <c r="D472" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E472">
         <v>2.087035013041425</v>
@@ -25133,7 +25139,7 @@
         <v>1.89858988459332</v>
       </c>
       <c r="D474" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E474">
         <v>2.07277816293363</v>
@@ -25183,7 +25189,7 @@
         <v>2.27342525786704</v>
       </c>
       <c r="D475" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E475">
         <v>2.050890844436287</v>
@@ -25233,7 +25239,7 @@
         <v>1.889192027490578</v>
       </c>
       <c r="D476" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E476">
         <v>2.058365638997408</v>
@@ -25283,7 +25289,7 @@
         <v>2.266210657543448</v>
       </c>
       <c r="D477" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E477">
         <v>2.042055342718407</v>
@@ -25333,7 +25339,7 @@
         <v>1.881151085279702</v>
       </c>
       <c r="D478" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E478">
         <v>2.046034075448713</v>
@@ -25383,7 +25389,7 @@
         <v>2.259792939301354</v>
       </c>
       <c r="D479" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E479">
         <v>2.034195758263333</v>
@@ -25433,7 +25439,7 @@
         <v>1.873998297987854</v>
       </c>
       <c r="D480" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E480">
         <v>2.061056685064424</v>
@@ -25483,7 +25489,7 @@
         <v>2.247400638043782</v>
       </c>
       <c r="D481" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E481">
         <v>2.019019283595469</v>
@@ -25533,7 +25539,7 @@
         <v>1.860186614207387</v>
       </c>
       <c r="D482" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E482">
         <v>2.039929722127505</v>
@@ -25583,7 +25589,7 @@
         <v>2.218696305669633</v>
       </c>
       <c r="D483" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E483">
         <v>1.983865960247392</v>
@@ -25633,7 +25639,7 @@
         <v>1.828194560944569</v>
       </c>
       <c r="D484" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E484">
         <v>1.990993261207699</v>
@@ -25683,7 +25689,7 @@
         <v>1.830127541068264</v>
       </c>
       <c r="D485" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E485">
         <v>2.018032125375022</v>
@@ -25769,7 +25775,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25783,7 +25789,7 @@
         <v>1.78228507381279</v>
       </c>
       <c r="D487" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E487">
         <v>2.022800472072064</v>
@@ -25819,7 +25825,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25833,7 +25839,7 @@
         <v>1.783722556644772</v>
       </c>
       <c r="D488" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E488">
         <v>1.972929321636883</v>
@@ -25869,7 +25875,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25883,7 +25889,7 @@
         <v>2.163345062458509</v>
       </c>
       <c r="D489" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E489">
         <v>1.877414831999107</v>
@@ -25933,7 +25939,7 @@
         <v>1.693507313006611</v>
       </c>
       <c r="D490" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E490">
         <v>1.978388335287718</v>
@@ -25983,7 +25989,7 @@
         <v>1.734543015346852</v>
       </c>
       <c r="D491" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E491">
         <v>1.925129818487629</v>
@@ -26033,7 +26039,7 @@
         <v>1.684218514250647</v>
       </c>
       <c r="D492" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E492">
         <v>1.570048693213578</v>
@@ -26083,7 +26089,7 @@
         <v>2.132031608016207</v>
       </c>
       <c r="D493" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E493">
         <v>1.840169754028087</v>
@@ -26133,7 +26139,7 @@
         <v>1.660262632299145</v>
       </c>
       <c r="D494" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E494">
         <v>1.929555899725715</v>
@@ -26183,7 +26189,7 @@
         <v>1.680468679922261</v>
       </c>
       <c r="D495" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E495">
         <v>1.872572875128523</v>
@@ -26233,7 +26239,7 @@
         <v>1.634006631356384</v>
       </c>
       <c r="D496" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E496">
         <v>1.60382087481427</v>
@@ -26283,7 +26289,7 @@
         <v>2.09863804467423</v>
       </c>
       <c r="D497" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E497">
         <v>1.800450537718246</v>
@@ -26333,7 +26339,7 @@
         <v>1.624809554037398</v>
       </c>
       <c r="D498" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E498">
         <v>1.877479593897257</v>
@@ -26383,7 +26389,7 @@
         <v>1.622802262168714</v>
       </c>
       <c r="D499" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E499">
         <v>1.752483946759322</v>
@@ -26433,7 +26439,7 @@
         <v>1.580459243442377</v>
       </c>
       <c r="D500" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E500">
         <v>1.752483946759322</v>
@@ -26483,7 +26489,7 @@
         <v>2.071221135479056</v>
       </c>
       <c r="D501" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E501">
         <v>1.767840117089625</v>
@@ -26533,7 +26539,7 @@
         <v>1.595701734142962</v>
       </c>
       <c r="D502" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E502">
         <v>1.834723709073065</v>
@@ -26683,7 +26689,7 @@
         <v>2.041322179557651</v>
       </c>
       <c r="D505" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E505">
         <v>1.73227748229324</v>
@@ -26733,7 +26739,7 @@
         <v>1.563958789750633</v>
       </c>
       <c r="D506" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E506">
         <v>1.788097143451137</v>
@@ -26783,7 +26789,7 @@
         <v>1.472686344256899</v>
       </c>
       <c r="D507" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E507">
         <v>1.788097143451137</v>
@@ -26833,7 +26839,7 @@
         <v>1.523825085403519</v>
       </c>
       <c r="D508" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E508">
         <v>1.630370751283219</v>
@@ -26883,7 +26889,7 @@
         <v>1.56168905637971</v>
       </c>
       <c r="D509" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E509">
         <v>1.630370751283219</v>
@@ -26933,7 +26939,7 @@
         <v>1.565051671294496</v>
       </c>
       <c r="D510" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E510">
         <v>1.630370751283219</v>
@@ -26983,7 +26989,7 @@
         <v>1.866585623391427</v>
       </c>
       <c r="D511" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E511">
         <v>1.689366599623595</v>
@@ -27033,7 +27039,7 @@
         <v>2.005245252276134</v>
       </c>
       <c r="D512" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E512">
         <v>1.689366599623595</v>
@@ -27083,7 +27089,7 @@
         <v>1.4318415411232</v>
       </c>
       <c r="D513" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E513">
         <v>1.73183620839538</v>
@@ -27133,7 +27139,7 @@
         <v>1.461524840934997</v>
       </c>
       <c r="D514" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E514">
         <v>1.564205583165584</v>
@@ -27183,7 +27189,7 @@
         <v>1.496369157204806</v>
       </c>
       <c r="D515" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E515">
         <v>1.564205583165584</v>
@@ -27233,7 +27239,7 @@
         <v>1.508949665433811</v>
       </c>
       <c r="D516" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E516">
         <v>1.564205583165584</v>
@@ -27283,7 +27289,7 @@
         <v>1.973924573324424</v>
       </c>
       <c r="D517" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E517">
         <v>1.612872963807592</v>
@@ -27333,7 +27339,7 @@
         <v>1.396381565393731</v>
       </c>
       <c r="D518" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E518">
         <v>1.682992506417824</v>
@@ -27383,7 +27389,7 @@
         <v>1.467141600577559</v>
       </c>
       <c r="D519" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E519">
         <v>1.682992506417824</v>
@@ -27433,7 +27439,7 @@
         <v>1.407438029705613</v>
       </c>
       <c r="D520" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E520">
         <v>1.521706666475579</v>
@@ -27483,7 +27489,7 @@
         <v>1.439660791349507</v>
       </c>
       <c r="D521" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E521">
         <v>1.521706666475579</v>
@@ -27533,7 +27539,7 @@
         <v>1.460243940015513</v>
       </c>
       <c r="D522" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E522">
         <v>1.521706666475579</v>
@@ -27583,7 +27589,7 @@
         <v>1.940579116805523</v>
       </c>
       <c r="D523" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E523">
         <v>1.574239241056619</v>
@@ -27633,7 +27639,7 @@
         <v>1.781069303182167</v>
       </c>
       <c r="D524" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E524">
         <v>1.574239241056619</v>
@@ -27683,7 +27689,7 @@
         <v>1.358629220348103</v>
       </c>
       <c r="D525" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E525">
         <v>1.630991221802445</v>
@@ -27733,7 +27739,7 @@
         <v>1.349854686289714</v>
       </c>
       <c r="D526" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E526">
         <v>1.479202912629048</v>
@@ -27783,7 +27789,7 @@
         <v>1.379286418533347</v>
       </c>
       <c r="D527" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E527">
         <v>1.479202912629048</v>
@@ -27833,7 +27839,7 @@
         <v>1.408389551684359</v>
       </c>
       <c r="D528" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E528">
         <v>1.479202912629048</v>
@@ -27883,7 +27889,7 @@
         <v>1.74645545085387</v>
       </c>
       <c r="D529" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E529">
         <v>1.54184264617284</v>
@@ -27933,7 +27939,7 @@
         <v>1.326971711279163</v>
       </c>
       <c r="D530" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E530">
         <v>1.58738515872694</v>
@@ -28133,7 +28139,7 @@
         <v>1.276676327166428</v>
       </c>
       <c r="D534" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E534">
         <v>1.518106691894613</v>
@@ -28183,7 +28189,7 @@
         <v>1.224852607973696</v>
       </c>
       <c r="D535" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E535">
         <v>1.33929930838555</v>
@@ -28233,7 +28239,7 @@
         <v>1.248225566013237</v>
       </c>
       <c r="D536" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E536">
         <v>1.33929930838555</v>
@@ -28283,7 +28289,7 @@
         <v>1.263762437199394</v>
       </c>
       <c r="D537" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E537">
         <v>1.33929930838555</v>
@@ -28333,7 +28339,7 @@
         <v>1.212947744952629</v>
       </c>
       <c r="D538" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E538">
         <v>1.430324909390002</v>
@@ -28383,7 +28389,7 @@
         <v>1.146309428698562</v>
       </c>
       <c r="D539" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E539">
         <v>1.238758183620087</v>
@@ -28433,7 +28439,7 @@
         <v>1.216483509339664</v>
       </c>
       <c r="D540" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E540">
         <v>1.238758183620087</v>
@@ -28483,7 +28489,7 @@
         <v>1.171021231954409</v>
       </c>
       <c r="D541" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E541">
         <v>1.238758183620087</v>
@@ -28683,7 +28689,7 @@
         <v>0.913889681656368</v>
       </c>
       <c r="D545" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E545">
         <v>0.9422215166785484</v>
@@ -28733,7 +28739,7 @@
         <v>0.9595249171276929</v>
       </c>
       <c r="D546" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E546">
         <v>0.9422215166785484</v>
@@ -28783,7 +28789,7 @@
         <v>0.9589976550364385</v>
       </c>
       <c r="D547" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E547">
         <v>0.9422215166785484</v>
@@ -28833,7 +28839,7 @@
         <v>0.8504189521355614</v>
       </c>
       <c r="D548" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E548">
         <v>0.937857691146331</v>
@@ -28883,7 +28889,7 @@
         <v>0.9017680975637474</v>
       </c>
       <c r="D549" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E549">
         <v>0.937857691146331</v>
@@ -28933,7 +28939,7 @@
         <v>0.908653475416529</v>
       </c>
       <c r="D550" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E550">
         <v>0.937857691146331</v>
@@ -29133,7 +29139,7 @@
         <v>0.7994059700977925</v>
       </c>
       <c r="D554" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E554">
         <v>0.9510460107817367</v>
@@ -29183,7 +29189,7 @@
         <v>0.8553475251011551</v>
       </c>
       <c r="D555" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E555">
         <v>0.9510460107817367</v>
@@ -29233,7 +29239,7 @@
         <v>0.8681906234838945</v>
       </c>
       <c r="D556" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E556">
         <v>0.9510460107817367</v>
@@ -29333,7 +29339,7 @@
         <v>0.7963844516425689</v>
       </c>
       <c r="D558" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E558">
         <v>0.9293442447455118</v>
@@ -29383,7 +29389,7 @@
         <v>0.9077462565202601</v>
       </c>
       <c r="D559" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E559">
         <v>0.9293442447455118</v>
@@ -29433,7 +29439,7 @@
         <v>0.8525980168231655</v>
       </c>
       <c r="D560" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E560">
         <v>0.9293442447455118</v>
@@ -29483,7 +29489,7 @@
         <v>0.8657939932736682</v>
       </c>
       <c r="D561" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E561">
         <v>0.9293442447455118</v>
@@ -30583,7 +30589,7 @@
         <v>0.751468861471289</v>
       </c>
       <c r="D583" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E583">
         <v>0.9385035221553486</v>
@@ -30633,7 +30639,7 @@
         <v>0.7709845877750583</v>
       </c>
       <c r="D584" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E584">
         <v>0.9385035221553486</v>
@@ -30683,7 +30689,7 @@
         <v>0.8117259226040443</v>
       </c>
       <c r="D585" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E585">
         <v>0.9385035221553486</v>
@@ -30733,7 +30739,7 @@
         <v>0.830167515424916</v>
       </c>
       <c r="D586" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E586">
         <v>0.9385035221553486</v>
@@ -30783,7 +30789,7 @@
         <v>0.8384277846341899</v>
       </c>
       <c r="D587" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E587">
         <v>0.9385035221553486</v>
@@ -31183,7 +31189,7 @@
         <v>0.8616555364163685</v>
       </c>
       <c r="D595" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E595">
         <v>0.9487042537756789</v>
@@ -31233,7 +31239,7 @@
         <v>0.8685708400378545</v>
       </c>
       <c r="D596" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E596">
         <v>0.9487042537756789</v>
@@ -31283,7 +31289,7 @@
         <v>0.9283666743289771</v>
       </c>
       <c r="D597" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E597">
         <v>0.9487042537756789</v>
@@ -31333,7 +31339,7 @@
         <v>0.9119931158630705</v>
       </c>
       <c r="D598" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E598">
         <v>0.9487042537756789</v>
@@ -31383,7 +31389,7 @@
         <v>0.917566191902035</v>
       </c>
       <c r="D599" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E599">
         <v>0.9487042537756789</v>
@@ -31433,7 +31439,7 @@
         <v>0.8850151504748149</v>
       </c>
       <c r="D600" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E600">
         <v>0.9487042537756789</v>
@@ -31483,7 +31489,7 @@
         <v>0.9303840608049012</v>
       </c>
       <c r="D601" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E601">
         <v>0.9487042537756789</v>
@@ -31533,7 +31539,7 @@
         <v>0.9319931158630701</v>
       </c>
       <c r="D602" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E602">
         <v>0.9487042537756789</v>
@@ -31619,7 +31625,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31669,7 +31675,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31719,7 +31725,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -31769,7 +31775,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31819,7 +31825,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31869,7 +31875,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31919,7 +31925,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31969,7 +31975,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32019,7 +32025,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32069,7 +32075,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32119,7 +32125,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32169,7 +32175,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32219,7 +32225,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32269,7 +32275,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32319,7 +32325,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -33383,7 +33389,7 @@
         <v>0.9426739735459577</v>
       </c>
       <c r="D639" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E639">
         <v>1.155481591635229</v>
@@ -33433,7 +33439,7 @@
         <v>0.9523699059372155</v>
       </c>
       <c r="D640" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E640">
         <v>0.9617333668754942</v>
@@ -33483,7 +33489,7 @@
         <v>0.9489115468641032</v>
       </c>
       <c r="D641" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E641">
         <v>0.9617333668754942</v>
@@ -33533,7 +33539,7 @@
         <v>0.994540984964766</v>
       </c>
       <c r="D642" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E642">
         <v>0.9617333668754942</v>
@@ -33583,7 +33589,7 @@
         <v>0.9895196820815877</v>
       </c>
       <c r="D643" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E643">
         <v>0.9617333668754942</v>
@@ -33633,7 +33639,7 @@
         <v>0.9598379516124478</v>
       </c>
       <c r="D644" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E644">
         <v>0.9617333668754942</v>
@@ -33683,7 +33689,7 @@
         <v>1.006089726852713</v>
       </c>
       <c r="D645" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E645">
         <v>0.9617333668754942</v>
@@ -33733,7 +33739,7 @@
         <v>0.9848592544956265</v>
       </c>
       <c r="D646" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E646">
         <v>0.9617333668754942</v>
@@ -34033,7 +34039,7 @@
         <v>0.9734565125913943</v>
       </c>
       <c r="D652" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E652">
         <v>1.185400334942146</v>
@@ -34083,7 +34089,7 @@
         <v>0.9846444558037319</v>
       </c>
       <c r="D653" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E653">
         <v>1.181231801994401</v>
@@ -34133,7 +34139,7 @@
         <v>0.9774953331205798</v>
       </c>
       <c r="D654" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E654">
         <v>1.181231801994401</v>
@@ -34183,7 +34189,7 @@
         <v>1.023910040074443</v>
       </c>
       <c r="D655" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E655">
         <v>1.181231801994401</v>
@@ -34233,7 +34239,7 @@
         <v>1.015119446695905</v>
       </c>
       <c r="D656" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E656">
         <v>1.181231801994401</v>
@@ -34283,7 +34289,7 @@
         <v>0.9864585657359251</v>
       </c>
       <c r="D657" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E657">
         <v>1.181231801994401</v>
@@ -34333,7 +34339,7 @@
         <v>1.007646508948263</v>
       </c>
       <c r="D658" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E658">
         <v>1.181231801994401</v>
@@ -34383,7 +34389,7 @@
         <v>1.015249159114463</v>
       </c>
       <c r="D659" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E659">
         <v>0.9834565125913941</v>
@@ -34683,7 +34689,7 @@
         <v>0.9989502799212269</v>
       </c>
       <c r="D665" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E665">
         <v>1.210178715943846</v>
@@ -34733,7 +34739,7 @@
         <v>1.011373890427612</v>
       </c>
       <c r="D666" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E666">
         <v>1.203864024011701</v>
@@ -34783,7 +34789,7 @@
         <v>1.00116811706971</v>
       </c>
       <c r="D667" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E667">
         <v>1.203864024011701</v>
@@ -34833,7 +34839,7 @@
         <v>1.048233175230966</v>
       </c>
       <c r="D668" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E668">
         <v>1.203864024011701</v>
@@ -34883,7 +34889,7 @@
         <v>1.036320896056939</v>
       </c>
       <c r="D669" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E669">
         <v>1.203864024011701</v>
@@ -34933,7 +34939,7 @@
         <v>1.008505471666571</v>
       </c>
       <c r="D670" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E670">
         <v>1.203864024011701</v>
@@ -34983,7 +34989,7 @@
         <v>1.030929082172957</v>
       </c>
       <c r="D671" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E671">
         <v>1.203864024011701</v>
@@ -35033,7 +35039,7 @@
         <v>1.040417750840599</v>
       </c>
       <c r="D672" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E672">
         <v>0.9957763031857296</v>
@@ -35119,7 +35125,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35169,7 +35175,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35219,7 +35225,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35269,7 +35275,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35283,7 +35289,7 @@
         <v>1.019721542843001</v>
       </c>
       <c r="D677" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E677">
         <v>1.230367111793835</v>
@@ -35319,7 +35325,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35333,7 +35339,7 @@
         <v>1.033151923746106</v>
       </c>
       <c r="D678" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E678">
         <v>1.222303818646338</v>
@@ -35369,7 +35375,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35383,7 +35389,7 @@
         <v>1.020455718354215</v>
       </c>
       <c r="D679" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E679">
         <v>1.222303818646338</v>
@@ -35419,7 +35425,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35433,7 +35439,7 @@
         <v>1.053594956548007</v>
       </c>
       <c r="D680" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E680">
         <v>1.222303818646338</v>
@@ -35469,7 +35475,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35483,7 +35489,7 @@
         <v>1.026468375060656</v>
       </c>
       <c r="D681" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E681">
         <v>1.222303818646338</v>
@@ -35519,7 +35525,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35533,7 +35539,7 @@
         <v>1.049898755963761</v>
       </c>
       <c r="D682" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E682">
         <v>1.222303818646338</v>
@@ -35569,7 +35575,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35583,7 +35589,7 @@
         <v>1.060924074184289</v>
       </c>
       <c r="D683" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E683">
         <v>1.017873442550878</v>
@@ -35619,7 +35625,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35833,7 +35839,7 @@
         <v>1.047332978384417</v>
       </c>
       <c r="D688" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E688">
         <v>1.257203736644038</v>
@@ -35883,7 +35889,7 @@
         <v>1.062101668663253</v>
       </c>
       <c r="D689" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E689">
         <v>1.2468160114229</v>
@@ -35933,7 +35939,7 @@
         <v>1.046094908499815</v>
       </c>
       <c r="D690" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E690">
         <v>1.2468160114229</v>
@@ -35983,7 +35989,7 @@
         <v>1.076557527942143</v>
       </c>
       <c r="D691" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E691">
         <v>1.2468160114229</v>
@@ -36033,7 +36039,7 @@
         <v>1.050346631817136</v>
       </c>
       <c r="D692" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E692">
         <v>1.2468160114229</v>
@@ -36083,7 +36089,7 @@
         <v>1.075115322095972</v>
       </c>
       <c r="D693" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E693">
         <v>1.2468160114229</v>
@@ -36133,7 +36139,7 @@
         <v>1.043673116249803</v>
       </c>
       <c r="D694" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E694">
         <v>1.123802357990182</v>
@@ -36183,7 +36189,7 @@
         <v>3.139280458423625</v>
       </c>
       <c r="D695" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E695">
         <v>3.025106410332782</v>
@@ -36219,7 +36225,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36233,7 +36239,7 @@
         <v>3.093454506514468</v>
       </c>
       <c r="D696" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E696">
         <v>3.025106410332782</v>
@@ -36269,7 +36275,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36283,7 +36289,7 @@
         <v>3.013365929424353</v>
       </c>
       <c r="D697" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E697">
         <v>3.025106410332782</v>
@@ -36319,7 +36325,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36333,7 +36339,7 @@
         <v>3.208498795059524</v>
       </c>
       <c r="D698" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E698">
         <v>3.025106410332782</v>
@@ -36369,7 +36375,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36380,40 +36386,40 @@
         <v>145</v>
       </c>
       <c r="C699">
-        <v>-0.3169225520614258</v>
+        <v>-0.8715193570106505</v>
       </c>
       <c r="D699" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E699">
-        <v>-0.056511128540226</v>
+        <v>-0.54680735347549</v>
       </c>
       <c r="F699">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G699">
-        <v>0.01089692255206143</v>
+        <v>0.01181151935701065</v>
       </c>
       <c r="H699">
-        <v>0.01265651112854023</v>
+        <v>0.01108680735347549</v>
       </c>
       <c r="I699">
-        <v>-0.2604114235211998</v>
+        <v>0.3247120035351605</v>
       </c>
       <c r="J699">
         <v>1.4991771529576</v>
       </c>
       <c r="K699">
-        <v>3.74</v>
+        <v>4.23</v>
       </c>
       <c r="L699">
-        <v>5.29</v>
+        <v>5.47</v>
       </c>
       <c r="M699">
-        <v>4.24</v>
+        <v>3.88</v>
       </c>
       <c r="N699">
-        <v>6.3</v>
+        <v>5.27</v>
       </c>
       <c r="O699">
         <v>1</v>
@@ -36436,7 +36442,7 @@
         <v>255</v>
       </c>
       <c r="E700">
-        <v>-0.056511128540226</v>
+        <v>0.003505328400622787</v>
       </c>
       <c r="F700">
         <v>-1</v>
@@ -36445,10 +36451,10 @@
         <v>0.01197168392641913</v>
       </c>
       <c r="H700">
-        <v>0.01265651112854023</v>
+        <v>0.01277649467159938</v>
       </c>
       <c r="I700">
-        <v>-0.05517279787890406</v>
+        <v>-0.1151892548197528</v>
       </c>
       <c r="J700">
         <v>1.4991771529576</v>
@@ -36460,10 +36466,10 @@
         <v>5.93</v>
       </c>
       <c r="M700">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="N700">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="O700">
         <v>1</v>
@@ -36480,40 +36486,40 @@
         <v>145</v>
       </c>
       <c r="C701">
-        <v>-0.3413704137738049</v>
+        <v>-0.8991702808190363</v>
       </c>
       <c r="D701" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E701">
-        <v>-0.08422742096281599</v>
+        <v>-0.5721703757867278</v>
       </c>
       <c r="F701">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G701">
-        <v>0.0109213704137738</v>
+        <v>0.01183917028081904</v>
       </c>
       <c r="H701">
-        <v>0.01268422742096282</v>
+        <v>0.01111217037578673</v>
       </c>
       <c r="I701">
-        <v>-0.257142992810989</v>
+        <v>0.3269999050323085</v>
       </c>
       <c r="J701">
         <v>1.505714014378023</v>
       </c>
       <c r="K701">
-        <v>3.74</v>
+        <v>4.23</v>
       </c>
       <c r="L701">
-        <v>5.29</v>
+        <v>5.47</v>
       </c>
       <c r="M701">
-        <v>4.24</v>
+        <v>3.88</v>
       </c>
       <c r="N701">
-        <v>6.3</v>
+        <v>5.27</v>
       </c>
       <c r="O701">
         <v>1</v>
@@ -36536,7 +36542,7 @@
         <v>255</v>
       </c>
       <c r="E702">
-        <v>-0.08422742096281599</v>
+        <v>-0.02434170125037571</v>
       </c>
       <c r="F702">
         <v>-1</v>
@@ -36545,10 +36551,10 @@
         <v>0.01199802747794343</v>
       </c>
       <c r="H702">
-        <v>0.01268422742096282</v>
+        <v>0.01280434170125038</v>
       </c>
       <c r="I702">
-        <v>-0.05380005698061563</v>
+        <v>-0.1136857766930559</v>
       </c>
       <c r="J702">
         <v>1.505714014378023</v>
@@ -36560,10 +36566,10 @@
         <v>5.93</v>
       </c>
       <c r="M702">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="N702">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="O702">
         <v>1</v>
@@ -36577,43 +36583,43 @@
         <v>0</v>
       </c>
       <c r="B703" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C703">
-        <v>-0.3719564214895099</v>
+        <v>-0.9016808854046587</v>
       </c>
       <c r="D703" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E703">
-        <v>-0.1189024671431875</v>
+        <v>-0.6039013142725391</v>
       </c>
       <c r="F703">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G703">
-        <v>0.01095195642148951</v>
+        <v>0.01254168088540466</v>
       </c>
       <c r="H703">
-        <v>0.01271890246714319</v>
+        <v>0.01114390131427254</v>
       </c>
       <c r="I703">
-        <v>-0.2530539543463224</v>
+        <v>0.2977795711321196</v>
       </c>
       <c r="J703">
         <v>1.513892091307355</v>
       </c>
       <c r="K703">
-        <v>3.74</v>
+        <v>4.44</v>
       </c>
       <c r="L703">
-        <v>5.29</v>
+        <v>5.82</v>
       </c>
       <c r="M703">
-        <v>4.24</v>
+        <v>3.88</v>
       </c>
       <c r="N703">
-        <v>6.3</v>
+        <v>5.27</v>
       </c>
       <c r="O703">
         <v>1</v>
@@ -36627,43 +36633,43 @@
         <v>1</v>
       </c>
       <c r="B704" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C704">
-        <v>-0.1709851279686436</v>
+        <v>-0.9337635462301144</v>
       </c>
       <c r="D704" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E704">
-        <v>-0.1189024671431875</v>
+        <v>-0.6039013142725391</v>
       </c>
       <c r="F704">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G704">
-        <v>0.01203098512796864</v>
+        <v>0.01187376354623011</v>
       </c>
       <c r="H704">
-        <v>0.01271890246714319</v>
+        <v>0.01114390131427254</v>
       </c>
       <c r="I704">
-        <v>-0.0520826608254561</v>
+        <v>0.3298622319575752</v>
       </c>
       <c r="J704">
         <v>1.513892091307355</v>
       </c>
       <c r="K704">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="L704">
-        <v>5.93</v>
+        <v>5.47</v>
       </c>
       <c r="M704">
-        <v>4.24</v>
+        <v>3.88</v>
       </c>
       <c r="N704">
-        <v>6.3</v>
+        <v>5.27</v>
       </c>
       <c r="O704">
         <v>1</v>
@@ -36674,40 +36680,40 @@
     </row>
     <row r="705" spans="1:16">
       <c r="A705" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B705" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C705">
-        <v>-0.9377349898599103</v>
+        <v>-0.9009851279686432</v>
       </c>
       <c r="D705" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E705">
-        <v>-0.6354080542019034</v>
+        <v>-0.6039013142725391</v>
       </c>
       <c r="F705">
         <v>1</v>
       </c>
       <c r="G705">
-        <v>0.01257773498985991</v>
+        <v>0.01130098512796864</v>
       </c>
       <c r="H705">
-        <v>0.0111754080542019</v>
+        <v>0.01114390131427254</v>
       </c>
       <c r="I705">
-        <v>0.3023269356580069</v>
+        <v>0.297083813696104</v>
       </c>
       <c r="J705">
-        <v>1.522012385103583</v>
+        <v>1.513892091307355</v>
       </c>
       <c r="K705">
-        <v>4.44</v>
+        <v>4.03</v>
       </c>
       <c r="L705">
-        <v>5.82</v>
+        <v>5.2</v>
       </c>
       <c r="M705">
         <v>3.88</v>
@@ -36719,71 +36725,71 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="706" spans="1:16">
       <c r="A706" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B706" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C706">
-        <v>-0.9681123889881587</v>
+        <v>-0.1709851279686436</v>
       </c>
       <c r="D706" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E706">
-        <v>-0.6354080542019034</v>
+        <v>-0.05918030896933413</v>
       </c>
       <c r="F706">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G706">
-        <v>0.01190811238898816</v>
+        <v>0.01203098512796864</v>
       </c>
       <c r="H706">
-        <v>0.0111754080542019</v>
+        <v>0.01283918030896933</v>
       </c>
       <c r="I706">
-        <v>0.3327043347862553</v>
+        <v>-0.1118048189993095</v>
       </c>
       <c r="J706">
-        <v>1.522012385103583</v>
+        <v>1.513892091307355</v>
       </c>
       <c r="K706">
-        <v>4.23</v>
+        <v>4.03</v>
       </c>
       <c r="L706">
-        <v>5.47</v>
+        <v>5.93</v>
       </c>
       <c r="M706">
-        <v>3.88</v>
+        <v>4.26</v>
       </c>
       <c r="N706">
-        <v>5.27</v>
+        <v>6.39</v>
       </c>
       <c r="O706">
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="707" spans="1:16">
       <c r="A707" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B707" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C707">
-        <v>-0.9337099119674415</v>
+        <v>-0.9377349898599103</v>
       </c>
       <c r="D707" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E707">
         <v>-0.6354080542019034</v>
@@ -36792,22 +36798,22 @@
         <v>1</v>
       </c>
       <c r="G707">
-        <v>0.01133370991196744</v>
+        <v>0.01257773498985991</v>
       </c>
       <c r="H707">
         <v>0.0111754080542019</v>
       </c>
       <c r="I707">
-        <v>0.2983018577655381</v>
+        <v>0.3023269356580069</v>
       </c>
       <c r="J707">
         <v>1.522012385103583</v>
       </c>
       <c r="K707">
-        <v>4.03</v>
+        <v>4.44</v>
       </c>
       <c r="L707">
-        <v>5.2</v>
+        <v>5.82</v>
       </c>
       <c r="M707">
         <v>3.88</v>
@@ -36824,46 +36830,46 @@
     </row>
     <row r="708" spans="1:16">
       <c r="A708" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B708" t="s">
         <v>145</v>
       </c>
       <c r="C708">
-        <v>-0.4023263202874023</v>
+        <v>-0.9681123889881587</v>
       </c>
       <c r="D708" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E708">
-        <v>-0.153332512839194</v>
+        <v>-0.6354080542019034</v>
       </c>
       <c r="F708">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G708">
-        <v>0.0109823263202874</v>
+        <v>0.01190811238898816</v>
       </c>
       <c r="H708">
-        <v>0.01275333251283919</v>
+        <v>0.0111754080542019</v>
       </c>
       <c r="I708">
-        <v>-0.2489938074482083</v>
+        <v>0.3327043347862553</v>
       </c>
       <c r="J708">
         <v>1.522012385103583</v>
       </c>
       <c r="K708">
-        <v>3.74</v>
+        <v>4.23</v>
       </c>
       <c r="L708">
-        <v>5.29</v>
+        <v>5.47</v>
       </c>
       <c r="M708">
-        <v>4.24</v>
+        <v>3.88</v>
       </c>
       <c r="N708">
-        <v>6.3</v>
+        <v>5.27</v>
       </c>
       <c r="O708">
         <v>1</v>
@@ -36874,31 +36880,31 @@
     </row>
     <row r="709" spans="1:16">
       <c r="A709" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B709" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C709">
-        <v>-0.2037099119674419</v>
+        <v>-0.9337099119674415</v>
       </c>
       <c r="D709" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E709">
-        <v>-0.153332512839194</v>
+        <v>-0.6354080542019034</v>
       </c>
       <c r="F709">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G709">
-        <v>0.01206370991196744</v>
+        <v>0.01133370991196744</v>
       </c>
       <c r="H709">
-        <v>0.01275333251283919</v>
+        <v>0.0111754080542019</v>
       </c>
       <c r="I709">
-        <v>-0.0503773991282479</v>
+        <v>0.2983018577655381</v>
       </c>
       <c r="J709">
         <v>1.522012385103583</v>
@@ -36907,13 +36913,13 @@
         <v>4.03</v>
       </c>
       <c r="L709">
-        <v>5.93</v>
+        <v>5.2</v>
       </c>
       <c r="M709">
-        <v>4.24</v>
+        <v>3.88</v>
       </c>
       <c r="N709">
-        <v>6.3</v>
+        <v>5.27</v>
       </c>
       <c r="O709">
         <v>1</v>
@@ -36924,66 +36930,66 @@
     </row>
     <row r="710" spans="1:16">
       <c r="A710" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B710" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C710">
-        <v>-0.9721715677020031</v>
+        <v>-0.2037099119674419</v>
       </c>
       <c r="D710" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E710">
-        <v>-0.6655012798837321</v>
+        <v>-0.09377276054126504</v>
       </c>
       <c r="F710">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G710">
-        <v>0.012612171567702</v>
+        <v>0.01206370991196744</v>
       </c>
       <c r="H710">
-        <v>0.01120550127988373</v>
+        <v>0.01287377276054126</v>
       </c>
       <c r="I710">
-        <v>0.306670287818271</v>
+        <v>-0.1099371514261769</v>
       </c>
       <c r="J710">
-        <v>1.529768371104055</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K710">
-        <v>4.44</v>
+        <v>4.03</v>
       </c>
       <c r="L710">
-        <v>5.82</v>
+        <v>5.93</v>
       </c>
       <c r="M710">
-        <v>3.88</v>
+        <v>4.26</v>
       </c>
       <c r="N710">
-        <v>5.27</v>
+        <v>6.39</v>
       </c>
       <c r="O710">
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="711" spans="1:16">
       <c r="A711" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B711" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C711">
-        <v>-1.000920209770152</v>
+        <v>-0.9721715677020031</v>
       </c>
       <c r="D711" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E711">
         <v>-0.6655012798837321</v>
@@ -36992,22 +36998,22 @@
         <v>1</v>
       </c>
       <c r="G711">
-        <v>0.01194092020977015</v>
+        <v>0.012612171567702</v>
       </c>
       <c r="H711">
         <v>0.01120550127988373</v>
       </c>
       <c r="I711">
-        <v>0.3354189298864201</v>
+        <v>0.306670287818271</v>
       </c>
       <c r="J711">
         <v>1.529768371104055</v>
       </c>
       <c r="K711">
-        <v>4.23</v>
+        <v>4.44</v>
       </c>
       <c r="L711">
-        <v>5.47</v>
+        <v>5.82</v>
       </c>
       <c r="M711">
         <v>3.88</v>
@@ -37024,16 +37030,16 @@
     </row>
     <row r="712" spans="1:16">
       <c r="A712" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B712" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C712">
-        <v>-0.9649665355493404</v>
+        <v>-1.000920209770152</v>
       </c>
       <c r="D712" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E712">
         <v>-0.6655012798837321</v>
@@ -37042,22 +37048,22 @@
         <v>1</v>
       </c>
       <c r="G712">
-        <v>0.01136496653554934</v>
+        <v>0.01194092020977015</v>
       </c>
       <c r="H712">
         <v>0.01120550127988373</v>
       </c>
       <c r="I712">
-        <v>0.2994652556656083</v>
+        <v>0.3354189298864201</v>
       </c>
       <c r="J712">
         <v>1.529768371104055</v>
       </c>
       <c r="K712">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="L712">
-        <v>5.2</v>
+        <v>5.47</v>
       </c>
       <c r="M712">
         <v>3.88</v>
@@ -37074,46 +37080,46 @@
     </row>
     <row r="713" spans="1:16">
       <c r="A713" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B713" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C713">
-        <v>-0.4313337079291646</v>
+        <v>-0.2349665355493409</v>
       </c>
       <c r="D713" t="s">
         <v>255</v>
       </c>
       <c r="E713">
-        <v>-0.1862178934811922</v>
+        <v>-0.1268132609032726</v>
       </c>
       <c r="F713">
         <v>-1</v>
       </c>
       <c r="G713">
-        <v>0.01101133370792916</v>
+        <v>0.01209496653554934</v>
       </c>
       <c r="H713">
-        <v>0.01278621789348119</v>
+        <v>0.01290681326090327</v>
       </c>
       <c r="I713">
-        <v>-0.2451158144479724</v>
+        <v>-0.1081532746460683</v>
       </c>
       <c r="J713">
         <v>1.529768371104055</v>
       </c>
       <c r="K713">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="L713">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="M713">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="N713">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="O713">
         <v>1</v>
@@ -37124,96 +37130,96 @@
     </row>
     <row r="714" spans="1:16">
       <c r="A714" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B714" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C714">
-        <v>-0.2349665355493409</v>
+        <v>-1.029266735877098</v>
       </c>
       <c r="D714" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E714">
-        <v>-0.1862178934811922</v>
+        <v>-0.6915023487477869</v>
       </c>
       <c r="F714">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G714">
-        <v>0.01209496653554934</v>
+        <v>0.0119692667358771</v>
       </c>
       <c r="H714">
-        <v>0.01278621789348119</v>
+        <v>0.01123150234874778</v>
       </c>
       <c r="I714">
-        <v>-0.04874864206814866</v>
+        <v>0.3377643871293108</v>
       </c>
       <c r="J714">
-        <v>1.529768371104055</v>
+        <v>1.536469677512316</v>
       </c>
       <c r="K714">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="L714">
-        <v>5.93</v>
+        <v>5.47</v>
       </c>
       <c r="M714">
-        <v>4.24</v>
+        <v>3.88</v>
       </c>
       <c r="N714">
-        <v>6.3</v>
+        <v>5.27</v>
       </c>
       <c r="O714">
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>356</v>
+        <v>147</v>
       </c>
     </row>
     <row r="715" spans="1:16">
       <c r="A715" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B715" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C715">
-        <v>-1.029266735877098</v>
+        <v>-0.2619728003746342</v>
       </c>
       <c r="D715" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E715">
-        <v>-0.6915023487477869</v>
+        <v>-0.1553608262024664</v>
       </c>
       <c r="F715">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G715">
-        <v>0.0119692667358771</v>
+        <v>0.01212197280037463</v>
       </c>
       <c r="H715">
-        <v>0.01123150234874778</v>
+        <v>0.01293536082620247</v>
       </c>
       <c r="I715">
-        <v>0.3377643871293108</v>
+        <v>-0.1066119741721678</v>
       </c>
       <c r="J715">
         <v>1.536469677512316</v>
       </c>
       <c r="K715">
-        <v>4.23</v>
+        <v>4.03</v>
       </c>
       <c r="L715">
-        <v>5.47</v>
+        <v>5.93</v>
       </c>
       <c r="M715">
-        <v>3.88</v>
+        <v>4.26</v>
       </c>
       <c r="N715">
-        <v>5.27</v>
+        <v>6.39</v>
       </c>
       <c r="O715">
         <v>1</v>
@@ -37224,284 +37230,284 @@
     </row>
     <row r="716" spans="1:16">
       <c r="A716" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B716" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C716">
-        <v>-0.9919728003746338</v>
+        <v>-1.070041708072165</v>
       </c>
       <c r="D716" t="s">
         <v>256</v>
       </c>
       <c r="E716">
-        <v>-0.6915023487477869</v>
+        <v>-0.6252147732090361</v>
       </c>
       <c r="F716">
         <v>1</v>
       </c>
       <c r="G716">
-        <v>0.01139197280037463</v>
+        <v>0.01201004170807217</v>
       </c>
       <c r="H716">
-        <v>0.01123150234874778</v>
+        <v>0.01112521477320904</v>
       </c>
       <c r="I716">
-        <v>0.3004704516268468</v>
+        <v>0.4448269348631291</v>
       </c>
       <c r="J716">
-        <v>1.536469677512316</v>
+        <v>1.546109150844483</v>
       </c>
       <c r="K716">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="L716">
-        <v>5.2</v>
+        <v>5.47</v>
       </c>
       <c r="M716">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="N716">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="O716">
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>147</v>
+        <v>357</v>
       </c>
     </row>
     <row r="717" spans="1:16">
       <c r="A717" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B717" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C717">
-        <v>-0.4563965938960628</v>
+        <v>-0.300819877903268</v>
       </c>
       <c r="D717" t="s">
         <v>255</v>
       </c>
       <c r="E717">
-        <v>-0.2146314326522205</v>
+        <v>-0.1964249825974989</v>
       </c>
       <c r="F717">
         <v>-1</v>
       </c>
       <c r="G717">
-        <v>0.01103639659389606</v>
+        <v>0.01216081987790327</v>
       </c>
       <c r="H717">
-        <v>0.01281463143265222</v>
+        <v>0.0129764249825975</v>
       </c>
       <c r="I717">
-        <v>-0.2417651612438423</v>
+        <v>-0.1043948953057692</v>
       </c>
       <c r="J717">
-        <v>1.536469677512316</v>
+        <v>1.546109150844483</v>
       </c>
       <c r="K717">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="L717">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="M717">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="N717">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="O717">
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>147</v>
+        <v>357</v>
       </c>
     </row>
     <row r="718" spans="1:16">
       <c r="A718" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B718" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C718">
-        <v>-0.2619728003746342</v>
+        <v>-1.104955489525656</v>
       </c>
       <c r="D718" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E718">
-        <v>-0.2146314326522205</v>
+        <v>-0.6565793995738742</v>
       </c>
       <c r="F718">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G718">
-        <v>0.01212197280037463</v>
+        <v>0.01204495548952566</v>
       </c>
       <c r="H718">
-        <v>0.01281463143265222</v>
+        <v>0.01115657939957388</v>
       </c>
       <c r="I718">
-        <v>-0.04734136772241371</v>
+        <v>0.4483760899517817</v>
       </c>
       <c r="J718">
-        <v>1.536469677512316</v>
+        <v>1.554362999887862</v>
       </c>
       <c r="K718">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="L718">
-        <v>5.93</v>
+        <v>5.47</v>
       </c>
       <c r="M718">
-        <v>4.24</v>
+        <v>3.8</v>
       </c>
       <c r="N718">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="O718">
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>147</v>
+        <v>358</v>
       </c>
     </row>
     <row r="719" spans="1:16">
       <c r="A719" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B719" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C719">
-        <v>-1.070041708072165</v>
+        <v>-0.3340828895480827</v>
       </c>
       <c r="D719" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E719">
-        <v>-0.7289035052765955</v>
+        <v>-0.231586379522291</v>
       </c>
       <c r="F719">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G719">
-        <v>0.01201004170807217</v>
+        <v>0.01219408288954808</v>
       </c>
       <c r="H719">
-        <v>0.01126890350527659</v>
+        <v>0.01301158637952229</v>
       </c>
       <c r="I719">
-        <v>0.3411382027955696</v>
+        <v>-0.1024965100257917</v>
       </c>
       <c r="J719">
-        <v>1.546109150844483</v>
+        <v>1.554362999887862</v>
       </c>
       <c r="K719">
-        <v>4.23</v>
+        <v>4.03</v>
       </c>
       <c r="L719">
-        <v>5.47</v>
+        <v>5.93</v>
       </c>
       <c r="M719">
-        <v>3.88</v>
+        <v>4.26</v>
       </c>
       <c r="N719">
-        <v>5.27</v>
+        <v>6.39</v>
       </c>
       <c r="O719">
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="720" spans="1:16">
       <c r="A720" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B720" t="s">
         <v>145</v>
       </c>
       <c r="C720">
-        <v>-0.4924482241583679</v>
+        <v>-1.146046740420904</v>
       </c>
       <c r="D720" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E720">
-        <v>-0.2555027995806096</v>
+        <v>-0.6934935256736248</v>
       </c>
       <c r="F720">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G720">
-        <v>0.01107244822415837</v>
+        <v>0.0120860467404209</v>
       </c>
       <c r="H720">
-        <v>0.01285550279958061</v>
+        <v>0.01119349352567362</v>
       </c>
       <c r="I720">
-        <v>-0.2369454245777582</v>
+        <v>0.4525532147472795</v>
       </c>
       <c r="J720">
-        <v>1.546109150844483</v>
+        <v>1.564077243598322</v>
       </c>
       <c r="K720">
-        <v>3.74</v>
+        <v>4.23</v>
       </c>
       <c r="L720">
-        <v>5.29</v>
+        <v>5.47</v>
       </c>
       <c r="M720">
-        <v>4.24</v>
+        <v>3.8</v>
       </c>
       <c r="N720">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="O720">
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="721" spans="1:16">
       <c r="A721" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B721" t="s">
         <v>146</v>
       </c>
       <c r="C721">
-        <v>-0.300819877903268</v>
+        <v>-0.3732312917012397</v>
       </c>
       <c r="D721" t="s">
         <v>255</v>
       </c>
       <c r="E721">
-        <v>-0.2555027995806096</v>
+        <v>-0.2729690577288535</v>
       </c>
       <c r="F721">
         <v>-1</v>
       </c>
       <c r="G721">
-        <v>0.01216081987790327</v>
+        <v>0.01223323129170124</v>
       </c>
       <c r="H721">
-        <v>0.01285550279958061</v>
+        <v>0.01305296905772885</v>
       </c>
       <c r="I721">
-        <v>-0.04531707832265841</v>
+        <v>-0.1002622339723862</v>
       </c>
       <c r="J721">
-        <v>1.546109150844483</v>
+        <v>1.564077243598322</v>
       </c>
       <c r="K721">
         <v>4.03</v>
@@ -37510,16 +37516,16 @@
         <v>5.93</v>
       </c>
       <c r="M721">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="N721">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="O721">
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37527,31 +37533,31 @@
         <v>0</v>
       </c>
       <c r="B722" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C722">
-        <v>-1.104955489525656</v>
+        <v>-1.194222080991625</v>
       </c>
       <c r="D722" t="s">
         <v>256</v>
       </c>
       <c r="E722">
-        <v>-0.7609284395649034</v>
+        <v>-0.7367716094014582</v>
       </c>
       <c r="F722">
         <v>1</v>
       </c>
       <c r="G722">
-        <v>0.01204495548952566</v>
+        <v>0.01213422208099162</v>
       </c>
       <c r="H722">
-        <v>0.0113009284395649</v>
+        <v>0.01123677160940146</v>
       </c>
       <c r="I722">
-        <v>0.3440270499607525</v>
+        <v>0.4574504715901666</v>
       </c>
       <c r="J722">
-        <v>1.554362999887862</v>
+        <v>1.575466213000384</v>
       </c>
       <c r="K722">
         <v>4.23</v>
@@ -37560,16 +37566,16 @@
         <v>5.47</v>
       </c>
       <c r="M722">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="N722">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="O722">
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37577,81 +37583,81 @@
         <v>1</v>
       </c>
       <c r="B723" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C723">
-        <v>-0.5233176195806024</v>
+        <v>-0.419128838391547</v>
       </c>
       <c r="D723" t="s">
         <v>255</v>
       </c>
       <c r="E723">
-        <v>-0.2904991195245339</v>
+        <v>-0.3214860673816347</v>
       </c>
       <c r="F723">
         <v>-1</v>
       </c>
       <c r="G723">
-        <v>0.0111033176195806</v>
+        <v>0.01227912883839155</v>
       </c>
       <c r="H723">
-        <v>0.01289049911952453</v>
+        <v>0.01310148606738163</v>
       </c>
       <c r="I723">
-        <v>-0.2328185000560685</v>
+        <v>-0.09764277100991237</v>
       </c>
       <c r="J723">
-        <v>1.554362999887862</v>
+        <v>1.575466213000384</v>
       </c>
       <c r="K723">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="L723">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="M723">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="N723">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="O723">
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="724" spans="1:16">
       <c r="A724" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B724" t="s">
         <v>146</v>
       </c>
       <c r="C724">
-        <v>-0.3340828895480827</v>
+        <v>-0.4644964405131953</v>
       </c>
       <c r="D724" t="s">
         <v>255</v>
       </c>
       <c r="E724">
-        <v>-0.2904991195245339</v>
+        <v>-0.3694428874903739</v>
       </c>
       <c r="F724">
         <v>-1</v>
       </c>
       <c r="G724">
-        <v>0.01219408288954808</v>
+        <v>0.01232449644051319</v>
       </c>
       <c r="H724">
-        <v>0.01289049911952453</v>
+        <v>0.01314944288749037</v>
       </c>
       <c r="I724">
-        <v>-0.04358377002354885</v>
+        <v>-0.09505355302282137</v>
       </c>
       <c r="J724">
-        <v>1.554362999887862</v>
+        <v>1.586723682509477</v>
       </c>
       <c r="K724">
         <v>4.03</v>
@@ -37660,16 +37666,16 @@
         <v>5.93</v>
       </c>
       <c r="M724">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="N724">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="O724">
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>358</v>
+        <v>145</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -37677,81 +37683,81 @@
         <v>0</v>
       </c>
       <c r="B725" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C725">
-        <v>-1.146046740420904</v>
+        <v>-0.522492276288939</v>
       </c>
       <c r="D725" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E725">
-        <v>-0.7986197051614914</v>
+        <v>-0.4307486593029477</v>
       </c>
       <c r="F725">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G725">
-        <v>0.0120860467404209</v>
+        <v>0.01238249227628894</v>
       </c>
       <c r="H725">
-        <v>0.01133861970516149</v>
+        <v>0.01321074865930295</v>
       </c>
       <c r="I725">
-        <v>0.3474270352594129</v>
+        <v>-0.09174361698599132</v>
       </c>
       <c r="J725">
-        <v>1.564077243598322</v>
+        <v>1.60111470875656</v>
       </c>
       <c r="K725">
-        <v>4.23</v>
+        <v>4.03</v>
       </c>
       <c r="L725">
-        <v>5.47</v>
+        <v>5.93</v>
       </c>
       <c r="M725">
-        <v>3.88</v>
+        <v>4.26</v>
       </c>
       <c r="N725">
-        <v>5.27</v>
+        <v>6.39</v>
       </c>
       <c r="O725">
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="726" spans="1:16">
       <c r="A726" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B726" t="s">
         <v>146</v>
       </c>
       <c r="C726">
-        <v>-0.3732312917012397</v>
+        <v>-0.5800395574451711</v>
       </c>
       <c r="D726" t="s">
         <v>255</v>
       </c>
       <c r="E726">
-        <v>-0.3316875128568872</v>
+        <v>-0.491580276604572</v>
       </c>
       <c r="F726">
         <v>-1</v>
       </c>
       <c r="G726">
-        <v>0.01223323129170124</v>
+        <v>0.01244003955744517</v>
       </c>
       <c r="H726">
-        <v>0.01293168751285689</v>
+        <v>0.01327158027660457</v>
       </c>
       <c r="I726">
-        <v>-0.04154377884435245</v>
+        <v>-0.08845928084059906</v>
       </c>
       <c r="J726">
-        <v>1.564077243598322</v>
+        <v>1.615394431127834</v>
       </c>
       <c r="K726">
         <v>4.03</v>
@@ -37760,16 +37766,16 @@
         <v>5.93</v>
       </c>
       <c r="M726">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="N726">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="O726">
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -37777,131 +37783,131 @@
         <v>0</v>
       </c>
       <c r="B727" t="s">
+        <v>146</v>
+      </c>
+      <c r="C727">
+        <v>-0.6212410958743844</v>
+      </c>
+      <c r="D727" t="s">
+        <v>255</v>
+      </c>
+      <c r="E727">
+        <v>-0.5351332675992237</v>
+      </c>
+      <c r="F727">
+        <v>-1</v>
+      </c>
+      <c r="G727">
+        <v>0.01248124109587439</v>
+      </c>
+      <c r="H727">
+        <v>0.01331513326759922</v>
+      </c>
+      <c r="I727">
+        <v>-0.08610782827516061</v>
+      </c>
+      <c r="J727">
+        <v>1.62561813793409</v>
+      </c>
+      <c r="K727">
+        <v>4.03</v>
+      </c>
+      <c r="L727">
+        <v>5.93</v>
+      </c>
+      <c r="M727">
+        <v>4.26</v>
+      </c>
+      <c r="N727">
+        <v>6.39</v>
+      </c>
+      <c r="O727">
+        <v>1</v>
+      </c>
+      <c r="P727" t="s">
         <v>148</v>
-      </c>
-      <c r="C727">
-        <v>-1.194222080991625</v>
-      </c>
-      <c r="D727" t="s">
-        <v>256</v>
-      </c>
-      <c r="E727">
-        <v>-0.8428089064414896</v>
-      </c>
-      <c r="F727">
-        <v>1</v>
-      </c>
-      <c r="G727">
-        <v>0.01213422208099162</v>
-      </c>
-      <c r="H727">
-        <v>0.01138280890644149</v>
-      </c>
-      <c r="I727">
-        <v>0.3514131745501352</v>
-      </c>
-      <c r="J727">
-        <v>1.575466213000384</v>
-      </c>
-      <c r="K727">
-        <v>4.23</v>
-      </c>
-      <c r="L727">
-        <v>5.47</v>
-      </c>
-      <c r="M727">
-        <v>3.88</v>
-      </c>
-      <c r="N727">
-        <v>5.27</v>
-      </c>
-      <c r="O727">
-        <v>1</v>
-      </c>
-      <c r="P727" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="728" spans="1:16">
       <c r="A728" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B728" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C728">
-        <v>-0.419128838391547</v>
+        <v>-1.265907451690905</v>
       </c>
       <c r="D728" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E728">
-        <v>-0.3799767431216274</v>
+        <v>-0.9728832466399586</v>
       </c>
       <c r="F728">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G728">
-        <v>0.01227912883839155</v>
+        <v>0.0119659074516909</v>
       </c>
       <c r="H728">
-        <v>0.01297997674312163</v>
+        <v>0.01147288324663996</v>
       </c>
       <c r="I728">
-        <v>-0.03915209526991958</v>
+        <v>0.293024205050946</v>
       </c>
       <c r="J728">
-        <v>1.575466213000384</v>
+        <v>1.637600854378937</v>
       </c>
       <c r="K728">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="L728">
-        <v>5.93</v>
+        <v>5.35</v>
       </c>
       <c r="M728">
-        <v>4.24</v>
+        <v>3.8</v>
       </c>
       <c r="N728">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="O728">
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="729" spans="1:16">
       <c r="A729" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B729" t="s">
         <v>146</v>
       </c>
       <c r="C729">
-        <v>-0.4644964405131953</v>
+        <v>-0.6695314431471155</v>
       </c>
       <c r="D729" t="s">
         <v>255</v>
       </c>
       <c r="E729">
-        <v>-0.4277084138401852</v>
+        <v>-0.5861796396542704</v>
       </c>
       <c r="F729">
         <v>-1</v>
       </c>
       <c r="G729">
-        <v>0.01232449644051319</v>
+        <v>0.01252953144314711</v>
       </c>
       <c r="H729">
-        <v>0.01302770841384019</v>
+        <v>0.01336617963965427</v>
       </c>
       <c r="I729">
-        <v>-0.03678802667301007</v>
+        <v>-0.0833518034928451</v>
       </c>
       <c r="J729">
-        <v>1.586723682509477</v>
+        <v>1.637600854378937</v>
       </c>
       <c r="K729">
         <v>4.03</v>
@@ -37910,16 +37916,16 @@
         <v>5.93</v>
       </c>
       <c r="M729">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="N729">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="O729">
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>148</v>
+        <v>363</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -37927,149 +37933,149 @@
         <v>0</v>
       </c>
       <c r="B730" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C730">
-        <v>-0.522492276288939</v>
+        <v>-1.320637609966599</v>
       </c>
       <c r="D730" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E730">
-        <v>-0.4887263651278166</v>
+        <v>-0.8852932329888805</v>
       </c>
       <c r="F730">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G730">
-        <v>0.01238249227628894</v>
+        <v>0.0120206376099666</v>
       </c>
       <c r="H730">
-        <v>0.01308872636512782</v>
+        <v>0.01146529323298888</v>
       </c>
       <c r="I730">
-        <v>-0.03376591116112238</v>
+        <v>0.4353443769777181</v>
       </c>
       <c r="J730">
-        <v>1.60111470875656</v>
+        <v>1.651147923259059</v>
       </c>
       <c r="K730">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="L730">
-        <v>5.93</v>
+        <v>5.35</v>
       </c>
       <c r="M730">
-        <v>4.24</v>
+        <v>3.74</v>
       </c>
       <c r="N730">
-        <v>6.3</v>
+        <v>5.29</v>
       </c>
       <c r="O730">
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="731" spans="1:16">
       <c r="A731" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B731" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C731">
-        <v>-1.241577724511336</v>
+        <v>-0.7241261307340077</v>
       </c>
       <c r="D731" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E731">
-        <v>-0.8884988382857681</v>
+        <v>-0.643890153083591</v>
       </c>
       <c r="F731">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G731">
-        <v>0.01168157772451133</v>
+        <v>0.01258412613073401</v>
       </c>
       <c r="H731">
-        <v>0.01138849883828577</v>
+        <v>0.01342389015308359</v>
       </c>
       <c r="I731">
-        <v>0.3530788862255676</v>
+        <v>-0.08023597765041668</v>
       </c>
       <c r="J731">
-        <v>1.615394431127834</v>
+        <v>1.651147923259059</v>
       </c>
       <c r="K731">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="L731">
-        <v>5.22</v>
+        <v>5.93</v>
       </c>
       <c r="M731">
-        <v>3.8</v>
+        <v>4.26</v>
       </c>
       <c r="N731">
-        <v>5.25</v>
+        <v>6.39</v>
       </c>
       <c r="O731">
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="732" spans="1:16">
       <c r="A732" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B732" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C732">
-        <v>-0.5800395574451711</v>
+        <v>-1.380277958041175</v>
       </c>
       <c r="D732" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E732">
-        <v>-0.5492723879820165</v>
+        <v>-0.9405048423450477</v>
       </c>
       <c r="F732">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G732">
-        <v>0.01244003955744517</v>
+        <v>0.01208027795804117</v>
       </c>
       <c r="H732">
-        <v>0.01314927238798202</v>
+        <v>0.01152050484234505</v>
       </c>
       <c r="I732">
-        <v>-0.03076716946315461</v>
+        <v>0.4397731156961271</v>
       </c>
       <c r="J732">
-        <v>1.615394431127834</v>
+        <v>1.665910385653756</v>
       </c>
       <c r="K732">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="L732">
-        <v>5.93</v>
+        <v>5.35</v>
       </c>
       <c r="M732">
-        <v>4.24</v>
+        <v>3.74</v>
       </c>
       <c r="N732">
-        <v>6.3</v>
+        <v>5.29</v>
       </c>
       <c r="O732">
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38077,49 +38083,49 @@
         <v>0</v>
       </c>
       <c r="B733" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C733">
-        <v>-0.6212410958743844</v>
+        <v>-0.8471886296523694</v>
       </c>
       <c r="D733" t="s">
         <v>255</v>
       </c>
       <c r="E733">
-        <v>-0.5926209048405431</v>
+        <v>-0.7562123131768042</v>
       </c>
       <c r="F733">
         <v>-1</v>
       </c>
       <c r="G733">
-        <v>0.01248124109587439</v>
+        <v>0.01374718862965237</v>
       </c>
       <c r="H733">
-        <v>0.01319262090484054</v>
+        <v>0.0135362123131768</v>
       </c>
       <c r="I733">
-        <v>-0.02862019103384128</v>
+        <v>-0.09097631647556526</v>
       </c>
       <c r="J733">
-        <v>1.62561813793409</v>
+        <v>1.677514627506292</v>
       </c>
       <c r="K733">
-        <v>4.03</v>
+        <v>4.35</v>
       </c>
       <c r="L733">
-        <v>5.93</v>
+        <v>6.45</v>
       </c>
       <c r="M733">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="N733">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="O733">
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>149</v>
+        <v>366</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38130,96 +38136,96 @@
         <v>151</v>
       </c>
       <c r="C734">
-        <v>-1.265907451690905</v>
+        <v>-0.8560902049162928</v>
       </c>
       <c r="D734" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E734">
-        <v>-0.9728832466399586</v>
+        <v>-0.7998453473923126</v>
       </c>
       <c r="F734">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G734">
-        <v>0.0119659074516909</v>
+        <v>0.01345609020491629</v>
       </c>
       <c r="H734">
-        <v>0.01147288324663996</v>
+        <v>0.01357984534739231</v>
       </c>
       <c r="I734">
-        <v>0.293024205050946</v>
+        <v>-0.05624485752398023</v>
       </c>
       <c r="J734">
-        <v>1.637600854378937</v>
+        <v>1.687757123801012</v>
       </c>
       <c r="K734">
-        <v>4.04</v>
+        <v>4.24</v>
       </c>
       <c r="L734">
-        <v>5.35</v>
+        <v>6.3</v>
       </c>
       <c r="M734">
-        <v>3.8</v>
+        <v>4.26</v>
       </c>
       <c r="N734">
-        <v>5.25</v>
+        <v>6.39</v>
       </c>
       <c r="O734">
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="735" spans="1:16">
       <c r="A735" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B735" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C735">
-        <v>-0.6695314431471155</v>
+        <v>-0.9066387773181477</v>
       </c>
       <c r="D735" t="s">
         <v>255</v>
       </c>
       <c r="E735">
-        <v>-0.6434276225666915</v>
+        <v>-0.8506323564564404</v>
       </c>
       <c r="F735">
         <v>-1</v>
       </c>
       <c r="G735">
-        <v>0.01252953144314711</v>
+        <v>0.01350663877731815</v>
       </c>
       <c r="H735">
-        <v>0.01324342762256669</v>
+        <v>0.01363063235645644</v>
       </c>
       <c r="I735">
-        <v>-0.02610382058042404</v>
+        <v>-0.05600642086170726</v>
       </c>
       <c r="J735">
-        <v>1.637600854378937</v>
+        <v>1.699678956914657</v>
       </c>
       <c r="K735">
-        <v>4.03</v>
+        <v>4.24</v>
       </c>
       <c r="L735">
-        <v>5.93</v>
+        <v>6.3</v>
       </c>
       <c r="M735">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="N735">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="O735">
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38227,99 +38233,99 @@
         <v>0</v>
       </c>
       <c r="B736" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C736">
-        <v>-1.320637609966599</v>
+        <v>-1.314126956385915</v>
       </c>
       <c r="D736" t="s">
         <v>257</v>
       </c>
       <c r="E736">
-        <v>-1.024362108384423</v>
+        <v>-1.071053476993034</v>
       </c>
       <c r="F736">
         <v>1</v>
       </c>
       <c r="G736">
-        <v>0.0120206376099666</v>
+        <v>0.01171412695638591</v>
       </c>
       <c r="H736">
-        <v>0.01152436210838442</v>
+        <v>0.01165105347699304</v>
       </c>
       <c r="I736">
-        <v>0.2962755015821754</v>
+        <v>0.2430734793928808</v>
       </c>
       <c r="J736">
-        <v>1.651147923259059</v>
+        <v>1.700816437698672</v>
       </c>
       <c r="K736">
-        <v>4.04</v>
+        <v>3.83</v>
       </c>
       <c r="L736">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="M736">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="N736">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="O736">
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="737" spans="1:16">
       <c r="A737" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B737" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C737">
-        <v>-0.7241261307340077</v>
+        <v>-1.319380887843892</v>
       </c>
       <c r="D737" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E737">
-        <v>-0.70086719461841</v>
+        <v>-1.076183947920669</v>
       </c>
       <c r="F737">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G737">
-        <v>0.01258412613073401</v>
+        <v>0.01171938088784389</v>
       </c>
       <c r="H737">
-        <v>0.01330086719461841</v>
+        <v>0.01165618394792067</v>
       </c>
       <c r="I737">
-        <v>-0.02325893611559771</v>
+        <v>0.2431969399232239</v>
       </c>
       <c r="J737">
-        <v>1.651147923259059</v>
+        <v>1.702188221369163</v>
       </c>
       <c r="K737">
-        <v>4.03</v>
+        <v>3.83</v>
       </c>
       <c r="L737">
-        <v>5.93</v>
+        <v>5.2</v>
       </c>
       <c r="M737">
-        <v>4.24</v>
+        <v>3.74</v>
       </c>
       <c r="N737">
-        <v>6.3</v>
+        <v>5.29</v>
       </c>
       <c r="O737">
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>150</v>
+        <v>254</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38327,399 +38333,49 @@
         <v>0</v>
       </c>
       <c r="B738" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C738">
-        <v>-1.380277958041175</v>
+        <v>-1.298506883780213</v>
       </c>
       <c r="D738" t="s">
-        <v>257</v>
+        <v>146</v>
       </c>
       <c r="E738">
-        <v>-1.080459465484273</v>
+        <v>-0.9078545017321833</v>
       </c>
       <c r="F738">
         <v>1</v>
       </c>
       <c r="G738">
-        <v>0.01208027795804117</v>
+        <v>0.01169850688378021</v>
       </c>
       <c r="H738">
-        <v>0.01158045946548427</v>
+        <v>0.01276785450173218</v>
       </c>
       <c r="I738">
-        <v>0.2998184925569021</v>
+        <v>0.3906523820480299</v>
       </c>
       <c r="J738">
-        <v>1.665910385653756</v>
+        <v>1.696738089759847</v>
       </c>
       <c r="K738">
-        <v>4.04</v>
+        <v>3.83</v>
       </c>
       <c r="L738">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="M738">
-        <v>3.8</v>
+        <v>4.03</v>
       </c>
       <c r="N738">
-        <v>5.25</v>
+        <v>5.93</v>
       </c>
       <c r="O738">
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="739" spans="1:16">
-      <c r="A739" s="1">
-        <v>1</v>
-      </c>
-      <c r="B739" t="s">
-        <v>146</v>
-      </c>
-      <c r="C739">
-        <v>-0.7836188541846374</v>
-      </c>
-      <c r="D739" t="s">
-        <v>255</v>
-      </c>
-      <c r="E739">
-        <v>-0.7634600351719261</v>
-      </c>
-      <c r="F739">
-        <v>-1</v>
-      </c>
-      <c r="G739">
-        <v>0.01264361885418464</v>
-      </c>
-      <c r="H739">
-        <v>0.01336346003517193</v>
-      </c>
-      <c r="I739">
-        <v>-0.02015881901271133</v>
-      </c>
-      <c r="J739">
-        <v>1.665910385653756</v>
-      </c>
-      <c r="K739">
-        <v>4.03</v>
-      </c>
-      <c r="L739">
-        <v>5.93</v>
-      </c>
-      <c r="M739">
-        <v>4.24</v>
-      </c>
-      <c r="N739">
-        <v>6.3</v>
-      </c>
-      <c r="O739">
-        <v>1</v>
-      </c>
-      <c r="P739" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="740" spans="1:16">
-      <c r="A740" s="1">
-        <v>0</v>
-      </c>
-      <c r="B740" t="s">
-        <v>151</v>
-      </c>
-      <c r="C740">
-        <v>-1.42715909512542</v>
-      </c>
-      <c r="D740" t="s">
-        <v>145</v>
-      </c>
-      <c r="E740">
-        <v>-0.983904706873532</v>
-      </c>
-      <c r="F740">
-        <v>1</v>
-      </c>
-      <c r="G740">
-        <v>0.01212715909512542</v>
-      </c>
-      <c r="H740">
-        <v>0.01156390470687353</v>
-      </c>
-      <c r="I740">
-        <v>0.443254388251888</v>
-      </c>
-      <c r="J740">
-        <v>1.677514627506292</v>
-      </c>
-      <c r="K740">
-        <v>4.04</v>
-      </c>
-      <c r="L740">
-        <v>5.35</v>
-      </c>
-      <c r="M740">
-        <v>3.74</v>
-      </c>
-      <c r="N740">
-        <v>5.29</v>
-      </c>
-      <c r="O740">
-        <v>1</v>
-      </c>
-      <c r="P740" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="741" spans="1:16">
-      <c r="A741" s="1">
-        <v>1</v>
-      </c>
-      <c r="B741" t="s">
-        <v>146</v>
-      </c>
-      <c r="C741">
-        <v>-0.8303839488503577</v>
-      </c>
-      <c r="D741" t="s">
-        <v>255</v>
-      </c>
-      <c r="E741">
-        <v>-0.8126620206266786</v>
-      </c>
-      <c r="F741">
-        <v>-1</v>
-      </c>
-      <c r="G741">
-        <v>0.01269038394885036</v>
-      </c>
-      <c r="H741">
-        <v>0.01341266202062668</v>
-      </c>
-      <c r="I741">
-        <v>-0.01772192822367913</v>
-      </c>
-      <c r="J741">
-        <v>1.677514627506292</v>
-      </c>
-      <c r="K741">
-        <v>4.03</v>
-      </c>
-      <c r="L741">
-        <v>5.93</v>
-      </c>
-      <c r="M741">
-        <v>4.24</v>
-      </c>
-      <c r="N741">
-        <v>6.3</v>
-      </c>
-      <c r="O741">
-        <v>1</v>
-      </c>
-      <c r="P741" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="742" spans="1:16">
-      <c r="A742" s="1">
-        <v>0</v>
-      </c>
-      <c r="B742" t="s">
-        <v>146</v>
-      </c>
-      <c r="C742">
-        <v>-0.8716612089180806</v>
-      </c>
-      <c r="D742" t="s">
-        <v>255</v>
-      </c>
-      <c r="E742">
-        <v>-0.8560902049162928</v>
-      </c>
-      <c r="F742">
-        <v>-1</v>
-      </c>
-      <c r="G742">
-        <v>0.01273166120891808</v>
-      </c>
-      <c r="H742">
-        <v>0.01345609020491629</v>
-      </c>
-      <c r="I742">
-        <v>-0.01557100400178779</v>
-      </c>
-      <c r="J742">
-        <v>1.687757123801012</v>
-      </c>
-      <c r="K742">
-        <v>4.03</v>
-      </c>
-      <c r="L742">
-        <v>5.93</v>
-      </c>
-      <c r="M742">
-        <v>4.24</v>
-      </c>
-      <c r="N742">
-        <v>6.3</v>
-      </c>
-      <c r="O742">
-        <v>1</v>
-      </c>
-      <c r="P742" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="743" spans="1:16">
-      <c r="A743" s="1">
-        <v>0</v>
-      </c>
-      <c r="B743" t="s">
-        <v>152</v>
-      </c>
-      <c r="C743">
-        <v>-1.319380887843892</v>
-      </c>
-      <c r="D743" t="s">
-        <v>145</v>
-      </c>
-      <c r="E743">
-        <v>-1.076183947920669</v>
-      </c>
-      <c r="F743">
-        <v>1</v>
-      </c>
-      <c r="G743">
-        <v>0.01171938088784389</v>
-      </c>
-      <c r="H743">
-        <v>0.01165618394792067</v>
-      </c>
-      <c r="I743">
-        <v>0.2431969399232239</v>
-      </c>
-      <c r="J743">
-        <v>1.702188221369163</v>
-      </c>
-      <c r="K743">
-        <v>3.83</v>
-      </c>
-      <c r="L743">
-        <v>5.2</v>
-      </c>
-      <c r="M743">
-        <v>3.74</v>
-      </c>
-      <c r="N743">
-        <v>5.29</v>
-      </c>
-      <c r="O743">
-        <v>1</v>
-      </c>
-      <c r="P743" t="s">
         <v>256</v>
-      </c>
-    </row>
-    <row r="744" spans="1:16">
-      <c r="A744" s="1">
-        <v>1</v>
-      </c>
-      <c r="B744" t="s">
-        <v>153</v>
-      </c>
-      <c r="C744">
-        <v>-0.9545187629558569</v>
-      </c>
-      <c r="D744" t="s">
-        <v>255</v>
-      </c>
-      <c r="E744">
-        <v>-0.91727805860525</v>
-      </c>
-      <c r="F744">
-        <v>-1</v>
-      </c>
-      <c r="G744">
-        <v>0.01385451876295586</v>
-      </c>
-      <c r="H744">
-        <v>0.01351727805860525</v>
-      </c>
-      <c r="I744">
-        <v>-0.03724070435060689</v>
-      </c>
-      <c r="J744">
-        <v>1.702188221369163</v>
-      </c>
-      <c r="K744">
-        <v>4.35</v>
-      </c>
-      <c r="L744">
-        <v>6.45</v>
-      </c>
-      <c r="M744">
-        <v>4.24</v>
-      </c>
-      <c r="N744">
-        <v>6.3</v>
-      </c>
-      <c r="O744">
-        <v>1</v>
-      </c>
-      <c r="P744" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="745" spans="1:16">
-      <c r="A745" s="1">
-        <v>0</v>
-      </c>
-      <c r="B745" t="s">
-        <v>152</v>
-      </c>
-      <c r="C745">
-        <v>-1.298506883780213</v>
-      </c>
-      <c r="D745" t="s">
-        <v>145</v>
-      </c>
-      <c r="E745">
-        <v>-1.055800455701827</v>
-      </c>
-      <c r="F745">
-        <v>1</v>
-      </c>
-      <c r="G745">
-        <v>0.01169850688378021</v>
-      </c>
-      <c r="H745">
-        <v>0.01163580045570183</v>
-      </c>
-      <c r="I745">
-        <v>0.2427064280783862</v>
-      </c>
-      <c r="J745">
-        <v>1.696738089759847</v>
-      </c>
-      <c r="K745">
-        <v>3.83</v>
-      </c>
-      <c r="L745">
-        <v>5.2</v>
-      </c>
-      <c r="M745">
-        <v>3.74</v>
-      </c>
-      <c r="N745">
-        <v>5.29</v>
-      </c>
-      <c r="O745">
-        <v>1</v>
-      </c>
-      <c r="P745" t="s">
-        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="372">
   <si>
     <t>trade_time</t>
   </si>
@@ -457,13 +457,10 @@
     <t>2021-12-06</t>
   </si>
   <si>
-    <t>2021-11-16</t>
-  </si>
-  <si>
     <t>2021-11-04</t>
   </si>
   <si>
-    <t>2021-11-18</t>
+    <t>2021-11-16</t>
   </si>
   <si>
     <t>2021-11-25</t>
@@ -479,6 +476,12 @@
   </si>
   <si>
     <t>2021-11-30</t>
+  </si>
+  <si>
+    <t>2021-12-14</t>
+  </si>
+  <si>
+    <t>2021-12-03</t>
   </si>
   <si>
     <t>2017-04-20</t>
@@ -784,13 +787,10 @@
     <t>2021-08-09</t>
   </si>
   <si>
-    <t>2021-11-26</t>
+    <t>2021-11-29</t>
   </si>
   <si>
-    <t>2021-12-14</t>
-  </si>
-  <si>
-    <t>2021-11-29</t>
+    <t>2021-12-15</t>
   </si>
   <si>
     <t>2021-12-02</t>
@@ -1114,6 +1114,9 @@
     <t>2021-11-17</t>
   </si>
   <si>
+    <t>2021-11-18</t>
+  </si>
+  <si>
     <t>2021-11-19</t>
   </si>
   <si>
@@ -1124,6 +1127,9 @@
   </si>
   <si>
     <t>2021-11-24</t>
+  </si>
+  <si>
+    <t>2021-11-26</t>
   </si>
 </sst>
 </file>
@@ -1481,7 +1487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P743"/>
+  <dimension ref="A1:P744"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1542,7 +1548,7 @@
         <v>1.855441043116508</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E2">
         <v>1.575397067571232</v>
@@ -1592,7 +1598,7 @@
         <v>1.844886436180541</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E3">
         <v>1.575397067571232</v>
@@ -1642,7 +1648,7 @@
         <v>1.879543169394645</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E4">
         <v>1.575397067571232</v>
@@ -1692,7 +1698,7 @@
         <v>1.931893523774336</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E5">
         <v>1.575397067571232</v>
@@ -1742,7 +1748,7 @@
         <v>1.864287853699299</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E6">
         <v>1.610229702966436</v>
@@ -1792,7 +1798,7 @@
         <v>1.420828285447678</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E7">
         <v>1.720097776330612</v>
@@ -1842,7 +1848,7 @@
         <v>1.444930411725815</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E8">
         <v>1.720097776330612</v>
@@ -1892,7 +1898,7 @@
         <v>1.415528994207057</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E9">
         <v>1.720097776330612</v>
@@ -1942,7 +1948,7 @@
         <v>1.417747421950922</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E10">
         <v>1.720097776330612</v>
@@ -1992,7 +1998,7 @@
         <v>1.837391318446252</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E11">
         <v>1.556576374761795</v>
@@ -2042,7 +2048,7 @@
         <v>1.827426275381424</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E12">
         <v>1.556576374761795</v>
@@ -2092,7 +2098,7 @@
         <v>1.861221338322326</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E13">
         <v>1.556576374761795</v>
@@ -2142,7 +2148,7 @@
         <v>1.913526341635005</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E14">
         <v>1.556576374761795</v>
@@ -2192,7 +2198,7 @@
         <v>1.84664628863214</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E15">
         <v>1.593631212440523</v>
@@ -2242,7 +2248,7 @@
         <v>1.404411199189807</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E16">
         <v>1.701186381387154</v>
@@ -2292,7 +2298,7 @@
         <v>1.428241219065881</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E17">
         <v>1.701186381387154</v>
@@ -2342,7 +2348,7 @@
         <v>1.399021205815165</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E18">
         <v>1.701186381387154</v>
@@ -2392,7 +2398,7 @@
         <v>1.398881378074474</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E19">
         <v>1.701186381387154</v>
@@ -2442,7 +2448,7 @@
         <v>1.772601053603223</v>
       </c>
       <c r="D20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E20">
         <v>1.513212850115657</v>
@@ -2492,7 +2498,7 @@
         <v>1.819007208305362</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E21">
         <v>1.513212850115657</v>
@@ -2542,7 +2548,7 @@
         <v>1.871207721197208</v>
       </c>
       <c r="D22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E22">
         <v>1.513212850115657</v>
@@ -2592,7 +2598,7 @@
         <v>1.805999514927688</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E23">
         <v>1.555387718415254</v>
@@ -2642,7 +2648,7 @@
         <v>1.366585666847875</v>
       </c>
       <c r="D24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E24">
         <v>1.657613875899347</v>
@@ -2692,7 +2698,7 @@
         <v>1.360986692631565</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E25">
         <v>1.657613875899347</v>
@@ -2742,7 +2748,7 @@
         <v>1.355413363007501</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E26">
         <v>1.657613875899347</v>
@@ -2792,7 +2798,7 @@
         <v>1.746707087766096</v>
       </c>
       <c r="D27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E27">
         <v>1.485799595466657</v>
@@ -2842,7 +2848,7 @@
         <v>1.792320570044649</v>
       </c>
       <c r="D28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E28">
         <v>1.485799595466657</v>
@@ -2892,7 +2898,7 @@
         <v>1.780303717196457</v>
       </c>
       <c r="D29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E29">
         <v>1.531211209495895</v>
@@ -2942,7 +2948,7 @@
         <v>1.342673382069711</v>
       </c>
       <c r="D30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E30">
         <v>1.63006850917975</v>
@@ -2992,7 +2998,7 @@
         <v>1.336942295782803</v>
       </c>
       <c r="D31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E31">
         <v>1.63006850917975</v>
@@ -3042,7 +3048,7 @@
         <v>1.327934052323203</v>
       </c>
       <c r="D32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E32">
         <v>1.63006850917975</v>
@@ -3092,7 +3098,7 @@
         <v>1.724897025074506</v>
       </c>
       <c r="D33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E33">
         <v>1.462709860729388</v>
@@ -3142,7 +3148,7 @@
         <v>1.713714740951758</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E34">
         <v>1.462709860729388</v>
@@ -3192,7 +3198,7 @@
         <v>1.769842852372705</v>
       </c>
       <c r="D35" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E35">
         <v>1.462709860729388</v>
@@ -3242,7 +3248,7 @@
         <v>1.758660568249956</v>
       </c>
       <c r="D36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E36">
         <v>1.510847732595075</v>
@@ -3292,7 +3298,7 @@
         <v>1.322532456829009</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E37">
         <v>1.606867498612421</v>
@@ -3342,7 +3348,7 @@
         <v>1.316690094712042</v>
       </c>
       <c r="D38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E38">
         <v>1.606867498612421</v>
@@ -3392,7 +3398,7 @@
         <v>1.304788679670904</v>
       </c>
       <c r="D39" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E39">
         <v>1.606867498612421</v>
@@ -3442,7 +3448,7 @@
         <v>1.698715924927888</v>
       </c>
       <c r="D40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E40">
         <v>1.451820073210847</v>
@@ -3492,7 +3498,7 @@
         <v>1.703822090603589</v>
       </c>
       <c r="D41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E41">
         <v>1.451820073210847</v>
@@ -3542,7 +3548,7 @@
         <v>1.759241709824535</v>
       </c>
       <c r="D42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E42">
         <v>1.451820073210847</v>
@@ -3592,7 +3598,7 @@
         <v>1.748453032479565</v>
       </c>
       <c r="D43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E43">
         <v>1.501243727217277</v>
@@ -3642,7 +3648,7 @@
         <v>1.313033413258619</v>
       </c>
       <c r="D44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E44">
         <v>1.595925230190177</v>
@@ -3692,7 +3698,7 @@
         <v>1.307138570237948</v>
       </c>
       <c r="D45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E45">
         <v>1.595925230190177</v>
@@ -3742,7 +3748,7 @@
         <v>1.293872651700511</v>
       </c>
       <c r="D46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E46">
         <v>1.595925230190177</v>
@@ -3792,7 +3798,7 @@
         <v>1.708440278144118</v>
       </c>
       <c r="D47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E47">
         <v>1.445287539361757</v>
@@ -3842,7 +3848,7 @@
         <v>1.75288232747506</v>
       </c>
       <c r="D48" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E48">
         <v>1.445287539361757</v>
@@ -3892,7 +3898,7 @@
         <v>1.742329765811383</v>
       </c>
       <c r="D49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E49">
         <v>1.495482504593743</v>
@@ -3942,7 +3948,7 @@
         <v>1.307335154816763</v>
       </c>
       <c r="D50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E50">
         <v>1.589361214250248</v>
@@ -3992,7 +3998,7 @@
         <v>1.301408829705253</v>
       </c>
       <c r="D51" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E51">
         <v>1.589361214250248</v>
@@ -4042,7 +4048,7 @@
         <v>1.287324376806003</v>
       </c>
       <c r="D52" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E52">
         <v>1.589361214250248</v>
@@ -4092,7 +4098,7 @@
         <v>1.741577671463358</v>
       </c>
       <c r="D53" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E53">
         <v>1.433675083310133</v>
@@ -4142,7 +4148,7 @@
         <v>1.793586527085793</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E54">
         <v>1.433675083310133</v>
@@ -4192,7 +4198,7 @@
         <v>1.731444837126847</v>
       </c>
       <c r="D55" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E55">
         <v>1.485241157810864</v>
@@ -4242,7 +4248,7 @@
         <v>1.297205735321128</v>
       </c>
       <c r="D56" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E56">
         <v>1.577692794555001</v>
@@ -4292,7 +4298,7 @@
         <v>1.291223446565996</v>
       </c>
       <c r="D57" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E57">
         <v>1.577692794555001</v>
@@ -4342,7 +4348,7 @@
         <v>1.275683938932566</v>
       </c>
       <c r="D58" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E58">
         <v>1.577692794555001</v>
@@ -4442,7 +4448,7 @@
         <v>1.725587143730334</v>
       </c>
       <c r="D60" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E60">
         <v>1.417249169921011</v>
@@ -4492,7 +4498,7 @@
         <v>1.777556418838578</v>
       </c>
       <c r="D61" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E61">
         <v>1.417249169921011</v>
@@ -4542,7 +4548,7 @@
         <v>1.716048017106683</v>
       </c>
       <c r="D62" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E62">
         <v>1.470754689617085</v>
@@ -4592,7 +4598,7 @@
         <v>1.282877589184112</v>
       </c>
       <c r="D63" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E63">
         <v>1.561187720137498</v>
@@ -4642,7 +4648,7 @@
         <v>1.276816139400598</v>
       </c>
       <c r="D64" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E64">
         <v>1.561187720137498</v>
@@ -4692,7 +4698,7 @@
         <v>1.259218445029255</v>
       </c>
       <c r="D65" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E65">
         <v>1.561187720137498</v>
@@ -4742,7 +4748,7 @@
         <v>1.799190602173319</v>
       </c>
       <c r="D66" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E66">
         <v>1.767682200441425</v>
@@ -4792,7 +4798,7 @@
         <v>1.704528128435052</v>
       </c>
       <c r="D67" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E67">
         <v>1.395616765595412</v>
@@ -4842,7 +4848,7 @@
         <v>1.756445277267813</v>
       </c>
       <c r="D68" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E68">
         <v>1.395616765595412</v>
@@ -4892,7 +4898,7 @@
         <v>1.695770895943651</v>
       </c>
       <c r="D69" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E69">
         <v>1.451676472790171</v>
@@ -4942,7 +4948,7 @@
         <v>1.264007877459131</v>
       </c>
       <c r="D70" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E70">
         <v>1.539451063260933</v>
@@ -4992,7 +4998,7 @@
         <v>1.257842175124651</v>
       </c>
       <c r="D71" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E71">
         <v>1.539451063260933</v>
@@ -5042,7 +5048,7 @@
         <v>1.237533914428172</v>
       </c>
       <c r="D72" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E72">
         <v>1.539451063260933</v>
@@ -5142,7 +5148,7 @@
         <v>1.678683818930752</v>
       </c>
       <c r="D74" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E74">
         <v>1.369068774396689</v>
@@ -5192,7 +5198,7 @@
         <v>1.730536996700383</v>
       </c>
       <c r="D75" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E75">
         <v>1.369068774396689</v>
@@ -5242,7 +5248,7 @@
         <v>1.670886152386294</v>
       </c>
       <c r="D76" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E76">
         <v>1.428263063684791</v>
@@ -5292,7 +5298,7 @@
         <v>1.240850352606269</v>
       </c>
       <c r="D77" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E77">
         <v>1.51277512993595</v>
@@ -5342,7 +5348,7 @@
         <v>1.234556708145529</v>
       </c>
       <c r="D78" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E78">
         <v>1.51277512993595</v>
@@ -5392,7 +5398,7 @@
         <v>1.210921952166319</v>
       </c>
       <c r="D79" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E79">
         <v>1.51277512993595</v>
@@ -5442,7 +5448,7 @@
         <v>1.661963549027058</v>
       </c>
       <c r="D80" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E80">
         <v>1.351893249619379</v>
@@ -5492,7 +5498,7 @@
         <v>1.713775339989997</v>
       </c>
       <c r="D81" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E81">
         <v>1.351893249619379</v>
@@ -5542,7 +5548,7 @@
         <v>1.654786684582984</v>
       </c>
       <c r="D82" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E82">
         <v>1.413115492435404</v>
@@ -5592,7 +5598,7 @@
         <v>1.225868328583652</v>
       </c>
       <c r="D83" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E83">
         <v>1.495516831545256</v>
@@ -5642,7 +5648,7 @@
         <v>1.219491910509528</v>
       </c>
       <c r="D84" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E84">
         <v>1.495516831545256</v>
@@ -5692,7 +5698,7 @@
         <v>1.193705040582317</v>
       </c>
       <c r="D85" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E85">
         <v>1.495516831545256</v>
@@ -5742,7 +5748,7 @@
         <v>1.600429769178104</v>
       </c>
       <c r="D86" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E86">
         <v>1.338006244585976</v>
@@ -5792,7 +5798,7 @@
         <v>1.648444633283697</v>
       </c>
       <c r="D87" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E87">
         <v>1.338006244585976</v>
@@ -5842,7 +5848,7 @@
         <v>1.700222961583904</v>
       </c>
       <c r="D88" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E88">
         <v>1.338006244585976</v>
@@ -5892,7 +5898,7 @@
         <v>1.641769708780589</v>
       </c>
       <c r="D89" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E89">
         <v>1.400868157875824</v>
@@ -5942,7 +5948,7 @@
         <v>1.213754844674996</v>
       </c>
       <c r="D90" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E90">
         <v>1.48156290118639</v>
@@ -5992,7 +5998,7 @@
         <v>1.20731150127541</v>
       </c>
       <c r="D91" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E91">
         <v>1.48156290118639</v>
@@ -6042,7 +6048,7 @@
         <v>1.179784572886182</v>
       </c>
       <c r="D92" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E92">
         <v>1.48156290118639</v>
@@ -6092,7 +6098,7 @@
         <v>1.642770386608872</v>
       </c>
       <c r="D93" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E93">
         <v>1.332177501095747</v>
@@ -6142,7 +6148,7 @@
         <v>1.636306139581315</v>
       </c>
       <c r="D94" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E94">
         <v>1.395727627472394</v>
@@ -6192,7 +6198,7 @@
         <v>1.208670494931713</v>
       </c>
       <c r="D95" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E95">
         <v>1.475706067366088</v>
@@ -6242,7 +6248,7 @@
         <v>1.202199061202053</v>
       </c>
       <c r="D96" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E96">
         <v>1.475706067366088</v>
@@ -6292,7 +6298,7 @@
         <v>1.173941784230917</v>
       </c>
       <c r="D97" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E97">
         <v>1.475706067366088</v>
@@ -6342,7 +6348,7 @@
         <v>1.635648220856852</v>
       </c>
       <c r="D98" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E98">
         <v>1.324861414989093</v>
@@ -6392,7 +6398,7 @@
         <v>1.687394874868875</v>
       </c>
       <c r="D99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E99">
         <v>1.324861414989093</v>
@@ -6442,7 +6448,7 @@
         <v>1.629448410676523</v>
       </c>
       <c r="D100" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E100">
         <v>1.38927536840002</v>
@@ -6492,7 +6498,7 @@
         <v>1.202288752351933</v>
       </c>
       <c r="D101" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E101">
         <v>1.468354723013138</v>
@@ -6542,7 +6548,7 @@
         <v>1.195782060375976</v>
       </c>
       <c r="D102" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E102">
         <v>1.468354723013138</v>
@@ -6592,7 +6598,7 @@
         <v>1.166608069001115</v>
       </c>
       <c r="D103" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E103">
         <v>1.468354723013138</v>
@@ -6642,7 +6648,7 @@
         <v>1.636237432923918</v>
       </c>
       <c r="D104" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E104">
         <v>1.325466669958976</v>
@@ -6692,7 +6698,7 @@
         <v>1.687985545381652</v>
       </c>
       <c r="D105" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E105">
         <v>1.325466669958976</v>
@@ -6742,7 +6748,7 @@
         <v>1.630015746057932</v>
       </c>
       <c r="D106" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E106">
         <v>1.389809159530085</v>
@@ -6792,7 +6798,7 @@
         <v>1.202816709699155</v>
       </c>
       <c r="D107" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E107">
         <v>1.468962894874441</v>
@@ -6842,7 +6848,7 @@
         <v>1.19631293461462</v>
       </c>
       <c r="D108" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E108">
         <v>1.468962894874441</v>
@@ -6892,7 +6898,7 @@
         <v>1.167214782416708</v>
       </c>
       <c r="D109" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E109">
         <v>1.468962894874441</v>
@@ -6992,7 +6998,7 @@
         <v>1.686969731933735</v>
       </c>
       <c r="D111" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E111">
         <v>1.32442577469753</v>
@@ -7042,7 +7048,7 @@
         <v>1.688566437853383</v>
       </c>
       <c r="D112" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E112">
         <v>1.388891165154931</v>
@@ -7092,7 +7098,7 @@
         <v>1.116820833577004</v>
       </c>
       <c r="D113" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E113">
         <v>1.46791698325029</v>
@@ -7142,7 +7148,7 @@
         <v>1.189838416471486</v>
       </c>
       <c r="D114" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E114">
         <v>1.46791698325029</v>
@@ -7192,7 +7198,7 @@
         <v>1.16617137897391</v>
       </c>
       <c r="D115" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E115">
         <v>1.46791698325029</v>
@@ -7292,7 +7298,7 @@
         <v>1.679044765444968</v>
       </c>
       <c r="D117" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E117">
         <v>1.316305130023856</v>
@@ -7342,7 +7348,7 @@
         <v>1.681071963371414</v>
       </c>
       <c r="D118" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E118">
         <v>1.381729343587304</v>
@@ -7392,7 +7398,7 @@
         <v>1.109345926913525</v>
       </c>
       <c r="D119" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E119">
         <v>1.459757202939633</v>
@@ -7442,7 +7448,7 @@
         <v>1.116606291492413</v>
       </c>
       <c r="D120" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E120">
         <v>1.459757202939633</v>
@@ -7492,7 +7498,7 @@
         <v>1.158031166481744</v>
       </c>
       <c r="D121" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E121">
         <v>1.459757202939633</v>
@@ -7542,7 +7548,7 @@
         <v>1.667785062291963</v>
       </c>
       <c r="D122" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E122">
         <v>1.323675609160295</v>
@@ -7642,7 +7648,7 @@
         <v>1.705523534148037</v>
       </c>
       <c r="D124" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E124">
         <v>1.306151805217721</v>
@@ -7692,7 +7698,7 @@
         <v>1.0999999749233</v>
       </c>
       <c r="D125" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E125">
         <v>1.449554946447687</v>
@@ -7742,7 +7748,7 @@
         <v>1.107015681073126</v>
       </c>
       <c r="D126" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E126">
         <v>1.449554946447687</v>
@@ -7792,7 +7798,7 @@
         <v>1.074450234602739</v>
       </c>
       <c r="D127" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E127">
         <v>1.449554946447687</v>
@@ -7842,7 +7848,7 @@
         <v>1.728036618426774</v>
       </c>
       <c r="D128" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E128">
         <v>1.311858607036529</v>
@@ -7942,7 +7948,7 @@
         <v>1.735732764200063</v>
       </c>
       <c r="D130" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E130">
         <v>1.301215982596513</v>
@@ -7992,7 +7998,7 @@
         <v>1.095456639402092</v>
       </c>
       <c r="D131" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E131">
         <v>1.444595336729509</v>
@@ -8042,7 +8048,7 @@
         <v>1.102353410067069</v>
       </c>
       <c r="D132" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E132">
         <v>1.444595336729509</v>
@@ -8092,7 +8098,7 @@
         <v>1.069526305530016</v>
       </c>
       <c r="D133" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E133">
         <v>1.444595336729509</v>
@@ -8192,7 +8198,7 @@
         <v>1.767688434264066</v>
       </c>
       <c r="D135" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E135">
         <v>1.290978663803567</v>
@@ -8242,7 +8248,7 @@
         <v>1.08603337246497</v>
       </c>
       <c r="D136" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E136">
         <v>1.434308681460452</v>
@@ -8292,7 +8298,7 @@
         <v>1.092683460749394</v>
       </c>
       <c r="D137" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E137">
         <v>1.434308681460452</v>
@@ -8342,7 +8348,7 @@
         <v>1.059313654975125</v>
       </c>
       <c r="D138" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E138">
         <v>1.434308681460452</v>
@@ -8992,7 +8998,7 @@
         <v>1.823420612308294</v>
       </c>
       <c r="D151" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E151">
         <v>2.204728303692967</v>
@@ -9078,7 +9084,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9128,7 +9134,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9392,7 +9398,7 @@
         <v>2.07884565528049</v>
       </c>
       <c r="D159" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E159">
         <v>2.424795934638657</v>
@@ -9542,7 +9548,7 @@
         <v>2.074698477808512</v>
       </c>
       <c r="D162" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E162">
         <v>2.228712809543505</v>
@@ -9842,7 +9848,7 @@
         <v>2.045995448659537</v>
       </c>
       <c r="D168" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E168">
         <v>2.697722827185737</v>
@@ -9992,7 +9998,7 @@
         <v>2.025703573192318</v>
       </c>
       <c r="D171" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E171">
         <v>2.585859069325287</v>
@@ -10092,7 +10098,7 @@
         <v>2.002237248721763</v>
       </c>
       <c r="D173" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E173">
         <v>2.933150127071722</v>
@@ -10178,7 +10184,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10192,7 +10198,7 @@
         <v>2.14690100237887</v>
       </c>
       <c r="D175" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E175">
         <v>3.035145626224377</v>
@@ -10228,7 +10234,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10292,7 +10298,7 @@
         <v>2.113865641885164</v>
       </c>
       <c r="D177" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E177">
         <v>2.99862999271211</v>
@@ -10442,7 +10448,7 @@
         <v>2.224552854469621</v>
       </c>
       <c r="D180" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E180">
         <v>2.747562112891602</v>
@@ -10492,7 +10498,7 @@
         <v>2.234582155562626</v>
       </c>
       <c r="D181" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E181">
         <v>2.747562112891602</v>
@@ -10542,7 +10548,7 @@
         <v>2.532227490792448</v>
       </c>
       <c r="D182" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E182">
         <v>2.747562112891602</v>
@@ -10692,7 +10698,7 @@
         <v>2.219578642489605</v>
       </c>
       <c r="D185" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E185">
         <v>2.748307309478141</v>
@@ -10742,7 +10748,7 @@
         <v>2.229273046142372</v>
       </c>
       <c r="D186" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E186">
         <v>2.748307309478141</v>
@@ -10792,7 +10798,7 @@
         <v>2.526938081221619</v>
       </c>
       <c r="D187" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E187">
         <v>2.748307309478141</v>
@@ -10942,7 +10948,7 @@
         <v>2.223095119495316</v>
       </c>
       <c r="D190" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E190">
         <v>2.585306324177835</v>
@@ -10992,7 +10998,7 @@
         <v>2.233026276055397</v>
       </c>
       <c r="D191" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E191">
         <v>2.585306324177835</v>
@@ -11042,7 +11048,7 @@
         <v>2.530677384493038</v>
       </c>
       <c r="D192" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E192">
         <v>2.585306324177835</v>
@@ -11192,7 +11198,7 @@
         <v>2.351296670264901</v>
       </c>
       <c r="D195" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E195">
         <v>2.34477901699545</v>
@@ -11242,7 +11248,7 @@
         <v>2.531296670264901</v>
       </c>
       <c r="D196" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E196">
         <v>2.34477901699545</v>
@@ -11442,7 +11448,7 @@
         <v>2.354338556588907</v>
       </c>
       <c r="D200" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E200">
         <v>2.692933327062218</v>
@@ -11492,7 +11498,7 @@
         <v>2.534338556588906</v>
       </c>
       <c r="D201" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E201">
         <v>2.692933327062218</v>
@@ -11692,7 +11698,7 @@
         <v>2.353252705775172</v>
       </c>
       <c r="D205" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E205">
         <v>3.037215179660817</v>
@@ -11742,7 +11748,7 @@
         <v>2.533252705775172</v>
       </c>
       <c r="D206" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E206">
         <v>3.037215179660817</v>
@@ -11792,7 +11798,7 @@
         <v>-1.066638455738899</v>
       </c>
       <c r="D207" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E207">
         <v>-1.465413797453388</v>
@@ -11842,7 +11848,7 @@
         <v>-1.0366384557389</v>
       </c>
       <c r="D208" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E208">
         <v>-1.465413797453388</v>
@@ -11892,7 +11898,7 @@
         <v>-0.9510556888450674</v>
       </c>
       <c r="D209" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E209">
         <v>-1.465413797453388</v>
@@ -11942,7 +11948,7 @@
         <v>-1.819265145803461</v>
       </c>
       <c r="D210" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E210">
         <v>-1.307592851757549</v>
@@ -11992,7 +11998,7 @@
         <v>-1.771950960365871</v>
       </c>
       <c r="D211" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E211">
         <v>-1.297263464992842</v>
@@ -12042,7 +12048,7 @@
         <v>-1.016934078228135</v>
       </c>
       <c r="D212" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E212">
         <v>-1.07654556696558</v>
@@ -12092,7 +12098,7 @@
         <v>-1.083441760674821</v>
       </c>
       <c r="D213" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E213">
         <v>-1.481089607902267</v>
@@ -12142,7 +12148,7 @@
         <v>-1.053441760674821</v>
       </c>
       <c r="D214" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E214">
         <v>-1.481089607902267</v>
@@ -12192,7 +12198,7 @@
         <v>-0.9668769824535648</v>
       </c>
       <c r="D215" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E215">
         <v>-1.481089607902267</v>
@@ -12242,7 +12248,7 @@
         <v>-1.83581385521005</v>
       </c>
       <c r="D216" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E216">
         <v>-1.323195920626619</v>
@@ -12292,7 +12298,7 @@
         <v>-1.787408546075322</v>
       </c>
       <c r="D217" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E217">
         <v>-1.311375331475824</v>
@@ -12392,7 +12398,7 @@
         <v>-1.07759404974841</v>
       </c>
       <c r="D219" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E219">
         <v>-1.503621288834554</v>
@@ -12442,7 +12448,7 @@
         <v>-0.9896177741137624</v>
       </c>
       <c r="D220" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E220">
         <v>-1.503621288834554</v>
@@ -12492,7 +12498,7 @@
         <v>-1.859600200509798</v>
       </c>
       <c r="D221" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E221">
         <v>-1.345623046194952</v>
@@ -12542,7 +12548,7 @@
         <v>-1.809626560915746</v>
       </c>
       <c r="D222" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E222">
         <v>-1.33165907208308</v>
@@ -12592,7 +12598,7 @@
         <v>-1.047695097971209</v>
       </c>
       <c r="D223" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E223">
         <v>-1.119714428935569</v>
@@ -12642,7 +12648,7 @@
         <v>-1.107622621715292</v>
       </c>
       <c r="D224" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E224">
         <v>-1.53163495662184</v>
@@ -12692,7 +12698,7 @@
         <v>-1.017891429537125</v>
       </c>
       <c r="D225" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E225">
         <v>-1.53163495662184</v>
@@ -12742,7 +12748,7 @@
         <v>-1.889173794113544</v>
       </c>
       <c r="D226" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E226">
         <v>-1.373506720164198</v>
@@ -12792,7 +12798,7 @@
         <v>-1.837250247248916</v>
       </c>
       <c r="D227" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E227">
         <v>-1.356877872782539</v>
@@ -12892,7 +12898,7 @@
         <v>-1.136466558905362</v>
       </c>
       <c r="D229" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E229">
         <v>-1.55854347811301</v>
@@ -12942,7 +12948,7 @@
         <v>-1.045049682086217</v>
       </c>
       <c r="D230" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E230">
         <v>-1.55854347811301</v>
@@ -12992,7 +12998,7 @@
         <v>-1.91758070195225</v>
       </c>
       <c r="D231" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E231">
         <v>-1.400290376126407</v>
@@ -13042,7 +13048,7 @@
         <v>-1.863784172153202</v>
       </c>
       <c r="D232" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E232">
         <v>-1.38110178540104</v>
@@ -13092,7 +13098,7 @@
         <v>-1.091913194675672</v>
       </c>
       <c r="D233" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E233">
         <v>-0.942243215869925</v>
@@ -13142,7 +13148,7 @@
         <v>-1.06938217480964</v>
       </c>
       <c r="D234" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E234">
         <v>-0.942243215869925</v>
@@ -13192,7 +13198,7 @@
         <v>-1.09938217480964</v>
       </c>
       <c r="D235" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E235">
         <v>-0.942243215869925</v>
@@ -13242,7 +13248,7 @@
         <v>-1.069955605077879</v>
       </c>
       <c r="D236" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E236">
         <v>-1.583220381123139</v>
@@ -13292,7 +13298,7 @@
         <v>-1.943631724851574</v>
       </c>
       <c r="D237" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E237">
         <v>-1.42485276914577</v>
@@ -13342,7 +13348,7 @@
         <v>-1.888117545191031</v>
       </c>
       <c r="D238" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E238">
         <v>-1.403316723609694</v>
@@ -13392,7 +13398,7 @@
         <v>-1.111780678073619</v>
       </c>
       <c r="D239" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E239">
         <v>-0.8811636624809664</v>
@@ -13442,7 +13448,7 @@
         <v>-1.088104558299923</v>
       </c>
       <c r="D240" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E240">
         <v>-0.8811636624809664</v>
@@ -13492,7 +13498,7 @@
         <v>-1.118104558299923</v>
       </c>
       <c r="D241" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E241">
         <v>-0.8811636624809664</v>
@@ -13542,7 +13548,7 @@
         <v>-1.100958399511376</v>
       </c>
       <c r="D242" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E242">
         <v>-1.613938092389432</v>
@@ -13592,7 +13598,7 @@
         <v>-1.976059935121095</v>
       </c>
       <c r="D243" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E243">
         <v>-1.455427938828461</v>
@@ -13642,7 +13648,7 @@
         <v>-1.918407631706518</v>
       </c>
       <c r="D244" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E244">
         <v>-1.430969790828538</v>
@@ -13692,7 +13698,7 @@
         <v>-1.136511642828615</v>
       </c>
       <c r="D245" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E245">
         <v>-1.028859339414037</v>
@@ -13742,7 +13748,7 @@
         <v>-1.111410107218897</v>
       </c>
       <c r="D246" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E246">
         <v>-1.028859339414037</v>
@@ -13792,7 +13798,7 @@
         <v>-1.141410107218897</v>
       </c>
       <c r="D247" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E247">
         <v>-1.028859339414037</v>
@@ -13842,7 +13848,7 @@
         <v>-1.117512484565025</v>
       </c>
       <c r="D248" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E248">
         <v>-1.630339955971323</v>
@@ -13892,7 +13898,7 @@
         <v>-1.993375127533532</v>
       </c>
       <c r="D249" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E249">
         <v>-1.471753691674473</v>
@@ -13942,7 +13948,7 @@
         <v>-1.934581163080772</v>
       </c>
       <c r="D250" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E250">
         <v>-1.445735273589034</v>
@@ -13992,7 +13998,7 @@
         <v>-1.149716855503595</v>
       </c>
       <c r="D251" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E251">
         <v>-1.032336626753983</v>
@@ -14042,7 +14048,7 @@
         <v>-1.123854212535088</v>
       </c>
       <c r="D252" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E252">
         <v>-1.032336626753983</v>
@@ -14092,7 +14098,7 @@
         <v>-1.153854212535088</v>
       </c>
       <c r="D253" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E253">
         <v>-1.032336626753983</v>
@@ -14142,7 +14148,7 @@
         <v>-1.135440729342402</v>
       </c>
       <c r="D254" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E254">
         <v>-1.64810334332546</v>
@@ -14192,7 +14198,7 @@
         <v>-2.012127659427111</v>
       </c>
       <c r="D255" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E255">
         <v>-1.489434650316991</v>
@@ -14242,7 +14248,7 @@
         <v>-1.95209726430005</v>
       </c>
       <c r="D256" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E256">
         <v>-1.461726443643339</v>
@@ -14292,7 +14298,7 @@
         <v>-1.164018236969687</v>
       </c>
       <c r="D257" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E257">
         <v>-1.112656534851095</v>
@@ -14342,7 +14348,7 @@
         <v>-1.137331306884979</v>
       </c>
       <c r="D258" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E258">
         <v>-1.112656534851095</v>
@@ -14392,7 +14398,7 @@
         <v>-1.167331306884979</v>
       </c>
       <c r="D259" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E259">
         <v>-1.112656534851095</v>
@@ -14442,7 +14448,7 @@
         <v>-2.029751754240792</v>
       </c>
       <c r="D260" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E260">
         <v>-1.506051653998461</v>
@@ -14492,7 +14498,7 @@
         <v>-1.968559330884256</v>
       </c>
       <c r="D261" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E261">
         <v>-1.476755342077862</v>
@@ -14542,7 +14548,7 @@
         <v>-1.177459030157264</v>
       </c>
       <c r="D262" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E262">
         <v>-1.113758929914932</v>
@@ -14592,7 +14598,7 @@
         <v>-1.149997414586239</v>
       </c>
       <c r="D263" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E263">
         <v>-1.113758929914932</v>
@@ -14642,7 +14648,7 @@
         <v>-1.179997414586239</v>
       </c>
       <c r="D264" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E264">
         <v>-1.113758929914932</v>
@@ -14692,7 +14698,7 @@
         <v>-2.049264235927141</v>
       </c>
       <c r="D265" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E265">
         <v>-1.524449136731304</v>
@@ -14742,7 +14748,7 @@
         <v>-1.986785275316561</v>
       </c>
       <c r="D266" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E266">
         <v>-1.493394557230178</v>
@@ -14792,7 +14798,7 @@
         <v>-1.192339977729051</v>
       </c>
       <c r="D267" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E267">
         <v>-0.9807727745942727</v>
@@ -14842,7 +14848,7 @@
         <v>-1.16402067065533</v>
       </c>
       <c r="D268" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E268">
         <v>-0.9807727745942727</v>
@@ -14892,7 +14898,7 @@
         <v>-1.19402067065533</v>
       </c>
       <c r="D269" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E269">
         <v>-0.9807727745942727</v>
@@ -14942,7 +14948,7 @@
         <v>-2.083260847634321</v>
       </c>
       <c r="D270" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E270">
         <v>-1.55650308491236</v>
@@ -14992,7 +14998,7 @@
         <v>-2.018540352185904</v>
       </c>
       <c r="D271" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E271">
         <v>-1.52238507446619</v>
@@ -15042,7 +15048,7 @@
         <v>-1.218267064020021</v>
       </c>
       <c r="D272" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E272">
         <v>-1.15072047992809</v>
@@ -15092,7 +15098,7 @@
         <v>-1.188453400387743</v>
       </c>
       <c r="D273" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E273">
         <v>-1.15072047992809</v>
@@ -15142,7 +15148,7 @@
         <v>-1.218453400387743</v>
       </c>
       <c r="D274" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E274">
         <v>-1.15072047992809</v>
@@ -15192,7 +15198,7 @@
         <v>-2.129173370599524</v>
       </c>
       <c r="D275" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E275">
         <v>-1.599792035136694</v>
@@ -15242,7 +15248,7 @@
         <v>-2.061425675834721</v>
       </c>
       <c r="D276" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E276">
         <v>-1.561536852291463</v>
@@ -15292,7 +15298,7 @@
         <v>-1.253281669446231</v>
       </c>
       <c r="D277" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E277">
         <v>-1.285422798224685</v>
@@ -15342,7 +15348,7 @@
         <v>-1.221449872936362</v>
       </c>
       <c r="D278" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E278">
         <v>-1.285422798224685</v>
@@ -15392,7 +15398,7 @@
         <v>-1.251449872936362</v>
       </c>
       <c r="D279" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E279">
         <v>-1.285422798224685</v>
@@ -15442,7 +15448,7 @@
         <v>-2.169540849194301</v>
       </c>
       <c r="D280" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E280">
         <v>-1.637852800668912</v>
@@ -15492,7 +15498,7 @@
         <v>-2.099131562434238</v>
       </c>
       <c r="D281" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E281">
         <v>-1.595960108763492</v>
@@ -15542,7 +15548,7 @@
         <v>-1.284067416858071</v>
       </c>
       <c r="D282" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E282">
         <v>-1.430231131562097</v>
@@ -15592,7 +15598,7 @@
         <v>-1.250461225684695</v>
       </c>
       <c r="D283" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E283">
         <v>-1.430231131562097</v>
@@ -15642,7 +15648,7 @@
         <v>-1.280461225684695</v>
       </c>
       <c r="D284" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E284">
         <v>-1.430231131562097</v>
@@ -15692,7 +15698,7 @@
         <v>-2.189959023684696</v>
       </c>
       <c r="D285" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E285">
         <v>-1.657104222331285</v>
@@ -15742,7 +15748,7 @@
         <v>-2.11820348366153</v>
       </c>
       <c r="D286" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E286">
         <v>-1.613371650966291</v>
@@ -15792,7 +15798,7 @@
         <v>-1.299639079601296</v>
       </c>
       <c r="D287" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E287">
         <v>-1.362715372273368</v>
@@ -15842,7 +15848,7 @@
         <v>-1.265135386252518</v>
       </c>
       <c r="D288" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E288">
         <v>-1.362715372273368</v>
@@ -15892,7 +15898,7 @@
         <v>-1.295135386252518</v>
       </c>
       <c r="D289" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E289">
         <v>-1.362715372273368</v>
@@ -15942,7 +15948,7 @@
         <v>-2.214173184477514</v>
       </c>
       <c r="D290" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E290">
         <v>-1.679934716793084</v>
@@ -15992,7 +15998,7 @@
         <v>-2.140821106380096</v>
       </c>
       <c r="D291" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E291">
         <v>-1.634020210059946</v>
@@ -16042,7 +16048,7 @@
         <v>-1.318105703326807</v>
       </c>
       <c r="D292" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E292">
         <v>-1.489781742375517</v>
@@ -16092,7 +16098,7 @@
         <v>-1.282537651261862</v>
       </c>
       <c r="D293" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E293">
         <v>-1.489781742375517</v>
@@ -16142,7 +16148,7 @@
         <v>-1.312537651261862</v>
       </c>
       <c r="D294" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E294">
         <v>-1.489781742375517</v>
@@ -16192,7 +16198,7 @@
         <v>-2.241121102143395</v>
       </c>
       <c r="D295" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E295">
         <v>-1.705342753449486</v>
@@ -16242,7 +16248,7 @@
         <v>-2.165992238265808</v>
       </c>
       <c r="D296" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E296">
         <v>-1.656999972816785</v>
@@ -16292,7 +16298,7 @@
         <v>-1.338657192184084</v>
       </c>
       <c r="D297" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E297">
         <v>-1.427033480143279</v>
@@ -16342,7 +16348,7 @@
         <v>-1.301904616265692</v>
       </c>
       <c r="D298" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E298">
         <v>-1.427033480143279</v>
@@ -16392,7 +16398,7 @@
         <v>-1.331904616265692</v>
       </c>
       <c r="D299" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E299">
         <v>-1.427033480143279</v>
@@ -16442,7 +16448,7 @@
         <v>1.347720014974502</v>
       </c>
       <c r="D300" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E300">
         <v>1.579062118830282</v>
@@ -16492,7 +16498,7 @@
         <v>1.334700016044109</v>
       </c>
       <c r="D301" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E301">
         <v>1.593089491417174</v>
@@ -16542,7 +16548,7 @@
         <v>1.841747387561394</v>
       </c>
       <c r="D302" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E302">
         <v>1.890874754800249</v>
@@ -16592,7 +16598,7 @@
         <v>1.862485279427185</v>
       </c>
       <c r="D303" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E303">
         <v>1.890874754800249</v>
@@ -16642,7 +16648,7 @@
         <v>1.441706845387347</v>
       </c>
       <c r="D304" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E304">
         <v>1.664215600520115</v>
@@ -16692,7 +16698,7 @@
         <v>1.435400191486443</v>
       </c>
       <c r="D305" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E305">
         <v>1.704389685327122</v>
@@ -16742,7 +16748,7 @@
         <v>1.856584782452771</v>
       </c>
       <c r="D306" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E306">
         <v>1.861880930194354</v>
@@ -16792,7 +16798,7 @@
         <v>1.9645987906652</v>
       </c>
       <c r="D307" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E307">
         <v>1.861880930194354</v>
@@ -16842,7 +16848,7 @@
         <v>2.014804950663784</v>
       </c>
       <c r="D308" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E308">
         <v>1.689180786611569</v>
@@ -16892,7 +16898,7 @@
         <v>1.927301606872644</v>
       </c>
       <c r="D309" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E309">
         <v>1.689180786611569</v>
@@ -16942,7 +16948,7 @@
         <v>1.922617032689892</v>
       </c>
       <c r="D310" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E310">
         <v>1.689180786611569</v>
@@ -16992,7 +16998,7 @@
         <v>1.696992868637676</v>
       </c>
       <c r="D311" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E311">
         <v>1.791368704585461</v>
@@ -17342,7 +17348,7 @@
         <v>1.869784887916945</v>
       </c>
       <c r="D318" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E318">
         <v>1.868536559812515</v>
@@ -17392,7 +17398,7 @@
         <v>1.892281544125805</v>
       </c>
       <c r="D319" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E319">
         <v>1.868536559812515</v>
@@ -17442,7 +17448,7 @@
         <v>1.879784887916945</v>
       </c>
       <c r="D320" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E320">
         <v>1.868536559812515</v>
@@ -17492,7 +17498,7 @@
         <v>1.830509026107986</v>
       </c>
       <c r="D321" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E321">
         <v>1.588842690067986</v>
@@ -17542,7 +17548,7 @@
         <v>1.823342590879987</v>
       </c>
       <c r="D322" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E322">
         <v>1.588842690067986</v>
@@ -17592,7 +17598,7 @@
         <v>1.597009323671986</v>
       </c>
       <c r="D323" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E323">
         <v>1.690676056463986</v>
@@ -17642,7 +17648,7 @@
         <v>1.564008728543987</v>
       </c>
       <c r="D324" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E324">
         <v>1.690841103059988</v>
@@ -17692,7 +17698,7 @@
         <v>1.612175362147987</v>
       </c>
       <c r="D325" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E325">
         <v>1.690841103059988</v>
@@ -17742,7 +17748,7 @@
         <v>1.608508629355987</v>
       </c>
       <c r="D326" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E326">
         <v>1.690841103059988</v>
@@ -17792,7 +17798,7 @@
         <v>1.611175163771987</v>
       </c>
       <c r="D327" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E327">
         <v>1.690841103059988</v>
@@ -17892,7 +17898,7 @@
         <v>1.787174370267988</v>
       </c>
       <c r="D329" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E329">
         <v>1.578675659711986</v>
@@ -17942,7 +17948,7 @@
         <v>1.812507439099989</v>
       </c>
       <c r="D330" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E330">
         <v>1.578675659711986</v>
@@ -17992,7 +17998,7 @@
         <v>1.783507637475988</v>
       </c>
       <c r="D331" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E331">
         <v>1.578675659711986</v>
@@ -18042,7 +18048,7 @@
         <v>1.797174370267989</v>
       </c>
       <c r="D332" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E332">
         <v>1.578675659711986</v>
@@ -18092,7 +18098,7 @@
         <v>1.796508232603987</v>
       </c>
       <c r="D333" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E333">
         <v>1.578675659711986</v>
@@ -18142,7 +18148,7 @@
         <v>1.60619577124814</v>
       </c>
       <c r="D334" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E334">
         <v>1.409496709559184</v>
@@ -18192,7 +18198,7 @@
         <v>1.639829926132983</v>
       </c>
       <c r="D335" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E335">
         <v>1.409496709559184</v>
@@ -18242,7 +18248,7 @@
         <v>1.641634855442047</v>
       </c>
       <c r="D336" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E336">
         <v>1.409496709559184</v>
@@ -18292,7 +18298,7 @@
         <v>1.294651169712725</v>
       </c>
       <c r="D337" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E337">
         <v>1.17011455017335</v>
@@ -18342,7 +18348,7 @@
         <v>1.309805629866267</v>
       </c>
       <c r="D338" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E338">
         <v>1.17011455017335</v>
@@ -18392,7 +18398,7 @@
         <v>1.302846240403662</v>
       </c>
       <c r="D339" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E339">
         <v>1.17011455017335</v>
@@ -18442,7 +18448,7 @@
         <v>1.302846240403662</v>
       </c>
       <c r="D340" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E340">
         <v>1.17011455017335</v>
@@ -18492,7 +18498,7 @@
         <v>1.306789315595589</v>
       </c>
       <c r="D341" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E341">
         <v>1.17011455017335</v>
@@ -18542,7 +18548,7 @@
         <v>1.225269010326891</v>
       </c>
       <c r="D342" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E342">
         <v>1.17011455017335</v>
@@ -18592,7 +18598,7 @@
         <v>1.444294269397325</v>
       </c>
       <c r="D343" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E343">
         <v>1.256000185094495</v>
@@ -18642,7 +18648,7 @@
         <v>1.501117816501946</v>
       </c>
       <c r="D344" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E344">
         <v>1.256000185094495</v>
@@ -18692,7 +18698,7 @@
         <v>1.083058995014017</v>
       </c>
       <c r="D345" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E345">
         <v>1.093353102453659</v>
@@ -18742,7 +18748,7 @@
         <v>1.408730452400234</v>
       </c>
       <c r="D346" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E346">
         <v>1.224172692200284</v>
@@ -18792,7 +18798,7 @@
         <v>1.47198161896276</v>
       </c>
       <c r="D347" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E347">
         <v>1.224172692200284</v>
@@ -18892,7 +18898,7 @@
         <v>1.382122760311682</v>
       </c>
       <c r="D349" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E349">
         <v>1.191863351807043</v>
@@ -18942,7 +18948,7 @@
         <v>1.442404318382183</v>
       </c>
       <c r="D350" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E350">
         <v>1.191863351807043</v>
@@ -19042,7 +19048,7 @@
         <v>1.370401955803482</v>
       </c>
       <c r="D352" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E352">
         <v>1.1776309463328</v>
@@ -19092,7 +19098,7 @@
         <v>1.429375388370835</v>
       </c>
       <c r="D353" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E353">
         <v>1.1776309463328</v>
@@ -19142,7 +19148,7 @@
         <v>1.010452200278918</v>
       </c>
       <c r="D354" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E354">
         <v>1.015068140738506</v>
@@ -19192,7 +19198,7 @@
         <v>1.025068140738506</v>
       </c>
       <c r="D355" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E355">
         <v>1.015068140738506</v>
@@ -19242,7 +19248,7 @@
         <v>1.355513343522262</v>
       </c>
       <c r="D356" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E356">
         <v>1.159551917134175</v>
@@ -19292,7 +19298,7 @@
         <v>1.4128251006118</v>
       </c>
       <c r="D357" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E357">
         <v>1.159551917134175</v>
@@ -19342,7 +19348,7 @@
         <v>0.9937025114625451</v>
       </c>
       <c r="D358" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E358">
         <v>1.019315457208822</v>
@@ -19392,7 +19398,7 @@
         <v>1.009315457208822</v>
       </c>
       <c r="D359" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E359">
         <v>1.019315457208822</v>
@@ -19442,7 +19448,7 @@
         <v>1.344301537527252</v>
       </c>
       <c r="D360" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E360">
         <v>1.145937581283092</v>
@@ -19492,7 +19498,7 @@
         <v>1.400361976983419</v>
       </c>
       <c r="D361" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E361">
         <v>1.145937581283092</v>
@@ -19642,7 +19648,7 @@
         <v>1.32595157423566</v>
       </c>
       <c r="D364" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E364">
         <v>1.123655483000445</v>
@@ -19692,7 +19698,7 @@
         <v>1.379964026717319</v>
       </c>
       <c r="D365" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E365">
         <v>1.123655483000445</v>
@@ -19742,7 +19748,7 @@
         <v>0.9604455210151182</v>
       </c>
       <c r="D366" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E366">
         <v>0.9494825324195202</v>
@@ -19792,7 +19798,7 @@
         <v>0.9780380495261229</v>
       </c>
       <c r="D367" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E367">
         <v>0.9494825324195202</v>
@@ -19842,7 +19848,7 @@
         <v>0.9780380495261229</v>
       </c>
       <c r="D368" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E368">
         <v>0.9494825324195202</v>
@@ -19892,7 +19898,7 @@
         <v>0.93948253241952</v>
       </c>
       <c r="D369" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E369">
         <v>0.9494825324195202</v>
@@ -19942,7 +19948,7 @@
         <v>1.346901155844391</v>
       </c>
       <c r="D370" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E370">
         <v>1.225539647019887</v>
@@ -19992,7 +19998,7 @@
         <v>1.331298641136886</v>
       </c>
       <c r="D371" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E371">
         <v>1.225539647019887</v>
@@ -20042,7 +20048,7 @@
         <v>1.154256377900131</v>
       </c>
       <c r="D372" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E372">
         <v>1.26001537201713</v>
@@ -20092,7 +20098,7 @@
         <v>1.14857562348788</v>
       </c>
       <c r="D373" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E373">
         <v>1.274334617604878</v>
@@ -20142,7 +20148,7 @@
         <v>1.324412857309625</v>
       </c>
       <c r="D374" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E374">
         <v>1.205852605838874</v>
@@ -20192,7 +20198,7 @@
         <v>1.043943419081145</v>
       </c>
       <c r="D375" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E375">
         <v>1.269702413198143</v>
@@ -20242,7 +20248,7 @@
         <v>1.36666643673015</v>
       </c>
       <c r="D376" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E376">
         <v>1.400907442613152</v>
@@ -20292,7 +20298,7 @@
         <v>1.3381061852594</v>
       </c>
       <c r="D377" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E377">
         <v>1.400907442613152</v>
@@ -20342,7 +20348,7 @@
         <v>1.337921514632137</v>
       </c>
       <c r="D378" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E378">
         <v>1.216329758597064</v>
@@ -20392,7 +20398,7 @@
         <v>1.321935254573682</v>
       </c>
       <c r="D379" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E379">
         <v>1.216329758597064</v>
@@ -20442,7 +20448,7 @@
         <v>1.144547620521072</v>
       </c>
       <c r="D380" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E380">
         <v>1.250153116497689</v>
@@ -20492,7 +20498,7 @@
         <v>1.138751742503535</v>
       </c>
       <c r="D381" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E381">
         <v>1.264357238480152</v>
@@ -20542,7 +20548,7 @@
         <v>1.314166856439233</v>
       </c>
       <c r="D382" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E382">
         <v>1.195568230433388</v>
@@ -20592,7 +20598,7 @@
         <v>1.035309148684748</v>
       </c>
       <c r="D383" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E383">
         <v>1.260914644661365</v>
@@ -20742,7 +20748,7 @@
         <v>1.326338641239302</v>
       </c>
       <c r="D386" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E386">
         <v>1.204449888450566</v>
@@ -20792,7 +20798,7 @@
         <v>1.309857386591409</v>
       </c>
       <c r="D387" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E387">
         <v>1.204449888450566</v>
@@ -20842,7 +20848,7 @@
         <v>1.132024257408305</v>
       </c>
       <c r="D388" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E388">
         <v>1.237431755549148</v>
@@ -20892,7 +20898,7 @@
         <v>1.126079881013937</v>
       </c>
       <c r="D389" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E389">
         <v>1.25148737915478</v>
@@ -20942,7 +20948,7 @@
         <v>1.300950500901255</v>
       </c>
       <c r="D390" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E390">
         <v>1.182302375436465</v>
@@ -20992,7 +20998,7 @@
         <v>1.024171770422406</v>
       </c>
       <c r="D391" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E391">
         <v>1.249579268563249</v>
@@ -21042,7 +21048,7 @@
         <v>1.347949275999877</v>
       </c>
       <c r="D392" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E392">
         <v>1.407134279718192</v>
@@ -21092,7 +21098,7 @@
         <v>1.319301150535088</v>
       </c>
       <c r="D393" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E393">
         <v>1.407134279718192</v>
@@ -21142,7 +21148,7 @@
         <v>1.31894662096582</v>
       </c>
       <c r="D394" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E394">
         <v>1.196868329195712</v>
@@ -21192,7 +21198,7 @@
         <v>1.302149468015641</v>
       </c>
       <c r="D395" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E395">
         <v>1.196868329195712</v>
@@ -21242,7 +21248,7 @@
         <v>1.12403203036048</v>
       </c>
       <c r="D396" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E396">
         <v>1.229313169180409</v>
@@ -21292,7 +21298,7 @@
         <v>1.117992884475426</v>
       </c>
       <c r="D397" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E397">
         <v>1.243274023295355</v>
@@ -21342,7 +21348,7 @@
         <v>1.017064058620981</v>
       </c>
       <c r="D398" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E398">
         <v>1.242345197440909</v>
@@ -21492,7 +21498,7 @@
         <v>1.309314370259902</v>
       </c>
       <c r="D401" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E401">
         <v>1.212105582664171</v>
@@ -21542,7 +21548,7 @@
         <v>1.113617673828013</v>
       </c>
       <c r="D402" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E402">
         <v>1.218734158789721</v>
@@ -21592,7 +21598,7 @@
         <v>1.107455037549294</v>
       </c>
       <c r="D403" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E403">
         <v>1.232571522511002</v>
@@ -21642,7 +21648,7 @@
         <v>1.00780227909606</v>
       </c>
       <c r="D404" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E404">
         <v>1.232918764057767</v>
@@ -21828,7 +21834,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21842,7 +21848,7 @@
         <v>1.096911392393543</v>
       </c>
       <c r="D408" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E408">
         <v>1.20176374642348</v>
@@ -21878,7 +21884,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21892,7 +21898,7 @@
         <v>1.090550657915995</v>
       </c>
       <c r="D409" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E409">
         <v>1.215403011945933</v>
@@ -21928,7 +21934,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21942,7 +21948,7 @@
         <v>0.9929449141839808</v>
       </c>
       <c r="D410" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E410">
         <v>1.217797268213918</v>
@@ -21978,7 +21984,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22028,7 +22034,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22078,7 +22084,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22092,7 +22098,7 @@
         <v>1.076787728620787</v>
       </c>
       <c r="D413" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E413">
         <v>1.194722566962074</v>
@@ -22142,7 +22148,7 @@
         <v>1.070188373624195</v>
       </c>
       <c r="D414" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E414">
         <v>1.194722566962074</v>
@@ -22192,7 +22198,7 @@
         <v>0.9750483752556411</v>
       </c>
       <c r="D415" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E415">
         <v>1.199582568593519</v>
@@ -22242,7 +22248,7 @@
         <v>1.06618192359011</v>
       </c>
       <c r="D416" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E416">
         <v>1.199582568593519</v>
@@ -22292,7 +22298,7 @@
         <v>1.301445795242007</v>
       </c>
       <c r="D417" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E417">
         <v>1.466305796873452</v>
@@ -22342,7 +22348,7 @@
         <v>1.325778053569659</v>
       </c>
       <c r="D418" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E418">
         <v>1.466305796873452</v>
@@ -22392,7 +22398,7 @@
         <v>1.061021828820504</v>
       </c>
       <c r="D419" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E419">
         <v>1.178520456495379</v>
@@ -22442,7 +22448,7 @@
         <v>1.05423552639545</v>
       </c>
       <c r="D420" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E420">
         <v>1.178520456495379</v>
@@ -22492,7 +22498,7 @@
         <v>0.9610273181210012</v>
       </c>
       <c r="D421" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E421">
         <v>1.18531224822093</v>
@@ -22542,7 +22548,7 @@
         <v>1.052098550645983</v>
       </c>
       <c r="D422" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E422">
         <v>1.18531224822093</v>
@@ -22592,7 +22598,7 @@
         <v>1.288172527821214</v>
       </c>
       <c r="D423" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E423">
         <v>1.460679389446836</v>
@@ -22642,7 +22648,7 @@
         <v>1.312816365196303</v>
       </c>
       <c r="D424" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E424">
         <v>1.460679389446836</v>
@@ -22792,7 +22798,7 @@
         <v>0.8755952802088971</v>
       </c>
       <c r="D427" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E427">
         <v>1.122137607315365</v>
@@ -22842,7 +22848,7 @@
         <v>1.266605330685716</v>
       </c>
       <c r="D428" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E428">
         <v>1.559580979333694</v>
@@ -22928,7 +22934,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22942,7 +22948,7 @@
         <v>0.8602148664207081</v>
       </c>
       <c r="D430" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E430">
         <v>1.107098980500247</v>
@@ -22978,7 +22984,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -22992,7 +22998,7 @@
         <v>1.280896373713855</v>
       </c>
       <c r="D431" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E431">
         <v>1.524099754797897</v>
@@ -23028,7 +23034,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23192,7 +23198,7 @@
         <v>1.302688953291221</v>
       </c>
       <c r="D435" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E435">
         <v>1.419681456386476</v>
@@ -23278,7 +23284,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23328,7 +23334,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23378,7 +23384,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23392,7 +23398,7 @@
         <v>1.257626439327654</v>
       </c>
       <c r="D439" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E439">
         <v>1.411664944525371</v>
@@ -23428,7 +23434,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23442,7 +23448,7 @@
         <v>1.840766780529548</v>
       </c>
       <c r="D440" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E440">
         <v>2.000338151296236</v>
@@ -23492,7 +23498,7 @@
         <v>2.174266578212954</v>
       </c>
       <c r="D441" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E441">
         <v>2.309284269167179</v>
@@ -23542,7 +23548,7 @@
         <v>2.096677111858851</v>
       </c>
       <c r="D442" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E442">
         <v>1.937337746663046</v>
@@ -23592,7 +23598,7 @@
         <v>1.86232005570882</v>
       </c>
       <c r="D443" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E443">
         <v>1.975355842250461</v>
@@ -23642,7 +23648,7 @@
         <v>1.842592596122513</v>
       </c>
       <c r="D444" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E444">
         <v>2.002261997256608</v>
@@ -23692,7 +23698,7 @@
         <v>2.176435500091845</v>
       </c>
       <c r="D445" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E445">
         <v>2.311735028352367</v>
@@ -23742,7 +23748,7 @@
         <v>2.099152378635891</v>
       </c>
       <c r="D446" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E446">
         <v>1.939947805195271</v>
@@ -23792,7 +23798,7 @@
         <v>1.864648276934749</v>
       </c>
       <c r="D447" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E447">
         <v>1.97756152551713</v>
@@ -23842,7 +23848,7 @@
         <v>1.84474004582061</v>
       </c>
       <c r="D448" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E448">
         <v>2.004524746267355</v>
@@ -23892,7 +23898,7 @@
         <v>2.178986497384215</v>
       </c>
       <c r="D449" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E449">
         <v>2.314617511168604</v>
@@ -23942,7 +23948,7 @@
         <v>2.102063686280291</v>
       </c>
       <c r="D450" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E450">
         <v>1.943017649394564</v>
@@ -23992,7 +23998,7 @@
         <v>1.867386635610175</v>
       </c>
       <c r="D451" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E451">
         <v>1.980155760051744</v>
@@ -24042,7 +24048,7 @@
         <v>2.182944230037506</v>
       </c>
       <c r="D452" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E452">
         <v>2.319089525466108</v>
@@ -24092,7 +24098,7 @@
         <v>2.106580420720769</v>
       </c>
       <c r="D453" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E453">
         <v>1.947780344621405</v>
@@ -24142,7 +24148,7 @@
         <v>1.871635049192803</v>
       </c>
       <c r="D454" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E454">
         <v>1.984180572919497</v>
@@ -24192,7 +24198,7 @@
         <v>2.18904965856885</v>
       </c>
       <c r="D455" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E455">
         <v>2.325988314767062</v>
@@ -24242,7 +24248,7 @@
         <v>2.113548197914732</v>
       </c>
       <c r="D456" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E456">
         <v>1.955127555226921</v>
@@ -24292,7 +24298,7 @@
         <v>1.878188899028709</v>
       </c>
       <c r="D457" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E457">
         <v>2.015269716995014</v>
@@ -24342,7 +24348,7 @@
         <v>1.88583444385064</v>
       </c>
       <c r="D458" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E458">
         <v>2.125307034142769</v>
@@ -24392,7 +24398,7 @@
         <v>2.298073483752043</v>
       </c>
       <c r="D459" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E459">
         <v>2.037664496092738</v>
@@ -24442,7 +24448,7 @@
         <v>1.897427651995606</v>
       </c>
       <c r="D460" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E460">
         <v>2.100495646236972</v>
@@ -24492,7 +24498,7 @@
         <v>1.886668859096591</v>
       </c>
       <c r="D461" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E461">
         <v>2.126294507806616</v>
@@ -24542,7 +24548,7 @@
         <v>2.29919426636051</v>
       </c>
       <c r="D462" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E462">
         <v>2.038997585538931</v>
@@ -24592,7 +24598,7 @@
         <v>1.898642244602138</v>
       </c>
       <c r="D463" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E463">
         <v>2.102411345144836</v>
@@ -24642,7 +24648,7 @@
         <v>1.887695818378956</v>
       </c>
       <c r="D464" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E464">
         <v>2.127509844235451</v>
@@ -24742,7 +24748,7 @@
         <v>1.900137108409605</v>
       </c>
       <c r="D466" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E466">
         <v>2.104769097816775</v>
@@ -24792,7 +24798,7 @@
         <v>1.882492570308907</v>
       </c>
       <c r="D467" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E467">
         <v>2.121352154211724</v>
@@ -24892,7 +24898,7 @@
         <v>1.911660475077831</v>
       </c>
       <c r="D469" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E469">
         <v>2.092823179170745</v>
@@ -24942,7 +24948,7 @@
         <v>1.879971436092785</v>
       </c>
       <c r="D470" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E470">
         <v>2.118368563423415</v>
@@ -25042,7 +25048,7 @@
         <v>1.90788623273062</v>
       </c>
       <c r="D472" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E472">
         <v>2.087035013041425</v>
@@ -25142,7 +25148,7 @@
         <v>1.89858988459332</v>
       </c>
       <c r="D474" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E474">
         <v>2.07277816293363</v>
@@ -25192,7 +25198,7 @@
         <v>2.27342525786704</v>
       </c>
       <c r="D475" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E475">
         <v>2.050890844436287</v>
@@ -25242,7 +25248,7 @@
         <v>1.889192027490578</v>
       </c>
       <c r="D476" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E476">
         <v>2.058365638997408</v>
@@ -25292,7 +25298,7 @@
         <v>2.266210657543448</v>
       </c>
       <c r="D477" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E477">
         <v>2.042055342718407</v>
@@ -25342,7 +25348,7 @@
         <v>1.881151085279702</v>
       </c>
       <c r="D478" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E478">
         <v>2.046034075448713</v>
@@ -25392,7 +25398,7 @@
         <v>2.259792939301354</v>
       </c>
       <c r="D479" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E479">
         <v>2.034195758263333</v>
@@ -25442,7 +25448,7 @@
         <v>1.873998297987854</v>
       </c>
       <c r="D480" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E480">
         <v>2.061056685064424</v>
@@ -25492,7 +25498,7 @@
         <v>2.247400638043782</v>
       </c>
       <c r="D481" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E481">
         <v>2.019019283595469</v>
@@ -25542,7 +25548,7 @@
         <v>1.860186614207387</v>
       </c>
       <c r="D482" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E482">
         <v>2.039929722127505</v>
@@ -25592,7 +25598,7 @@
         <v>2.218696305669633</v>
       </c>
       <c r="D483" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E483">
         <v>1.983865960247392</v>
@@ -25642,7 +25648,7 @@
         <v>1.828194560944569</v>
       </c>
       <c r="D484" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E484">
         <v>1.990993261207699</v>
@@ -25692,7 +25698,7 @@
         <v>1.830127541068264</v>
       </c>
       <c r="D485" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E485">
         <v>2.018032125375022</v>
@@ -25778,7 +25784,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25792,7 +25798,7 @@
         <v>1.78228507381279</v>
       </c>
       <c r="D487" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E487">
         <v>2.022800472072064</v>
@@ -25828,7 +25834,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25842,7 +25848,7 @@
         <v>1.783722556644772</v>
       </c>
       <c r="D488" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E488">
         <v>1.972929321636883</v>
@@ -25878,7 +25884,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25892,7 +25898,7 @@
         <v>2.163345062458509</v>
       </c>
       <c r="D489" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E489">
         <v>1.877414831999107</v>
@@ -25942,7 +25948,7 @@
         <v>1.693507313006611</v>
       </c>
       <c r="D490" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E490">
         <v>1.978388335287718</v>
@@ -25992,7 +25998,7 @@
         <v>1.734543015346852</v>
       </c>
       <c r="D491" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E491">
         <v>1.925129818487629</v>
@@ -26042,7 +26048,7 @@
         <v>1.684218514250647</v>
       </c>
       <c r="D492" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E492">
         <v>1.570048693213578</v>
@@ -26092,7 +26098,7 @@
         <v>2.132031608016207</v>
       </c>
       <c r="D493" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E493">
         <v>1.840169754028087</v>
@@ -26142,7 +26148,7 @@
         <v>1.660262632299145</v>
       </c>
       <c r="D494" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E494">
         <v>1.929555899725715</v>
@@ -26192,7 +26198,7 @@
         <v>1.680468679922261</v>
       </c>
       <c r="D495" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E495">
         <v>1.872572875128523</v>
@@ -26242,7 +26248,7 @@
         <v>1.634006631356384</v>
       </c>
       <c r="D496" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E496">
         <v>1.60382087481427</v>
@@ -26292,7 +26298,7 @@
         <v>2.09863804467423</v>
       </c>
       <c r="D497" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E497">
         <v>1.800450537718246</v>
@@ -26342,7 +26348,7 @@
         <v>1.624809554037398</v>
       </c>
       <c r="D498" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E498">
         <v>1.877479593897257</v>
@@ -26392,7 +26398,7 @@
         <v>1.622802262168714</v>
       </c>
       <c r="D499" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E499">
         <v>1.752483946759322</v>
@@ -26442,7 +26448,7 @@
         <v>1.580459243442377</v>
       </c>
       <c r="D500" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E500">
         <v>1.752483946759322</v>
@@ -26492,7 +26498,7 @@
         <v>2.071221135479056</v>
       </c>
       <c r="D501" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E501">
         <v>1.767840117089625</v>
@@ -26542,7 +26548,7 @@
         <v>1.595701734142962</v>
       </c>
       <c r="D502" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E502">
         <v>1.834723709073065</v>
@@ -26692,7 +26698,7 @@
         <v>2.041322179557651</v>
       </c>
       <c r="D505" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E505">
         <v>1.73227748229324</v>
@@ -26742,7 +26748,7 @@
         <v>1.563958789750633</v>
       </c>
       <c r="D506" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E506">
         <v>1.788097143451137</v>
@@ -26792,7 +26798,7 @@
         <v>1.472686344256899</v>
       </c>
       <c r="D507" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E507">
         <v>1.788097143451137</v>
@@ -26842,7 +26848,7 @@
         <v>1.523825085403519</v>
       </c>
       <c r="D508" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E508">
         <v>1.630370751283219</v>
@@ -26892,7 +26898,7 @@
         <v>1.56168905637971</v>
       </c>
       <c r="D509" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E509">
         <v>1.630370751283219</v>
@@ -26942,7 +26948,7 @@
         <v>1.565051671294496</v>
       </c>
       <c r="D510" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E510">
         <v>1.630370751283219</v>
@@ -26992,7 +26998,7 @@
         <v>1.866585623391427</v>
       </c>
       <c r="D511" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E511">
         <v>1.689366599623595</v>
@@ -27042,7 +27048,7 @@
         <v>2.005245252276134</v>
       </c>
       <c r="D512" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E512">
         <v>1.689366599623595</v>
@@ -27092,7 +27098,7 @@
         <v>1.4318415411232</v>
       </c>
       <c r="D513" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E513">
         <v>1.73183620839538</v>
@@ -27142,7 +27148,7 @@
         <v>1.461524840934997</v>
       </c>
       <c r="D514" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E514">
         <v>1.564205583165584</v>
@@ -27192,7 +27198,7 @@
         <v>1.496369157204806</v>
       </c>
       <c r="D515" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E515">
         <v>1.564205583165584</v>
@@ -27242,7 +27248,7 @@
         <v>1.508949665433811</v>
       </c>
       <c r="D516" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E516">
         <v>1.564205583165584</v>
@@ -27292,7 +27298,7 @@
         <v>1.973924573324424</v>
       </c>
       <c r="D517" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E517">
         <v>1.612872963807592</v>
@@ -27342,7 +27348,7 @@
         <v>1.396381565393731</v>
       </c>
       <c r="D518" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E518">
         <v>1.682992506417824</v>
@@ -27392,7 +27398,7 @@
         <v>1.467141600577559</v>
       </c>
       <c r="D519" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E519">
         <v>1.682992506417824</v>
@@ -27442,7 +27448,7 @@
         <v>1.407438029705613</v>
       </c>
       <c r="D520" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E520">
         <v>1.521706666475579</v>
@@ -27492,7 +27498,7 @@
         <v>1.439660791349507</v>
       </c>
       <c r="D521" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E521">
         <v>1.521706666475579</v>
@@ -27542,7 +27548,7 @@
         <v>1.460243940015513</v>
       </c>
       <c r="D522" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E522">
         <v>1.521706666475579</v>
@@ -27592,7 +27598,7 @@
         <v>1.940579116805523</v>
       </c>
       <c r="D523" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E523">
         <v>1.574239241056619</v>
@@ -27642,7 +27648,7 @@
         <v>1.781069303182167</v>
       </c>
       <c r="D524" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E524">
         <v>1.574239241056619</v>
@@ -27692,7 +27698,7 @@
         <v>1.358629220348103</v>
       </c>
       <c r="D525" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E525">
         <v>1.630991221802445</v>
@@ -27742,7 +27748,7 @@
         <v>1.349854686289714</v>
       </c>
       <c r="D526" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E526">
         <v>1.479202912629048</v>
@@ -27792,7 +27798,7 @@
         <v>1.379286418533347</v>
       </c>
       <c r="D527" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E527">
         <v>1.479202912629048</v>
@@ -27842,7 +27848,7 @@
         <v>1.408389551684359</v>
       </c>
       <c r="D528" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E528">
         <v>1.479202912629048</v>
@@ -27892,7 +27898,7 @@
         <v>1.74645545085387</v>
       </c>
       <c r="D529" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E529">
         <v>1.54184264617284</v>
@@ -27942,7 +27948,7 @@
         <v>1.326971711279163</v>
       </c>
       <c r="D530" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E530">
         <v>1.58738515872694</v>
@@ -28142,7 +28148,7 @@
         <v>1.276676327166428</v>
       </c>
       <c r="D534" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E534">
         <v>1.518106691894613</v>
@@ -28192,7 +28198,7 @@
         <v>1.224852607973696</v>
       </c>
       <c r="D535" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E535">
         <v>1.33929930838555</v>
@@ -28242,7 +28248,7 @@
         <v>1.248225566013237</v>
       </c>
       <c r="D536" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E536">
         <v>1.33929930838555</v>
@@ -28292,7 +28298,7 @@
         <v>1.263762437199394</v>
       </c>
       <c r="D537" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E537">
         <v>1.33929930838555</v>
@@ -28342,7 +28348,7 @@
         <v>1.212947744952629</v>
       </c>
       <c r="D538" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E538">
         <v>1.430324909390002</v>
@@ -28392,7 +28398,7 @@
         <v>1.146309428698562</v>
       </c>
       <c r="D539" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E539">
         <v>1.238758183620087</v>
@@ -28442,7 +28448,7 @@
         <v>1.216483509339664</v>
       </c>
       <c r="D540" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E540">
         <v>1.238758183620087</v>
@@ -28492,7 +28498,7 @@
         <v>1.171021231954409</v>
       </c>
       <c r="D541" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E541">
         <v>1.238758183620087</v>
@@ -28692,7 +28698,7 @@
         <v>0.913889681656368</v>
       </c>
       <c r="D545" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E545">
         <v>0.9422215166785484</v>
@@ -28742,7 +28748,7 @@
         <v>0.9595249171276929</v>
       </c>
       <c r="D546" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E546">
         <v>0.9422215166785484</v>
@@ -28792,7 +28798,7 @@
         <v>0.9589976550364385</v>
       </c>
       <c r="D547" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E547">
         <v>0.9422215166785484</v>
@@ -28842,7 +28848,7 @@
         <v>0.8504189521355614</v>
       </c>
       <c r="D548" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E548">
         <v>0.937857691146331</v>
@@ -28892,7 +28898,7 @@
         <v>0.9017680975637474</v>
       </c>
       <c r="D549" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E549">
         <v>0.937857691146331</v>
@@ -28942,7 +28948,7 @@
         <v>0.908653475416529</v>
       </c>
       <c r="D550" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E550">
         <v>0.937857691146331</v>
@@ -29142,7 +29148,7 @@
         <v>0.7994059700977925</v>
       </c>
       <c r="D554" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E554">
         <v>0.9510460107817367</v>
@@ -29192,7 +29198,7 @@
         <v>0.8553475251011551</v>
       </c>
       <c r="D555" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E555">
         <v>0.9510460107817367</v>
@@ -29242,7 +29248,7 @@
         <v>0.8681906234838945</v>
       </c>
       <c r="D556" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E556">
         <v>0.9510460107817367</v>
@@ -29342,7 +29348,7 @@
         <v>0.7963844516425689</v>
       </c>
       <c r="D558" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E558">
         <v>0.9293442447455118</v>
@@ -29392,7 +29398,7 @@
         <v>0.9077462565202601</v>
       </c>
       <c r="D559" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E559">
         <v>0.9293442447455118</v>
@@ -29442,7 +29448,7 @@
         <v>0.8525980168231655</v>
       </c>
       <c r="D560" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E560">
         <v>0.9293442447455118</v>
@@ -29492,7 +29498,7 @@
         <v>0.8657939932736682</v>
       </c>
       <c r="D561" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E561">
         <v>0.9293442447455118</v>
@@ -30592,7 +30598,7 @@
         <v>0.751468861471289</v>
       </c>
       <c r="D583" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E583">
         <v>0.9385035221553486</v>
@@ -30642,7 +30648,7 @@
         <v>0.7709845877750583</v>
       </c>
       <c r="D584" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E584">
         <v>0.9385035221553486</v>
@@ -30692,7 +30698,7 @@
         <v>0.8117259226040443</v>
       </c>
       <c r="D585" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E585">
         <v>0.9385035221553486</v>
@@ -30742,7 +30748,7 @@
         <v>0.830167515424916</v>
       </c>
       <c r="D586" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E586">
         <v>0.9385035221553486</v>
@@ -30792,7 +30798,7 @@
         <v>0.8384277846341899</v>
       </c>
       <c r="D587" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E587">
         <v>0.9385035221553486</v>
@@ -31192,7 +31198,7 @@
         <v>0.8616555364163685</v>
       </c>
       <c r="D595" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E595">
         <v>0.9487042537756789</v>
@@ -31242,7 +31248,7 @@
         <v>0.8685708400378545</v>
       </c>
       <c r="D596" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E596">
         <v>0.9487042537756789</v>
@@ -31292,7 +31298,7 @@
         <v>0.9283666743289771</v>
       </c>
       <c r="D597" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E597">
         <v>0.9487042537756789</v>
@@ -31342,7 +31348,7 @@
         <v>0.9119931158630705</v>
       </c>
       <c r="D598" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E598">
         <v>0.9487042537756789</v>
@@ -31392,7 +31398,7 @@
         <v>0.917566191902035</v>
       </c>
       <c r="D599" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E599">
         <v>0.9487042537756789</v>
@@ -31442,7 +31448,7 @@
         <v>0.8850151504748149</v>
       </c>
       <c r="D600" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E600">
         <v>0.9487042537756789</v>
@@ -31492,7 +31498,7 @@
         <v>0.9303840608049012</v>
       </c>
       <c r="D601" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E601">
         <v>0.9487042537756789</v>
@@ -31542,7 +31548,7 @@
         <v>0.9319931158630701</v>
       </c>
       <c r="D602" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E602">
         <v>0.9487042537756789</v>
@@ -31628,7 +31634,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31678,7 +31684,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31728,7 +31734,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -31778,7 +31784,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31828,7 +31834,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31878,7 +31884,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31928,7 +31934,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31978,7 +31984,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32028,7 +32034,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32078,7 +32084,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32128,7 +32134,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32178,7 +32184,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32228,7 +32234,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32278,7 +32284,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32328,7 +32334,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -33392,7 +33398,7 @@
         <v>0.9426739735459577</v>
       </c>
       <c r="D639" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E639">
         <v>1.155481591635229</v>
@@ -33442,7 +33448,7 @@
         <v>0.9523699059372155</v>
       </c>
       <c r="D640" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E640">
         <v>0.9617333668754942</v>
@@ -33492,7 +33498,7 @@
         <v>0.9489115468641032</v>
       </c>
       <c r="D641" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E641">
         <v>0.9617333668754942</v>
@@ -33542,7 +33548,7 @@
         <v>0.994540984964766</v>
       </c>
       <c r="D642" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E642">
         <v>0.9617333668754942</v>
@@ -33592,7 +33598,7 @@
         <v>0.9895196820815877</v>
       </c>
       <c r="D643" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E643">
         <v>0.9617333668754942</v>
@@ -33642,7 +33648,7 @@
         <v>0.9598379516124478</v>
       </c>
       <c r="D644" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E644">
         <v>0.9617333668754942</v>
@@ -33692,7 +33698,7 @@
         <v>1.006089726852713</v>
       </c>
       <c r="D645" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E645">
         <v>0.9617333668754942</v>
@@ -33742,7 +33748,7 @@
         <v>0.9848592544956265</v>
       </c>
       <c r="D646" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E646">
         <v>0.9617333668754942</v>
@@ -34042,7 +34048,7 @@
         <v>0.9734565125913943</v>
       </c>
       <c r="D652" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E652">
         <v>1.185400334942146</v>
@@ -34092,7 +34098,7 @@
         <v>0.9846444558037319</v>
       </c>
       <c r="D653" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E653">
         <v>1.181231801994401</v>
@@ -34142,7 +34148,7 @@
         <v>0.9774953331205798</v>
       </c>
       <c r="D654" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E654">
         <v>1.181231801994401</v>
@@ -34192,7 +34198,7 @@
         <v>1.023910040074443</v>
       </c>
       <c r="D655" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E655">
         <v>1.181231801994401</v>
@@ -34242,7 +34248,7 @@
         <v>1.015119446695905</v>
       </c>
       <c r="D656" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E656">
         <v>1.181231801994401</v>
@@ -34292,7 +34298,7 @@
         <v>0.9864585657359251</v>
       </c>
       <c r="D657" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E657">
         <v>1.181231801994401</v>
@@ -34342,7 +34348,7 @@
         <v>1.007646508948263</v>
       </c>
       <c r="D658" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E658">
         <v>1.181231801994401</v>
@@ -34392,7 +34398,7 @@
         <v>1.015249159114463</v>
       </c>
       <c r="D659" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E659">
         <v>0.9834565125913941</v>
@@ -34692,7 +34698,7 @@
         <v>0.9989502799212269</v>
       </c>
       <c r="D665" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E665">
         <v>1.210178715943846</v>
@@ -34742,7 +34748,7 @@
         <v>1.011373890427612</v>
       </c>
       <c r="D666" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E666">
         <v>1.203864024011701</v>
@@ -34792,7 +34798,7 @@
         <v>1.00116811706971</v>
       </c>
       <c r="D667" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E667">
         <v>1.203864024011701</v>
@@ -34842,7 +34848,7 @@
         <v>1.048233175230966</v>
       </c>
       <c r="D668" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E668">
         <v>1.203864024011701</v>
@@ -34892,7 +34898,7 @@
         <v>1.036320896056939</v>
       </c>
       <c r="D669" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E669">
         <v>1.203864024011701</v>
@@ -34942,7 +34948,7 @@
         <v>1.008505471666571</v>
       </c>
       <c r="D670" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E670">
         <v>1.203864024011701</v>
@@ -34992,7 +34998,7 @@
         <v>1.030929082172957</v>
       </c>
       <c r="D671" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E671">
         <v>1.203864024011701</v>
@@ -35042,7 +35048,7 @@
         <v>1.040417750840599</v>
       </c>
       <c r="D672" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E672">
         <v>0.9957763031857296</v>
@@ -35128,7 +35134,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35178,7 +35184,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35228,7 +35234,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35278,7 +35284,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35292,7 +35298,7 @@
         <v>1.019721542843001</v>
       </c>
       <c r="D677" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E677">
         <v>1.230367111793835</v>
@@ -35328,7 +35334,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35342,7 +35348,7 @@
         <v>1.033151923746106</v>
       </c>
       <c r="D678" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E678">
         <v>1.222303818646338</v>
@@ -35378,7 +35384,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35392,7 +35398,7 @@
         <v>1.020455718354215</v>
       </c>
       <c r="D679" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E679">
         <v>1.222303818646338</v>
@@ -35428,7 +35434,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35442,7 +35448,7 @@
         <v>1.053594956548007</v>
       </c>
       <c r="D680" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E680">
         <v>1.222303818646338</v>
@@ -35478,7 +35484,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35492,7 +35498,7 @@
         <v>1.026468375060656</v>
       </c>
       <c r="D681" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E681">
         <v>1.222303818646338</v>
@@ -35528,7 +35534,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35542,7 +35548,7 @@
         <v>1.049898755963761</v>
       </c>
       <c r="D682" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E682">
         <v>1.222303818646338</v>
@@ -35578,7 +35584,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35592,7 +35598,7 @@
         <v>1.060924074184289</v>
       </c>
       <c r="D683" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E683">
         <v>1.017873442550878</v>
@@ -35628,7 +35634,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35842,7 +35848,7 @@
         <v>1.047332978384417</v>
       </c>
       <c r="D688" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E688">
         <v>1.257203736644038</v>
@@ -35892,7 +35898,7 @@
         <v>1.062101668663253</v>
       </c>
       <c r="D689" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E689">
         <v>1.2468160114229</v>
@@ -35942,7 +35948,7 @@
         <v>1.046094908499815</v>
       </c>
       <c r="D690" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E690">
         <v>1.2468160114229</v>
@@ -35992,7 +35998,7 @@
         <v>1.076557527942143</v>
       </c>
       <c r="D691" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E691">
         <v>1.2468160114229</v>
@@ -36042,7 +36048,7 @@
         <v>1.050346631817136</v>
       </c>
       <c r="D692" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E692">
         <v>1.2468160114229</v>
@@ -36092,7 +36098,7 @@
         <v>1.075115322095972</v>
       </c>
       <c r="D693" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E693">
         <v>1.2468160114229</v>
@@ -36142,7 +36148,7 @@
         <v>1.043673116249803</v>
       </c>
       <c r="D694" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E694">
         <v>1.123802357990182</v>
@@ -36192,7 +36198,7 @@
         <v>3.139280458423625</v>
       </c>
       <c r="D695" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E695">
         <v>3.025106410332782</v>
@@ -36228,7 +36234,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36242,7 +36248,7 @@
         <v>3.093454506514468</v>
       </c>
       <c r="D696" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E696">
         <v>3.025106410332782</v>
@@ -36278,7 +36284,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36292,7 +36298,7 @@
         <v>3.013365929424353</v>
       </c>
       <c r="D697" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E697">
         <v>3.025106410332782</v>
@@ -36328,7 +36334,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36342,7 +36348,7 @@
         <v>3.208498795059524</v>
       </c>
       <c r="D698" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E698">
         <v>3.025106410332782</v>
@@ -36378,7 +36384,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36392,10 +36398,10 @@
         <v>-0.8715193570106505</v>
       </c>
       <c r="D699" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E699">
-        <v>-0.54680735347549</v>
+        <v>-0.4468731812388809</v>
       </c>
       <c r="F699">
         <v>1</v>
@@ -36404,10 +36410,10 @@
         <v>0.01181151935701065</v>
       </c>
       <c r="H699">
-        <v>0.01108680735347549</v>
+        <v>0.01094687318123888</v>
       </c>
       <c r="I699">
-        <v>0.3247120035351605</v>
+        <v>0.4246461757717697</v>
       </c>
       <c r="J699">
         <v>1.4991771529576</v>
@@ -36419,10 +36425,10 @@
         <v>5.47</v>
       </c>
       <c r="M699">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="N699">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="O699">
         <v>1</v>
@@ -36442,10 +36448,10 @@
         <v>-0.1116839264191301</v>
       </c>
       <c r="D700" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E700">
-        <v>0.008332530521719228</v>
+        <v>0.02828315969917394</v>
       </c>
       <c r="F700">
         <v>-1</v>
@@ -36454,10 +36460,10 @@
         <v>0.01197168392641913</v>
       </c>
       <c r="H700">
-        <v>0.01215166746947828</v>
+        <v>0.01199171684030082</v>
       </c>
       <c r="I700">
-        <v>-0.1200164569408493</v>
+        <v>-0.139967086118304</v>
       </c>
       <c r="J700">
         <v>1.4991771529576</v>
@@ -36469,10 +36475,10 @@
         <v>5.93</v>
       </c>
       <c r="M700">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N700">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O700">
         <v>1</v>
@@ -36486,43 +36492,43 @@
         <v>0</v>
       </c>
       <c r="B701" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C701">
-        <v>-0.8991702808190363</v>
+        <v>-0.8653702238384202</v>
       </c>
       <c r="D701" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E701">
-        <v>-0.5721703757867278</v>
+        <v>-0.4717132546364855</v>
       </c>
       <c r="F701">
         <v>1</v>
       </c>
       <c r="G701">
-        <v>0.01183917028081904</v>
+        <v>0.01250537022383842</v>
       </c>
       <c r="H701">
-        <v>0.01111217037578673</v>
+        <v>0.01097171325463649</v>
       </c>
       <c r="I701">
-        <v>0.3269999050323085</v>
+        <v>0.3936569692019347</v>
       </c>
       <c r="J701">
         <v>1.505714014378023</v>
       </c>
       <c r="K701">
-        <v>4.23</v>
+        <v>4.44</v>
       </c>
       <c r="L701">
-        <v>5.47</v>
+        <v>5.82</v>
       </c>
       <c r="M701">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="N701">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="O701">
         <v>1</v>
@@ -36536,43 +36542,43 @@
         <v>1</v>
       </c>
       <c r="B702" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C702">
-        <v>-0.8680274779434312</v>
+        <v>-0.8991702808190363</v>
       </c>
       <c r="D702" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E702">
-        <v>-0.5721703757867278</v>
+        <v>-0.4717132546364855</v>
       </c>
       <c r="F702">
         <v>1</v>
       </c>
       <c r="G702">
-        <v>0.01126802747794343</v>
+        <v>0.01183917028081904</v>
       </c>
       <c r="H702">
-        <v>0.01111217037578673</v>
+        <v>0.01097171325463649</v>
       </c>
       <c r="I702">
-        <v>0.2958571021567034</v>
+        <v>0.4274570261825508</v>
       </c>
       <c r="J702">
         <v>1.505714014378023</v>
       </c>
       <c r="K702">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="L702">
-        <v>5.2</v>
+        <v>5.47</v>
       </c>
       <c r="M702">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="N702">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="O702">
         <v>1</v>
@@ -36586,28 +36592,28 @@
         <v>2</v>
       </c>
       <c r="B703" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C703">
-        <v>-0.1380274779434316</v>
+        <v>-0.8680274779434312</v>
       </c>
       <c r="D703" t="s">
         <v>257</v>
       </c>
       <c r="E703">
-        <v>-0.01814175823099085</v>
+        <v>-0.4717132546364855</v>
       </c>
       <c r="F703">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G703">
-        <v>0.01199802747794343</v>
+        <v>0.01126802747794343</v>
       </c>
       <c r="H703">
-        <v>0.01217814175823099</v>
+        <v>0.01097171325463649</v>
       </c>
       <c r="I703">
-        <v>-0.1198857197124408</v>
+        <v>0.3963142233069457</v>
       </c>
       <c r="J703">
         <v>1.505714014378023</v>
@@ -36616,13 +36622,13 @@
         <v>4.03</v>
       </c>
       <c r="L703">
-        <v>5.93</v>
+        <v>5.2</v>
       </c>
       <c r="M703">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="N703">
-        <v>6.08</v>
+        <v>5.25</v>
       </c>
       <c r="O703">
         <v>1</v>
@@ -36633,66 +36639,66 @@
     </row>
     <row r="704" spans="1:16">
       <c r="A704" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B704" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C704">
-        <v>-0.9016808854046587</v>
+        <v>-0.1380274779434316</v>
       </c>
       <c r="D704" t="s">
         <v>258</v>
       </c>
       <c r="E704">
-        <v>-0.5027899469679502</v>
+        <v>0.002201082631689388</v>
       </c>
       <c r="F704">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G704">
-        <v>0.01254168088540466</v>
+        <v>0.01199802747794343</v>
       </c>
       <c r="H704">
-        <v>0.01100278994696795</v>
+        <v>0.01201779891736831</v>
       </c>
       <c r="I704">
-        <v>0.3988909384367085</v>
+        <v>-0.140228560575121</v>
       </c>
       <c r="J704">
-        <v>1.513892091307355</v>
+        <v>1.505714014378023</v>
       </c>
       <c r="K704">
-        <v>4.44</v>
+        <v>4.03</v>
       </c>
       <c r="L704">
-        <v>5.82</v>
+        <v>5.93</v>
       </c>
       <c r="M704">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="N704">
-        <v>5.25</v>
+        <v>6.01</v>
       </c>
       <c r="O704">
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="705" spans="1:16">
       <c r="A705" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B705" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C705">
-        <v>-0.9337635462301144</v>
+        <v>-0.9016808854046587</v>
       </c>
       <c r="D705" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E705">
         <v>-0.5027899469679502</v>
@@ -36701,22 +36707,22 @@
         <v>1</v>
       </c>
       <c r="G705">
-        <v>0.01187376354623011</v>
+        <v>0.01254168088540466</v>
       </c>
       <c r="H705">
         <v>0.01100278994696795</v>
       </c>
       <c r="I705">
-        <v>0.4309735992621642</v>
+        <v>0.3988909384367085</v>
       </c>
       <c r="J705">
         <v>1.513892091307355</v>
       </c>
       <c r="K705">
-        <v>4.23</v>
+        <v>4.44</v>
       </c>
       <c r="L705">
-        <v>5.47</v>
+        <v>5.82</v>
       </c>
       <c r="M705">
         <v>3.8</v>
@@ -36733,16 +36739,16 @@
     </row>
     <row r="706" spans="1:16">
       <c r="A706" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B706" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C706">
-        <v>-0.9009851279686432</v>
+        <v>-0.9337635462301144</v>
       </c>
       <c r="D706" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E706">
         <v>-0.5027899469679502</v>
@@ -36751,22 +36757,22 @@
         <v>1</v>
       </c>
       <c r="G706">
-        <v>0.01130098512796864</v>
+        <v>0.01187376354623011</v>
       </c>
       <c r="H706">
         <v>0.01100278994696795</v>
       </c>
       <c r="I706">
-        <v>0.398195181000693</v>
+        <v>0.4309735992621642</v>
       </c>
       <c r="J706">
         <v>1.513892091307355</v>
       </c>
       <c r="K706">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="L706">
-        <v>5.2</v>
+        <v>5.47</v>
       </c>
       <c r="M706">
         <v>3.8</v>
@@ -36783,7 +36789,7 @@
     </row>
     <row r="707" spans="1:16">
       <c r="A707" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B707" t="s">
         <v>146</v>
@@ -36792,10 +36798,10 @@
         <v>-0.1709851279686436</v>
       </c>
       <c r="D707" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E707">
-        <v>-0.05126296979478973</v>
+        <v>-0.03042944431634886</v>
       </c>
       <c r="F707">
         <v>-1</v>
@@ -36804,10 +36810,10 @@
         <v>0.01203098512796864</v>
       </c>
       <c r="H707">
-        <v>0.01221126296979479</v>
+        <v>0.01205042944431635</v>
       </c>
       <c r="I707">
-        <v>-0.1197221581738539</v>
+        <v>-0.1405556836522948</v>
       </c>
       <c r="J707">
         <v>1.513892091307355</v>
@@ -36819,10 +36825,10 @@
         <v>5.93</v>
       </c>
       <c r="M707">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N707">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O707">
         <v>1</v>
@@ -36836,13 +36842,13 @@
         <v>0</v>
       </c>
       <c r="B708" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C708">
         <v>-0.9377349898599103</v>
       </c>
       <c r="D708" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E708">
         <v>-0.5336470633936168</v>
@@ -36892,7 +36898,7 @@
         <v>-0.9681123889881587</v>
       </c>
       <c r="D709" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E709">
         <v>-0.5336470633936168</v>
@@ -36942,10 +36948,10 @@
         <v>-0.2037099119674419</v>
       </c>
       <c r="D710" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E710">
-        <v>-0.08415015966951245</v>
+        <v>-0.06282941656329832</v>
       </c>
       <c r="F710">
         <v>-1</v>
@@ -36954,10 +36960,10 @@
         <v>0.01206370991196744</v>
       </c>
       <c r="H710">
-        <v>0.01224415015966951</v>
+        <v>0.0120828294165633</v>
       </c>
       <c r="I710">
-        <v>-0.1195597522979295</v>
+        <v>-0.1408804954041436</v>
       </c>
       <c r="J710">
         <v>1.522012385103583</v>
@@ -36969,10 +36975,10 @@
         <v>5.93</v>
       </c>
       <c r="M710">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N710">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O710">
         <v>1</v>
@@ -36986,13 +36992,13 @@
         <v>0</v>
       </c>
       <c r="B711" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C711">
         <v>-0.9721715677020031</v>
       </c>
       <c r="D711" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E711">
         <v>-0.5631198101954071</v>
@@ -37042,7 +37048,7 @@
         <v>-1.000920209770152</v>
       </c>
       <c r="D712" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E712">
         <v>-0.5631198101954071</v>
@@ -37092,10 +37098,10 @@
         <v>-0.2349665355493409</v>
       </c>
       <c r="D713" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E713">
-        <v>-0.1155619029714208</v>
+        <v>-0.09377580070517855</v>
       </c>
       <c r="F713">
         <v>-1</v>
@@ -37104,10 +37110,10 @@
         <v>0.01209496653554934</v>
       </c>
       <c r="H713">
-        <v>0.01227556190297142</v>
+        <v>0.01211377580070518</v>
       </c>
       <c r="I713">
-        <v>-0.1194046325779201</v>
+        <v>-0.1411907348441623</v>
       </c>
       <c r="J713">
         <v>1.529768371104055</v>
@@ -37119,10 +37125,10 @@
         <v>5.93</v>
       </c>
       <c r="M713">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N713">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O713">
         <v>1</v>
@@ -37142,7 +37148,7 @@
         <v>-1.029266735877098</v>
       </c>
       <c r="D714" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E714">
         <v>-0.5885847745468009</v>
@@ -37178,7 +37184,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37192,10 +37198,10 @@
         <v>-0.2619728003746342</v>
       </c>
       <c r="D715" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E715">
-        <v>-0.1427021939248796</v>
+        <v>-0.1205140132741418</v>
       </c>
       <c r="F715">
         <v>-1</v>
@@ -37204,10 +37210,10 @@
         <v>0.01212197280037463</v>
       </c>
       <c r="H715">
-        <v>0.01230270219392488</v>
+        <v>0.01214051401327414</v>
       </c>
       <c r="I715">
-        <v>-0.1192706064497546</v>
+        <v>-0.1414587871004924</v>
       </c>
       <c r="J715">
         <v>1.536469677512316</v>
@@ -37219,16 +37225,16 @@
         <v>5.93</v>
       </c>
       <c r="M715">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N715">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O715">
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37242,7 +37248,7 @@
         <v>-1.070041708072165</v>
       </c>
       <c r="D716" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E716">
         <v>-0.6252147732090361</v>
@@ -37292,10 +37298,10 @@
         <v>-0.300819877903268</v>
       </c>
       <c r="D717" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E717">
-        <v>-0.1817420609201568</v>
+        <v>-0.1589755118694889</v>
       </c>
       <c r="F717">
         <v>-1</v>
@@ -37304,10 +37310,10 @@
         <v>0.01216081987790327</v>
       </c>
       <c r="H717">
-        <v>0.01234174206092016</v>
+        <v>0.01217897551186949</v>
       </c>
       <c r="I717">
-        <v>-0.1190778169831113</v>
+        <v>-0.1418443660337791</v>
       </c>
       <c r="J717">
         <v>1.546109150844483</v>
@@ -37319,10 +37325,10 @@
         <v>5.93</v>
       </c>
       <c r="M717">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N717">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O717">
         <v>1</v>
@@ -37342,7 +37348,7 @@
         <v>-1.104955489525656</v>
       </c>
       <c r="D718" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E718">
         <v>-0.6565793995738742</v>
@@ -37392,10 +37398,10 @@
         <v>-0.3340828895480827</v>
       </c>
       <c r="D719" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E719">
-        <v>-0.2151701495458394</v>
+        <v>-0.1919083695525687</v>
       </c>
       <c r="F719">
         <v>-1</v>
@@ -37404,10 +37410,10 @@
         <v>0.01219408288954808</v>
       </c>
       <c r="H719">
-        <v>0.01237517014954584</v>
+        <v>0.01221190836955257</v>
       </c>
       <c r="I719">
-        <v>-0.1189127400022434</v>
+        <v>-0.142174519995514</v>
       </c>
       <c r="J719">
         <v>1.554362999887862</v>
@@ -37419,10 +37425,10 @@
         <v>5.93</v>
       </c>
       <c r="M719">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N719">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O719">
         <v>1</v>
@@ -37442,7 +37448,7 @@
         <v>-1.146046740420904</v>
       </c>
       <c r="D720" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E720">
         <v>-0.6934935256736248</v>
@@ -37492,10 +37498,10 @@
         <v>-0.3732312917012397</v>
       </c>
       <c r="D721" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E721">
-        <v>-0.2545128365732054</v>
+        <v>-0.2306682019573065</v>
       </c>
       <c r="F721">
         <v>-1</v>
@@ -37504,10 +37510,10 @@
         <v>0.01223323129170124</v>
       </c>
       <c r="H721">
-        <v>0.01241451283657321</v>
+        <v>0.01225066820195731</v>
       </c>
       <c r="I721">
-        <v>-0.1187184551280343</v>
+        <v>-0.1425630897439332</v>
       </c>
       <c r="J721">
         <v>1.564077243598322</v>
@@ -37519,10 +37525,10 @@
         <v>5.93</v>
       </c>
       <c r="M721">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N721">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O721">
         <v>1</v>
@@ -37542,7 +37548,7 @@
         <v>-1.194222080991625</v>
       </c>
       <c r="D722" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E722">
         <v>-0.7367716094014582</v>
@@ -37592,10 +37598,10 @@
         <v>-0.419128838391547</v>
       </c>
       <c r="D723" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E723">
-        <v>-0.3006381626515537</v>
+        <v>-0.2761101898715319</v>
       </c>
       <c r="F723">
         <v>-1</v>
@@ -37604,10 +37610,10 @@
         <v>0.01227912883839155</v>
       </c>
       <c r="H723">
-        <v>0.01246063816265155</v>
+        <v>0.01229611018987153</v>
       </c>
       <c r="I723">
-        <v>-0.1184906757399933</v>
+        <v>-0.1430186485200151</v>
       </c>
       <c r="J723">
         <v>1.575466213000384</v>
@@ -37619,10 +37625,10 @@
         <v>5.93</v>
       </c>
       <c r="M723">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N723">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O723">
         <v>1</v>
@@ -37642,10 +37648,10 @@
         <v>-0.4644964405131953</v>
       </c>
       <c r="D724" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E724">
-        <v>-0.3462309141633835</v>
+        <v>-0.3210274932128154</v>
       </c>
       <c r="F724">
         <v>-1</v>
@@ -37654,10 +37660,10 @@
         <v>0.01232449644051319</v>
       </c>
       <c r="H724">
-        <v>0.01250623091416338</v>
+        <v>0.01234102749321282</v>
       </c>
       <c r="I724">
-        <v>-0.1182655263498118</v>
+        <v>-0.1434689473003798</v>
       </c>
       <c r="J724">
         <v>1.586723682509477</v>
@@ -37669,10 +37675,10 @@
         <v>5.93</v>
       </c>
       <c r="M724">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N724">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O724">
         <v>1</v>
@@ -37686,43 +37692,43 @@
         <v>0</v>
       </c>
       <c r="B725" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C725">
-        <v>-1.184458835026242</v>
+        <v>-0.522492276288939</v>
       </c>
       <c r="D725" t="s">
         <v>258</v>
       </c>
       <c r="E725">
-        <v>-0.8342358932749292</v>
+        <v>-0.3784476879386771</v>
       </c>
       <c r="F725">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G725">
-        <v>0.01162445883502624</v>
+        <v>0.01238249227628894</v>
       </c>
       <c r="H725">
-        <v>0.01133423589327493</v>
+        <v>0.01239844768793868</v>
       </c>
       <c r="I725">
-        <v>0.350222941751313</v>
+        <v>-0.1440445883502619</v>
       </c>
       <c r="J725">
         <v>1.60111470875656</v>
       </c>
       <c r="K725">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="L725">
-        <v>5.22</v>
+        <v>5.93</v>
       </c>
       <c r="M725">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="N725">
-        <v>5.25</v>
+        <v>6.01</v>
       </c>
       <c r="O725">
         <v>1</v>
@@ -37733,34 +37739,34 @@
     </row>
     <row r="726" spans="1:16">
       <c r="A726" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B726" t="s">
         <v>146</v>
       </c>
       <c r="C726">
-        <v>-0.522492276288939</v>
+        <v>-0.5800395574451711</v>
       </c>
       <c r="D726" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E726">
-        <v>-0.4045145704640696</v>
+        <v>-0.4354237802000576</v>
       </c>
       <c r="F726">
         <v>-1</v>
       </c>
       <c r="G726">
-        <v>0.01238249227628894</v>
+        <v>0.01244003955744517</v>
       </c>
       <c r="H726">
-        <v>0.01256451457046407</v>
+        <v>0.01245542378020006</v>
       </c>
       <c r="I726">
-        <v>-0.1179777058248694</v>
+        <v>-0.1446157772451135</v>
       </c>
       <c r="J726">
-        <v>1.60111470875656</v>
+        <v>1.615394431127834</v>
       </c>
       <c r="K726">
         <v>4.03</v>
@@ -37769,16 +37775,16 @@
         <v>5.93</v>
       </c>
       <c r="M726">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N726">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O726">
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -37786,149 +37792,149 @@
         <v>0</v>
       </c>
       <c r="B727" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C727">
-        <v>-0.5800395574451711</v>
+        <v>-1.217497277253725</v>
       </c>
       <c r="D727" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E727">
-        <v>-0.462347446067727</v>
+        <v>-0.7898118358734978</v>
       </c>
       <c r="F727">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G727">
-        <v>0.01244003955744517</v>
+        <v>0.01191749727725372</v>
       </c>
       <c r="H727">
-        <v>0.01262234744606773</v>
+        <v>0.0113698118358735</v>
       </c>
       <c r="I727">
-        <v>-0.1176921113774441</v>
+        <v>0.4276854413802269</v>
       </c>
       <c r="J727">
-        <v>1.615394431127834</v>
+        <v>1.62561813793409</v>
       </c>
       <c r="K727">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="L727">
-        <v>5.93</v>
+        <v>5.35</v>
       </c>
       <c r="M727">
-        <v>4.05</v>
+        <v>3.74</v>
       </c>
       <c r="N727">
-        <v>6.08</v>
+        <v>5.29</v>
       </c>
       <c r="O727">
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>364</v>
+        <v>148</v>
       </c>
     </row>
     <row r="728" spans="1:16">
       <c r="A728" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B728" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C728">
-        <v>-1.217497277253725</v>
+        <v>-0.6212410958743844</v>
       </c>
       <c r="D728" t="s">
         <v>258</v>
       </c>
       <c r="E728">
-        <v>-0.9273489241495421</v>
+        <v>-0.4762163703570206</v>
       </c>
       <c r="F728">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G728">
-        <v>0.01191749727725372</v>
+        <v>0.01248124109587439</v>
       </c>
       <c r="H728">
-        <v>0.01142734892414954</v>
+        <v>0.01249621637035702</v>
       </c>
       <c r="I728">
-        <v>0.2901483531041826</v>
+        <v>-0.1450247255173638</v>
       </c>
       <c r="J728">
         <v>1.62561813793409</v>
       </c>
       <c r="K728">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="L728">
-        <v>5.35</v>
+        <v>5.93</v>
       </c>
       <c r="M728">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="N728">
-        <v>5.25</v>
+        <v>6.01</v>
       </c>
       <c r="O728">
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="729" spans="1:16">
       <c r="A729" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B729" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C729">
-        <v>-0.6212410958743844</v>
+        <v>-0.6214389000132918</v>
       </c>
       <c r="D729" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E729">
-        <v>-0.5037534586330645</v>
+        <v>-0.4762163703570206</v>
       </c>
       <c r="F729">
         <v>-1</v>
       </c>
       <c r="G729">
-        <v>0.01248124109587439</v>
+        <v>0.01352143890001329</v>
       </c>
       <c r="H729">
-        <v>0.01266375345863306</v>
+        <v>0.01249621637035702</v>
       </c>
       <c r="I729">
-        <v>-0.1174876372413198</v>
+        <v>-0.1452225296562712</v>
       </c>
       <c r="J729">
         <v>1.62561813793409</v>
       </c>
       <c r="K729">
-        <v>4.03</v>
+        <v>4.35</v>
       </c>
       <c r="L729">
-        <v>5.93</v>
+        <v>6.45</v>
       </c>
       <c r="M729">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N729">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O729">
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -37936,7 +37942,7 @@
         <v>0</v>
       </c>
       <c r="B730" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C730">
         <v>-1.265907451690905</v>
@@ -37986,43 +37992,43 @@
         <v>1</v>
       </c>
       <c r="B731" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C731">
-        <v>-0.6695314431471155</v>
+        <v>-0.6434276225666915</v>
       </c>
       <c r="D731" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E731">
-        <v>-0.5522834602346931</v>
+        <v>-0.5240274089719579</v>
       </c>
       <c r="F731">
         <v>-1</v>
       </c>
       <c r="G731">
-        <v>0.01252953144314711</v>
+        <v>0.01324342762256669</v>
       </c>
       <c r="H731">
-        <v>0.01271228346023469</v>
+        <v>0.01254402740897196</v>
       </c>
       <c r="I731">
-        <v>-0.1172479829124224</v>
+        <v>-0.1194002135947336</v>
       </c>
       <c r="J731">
         <v>1.637600854378937</v>
       </c>
       <c r="K731">
-        <v>4.03</v>
+        <v>4.24</v>
       </c>
       <c r="L731">
-        <v>5.93</v>
+        <v>6.3</v>
       </c>
       <c r="M731">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N731">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O731">
         <v>1</v>
@@ -38036,7 +38042,7 @@
         <v>0</v>
       </c>
       <c r="B732" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C732">
         <v>-1.320637609966599</v>
@@ -38078,7 +38084,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>149</v>
+        <v>366</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38089,46 +38095,46 @@
         <v>151</v>
       </c>
       <c r="C733">
-        <v>-0.7324934661769058</v>
+        <v>-0.70086719461841</v>
       </c>
       <c r="D733" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E733">
-        <v>-0.6071490891991882</v>
+        <v>-0.5780802138036458</v>
       </c>
       <c r="F733">
         <v>-1</v>
       </c>
       <c r="G733">
-        <v>0.01363249346617691</v>
+        <v>0.01330086719461841</v>
       </c>
       <c r="H733">
-        <v>0.01276714908919919</v>
+        <v>0.01259808021380364</v>
       </c>
       <c r="I733">
-        <v>-0.1253443769777176</v>
+        <v>-0.1227869808147641</v>
       </c>
       <c r="J733">
         <v>1.651147923259059</v>
       </c>
       <c r="K733">
-        <v>4.35</v>
+        <v>4.24</v>
       </c>
       <c r="L733">
-        <v>6.45</v>
+        <v>6.3</v>
       </c>
       <c r="M733">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N733">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O733">
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>149</v>
+        <v>366</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38136,7 +38142,7 @@
         <v>0</v>
       </c>
       <c r="B734" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C734">
         <v>-1.380277958041175</v>
@@ -38178,7 +38184,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38189,46 +38195,46 @@
         <v>152</v>
       </c>
       <c r="C735">
-        <v>-0.7634600351719261</v>
+        <v>-0.7067782428850009</v>
       </c>
       <c r="D735" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E735">
-        <v>-0.6669370618977117</v>
+        <v>-0.636982438758487</v>
       </c>
       <c r="F735">
         <v>-1</v>
       </c>
       <c r="G735">
-        <v>0.01336346003517193</v>
+        <v>0.013486778242885</v>
       </c>
       <c r="H735">
-        <v>0.01282693706189771</v>
+        <v>0.01265698243875849</v>
       </c>
       <c r="I735">
-        <v>-0.09652297327421433</v>
+        <v>-0.06979580412651387</v>
       </c>
       <c r="J735">
         <v>1.665910385653756</v>
       </c>
       <c r="K735">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="L735">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="M735">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N735">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O735">
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38239,46 +38245,46 @@
         <v>152</v>
       </c>
       <c r="C736">
-        <v>-0.8126620206266786</v>
+        <v>-0.7562123131768042</v>
       </c>
       <c r="D736" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E736">
-        <v>-0.7139342414004819</v>
+        <v>-0.6832833637501059</v>
       </c>
       <c r="F736">
         <v>-1</v>
       </c>
       <c r="G736">
-        <v>0.01341266202062668</v>
+        <v>0.0135362123131768</v>
       </c>
       <c r="H736">
-        <v>0.01287393424140048</v>
+        <v>0.01270328336375011</v>
       </c>
       <c r="I736">
-        <v>-0.09872777922619669</v>
+        <v>-0.07292894942669825</v>
       </c>
       <c r="J736">
         <v>1.677514627506292</v>
       </c>
       <c r="K736">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="L736">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="M736">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N736">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O736">
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38286,16 +38292,16 @@
         <v>0</v>
       </c>
       <c r="B737" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C737">
         <v>-0.7998453473923126</v>
       </c>
       <c r="D737" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E737">
-        <v>-0.755416351394099</v>
+        <v>-0.7241509239660395</v>
       </c>
       <c r="F737">
         <v>-1</v>
@@ -38304,10 +38310,10 @@
         <v>0.01357984534739231</v>
       </c>
       <c r="H737">
-        <v>0.0129154163513941</v>
+        <v>0.01274415092396604</v>
       </c>
       <c r="I737">
-        <v>-0.04442899599821359</v>
+        <v>-0.07569442342627308</v>
       </c>
       <c r="J737">
         <v>1.687757123801012</v>
@@ -38319,16 +38325,16 @@
         <v>6.39</v>
       </c>
       <c r="M737">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N737">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O737">
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38336,16 +38342,16 @@
         <v>0</v>
       </c>
       <c r="B738" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C738">
         <v>-0.8506323564564404</v>
       </c>
       <c r="D738" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E738">
-        <v>-0.803699775504362</v>
+        <v>-0.7717190380894836</v>
       </c>
       <c r="F738">
         <v>-1</v>
@@ -38354,10 +38360,10 @@
         <v>0.01363063235645644</v>
       </c>
       <c r="H738">
-        <v>0.01296369977550436</v>
+        <v>0.01279171903808948</v>
       </c>
       <c r="I738">
-        <v>-0.04693258095207842</v>
+        <v>-0.07891331836695681</v>
       </c>
       <c r="J738">
         <v>1.699678956914657</v>
@@ -38369,16 +38375,16 @@
         <v>6.39</v>
       </c>
       <c r="M738">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N738">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O738">
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38386,16 +38392,16 @@
         <v>0</v>
       </c>
       <c r="B739" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C739">
         <v>-1.314126956385915</v>
       </c>
       <c r="D739" t="s">
-        <v>259</v>
+        <v>146</v>
       </c>
       <c r="E739">
-        <v>-1.071053476993034</v>
+        <v>-0.9242902439256504</v>
       </c>
       <c r="F739">
         <v>1</v>
@@ -38404,10 +38410,10 @@
         <v>0.01171412695638591</v>
       </c>
       <c r="H739">
-        <v>0.01165105347699304</v>
+        <v>0.01278429024392565</v>
       </c>
       <c r="I739">
-        <v>0.2430734793928808</v>
+        <v>0.3898367124602649</v>
       </c>
       <c r="J739">
         <v>1.700816437698672</v>
@@ -38419,16 +38425,16 @@
         <v>5.2</v>
       </c>
       <c r="M739">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="N739">
-        <v>5.29</v>
+        <v>5.93</v>
       </c>
       <c r="O739">
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38436,49 +38442,49 @@
         <v>1</v>
       </c>
       <c r="B740" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C740">
-        <v>-0.8554780245963443</v>
+        <v>-0.8083065726796228</v>
       </c>
       <c r="D740" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E740">
-        <v>-0.8083065726796228</v>
+        <v>-0.776257586417703</v>
       </c>
       <c r="F740">
         <v>-1</v>
       </c>
       <c r="G740">
-        <v>0.01363547802459634</v>
+        <v>0.01296830657267962</v>
       </c>
       <c r="H740">
-        <v>0.01296830657267962</v>
+        <v>0.0127962575864177</v>
       </c>
       <c r="I740">
-        <v>-0.04717145191672145</v>
+        <v>-0.03204898626191977</v>
       </c>
       <c r="J740">
         <v>1.700816437698672</v>
       </c>
       <c r="K740">
-        <v>4.26</v>
+        <v>4.05</v>
       </c>
       <c r="L740">
-        <v>6.39</v>
+        <v>6.08</v>
       </c>
       <c r="M740">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N740">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O740">
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38486,7 +38492,7 @@
         <v>0</v>
       </c>
       <c r="B741" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C741">
         <v>-1.319380887843892</v>
@@ -38528,7 +38534,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>256</v>
+        <v>371</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38536,49 +38542,49 @@
         <v>1</v>
       </c>
       <c r="B742" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C742">
-        <v>-0.8613218230326325</v>
+        <v>-0.8138622965451079</v>
       </c>
       <c r="D742" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E742">
-        <v>-0.8138622965451079</v>
+        <v>-0.7817310032629594</v>
       </c>
       <c r="F742">
         <v>-1</v>
       </c>
       <c r="G742">
-        <v>0.01364132182303263</v>
+        <v>0.01297386229654511</v>
       </c>
       <c r="H742">
-        <v>0.01297386229654511</v>
+        <v>0.01280173100326296</v>
       </c>
       <c r="I742">
-        <v>-0.04745952648752461</v>
+        <v>-0.03213129328214848</v>
       </c>
       <c r="J742">
         <v>1.702188221369163</v>
       </c>
       <c r="K742">
-        <v>4.26</v>
+        <v>4.05</v>
       </c>
       <c r="L742">
-        <v>6.39</v>
+        <v>6.08</v>
       </c>
       <c r="M742">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="N742">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="O742">
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>256</v>
+        <v>371</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38586,49 +38592,99 @@
         <v>0</v>
       </c>
       <c r="B743" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C743">
-        <v>-0.8381042623769472</v>
+        <v>-1.176376407370608</v>
       </c>
       <c r="D743" t="s">
-        <v>257</v>
+        <v>146</v>
       </c>
       <c r="E743">
-        <v>-0.7917892635273791</v>
+        <v>-0.9078545017321833</v>
       </c>
       <c r="F743">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G743">
-        <v>0.01361810426237695</v>
+        <v>0.01195637640737061</v>
       </c>
       <c r="H743">
-        <v>0.01295178926352738</v>
+        <v>0.01276785450173218</v>
       </c>
       <c r="I743">
-        <v>-0.04631499884956813</v>
+        <v>0.2685219056384245</v>
       </c>
       <c r="J743">
         <v>1.696738089759847</v>
       </c>
       <c r="K743">
-        <v>4.26</v>
+        <v>3.87</v>
       </c>
       <c r="L743">
-        <v>6.39</v>
+        <v>5.39</v>
       </c>
       <c r="M743">
+        <v>4.03</v>
+      </c>
+      <c r="N743">
+        <v>5.93</v>
+      </c>
+      <c r="O743">
+        <v>1</v>
+      </c>
+      <c r="P743" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="744" spans="1:16">
+      <c r="A744" s="1">
+        <v>1</v>
+      </c>
+      <c r="B744" t="s">
+        <v>154</v>
+      </c>
+      <c r="C744">
+        <v>-0.7917892635273791</v>
+      </c>
+      <c r="D744" t="s">
+        <v>258</v>
+      </c>
+      <c r="E744">
+        <v>-0.7599849781417891</v>
+      </c>
+      <c r="F744">
+        <v>-1</v>
+      </c>
+      <c r="G744">
+        <v>0.01295178926352738</v>
+      </c>
+      <c r="H744">
+        <v>0.01277998497814179</v>
+      </c>
+      <c r="I744">
+        <v>-0.03180428538558999</v>
+      </c>
+      <c r="J744">
+        <v>1.696738089759847</v>
+      </c>
+      <c r="K744">
         <v>4.05</v>
       </c>
-      <c r="N743">
+      <c r="L744">
         <v>6.08</v>
       </c>
-      <c r="O743">
-        <v>1</v>
-      </c>
-      <c r="P743" t="s">
-        <v>258</v>
+      <c r="M744">
+        <v>3.99</v>
+      </c>
+      <c r="N744">
+        <v>6.01</v>
+      </c>
+      <c r="O744">
+        <v>1</v>
+      </c>
+      <c r="P744" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02600-601600.xlsx
+++ b/s60_signal/position-02600-601600.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="374">
   <si>
     <t>trade_time</t>
   </si>
@@ -451,28 +451,25 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-11-11</t>
+    <t>2021-11-04</t>
   </si>
   <si>
-    <t>2021-11-16</t>
+    <t>2021-11-11</t>
   </si>
   <si>
     <t>2021-12-06</t>
   </si>
   <si>
-    <t>2021-11-04</t>
-  </si>
-  <si>
     <t>2021-11-18</t>
-  </si>
-  <si>
-    <t>2021-11-25</t>
   </si>
   <si>
     <t>2021-12-08</t>
   </si>
   <si>
     <t>2021-12-09</t>
+  </si>
+  <si>
+    <t>2021-11-25</t>
   </si>
   <si>
     <t>2021-12-10</t>
@@ -796,10 +793,13 @@
     <t>2021-11-29</t>
   </si>
   <si>
-    <t>2021-12-16</t>
+    <t>2021-12-20</t>
   </si>
   <si>
     <t>2021-12-02</t>
+  </si>
+  <si>
+    <t>2021-12-17</t>
   </si>
   <si>
     <t>2017-03-09</t>
@@ -1115,6 +1115,9 @@
   </si>
   <si>
     <t>2021-11-15</t>
+  </si>
+  <si>
+    <t>2021-11-16</t>
   </si>
   <si>
     <t>2021-11-17</t>
@@ -1490,7 +1493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P747"/>
+  <dimension ref="A1:P746"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1551,7 +1554,7 @@
         <v>1.855441043116508</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E2">
         <v>1.575397067571232</v>
@@ -1601,7 +1604,7 @@
         <v>1.844886436180541</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E3">
         <v>1.575397067571232</v>
@@ -1651,7 +1654,7 @@
         <v>1.879543169394645</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E4">
         <v>1.575397067571232</v>
@@ -1701,7 +1704,7 @@
         <v>1.931893523774336</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E5">
         <v>1.575397067571232</v>
@@ -1751,7 +1754,7 @@
         <v>1.864287853699299</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E6">
         <v>1.610229702966436</v>
@@ -1801,7 +1804,7 @@
         <v>1.420828285447678</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E7">
         <v>1.720097776330612</v>
@@ -1851,7 +1854,7 @@
         <v>1.444930411725815</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E8">
         <v>1.720097776330612</v>
@@ -1901,7 +1904,7 @@
         <v>1.415528994207057</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E9">
         <v>1.720097776330612</v>
@@ -1951,7 +1954,7 @@
         <v>1.417747421950922</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E10">
         <v>1.720097776330612</v>
@@ -2001,7 +2004,7 @@
         <v>1.837391318446252</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11">
         <v>1.556576374761795</v>
@@ -2051,7 +2054,7 @@
         <v>1.827426275381424</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E12">
         <v>1.556576374761795</v>
@@ -2101,7 +2104,7 @@
         <v>1.861221338322326</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E13">
         <v>1.556576374761795</v>
@@ -2151,7 +2154,7 @@
         <v>1.913526341635005</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E14">
         <v>1.556576374761795</v>
@@ -2201,7 +2204,7 @@
         <v>1.84664628863214</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E15">
         <v>1.593631212440523</v>
@@ -2251,7 +2254,7 @@
         <v>1.404411199189807</v>
       </c>
       <c r="D16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E16">
         <v>1.701186381387154</v>
@@ -2301,7 +2304,7 @@
         <v>1.428241219065881</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E17">
         <v>1.701186381387154</v>
@@ -2351,7 +2354,7 @@
         <v>1.399021205815165</v>
       </c>
       <c r="D18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E18">
         <v>1.701186381387154</v>
@@ -2401,7 +2404,7 @@
         <v>1.398881378074474</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E19">
         <v>1.701186381387154</v>
@@ -2451,7 +2454,7 @@
         <v>1.772601053603223</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E20">
         <v>1.513212850115657</v>
@@ -2501,7 +2504,7 @@
         <v>1.819007208305362</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E21">
         <v>1.513212850115657</v>
@@ -2551,7 +2554,7 @@
         <v>1.871207721197208</v>
       </c>
       <c r="D22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E22">
         <v>1.513212850115657</v>
@@ -2601,7 +2604,7 @@
         <v>1.805999514927688</v>
       </c>
       <c r="D23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E23">
         <v>1.555387718415254</v>
@@ -2651,7 +2654,7 @@
         <v>1.366585666847875</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E24">
         <v>1.657613875899347</v>
@@ -2701,7 +2704,7 @@
         <v>1.360986692631565</v>
       </c>
       <c r="D25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E25">
         <v>1.657613875899347</v>
@@ -2751,7 +2754,7 @@
         <v>1.355413363007501</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E26">
         <v>1.657613875899347</v>
@@ -2801,7 +2804,7 @@
         <v>1.746707087766096</v>
       </c>
       <c r="D27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E27">
         <v>1.485799595466657</v>
@@ -2851,7 +2854,7 @@
         <v>1.792320570044649</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E28">
         <v>1.485799595466657</v>
@@ -2901,7 +2904,7 @@
         <v>1.780303717196457</v>
       </c>
       <c r="D29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E29">
         <v>1.531211209495895</v>
@@ -2951,7 +2954,7 @@
         <v>1.342673382069711</v>
       </c>
       <c r="D30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E30">
         <v>1.63006850917975</v>
@@ -3001,7 +3004,7 @@
         <v>1.336942295782803</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E31">
         <v>1.63006850917975</v>
@@ -3051,7 +3054,7 @@
         <v>1.327934052323203</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E32">
         <v>1.63006850917975</v>
@@ -3101,7 +3104,7 @@
         <v>1.724897025074506</v>
       </c>
       <c r="D33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E33">
         <v>1.462709860729388</v>
@@ -3151,7 +3154,7 @@
         <v>1.713714740951758</v>
       </c>
       <c r="D34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E34">
         <v>1.462709860729388</v>
@@ -3201,7 +3204,7 @@
         <v>1.769842852372705</v>
       </c>
       <c r="D35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E35">
         <v>1.462709860729388</v>
@@ -3251,7 +3254,7 @@
         <v>1.758660568249956</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E36">
         <v>1.510847732595075</v>
@@ -3301,7 +3304,7 @@
         <v>1.322532456829009</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E37">
         <v>1.606867498612421</v>
@@ -3351,7 +3354,7 @@
         <v>1.316690094712042</v>
       </c>
       <c r="D38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E38">
         <v>1.606867498612421</v>
@@ -3401,7 +3404,7 @@
         <v>1.304788679670904</v>
       </c>
       <c r="D39" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E39">
         <v>1.606867498612421</v>
@@ -3451,7 +3454,7 @@
         <v>1.698715924927888</v>
       </c>
       <c r="D40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E40">
         <v>1.451820073210847</v>
@@ -3501,7 +3504,7 @@
         <v>1.703822090603589</v>
       </c>
       <c r="D41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E41">
         <v>1.451820073210847</v>
@@ -3551,7 +3554,7 @@
         <v>1.759241709824535</v>
       </c>
       <c r="D42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E42">
         <v>1.451820073210847</v>
@@ -3601,7 +3604,7 @@
         <v>1.748453032479565</v>
       </c>
       <c r="D43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E43">
         <v>1.501243727217277</v>
@@ -3651,7 +3654,7 @@
         <v>1.313033413258619</v>
       </c>
       <c r="D44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E44">
         <v>1.595925230190177</v>
@@ -3701,7 +3704,7 @@
         <v>1.307138570237948</v>
       </c>
       <c r="D45" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E45">
         <v>1.595925230190177</v>
@@ -3751,7 +3754,7 @@
         <v>1.293872651700511</v>
       </c>
       <c r="D46" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E46">
         <v>1.595925230190177</v>
@@ -3801,7 +3804,7 @@
         <v>1.708440278144118</v>
       </c>
       <c r="D47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E47">
         <v>1.445287539361757</v>
@@ -3851,7 +3854,7 @@
         <v>1.75288232747506</v>
       </c>
       <c r="D48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E48">
         <v>1.445287539361757</v>
@@ -3901,7 +3904,7 @@
         <v>1.742329765811383</v>
       </c>
       <c r="D49" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E49">
         <v>1.495482504593743</v>
@@ -3951,7 +3954,7 @@
         <v>1.307335154816763</v>
       </c>
       <c r="D50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E50">
         <v>1.589361214250248</v>
@@ -4001,7 +4004,7 @@
         <v>1.301408829705253</v>
       </c>
       <c r="D51" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E51">
         <v>1.589361214250248</v>
@@ -4051,7 +4054,7 @@
         <v>1.287324376806003</v>
       </c>
       <c r="D52" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E52">
         <v>1.589361214250248</v>
@@ -4101,7 +4104,7 @@
         <v>1.741577671463358</v>
       </c>
       <c r="D53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E53">
         <v>1.433675083310133</v>
@@ -4151,7 +4154,7 @@
         <v>1.793586527085793</v>
       </c>
       <c r="D54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E54">
         <v>1.433675083310133</v>
@@ -4201,7 +4204,7 @@
         <v>1.731444837126847</v>
       </c>
       <c r="D55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E55">
         <v>1.485241157810864</v>
@@ -4251,7 +4254,7 @@
         <v>1.297205735321128</v>
       </c>
       <c r="D56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E56">
         <v>1.577692794555001</v>
@@ -4301,7 +4304,7 @@
         <v>1.291223446565996</v>
       </c>
       <c r="D57" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E57">
         <v>1.577692794555001</v>
@@ -4351,7 +4354,7 @@
         <v>1.275683938932566</v>
       </c>
       <c r="D58" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E58">
         <v>1.577692794555001</v>
@@ -4451,7 +4454,7 @@
         <v>1.725587143730334</v>
       </c>
       <c r="D60" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E60">
         <v>1.417249169921011</v>
@@ -4501,7 +4504,7 @@
         <v>1.777556418838578</v>
       </c>
       <c r="D61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E61">
         <v>1.417249169921011</v>
@@ -4551,7 +4554,7 @@
         <v>1.716048017106683</v>
       </c>
       <c r="D62" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E62">
         <v>1.470754689617085</v>
@@ -4601,7 +4604,7 @@
         <v>1.282877589184112</v>
       </c>
       <c r="D63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E63">
         <v>1.561187720137498</v>
@@ -4651,7 +4654,7 @@
         <v>1.276816139400598</v>
       </c>
       <c r="D64" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E64">
         <v>1.561187720137498</v>
@@ -4701,7 +4704,7 @@
         <v>1.259218445029255</v>
       </c>
       <c r="D65" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E65">
         <v>1.561187720137498</v>
@@ -4751,7 +4754,7 @@
         <v>1.799190602173319</v>
       </c>
       <c r="D66" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E66">
         <v>1.767682200441425</v>
@@ -4801,7 +4804,7 @@
         <v>1.704528128435052</v>
       </c>
       <c r="D67" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E67">
         <v>1.395616765595412</v>
@@ -4851,7 +4854,7 @@
         <v>1.756445277267813</v>
       </c>
       <c r="D68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E68">
         <v>1.395616765595412</v>
@@ -4901,7 +4904,7 @@
         <v>1.695770895943651</v>
       </c>
       <c r="D69" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E69">
         <v>1.451676472790171</v>
@@ -4951,7 +4954,7 @@
         <v>1.264007877459131</v>
       </c>
       <c r="D70" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E70">
         <v>1.539451063260933</v>
@@ -5001,7 +5004,7 @@
         <v>1.257842175124651</v>
       </c>
       <c r="D71" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E71">
         <v>1.539451063260933</v>
@@ -5051,7 +5054,7 @@
         <v>1.237533914428172</v>
       </c>
       <c r="D72" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E72">
         <v>1.539451063260933</v>
@@ -5151,7 +5154,7 @@
         <v>1.678683818930752</v>
       </c>
       <c r="D74" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E74">
         <v>1.369068774396689</v>
@@ -5201,7 +5204,7 @@
         <v>1.730536996700383</v>
       </c>
       <c r="D75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E75">
         <v>1.369068774396689</v>
@@ -5251,7 +5254,7 @@
         <v>1.670886152386294</v>
       </c>
       <c r="D76" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E76">
         <v>1.428263063684791</v>
@@ -5301,7 +5304,7 @@
         <v>1.240850352606269</v>
       </c>
       <c r="D77" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E77">
         <v>1.51277512993595</v>
@@ -5351,7 +5354,7 @@
         <v>1.234556708145529</v>
       </c>
       <c r="D78" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E78">
         <v>1.51277512993595</v>
@@ -5401,7 +5404,7 @@
         <v>1.210921952166319</v>
       </c>
       <c r="D79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E79">
         <v>1.51277512993595</v>
@@ -5451,7 +5454,7 @@
         <v>1.661963549027058</v>
       </c>
       <c r="D80" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E80">
         <v>1.351893249619379</v>
@@ -5501,7 +5504,7 @@
         <v>1.713775339989997</v>
       </c>
       <c r="D81" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E81">
         <v>1.351893249619379</v>
@@ -5551,7 +5554,7 @@
         <v>1.654786684582984</v>
       </c>
       <c r="D82" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E82">
         <v>1.413115492435404</v>
@@ -5601,7 +5604,7 @@
         <v>1.225868328583652</v>
       </c>
       <c r="D83" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E83">
         <v>1.495516831545256</v>
@@ -5651,7 +5654,7 @@
         <v>1.219491910509528</v>
       </c>
       <c r="D84" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E84">
         <v>1.495516831545256</v>
@@ -5701,7 +5704,7 @@
         <v>1.193705040582317</v>
       </c>
       <c r="D85" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E85">
         <v>1.495516831545256</v>
@@ -5751,7 +5754,7 @@
         <v>1.600429769178104</v>
       </c>
       <c r="D86" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E86">
         <v>1.338006244585976</v>
@@ -5801,7 +5804,7 @@
         <v>1.648444633283697</v>
       </c>
       <c r="D87" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E87">
         <v>1.338006244585976</v>
@@ -5851,7 +5854,7 @@
         <v>1.700222961583904</v>
       </c>
       <c r="D88" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E88">
         <v>1.338006244585976</v>
@@ -5901,7 +5904,7 @@
         <v>1.641769708780589</v>
       </c>
       <c r="D89" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E89">
         <v>1.400868157875824</v>
@@ -5951,7 +5954,7 @@
         <v>1.213754844674996</v>
       </c>
       <c r="D90" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E90">
         <v>1.48156290118639</v>
@@ -6001,7 +6004,7 @@
         <v>1.20731150127541</v>
       </c>
       <c r="D91" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E91">
         <v>1.48156290118639</v>
@@ -6051,7 +6054,7 @@
         <v>1.179784572886182</v>
       </c>
       <c r="D92" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E92">
         <v>1.48156290118639</v>
@@ -6101,7 +6104,7 @@
         <v>1.642770386608872</v>
       </c>
       <c r="D93" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E93">
         <v>1.332177501095747</v>
@@ -6151,7 +6154,7 @@
         <v>1.636306139581315</v>
       </c>
       <c r="D94" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E94">
         <v>1.395727627472394</v>
@@ -6201,7 +6204,7 @@
         <v>1.208670494931713</v>
       </c>
       <c r="D95" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E95">
         <v>1.475706067366088</v>
@@ -6251,7 +6254,7 @@
         <v>1.202199061202053</v>
       </c>
       <c r="D96" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E96">
         <v>1.475706067366088</v>
@@ -6301,7 +6304,7 @@
         <v>1.173941784230917</v>
       </c>
       <c r="D97" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E97">
         <v>1.475706067366088</v>
@@ -6351,7 +6354,7 @@
         <v>1.635648220856852</v>
       </c>
       <c r="D98" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E98">
         <v>1.324861414989093</v>
@@ -6401,7 +6404,7 @@
         <v>1.687394874868875</v>
       </c>
       <c r="D99" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E99">
         <v>1.324861414989093</v>
@@ -6451,7 +6454,7 @@
         <v>1.629448410676523</v>
       </c>
       <c r="D100" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E100">
         <v>1.38927536840002</v>
@@ -6501,7 +6504,7 @@
         <v>1.202288752351933</v>
       </c>
       <c r="D101" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E101">
         <v>1.468354723013138</v>
@@ -6551,7 +6554,7 @@
         <v>1.195782060375976</v>
       </c>
       <c r="D102" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E102">
         <v>1.468354723013138</v>
@@ -6601,7 +6604,7 @@
         <v>1.166608069001115</v>
       </c>
       <c r="D103" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E103">
         <v>1.468354723013138</v>
@@ -6651,7 +6654,7 @@
         <v>1.636237432923918</v>
       </c>
       <c r="D104" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E104">
         <v>1.325466669958976</v>
@@ -6701,7 +6704,7 @@
         <v>1.687985545381652</v>
       </c>
       <c r="D105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E105">
         <v>1.325466669958976</v>
@@ -6751,7 +6754,7 @@
         <v>1.630015746057932</v>
       </c>
       <c r="D106" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E106">
         <v>1.389809159530085</v>
@@ -6801,7 +6804,7 @@
         <v>1.202816709699155</v>
       </c>
       <c r="D107" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E107">
         <v>1.468962894874441</v>
@@ -6851,7 +6854,7 @@
         <v>1.19631293461462</v>
       </c>
       <c r="D108" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E108">
         <v>1.468962894874441</v>
@@ -6901,7 +6904,7 @@
         <v>1.167214782416708</v>
       </c>
       <c r="D109" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E109">
         <v>1.468962894874441</v>
@@ -7001,7 +7004,7 @@
         <v>1.686969731933735</v>
       </c>
       <c r="D111" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E111">
         <v>1.32442577469753</v>
@@ -7051,7 +7054,7 @@
         <v>1.688566437853383</v>
       </c>
       <c r="D112" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E112">
         <v>1.388891165154931</v>
@@ -7101,7 +7104,7 @@
         <v>1.116820833577004</v>
       </c>
       <c r="D113" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E113">
         <v>1.46791698325029</v>
@@ -7151,7 +7154,7 @@
         <v>1.189838416471486</v>
       </c>
       <c r="D114" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E114">
         <v>1.46791698325029</v>
@@ -7201,7 +7204,7 @@
         <v>1.16617137897391</v>
       </c>
       <c r="D115" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E115">
         <v>1.46791698325029</v>
@@ -7301,7 +7304,7 @@
         <v>1.679044765444968</v>
       </c>
       <c r="D117" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E117">
         <v>1.316305130023856</v>
@@ -7351,7 +7354,7 @@
         <v>1.681071963371414</v>
       </c>
       <c r="D118" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E118">
         <v>1.381729343587304</v>
@@ -7401,7 +7404,7 @@
         <v>1.109345926913525</v>
       </c>
       <c r="D119" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E119">
         <v>1.459757202939633</v>
@@ -7451,7 +7454,7 @@
         <v>1.116606291492413</v>
       </c>
       <c r="D120" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E120">
         <v>1.459757202939633</v>
@@ -7501,7 +7504,7 @@
         <v>1.158031166481744</v>
       </c>
       <c r="D121" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E121">
         <v>1.459757202939633</v>
@@ -7551,7 +7554,7 @@
         <v>1.667785062291963</v>
       </c>
       <c r="D122" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E122">
         <v>1.323675609160295</v>
@@ -7651,7 +7654,7 @@
         <v>1.705523534148037</v>
       </c>
       <c r="D124" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E124">
         <v>1.306151805217721</v>
@@ -7701,7 +7704,7 @@
         <v>1.0999999749233</v>
       </c>
       <c r="D125" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E125">
         <v>1.449554946447687</v>
@@ -7751,7 +7754,7 @@
         <v>1.107015681073126</v>
       </c>
       <c r="D126" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E126">
         <v>1.449554946447687</v>
@@ -7801,7 +7804,7 @@
         <v>1.074450234602739</v>
       </c>
       <c r="D127" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E127">
         <v>1.449554946447687</v>
@@ -7851,7 +7854,7 @@
         <v>1.728036618426774</v>
       </c>
       <c r="D128" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E128">
         <v>1.311858607036529</v>
@@ -7951,7 +7954,7 @@
         <v>1.735732764200063</v>
       </c>
       <c r="D130" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E130">
         <v>1.301215982596513</v>
@@ -8001,7 +8004,7 @@
         <v>1.095456639402092</v>
       </c>
       <c r="D131" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E131">
         <v>1.444595336729509</v>
@@ -8051,7 +8054,7 @@
         <v>1.102353410067069</v>
       </c>
       <c r="D132" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E132">
         <v>1.444595336729509</v>
@@ -8101,7 +8104,7 @@
         <v>1.069526305530016</v>
       </c>
       <c r="D133" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E133">
         <v>1.444595336729509</v>
@@ -8201,7 +8204,7 @@
         <v>1.767688434264066</v>
       </c>
       <c r="D135" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E135">
         <v>1.290978663803567</v>
@@ -8251,7 +8254,7 @@
         <v>1.08603337246497</v>
       </c>
       <c r="D136" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E136">
         <v>1.434308681460452</v>
@@ -8301,7 +8304,7 @@
         <v>1.092683460749394</v>
       </c>
       <c r="D137" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E137">
         <v>1.434308681460452</v>
@@ -8351,7 +8354,7 @@
         <v>1.059313654975125</v>
       </c>
       <c r="D138" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E138">
         <v>1.434308681460452</v>
@@ -9001,7 +9004,7 @@
         <v>1.823420612308294</v>
       </c>
       <c r="D151" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E151">
         <v>2.204728303692967</v>
@@ -9087,7 +9090,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9137,7 +9140,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9401,7 +9404,7 @@
         <v>2.07884565528049</v>
       </c>
       <c r="D159" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E159">
         <v>2.424795934638657</v>
@@ -9551,7 +9554,7 @@
         <v>2.074698477808512</v>
       </c>
       <c r="D162" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E162">
         <v>2.228712809543505</v>
@@ -9851,7 +9854,7 @@
         <v>2.045995448659537</v>
       </c>
       <c r="D168" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E168">
         <v>2.697722827185737</v>
@@ -10001,7 +10004,7 @@
         <v>2.025703573192318</v>
       </c>
       <c r="D171" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E171">
         <v>2.585859069325287</v>
@@ -10101,7 +10104,7 @@
         <v>2.002237248721763</v>
       </c>
       <c r="D173" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E173">
         <v>2.933150127071722</v>
@@ -10187,7 +10190,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10201,7 +10204,7 @@
         <v>2.14690100237887</v>
       </c>
       <c r="D175" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E175">
         <v>3.035145626224377</v>
@@ -10237,7 +10240,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10301,7 +10304,7 @@
         <v>2.113865641885164</v>
       </c>
       <c r="D177" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E177">
         <v>2.99862999271211</v>
@@ -10451,7 +10454,7 @@
         <v>2.224552854469621</v>
       </c>
       <c r="D180" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E180">
         <v>2.747562112891602</v>
@@ -10501,7 +10504,7 @@
         <v>2.234582155562626</v>
       </c>
       <c r="D181" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E181">
         <v>2.747562112891602</v>
@@ -10551,7 +10554,7 @@
         <v>2.532227490792448</v>
       </c>
       <c r="D182" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E182">
         <v>2.747562112891602</v>
@@ -10701,7 +10704,7 @@
         <v>2.219578642489605</v>
       </c>
       <c r="D185" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E185">
         <v>2.748307309478141</v>
@@ -10751,7 +10754,7 @@
         <v>2.229273046142372</v>
       </c>
       <c r="D186" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E186">
         <v>2.748307309478141</v>
@@ -10801,7 +10804,7 @@
         <v>2.526938081221619</v>
       </c>
       <c r="D187" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E187">
         <v>2.748307309478141</v>
@@ -10951,7 +10954,7 @@
         <v>2.223095119495316</v>
       </c>
       <c r="D190" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E190">
         <v>2.585306324177835</v>
@@ -11001,7 +11004,7 @@
         <v>2.233026276055397</v>
       </c>
       <c r="D191" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E191">
         <v>2.585306324177835</v>
@@ -11051,7 +11054,7 @@
         <v>2.530677384493038</v>
       </c>
       <c r="D192" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E192">
         <v>2.585306324177835</v>
@@ -11201,7 +11204,7 @@
         <v>2.351296670264901</v>
       </c>
       <c r="D195" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E195">
         <v>2.34477901699545</v>
@@ -11251,7 +11254,7 @@
         <v>2.531296670264901</v>
       </c>
       <c r="D196" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E196">
         <v>2.34477901699545</v>
@@ -11451,7 +11454,7 @@
         <v>2.354338556588907</v>
       </c>
       <c r="D200" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E200">
         <v>2.692933327062218</v>
@@ -11501,7 +11504,7 @@
         <v>2.534338556588906</v>
       </c>
       <c r="D201" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E201">
         <v>2.692933327062218</v>
@@ -11701,7 +11704,7 @@
         <v>2.353252705775172</v>
       </c>
       <c r="D205" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E205">
         <v>3.037215179660817</v>
@@ -11751,7 +11754,7 @@
         <v>2.533252705775172</v>
       </c>
       <c r="D206" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E206">
         <v>3.037215179660817</v>
@@ -11801,7 +11804,7 @@
         <v>-1.066638455738899</v>
       </c>
       <c r="D207" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E207">
         <v>-1.465413797453388</v>
@@ -11851,7 +11854,7 @@
         <v>-1.0366384557389</v>
       </c>
       <c r="D208" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E208">
         <v>-1.465413797453388</v>
@@ -11901,7 +11904,7 @@
         <v>-0.9510556888450674</v>
       </c>
       <c r="D209" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E209">
         <v>-1.465413797453388</v>
@@ -11951,7 +11954,7 @@
         <v>-1.819265145803461</v>
       </c>
       <c r="D210" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E210">
         <v>-1.307592851757549</v>
@@ -12001,7 +12004,7 @@
         <v>-1.771950960365871</v>
       </c>
       <c r="D211" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E211">
         <v>-1.297263464992842</v>
@@ -12051,7 +12054,7 @@
         <v>-1.016934078228135</v>
       </c>
       <c r="D212" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E212">
         <v>-1.07654556696558</v>
@@ -12101,7 +12104,7 @@
         <v>-1.083441760674821</v>
       </c>
       <c r="D213" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E213">
         <v>-1.481089607902267</v>
@@ -12151,7 +12154,7 @@
         <v>-1.053441760674821</v>
       </c>
       <c r="D214" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E214">
         <v>-1.481089607902267</v>
@@ -12201,7 +12204,7 @@
         <v>-0.9668769824535648</v>
       </c>
       <c r="D215" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E215">
         <v>-1.481089607902267</v>
@@ -12251,7 +12254,7 @@
         <v>-1.83581385521005</v>
       </c>
       <c r="D216" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E216">
         <v>-1.323195920626619</v>
@@ -12301,7 +12304,7 @@
         <v>-1.787408546075322</v>
       </c>
       <c r="D217" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E217">
         <v>-1.311375331475824</v>
@@ -12401,7 +12404,7 @@
         <v>-1.07759404974841</v>
       </c>
       <c r="D219" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E219">
         <v>-1.503621288834554</v>
@@ -12451,7 +12454,7 @@
         <v>-0.9896177741137624</v>
       </c>
       <c r="D220" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E220">
         <v>-1.503621288834554</v>
@@ -12501,7 +12504,7 @@
         <v>-1.859600200509798</v>
       </c>
       <c r="D221" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E221">
         <v>-1.345623046194952</v>
@@ -12551,7 +12554,7 @@
         <v>-1.809626560915746</v>
       </c>
       <c r="D222" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E222">
         <v>-1.33165907208308</v>
@@ -12601,7 +12604,7 @@
         <v>-1.047695097971209</v>
       </c>
       <c r="D223" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E223">
         <v>-1.119714428935569</v>
@@ -12651,7 +12654,7 @@
         <v>-1.107622621715292</v>
       </c>
       <c r="D224" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E224">
         <v>-1.53163495662184</v>
@@ -12701,7 +12704,7 @@
         <v>-1.017891429537125</v>
       </c>
       <c r="D225" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E225">
         <v>-1.53163495662184</v>
@@ -12751,7 +12754,7 @@
         <v>-1.889173794113544</v>
       </c>
       <c r="D226" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E226">
         <v>-1.373506720164198</v>
@@ -12801,7 +12804,7 @@
         <v>-1.837250247248916</v>
       </c>
       <c r="D227" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E227">
         <v>-1.356877872782539</v>
@@ -12901,7 +12904,7 @@
         <v>-1.136466558905362</v>
       </c>
       <c r="D229" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E229">
         <v>-1.55854347811301</v>
@@ -12951,7 +12954,7 @@
         <v>-1.045049682086217</v>
       </c>
       <c r="D230" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E230">
         <v>-1.55854347811301</v>
@@ -13001,7 +13004,7 @@
         <v>-1.91758070195225</v>
       </c>
       <c r="D231" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E231">
         <v>-1.400290376126407</v>
@@ -13051,7 +13054,7 @@
         <v>-1.863784172153202</v>
       </c>
       <c r="D232" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E232">
         <v>-1.38110178540104</v>
@@ -13101,7 +13104,7 @@
         <v>-1.091913194675672</v>
       </c>
       <c r="D233" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E233">
         <v>-0.942243215869925</v>
@@ -13151,7 +13154,7 @@
         <v>-1.06938217480964</v>
       </c>
       <c r="D234" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E234">
         <v>-0.942243215869925</v>
@@ -13201,7 +13204,7 @@
         <v>-1.09938217480964</v>
       </c>
       <c r="D235" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E235">
         <v>-0.942243215869925</v>
@@ -13251,7 +13254,7 @@
         <v>-1.069955605077879</v>
       </c>
       <c r="D236" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E236">
         <v>-1.583220381123139</v>
@@ -13301,7 +13304,7 @@
         <v>-1.943631724851574</v>
       </c>
       <c r="D237" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E237">
         <v>-1.42485276914577</v>
@@ -13351,7 +13354,7 @@
         <v>-1.888117545191031</v>
       </c>
       <c r="D238" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E238">
         <v>-1.403316723609694</v>
@@ -13401,7 +13404,7 @@
         <v>-1.111780678073619</v>
       </c>
       <c r="D239" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E239">
         <v>-0.8811636624809664</v>
@@ -13451,7 +13454,7 @@
         <v>-1.088104558299923</v>
       </c>
       <c r="D240" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E240">
         <v>-0.8811636624809664</v>
@@ -13501,7 +13504,7 @@
         <v>-1.118104558299923</v>
       </c>
       <c r="D241" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E241">
         <v>-0.8811636624809664</v>
@@ -13551,7 +13554,7 @@
         <v>-1.100958399511376</v>
       </c>
       <c r="D242" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E242">
         <v>-1.613938092389432</v>
@@ -13601,7 +13604,7 @@
         <v>-1.976059935121095</v>
       </c>
       <c r="D243" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E243">
         <v>-1.455427938828461</v>
@@ -13651,7 +13654,7 @@
         <v>-1.918407631706518</v>
       </c>
       <c r="D244" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E244">
         <v>-1.430969790828538</v>
@@ -13701,7 +13704,7 @@
         <v>-1.136511642828615</v>
       </c>
       <c r="D245" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E245">
         <v>-1.028859339414037</v>
@@ -13751,7 +13754,7 @@
         <v>-1.111410107218897</v>
       </c>
       <c r="D246" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E246">
         <v>-1.028859339414037</v>
@@ -13801,7 +13804,7 @@
         <v>-1.141410107218897</v>
       </c>
       <c r="D247" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E247">
         <v>-1.028859339414037</v>
@@ -13851,7 +13854,7 @@
         <v>-1.117512484565025</v>
       </c>
       <c r="D248" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E248">
         <v>-1.630339955971323</v>
@@ -13901,7 +13904,7 @@
         <v>-1.993375127533532</v>
       </c>
       <c r="D249" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E249">
         <v>-1.471753691674473</v>
@@ -13951,7 +13954,7 @@
         <v>-1.934581163080772</v>
       </c>
       <c r="D250" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E250">
         <v>-1.445735273589034</v>
@@ -14001,7 +14004,7 @@
         <v>-1.149716855503595</v>
       </c>
       <c r="D251" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E251">
         <v>-1.032336626753983</v>
@@ -14051,7 +14054,7 @@
         <v>-1.123854212535088</v>
       </c>
       <c r="D252" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E252">
         <v>-1.032336626753983</v>
@@ -14101,7 +14104,7 @@
         <v>-1.153854212535088</v>
       </c>
       <c r="D253" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E253">
         <v>-1.032336626753983</v>
@@ -14151,7 +14154,7 @@
         <v>-1.135440729342402</v>
       </c>
       <c r="D254" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E254">
         <v>-1.64810334332546</v>
@@ -14201,7 +14204,7 @@
         <v>-2.012127659427111</v>
       </c>
       <c r="D255" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E255">
         <v>-1.489434650316991</v>
@@ -14251,7 +14254,7 @@
         <v>-1.95209726430005</v>
       </c>
       <c r="D256" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E256">
         <v>-1.461726443643339</v>
@@ -14301,7 +14304,7 @@
         <v>-1.164018236969687</v>
       </c>
       <c r="D257" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E257">
         <v>-1.112656534851095</v>
@@ -14351,7 +14354,7 @@
         <v>-1.137331306884979</v>
       </c>
       <c r="D258" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E258">
         <v>-1.112656534851095</v>
@@ -14401,7 +14404,7 @@
         <v>-1.167331306884979</v>
       </c>
       <c r="D259" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E259">
         <v>-1.112656534851095</v>
@@ -14451,7 +14454,7 @@
         <v>-2.029751754240792</v>
       </c>
       <c r="D260" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E260">
         <v>-1.506051653998461</v>
@@ -14501,7 +14504,7 @@
         <v>-1.968559330884256</v>
       </c>
       <c r="D261" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E261">
         <v>-1.476755342077862</v>
@@ -14551,7 +14554,7 @@
         <v>-1.177459030157264</v>
       </c>
       <c r="D262" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E262">
         <v>-1.113758929914932</v>
@@ -14601,7 +14604,7 @@
         <v>-1.149997414586239</v>
       </c>
       <c r="D263" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E263">
         <v>-1.113758929914932</v>
@@ -14651,7 +14654,7 @@
         <v>-1.179997414586239</v>
       </c>
       <c r="D264" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E264">
         <v>-1.113758929914932</v>
@@ -14701,7 +14704,7 @@
         <v>-2.049264235927141</v>
       </c>
       <c r="D265" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E265">
         <v>-1.524449136731304</v>
@@ -14751,7 +14754,7 @@
         <v>-1.986785275316561</v>
       </c>
       <c r="D266" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E266">
         <v>-1.493394557230178</v>
@@ -14801,7 +14804,7 @@
         <v>-1.192339977729051</v>
       </c>
       <c r="D267" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E267">
         <v>-0.9807727745942727</v>
@@ -14851,7 +14854,7 @@
         <v>-1.16402067065533</v>
       </c>
       <c r="D268" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E268">
         <v>-0.9807727745942727</v>
@@ -14901,7 +14904,7 @@
         <v>-1.19402067065533</v>
       </c>
       <c r="D269" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E269">
         <v>-0.9807727745942727</v>
@@ -14951,7 +14954,7 @@
         <v>-2.083260847634321</v>
       </c>
       <c r="D270" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E270">
         <v>-1.55650308491236</v>
@@ -15001,7 +15004,7 @@
         <v>-2.018540352185904</v>
       </c>
       <c r="D271" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E271">
         <v>-1.52238507446619</v>
@@ -15051,7 +15054,7 @@
         <v>-1.218267064020021</v>
       </c>
       <c r="D272" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E272">
         <v>-1.15072047992809</v>
@@ -15101,7 +15104,7 @@
         <v>-1.188453400387743</v>
       </c>
       <c r="D273" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E273">
         <v>-1.15072047992809</v>
@@ -15151,7 +15154,7 @@
         <v>-1.218453400387743</v>
       </c>
       <c r="D274" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E274">
         <v>-1.15072047992809</v>
@@ -15201,7 +15204,7 @@
         <v>-2.129173370599524</v>
       </c>
       <c r="D275" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E275">
         <v>-1.599792035136694</v>
@@ -15251,7 +15254,7 @@
         <v>-2.061425675834721</v>
       </c>
       <c r="D276" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E276">
         <v>-1.561536852291463</v>
@@ -15301,7 +15304,7 @@
         <v>-1.253281669446231</v>
       </c>
       <c r="D277" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E277">
         <v>-1.285422798224685</v>
@@ -15351,7 +15354,7 @@
         <v>-1.221449872936362</v>
       </c>
       <c r="D278" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E278">
         <v>-1.285422798224685</v>
@@ -15401,7 +15404,7 @@
         <v>-1.251449872936362</v>
       </c>
       <c r="D279" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E279">
         <v>-1.285422798224685</v>
@@ -15451,7 +15454,7 @@
         <v>-2.169540849194301</v>
       </c>
       <c r="D280" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E280">
         <v>-1.637852800668912</v>
@@ -15501,7 +15504,7 @@
         <v>-2.099131562434238</v>
       </c>
       <c r="D281" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E281">
         <v>-1.595960108763492</v>
@@ -15551,7 +15554,7 @@
         <v>-1.284067416858071</v>
       </c>
       <c r="D282" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E282">
         <v>-1.430231131562097</v>
@@ -15601,7 +15604,7 @@
         <v>-1.250461225684695</v>
       </c>
       <c r="D283" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E283">
         <v>-1.430231131562097</v>
@@ -15651,7 +15654,7 @@
         <v>-1.280461225684695</v>
       </c>
       <c r="D284" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E284">
         <v>-1.430231131562097</v>
@@ -15701,7 +15704,7 @@
         <v>-2.189959023684696</v>
       </c>
       <c r="D285" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E285">
         <v>-1.657104222331285</v>
@@ -15751,7 +15754,7 @@
         <v>-2.11820348366153</v>
       </c>
       <c r="D286" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E286">
         <v>-1.613371650966291</v>
@@ -15801,7 +15804,7 @@
         <v>-1.299639079601296</v>
       </c>
       <c r="D287" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E287">
         <v>-1.362715372273368</v>
@@ -15851,7 +15854,7 @@
         <v>-1.265135386252518</v>
       </c>
       <c r="D288" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E288">
         <v>-1.362715372273368</v>
@@ -15901,7 +15904,7 @@
         <v>-1.295135386252518</v>
       </c>
       <c r="D289" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E289">
         <v>-1.362715372273368</v>
@@ -15951,7 +15954,7 @@
         <v>-2.214173184477514</v>
       </c>
       <c r="D290" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E290">
         <v>-1.679934716793084</v>
@@ -16001,7 +16004,7 @@
         <v>-2.140821106380096</v>
       </c>
       <c r="D291" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E291">
         <v>-1.634020210059946</v>
@@ -16051,7 +16054,7 @@
         <v>-1.318105703326807</v>
       </c>
       <c r="D292" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E292">
         <v>-1.489781742375517</v>
@@ -16101,7 +16104,7 @@
         <v>-1.282537651261862</v>
       </c>
       <c r="D293" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E293">
         <v>-1.489781742375517</v>
@@ -16151,7 +16154,7 @@
         <v>-1.312537651261862</v>
       </c>
       <c r="D294" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E294">
         <v>-1.489781742375517</v>
@@ -16201,7 +16204,7 @@
         <v>-2.241121102143395</v>
       </c>
       <c r="D295" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E295">
         <v>-1.705342753449486</v>
@@ -16251,7 +16254,7 @@
         <v>-2.165992238265808</v>
       </c>
       <c r="D296" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E296">
         <v>-1.656999972816785</v>
@@ -16301,7 +16304,7 @@
         <v>-1.338657192184084</v>
       </c>
       <c r="D297" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E297">
         <v>-1.427033480143279</v>
@@ -16351,7 +16354,7 @@
         <v>-1.301904616265692</v>
       </c>
       <c r="D298" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E298">
         <v>-1.427033480143279</v>
@@ -16401,7 +16404,7 @@
         <v>-1.331904616265692</v>
       </c>
       <c r="D299" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E299">
         <v>-1.427033480143279</v>
@@ -16451,7 +16454,7 @@
         <v>1.347720014974502</v>
       </c>
       <c r="D300" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E300">
         <v>1.579062118830282</v>
@@ -16501,7 +16504,7 @@
         <v>1.334700016044109</v>
       </c>
       <c r="D301" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E301">
         <v>1.593089491417174</v>
@@ -16551,7 +16554,7 @@
         <v>1.841747387561394</v>
       </c>
       <c r="D302" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E302">
         <v>1.890874754800249</v>
@@ -16601,7 +16604,7 @@
         <v>1.862485279427185</v>
       </c>
       <c r="D303" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E303">
         <v>1.890874754800249</v>
@@ -16651,7 +16654,7 @@
         <v>1.441706845387347</v>
       </c>
       <c r="D304" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E304">
         <v>1.664215600520115</v>
@@ -16701,7 +16704,7 @@
         <v>1.435400191486443</v>
       </c>
       <c r="D305" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E305">
         <v>1.704389685327122</v>
@@ -16751,7 +16754,7 @@
         <v>1.856584782452771</v>
       </c>
       <c r="D306" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E306">
         <v>1.861880930194354</v>
@@ -16801,7 +16804,7 @@
         <v>1.9645987906652</v>
       </c>
       <c r="D307" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E307">
         <v>1.861880930194354</v>
@@ -16851,7 +16854,7 @@
         <v>2.014804950663784</v>
       </c>
       <c r="D308" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E308">
         <v>1.689180786611569</v>
@@ -16901,7 +16904,7 @@
         <v>1.927301606872644</v>
       </c>
       <c r="D309" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E309">
         <v>1.689180786611569</v>
@@ -16951,7 +16954,7 @@
         <v>1.922617032689892</v>
       </c>
       <c r="D310" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E310">
         <v>1.689180786611569</v>
@@ -17001,7 +17004,7 @@
         <v>1.696992868637676</v>
       </c>
       <c r="D311" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E311">
         <v>1.791368704585461</v>
@@ -17351,7 +17354,7 @@
         <v>1.869784887916945</v>
       </c>
       <c r="D318" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E318">
         <v>1.868536559812515</v>
@@ -17401,7 +17404,7 @@
         <v>1.892281544125805</v>
       </c>
       <c r="D319" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E319">
         <v>1.868536559812515</v>
@@ -17451,7 +17454,7 @@
         <v>1.879784887916945</v>
       </c>
       <c r="D320" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E320">
         <v>1.868536559812515</v>
@@ -17501,7 +17504,7 @@
         <v>1.830509026107986</v>
       </c>
       <c r="D321" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E321">
         <v>1.588842690067986</v>
@@ -17551,7 +17554,7 @@
         <v>1.823342590879987</v>
       </c>
       <c r="D322" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E322">
         <v>1.588842690067986</v>
@@ -17601,7 +17604,7 @@
         <v>1.597009323671986</v>
       </c>
       <c r="D323" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E323">
         <v>1.690676056463986</v>
@@ -17651,7 +17654,7 @@
         <v>1.564008728543987</v>
       </c>
       <c r="D324" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E324">
         <v>1.690841103059988</v>
@@ -17701,7 +17704,7 @@
         <v>1.612175362147987</v>
       </c>
       <c r="D325" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E325">
         <v>1.690841103059988</v>
@@ -17751,7 +17754,7 @@
         <v>1.608508629355987</v>
       </c>
       <c r="D326" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E326">
         <v>1.690841103059988</v>
@@ -17801,7 +17804,7 @@
         <v>1.611175163771987</v>
       </c>
       <c r="D327" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E327">
         <v>1.690841103059988</v>
@@ -17901,7 +17904,7 @@
         <v>1.787174370267988</v>
       </c>
       <c r="D329" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E329">
         <v>1.578675659711986</v>
@@ -17951,7 +17954,7 @@
         <v>1.812507439099989</v>
       </c>
       <c r="D330" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E330">
         <v>1.578675659711986</v>
@@ -18001,7 +18004,7 @@
         <v>1.783507637475988</v>
       </c>
       <c r="D331" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E331">
         <v>1.578675659711986</v>
@@ -18051,7 +18054,7 @@
         <v>1.797174370267989</v>
       </c>
       <c r="D332" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E332">
         <v>1.578675659711986</v>
@@ -18101,7 +18104,7 @@
         <v>1.796508232603987</v>
       </c>
       <c r="D333" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E333">
         <v>1.578675659711986</v>
@@ -18151,7 +18154,7 @@
         <v>1.60619577124814</v>
       </c>
       <c r="D334" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E334">
         <v>1.409496709559184</v>
@@ -18201,7 +18204,7 @@
         <v>1.639829926132983</v>
       </c>
       <c r="D335" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E335">
         <v>1.409496709559184</v>
@@ -18251,7 +18254,7 @@
         <v>1.641634855442047</v>
       </c>
       <c r="D336" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E336">
         <v>1.409496709559184</v>
@@ -18301,7 +18304,7 @@
         <v>1.294651169712725</v>
       </c>
       <c r="D337" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E337">
         <v>1.17011455017335</v>
@@ -18351,7 +18354,7 @@
         <v>1.309805629866267</v>
       </c>
       <c r="D338" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E338">
         <v>1.17011455017335</v>
@@ -18401,7 +18404,7 @@
         <v>1.302846240403662</v>
       </c>
       <c r="D339" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E339">
         <v>1.17011455017335</v>
@@ -18451,7 +18454,7 @@
         <v>1.302846240403662</v>
       </c>
       <c r="D340" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E340">
         <v>1.17011455017335</v>
@@ -18501,7 +18504,7 @@
         <v>1.306789315595589</v>
       </c>
       <c r="D341" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E341">
         <v>1.17011455017335</v>
@@ -18551,7 +18554,7 @@
         <v>1.225269010326891</v>
       </c>
       <c r="D342" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E342">
         <v>1.17011455017335</v>
@@ -18601,7 +18604,7 @@
         <v>1.444294269397325</v>
       </c>
       <c r="D343" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E343">
         <v>1.256000185094495</v>
@@ -18651,7 +18654,7 @@
         <v>1.501117816501946</v>
       </c>
       <c r="D344" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E344">
         <v>1.256000185094495</v>
@@ -18701,7 +18704,7 @@
         <v>1.083058995014017</v>
       </c>
       <c r="D345" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E345">
         <v>1.093353102453659</v>
@@ -18751,7 +18754,7 @@
         <v>1.408730452400234</v>
       </c>
       <c r="D346" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E346">
         <v>1.224172692200284</v>
@@ -18801,7 +18804,7 @@
         <v>1.47198161896276</v>
       </c>
       <c r="D347" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E347">
         <v>1.224172692200284</v>
@@ -18901,7 +18904,7 @@
         <v>1.382122760311682</v>
       </c>
       <c r="D349" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E349">
         <v>1.191863351807043</v>
@@ -18951,7 +18954,7 @@
         <v>1.442404318382183</v>
       </c>
       <c r="D350" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E350">
         <v>1.191863351807043</v>
@@ -19051,7 +19054,7 @@
         <v>1.370401955803482</v>
       </c>
       <c r="D352" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E352">
         <v>1.1776309463328</v>
@@ -19101,7 +19104,7 @@
         <v>1.429375388370835</v>
       </c>
       <c r="D353" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E353">
         <v>1.1776309463328</v>
@@ -19151,7 +19154,7 @@
         <v>1.010452200278918</v>
       </c>
       <c r="D354" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E354">
         <v>1.015068140738506</v>
@@ -19201,7 +19204,7 @@
         <v>1.025068140738506</v>
       </c>
       <c r="D355" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E355">
         <v>1.015068140738506</v>
@@ -19251,7 +19254,7 @@
         <v>1.355513343522262</v>
       </c>
       <c r="D356" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E356">
         <v>1.159551917134175</v>
@@ -19301,7 +19304,7 @@
         <v>1.4128251006118</v>
       </c>
       <c r="D357" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E357">
         <v>1.159551917134175</v>
@@ -19351,7 +19354,7 @@
         <v>0.9937025114625451</v>
       </c>
       <c r="D358" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E358">
         <v>1.019315457208822</v>
@@ -19401,7 +19404,7 @@
         <v>1.009315457208822</v>
       </c>
       <c r="D359" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E359">
         <v>1.019315457208822</v>
@@ -19451,7 +19454,7 @@
         <v>1.344301537527252</v>
       </c>
       <c r="D360" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E360">
         <v>1.145937581283092</v>
@@ -19501,7 +19504,7 @@
         <v>1.400361976983419</v>
       </c>
       <c r="D361" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E361">
         <v>1.145937581283092</v>
@@ -19651,7 +19654,7 @@
         <v>1.32595157423566</v>
       </c>
       <c r="D364" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E364">
         <v>1.123655483000445</v>
@@ -19701,7 +19704,7 @@
         <v>1.379964026717319</v>
       </c>
       <c r="D365" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E365">
         <v>1.123655483000445</v>
@@ -19751,7 +19754,7 @@
         <v>0.9604455210151182</v>
       </c>
       <c r="D366" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E366">
         <v>0.9494825324195202</v>
@@ -19801,7 +19804,7 @@
         <v>0.9780380495261229</v>
       </c>
       <c r="D367" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E367">
         <v>0.9494825324195202</v>
@@ -19851,7 +19854,7 @@
         <v>0.9780380495261229</v>
       </c>
       <c r="D368" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E368">
         <v>0.9494825324195202</v>
@@ -19901,7 +19904,7 @@
         <v>0.93948253241952</v>
       </c>
       <c r="D369" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E369">
         <v>0.9494825324195202</v>
@@ -19951,7 +19954,7 @@
         <v>1.346901155844391</v>
       </c>
       <c r="D370" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E370">
         <v>1.225539647019887</v>
@@ -20001,7 +20004,7 @@
         <v>1.331298641136886</v>
       </c>
       <c r="D371" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E371">
         <v>1.225539647019887</v>
@@ -20051,7 +20054,7 @@
         <v>1.154256377900131</v>
       </c>
       <c r="D372" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E372">
         <v>1.26001537201713</v>
@@ -20101,7 +20104,7 @@
         <v>1.14857562348788</v>
       </c>
       <c r="D373" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E373">
         <v>1.274334617604878</v>
@@ -20151,7 +20154,7 @@
         <v>1.324412857309625</v>
       </c>
       <c r="D374" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E374">
         <v>1.205852605838874</v>
@@ -20201,7 +20204,7 @@
         <v>1.043943419081145</v>
       </c>
       <c r="D375" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E375">
         <v>1.269702413198143</v>
@@ -20251,7 +20254,7 @@
         <v>1.36666643673015</v>
       </c>
       <c r="D376" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E376">
         <v>1.400907442613152</v>
@@ -20301,7 +20304,7 @@
         <v>1.3381061852594</v>
       </c>
       <c r="D377" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E377">
         <v>1.400907442613152</v>
@@ -20351,7 +20354,7 @@
         <v>1.337921514632137</v>
       </c>
       <c r="D378" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E378">
         <v>1.216329758597064</v>
@@ -20401,7 +20404,7 @@
         <v>1.321935254573682</v>
       </c>
       <c r="D379" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E379">
         <v>1.216329758597064</v>
@@ -20451,7 +20454,7 @@
         <v>1.144547620521072</v>
       </c>
       <c r="D380" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E380">
         <v>1.250153116497689</v>
@@ -20501,7 +20504,7 @@
         <v>1.138751742503535</v>
       </c>
       <c r="D381" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E381">
         <v>1.264357238480152</v>
@@ -20551,7 +20554,7 @@
         <v>1.314166856439233</v>
       </c>
       <c r="D382" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E382">
         <v>1.195568230433388</v>
@@ -20601,7 +20604,7 @@
         <v>1.035309148684748</v>
       </c>
       <c r="D383" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E383">
         <v>1.260914644661365</v>
@@ -20751,7 +20754,7 @@
         <v>1.326338641239302</v>
       </c>
       <c r="D386" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E386">
         <v>1.204449888450566</v>
@@ -20801,7 +20804,7 @@
         <v>1.309857386591409</v>
       </c>
       <c r="D387" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E387">
         <v>1.204449888450566</v>
@@ -20851,7 +20854,7 @@
         <v>1.132024257408305</v>
       </c>
       <c r="D388" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E388">
         <v>1.237431755549148</v>
@@ -20901,7 +20904,7 @@
         <v>1.126079881013937</v>
       </c>
       <c r="D389" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E389">
         <v>1.25148737915478</v>
@@ -20951,7 +20954,7 @@
         <v>1.300950500901255</v>
       </c>
       <c r="D390" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E390">
         <v>1.182302375436465</v>
@@ -21001,7 +21004,7 @@
         <v>1.024171770422406</v>
       </c>
       <c r="D391" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E391">
         <v>1.249579268563249</v>
@@ -21051,7 +21054,7 @@
         <v>1.347949275999877</v>
       </c>
       <c r="D392" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E392">
         <v>1.407134279718192</v>
@@ -21101,7 +21104,7 @@
         <v>1.319301150535088</v>
       </c>
       <c r="D393" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E393">
         <v>1.407134279718192</v>
@@ -21151,7 +21154,7 @@
         <v>1.31894662096582</v>
       </c>
       <c r="D394" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E394">
         <v>1.196868329195712</v>
@@ -21201,7 +21204,7 @@
         <v>1.302149468015641</v>
       </c>
       <c r="D395" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E395">
         <v>1.196868329195712</v>
@@ -21251,7 +21254,7 @@
         <v>1.12403203036048</v>
       </c>
       <c r="D396" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E396">
         <v>1.229313169180409</v>
@@ -21301,7 +21304,7 @@
         <v>1.117992884475426</v>
       </c>
       <c r="D397" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E397">
         <v>1.243274023295355</v>
@@ -21351,7 +21354,7 @@
         <v>1.017064058620981</v>
       </c>
       <c r="D398" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E398">
         <v>1.242345197440909</v>
@@ -21501,7 +21504,7 @@
         <v>1.309314370259902</v>
       </c>
       <c r="D401" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E401">
         <v>1.212105582664171</v>
@@ -21551,7 +21554,7 @@
         <v>1.113617673828013</v>
       </c>
       <c r="D402" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E402">
         <v>1.218734158789721</v>
@@ -21601,7 +21604,7 @@
         <v>1.107455037549294</v>
       </c>
       <c r="D403" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E403">
         <v>1.232571522511002</v>
@@ -21651,7 +21654,7 @@
         <v>1.00780227909606</v>
       </c>
       <c r="D404" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E404">
         <v>1.232918764057767</v>
@@ -21837,7 +21840,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21851,7 +21854,7 @@
         <v>1.096911392393543</v>
       </c>
       <c r="D408" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E408">
         <v>1.20176374642348</v>
@@ -21887,7 +21890,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21901,7 +21904,7 @@
         <v>1.090550657915995</v>
       </c>
       <c r="D409" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E409">
         <v>1.215403011945933</v>
@@ -21937,7 +21940,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21951,7 +21954,7 @@
         <v>0.9929449141839808</v>
       </c>
       <c r="D410" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E410">
         <v>1.217797268213918</v>
@@ -21987,7 +21990,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22037,7 +22040,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22087,7 +22090,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22101,7 +22104,7 @@
         <v>1.076787728620787</v>
       </c>
       <c r="D413" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E413">
         <v>1.194722566962074</v>
@@ -22151,7 +22154,7 @@
         <v>1.070188373624195</v>
       </c>
       <c r="D414" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E414">
         <v>1.194722566962074</v>
@@ -22201,7 +22204,7 @@
         <v>0.9750483752556411</v>
       </c>
       <c r="D415" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E415">
         <v>1.199582568593519</v>
@@ -22251,7 +22254,7 @@
         <v>1.06618192359011</v>
       </c>
       <c r="D416" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E416">
         <v>1.199582568593519</v>
@@ -22301,7 +22304,7 @@
         <v>1.301445795242007</v>
       </c>
       <c r="D417" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E417">
         <v>1.466305796873452</v>
@@ -22351,7 +22354,7 @@
         <v>1.325778053569659</v>
       </c>
       <c r="D418" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E418">
         <v>1.466305796873452</v>
@@ -22401,7 +22404,7 @@
         <v>1.061021828820504</v>
       </c>
       <c r="D419" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E419">
         <v>1.178520456495379</v>
@@ -22451,7 +22454,7 @@
         <v>1.05423552639545</v>
       </c>
       <c r="D420" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E420">
         <v>1.178520456495379</v>
@@ -22501,7 +22504,7 @@
         <v>0.9610273181210012</v>
       </c>
       <c r="D421" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E421">
         <v>1.18531224822093</v>
@@ -22551,7 +22554,7 @@
         <v>1.052098550645983</v>
       </c>
       <c r="D422" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E422">
         <v>1.18531224822093</v>
@@ -22601,7 +22604,7 @@
         <v>1.288172527821214</v>
       </c>
       <c r="D423" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E423">
         <v>1.460679389446836</v>
@@ -22651,7 +22654,7 @@
         <v>1.312816365196303</v>
       </c>
       <c r="D424" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E424">
         <v>1.460679389446836</v>
@@ -22801,7 +22804,7 @@
         <v>0.8755952802088971</v>
       </c>
       <c r="D427" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E427">
         <v>1.122137607315365</v>
@@ -22851,7 +22854,7 @@
         <v>1.266605330685716</v>
       </c>
       <c r="D428" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E428">
         <v>1.559580979333694</v>
@@ -22937,7 +22940,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22951,7 +22954,7 @@
         <v>0.8602148664207081</v>
       </c>
       <c r="D430" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E430">
         <v>1.107098980500247</v>
@@ -22987,7 +22990,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23001,7 +23004,7 @@
         <v>1.280896373713855</v>
       </c>
       <c r="D431" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E431">
         <v>1.524099754797897</v>
@@ -23037,7 +23040,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23201,7 +23204,7 @@
         <v>1.302688953291221</v>
       </c>
       <c r="D435" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E435">
         <v>1.419681456386476</v>
@@ -23287,7 +23290,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23337,7 +23340,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23387,7 +23390,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23401,7 +23404,7 @@
         <v>1.257626439327654</v>
       </c>
       <c r="D439" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E439">
         <v>1.411664944525371</v>
@@ -23437,7 +23440,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23451,7 +23454,7 @@
         <v>1.840766780529548</v>
       </c>
       <c r="D440" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E440">
         <v>2.000338151296236</v>
@@ -23501,7 +23504,7 @@
         <v>2.174266578212954</v>
       </c>
       <c r="D441" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E441">
         <v>2.309284269167179</v>
@@ -23551,7 +23554,7 @@
         <v>2.096677111858851</v>
       </c>
       <c r="D442" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E442">
         <v>1.937337746663046</v>
@@ -23601,7 +23604,7 @@
         <v>1.86232005570882</v>
       </c>
       <c r="D443" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E443">
         <v>1.975355842250461</v>
@@ -23651,7 +23654,7 @@
         <v>1.842592596122513</v>
       </c>
       <c r="D444" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E444">
         <v>2.002261997256608</v>
@@ -23701,7 +23704,7 @@
         <v>2.176435500091845</v>
       </c>
       <c r="D445" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E445">
         <v>2.311735028352367</v>
@@ -23751,7 +23754,7 @@
         <v>2.099152378635891</v>
       </c>
       <c r="D446" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E446">
         <v>1.939947805195271</v>
@@ -23801,7 +23804,7 @@
         <v>1.864648276934749</v>
       </c>
       <c r="D447" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E447">
         <v>1.97756152551713</v>
@@ -23851,7 +23854,7 @@
         <v>1.84474004582061</v>
       </c>
       <c r="D448" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E448">
         <v>2.004524746267355</v>
@@ -23901,7 +23904,7 @@
         <v>2.178986497384215</v>
       </c>
       <c r="D449" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E449">
         <v>2.314617511168604</v>
@@ -23951,7 +23954,7 @@
         <v>2.102063686280291</v>
       </c>
       <c r="D450" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E450">
         <v>1.943017649394564</v>
@@ -24001,7 +24004,7 @@
         <v>1.867386635610175</v>
       </c>
       <c r="D451" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E451">
         <v>1.980155760051744</v>
@@ -24051,7 +24054,7 @@
         <v>2.182944230037506</v>
       </c>
       <c r="D452" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E452">
         <v>2.319089525466108</v>
@@ -24101,7 +24104,7 @@
         <v>2.106580420720769</v>
       </c>
       <c r="D453" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E453">
         <v>1.947780344621405</v>
@@ -24151,7 +24154,7 @@
         <v>1.871635049192803</v>
       </c>
       <c r="D454" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E454">
         <v>1.984180572919497</v>
@@ -24201,7 +24204,7 @@
         <v>2.18904965856885</v>
       </c>
       <c r="D455" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E455">
         <v>2.325988314767062</v>
@@ -24251,7 +24254,7 @@
         <v>2.113548197914732</v>
       </c>
       <c r="D456" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E456">
         <v>1.955127555226921</v>
@@ -24301,7 +24304,7 @@
         <v>1.878188899028709</v>
       </c>
       <c r="D457" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E457">
         <v>2.015269716995014</v>
@@ -24351,7 +24354,7 @@
         <v>1.88583444385064</v>
       </c>
       <c r="D458" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E458">
         <v>2.125307034142769</v>
@@ -24401,7 +24404,7 @@
         <v>2.298073483752043</v>
       </c>
       <c r="D459" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E459">
         <v>2.037664496092738</v>
@@ -24451,7 +24454,7 @@
         <v>1.897427651995606</v>
       </c>
       <c r="D460" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E460">
         <v>2.100495646236972</v>
@@ -24501,7 +24504,7 @@
         <v>1.886668859096591</v>
       </c>
       <c r="D461" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E461">
         <v>2.126294507806616</v>
@@ -24551,7 +24554,7 @@
         <v>2.29919426636051</v>
       </c>
       <c r="D462" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E462">
         <v>2.038997585538931</v>
@@ -24601,7 +24604,7 @@
         <v>1.898642244602138</v>
       </c>
       <c r="D463" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E463">
         <v>2.102411345144836</v>
@@ -24651,7 +24654,7 @@
         <v>1.887695818378956</v>
       </c>
       <c r="D464" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E464">
         <v>2.127509844235451</v>
@@ -24751,7 +24754,7 @@
         <v>1.900137108409605</v>
       </c>
       <c r="D466" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E466">
         <v>2.104769097816775</v>
@@ -24801,7 +24804,7 @@
         <v>1.882492570308907</v>
       </c>
       <c r="D467" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E467">
         <v>2.121352154211724</v>
@@ -24901,7 +24904,7 @@
         <v>1.911660475077831</v>
       </c>
       <c r="D469" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E469">
         <v>2.092823179170745</v>
@@ -24951,7 +24954,7 @@
         <v>1.879971436092785</v>
       </c>
       <c r="D470" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E470">
         <v>2.118368563423415</v>
@@ -25051,7 +25054,7 @@
         <v>1.90788623273062</v>
       </c>
       <c r="D472" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E472">
         <v>2.087035013041425</v>
@@ -25151,7 +25154,7 @@
         <v>1.89858988459332</v>
       </c>
       <c r="D474" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E474">
         <v>2.07277816293363</v>
@@ -25201,7 +25204,7 @@
         <v>2.27342525786704</v>
       </c>
       <c r="D475" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E475">
         <v>2.050890844436287</v>
@@ -25251,7 +25254,7 @@
         <v>1.889192027490578</v>
       </c>
       <c r="D476" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E476">
         <v>2.058365638997408</v>
@@ -25301,7 +25304,7 @@
         <v>2.266210657543448</v>
       </c>
       <c r="D477" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E477">
         <v>2.042055342718407</v>
@@ -25351,7 +25354,7 @@
         <v>1.881151085279702</v>
       </c>
       <c r="D478" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E478">
         <v>2.046034075448713</v>
@@ -25401,7 +25404,7 @@
         <v>2.259792939301354</v>
       </c>
       <c r="D479" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E479">
         <v>2.034195758263333</v>
@@ -25451,7 +25454,7 @@
         <v>1.873998297987854</v>
       </c>
       <c r="D480" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E480">
         <v>2.061056685064424</v>
@@ -25501,7 +25504,7 @@
         <v>2.247400638043782</v>
       </c>
       <c r="D481" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E481">
         <v>2.019019283595469</v>
@@ -25551,7 +25554,7 @@
         <v>1.860186614207387</v>
       </c>
       <c r="D482" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E482">
         <v>2.039929722127505</v>
@@ -25601,7 +25604,7 @@
         <v>2.218696305669633</v>
       </c>
       <c r="D483" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E483">
         <v>1.983865960247392</v>
@@ -25651,7 +25654,7 @@
         <v>1.828194560944569</v>
       </c>
       <c r="D484" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E484">
         <v>1.990993261207699</v>
@@ -25701,7 +25704,7 @@
         <v>1.830127541068264</v>
       </c>
       <c r="D485" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E485">
         <v>2.018032125375022</v>
@@ -25787,7 +25790,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25801,7 +25804,7 @@
         <v>1.78228507381279</v>
       </c>
       <c r="D487" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E487">
         <v>2.022800472072064</v>
@@ -25837,7 +25840,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25851,7 +25854,7 @@
         <v>1.783722556644772</v>
       </c>
       <c r="D488" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E488">
         <v>1.972929321636883</v>
@@ -25887,7 +25890,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25901,7 +25904,7 @@
         <v>2.163345062458509</v>
       </c>
       <c r="D489" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E489">
         <v>1.877414831999107</v>
@@ -25951,7 +25954,7 @@
         <v>1.693507313006611</v>
       </c>
       <c r="D490" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E490">
         <v>1.978388335287718</v>
@@ -26001,7 +26004,7 @@
         <v>1.734543015346852</v>
       </c>
       <c r="D491" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E491">
         <v>1.925129818487629</v>
@@ -26051,7 +26054,7 @@
         <v>1.684218514250647</v>
       </c>
       <c r="D492" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E492">
         <v>1.570048693213578</v>
@@ -26101,7 +26104,7 @@
         <v>2.132031608016207</v>
       </c>
       <c r="D493" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E493">
         <v>1.840169754028087</v>
@@ -26151,7 +26154,7 @@
         <v>1.660262632299145</v>
       </c>
       <c r="D494" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E494">
         <v>1.929555899725715</v>
@@ -26201,7 +26204,7 @@
         <v>1.680468679922261</v>
       </c>
       <c r="D495" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E495">
         <v>1.872572875128523</v>
@@ -26251,7 +26254,7 @@
         <v>1.634006631356384</v>
       </c>
       <c r="D496" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E496">
         <v>1.60382087481427</v>
@@ -26301,7 +26304,7 @@
         <v>2.09863804467423</v>
       </c>
       <c r="D497" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E497">
         <v>1.800450537718246</v>
@@ -26351,7 +26354,7 @@
         <v>1.624809554037398</v>
       </c>
       <c r="D498" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E498">
         <v>1.877479593897257</v>
@@ -26401,7 +26404,7 @@
         <v>1.622802262168714</v>
       </c>
       <c r="D499" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E499">
         <v>1.752483946759322</v>
@@ -26451,7 +26454,7 @@
         <v>1.580459243442377</v>
       </c>
       <c r="D500" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E500">
         <v>1.752483946759322</v>
@@ -26501,7 +26504,7 @@
         <v>2.071221135479056</v>
       </c>
       <c r="D501" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E501">
         <v>1.767840117089625</v>
@@ -26551,7 +26554,7 @@
         <v>1.595701734142962</v>
       </c>
       <c r="D502" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E502">
         <v>1.834723709073065</v>
@@ -26701,7 +26704,7 @@
         <v>2.041322179557651</v>
       </c>
       <c r="D505" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E505">
         <v>1.73227748229324</v>
@@ -26751,7 +26754,7 @@
         <v>1.563958789750633</v>
       </c>
       <c r="D506" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E506">
         <v>1.788097143451137</v>
@@ -26801,7 +26804,7 @@
         <v>1.472686344256899</v>
       </c>
       <c r="D507" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E507">
         <v>1.788097143451137</v>
@@ -26851,7 +26854,7 @@
         <v>1.523825085403519</v>
       </c>
       <c r="D508" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E508">
         <v>1.630370751283219</v>
@@ -26901,7 +26904,7 @@
         <v>1.56168905637971</v>
       </c>
       <c r="D509" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E509">
         <v>1.630370751283219</v>
@@ -26951,7 +26954,7 @@
         <v>1.565051671294496</v>
       </c>
       <c r="D510" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E510">
         <v>1.630370751283219</v>
@@ -27001,7 +27004,7 @@
         <v>1.866585623391427</v>
       </c>
       <c r="D511" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E511">
         <v>1.689366599623595</v>
@@ -27051,7 +27054,7 @@
         <v>2.005245252276134</v>
       </c>
       <c r="D512" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E512">
         <v>1.689366599623595</v>
@@ -27101,7 +27104,7 @@
         <v>1.4318415411232</v>
       </c>
       <c r="D513" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E513">
         <v>1.73183620839538</v>
@@ -27151,7 +27154,7 @@
         <v>1.461524840934997</v>
       </c>
       <c r="D514" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E514">
         <v>1.564205583165584</v>
@@ -27201,7 +27204,7 @@
         <v>1.496369157204806</v>
       </c>
       <c r="D515" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E515">
         <v>1.564205583165584</v>
@@ -27251,7 +27254,7 @@
         <v>1.508949665433811</v>
       </c>
       <c r="D516" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E516">
         <v>1.564205583165584</v>
@@ -27301,7 +27304,7 @@
         <v>1.973924573324424</v>
       </c>
       <c r="D517" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E517">
         <v>1.612872963807592</v>
@@ -27351,7 +27354,7 @@
         <v>1.396381565393731</v>
       </c>
       <c r="D518" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E518">
         <v>1.682992506417824</v>
@@ -27401,7 +27404,7 @@
         <v>1.467141600577559</v>
       </c>
       <c r="D519" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E519">
         <v>1.682992506417824</v>
@@ -27451,7 +27454,7 @@
         <v>1.407438029705613</v>
       </c>
       <c r="D520" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E520">
         <v>1.521706666475579</v>
@@ -27501,7 +27504,7 @@
         <v>1.439660791349507</v>
       </c>
       <c r="D521" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E521">
         <v>1.521706666475579</v>
@@ -27551,7 +27554,7 @@
         <v>1.460243940015513</v>
       </c>
       <c r="D522" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E522">
         <v>1.521706666475579</v>
@@ -27601,7 +27604,7 @@
         <v>1.940579116805523</v>
       </c>
       <c r="D523" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E523">
         <v>1.574239241056619</v>
@@ -27651,7 +27654,7 @@
         <v>1.781069303182167</v>
       </c>
       <c r="D524" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E524">
         <v>1.574239241056619</v>
@@ -27701,7 +27704,7 @@
         <v>1.358629220348103</v>
       </c>
       <c r="D525" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E525">
         <v>1.630991221802445</v>
@@ -27751,7 +27754,7 @@
         <v>1.349854686289714</v>
       </c>
       <c r="D526" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E526">
         <v>1.479202912629048</v>
@@ -27801,7 +27804,7 @@
         <v>1.379286418533347</v>
       </c>
       <c r="D527" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E527">
         <v>1.479202912629048</v>
@@ -27851,7 +27854,7 @@
         <v>1.408389551684359</v>
       </c>
       <c r="D528" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E528">
         <v>1.479202912629048</v>
@@ -27901,7 +27904,7 @@
         <v>1.74645545085387</v>
       </c>
       <c r="D529" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E529">
         <v>1.54184264617284</v>
@@ -27951,7 +27954,7 @@
         <v>1.326971711279163</v>
       </c>
       <c r="D530" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E530">
         <v>1.58738515872694</v>
@@ -28151,7 +28154,7 @@
         <v>1.276676327166428</v>
       </c>
       <c r="D534" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E534">
         <v>1.518106691894613</v>
@@ -28201,7 +28204,7 @@
         <v>1.224852607973696</v>
       </c>
       <c r="D535" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E535">
         <v>1.33929930838555</v>
@@ -28251,7 +28254,7 @@
         <v>1.248225566013237</v>
       </c>
       <c r="D536" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E536">
         <v>1.33929930838555</v>
@@ -28301,7 +28304,7 @@
         <v>1.263762437199394</v>
       </c>
       <c r="D537" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E537">
         <v>1.33929930838555</v>
@@ -28351,7 +28354,7 @@
         <v>1.212947744952629</v>
       </c>
       <c r="D538" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E538">
         <v>1.430324909390002</v>
@@ -28401,7 +28404,7 @@
         <v>1.146309428698562</v>
       </c>
       <c r="D539" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E539">
         <v>1.238758183620087</v>
@@ -28451,7 +28454,7 @@
         <v>1.216483509339664</v>
       </c>
       <c r="D540" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E540">
         <v>1.238758183620087</v>
@@ -28501,7 +28504,7 @@
         <v>1.171021231954409</v>
       </c>
       <c r="D541" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E541">
         <v>1.238758183620087</v>
@@ -28701,7 +28704,7 @@
         <v>0.913889681656368</v>
       </c>
       <c r="D545" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E545">
         <v>0.9422215166785484</v>
@@ -28751,7 +28754,7 @@
         <v>0.9595249171276929</v>
       </c>
       <c r="D546" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E546">
         <v>0.9422215166785484</v>
@@ -28801,7 +28804,7 @@
         <v>0.9589976550364385</v>
       </c>
       <c r="D547" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E547">
         <v>0.9422215166785484</v>
@@ -28851,7 +28854,7 @@
         <v>0.8504189521355614</v>
       </c>
       <c r="D548" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E548">
         <v>0.937857691146331</v>
@@ -28901,7 +28904,7 @@
         <v>0.9017680975637474</v>
       </c>
       <c r="D549" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E549">
         <v>0.937857691146331</v>
@@ -28951,7 +28954,7 @@
         <v>0.908653475416529</v>
       </c>
       <c r="D550" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E550">
         <v>0.937857691146331</v>
@@ -29151,7 +29154,7 @@
         <v>0.7994059700977925</v>
       </c>
       <c r="D554" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E554">
         <v>0.9510460107817367</v>
@@ -29201,7 +29204,7 @@
         <v>0.8553475251011551</v>
       </c>
       <c r="D555" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E555">
         <v>0.9510460107817367</v>
@@ -29251,7 +29254,7 @@
         <v>0.8681906234838945</v>
       </c>
       <c r="D556" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E556">
         <v>0.9510460107817367</v>
@@ -29351,7 +29354,7 @@
         <v>0.7963844516425689</v>
       </c>
       <c r="D558" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E558">
         <v>0.9293442447455118</v>
@@ -29401,7 +29404,7 @@
         <v>0.9077462565202601</v>
       </c>
       <c r="D559" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E559">
         <v>0.9293442447455118</v>
@@ -29451,7 +29454,7 @@
         <v>0.8525980168231655</v>
       </c>
       <c r="D560" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E560">
         <v>0.9293442447455118</v>
@@ -29501,7 +29504,7 @@
         <v>0.8657939932736682</v>
       </c>
       <c r="D561" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E561">
         <v>0.9293442447455118</v>
@@ -30601,7 +30604,7 @@
         <v>0.751468861471289</v>
       </c>
       <c r="D583" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E583">
         <v>0.9385035221553486</v>
@@ -30651,7 +30654,7 @@
         <v>0.7709845877750583</v>
       </c>
       <c r="D584" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E584">
         <v>0.9385035221553486</v>
@@ -30701,7 +30704,7 @@
         <v>0.8117259226040443</v>
       </c>
       <c r="D585" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E585">
         <v>0.9385035221553486</v>
@@ -30751,7 +30754,7 @@
         <v>0.830167515424916</v>
       </c>
       <c r="D586" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E586">
         <v>0.9385035221553486</v>
@@ -30801,7 +30804,7 @@
         <v>0.8384277846341899</v>
       </c>
       <c r="D587" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E587">
         <v>0.9385035221553486</v>
@@ -31201,7 +31204,7 @@
         <v>0.8616555364163685</v>
       </c>
       <c r="D595" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E595">
         <v>0.9487042537756789</v>
@@ -31251,7 +31254,7 @@
         <v>0.8685708400378545</v>
       </c>
       <c r="D596" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E596">
         <v>0.9487042537756789</v>
@@ -31301,7 +31304,7 @@
         <v>0.9283666743289771</v>
       </c>
       <c r="D597" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E597">
         <v>0.9487042537756789</v>
@@ -31351,7 +31354,7 @@
         <v>0.9119931158630705</v>
       </c>
       <c r="D598" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E598">
         <v>0.9487042537756789</v>
@@ -31401,7 +31404,7 @@
         <v>0.917566191902035</v>
       </c>
       <c r="D599" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E599">
         <v>0.9487042537756789</v>
@@ -31451,7 +31454,7 @@
         <v>0.8850151504748149</v>
       </c>
       <c r="D600" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E600">
         <v>0.9487042537756789</v>
@@ -31501,7 +31504,7 @@
         <v>0.9303840608049012</v>
       </c>
       <c r="D601" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E601">
         <v>0.9487042537756789</v>
@@ -31551,7 +31554,7 @@
         <v>0.9319931158630701</v>
       </c>
       <c r="D602" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E602">
         <v>0.9487042537756789</v>
@@ -31637,7 +31640,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31687,7 +31690,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31737,7 +31740,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -31787,7 +31790,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31837,7 +31840,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31887,7 +31890,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -31937,7 +31940,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -31987,7 +31990,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32037,7 +32040,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32087,7 +32090,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32137,7 +32140,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32187,7 +32190,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32237,7 +32240,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32287,7 +32290,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32337,7 +32340,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -33401,7 +33404,7 @@
         <v>0.9426739735459577</v>
       </c>
       <c r="D639" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E639">
         <v>1.155481591635229</v>
@@ -33451,7 +33454,7 @@
         <v>0.9523699059372155</v>
       </c>
       <c r="D640" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E640">
         <v>0.9617333668754942</v>
@@ -33501,7 +33504,7 @@
         <v>0.9489115468641032</v>
       </c>
       <c r="D641" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E641">
         <v>0.9617333668754942</v>
@@ -33551,7 +33554,7 @@
         <v>0.994540984964766</v>
       </c>
       <c r="D642" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E642">
         <v>0.9617333668754942</v>
@@ -33601,7 +33604,7 @@
         <v>0.9895196820815877</v>
       </c>
       <c r="D643" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E643">
         <v>0.9617333668754942</v>
@@ -33651,7 +33654,7 @@
         <v>0.9598379516124478</v>
       </c>
       <c r="D644" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E644">
         <v>0.9617333668754942</v>
@@ -33701,7 +33704,7 @@
         <v>1.006089726852713</v>
       </c>
       <c r="D645" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E645">
         <v>0.9617333668754942</v>
@@ -33751,7 +33754,7 @@
         <v>0.9848592544956265</v>
       </c>
       <c r="D646" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E646">
         <v>0.9617333668754942</v>
@@ -34051,7 +34054,7 @@
         <v>0.9734565125913943</v>
       </c>
       <c r="D652" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E652">
         <v>1.185400334942146</v>
@@ -34101,7 +34104,7 @@
         <v>0.9846444558037319</v>
       </c>
       <c r="D653" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E653">
         <v>1.181231801994401</v>
@@ -34151,7 +34154,7 @@
         <v>0.9774953331205798</v>
       </c>
       <c r="D654" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E654">
         <v>1.181231801994401</v>
@@ -34201,7 +34204,7 @@
         <v>1.023910040074443</v>
       </c>
       <c r="D655" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E655">
         <v>1.181231801994401</v>
@@ -34251,7 +34254,7 @@
         <v>1.015119446695905</v>
       </c>
       <c r="D656" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E656">
         <v>1.181231801994401</v>
@@ -34301,7 +34304,7 @@
         <v>0.9864585657359251</v>
       </c>
       <c r="D657" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E657">
         <v>1.181231801994401</v>
@@ -34351,7 +34354,7 @@
         <v>1.007646508948263</v>
       </c>
       <c r="D658" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E658">
         <v>1.181231801994401</v>
@@ -34401,7 +34404,7 @@
         <v>1.015249159114463</v>
       </c>
       <c r="D659" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E659">
         <v>0.9834565125913941</v>
@@ -34701,7 +34704,7 @@
         <v>0.9989502799212269</v>
       </c>
       <c r="D665" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E665">
         <v>1.210178715943846</v>
@@ -34751,7 +34754,7 @@
         <v>1.011373890427612</v>
       </c>
       <c r="D666" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E666">
         <v>1.203864024011701</v>
@@ -34801,7 +34804,7 @@
         <v>1.00116811706971</v>
       </c>
       <c r="D667" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E667">
         <v>1.203864024011701</v>
@@ -34851,7 +34854,7 @@
         <v>1.048233175230966</v>
       </c>
       <c r="D668" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E668">
         <v>1.203864024011701</v>
@@ -34901,7 +34904,7 @@
         <v>1.036320896056939</v>
       </c>
       <c r="D669" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E669">
         <v>1.203864024011701</v>
@@ -34951,7 +34954,7 @@
         <v>1.008505471666571</v>
       </c>
       <c r="D670" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E670">
         <v>1.203864024011701</v>
@@ -35001,7 +35004,7 @@
         <v>1.030929082172957</v>
       </c>
       <c r="D671" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E671">
         <v>1.203864024011701</v>
@@ -35051,7 +35054,7 @@
         <v>1.040417750840599</v>
       </c>
       <c r="D672" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E672">
         <v>0.9957763031857296</v>
@@ -35137,7 +35140,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35187,7 +35190,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35237,7 +35240,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35287,7 +35290,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35301,7 +35304,7 @@
         <v>1.019721542843001</v>
       </c>
       <c r="D677" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E677">
         <v>1.230367111793835</v>
@@ -35337,7 +35340,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35351,7 +35354,7 @@
         <v>1.033151923746106</v>
       </c>
       <c r="D678" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E678">
         <v>1.222303818646338</v>
@@ -35387,7 +35390,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35401,7 +35404,7 @@
         <v>1.020455718354215</v>
       </c>
       <c r="D679" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E679">
         <v>1.222303818646338</v>
@@ -35437,7 +35440,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35451,7 +35454,7 @@
         <v>1.053594956548007</v>
       </c>
       <c r="D680" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E680">
         <v>1.222303818646338</v>
@@ -35487,7 +35490,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35501,7 +35504,7 @@
         <v>1.026468375060656</v>
       </c>
       <c r="D681" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E681">
         <v>1.222303818646338</v>
@@ -35537,7 +35540,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35551,7 +35554,7 @@
         <v>1.049898755963761</v>
       </c>
       <c r="D682" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E682">
         <v>1.222303818646338</v>
@@ -35587,7 +35590,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35601,7 +35604,7 @@
         <v>1.060924074184289</v>
       </c>
       <c r="D683" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E683">
         <v>1.017873442550878</v>
@@ -35637,7 +35640,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35851,7 +35854,7 @@
         <v>1.047332978384417</v>
       </c>
       <c r="D688" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E688">
         <v>1.257203736644038</v>
@@ -35901,7 +35904,7 @@
         <v>1.062101668663253</v>
       </c>
       <c r="D689" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E689">
         <v>1.2468160114229</v>
@@ -35951,7 +35954,7 @@
         <v>1.046094908499815</v>
       </c>
       <c r="D690" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E690">
         <v>1.2468160114229</v>
@@ -36001,7 +36004,7 @@
         <v>1.076557527942143</v>
       </c>
       <c r="D691" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E691">
         <v>1.2468160114229</v>
@@ -36051,7 +36054,7 @@
         <v>1.050346631817136</v>
       </c>
       <c r="D692" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E692">
         <v>1.2468160114229</v>
@@ -36101,7 +36104,7 @@
         <v>1.075115322095972</v>
       </c>
       <c r="D693" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E693">
         <v>1.2468160114229</v>
@@ -36151,7 +36154,7 @@
         <v>1.043673116249803</v>
       </c>
       <c r="D694" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E694">
         <v>1.123802357990182</v>
@@ -36201,7 +36204,7 @@
         <v>3.139280458423625</v>
       </c>
       <c r="D695" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E695">
         <v>3.025106410332782</v>
@@ -36237,7 +36240,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36251,7 +36254,7 @@
         <v>3.093454506514468</v>
       </c>
       <c r="D696" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E696">
         <v>3.025106410332782</v>
@@ -36287,7 +36290,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36301,7 +36304,7 @@
         <v>3.013365929424353</v>
       </c>
       <c r="D697" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E697">
         <v>3.025106410332782</v>
@@ -36337,7 +36340,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36351,7 +36354,7 @@
         <v>3.208498795059524</v>
       </c>
       <c r="D698" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E698">
         <v>3.025106410332782</v>
@@ -36387,7 +36390,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36398,10 +36401,10 @@
         <v>145</v>
       </c>
       <c r="C699">
-        <v>-0.8715193570106505</v>
+        <v>-0.836346559131746</v>
       </c>
       <c r="D699" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E699">
         <v>-0.4468731812388809</v>
@@ -36410,22 +36413,22 @@
         <v>1</v>
       </c>
       <c r="G699">
-        <v>0.01181151935701065</v>
+        <v>0.01247634655913175</v>
       </c>
       <c r="H699">
         <v>0.01094687318123888</v>
       </c>
       <c r="I699">
-        <v>0.4246461757717697</v>
+        <v>0.3894733778928652</v>
       </c>
       <c r="J699">
         <v>1.4991771529576</v>
       </c>
       <c r="K699">
-        <v>4.23</v>
+        <v>4.44</v>
       </c>
       <c r="L699">
-        <v>5.47</v>
+        <v>5.82</v>
       </c>
       <c r="M699">
         <v>3.8</v>
@@ -36448,10 +36451,10 @@
         <v>146</v>
       </c>
       <c r="C700">
-        <v>-0.8416839264191296</v>
+        <v>-0.8715193570106505</v>
       </c>
       <c r="D700" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E700">
         <v>-0.4468731812388809</v>
@@ -36460,22 +36463,22 @@
         <v>1</v>
       </c>
       <c r="G700">
-        <v>0.01124168392641913</v>
+        <v>0.01181151935701065</v>
       </c>
       <c r="H700">
         <v>0.01094687318123888</v>
       </c>
       <c r="I700">
-        <v>0.3948107451802487</v>
+        <v>0.4246461757717697</v>
       </c>
       <c r="J700">
         <v>1.4991771529576</v>
       </c>
       <c r="K700">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="L700">
-        <v>5.2</v>
+        <v>5.47</v>
       </c>
       <c r="M700">
         <v>3.8</v>
@@ -36501,10 +36504,10 @@
         <v>-0.1116839264191301</v>
       </c>
       <c r="D701" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E701">
-        <v>-0.1265604993627694</v>
+        <v>0.03838190134426256</v>
       </c>
       <c r="F701">
         <v>-1</v>
@@ -36513,10 +36516,10 @@
         <v>0.01197168392641913</v>
       </c>
       <c r="H701">
-        <v>0.01240656049936277</v>
+        <v>0.01236161809865574</v>
       </c>
       <c r="I701">
-        <v>0.01487657294363931</v>
+        <v>-0.1500658277633926</v>
       </c>
       <c r="J701">
         <v>1.4991771529576</v>
@@ -36528,10 +36531,10 @@
         <v>5.93</v>
       </c>
       <c r="M701">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="N701">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="O701">
         <v>1</v>
@@ -36545,13 +36548,13 @@
         <v>0</v>
       </c>
       <c r="B702" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C702">
         <v>-0.8653702238384202</v>
       </c>
       <c r="D702" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E702">
         <v>-0.4717132546364855</v>
@@ -36595,13 +36598,13 @@
         <v>1</v>
       </c>
       <c r="B703" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C703">
         <v>-0.8991702808190363</v>
       </c>
       <c r="D703" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E703">
         <v>-0.4717132546364855</v>
@@ -36645,28 +36648,28 @@
         <v>2</v>
       </c>
       <c r="B704" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C704">
-        <v>-0.8680274779434312</v>
+        <v>-0.1380274779434316</v>
       </c>
       <c r="D704" t="s">
         <v>259</v>
       </c>
       <c r="E704">
-        <v>-0.4717132546364855</v>
+        <v>0.01151540090632697</v>
       </c>
       <c r="F704">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G704">
-        <v>0.01126802747794343</v>
+        <v>0.01199802747794343</v>
       </c>
       <c r="H704">
-        <v>0.01097171325463649</v>
+        <v>0.01238848459909367</v>
       </c>
       <c r="I704">
-        <v>0.3963142233069457</v>
+        <v>-0.1495428788497586</v>
       </c>
       <c r="J704">
         <v>1.505714014378023</v>
@@ -36675,13 +36678,13 @@
         <v>4.03</v>
       </c>
       <c r="L704">
-        <v>5.2</v>
+        <v>5.93</v>
       </c>
       <c r="M704">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="N704">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="O704">
         <v>1</v>
@@ -36692,66 +36695,66 @@
     </row>
     <row r="705" spans="1:16">
       <c r="A705" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B705" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C705">
-        <v>-0.1380274779434316</v>
+        <v>-0.9016808854046587</v>
       </c>
       <c r="D705" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E705">
-        <v>-0.1538845801001338</v>
+        <v>-0.5027899469679502</v>
       </c>
       <c r="F705">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G705">
-        <v>0.01199802747794343</v>
+        <v>0.01254168088540466</v>
       </c>
       <c r="H705">
-        <v>0.01243388458010013</v>
+        <v>0.01100278994696795</v>
       </c>
       <c r="I705">
-        <v>0.01585710215670222</v>
+        <v>0.3988909384367085</v>
       </c>
       <c r="J705">
-        <v>1.505714014378023</v>
+        <v>1.513892091307355</v>
       </c>
       <c r="K705">
-        <v>4.03</v>
+        <v>4.44</v>
       </c>
       <c r="L705">
-        <v>5.93</v>
+        <v>5.82</v>
       </c>
       <c r="M705">
-        <v>4.18</v>
+        <v>3.8</v>
       </c>
       <c r="N705">
-        <v>6.14</v>
+        <v>5.25</v>
       </c>
       <c r="O705">
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="706" spans="1:16">
       <c r="A706" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B706" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C706">
-        <v>-0.9016808854046587</v>
+        <v>-0.9337635462301144</v>
       </c>
       <c r="D706" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E706">
         <v>-0.5027899469679502</v>
@@ -36760,22 +36763,22 @@
         <v>1</v>
       </c>
       <c r="G706">
-        <v>0.01254168088540466</v>
+        <v>0.01187376354623011</v>
       </c>
       <c r="H706">
         <v>0.01100278994696795</v>
       </c>
       <c r="I706">
-        <v>0.3988909384367085</v>
+        <v>0.4309735992621642</v>
       </c>
       <c r="J706">
         <v>1.513892091307355</v>
       </c>
       <c r="K706">
-        <v>4.44</v>
+        <v>4.23</v>
       </c>
       <c r="L706">
-        <v>5.82</v>
+        <v>5.47</v>
       </c>
       <c r="M706">
         <v>3.8</v>
@@ -36792,46 +36795,46 @@
     </row>
     <row r="707" spans="1:16">
       <c r="A707" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B707" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C707">
-        <v>-0.9337635462301144</v>
+        <v>-0.1709851279686436</v>
       </c>
       <c r="D707" t="s">
         <v>259</v>
       </c>
       <c r="E707">
-        <v>-0.5027899469679502</v>
+        <v>-0.02209649527323165</v>
       </c>
       <c r="F707">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G707">
-        <v>0.01187376354623011</v>
+        <v>0.01203098512796864</v>
       </c>
       <c r="H707">
-        <v>0.01100278994696795</v>
+        <v>0.01242209649527323</v>
       </c>
       <c r="I707">
-        <v>0.4309735992621642</v>
+        <v>-0.148888632695412</v>
       </c>
       <c r="J707">
         <v>1.513892091307355</v>
       </c>
       <c r="K707">
-        <v>4.23</v>
+        <v>4.03</v>
       </c>
       <c r="L707">
-        <v>5.47</v>
+        <v>5.93</v>
       </c>
       <c r="M707">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="N707">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="O707">
         <v>1</v>
@@ -36842,66 +36845,66 @@
     </row>
     <row r="708" spans="1:16">
       <c r="A708" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B708" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C708">
-        <v>-0.1709851279686436</v>
+        <v>-0.9377349898599103</v>
       </c>
       <c r="D708" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E708">
-        <v>-0.1880689416647456</v>
+        <v>-0.5336470633936168</v>
       </c>
       <c r="F708">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G708">
-        <v>0.01203098512796864</v>
+        <v>0.01257773498985991</v>
       </c>
       <c r="H708">
-        <v>0.01246806894166474</v>
+        <v>0.01103364706339362</v>
       </c>
       <c r="I708">
-        <v>0.01708381369610201</v>
+        <v>0.4040879264662935</v>
       </c>
       <c r="J708">
-        <v>1.513892091307355</v>
+        <v>1.522012385103583</v>
       </c>
       <c r="K708">
-        <v>4.03</v>
+        <v>4.44</v>
       </c>
       <c r="L708">
-        <v>5.93</v>
+        <v>5.82</v>
       </c>
       <c r="M708">
-        <v>4.18</v>
+        <v>3.8</v>
       </c>
       <c r="N708">
-        <v>6.14</v>
+        <v>5.25</v>
       </c>
       <c r="O708">
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="709" spans="1:16">
       <c r="A709" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B709" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C709">
-        <v>-0.9377349898599103</v>
+        <v>-0.9681123889881587</v>
       </c>
       <c r="D709" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E709">
         <v>-0.5336470633936168</v>
@@ -36910,22 +36913,22 @@
         <v>1</v>
       </c>
       <c r="G709">
-        <v>0.01257773498985991</v>
+        <v>0.01190811238898816</v>
       </c>
       <c r="H709">
         <v>0.01103364706339362</v>
       </c>
       <c r="I709">
-        <v>0.4040879264662935</v>
+        <v>0.4344653255945419</v>
       </c>
       <c r="J709">
         <v>1.522012385103583</v>
       </c>
       <c r="K709">
-        <v>4.44</v>
+        <v>4.23</v>
       </c>
       <c r="L709">
-        <v>5.82</v>
+        <v>5.47</v>
       </c>
       <c r="M709">
         <v>3.8</v>
@@ -36942,46 +36945,46 @@
     </row>
     <row r="710" spans="1:16">
       <c r="A710" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B710" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C710">
-        <v>-0.9681123889881587</v>
+        <v>-0.2037099119674419</v>
       </c>
       <c r="D710" t="s">
         <v>259</v>
       </c>
       <c r="E710">
-        <v>-0.5336470633936168</v>
+        <v>-0.05547090277572764</v>
       </c>
       <c r="F710">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G710">
-        <v>0.01190811238898816</v>
+        <v>0.01206370991196744</v>
       </c>
       <c r="H710">
-        <v>0.01103364706339362</v>
+        <v>0.01245547090277573</v>
       </c>
       <c r="I710">
-        <v>0.4344653255945419</v>
+        <v>-0.1482390091917143</v>
       </c>
       <c r="J710">
         <v>1.522012385103583</v>
       </c>
       <c r="K710">
-        <v>4.23</v>
+        <v>4.03</v>
       </c>
       <c r="L710">
-        <v>5.47</v>
+        <v>5.93</v>
       </c>
       <c r="M710">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="N710">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="O710">
         <v>1</v>
@@ -36992,66 +36995,66 @@
     </row>
     <row r="711" spans="1:16">
       <c r="A711" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B711" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C711">
-        <v>-0.2037099119674419</v>
+        <v>-0.9721715677020031</v>
       </c>
       <c r="D711" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E711">
-        <v>-0.2220117697329789</v>
+        <v>-0.5631198101954071</v>
       </c>
       <c r="F711">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G711">
-        <v>0.01206370991196744</v>
+        <v>0.012612171567702</v>
       </c>
       <c r="H711">
-        <v>0.01250201176973298</v>
+        <v>0.01106311981019541</v>
       </c>
       <c r="I711">
-        <v>0.01830185776553694</v>
+        <v>0.4090517575065959</v>
       </c>
       <c r="J711">
-        <v>1.522012385103583</v>
+        <v>1.529768371104055</v>
       </c>
       <c r="K711">
-        <v>4.03</v>
+        <v>4.44</v>
       </c>
       <c r="L711">
-        <v>5.93</v>
+        <v>5.82</v>
       </c>
       <c r="M711">
-        <v>4.18</v>
+        <v>3.8</v>
       </c>
       <c r="N711">
-        <v>6.14</v>
+        <v>5.25</v>
       </c>
       <c r="O711">
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="712" spans="1:16">
       <c r="A712" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B712" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C712">
-        <v>-0.9721715677020031</v>
+        <v>-1.000920209770152</v>
       </c>
       <c r="D712" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E712">
         <v>-0.5631198101954071</v>
@@ -37060,22 +37063,22 @@
         <v>1</v>
       </c>
       <c r="G712">
-        <v>0.012612171567702</v>
+        <v>0.01194092020977015</v>
       </c>
       <c r="H712">
         <v>0.01106311981019541</v>
       </c>
       <c r="I712">
-        <v>0.4090517575065959</v>
+        <v>0.437800399574745</v>
       </c>
       <c r="J712">
         <v>1.529768371104055</v>
       </c>
       <c r="K712">
-        <v>4.44</v>
+        <v>4.23</v>
       </c>
       <c r="L712">
-        <v>5.82</v>
+        <v>5.47</v>
       </c>
       <c r="M712">
         <v>3.8</v>
@@ -37092,46 +37095,46 @@
     </row>
     <row r="713" spans="1:16">
       <c r="A713" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B713" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C713">
-        <v>-1.000920209770152</v>
+        <v>-0.2349665355493409</v>
       </c>
       <c r="D713" t="s">
         <v>259</v>
       </c>
       <c r="E713">
-        <v>-0.5631198101954071</v>
+        <v>-0.08734800523766495</v>
       </c>
       <c r="F713">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G713">
-        <v>0.01194092020977015</v>
+        <v>0.01209496653554934</v>
       </c>
       <c r="H713">
-        <v>0.01106311981019541</v>
+        <v>0.01248734800523767</v>
       </c>
       <c r="I713">
-        <v>0.437800399574745</v>
+        <v>-0.1476185303116759</v>
       </c>
       <c r="J713">
         <v>1.529768371104055</v>
       </c>
       <c r="K713">
-        <v>4.23</v>
+        <v>4.03</v>
       </c>
       <c r="L713">
-        <v>5.47</v>
+        <v>5.93</v>
       </c>
       <c r="M713">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="N713">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="O713">
         <v>1</v>
@@ -37142,166 +37145,166 @@
     </row>
     <row r="714" spans="1:16">
       <c r="A714" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B714" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C714">
-        <v>-0.2349665355493409</v>
+        <v>-1.029266735877098</v>
       </c>
       <c r="D714" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E714">
-        <v>-0.2544317912149481</v>
+        <v>-0.5885847745468009</v>
       </c>
       <c r="F714">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G714">
-        <v>0.01209496653554934</v>
+        <v>0.0119692667358771</v>
       </c>
       <c r="H714">
-        <v>0.01253443179121495</v>
+        <v>0.0110885847745468</v>
       </c>
       <c r="I714">
-        <v>0.0194652556656072</v>
+        <v>0.4406819613302968</v>
       </c>
       <c r="J714">
-        <v>1.529768371104055</v>
+        <v>1.536469677512316</v>
       </c>
       <c r="K714">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="L714">
-        <v>5.93</v>
+        <v>5.47</v>
       </c>
       <c r="M714">
-        <v>4.18</v>
+        <v>3.8</v>
       </c>
       <c r="N714">
-        <v>6.14</v>
+        <v>5.25</v>
       </c>
       <c r="O714">
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>360</v>
+        <v>145</v>
       </c>
     </row>
     <row r="715" spans="1:16">
       <c r="A715" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B715" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C715">
-        <v>-1.029266735877098</v>
+        <v>-0.2619728003746342</v>
       </c>
       <c r="D715" t="s">
         <v>259</v>
       </c>
       <c r="E715">
-        <v>-0.5885847745468009</v>
+        <v>-0.1148903745756193</v>
       </c>
       <c r="F715">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G715">
-        <v>0.0119692667358771</v>
+        <v>0.01212197280037463</v>
       </c>
       <c r="H715">
-        <v>0.0110885847745468</v>
+        <v>0.01251489037457562</v>
       </c>
       <c r="I715">
-        <v>0.4406819613302968</v>
+        <v>-0.1470824257990149</v>
       </c>
       <c r="J715">
         <v>1.536469677512316</v>
       </c>
       <c r="K715">
-        <v>4.23</v>
+        <v>4.03</v>
       </c>
       <c r="L715">
-        <v>5.47</v>
+        <v>5.93</v>
       </c>
       <c r="M715">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="N715">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="O715">
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="716" spans="1:16">
       <c r="A716" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B716" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C716">
-        <v>-0.2619728003746342</v>
+        <v>-1.070041708072165</v>
       </c>
       <c r="D716" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E716">
-        <v>-0.2824432520014808</v>
+        <v>-0.6252147732090361</v>
       </c>
       <c r="F716">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G716">
-        <v>0.01212197280037463</v>
+        <v>0.01201004170807217</v>
       </c>
       <c r="H716">
-        <v>0.01256244325200148</v>
+        <v>0.01112521477320904</v>
       </c>
       <c r="I716">
-        <v>0.02047045162684658</v>
+        <v>0.4448269348631291</v>
       </c>
       <c r="J716">
-        <v>1.536469677512316</v>
+        <v>1.546109150844483</v>
       </c>
       <c r="K716">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="L716">
-        <v>5.93</v>
+        <v>5.47</v>
       </c>
       <c r="M716">
-        <v>4.18</v>
+        <v>3.8</v>
       </c>
       <c r="N716">
-        <v>6.14</v>
+        <v>5.25</v>
       </c>
       <c r="O716">
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>148</v>
+        <v>361</v>
       </c>
     </row>
     <row r="717" spans="1:16">
       <c r="A717" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B717" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C717">
-        <v>-1.070041708072165</v>
+        <v>-0.9644366033779335</v>
       </c>
       <c r="D717" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E717">
         <v>-0.6252147732090361</v>
@@ -37310,22 +37313,22 @@
         <v>1</v>
       </c>
       <c r="G717">
-        <v>0.01201004170807217</v>
+        <v>0.01140443660337793</v>
       </c>
       <c r="H717">
         <v>0.01112521477320904</v>
       </c>
       <c r="I717">
-        <v>0.4448269348631291</v>
+        <v>0.3392218301688974</v>
       </c>
       <c r="J717">
         <v>1.546109150844483</v>
       </c>
       <c r="K717">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="L717">
-        <v>5.47</v>
+        <v>5.22</v>
       </c>
       <c r="M717">
         <v>3.8</v>
@@ -37342,7 +37345,7 @@
     </row>
     <row r="718" spans="1:16">
       <c r="A718" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B718" t="s">
         <v>147</v>
@@ -37351,10 +37354,10 @@
         <v>-0.300819877903268</v>
       </c>
       <c r="D718" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E718">
-        <v>-0.3227362505299398</v>
+        <v>-0.1545086099708266</v>
       </c>
       <c r="F718">
         <v>-1</v>
@@ -37363,10 +37366,10 @@
         <v>0.01216081987790327</v>
       </c>
       <c r="H718">
-        <v>0.01260273625052994</v>
+        <v>0.01255450860997083</v>
       </c>
       <c r="I718">
-        <v>0.02191637262667179</v>
+        <v>-0.1463112679324414</v>
       </c>
       <c r="J718">
         <v>1.546109150844483</v>
@@ -37378,10 +37381,10 @@
         <v>5.93</v>
       </c>
       <c r="M718">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="N718">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="O718">
         <v>1</v>
@@ -37395,13 +37398,13 @@
         <v>0</v>
       </c>
       <c r="B719" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C719">
         <v>-1.104955489525656</v>
       </c>
       <c r="D719" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E719">
         <v>-0.6565793995738742</v>
@@ -37445,43 +37448,43 @@
         <v>1</v>
       </c>
       <c r="B720" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C720">
-        <v>-0.3340828895480827</v>
+        <v>-0.9974519995514468</v>
       </c>
       <c r="D720" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E720">
-        <v>-0.3572373395312614</v>
+        <v>-0.6565793995738742</v>
       </c>
       <c r="F720">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G720">
-        <v>0.01219408288954808</v>
+        <v>0.01143745199955145</v>
       </c>
       <c r="H720">
-        <v>0.01263723733953126</v>
+        <v>0.01115657939957388</v>
       </c>
       <c r="I720">
-        <v>0.02315444998317862</v>
+        <v>0.3408725999775726</v>
       </c>
       <c r="J720">
         <v>1.554362999887862</v>
       </c>
       <c r="K720">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="L720">
-        <v>5.93</v>
+        <v>5.22</v>
       </c>
       <c r="M720">
-        <v>4.18</v>
+        <v>3.8</v>
       </c>
       <c r="N720">
-        <v>6.14</v>
+        <v>5.25</v>
       </c>
       <c r="O720">
         <v>1</v>
@@ -37492,96 +37495,96 @@
     </row>
     <row r="721" spans="1:16">
       <c r="A721" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B721" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C721">
-        <v>-1.146046740420904</v>
+        <v>-0.3340828895480827</v>
       </c>
       <c r="D721" t="s">
         <v>259</v>
       </c>
       <c r="E721">
-        <v>-0.6934935256736248</v>
+        <v>-0.1884319295391119</v>
       </c>
       <c r="F721">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G721">
-        <v>0.0120860467404209</v>
+        <v>0.01219408288954808</v>
       </c>
       <c r="H721">
-        <v>0.01119349352567362</v>
+        <v>0.01258843192953911</v>
       </c>
       <c r="I721">
-        <v>0.4525532147472795</v>
+        <v>-0.1456509600089708</v>
       </c>
       <c r="J721">
-        <v>1.564077243598322</v>
+        <v>1.554362999887862</v>
       </c>
       <c r="K721">
-        <v>4.23</v>
+        <v>4.03</v>
       </c>
       <c r="L721">
-        <v>5.47</v>
+        <v>5.93</v>
       </c>
       <c r="M721">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="N721">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="O721">
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="722" spans="1:16">
       <c r="A722" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B722" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C722">
-        <v>-0.3732312917012397</v>
+        <v>-1.146046740420904</v>
       </c>
       <c r="D722" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E722">
-        <v>-0.3978428782409873</v>
+        <v>-0.6934935256736248</v>
       </c>
       <c r="F722">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G722">
-        <v>0.01223323129170124</v>
+        <v>0.0120860467404209</v>
       </c>
       <c r="H722">
-        <v>0.01267784287824099</v>
+        <v>0.01119349352567362</v>
       </c>
       <c r="I722">
-        <v>0.0246115865397476</v>
+        <v>0.4525532147472795</v>
       </c>
       <c r="J722">
         <v>1.564077243598322</v>
       </c>
       <c r="K722">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="L722">
-        <v>5.93</v>
+        <v>5.47</v>
       </c>
       <c r="M722">
-        <v>4.18</v>
+        <v>3.8</v>
       </c>
       <c r="N722">
-        <v>6.14</v>
+        <v>5.25</v>
       </c>
       <c r="O722">
         <v>1</v>
@@ -37592,66 +37595,66 @@
     </row>
     <row r="723" spans="1:16">
       <c r="A723" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B723" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C723">
-        <v>-1.194222080991625</v>
+        <v>-0.3732312917012397</v>
       </c>
       <c r="D723" t="s">
         <v>259</v>
       </c>
       <c r="E723">
-        <v>-0.7367716094014582</v>
+        <v>-0.2283574711891054</v>
       </c>
       <c r="F723">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G723">
-        <v>0.01213422208099162</v>
+        <v>0.01223323129170124</v>
       </c>
       <c r="H723">
-        <v>0.01123677160940146</v>
+        <v>0.0126283574711891</v>
       </c>
       <c r="I723">
-        <v>0.4574504715901666</v>
+        <v>-0.1448738205121343</v>
       </c>
       <c r="J723">
-        <v>1.575466213000384</v>
+        <v>1.564077243598322</v>
       </c>
       <c r="K723">
-        <v>4.23</v>
+        <v>4.03</v>
       </c>
       <c r="L723">
-        <v>5.47</v>
+        <v>5.93</v>
       </c>
       <c r="M723">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="N723">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="O723">
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="724" spans="1:16">
       <c r="A724" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B724" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C724">
-        <v>-1.081864852001535</v>
+        <v>-1.194222080991625</v>
       </c>
       <c r="D724" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E724">
         <v>-0.7367716094014582</v>
@@ -37660,22 +37663,22 @@
         <v>1</v>
       </c>
       <c r="G724">
-        <v>0.01152186485200154</v>
+        <v>0.01213422208099162</v>
       </c>
       <c r="H724">
         <v>0.01123677160940146</v>
       </c>
       <c r="I724">
-        <v>0.3450932426000772</v>
+        <v>0.4574504715901666</v>
       </c>
       <c r="J724">
         <v>1.575466213000384</v>
       </c>
       <c r="K724">
-        <v>4</v>
+        <v>4.23</v>
       </c>
       <c r="L724">
-        <v>5.22</v>
+        <v>5.47</v>
       </c>
       <c r="M724">
         <v>3.8</v>
@@ -37692,46 +37695,46 @@
     </row>
     <row r="725" spans="1:16">
       <c r="A725" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B725" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C725">
-        <v>-0.419128838391547</v>
+        <v>-0.4032780265516687</v>
       </c>
       <c r="D725" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E725">
-        <v>-0.4454487703416046</v>
+        <v>-0.2751661354315775</v>
       </c>
       <c r="F725">
         <v>-1</v>
       </c>
       <c r="G725">
-        <v>0.01227912883839155</v>
+        <v>0.01330327802655167</v>
       </c>
       <c r="H725">
-        <v>0.01272544877034161</v>
+        <v>0.01267516613543158</v>
       </c>
       <c r="I725">
-        <v>0.02631993195005755</v>
+        <v>-0.1281118911200911</v>
       </c>
       <c r="J725">
         <v>1.575466213000384</v>
       </c>
       <c r="K725">
-        <v>4.03</v>
+        <v>4.35</v>
       </c>
       <c r="L725">
-        <v>5.93</v>
+        <v>6.45</v>
       </c>
       <c r="M725">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="N725">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="O725">
         <v>1</v>
@@ -37748,96 +37751,96 @@
         <v>149</v>
       </c>
       <c r="C726">
-        <v>-1.12689473003791</v>
+        <v>-0.4522480189162259</v>
       </c>
       <c r="D726" t="s">
         <v>259</v>
       </c>
       <c r="E726">
-        <v>-0.7795499935360137</v>
+        <v>-0.3214343351139526</v>
       </c>
       <c r="F726">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G726">
-        <v>0.01156689473003791</v>
+        <v>0.01335224801891623</v>
       </c>
       <c r="H726">
-        <v>0.01127954999353601</v>
+        <v>0.01272143433511395</v>
       </c>
       <c r="I726">
-        <v>0.3473447365018965</v>
+        <v>-0.1308136838022733</v>
       </c>
       <c r="J726">
         <v>1.586723682509477</v>
       </c>
       <c r="K726">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="L726">
-        <v>5.22</v>
+        <v>6.45</v>
       </c>
       <c r="M726">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="N726">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="O726">
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="727" spans="1:16">
       <c r="A727" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B727" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C727">
-        <v>-0.4644964405131953</v>
+        <v>-0.4887263651278166</v>
       </c>
       <c r="D727" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E727">
-        <v>-0.4925049928896161</v>
+        <v>-0.380581452989464</v>
       </c>
       <c r="F727">
         <v>-1</v>
       </c>
       <c r="G727">
-        <v>0.01232449644051319</v>
+        <v>0.01308872636512782</v>
       </c>
       <c r="H727">
-        <v>0.01277250499288962</v>
+        <v>0.01278058145298946</v>
       </c>
       <c r="I727">
-        <v>0.02800855237642086</v>
+        <v>-0.1081449121383526</v>
       </c>
       <c r="J727">
-        <v>1.586723682509477</v>
+        <v>1.60111470875656</v>
       </c>
       <c r="K727">
-        <v>4.03</v>
+        <v>4.24</v>
       </c>
       <c r="L727">
-        <v>5.93</v>
+        <v>6.3</v>
       </c>
       <c r="M727">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="N727">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="O727">
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>145</v>
+        <v>365</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -37845,93 +37848,93 @@
         <v>0</v>
       </c>
       <c r="B728" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C728">
-        <v>-0.522492276288939</v>
+        <v>-1.176193501756449</v>
       </c>
       <c r="D728" t="s">
         <v>260</v>
       </c>
       <c r="E728">
-        <v>-0.5526594826024223</v>
+        <v>-0.7515751724180992</v>
       </c>
       <c r="F728">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G728">
-        <v>0.01238249227628894</v>
+        <v>0.01187619350175645</v>
       </c>
       <c r="H728">
-        <v>0.01283265948260242</v>
+        <v>0.0113315751724181</v>
       </c>
       <c r="I728">
-        <v>0.03016720631348324</v>
+        <v>0.4246183293383501</v>
       </c>
       <c r="J728">
-        <v>1.60111470875656</v>
+        <v>1.615394431127834</v>
       </c>
       <c r="K728">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="L728">
-        <v>5.93</v>
+        <v>5.35</v>
       </c>
       <c r="M728">
-        <v>4.18</v>
+        <v>3.74</v>
       </c>
       <c r="N728">
-        <v>6.14</v>
+        <v>5.29</v>
       </c>
       <c r="O728">
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="729" spans="1:16">
       <c r="A729" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B729" t="s">
         <v>150</v>
       </c>
       <c r="C729">
-        <v>-1.176193501756449</v>
+        <v>-0.5492723879820165</v>
       </c>
       <c r="D729" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E729">
-        <v>-0.7515751724180992</v>
+        <v>-0.4392711119353976</v>
       </c>
       <c r="F729">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G729">
-        <v>0.01187619350175645</v>
+        <v>0.01314927238798202</v>
       </c>
       <c r="H729">
-        <v>0.0113315751724181</v>
+        <v>0.0128392711119354</v>
       </c>
       <c r="I729">
-        <v>0.4246183293383501</v>
+        <v>-0.1100012760466189</v>
       </c>
       <c r="J729">
         <v>1.615394431127834</v>
       </c>
       <c r="K729">
-        <v>4.04</v>
+        <v>4.24</v>
       </c>
       <c r="L729">
-        <v>5.35</v>
+        <v>6.3</v>
       </c>
       <c r="M729">
-        <v>3.74</v>
+        <v>4.11</v>
       </c>
       <c r="N729">
-        <v>5.29</v>
+        <v>6.2</v>
       </c>
       <c r="O729">
         <v>1</v>
@@ -37942,102 +37945,102 @@
     </row>
     <row r="730" spans="1:16">
       <c r="A730" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B730" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C730">
-        <v>-0.5800395574451711</v>
+        <v>-1.217497277253725</v>
       </c>
       <c r="D730" t="s">
         <v>260</v>
       </c>
       <c r="E730">
-        <v>-0.6123487221143451</v>
+        <v>-0.7898118358734978</v>
       </c>
       <c r="F730">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G730">
-        <v>0.01244003955744517</v>
+        <v>0.01191749727725372</v>
       </c>
       <c r="H730">
-        <v>0.01289234872211435</v>
+        <v>0.0113698118358735</v>
       </c>
       <c r="I730">
-        <v>0.032309164669174</v>
+        <v>0.4276854413802269</v>
       </c>
       <c r="J730">
-        <v>1.615394431127834</v>
+        <v>1.62561813793409</v>
       </c>
       <c r="K730">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="L730">
-        <v>5.93</v>
+        <v>5.35</v>
       </c>
       <c r="M730">
-        <v>4.18</v>
+        <v>3.74</v>
       </c>
       <c r="N730">
-        <v>6.14</v>
+        <v>5.29</v>
       </c>
       <c r="O730">
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="731" spans="1:16">
       <c r="A731" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B731" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C731">
-        <v>-0.5769657754060766</v>
+        <v>-0.5839018117372472</v>
       </c>
       <c r="D731" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E731">
-        <v>-0.6123487221143451</v>
+        <v>-0.4812905469091113</v>
       </c>
       <c r="F731">
         <v>-1</v>
       </c>
       <c r="G731">
-        <v>0.01347696577540608</v>
+        <v>0.01336390181173725</v>
       </c>
       <c r="H731">
-        <v>0.01289234872211435</v>
+        <v>0.01288129054690911</v>
       </c>
       <c r="I731">
-        <v>0.03538294670826847</v>
+        <v>-0.1026112648281359</v>
       </c>
       <c r="J731">
-        <v>1.615394431127834</v>
+        <v>1.62561813793409</v>
       </c>
       <c r="K731">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="L731">
-        <v>6.45</v>
+        <v>6.39</v>
       </c>
       <c r="M731">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="N731">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="O731">
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38045,31 +38048,31 @@
         <v>0</v>
       </c>
       <c r="B732" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C732">
-        <v>-1.217497277253725</v>
+        <v>-1.265907451690905</v>
       </c>
       <c r="D732" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E732">
-        <v>-0.7898118358734978</v>
+        <v>-0.8346271953772231</v>
       </c>
       <c r="F732">
         <v>1</v>
       </c>
       <c r="G732">
-        <v>0.01191749727725372</v>
+        <v>0.0119659074516909</v>
       </c>
       <c r="H732">
-        <v>0.0113698118358735</v>
+        <v>0.01141462719537722</v>
       </c>
       <c r="I732">
-        <v>0.4276854413802269</v>
+        <v>0.4312802563136815</v>
       </c>
       <c r="J732">
-        <v>1.62561813793409</v>
+        <v>1.637600854378937</v>
       </c>
       <c r="K732">
         <v>4.04</v>
@@ -38087,7 +38090,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>146</v>
+        <v>368</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38095,49 +38098,49 @@
         <v>1</v>
       </c>
       <c r="B733" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C733">
-        <v>-0.5926209048405431</v>
+        <v>-0.5861796396542704</v>
       </c>
       <c r="D733" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E733">
-        <v>-0.6550838165644963</v>
+        <v>-0.5305395114974303</v>
       </c>
       <c r="F733">
         <v>-1</v>
       </c>
       <c r="G733">
-        <v>0.01319262090484054</v>
+        <v>0.01336617963965427</v>
       </c>
       <c r="H733">
-        <v>0.0129350838165645</v>
+        <v>0.01293053951149743</v>
       </c>
       <c r="I733">
-        <v>0.06246291172395324</v>
+        <v>-0.05564012815684016</v>
       </c>
       <c r="J733">
-        <v>1.62561813793409</v>
+        <v>1.637600854378937</v>
       </c>
       <c r="K733">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="L733">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="M733">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="N733">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="O733">
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>146</v>
+        <v>368</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38145,31 +38148,31 @@
         <v>0</v>
       </c>
       <c r="B734" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C734">
-        <v>-1.265907451690905</v>
+        <v>-1.320637609966599</v>
       </c>
       <c r="D734" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E734">
-        <v>-0.8346271953772231</v>
+        <v>-0.8852932329888805</v>
       </c>
       <c r="F734">
         <v>1</v>
       </c>
       <c r="G734">
-        <v>0.0119659074516909</v>
+        <v>0.0120206376099666</v>
       </c>
       <c r="H734">
-        <v>0.01141462719537722</v>
+        <v>0.01146529323298888</v>
       </c>
       <c r="I734">
-        <v>0.4312802563136815</v>
+        <v>0.4353443769777181</v>
       </c>
       <c r="J734">
-        <v>1.637600854378937</v>
+        <v>1.651147923259059</v>
       </c>
       <c r="K734">
         <v>4.04</v>
@@ -38187,7 +38190,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>367</v>
+        <v>148</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38195,49 +38198,49 @@
         <v>1</v>
       </c>
       <c r="B735" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C735">
-        <v>-0.6434276225666915</v>
+        <v>-0.643890153083591</v>
       </c>
       <c r="D735" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E735">
-        <v>-0.7051715713039552</v>
+        <v>-0.5862179645947325</v>
       </c>
       <c r="F735">
         <v>-1</v>
       </c>
       <c r="G735">
-        <v>0.01324342762256669</v>
+        <v>0.01342389015308359</v>
       </c>
       <c r="H735">
-        <v>0.01298517157130395</v>
+        <v>0.01298621796459473</v>
       </c>
       <c r="I735">
-        <v>0.06174394873726374</v>
+        <v>-0.05767218848885847</v>
       </c>
       <c r="J735">
-        <v>1.637600854378937</v>
+        <v>1.651147923259059</v>
       </c>
       <c r="K735">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="L735">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="M735">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="N735">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="O735">
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>367</v>
+        <v>148</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38245,99 +38248,99 @@
         <v>0</v>
       </c>
       <c r="B736" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C736">
-        <v>-1.320637609966599</v>
+        <v>-0.7067782428850009</v>
       </c>
       <c r="D736" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E736">
-        <v>-0.8852932329888805</v>
+        <v>-0.6468916850369375</v>
       </c>
       <c r="F736">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G736">
-        <v>0.0120206376099666</v>
+        <v>0.013486778242885</v>
       </c>
       <c r="H736">
-        <v>0.01146529323298888</v>
+        <v>0.01304689168503694</v>
       </c>
       <c r="I736">
-        <v>0.4353443769777181</v>
+        <v>-0.0598865578480634</v>
       </c>
       <c r="J736">
-        <v>1.651147923259059</v>
+        <v>1.665910385653756</v>
       </c>
       <c r="K736">
-        <v>4.04</v>
+        <v>4.26</v>
       </c>
       <c r="L736">
-        <v>5.35</v>
+        <v>6.39</v>
       </c>
       <c r="M736">
-        <v>3.74</v>
+        <v>4.11</v>
       </c>
       <c r="N736">
-        <v>5.29</v>
+        <v>6.2</v>
       </c>
       <c r="O736">
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>149</v>
+        <v>369</v>
       </c>
     </row>
     <row r="737" spans="1:16">
       <c r="A737" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B737" t="s">
         <v>153</v>
       </c>
       <c r="C737">
-        <v>-0.6934245907813628</v>
+        <v>-0.7562123131768042</v>
       </c>
       <c r="D737" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E737">
-        <v>-0.7617983192228657</v>
+        <v>-0.6945851190508607</v>
       </c>
       <c r="F737">
         <v>-1</v>
       </c>
       <c r="G737">
-        <v>0.01347342459078136</v>
+        <v>0.0135362123131768</v>
       </c>
       <c r="H737">
-        <v>0.01304179831922287</v>
+        <v>0.01309458511905086</v>
       </c>
       <c r="I737">
-        <v>0.06837372844150291</v>
+        <v>-0.06162719412594342</v>
       </c>
       <c r="J737">
-        <v>1.651147923259059</v>
+        <v>1.677514627506292</v>
       </c>
       <c r="K737">
-        <v>4.29</v>
+        <v>4.26</v>
       </c>
       <c r="L737">
         <v>6.39</v>
       </c>
       <c r="M737">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="N737">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="O737">
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>149</v>
+        <v>370</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38348,96 +38351,96 @@
         <v>154</v>
       </c>
       <c r="C738">
-        <v>-0.7067782428850009</v>
+        <v>-1.264109784157877</v>
       </c>
       <c r="D738" t="s">
         <v>260</v>
       </c>
       <c r="E738">
-        <v>-0.8235054120327003</v>
+        <v>-1.022211643015786</v>
       </c>
       <c r="F738">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G738">
-        <v>0.013486778242885</v>
+        <v>0.01166410978415788</v>
       </c>
       <c r="H738">
-        <v>0.0131035054120327</v>
+        <v>0.01160221164301579</v>
       </c>
       <c r="I738">
-        <v>0.1167271691476994</v>
+        <v>0.2418981411420909</v>
       </c>
       <c r="J738">
-        <v>1.665910385653756</v>
+        <v>1.687757123801012</v>
       </c>
       <c r="K738">
-        <v>4.26</v>
+        <v>3.83</v>
       </c>
       <c r="L738">
-        <v>6.39</v>
+        <v>5.2</v>
       </c>
       <c r="M738">
-        <v>4.18</v>
+        <v>3.74</v>
       </c>
       <c r="N738">
-        <v>6.14</v>
+        <v>5.29</v>
       </c>
       <c r="O738">
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="739" spans="1:16">
       <c r="A739" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B739" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C739">
-        <v>-0.7562123131768042</v>
+        <v>-0.755416351394099</v>
       </c>
       <c r="D739" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E739">
-        <v>-0.8720111429763007</v>
+        <v>-0.7366817788221605</v>
       </c>
       <c r="F739">
         <v>-1</v>
       </c>
       <c r="G739">
-        <v>0.0135362123131768</v>
+        <v>0.0129154163513941</v>
       </c>
       <c r="H739">
-        <v>0.0131520111429763</v>
+        <v>0.01313668177882216</v>
       </c>
       <c r="I739">
-        <v>0.1157988297994965</v>
+        <v>-0.01873457257193856</v>
       </c>
       <c r="J739">
-        <v>1.677514627506292</v>
+        <v>1.687757123801012</v>
       </c>
       <c r="K739">
-        <v>4.26</v>
+        <v>4.05</v>
       </c>
       <c r="L739">
-        <v>6.39</v>
+        <v>6.08</v>
       </c>
       <c r="M739">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="N739">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="O739">
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38448,228 +38451,228 @@
         <v>154</v>
       </c>
       <c r="C740">
-        <v>-0.7998453473923126</v>
+        <v>-1.309770404983137</v>
       </c>
       <c r="D740" t="s">
-        <v>260</v>
+        <v>147</v>
       </c>
       <c r="E740">
-        <v>-0.9148247774882314</v>
+        <v>-0.9197061963660698</v>
       </c>
       <c r="F740">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G740">
-        <v>0.01357984534739231</v>
+        <v>0.01170977040498314</v>
       </c>
       <c r="H740">
-        <v>0.01319482477748823</v>
+        <v>0.01277970619636607</v>
       </c>
       <c r="I740">
-        <v>0.1149794300959188</v>
+        <v>0.3900642086170674</v>
       </c>
       <c r="J740">
-        <v>1.687757123801012</v>
+        <v>1.699678956914657</v>
       </c>
       <c r="K740">
-        <v>4.26</v>
+        <v>3.83</v>
       </c>
       <c r="L740">
-        <v>6.39</v>
+        <v>5.2</v>
       </c>
       <c r="M740">
-        <v>4.18</v>
+        <v>4.03</v>
       </c>
       <c r="N740">
-        <v>6.14</v>
+        <v>5.93</v>
       </c>
       <c r="O740">
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="741" spans="1:16">
       <c r="A741" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B741" t="s">
         <v>155</v>
       </c>
       <c r="C741">
-        <v>-1.309770404983137</v>
+        <v>-0.803699775504362</v>
       </c>
       <c r="D741" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E741">
-        <v>-1.066799298860818</v>
+        <v>-0.7856805129192423</v>
       </c>
       <c r="F741">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G741">
-        <v>0.01170977040498314</v>
+        <v>0.01296369977550436</v>
       </c>
       <c r="H741">
-        <v>0.01164679929886082</v>
+        <v>0.01318568051291924</v>
       </c>
       <c r="I741">
-        <v>0.2429711061223188</v>
+        <v>-0.01801926258511966</v>
       </c>
       <c r="J741">
         <v>1.699678956914657</v>
       </c>
       <c r="K741">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="L741">
-        <v>5.2</v>
+        <v>6.08</v>
       </c>
       <c r="M741">
-        <v>3.74</v>
+        <v>4.11</v>
       </c>
       <c r="N741">
-        <v>5.29</v>
+        <v>6.2</v>
       </c>
       <c r="O741">
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="742" spans="1:16">
       <c r="A742" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B742" t="s">
         <v>154</v>
       </c>
       <c r="C742">
-        <v>-0.8506323564564404</v>
+        <v>-1.314126956385915</v>
       </c>
       <c r="D742" t="s">
-        <v>260</v>
+        <v>147</v>
       </c>
       <c r="E742">
-        <v>-0.9646580399032674</v>
+        <v>-0.9242902439256504</v>
       </c>
       <c r="F742">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G742">
-        <v>0.01363063235645644</v>
+        <v>0.01171412695638591</v>
       </c>
       <c r="H742">
-        <v>0.01324465803990327</v>
+        <v>0.01278429024392565</v>
       </c>
       <c r="I742">
-        <v>0.114025683446827</v>
+        <v>0.3898367124602649</v>
       </c>
       <c r="J742">
-        <v>1.699678956914657</v>
+        <v>1.700816437698672</v>
       </c>
       <c r="K742">
-        <v>4.26</v>
+        <v>3.83</v>
       </c>
       <c r="L742">
-        <v>6.39</v>
+        <v>5.2</v>
       </c>
       <c r="M742">
-        <v>4.18</v>
+        <v>4.03</v>
       </c>
       <c r="N742">
-        <v>6.14</v>
+        <v>5.93</v>
       </c>
       <c r="O742">
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>371</v>
+        <v>151</v>
       </c>
     </row>
     <row r="743" spans="1:16">
       <c r="A743" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B743" t="s">
         <v>155</v>
       </c>
       <c r="C743">
-        <v>-1.314126956385915</v>
+        <v>-0.8083065726796228</v>
       </c>
       <c r="D743" t="s">
-        <v>147</v>
+        <v>261</v>
       </c>
       <c r="E743">
-        <v>-0.9242902439256504</v>
+        <v>-1.051461695842371</v>
       </c>
       <c r="F743">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G743">
-        <v>0.01171412695638591</v>
+        <v>0.01296830657267962</v>
       </c>
       <c r="H743">
-        <v>0.01278429024392565</v>
+        <v>0.01337146169584237</v>
       </c>
       <c r="I743">
-        <v>0.3898367124602649</v>
+        <v>0.2431551231627482</v>
       </c>
       <c r="J743">
         <v>1.700816437698672</v>
       </c>
       <c r="K743">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="L743">
-        <v>5.2</v>
+        <v>6.08</v>
       </c>
       <c r="M743">
-        <v>4.03</v>
+        <v>4.24</v>
       </c>
       <c r="N743">
-        <v>5.93</v>
+        <v>6.16</v>
       </c>
       <c r="O743">
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="744" spans="1:16">
       <c r="A744" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B744" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C744">
-        <v>-0.8083065726796228</v>
+        <v>-0.8138622965451079</v>
       </c>
       <c r="D744" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E744">
-        <v>-0.9694127095804497</v>
+        <v>-1.05727805860525</v>
       </c>
       <c r="F744">
         <v>-1</v>
       </c>
       <c r="G744">
-        <v>0.01296830657267962</v>
+        <v>0.01297386229654511</v>
       </c>
       <c r="H744">
-        <v>0.01324941270958045</v>
+        <v>0.01337727805860525</v>
       </c>
       <c r="I744">
-        <v>0.1611061369008269</v>
+        <v>0.2434157620601418</v>
       </c>
       <c r="J744">
-        <v>1.700816437698672</v>
+        <v>1.702188221369163</v>
       </c>
       <c r="K744">
         <v>4.05</v>
@@ -38678,16 +38681,16 @@
         <v>6.08</v>
       </c>
       <c r="M744">
-        <v>4.18</v>
+        <v>4.24</v>
       </c>
       <c r="N744">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
       <c r="O744">
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>150</v>
+        <v>373</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38698,146 +38701,96 @@
         <v>156</v>
       </c>
       <c r="C745">
-        <v>-0.8138622965451079</v>
+        <v>-1.176376407370608</v>
       </c>
       <c r="D745" t="s">
-        <v>260</v>
+        <v>147</v>
       </c>
       <c r="E745">
-        <v>-0.9751467653230996</v>
+        <v>-0.9078545017321833</v>
       </c>
       <c r="F745">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G745">
-        <v>0.01297386229654511</v>
+        <v>0.01195637640737061</v>
       </c>
       <c r="H745">
-        <v>0.0132551467653231</v>
+        <v>0.01276785450173218</v>
       </c>
       <c r="I745">
-        <v>0.1612844687779917</v>
+        <v>0.2685219056384245</v>
       </c>
       <c r="J745">
-        <v>1.702188221369163</v>
+        <v>1.696738089759847</v>
       </c>
       <c r="K745">
-        <v>4.05</v>
+        <v>3.87</v>
       </c>
       <c r="L745">
-        <v>6.08</v>
+        <v>5.39</v>
       </c>
       <c r="M745">
-        <v>4.18</v>
+        <v>4.03</v>
       </c>
       <c r="N745">
-        <v>6.14</v>
+        <v>5.93</v>
       </c>
       <c r="O745">
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>372</v>
+        <v>258</v>
       </c>
     </row>
     <row r="746" spans="1:16">
       <c r="A746" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B746" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C746">
-        <v>-1.176376407370608</v>
+        <v>-0.7917892635273791</v>
       </c>
       <c r="D746" t="s">
-        <v>147</v>
+        <v>261</v>
       </c>
       <c r="E746">
-        <v>-0.9078545017321833</v>
+        <v>-1.034169500581751</v>
       </c>
       <c r="F746">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G746">
-        <v>0.01195637640737061</v>
+        <v>0.01295178926352738</v>
       </c>
       <c r="H746">
-        <v>0.01276785450173218</v>
+        <v>0.01335416950058175</v>
       </c>
       <c r="I746">
-        <v>0.2685219056384245</v>
+        <v>0.2423802370543715</v>
       </c>
       <c r="J746">
         <v>1.696738089759847</v>
       </c>
       <c r="K746">
-        <v>3.87</v>
+        <v>4.05</v>
       </c>
       <c r="L746">
-        <v>5.39</v>
+        <v>6.08</v>
       </c>
       <c r="M746">
-        <v>4.03</v>
+        <v>4.24</v>
       </c>
       <c r="N746">
-        <v>5.93</v>
+        <v>6.16</v>
       </c>
       <c r="O746">
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="747" spans="1:16">
-      <c r="A747" s="1">
-        <v>1</v>
-      </c>
-      <c r="B747" t="s">
-        <v>156</v>
-      </c>
-      <c r="C747">
-        <v>-0.7917892635273791</v>
-      </c>
-      <c r="D747" t="s">
-        <v>260</v>
-      </c>
-      <c r="E747">
-        <v>-0.952365215196159</v>
-      </c>
-      <c r="F747">
-        <v>-1</v>
-      </c>
-      <c r="G747">
-        <v>0.01295178926352738</v>
-      </c>
-      <c r="H747">
-        <v>0.01323236521519616</v>
-      </c>
-      <c r="I747">
-        <v>0.1605759516687799</v>
-      </c>
-      <c r="J747">
-        <v>1.696738089759847</v>
-      </c>
-      <c r="K747">
-        <v>4.05</v>
-      </c>
-      <c r="L747">
-        <v>6.08</v>
-      </c>
-      <c r="M747">
-        <v>4.18</v>
-      </c>
-      <c r="N747">
-        <v>6.14</v>
-      </c>
-      <c r="O747">
-        <v>1</v>
-      </c>
-      <c r="P747" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
